--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,52 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <color rgb="00FF0000"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <color rgb="00008000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0FFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFDAB9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B0C4DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFE0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0090EE90"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF7F50"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,10 +94,40 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F237"/>
+  <dimension ref="A1:F230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,6608 +530,6412 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>WR1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Ja'Marr Chase</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>WR2</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Puka Nacua</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>RB1</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Bijan Robinson</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>ATL (11)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>RB2</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Jahmyr Gibbs</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>WR3</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>WR4</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Amon-Ra St. Brown</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>WR5</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>CeeDee Lamb</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>DAL (14)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>RB3</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Christian McCaffrey</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>WR6</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Justin Jefferson</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>RB4</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Jonathan Taylor</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>IND (13)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>WR7</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Drake London</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>ATL (11)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>WR8</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Nico Collins</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>WR9</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>A.J. Brown</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>NE (11)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>RB5</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Ashton Jeanty</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>WR10</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>George Pickens</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>DAL (14)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>TE1</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Trey McBride</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>RB6</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>De'Von Achane</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>RB7</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>James Cook</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>WR11</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Chris Olave</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>RB8</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Chase Brown</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>TE2</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Brock Bowers</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>WR12</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Rashee Rice</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>QB1</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Josh Allen</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>RB9</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Omarion Hampton</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>WR13</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>DeVonta Smith</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>RB10</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Saquon Barkley</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>WR14</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Tetairoa McMillan</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>CAR (5)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>WR15</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Garrett Wilson</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>RB11</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Kenneth Walker</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>WR16</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Zay Flowers</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>WR17</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="6" t="n">
         <v>32</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Tee Higgins</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>QB2</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Lamar Jackson</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>QB3</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" s="8" t="n">
         <v>71</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Drake Maye</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>NE (11)</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>WR18</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Ladd McConkey</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>RB12</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Jeremiyah Love</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>WR19</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Malik Nabers</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>TE3</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Colston Loveland</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>CHI (10)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>WR20</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Jaylen Waddle</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>RB13</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="3" t="n">
         <v>39</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Derrick Henry</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>WR21</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Emeka Egbuka</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>RB14</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Breece Hall</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>RB15</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Kyren Williams</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>WR22</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Terry McLaurin</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>QB4</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" s="8" t="n">
         <v>64</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Joe Burrow</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>RB16</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Josh Jacobs</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>WR23</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" s="8" t="n">
         <v>59</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Luther Burden</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>CHI (10)</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>RB17</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" s="3" t="n">
         <v>47</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Javonte Williams</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>DAL (14)</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>RB18</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" s="3" t="n">
         <v>48</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Travis Etienne</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>WR24</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" s="6" t="n">
         <v>52</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Davante Adams</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>WR26</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" s="6" t="n">
         <v>43</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Jameson Williams</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>TE4</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" s="6" t="n">
         <v>63</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Tyler Warren</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>IND (13)</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>WR27</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" s="6" t="n">
         <v>51</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Mike Evans</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>RB19</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Cam Skattebo</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>QB5</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Jayden Daniels</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>WR28</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Christian Watson</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>RB20</t>
         </is>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Bucky Irving</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>QB6</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58" s="8" t="n">
         <v>79</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Jalen Hurts</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>WR29</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="B59" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Rome Odunze</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>CHI (10)</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>RB21</t>
         </is>
       </c>
-      <c r="B60" t="n">
+      <c r="B60" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>TreVeyon Henderson</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>NE (11)</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>RB22</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="B61" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Quinshon Judkins</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>RB23</t>
         </is>
       </c>
-      <c r="B62" t="n">
+      <c r="B62" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>D'Andre Swift</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>CHI (10)</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>WR30</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="B63" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Carnell Tate</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>RB24</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="B64" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>David Montgomery</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>QB7</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="B65" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Caleb Williams</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>CHI (10)</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>WR31</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="B66" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Marvin Harrison</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>QB8</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="B67" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67" s="6" t="n">
         <v>72</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Justin Herbert</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="9" t="inlineStr">
         <is>
           <t>TE5</t>
         </is>
       </c>
-      <c r="B68" t="n">
+      <c r="B68" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Tucker Kraft</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>RB25</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="B69" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Jaylen Warren</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>RB26</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B70" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Bhayshul Tuten</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="9" t="inlineStr">
         <is>
           <t>TE6</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71" s="6" t="n">
         <v>80</v>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>Harold Fannin</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>WR32</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72" s="6" t="n">
         <v>67</v>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>Alec Pierce</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>IND (13)</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>WR33</t>
         </is>
       </c>
-      <c r="B73" t="n">
+      <c r="B73" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>DK Metcalf</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>WR34</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="B74" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Courtland Sutton</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>RB27</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="B75" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Jadarian Price</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="10" t="inlineStr">
         <is>
           <t>QB9</t>
         </is>
       </c>
-      <c r="B76" t="n">
+      <c r="B76" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76" s="8" t="n">
         <v>93</v>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Trevor Lawrence</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>WR35</t>
         </is>
       </c>
-      <c r="B77" t="n">
+      <c r="B77" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Brian Thomas</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>TE7</t>
         </is>
       </c>
-      <c r="B78" t="n">
+      <c r="B78" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78" s="6" t="n">
         <v>101</v>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Kyle Pitts</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>ATL (11)</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>QB10</t>
         </is>
       </c>
-      <c r="B79" t="n">
+      <c r="B79" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79" s="8" t="n">
         <v>94</v>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Dak Prescott</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>DAL (14)</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>WR36</t>
         </is>
       </c>
-      <c r="B80" t="n">
+      <c r="B80" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Chris Godwin</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>RB28</t>
         </is>
       </c>
-      <c r="B81" t="n">
+      <c r="B81" s="3" t="n">
         <v>81</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Rhamondre Stevenson</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>NE (11)</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>RB29</t>
         </is>
       </c>
-      <c r="B82" t="n">
+      <c r="B82" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82" s="7" t="n">
         <v>61</v>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>Chuba Hubbard</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>CAR (5)</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>WR37</t>
         </is>
       </c>
-      <c r="B83" t="n">
+      <c r="B83" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83" s="8" t="n">
         <v>113</v>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>Michael Pittman</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>RB30</t>
         </is>
       </c>
-      <c r="B84" t="n">
+      <c r="B84" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>Tony Pollard</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>RB31</t>
         </is>
       </c>
-      <c r="B85" t="n">
+      <c r="B85" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>RJ Harvey</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>WR38</t>
         </is>
       </c>
-      <c r="B86" t="n">
+      <c r="B86" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>Jordyn Tyson</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>WR39</t>
         </is>
       </c>
-      <c r="B87" t="n">
+      <c r="B87" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87" s="8" t="n">
         <v>121</v>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Wan'Dale Robinson</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>TE8</t>
         </is>
       </c>
-      <c r="B88" t="n">
+      <c r="B88" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88" s="11" t="n">
         <v>81</v>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Sam LaPorta</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>RB32</t>
         </is>
       </c>
-      <c r="B89" t="n">
+      <c r="B89" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Rico Dowdle</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>WR40</t>
         </is>
       </c>
-      <c r="B90" t="n">
+      <c r="B90" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90" s="6" t="n">
         <v>77</v>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>Michael Wilson</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>QB11</t>
         </is>
       </c>
-      <c r="B91" t="n">
+      <c r="B91" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Jaxson Dart</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>WR41</t>
         </is>
       </c>
-      <c r="B92" t="n">
+      <c r="B92" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>Parker Washington</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>WR42</t>
         </is>
       </c>
-      <c r="B93" t="n">
+      <c r="B93" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93" s="8" t="n">
         <v>112</v>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>Jakobi Meyers</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>QB12</t>
         </is>
       </c>
-      <c r="B94" t="n">
+      <c r="B94" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>Brock Purdy</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E94" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>WR43</t>
         </is>
       </c>
-      <c r="B95" t="n">
+      <c r="B95" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>Josh Downs</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>IND (13)</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F95" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>WR44</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96" s="6" t="n">
         <v>83</v>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Makai Lemon</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="9" t="inlineStr">
         <is>
           <t>TE9</t>
         </is>
       </c>
-      <c r="B97" t="n">
+      <c r="B97" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97" s="6" t="n">
         <v>124</v>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Travis Kelce</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>RB33</t>
         </is>
       </c>
-      <c r="B98" t="n">
+      <c r="B98" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>Kyle Monangai</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>CHI (10)</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F98" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="10" t="inlineStr">
         <is>
           <t>QB13</t>
         </is>
       </c>
-      <c r="B99" t="n">
+      <c r="B99" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99" s="6" t="n">
         <v>102</v>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>Patrick Mahomes</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>WR45</t>
         </is>
       </c>
-      <c r="B100" t="n">
+      <c r="B100" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100" s="4" t="n">
         <v>111</v>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>Ricky Pearsall</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F100" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="10" t="inlineStr">
         <is>
           <t>QB14</t>
         </is>
       </c>
-      <c r="B101" t="n">
+      <c r="B101" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>Bo Nix</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F101" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="10" t="inlineStr">
         <is>
           <t>QB15</t>
         </is>
       </c>
-      <c r="B102" t="n">
+      <c r="B102" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102" s="6" t="n">
         <v>103</v>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>Matthew Stafford</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>WR46</t>
         </is>
       </c>
-      <c r="B103" t="n">
+      <c r="B103" s="3" t="n">
         <v>104</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103" s="4" t="n">
         <v>114</v>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>Quentin Johnston</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="9" t="inlineStr">
         <is>
           <t>TE10</t>
         </is>
       </c>
-      <c r="B104" t="n">
+      <c r="B104" s="3" t="n">
         <v>105</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104" s="6" t="n">
         <v>123</v>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>Jake Ferguson</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>DAL (14)</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F104" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>WR47</t>
         </is>
       </c>
-      <c r="B105" t="n">
+      <c r="B105" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105" s="7" t="n">
         <v>74</v>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>Jordan Addison</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F105" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="5" t="inlineStr">
         <is>
           <t>RB35</t>
         </is>
       </c>
-      <c r="B106" t="n">
+      <c r="B106" s="3" t="n">
         <v>107</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106" s="6" t="n">
         <v>117</v>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>J.K. Dobbins</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="5" t="inlineStr">
         <is>
           <t>RB36</t>
         </is>
       </c>
-      <c r="B107" t="n">
+      <c r="B107" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="C107" t="n">
+      <c r="C107" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>Aaron Jones</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F107" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="10" t="inlineStr">
         <is>
           <t>QB16</t>
         </is>
       </c>
-      <c r="B108" t="n">
+      <c r="B108" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="C108" t="n">
+      <c r="C108" s="6" t="n">
         <v>104</v>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>Jared Goff</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F108" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
+      <c r="A109" s="5" t="inlineStr">
         <is>
           <t>RB37</t>
         </is>
       </c>
-      <c r="B109" t="n">
+      <c r="B109" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="C109" t="n">
+      <c r="C109" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>Blake Corum</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E109" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F109" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A110" s="9" t="inlineStr">
         <is>
           <t>TE11</t>
         </is>
       </c>
-      <c r="B110" t="n">
+      <c r="B110" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="C110" t="n">
+      <c r="C110" s="6" t="n">
         <v>126</v>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>George Kittle</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F110" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>WR48</t>
         </is>
       </c>
-      <c r="B111" t="n">
+      <c r="B111" s="3" t="n">
         <v>112</v>
       </c>
-      <c r="C111" t="n">
+      <c r="C111" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>Jayden Reed</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
+      <c r="A112" s="5" t="inlineStr">
         <is>
           <t>RB38</t>
         </is>
       </c>
-      <c r="B112" t="n">
+      <c r="B112" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="C112" t="n">
+      <c r="C112" s="11" t="n">
         <v>108</v>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>Rachaad White</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A113" s="10" t="inlineStr">
         <is>
           <t>QB17</t>
         </is>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" s="3" t="n">
         <v>114</v>
       </c>
-      <c r="C113" t="n">
+      <c r="C113" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>Kyler Murray</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F113" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="9" t="inlineStr">
         <is>
           <t>TE12</t>
         </is>
       </c>
-      <c r="B114" t="n">
+      <c r="B114" s="3" t="n">
         <v>115</v>
       </c>
-      <c r="C114" t="n">
+      <c r="C114" s="6" t="n">
         <v>125</v>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>Dalton Kincaid</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F114" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>WR49</t>
         </is>
       </c>
-      <c r="B115" t="n">
+      <c r="B115" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="C115" t="n">
+      <c r="C115" s="4" t="n">
         <v>128</v>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>Khalil Shakir</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E115" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F115" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
+      <c r="A116" s="10" t="inlineStr">
         <is>
           <t>QB18</t>
         </is>
       </c>
-      <c r="B116" t="n">
+      <c r="B116" s="3" t="n">
         <v>117</v>
       </c>
-      <c r="C116" t="n">
+      <c r="C116" s="6" t="n">
         <v>105</v>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
         <is>
           <t>Jordan Love</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
+      <c r="A117" s="10" t="inlineStr">
         <is>
           <t>QB19</t>
         </is>
       </c>
-      <c r="B117" t="n">
+      <c r="B117" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="C117" t="n">
+      <c r="C117" s="6" t="n">
         <v>129</v>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>Baker Mayfield</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="9" t="inlineStr">
         <is>
           <t>TE13</t>
         </is>
       </c>
-      <c r="B118" t="n">
+      <c r="B118" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="C118" t="n">
+      <c r="C118" s="6" t="n">
         <v>134</v>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>Isaiah Likely</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>WR50</t>
         </is>
       </c>
-      <c r="B119" t="n">
+      <c r="B119" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="C119" t="n">
+      <c r="C119" s="4" t="n">
         <v>127</v>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>Jayden Higgins</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>WR51</t>
         </is>
       </c>
-      <c r="B120" t="n">
+      <c r="B120" s="3" t="n">
         <v>121</v>
       </c>
-      <c r="C120" t="n">
+      <c r="C120" s="6" t="n">
         <v>97</v>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>Xavier Worthy</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A121" s="10" t="inlineStr">
         <is>
           <t>QB20</t>
         </is>
       </c>
-      <c r="B121" t="n">
+      <c r="B121" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="C121" t="n">
+      <c r="C121" s="6" t="n">
         <v>131</v>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>Tyler Shough</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A122" s="9" t="inlineStr">
         <is>
           <t>TE14</t>
         </is>
       </c>
-      <c r="B122" t="n">
+      <c r="B122" s="3" t="n">
         <v>123</v>
       </c>
-      <c r="C122" t="n">
+      <c r="C122" s="6" t="n">
         <v>132</v>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>Dallas Goedert</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F122" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="5" t="inlineStr">
         <is>
           <t>RB39</t>
         </is>
       </c>
-      <c r="B123" t="n">
+      <c r="B123" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="C123" t="n">
+      <c r="C123" s="7" t="n">
         <v>109</v>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
+      <c r="A124" s="5" t="inlineStr">
         <is>
           <t>RB40</t>
         </is>
       </c>
-      <c r="B124" t="n">
+      <c r="B124" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="C124" t="n">
+      <c r="C124" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>Jordan Mason</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>WR52</t>
         </is>
       </c>
-      <c r="B125" t="n">
+      <c r="B125" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="C125" t="n">
+      <c r="C125" s="6" t="n">
         <v>122</v>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>KC Concepcion</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>WR53</t>
         </is>
       </c>
-      <c r="B126" t="n">
+      <c r="B126" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="C126" t="n">
+      <c r="C126" s="6" t="n">
         <v>115</v>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D126" s="3" t="inlineStr">
         <is>
           <t>Romeo Doubs</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>NE (11)</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F126" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="A127" s="5" t="inlineStr">
         <is>
           <t>RB41</t>
         </is>
       </c>
-      <c r="B127" t="n">
+      <c r="B127" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="C127" t="n">
+      <c r="C127" s="11" t="n">
         <v>120</v>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>Jonathon Brooks</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>CAR (5)</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>RB42</t>
         </is>
       </c>
-      <c r="B128" t="n">
+      <c r="B128" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="C128" t="n">
+      <c r="C128" s="6" t="n">
         <v>140</v>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>Tyrone Tracy</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E128" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F128" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>TE15</t>
         </is>
       </c>
-      <c r="B129" t="n">
+      <c r="B129" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="C129" t="n">
+      <c r="C129" s="6" t="n">
         <v>135</v>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>Mark Andrews</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E129" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F129" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
+      <c r="A130" s="10" t="inlineStr">
         <is>
           <t>QB21</t>
         </is>
       </c>
-      <c r="B130" t="n">
+      <c r="B130" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="C130" t="n">
+      <c r="C130" s="11" t="n">
         <v>106</v>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
         <is>
           <t>Malik Willis</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F130" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>WR54</t>
         </is>
       </c>
-      <c r="B131" t="n">
+      <c r="B131" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="C131" t="n">
+      <c r="C131" s="6" t="n">
         <v>116</v>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>Jalen Coker</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>CAR (5)</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F131" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>WR55</t>
         </is>
       </c>
-      <c r="B132" t="n">
+      <c r="B132" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="C132" t="n">
+      <c r="C132" s="11" t="n">
         <v>98</v>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>Matthew Golden</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E132" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F132" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="A133" s="10" t="inlineStr">
         <is>
           <t>QB22</t>
         </is>
       </c>
-      <c r="B133" t="n">
+      <c r="B133" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="C133" t="n">
+      <c r="C133" s="6" t="n">
         <v>139</v>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>C.J. Stroud</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>RB43</t>
         </is>
       </c>
-      <c r="B134" t="n">
+      <c r="B134" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="C134" t="n">
+      <c r="C134" s="6" t="n">
         <v>141</v>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>Woody Marks</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
+      <c r="A135" s="5" t="inlineStr">
         <is>
           <t>RB44</t>
         </is>
       </c>
-      <c r="B135" t="n">
+      <c r="B135" s="3" t="n">
         <v>136</v>
       </c>
-      <c r="C135" t="n">
+      <c r="C135" s="6" t="n">
         <v>152</v>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
         <is>
           <t>Tyler Allgeier</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>RB45</t>
         </is>
       </c>
-      <c r="B136" t="n">
+      <c r="B136" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="C136" t="n">
+      <c r="C136" s="6" t="n">
         <v>191</v>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>Zach Charbonnet</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F136" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
+      <c r="A137" s="10" t="inlineStr">
         <is>
           <t>QB23</t>
         </is>
       </c>
-      <c r="B137" t="n">
+      <c r="B137" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="C137" t="n">
+      <c r="C137" s="6" t="n">
         <v>138</v>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t>Sam Darnold</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E137" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F137" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
+      <c r="A138" s="5" t="inlineStr">
         <is>
           <t>RB46</t>
         </is>
       </c>
-      <c r="B138" t="n">
+      <c r="B138" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C138" t="n">
+      <c r="C138" s="7" t="n">
         <v>110</v>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>Chris Rodriguez</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E138" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
+      <c r="A139" s="5" t="inlineStr">
         <is>
           <t>RB47</t>
         </is>
       </c>
-      <c r="B139" t="n">
+      <c r="B139" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="C139" t="n">
+      <c r="C139" s="6" t="n">
         <v>169</v>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>Tyjae Spears</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E139" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
+      <c r="A140" s="9" t="inlineStr">
         <is>
           <t>TE16</t>
         </is>
       </c>
-      <c r="B140" t="n">
+      <c r="B140" s="3" t="n">
         <v>141</v>
       </c>
-      <c r="C140" t="n">
+      <c r="C140" s="6" t="n">
         <v>158</v>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>Juwan Johnson</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E140" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F140" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
+      <c r="A141" s="5" t="inlineStr">
         <is>
           <t>RB48</t>
         </is>
       </c>
-      <c r="B141" t="n">
+      <c r="B141" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="C141" t="n">
+      <c r="C141" s="6" t="n">
         <v>142</v>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>Dylan Sampson</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F141" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>RB49</t>
         </is>
       </c>
-      <c r="B142" t="n">
+      <c r="B142" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="C142" t="n">
+      <c r="C142" s="6" t="n">
         <v>154</v>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>Isiah Pacheco</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E142" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F142" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="A143" s="5" t="inlineStr">
         <is>
           <t>RB50</t>
         </is>
       </c>
-      <c r="B143" t="n">
+      <c r="B143" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="C143" t="n">
+      <c r="C143" s="6" t="n">
         <v>188</v>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>Alvin Kamara</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F143" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
+      <c r="A144" s="10" t="inlineStr">
         <is>
           <t>QB24</t>
         </is>
       </c>
-      <c r="B144" t="n">
+      <c r="B144" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="C144" t="n">
+      <c r="C144" s="6" t="n">
         <v>149</v>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D144" s="3" t="inlineStr">
         <is>
           <t>Cam Ward</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="E144" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="F144" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>WR56</t>
         </is>
       </c>
-      <c r="B145" t="n">
+      <c r="B145" s="3" t="n">
         <v>146</v>
       </c>
-      <c r="C145" t="n">
+      <c r="C145" s="6" t="n">
         <v>144</v>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>Rashid Shaheed</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="A146" s="9" t="inlineStr">
         <is>
           <t>TE17</t>
         </is>
       </c>
-      <c r="B146" t="n">
+      <c r="B146" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="C146" t="n">
+      <c r="C146" s="6" t="n">
         <v>151</v>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t>Brenton Strange</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>WR57</t>
         </is>
       </c>
-      <c r="B147" t="n">
+      <c r="B147" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="C147" t="n">
+      <c r="C147" s="8" t="n">
         <v>176</v>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D147" s="3" t="inlineStr">
         <is>
           <t>Omar Cooper</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="E147" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="F147" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>WR58</t>
         </is>
       </c>
-      <c r="B148" t="n">
+      <c r="B148" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="C148" t="n">
+      <c r="C148" s="8" t="n">
         <v>180</v>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D148" s="3" t="inlineStr">
         <is>
           <t>Denzel Boston</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="E148" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="F148" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>WR59</t>
         </is>
       </c>
-      <c r="B149" t="n">
+      <c r="B149" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="C149" t="n">
+      <c r="C149" s="6" t="n">
         <v>155</v>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D149" s="3" t="inlineStr">
         <is>
           <t>Jerry Jeudy</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E149" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F149" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A150" s="10" t="inlineStr">
         <is>
           <t>QB25</t>
         </is>
       </c>
-      <c r="B150" t="n">
+      <c r="B150" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="C150" t="n">
+      <c r="C150" s="6" t="n">
         <v>162</v>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D150" s="3" t="inlineStr">
         <is>
           <t>Daniel Jones</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E150" s="3" t="inlineStr">
         <is>
           <t>IND (13)</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F150" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
+      <c r="A151" s="10" t="inlineStr">
         <is>
           <t>QB26</t>
         </is>
       </c>
-      <c r="B151" t="n">
+      <c r="B151" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="C151" t="n">
+      <c r="C151" s="6" t="n">
         <v>130</v>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D151" s="3" t="inlineStr">
         <is>
           <t>Bryce Young</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E151" s="3" t="inlineStr">
         <is>
           <t>CAR (5)</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="F151" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>WR60</t>
         </is>
       </c>
-      <c r="B152" t="n">
+      <c r="B152" s="3" t="n">
         <v>153</v>
       </c>
-      <c r="C152" t="n">
+      <c r="C152" s="6" t="n">
         <v>147</v>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="D152" s="3" t="inlineStr">
         <is>
           <t>Jauan Jennings</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="E152" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
+      <c r="F152" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
+      <c r="A153" s="9" t="inlineStr">
         <is>
           <t>TE18</t>
         </is>
       </c>
-      <c r="B153" t="n">
+      <c r="B153" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="C153" t="n">
+      <c r="C153" s="6" t="n">
         <v>163</v>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D153" s="3" t="inlineStr">
         <is>
           <t>Chig Okonkwo</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E153" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="F153" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
+      <c r="A154" s="9" t="inlineStr">
         <is>
           <t>TE19</t>
         </is>
       </c>
-      <c r="B154" t="n">
+      <c r="B154" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="C154" t="n">
+      <c r="C154" s="7" t="n">
         <v>133</v>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="D154" s="3" t="inlineStr">
         <is>
           <t>Oronde Gadsden</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E154" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="F154" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="A155" s="9" t="inlineStr">
         <is>
           <t>TE20</t>
         </is>
       </c>
-      <c r="B155" t="n">
+      <c r="B155" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="C155" t="n">
+      <c r="C155" s="6" t="n">
         <v>161</v>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D155" s="3" t="inlineStr">
         <is>
           <t>Hunter Henry</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="E155" s="3" t="inlineStr">
         <is>
           <t>NE (11)</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="F155" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="5" t="inlineStr">
         <is>
           <t>RB51</t>
         </is>
       </c>
-      <c r="B156" t="n">
+      <c r="B156" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="C156" t="n">
+      <c r="C156" s="6" t="n">
         <v>168</v>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="D156" s="3" t="inlineStr">
         <is>
           <t>Jonah Coleman</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="E156" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
+      <c r="F156" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
+      <c r="A157" s="5" t="inlineStr">
         <is>
           <t>RB52</t>
         </is>
       </c>
-      <c r="B157" t="n">
+      <c r="B157" s="3" t="n">
         <v>159</v>
       </c>
-      <c r="C157" t="n">
+      <c r="C157" s="6" t="n">
         <v>181</v>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D157" s="3" t="inlineStr">
         <is>
           <t>Keaton Mitchell</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="E157" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
+      <c r="F157" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>WR61</t>
         </is>
       </c>
-      <c r="B158" t="n">
+      <c r="B158" s="3" t="n">
         <v>160</v>
       </c>
-      <c r="C158" t="n">
+      <c r="C158" s="4" t="n">
         <v>199</v>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D158" s="3" t="inlineStr">
         <is>
           <t>Adonai Mitchell</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="E158" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F158" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>WR62</t>
         </is>
       </c>
-      <c r="B159" t="n">
+      <c r="B159" s="3" t="n">
         <v>161</v>
       </c>
-      <c r="C159" t="n">
+      <c r="C159" s="6" t="n">
         <v>143</v>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>Jalen McMillan</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="E159" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="F159" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>WR63</t>
         </is>
       </c>
-      <c r="B160" t="n">
+      <c r="B160" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="C160" t="n">
+      <c r="C160" s="6" t="n">
         <v>178</v>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D160" s="3" t="inlineStr">
         <is>
           <t>Tre Tucker</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="E160" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
+      <c r="F160" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
+      <c r="A161" s="5" t="inlineStr">
         <is>
           <t>RB53</t>
         </is>
       </c>
-      <c r="B161" t="n">
+      <c r="B161" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="C161" t="n">
+      <c r="C161" s="6" t="n">
         <v>165</v>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D161" s="3" t="inlineStr">
         <is>
           <t>Brian Robinson</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="E161" s="3" t="inlineStr">
         <is>
           <t>ATL (11)</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="F161" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
+      <c r="A162" s="5" t="inlineStr">
         <is>
           <t>RB54</t>
         </is>
       </c>
-      <c r="B162" t="n">
+      <c r="B162" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="C162" t="n">
+      <c r="C162" s="6" t="n">
         <v>166</v>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="D162" s="3" t="inlineStr">
         <is>
           <t>Tank Bigsby</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="E162" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="F162" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
+      <c r="A163" s="9" t="inlineStr">
         <is>
           <t>TE21</t>
         </is>
       </c>
-      <c r="B163" t="n">
+      <c r="B163" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="C163" t="n">
+      <c r="C163" s="6" t="n">
         <v>160</v>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t>Dalton Schultz</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E163" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
+      <c r="F163" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>WR64</t>
         </is>
       </c>
-      <c r="B164" t="n">
+      <c r="B164" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="C164" t="n">
+      <c r="C164" s="11" t="n">
         <v>136</v>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D164" s="3" t="inlineStr">
         <is>
           <t>Travis Hunter</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="E164" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
+      <c r="F164" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
+      <c r="A165" s="5" t="inlineStr">
         <is>
           <t>RB55</t>
         </is>
       </c>
-      <c r="B165" t="n">
+      <c r="B165" s="3" t="n">
         <v>169</v>
       </c>
-      <c r="C165" t="n">
+      <c r="C165" s="6" t="n">
         <v>167</v>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D165" s="3" t="inlineStr">
         <is>
           <t>Braelon Allen</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="E165" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
+      <c r="F165" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>WR65</t>
         </is>
       </c>
-      <c r="B166" t="n">
+      <c r="B166" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="C166" t="n">
+      <c r="C166" s="6" t="n">
         <v>187</v>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>Tre' Harris</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="E166" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="F166" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
+      <c r="A167" s="9" t="inlineStr">
         <is>
           <t>TE22</t>
         </is>
       </c>
-      <c r="B167" t="n">
+      <c r="B167" s="3" t="n">
         <v>173</v>
       </c>
-      <c r="C167" t="n">
+      <c r="C167" s="6" t="n">
         <v>159</v>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t>T.J. Hockenson</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="E167" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="F167" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>WR66</t>
         </is>
       </c>
-      <c r="B168" t="n">
+      <c r="B168" s="3" t="n">
         <v>174</v>
       </c>
-      <c r="C168" t="n">
+      <c r="C168" s="4" t="n">
         <v>228</v>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D168" s="3" t="inlineStr">
         <is>
           <t>Troy Franklin</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
+      <c r="E168" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
+      <c r="F168" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>WR67</t>
         </is>
       </c>
-      <c r="B169" t="n">
+      <c r="B169" s="3" t="n">
         <v>175</v>
       </c>
-      <c r="C169" t="n">
+      <c r="C169" s="6" t="n">
         <v>186</v>
       </c>
-      <c r="D169" t="inlineStr">
+      <c r="D169" s="3" t="inlineStr">
         <is>
           <t>Kayshon Boutte</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
+      <c r="E169" s="3" t="inlineStr">
         <is>
           <t>NE (11)</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
+      <c r="F169" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>WR68</t>
         </is>
       </c>
-      <c r="B170" t="n">
+      <c r="B170" s="3" t="n">
         <v>176</v>
       </c>
-      <c r="C170" t="n">
+      <c r="C170" s="6" t="n">
         <v>177</v>
       </c>
-      <c r="D170" t="inlineStr">
+      <c r="D170" s="3" t="inlineStr">
         <is>
           <t>Ryan Flournoy</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
+      <c r="E170" s="3" t="inlineStr">
         <is>
           <t>DAL (14)</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
+      <c r="F170" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>WR69</t>
         </is>
       </c>
-      <c r="B171" t="n">
+      <c r="B171" s="3" t="n">
         <v>177</v>
       </c>
-      <c r="C171" t="n">
+      <c r="C171" s="11" t="n">
         <v>146</v>
       </c>
-      <c r="D171" t="inlineStr">
+      <c r="D171" s="3" t="inlineStr">
         <is>
           <t>Stefon Diggs</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
+      <c r="E171" s="3" t="inlineStr">
         <is>
           <t>FA ()</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F171" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
+      <c r="A172" s="5" t="inlineStr">
         <is>
           <t>RB56</t>
         </is>
       </c>
-      <c r="B172" t="n">
+      <c r="B172" s="3" t="n">
         <v>178</v>
       </c>
-      <c r="C172" t="n">
+      <c r="C172" s="4" t="n">
         <v>219</v>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D172" s="3" t="inlineStr">
         <is>
           <t>James Conner</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
+      <c r="E172" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="F172" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
+      <c r="A173" s="10" t="inlineStr">
         <is>
           <t>QB27</t>
         </is>
       </c>
-      <c r="B173" t="n">
+      <c r="B173" s="3" t="n">
         <v>179</v>
       </c>
-      <c r="C173" t="n">
+      <c r="C173" s="6" t="n">
         <v>172</v>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t>Jacoby Brissett</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="E173" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
+      <c r="F173" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="A174" s="5" t="inlineStr">
         <is>
           <t>RB57</t>
         </is>
       </c>
-      <c r="B174" t="n">
+      <c r="B174" s="3" t="n">
         <v>186</v>
       </c>
-      <c r="C174" t="n">
+      <c r="C174" s="6" t="n">
         <v>190</v>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="D174" s="3" t="inlineStr">
         <is>
           <t>Emanuel Wilson</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="E174" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
+      <c r="F174" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>WR71</t>
         </is>
       </c>
-      <c r="B175" t="n">
+      <c r="B175" s="3" t="n">
         <v>187</v>
       </c>
-      <c r="C175" t="n">
+      <c r="C175" s="11" t="n">
         <v>156</v>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="D175" s="3" t="inlineStr">
         <is>
           <t>Calvin Ridley</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
+      <c r="E175" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="F175" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>WR72</t>
         </is>
       </c>
-      <c r="B176" t="n">
+      <c r="B176" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="C176" t="n">
+      <c r="C176" s="6" t="n">
         <v>185</v>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="D176" s="3" t="inlineStr">
         <is>
           <t>Isaac TeSlaa</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
+      <c r="E176" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
+      <c r="F176" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="A177" s="9" t="inlineStr">
         <is>
           <t>TE23</t>
         </is>
       </c>
-      <c r="B177" t="n">
+      <c r="B177" s="3" t="n">
         <v>191</v>
       </c>
-      <c r="C177" t="n">
+      <c r="C177" s="11" t="n">
         <v>157</v>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D177" s="3" t="inlineStr">
         <is>
           <t>Kenyon Sadiq</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="E177" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
+      <c r="F177" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="A178" s="5" t="inlineStr">
         <is>
           <t>RB58</t>
         </is>
       </c>
-      <c r="B178" t="n">
+      <c r="B178" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="C178" t="n">
+      <c r="C178" s="6" t="n">
         <v>189</v>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D178" s="3" t="inlineStr">
         <is>
           <t>Emmett Johnson</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="E178" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
+      <c r="F178" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
+      <c r="A179" s="5" t="inlineStr">
         <is>
           <t>RB59</t>
         </is>
       </c>
-      <c r="B179" t="n">
+      <c r="B179" s="3" t="n">
         <v>194</v>
       </c>
-      <c r="C179" t="n">
+      <c r="C179" s="6" t="n">
         <v>210</v>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D179" s="3" t="inlineStr">
         <is>
           <t>Kimani Vidal</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="E179" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
+      <c r="F179" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
+      <c r="A180" s="5" t="inlineStr">
         <is>
           <t>RB60</t>
         </is>
       </c>
-      <c r="B180" t="n">
+      <c r="B180" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="C180" t="n">
+      <c r="C180" s="6" t="n">
         <v>209</v>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D180" s="3" t="inlineStr">
         <is>
           <t>Ray Davis</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E180" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="F180" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
+      <c r="A181" s="9" t="inlineStr">
         <is>
           <t>TE24</t>
         </is>
       </c>
-      <c r="B181" t="n">
+      <c r="B181" s="3" t="n">
         <v>196</v>
       </c>
-      <c r="C181" t="n">
+      <c r="C181" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D181" s="3" t="inlineStr">
         <is>
           <t>AJ Barner</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="E181" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
+      <c r="F181" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>WR73</t>
         </is>
       </c>
-      <c r="B182" t="n">
+      <c r="B182" s="3" t="n">
         <v>197</v>
       </c>
-      <c r="C182" t="n">
+      <c r="C182" s="6" t="n">
         <v>223</v>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D182" s="3" t="inlineStr">
         <is>
           <t>Darnell Mooney</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="E182" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
+      <c r="F182" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>WR74</t>
         </is>
       </c>
-      <c r="B183" t="n">
+      <c r="B183" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="C183" t="n">
+      <c r="C183" s="7" t="n">
         <v>137</v>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D183" s="3" t="inlineStr">
         <is>
           <t>Jalen Nailor</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="E183" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
+      <c r="F183" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>WR75</t>
         </is>
       </c>
-      <c r="B184" t="n">
+      <c r="B184" s="3" t="n">
         <v>201</v>
       </c>
-      <c r="C184" t="n">
+      <c r="C184" s="11" t="n">
         <v>148</v>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D184" s="3" t="inlineStr">
         <is>
           <t>Deebo Samuel</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="E184" s="3" t="inlineStr">
         <is>
           <t>FA ()</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="F184" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>WR76</t>
         </is>
       </c>
-      <c r="B185" t="n">
+      <c r="B185" s="3" t="n">
         <v>202</v>
       </c>
-      <c r="C185" t="n">
+      <c r="C185" s="6" t="n">
         <v>204</v>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D185" s="3" t="inlineStr">
         <is>
           <t>Malik Washington</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
+      <c r="E185" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
+      <c r="F185" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
+      <c r="A186" s="5" t="inlineStr">
         <is>
           <t>RB61</t>
         </is>
       </c>
-      <c r="B186" t="n">
+      <c r="B186" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="C186" t="n">
+      <c r="C186" s="11" t="n">
         <v>153</v>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D186" s="3" t="inlineStr">
         <is>
           <t>Mike Washington</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="E186" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
+      <c r="F186" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>WR77</t>
         </is>
       </c>
-      <c r="B187" t="n">
+      <c r="B187" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C187" t="n">
+      <c r="C187" s="6" t="n">
         <v>226</v>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D187" s="3" t="inlineStr">
         <is>
           <t>Pat Bryant</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="E187" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
+      <c r="F187" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>WR78</t>
         </is>
       </c>
-      <c r="B188" t="n">
+      <c r="B188" s="3" t="n">
         <v>206</v>
       </c>
-      <c r="C188" t="n">
+      <c r="C188" s="11" t="n">
         <v>174</v>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="D188" s="3" t="inlineStr">
         <is>
           <t>Antonio Williams</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
+      <c r="E188" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
+      <c r="F188" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
+      <c r="A189" s="9" t="inlineStr">
         <is>
           <t>TE25</t>
         </is>
       </c>
-      <c r="B189" t="n">
+      <c r="B189" s="3" t="n">
         <v>207</v>
       </c>
-      <c r="C189" t="n">
+      <c r="C189" s="6" t="n">
         <v>197</v>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="D189" s="3" t="inlineStr">
         <is>
           <t>Gunnar Helm</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
+      <c r="E189" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
+      <c r="F189" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
+      <c r="A190" s="2" t="inlineStr">
         <is>
           <t>WR79</t>
         </is>
       </c>
-      <c r="B190" t="n">
+      <c r="B190" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="C190" t="n">
+      <c r="C190" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="D190" t="inlineStr">
+      <c r="D190" s="3" t="inlineStr">
         <is>
           <t>Dontayvion Wicks</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
+      <c r="E190" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
+      <c r="F190" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
+      <c r="A191" s="5" t="inlineStr">
         <is>
           <t>RB62</t>
         </is>
       </c>
-      <c r="B191" t="n">
+      <c r="B191" s="3" t="n">
         <v>212</v>
       </c>
-      <c r="C191" t="n">
+      <c r="C191" s="6" t="n">
         <v>193</v>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D191" s="3" t="inlineStr">
         <is>
           <t>Sean Tucker</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
+      <c r="E191" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr">
+      <c r="F191" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
+      <c r="A192" s="5" t="inlineStr">
         <is>
           <t>RB63</t>
         </is>
       </c>
-      <c r="B192" t="n">
+      <c r="B192" s="3" t="n">
         <v>213</v>
       </c>
-      <c r="C192" t="n">
+      <c r="C192" s="6" t="n">
         <v>212</v>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D192" s="3" t="inlineStr">
         <is>
           <t>Nicholas Singleton</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
+      <c r="E192" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
+      <c r="F192" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>WR80</t>
         </is>
       </c>
-      <c r="B193" t="n">
+      <c r="B193" s="3" t="n">
         <v>217</v>
       </c>
-      <c r="C193" t="n">
+      <c r="C193" s="6" t="n">
         <v>224</v>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D193" s="3" t="inlineStr">
         <is>
           <t>Tank Dell</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
+      <c r="E193" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
+      <c r="F193" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="10" t="inlineStr">
         <is>
           <t>QB28</t>
         </is>
       </c>
-      <c r="B194" t="n">
+      <c r="B194" s="3" t="n">
         <v>219</v>
       </c>
-      <c r="C194" t="n">
+      <c r="C194" s="11" t="n">
         <v>173</v>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D194" s="3" t="inlineStr">
         <is>
           <t>Aaron Rodgers</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="E194" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
+      <c r="F194" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>WR81</t>
         </is>
       </c>
-      <c r="B195" t="n">
+      <c r="B195" s="3" t="n">
         <v>221</v>
       </c>
-      <c r="C195" t="n">
+      <c r="C195" s="6" t="n">
         <v>198</v>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D195" s="3" t="inlineStr">
         <is>
           <t>Cooper Kupp</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="E195" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
+      <c r="F195" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
+      <c r="A196" s="5" t="inlineStr">
         <is>
           <t>RB64</t>
         </is>
       </c>
-      <c r="B196" t="n">
+      <c r="B196" s="3" t="n">
         <v>222</v>
       </c>
-      <c r="C196" t="n">
+      <c r="C196" s="11" t="n">
         <v>182</v>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D196" s="3" t="inlineStr">
         <is>
           <t>Kaytron Allen</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
+      <c r="E196" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
+      <c r="F196" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
+      <c r="A197" s="10" t="inlineStr">
         <is>
           <t>QB29</t>
         </is>
       </c>
-      <c r="B197" t="n">
+      <c r="B197" s="3" t="n">
         <v>223</v>
       </c>
-      <c r="C197" t="n">
+      <c r="C197" s="11" t="n">
         <v>170</v>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="D197" s="3" t="inlineStr">
         <is>
           <t>Geno Smith</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
+      <c r="E197" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
+      <c r="F197" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
+      <c r="A198" s="2" t="inlineStr">
         <is>
           <t>WR83</t>
         </is>
       </c>
-      <c r="B198" t="n">
+      <c r="B198" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="C198" t="n">
+      <c r="C198" s="11" t="n">
         <v>175</v>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D198" s="3" t="inlineStr">
         <is>
           <t>De'Zhaun Stribling</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="E198" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
+      <c r="F198" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>WR84</t>
         </is>
       </c>
-      <c r="B199" t="n">
+      <c r="B199" s="3" t="n">
         <v>228</v>
       </c>
-      <c r="C199" t="n">
+      <c r="C199" s="6" t="n">
         <v>203</v>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="D199" s="3" t="inlineStr">
         <is>
           <t>Germie Bernard</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="E199" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
+      <c r="F199" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>WR85</t>
         </is>
       </c>
-      <c r="B200" t="n">
+      <c r="B200" s="3" t="n">
         <v>230</v>
       </c>
-      <c r="C200" t="n">
+      <c r="C200" s="6" t="n">
         <v>232</v>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="D200" s="3" t="inlineStr">
         <is>
           <t>Rashod Bateman</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
+      <c r="E200" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
+      <c r="F200" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>WR86</t>
         </is>
       </c>
-      <c r="B201" t="n">
+      <c r="B201" s="3" t="n">
         <v>232</v>
       </c>
-      <c r="C201" t="n">
+      <c r="C201" s="11" t="n">
         <v>145</v>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D201" s="3" t="inlineStr">
         <is>
           <t>Brandon Aiyuk</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="E201" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr">
+      <c r="F201" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
+      <c r="A202" s="10" t="inlineStr">
         <is>
           <t>QB30</t>
         </is>
       </c>
-      <c r="B202" t="n">
+      <c r="B202" s="3" t="n">
         <v>234</v>
       </c>
-      <c r="C202" t="n">
+      <c r="C202" s="11" t="n">
         <v>171</v>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D202" s="3" t="inlineStr">
         <is>
           <t>Fernando Mendoza</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="E202" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="F202" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
+      <c r="A203" s="9" t="inlineStr">
         <is>
           <t>TE26</t>
         </is>
       </c>
-      <c r="B203" t="n">
+      <c r="B203" s="3" t="n">
         <v>235</v>
       </c>
-      <c r="C203" t="n">
+      <c r="C203" s="6" t="n">
         <v>217</v>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D203" s="3" t="inlineStr">
         <is>
           <t>Pat Freiermuth</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="E203" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr">
+      <c r="F203" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>WR87</t>
         </is>
       </c>
-      <c r="B204" t="n">
+      <c r="B204" s="3" t="n">
         <v>237</v>
       </c>
-      <c r="C204" t="n">
+      <c r="C204" s="6" t="n">
         <v>231</v>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D204" s="3" t="inlineStr">
         <is>
           <t>Zachariah Branch</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E204" s="3" t="inlineStr">
         <is>
           <t>ATL (11)</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="F204" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
+      <c r="A205" s="9" t="inlineStr">
         <is>
           <t>TE27</t>
         </is>
       </c>
-      <c r="B205" t="n">
+      <c r="B205" s="3" t="n">
         <v>238</v>
       </c>
-      <c r="C205" t="n">
+      <c r="C205" s="11" t="n">
         <v>164</v>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D205" s="3" t="inlineStr">
         <is>
           <t>Cade Otton</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="E205" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
+      <c r="F205" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
+      <c r="A206" s="9" t="inlineStr">
         <is>
           <t>TE28</t>
         </is>
       </c>
-      <c r="B206" t="n">
+      <c r="B206" s="3" t="n">
         <v>239</v>
       </c>
-      <c r="C206" t="n">
+      <c r="C206" s="11" t="n">
         <v>194</v>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D206" s="3" t="inlineStr">
         <is>
           <t>David Njoku</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="E206" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
+      <c r="F206" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
+      <c r="A207" s="5" t="inlineStr">
         <is>
           <t>RB66</t>
         </is>
       </c>
-      <c r="B207" t="n">
+      <c r="B207" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="C207" t="n">
+      <c r="C207" s="11" t="n">
         <v>184</v>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D207" s="3" t="inlineStr">
         <is>
           <t>Justice Hill</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="E207" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
+      <c r="F207" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>WR88</t>
         </is>
       </c>
-      <c r="B208" t="n">
+      <c r="B208" s="3" t="n">
         <v>241</v>
       </c>
-      <c r="C208" t="n">
+      <c r="C208" s="11" t="n">
         <v>179</v>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D208" s="3" t="inlineStr">
         <is>
           <t>Jack Bech</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="E208" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
+      <c r="F208" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
+      <c r="A209" s="9" t="inlineStr">
         <is>
           <t>TE29</t>
         </is>
       </c>
-      <c r="B209" t="n">
+      <c r="B209" s="3" t="n">
         <v>243</v>
       </c>
-      <c r="C209" t="n">
+      <c r="C209" s="11" t="n">
         <v>195</v>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D209" s="3" t="inlineStr">
         <is>
           <t>Terrance Ferguson</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="E209" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="F209" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>WR91</t>
         </is>
       </c>
-      <c r="B210" t="n">
+      <c r="B210" s="3" t="n">
         <v>249</v>
       </c>
-      <c r="C210" t="n">
+      <c r="C210" s="6" t="n">
         <v>233</v>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D210" s="3" t="inlineStr">
         <is>
           <t>Keon Coleman</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E210" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
+      <c r="F210" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>WR92</t>
         </is>
       </c>
-      <c r="B211" t="n">
+      <c r="B211" s="3" t="n">
         <v>251</v>
       </c>
-      <c r="C211" t="n">
+      <c r="C211" s="6" t="n">
         <v>201</v>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D211" s="3" t="inlineStr">
         <is>
           <t>Chris Bell</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="E211" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F211" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>WR93</t>
         </is>
       </c>
-      <c r="B212" t="n">
+      <c r="B212" s="3" t="n">
         <v>252</v>
       </c>
-      <c r="C212" t="n">
+      <c r="C212" s="6" t="n">
         <v>225</v>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="D212" s="3" t="inlineStr">
         <is>
           <t>Elijah Sarratt</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
+      <c r="E212" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
+      <c r="F212" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>WR94</t>
         </is>
       </c>
-      <c r="B213" t="n">
+      <c r="B213" s="3" t="n">
         <v>255</v>
       </c>
-      <c r="C213" t="n">
+      <c r="C213" s="6" t="n">
         <v>222</v>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="D213" s="3" t="inlineStr">
         <is>
           <t>Christian Kirk</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="E213" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
+      <c r="F213" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
+      <c r="A214" s="5" t="inlineStr">
         <is>
           <t>RB70</t>
         </is>
       </c>
-      <c r="B214" t="n">
+      <c r="B214" s="3" t="n">
         <v>257</v>
       </c>
-      <c r="C214" t="n">
+      <c r="C214" s="6" t="n">
         <v>220</v>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D214" s="3" t="inlineStr">
         <is>
           <t>DJ Giddens</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
+      <c r="E214" s="3" t="inlineStr">
         <is>
           <t>IND (13)</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
+      <c r="F214" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>WR96</t>
         </is>
       </c>
-      <c r="B215" t="n">
+      <c r="B215" s="3" t="n">
         <v>258</v>
       </c>
-      <c r="C215" t="n">
+      <c r="C215" s="6" t="n">
         <v>221</v>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="D215" s="3" t="inlineStr">
         <is>
           <t>Tyreek Hill</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
+      <c r="E215" s="3" t="inlineStr">
         <is>
           <t>FA ()</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
+      <c r="F215" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
+      <c r="A216" s="9" t="inlineStr">
         <is>
           <t>TE32</t>
         </is>
       </c>
-      <c r="B216" t="n">
+      <c r="B216" s="3" t="n">
         <v>259</v>
       </c>
-      <c r="C216" t="n">
+      <c r="C216" s="11" t="n">
         <v>196</v>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="D216" s="3" t="inlineStr">
         <is>
           <t>Eli Stowers</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
+      <c r="E216" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
+      <c r="F216" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>WR97</t>
         </is>
       </c>
-      <c r="B217" t="n">
+      <c r="B217" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="C217" t="n">
+      <c r="C217" s="6" t="n">
         <v>227</v>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D217" s="3" t="inlineStr">
         <is>
           <t>Tory Horton</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="E217" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
+      <c r="F217" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>WR99</t>
         </is>
       </c>
-      <c r="B218" t="n">
+      <c r="B218" s="3" t="n">
         <v>263</v>
       </c>
-      <c r="C218" t="n">
+      <c r="C218" s="6" t="n">
         <v>202</v>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D218" s="3" t="inlineStr">
         <is>
           <t>Chris Brazzell</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="E218" s="3" t="inlineStr">
         <is>
           <t>CAR (5)</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
+      <c r="F218" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
+      <c r="A219" s="5" t="inlineStr">
         <is>
           <t>RB72</t>
         </is>
       </c>
-      <c r="B219" t="n">
+      <c r="B219" s="3" t="n">
         <v>265</v>
       </c>
-      <c r="C219" t="n">
+      <c r="C219" s="11" t="n">
         <v>192</v>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D219" s="3" t="inlineStr">
         <is>
           <t>Chris Brooks</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="E219" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
+      <c r="F219" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
+      <c r="A220" s="10" t="inlineStr">
         <is>
           <t>QB31</t>
         </is>
       </c>
-      <c r="B220" t="n">
+      <c r="B220" s="3" t="n">
         <v>266</v>
       </c>
-      <c r="C220" t="n">
+      <c r="C220" s="6" t="n">
         <v>205</v>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D220" s="3" t="inlineStr">
         <is>
           <t>Tua Tagovailoa</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E220" s="3" t="inlineStr">
         <is>
           <t>ATL (11)</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
+      <c r="F220" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>WR100</t>
         </is>
       </c>
-      <c r="B221" t="n">
+      <c r="B221" s="3" t="n">
         <v>267</v>
       </c>
-      <c r="C221" t="n">
+      <c r="C221" s="6" t="n">
         <v>238</v>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D221" s="3" t="inlineStr">
         <is>
           <t>Darius Slayton</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E221" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
+      <c r="F221" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
+      <c r="A222" s="10" t="inlineStr">
         <is>
           <t>QB32</t>
         </is>
       </c>
-      <c r="B222" t="n">
+      <c r="B222" s="3" t="n">
         <v>276</v>
       </c>
-      <c r="C222" t="n">
+      <c r="C222" s="6" t="n">
         <v>206</v>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D222" s="3" t="inlineStr">
         <is>
           <t>Michael Penix</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E222" s="3" t="inlineStr">
         <is>
           <t>ATL (11)</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
+      <c r="F222" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
+      <c r="A223" s="5" t="inlineStr">
         <is>
           <t>RB79</t>
         </is>
       </c>
-      <c r="B223" t="n">
+      <c r="B223" s="3" t="n">
         <v>277</v>
       </c>
-      <c r="C223" t="n">
+      <c r="C223" s="6" t="n">
         <v>214</v>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D223" s="3" t="inlineStr">
         <is>
           <t>Jordan James</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E223" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
+      <c r="F223" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>WR103</t>
         </is>
       </c>
-      <c r="B224" t="n">
+      <c r="B224" s="3" t="n">
         <v>285</v>
       </c>
-      <c r="C224" t="n">
+      <c r="C224" s="6" t="n">
         <v>230</v>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D224" s="3" t="inlineStr">
         <is>
           <t>Devaughn Vele</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="E224" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
+      <c r="F224" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
+      <c r="A225" s="10" t="inlineStr">
         <is>
           <t>QB33</t>
         </is>
       </c>
-      <c r="B225" t="n">
+      <c r="B225" s="3" t="n">
         <v>289</v>
       </c>
-      <c r="C225" t="n">
+      <c r="C225" s="6" t="n">
         <v>218</v>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D225" s="3" t="inlineStr">
         <is>
           <t>Shedeur Sanders</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E225" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
+      <c r="F225" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>WR105</t>
         </is>
       </c>
-      <c r="B226" t="n">
+      <c r="B226" s="3" t="n">
         <v>290</v>
       </c>
-      <c r="C226" t="n">
+      <c r="C226" s="6" t="n">
         <v>234</v>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D226" s="3" t="inlineStr">
         <is>
           <t>Keenan Allen</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E226" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
+      <c r="F226" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
+      <c r="A227" s="5" t="inlineStr">
         <is>
           <t>RB85</t>
         </is>
       </c>
-      <c r="B227" t="n">
+      <c r="B227" s="3" t="n">
         <v>293</v>
       </c>
-      <c r="C227" t="n">
+      <c r="C227" s="11" t="n">
         <v>183</v>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D227" s="3" t="inlineStr">
         <is>
           <t>Kaelon Black</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="E227" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="F227" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>WR106</t>
         </is>
       </c>
-      <c r="B228" t="n">
+      <c r="B228" s="3" t="n">
         <v>294</v>
       </c>
-      <c r="C228" t="n">
+      <c r="C228" s="6" t="n">
         <v>229</v>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D228" s="3" t="inlineStr">
         <is>
           <t>Hollywood Brown</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E228" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
+      <c r="F228" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
+      <c r="A229" s="10" t="inlineStr">
         <is>
           <t>QB34</t>
         </is>
       </c>
-      <c r="B229" t="n">
+      <c r="B229" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="C229" t="n">
+      <c r="C229" s="6" t="n">
         <v>208</v>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D229" s="3" t="inlineStr">
         <is>
           <t>Deshaun Watson</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E229" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
+      <c r="F229" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
+      <c r="A230" s="9" t="inlineStr">
         <is>
           <t>TE37</t>
         </is>
       </c>
-      <c r="B230" t="n">
+      <c r="B230" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="C230" t="n">
+      <c r="C230" s="6" t="n">
         <v>216</v>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="D230" s="3" t="inlineStr">
         <is>
           <t>Mike Gesicki</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="E230" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>QB35</t>
-        </is>
-      </c>
-      <c r="B231" t="n">
-        <v>302</v>
-      </c>
-      <c r="C231" t="n">
-        <v>207</v>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>Kirk Cousins</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>LV (13)</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>RB90</t>
-        </is>
-      </c>
-      <c r="B232" t="n">
-        <v>304</v>
-      </c>
-      <c r="C232" t="n">
-        <v>211</v>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>Najee Harris</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>LAC (7)</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>RB91</t>
-        </is>
-      </c>
-      <c r="B233" t="n">
-        <v>305</v>
-      </c>
-      <c r="C233" t="n">
-        <v>213</v>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>Adam Randall</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>BAL (13)</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>WR108</t>
-        </is>
-      </c>
-      <c r="B234" t="n">
-        <v>306</v>
-      </c>
-      <c r="C234" t="n">
-        <v>236</v>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>BAL (13)</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>WR111</t>
-        </is>
-      </c>
-      <c r="B235" t="n">
-        <v>316</v>
-      </c>
-      <c r="C235" t="n">
-        <v>235</v>
-      </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>Andrei Iosivas</t>
-        </is>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>CIN (6)</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>WR120</t>
-        </is>
-      </c>
-      <c r="B236" t="n">
-        <v>335</v>
-      </c>
-      <c r="C236" t="n">
-        <v>237</v>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>Jalen Tolbert</t>
-        </is>
-      </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>MIA (6)</t>
-        </is>
-      </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>TE45</t>
-        </is>
-      </c>
-      <c r="B237" t="n">
-        <v>344</v>
-      </c>
-      <c r="C237" t="n">
-        <v>215</v>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>Dawson Knox</t>
-        </is>
-      </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>BUF (7)</t>
-        </is>
-      </c>
-      <c r="F237" t="inlineStr">
+      <c r="F230" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -117,10 +117,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F230"/>
+  <dimension ref="A1:F250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,7 +651,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
@@ -846,8 +846,8 @@
       <c r="B13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="8" t="n">
-        <v>29</v>
+      <c r="C13" s="4" t="n">
+        <v>20</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
@@ -874,8 +874,8 @@
       <c r="B14" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C14" s="8" t="n">
-        <v>37</v>
+      <c r="C14" s="4" t="n">
+        <v>21</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>TE1</t>
         </is>
@@ -958,8 +958,8 @@
       <c r="B17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>28</v>
+      <c r="C17" s="9" t="n">
+        <v>29</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
@@ -1042,8 +1042,8 @@
       <c r="B20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="8" t="n">
-        <v>35</v>
+      <c r="C20" s="4" t="n">
+        <v>30</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
@@ -1070,8 +1070,8 @@
       <c r="B21" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="C21" s="6" t="n">
-        <v>20</v>
+      <c r="C21" s="7" t="n">
+        <v>17</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>TE2</t>
         </is>
@@ -1098,8 +1098,8 @@
       <c r="B22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C22" s="7" t="n">
-        <v>15</v>
+      <c r="C22" s="6" t="n">
+        <v>18</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
@@ -1126,8 +1126,8 @@
       <c r="B23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="6" t="n">
-        <v>24</v>
+      <c r="C23" s="4" t="n">
+        <v>31</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -1182,8 +1182,8 @@
       <c r="B25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C25" s="7" t="n">
-        <v>17</v>
+      <c r="C25" s="6" t="n">
+        <v>22</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
@@ -1210,8 +1210,8 @@
       <c r="B26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C26" s="4" t="n">
-        <v>36</v>
+      <c r="C26" s="6" t="n">
+        <v>25</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -1406,8 +1406,8 @@
       <c r="B33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="C33" s="8" t="n">
-        <v>47</v>
+      <c r="C33" s="9" t="n">
+        <v>45</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
@@ -1434,8 +1434,8 @@
       <c r="B34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="C34" s="8" t="n">
-        <v>71</v>
+      <c r="C34" s="9" t="n">
+        <v>63</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
@@ -1518,8 +1518,8 @@
       <c r="B37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="C37" s="7" t="n">
-        <v>23</v>
+      <c r="C37" s="4" t="n">
+        <v>43</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>TE3</t>
         </is>
@@ -1547,7 +1547,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
@@ -1630,8 +1630,8 @@
       <c r="B41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="C41" s="4" t="n">
-        <v>50</v>
+      <c r="C41" s="6" t="n">
+        <v>38</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -1714,8 +1714,8 @@
       <c r="B44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="C44" s="4" t="n">
-        <v>54</v>
+      <c r="C44" s="6" t="n">
+        <v>46</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -1742,8 +1742,8 @@
       <c r="B45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="C45" s="8" t="n">
-        <v>64</v>
+      <c r="C45" s="4" t="n">
+        <v>55</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -1798,8 +1798,8 @@
       <c r="B47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="C47" s="8" t="n">
-        <v>59</v>
+      <c r="C47" s="4" t="n">
+        <v>53</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
@@ -1904,303 +1904,303 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>WR25</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>DJ Moore</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>BUF (7)</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
           <t>WR26</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n">
+      <c r="B52" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="C51" s="6" t="n">
-        <v>43</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="C52" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Jameson Williams</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>TE4</t>
         </is>
       </c>
-      <c r="B52" s="3" t="n">
+      <c r="B53" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="C52" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="C53" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Tyler Warren</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>IND (13)</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>WR27</t>
         </is>
       </c>
-      <c r="B53" s="3" t="n">
+      <c r="B54" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="C53" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="C54" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Mike Evans</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>RB19</t>
         </is>
       </c>
-      <c r="B54" s="3" t="n">
+      <c r="B55" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="C54" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="C55" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Cam Skattebo</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>QB5</t>
         </is>
       </c>
-      <c r="B55" s="3" t="n">
+      <c r="B56" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="C55" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="C56" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Jayden Daniels</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>WR28</t>
         </is>
       </c>
-      <c r="B56" s="3" t="n">
+      <c r="B57" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="C56" s="4" t="n">
+      <c r="C57" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Christian Watson</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>GB (11)</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>RB20</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Christian Watson</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>GB (11)</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>RB20</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>57</v>
-      </c>
-      <c r="C57" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Bucky Irving</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>QB6</t>
         </is>
       </c>
-      <c r="B58" s="3" t="n">
+      <c r="B59" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="C58" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="C59" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Jalen Hurts</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>WR29</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n">
+      <c r="B60" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="C59" s="4" t="n">
-        <v>66</v>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="C60" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Rome Odunze</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>CHI (10)</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>RB21</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="C60" s="7" t="n">
-        <v>45</v>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>TreVeyon Henderson</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>NE (11)</t>
-        </is>
-      </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>RB22</t>
+          <t>RB21</t>
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="C61" s="11" t="n">
-        <v>55</v>
+        <v>60</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>59</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Quinshon Judkins</t>
+          <t>TreVeyon Henderson</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -2212,331 +2212,331 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
+          <t>RB22</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Quinshon Judkins</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
           <t>RB23</t>
         </is>
       </c>
-      <c r="B62" s="3" t="n">
+      <c r="B63" s="3" t="n">
         <v>62</v>
       </c>
-      <c r="C62" s="7" t="n">
-        <v>46</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="C63" s="7" t="n">
+        <v>51</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>D'Andre Swift</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>CHI (10)</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>WR30</t>
         </is>
       </c>
-      <c r="B63" s="3" t="n">
+      <c r="B64" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="C63" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="C64" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Carnell Tate</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>RB24</t>
         </is>
       </c>
-      <c r="B64" s="3" t="n">
+      <c r="B65" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="C64" s="7" t="n">
-        <v>56</v>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="C65" s="7" t="n">
+        <v>57</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>David Montgomery</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>QB7</t>
         </is>
       </c>
-      <c r="B65" s="3" t="n">
+      <c r="B66" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="C65" s="6" t="n">
-        <v>70</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="C66" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Caleb Williams</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>CHI (10)</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>WR31</t>
         </is>
       </c>
-      <c r="B66" s="3" t="n">
+      <c r="B67" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="C66" s="4" t="n">
-        <v>76</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="C67" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Marvin Harrison</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="10" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>QB8</t>
         </is>
       </c>
-      <c r="B67" s="3" t="n">
+      <c r="B68" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="C67" s="6" t="n">
-        <v>72</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="C68" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Justin Herbert</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="9" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>TE5</t>
         </is>
       </c>
-      <c r="B68" s="3" t="n">
+      <c r="B69" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="C68" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="C69" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Tucker Kraft</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>RB25</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="n">
-        <v>69</v>
-      </c>
-      <c r="C69" s="7" t="n">
-        <v>62</v>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Jaylen Warren</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>PIT (9)</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
+          <t>RB25</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Jaylen Warren</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>PIT (9)</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
           <t>RB26</t>
         </is>
       </c>
-      <c r="B70" s="3" t="n">
+      <c r="B71" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C70" s="7" t="n">
-        <v>57</v>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="C71" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>Bhayshul Tuten</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>TE6</t>
         </is>
       </c>
-      <c r="B71" s="3" t="n">
+      <c r="B72" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="C71" s="6" t="n">
-        <v>80</v>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="C72" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>Harold Fannin</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>WR32</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="C72" s="6" t="n">
-        <v>67</v>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Alec Pierce</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>IND (13)</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>WR33</t>
+          <t>WR32</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="C73" s="4" t="n">
-        <v>84</v>
+        <v>72</v>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>72</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>DK Metcalf</t>
+          <t>Alec Pierce</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>PIT (9)</t>
+          <t>IND (13)</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -2548,1759 +2548,1759 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>WR33</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>DK Metcalf</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>PIT (9)</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
           <t>WR34</t>
         </is>
       </c>
-      <c r="B74" s="3" t="n">
+      <c r="B75" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="C74" s="4" t="n">
-        <v>85</v>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="C75" s="9" t="n">
+        <v>98</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Courtland Sutton</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>RB27</t>
         </is>
       </c>
-      <c r="B75" s="3" t="n">
+      <c r="B76" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="C75" s="7" t="n">
-        <v>53</v>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="C76" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Jadarian Price</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="10" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>QB9</t>
         </is>
       </c>
-      <c r="B76" s="3" t="n">
+      <c r="B77" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C76" s="8" t="n">
-        <v>93</v>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="C77" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Trevor Lawrence</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>WR35</t>
         </is>
       </c>
-      <c r="B77" s="3" t="n">
+      <c r="B78" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="C77" s="6" t="n">
-        <v>73</v>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="C78" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Brian Thomas</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>TE7</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n">
+      <c r="B79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C78" s="6" t="n">
+      <c r="C79" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Kyle Pitts</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>ATL (11)</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>QB10</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="C80" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Dak Prescott</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>DAL (14)</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>WR36</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="C81" s="9" t="n">
         <v>101</v>
       </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>Kyle Pitts</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>ATL (11)</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>QB10</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="C79" s="8" t="n">
-        <v>94</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Dak Prescott</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>DAL (14)</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>WR36</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>86</v>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Chris Godwin</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>RB28</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="n">
-        <v>81</v>
-      </c>
-      <c r="C81" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>Rhamondre Stevenson</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>NE (11)</t>
-        </is>
-      </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
+          <t>RB28</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Rhamondre Stevenson</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>NE (11)</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
           <t>RB29</t>
         </is>
       </c>
-      <c r="B82" s="3" t="n">
+      <c r="B83" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="C82" s="7" t="n">
-        <v>61</v>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="C83" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>Chuba Hubbard</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>CAR (5)</t>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>WR37</t>
         </is>
       </c>
-      <c r="B83" s="3" t="n">
+      <c r="B84" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="C83" s="8" t="n">
-        <v>113</v>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="C84" s="9" t="n">
+        <v>109</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>Michael Pittman</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>RB30</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="C84" s="6" t="n">
-        <v>82</v>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>Tony Pollard</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>TEN (9)</t>
-        </is>
-      </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
+          <t>RB30</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Tony Pollard</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>TEN (9)</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
           <t>RB31</t>
         </is>
       </c>
-      <c r="B85" s="3" t="n">
+      <c r="B86" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="C85" s="7" t="n">
-        <v>69</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="C86" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>RJ Harvey</t>
         </is>
       </c>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>WR38</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="n">
-        <v>86</v>
-      </c>
-      <c r="C86" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>Jordyn Tyson</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>NO (8)</t>
-        </is>
-      </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>WR38</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="C87" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Jordyn Tyson</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
           <t>WR39</t>
         </is>
       </c>
-      <c r="B87" s="3" t="n">
+      <c r="B88" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="C87" s="8" t="n">
-        <v>121</v>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="C88" s="9" t="n">
+        <v>149</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Wan'Dale Robinson</t>
         </is>
       </c>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="9" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>TE8</t>
         </is>
       </c>
-      <c r="B88" s="3" t="n">
+      <c r="B89" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="C88" s="11" t="n">
-        <v>81</v>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="C89" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Sam LaPorta</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="5" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>RB32</t>
         </is>
       </c>
-      <c r="B89" s="3" t="n">
+      <c r="B90" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="C89" s="6" t="n">
+      <c r="C90" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Rico Dowdle</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>PIT (9)</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>WR40</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>Rico Dowdle</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>PIT (9)</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>WR40</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="C90" s="6" t="n">
-        <v>77</v>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="C91" s="9" t="n">
+        <v>108</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Michael Wilson</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="10" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>QB11</t>
         </is>
       </c>
-      <c r="B91" s="3" t="n">
+      <c r="B92" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="C91" s="6" t="n">
-        <v>78</v>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="C92" s="9" t="n">
+        <v>112</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>Jaxson Dart</t>
         </is>
       </c>
-      <c r="E91" s="3" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F91" s="3" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>WR41</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="C92" s="6" t="n">
-        <v>95</v>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>Parker Washington</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>JAC (7)</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>WR41</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="C93" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Parker Washington</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>JAC (7)</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
           <t>WR42</t>
         </is>
       </c>
-      <c r="B93" s="3" t="n">
+      <c r="B94" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="C93" s="8" t="n">
-        <v>112</v>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="C94" s="9" t="n">
+        <v>137</v>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>Jakobi Meyers</t>
         </is>
       </c>
-      <c r="E93" s="3" t="inlineStr">
+      <c r="E94" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F93" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="10" t="inlineStr">
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>QB12</t>
         </is>
       </c>
-      <c r="B94" s="3" t="n">
+      <c r="B95" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="C94" s="6" t="n">
-        <v>88</v>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="C95" s="6" t="n">
+        <v>96</v>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>Brock Purdy</t>
         </is>
       </c>
-      <c r="E94" s="3" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr">
+      <c r="F95" s="3" t="inlineStr">
         <is>
           <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>WR43</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="C95" s="6" t="n">
-        <v>99</v>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>Josh Downs</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>IND (13)</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>WR43</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Josh Downs</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>IND (13)</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
           <t>WR44</t>
         </is>
       </c>
-      <c r="B96" s="3" t="n">
+      <c r="B97" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="C96" s="6" t="n">
-        <v>83</v>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="C97" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Makai Lemon</t>
         </is>
       </c>
-      <c r="E96" s="3" t="inlineStr">
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="9" t="inlineStr">
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>TE9</t>
         </is>
       </c>
-      <c r="B97" s="3" t="n">
+      <c r="B98" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="C97" s="6" t="n">
-        <v>124</v>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="C98" s="6" t="n">
+        <v>121</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>Travis Kelce</t>
         </is>
       </c>
-      <c r="E97" s="3" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F97" s="3" t="inlineStr">
+      <c r="F98" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="5" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>RB33</t>
         </is>
       </c>
-      <c r="B98" s="3" t="n">
+      <c r="B99" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="C98" s="11" t="n">
+      <c r="C99" s="11" t="n">
+        <v>93</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Kyle Monangai</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>CHI (10)</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>QB13</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Patrick Mahomes</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>KC (5)</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>WR45</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C101" s="6" t="n">
         <v>91</v>
       </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>Kyle Monangai</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>CHI (10)</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="10" t="inlineStr">
-        <is>
-          <t>QB13</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="C99" s="6" t="n">
-        <v>102</v>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>Patrick Mahomes</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>KC (5)</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>WR45</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="C100" s="4" t="n">
-        <v>111</v>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>Ricky Pearsall</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="10" t="inlineStr">
-        <is>
-          <t>QB14</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="n">
-        <v>101</v>
-      </c>
-      <c r="C101" s="6" t="n">
-        <v>87</v>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>Bo Nix</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>DEN (10)</t>
-        </is>
-      </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
+          <t>QB14</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Bo Nix</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>DEN (10)</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>RB34</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>142</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>TB (10)</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
           <t>QB15</t>
         </is>
       </c>
-      <c r="B102" s="3" t="n">
+      <c r="B104" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="C102" s="6" t="n">
-        <v>103</v>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="C104" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>Matthew Stafford</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
+      <c r="F104" s="3" t="inlineStr">
         <is>
           <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>WR46</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="n">
-        <v>104</v>
-      </c>
-      <c r="C103" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>LAC (7)</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="9" t="inlineStr">
-        <is>
-          <t>TE10</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="C104" s="6" t="n">
-        <v>123</v>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>Jake Ferguson</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>DAL (14)</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>WR46</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="C105" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>LAC (7)</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>TE10</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Jake Ferguson</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>DAL (14)</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
           <t>WR47</t>
         </is>
       </c>
-      <c r="B105" s="3" t="n">
+      <c r="B107" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="C105" s="7" t="n">
-        <v>74</v>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="C107" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>Jordan Addison</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="inlineStr">
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>RB35</t>
         </is>
       </c>
-      <c r="B106" s="3" t="n">
+      <c r="B108" s="3" t="n">
         <v>107</v>
       </c>
-      <c r="C106" s="6" t="n">
-        <v>117</v>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="C108" s="7" t="n">
+        <v>88</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>J.K. Dobbins</t>
         </is>
       </c>
-      <c r="E106" s="3" t="inlineStr">
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="inlineStr">
-        <is>
-          <t>RB36</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="n">
-        <v>108</v>
-      </c>
-      <c r="C107" s="6" t="n">
-        <v>118</v>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>Aaron Jones</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>MIN (6)</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="10" t="inlineStr">
-        <is>
-          <t>QB16</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="n">
-        <v>109</v>
-      </c>
-      <c r="C108" s="6" t="n">
-        <v>104</v>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>Jared Goff</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>DET (6)</t>
-        </is>
-      </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
+          <t>RB36</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="C109" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>Aaron Jones</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>MIN (6)</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>QB16</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="C110" s="6" t="n">
+        <v>114</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Jared Goff</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>DET (6)</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
           <t>RB37</t>
         </is>
       </c>
-      <c r="B109" s="3" t="n">
+      <c r="B111" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="C109" s="7" t="n">
+      <c r="C111" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>LAR (11)</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>TE11</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="C112" s="6" t="n">
+        <v>139</v>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>SF (8)</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>WR48</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="C113" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Jayden Reed</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>GB (11)</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>RB38</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="C114" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>LAR (11)</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="9" t="inlineStr">
-        <is>
-          <t>TE11</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="n">
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>WAS (7)</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>QB17</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="C115" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Kyler Murray</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>MIN (6)</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>TE12</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="C116" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Dalton Kincaid</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>BUF (7)</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>WR49</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="C117" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Khalil Shakir</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>BUF (7)</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>QB18</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="C118" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>Jordan Love</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>GB (11)</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>QB19</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="C119" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Baker Mayfield</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>TB (10)</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>TE13</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="C120" s="6" t="n">
+        <v>119</v>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Isaiah Likely</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>NYG (8)</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>WR50</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="C121" s="4" t="n">
+        <v>131</v>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Jayden Higgins</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>HOU (8)</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>WR51</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="C122" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>Xavier Worthy</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>KC (5)</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>QB20</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="C123" s="9" t="n">
+        <v>164</v>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Tyler Shough</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>TE14</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="C124" s="11" t="n">
+        <v>118</v>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Dallas Goedert</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>PHI (10)</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>RB39</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="C125" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Jacory Croskey-Merritt</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>WAS (7)</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>RB40</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="C126" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="C110" s="6" t="n">
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Jordan Mason</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>MIN (6)</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>WR52</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>SF (8)</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr">
+      <c r="C127" s="6" t="n">
+        <v>122</v>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>KC Concepcion</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>WR53</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="C128" s="4" t="n">
+        <v>136</v>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Romeo Doubs</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>NE (11)</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>RB41</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="C129" s="11" t="n">
+        <v>123</v>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>CAR (5)</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>RB42</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="C130" s="6" t="n">
+        <v>143</v>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Tyrone Tracy</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>NYG (8)</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>TE15</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="C131" s="11" t="n">
+        <v>120</v>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Mark Andrews</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>BAL (13)</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>WR48</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="C111" s="6" t="n">
-        <v>96</v>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>Jayden Reed</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>QB21</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="C132" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Malik Willis</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>WR54</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="C133" s="6" t="n">
+        <v>134</v>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Jalen Coker</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>CAR (5)</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>WR55</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="C134" s="11" t="n">
+        <v>99</v>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="5" t="inlineStr">
-        <is>
-          <t>RB38</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="C112" s="11" t="n">
-        <v>108</v>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>WAS (7)</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="10" t="inlineStr">
-        <is>
-          <t>QB17</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="n">
-        <v>114</v>
-      </c>
-      <c r="C113" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>Kyler Murray</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>MIN (6)</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="inlineStr">
+        <is>
+          <t>QB22</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="C135" s="9" t="n">
+        <v>163</v>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>C.J. Stroud</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>HOU (8)</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
         <is>
           <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="9" t="inlineStr">
-        <is>
-          <t>TE12</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="n">
-        <v>115</v>
-      </c>
-      <c r="C114" s="6" t="n">
-        <v>125</v>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>Dalton Kincaid</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>BUF (7)</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>WR49</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="C115" s="4" t="n">
-        <v>128</v>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>Khalil Shakir</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>BUF (7)</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="10" t="inlineStr">
-        <is>
-          <t>QB18</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="n">
-        <v>117</v>
-      </c>
-      <c r="C116" s="6" t="n">
-        <v>105</v>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>Jordan Love</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>GB (11)</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="10" t="inlineStr">
-        <is>
-          <t>QB19</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="C117" s="6" t="n">
-        <v>129</v>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>Baker Mayfield</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>TB (10)</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
-        <is>
-          <t>TE13</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="C118" s="6" t="n">
-        <v>134</v>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>Isaiah Likely</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>NYG (8)</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>WR50</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="C119" s="4" t="n">
-        <v>127</v>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>Jayden Higgins</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>HOU (8)</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>WR51</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="n">
-        <v>121</v>
-      </c>
-      <c r="C120" s="6" t="n">
-        <v>97</v>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>Xavier Worthy</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>KC (5)</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="10" t="inlineStr">
-        <is>
-          <t>QB20</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="n">
-        <v>122</v>
-      </c>
-      <c r="C121" s="6" t="n">
-        <v>131</v>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>Tyler Shough</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>NO (8)</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="9" t="inlineStr">
-        <is>
-          <t>TE14</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="n">
-        <v>123</v>
-      </c>
-      <c r="C122" s="6" t="n">
-        <v>132</v>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>Dallas Goedert</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>PHI (10)</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="5" t="inlineStr">
-        <is>
-          <t>RB39</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="n">
-        <v>124</v>
-      </c>
-      <c r="C123" s="7" t="n">
-        <v>109</v>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>Jacory Croskey-Merritt</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>WAS (7)</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="inlineStr">
-        <is>
-          <t>RB40</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="C124" s="7" t="n">
-        <v>107</v>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>Jordan Mason</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>MIN (6)</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>WR52</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="C125" s="6" t="n">
-        <v>122</v>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>KC Concepcion</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>CLE (11)</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>WR53</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="C126" s="6" t="n">
-        <v>115</v>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>Romeo Doubs</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>NE (11)</t>
-        </is>
-      </c>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>RB41</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="C127" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>CAR (5)</t>
-        </is>
-      </c>
-      <c r="F127" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr">
-        <is>
-          <t>RB42</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="C128" s="6" t="n">
-        <v>140</v>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>Tyrone Tracy</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="inlineStr">
-        <is>
-          <t>NYG (8)</t>
-        </is>
-      </c>
-      <c r="F128" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="9" t="inlineStr">
-        <is>
-          <t>TE15</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="C129" s="6" t="n">
-        <v>135</v>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>Mark Andrews</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>BAL (13)</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="10" t="inlineStr">
-        <is>
-          <t>QB21</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="n">
-        <v>131</v>
-      </c>
-      <c r="C130" s="11" t="n">
-        <v>106</v>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>Malik Willis</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>MIA (6)</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>WR54</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="n">
-        <v>132</v>
-      </c>
-      <c r="C131" s="6" t="n">
-        <v>116</v>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>Jalen Coker</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>CAR (5)</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>WR55</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="C132" s="11" t="n">
-        <v>98</v>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="inlineStr">
-        <is>
-          <t>GB (11)</t>
-        </is>
-      </c>
-      <c r="F132" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="10" t="inlineStr">
-        <is>
-          <t>QB22</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="n">
-        <v>134</v>
-      </c>
-      <c r="C133" s="6" t="n">
-        <v>139</v>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>C.J. Stroud</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>HOU (8)</t>
-        </is>
-      </c>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>RB43</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="n">
-        <v>135</v>
-      </c>
-      <c r="C134" s="6" t="n">
-        <v>141</v>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>HOU (8)</t>
-        </is>
-      </c>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="5" t="inlineStr">
-        <is>
-          <t>RB44</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="n">
-        <v>136</v>
-      </c>
-      <c r="C135" s="6" t="n">
-        <v>152</v>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>Tyler Allgeier</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>ARI (14)</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>RB45</t>
+          <t>RB43</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C136" s="6" t="n">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Zach Charbonnet</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>HOU (8)</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -4310,137 +4310,137 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="10" t="inlineStr">
-        <is>
-          <t>QB23</t>
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>RB44</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C137" s="6" t="n">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Sam Darnold</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>ARI (14)</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
+          <t>RB45</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="C138" s="9" t="n">
+        <v>244</v>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>Zach Charbonnet</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>QB23</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="C139" s="9" t="n">
+        <v>165</v>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Sam Darnold</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
           <t>RB46</t>
         </is>
       </c>
-      <c r="B138" s="3" t="n">
+      <c r="B140" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C138" s="7" t="n">
+      <c r="C140" s="7" t="n">
         <v>110</v>
       </c>
-      <c r="D138" s="3" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>Chris Rodriguez</t>
         </is>
       </c>
-      <c r="E138" s="3" t="inlineStr">
+      <c r="E140" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F138" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="5" t="inlineStr">
-        <is>
-          <t>RB47</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="C139" s="6" t="n">
-        <v>169</v>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>Tyjae Spears</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>TEN (9)</t>
-        </is>
-      </c>
-      <c r="F139" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="9" t="inlineStr">
-        <is>
-          <t>TE16</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="n">
-        <v>141</v>
-      </c>
-      <c r="C140" s="6" t="n">
-        <v>158</v>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>Juwan Johnson</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>NO (8)</t>
-        </is>
-      </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>RB48</t>
+          <t>RB47</t>
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C141" s="6" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Dylan Sampson</t>
+          <t>Tyjae Spears</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>TEN (9)</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -4450,165 +4450,165 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="inlineStr">
-        <is>
-          <t>RB49</t>
+      <c r="A142" s="8" t="inlineStr">
+        <is>
+          <t>TE16</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C142" s="6" t="n">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Isiah Pacheco</t>
+          <t>Juwan Johnson</t>
         </is>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>DET (6)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
+          <t>RB48</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="C143" s="6" t="n">
+        <v>183</v>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Dylan Sampson</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>RB49</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="C144" s="6" t="n">
+        <v>169</v>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Isiah Pacheco</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>DET (6)</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="inlineStr">
+        <is>
           <t>RB50</t>
         </is>
       </c>
-      <c r="B143" s="3" t="n">
+      <c r="B145" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="C143" s="6" t="n">
-        <v>188</v>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
+      <c r="C145" s="6" t="n">
+        <v>171</v>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
         <is>
           <t>Alvin Kamara</t>
         </is>
       </c>
-      <c r="E143" s="3" t="inlineStr">
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="F143" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="10" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="inlineStr">
         <is>
           <t>QB24</t>
         </is>
       </c>
-      <c r="B144" s="3" t="n">
+      <c r="B146" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="C144" s="6" t="n">
-        <v>149</v>
-      </c>
-      <c r="D144" s="3" t="inlineStr">
+      <c r="C146" s="9" t="n">
+        <v>204</v>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t>Cam Ward</t>
         </is>
       </c>
-      <c r="E144" s="3" t="inlineStr">
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F144" s="3" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr">
         <is>
           <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>WR56</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="n">
-        <v>146</v>
-      </c>
-      <c r="C145" s="6" t="n">
-        <v>144</v>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>Rashid Shaheed</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>SEA (11)</t>
-        </is>
-      </c>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="9" t="inlineStr">
-        <is>
-          <t>TE17</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="n">
-        <v>147</v>
-      </c>
-      <c r="C146" s="6" t="n">
-        <v>151</v>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>Brenton Strange</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>JAC (7)</t>
-        </is>
-      </c>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>WR57</t>
+          <t>WR56</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>148</v>
-      </c>
-      <c r="C147" s="8" t="n">
-        <v>176</v>
+        <v>146</v>
+      </c>
+      <c r="C147" s="6" t="n">
+        <v>133</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Omar Cooper</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>NYJ (13)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -4618,529 +4618,529 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>WR58</t>
+      <c r="A148" s="8" t="inlineStr">
+        <is>
+          <t>TE17</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>149</v>
-      </c>
-      <c r="C148" s="8" t="n">
-        <v>180</v>
+        <v>147</v>
+      </c>
+      <c r="C148" s="6" t="n">
+        <v>186</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Denzel Boston</t>
+          <t>Brenton Strange</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>JAC (7)</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>WR57</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="C149" s="9" t="n">
+        <v>180</v>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Omar Cooper</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>NYJ (13)</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>WR58</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="C150" s="9" t="n">
+        <v>225</v>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Denzel Boston</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
           <t>WR59</t>
         </is>
       </c>
-      <c r="B149" s="3" t="n">
+      <c r="B151" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="C149" s="6" t="n">
+      <c r="C151" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Jerry Jeudy</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>QB25</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="n">
+        <v>151</v>
+      </c>
+      <c r="C152" s="4" t="n">
+        <v>177</v>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Daniel Jones</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>IND (13)</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
+          <t>QB26</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="C153" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Bryce Young</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>CAR (5)</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>WR60</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="C154" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Jauan Jennings</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>MIN (6)</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t>TE18</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="C155" s="6" t="n">
+        <v>166</v>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Chig Okonkwo</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>WAS (7)</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="8" t="inlineStr">
+        <is>
+          <t>TE19</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>Jerry Jeudy</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>CLE (11)</t>
-        </is>
-      </c>
-      <c r="F149" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="10" t="inlineStr">
-        <is>
-          <t>QB25</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="n">
-        <v>151</v>
-      </c>
-      <c r="C150" s="6" t="n">
-        <v>162</v>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>Daniel Jones</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>IND (13)</t>
-        </is>
-      </c>
-      <c r="F150" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="10" t="inlineStr">
-        <is>
-          <t>QB26</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="n">
-        <v>152</v>
-      </c>
-      <c r="C151" s="6" t="n">
-        <v>130</v>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>Bryce Young</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>CAR (5)</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>WR60</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="n">
-        <v>153</v>
-      </c>
-      <c r="C152" s="6" t="n">
-        <v>147</v>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
-        <is>
-          <t>Jauan Jennings</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>MIN (6)</t>
-        </is>
-      </c>
-      <c r="F152" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="9" t="inlineStr">
-        <is>
-          <t>TE18</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="n">
-        <v>154</v>
-      </c>
-      <c r="C153" s="6" t="n">
-        <v>163</v>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>Chig Okonkwo</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>WAS (7)</t>
-        </is>
-      </c>
-      <c r="F153" s="3" t="inlineStr">
+      <c r="C156" s="6" t="n">
+        <v>196</v>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>Oronde Gadsden</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>LAC (7)</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="9" t="inlineStr">
-        <is>
-          <t>TE19</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="n">
-        <v>155</v>
-      </c>
-      <c r="C154" s="7" t="n">
-        <v>133</v>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>Oronde Gadsden</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="8" t="inlineStr">
+        <is>
+          <t>TE20</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="C157" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Hunter Henry</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>NE (11)</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>RB51</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="C158" s="6" t="n">
+        <v>228</v>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Jonah Coleman</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>DEN (10)</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>RB52</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="C159" s="7" t="n">
+        <v>125</v>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Keaton Mitchell</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F154" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="9" t="inlineStr">
-        <is>
-          <t>TE20</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="C155" s="6" t="n">
-        <v>161</v>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t>Hunter Henry</t>
-        </is>
-      </c>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>NE (11)</t>
-        </is>
-      </c>
-      <c r="F155" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="5" t="inlineStr">
-        <is>
-          <t>RB51</t>
-        </is>
-      </c>
-      <c r="B156" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="C156" s="6" t="n">
-        <v>168</v>
-      </c>
-      <c r="D156" s="3" t="inlineStr">
-        <is>
-          <t>Jonah Coleman</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="inlineStr">
-        <is>
-          <t>DEN (10)</t>
-        </is>
-      </c>
-      <c r="F156" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="5" t="inlineStr">
-        <is>
-          <t>RB52</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="n">
-        <v>159</v>
-      </c>
-      <c r="C157" s="6" t="n">
-        <v>181</v>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>Keaton Mitchell</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>LAC (7)</t>
-        </is>
-      </c>
-      <c r="F157" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>WR61</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="C158" s="4" t="n">
-        <v>199</v>
-      </c>
-      <c r="D158" s="3" t="inlineStr">
-        <is>
-          <t>Adonai Mitchell</t>
-        </is>
-      </c>
-      <c r="E158" s="3" t="inlineStr">
-        <is>
-          <t>NYJ (13)</t>
-        </is>
-      </c>
-      <c r="F158" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>WR62</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="C159" s="6" t="n">
-        <v>143</v>
-      </c>
-      <c r="D159" s="3" t="inlineStr">
-        <is>
-          <t>Jalen McMillan</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="inlineStr">
-        <is>
-          <t>TB (10)</t>
-        </is>
-      </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>WR61</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="C160" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Adonai Mitchell</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>NYJ (13)</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>WR62</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="C161" s="6" t="n">
+        <v>181</v>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Jalen McMillan</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>TB (10)</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
           <t>WR63</t>
         </is>
       </c>
-      <c r="B160" s="3" t="n">
+      <c r="B162" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="C160" s="6" t="n">
-        <v>178</v>
-      </c>
-      <c r="D160" s="3" t="inlineStr">
+      <c r="C162" s="4" t="n">
+        <v>207</v>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
         <is>
           <t>Tre Tucker</t>
         </is>
       </c>
-      <c r="E160" s="3" t="inlineStr">
+      <c r="E162" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F160" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="5" t="inlineStr">
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="inlineStr">
         <is>
           <t>RB53</t>
         </is>
       </c>
-      <c r="B161" s="3" t="n">
+      <c r="B163" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="C161" s="6" t="n">
+      <c r="C163" s="6" t="n">
+        <v>170</v>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Brian Robinson</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>ATL (11)</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>RB54</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>Brian Robinson</t>
-        </is>
-      </c>
-      <c r="E161" s="3" t="inlineStr">
-        <is>
-          <t>ATL (11)</t>
-        </is>
-      </c>
-      <c r="F161" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="5" t="inlineStr">
-        <is>
-          <t>RB54</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="n">
-        <v>165</v>
-      </c>
-      <c r="C162" s="6" t="n">
+      <c r="C164" s="6" t="n">
+        <v>167</v>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Tank Bigsby</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>PHI (10)</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t>TE21</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="n">
         <v>166</v>
       </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>Tank Bigsby</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="inlineStr">
-        <is>
-          <t>PHI (10)</t>
-        </is>
-      </c>
-      <c r="F162" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="9" t="inlineStr">
-        <is>
-          <t>TE21</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="C163" s="6" t="n">
-        <v>160</v>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
+      <c r="C165" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
         <is>
           <t>Dalton Schultz</t>
         </is>
       </c>
-      <c r="E163" s="3" t="inlineStr">
+      <c r="E165" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F163" s="3" t="inlineStr">
+      <c r="F165" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>WR64</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="C164" s="11" t="n">
-        <v>136</v>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>Travis Hunter</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>JAC (7)</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="5" t="inlineStr">
-        <is>
-          <t>RB55</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="n">
-        <v>169</v>
-      </c>
-      <c r="C165" s="6" t="n">
-        <v>167</v>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>Braelon Allen</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>NYJ (13)</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>WR65</t>
+          <t>WR64</t>
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C166" s="6" t="n">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Tre' Harris</t>
+          <t>Travis Hunter</t>
         </is>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>JAC (7)</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
@@ -5150,53 +5150,53 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="9" t="inlineStr">
-        <is>
-          <t>TE22</t>
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>RB55</t>
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C167" s="6" t="n">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>T.J. Hockenson</t>
+          <t>Braelon Allen</t>
         </is>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>NYJ (13)</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>WR66</t>
+          <t>WR65</t>
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="C168" s="4" t="n">
-        <v>228</v>
+        <v>170</v>
+      </c>
+      <c r="C168" s="6" t="n">
+        <v>178</v>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Troy Franklin</t>
+          <t>Tre' Harris</t>
         </is>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>DEN (10)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
@@ -5206,53 +5206,53 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>WR67</t>
+      <c r="A169" s="8" t="inlineStr">
+        <is>
+          <t>TE22</t>
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="C169" s="6" t="n">
-        <v>186</v>
+        <v>173</v>
+      </c>
+      <c r="C169" s="4" t="n">
+        <v>213</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>Kayshon Boutte</t>
+          <t>T.J. Hockenson</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>WR68</t>
+          <t>WR66</t>
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="C170" s="6" t="n">
-        <v>177</v>
+        <v>174</v>
+      </c>
+      <c r="C170" s="4" t="n">
+        <v>296</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Ryan Flournoy</t>
+          <t>Troy Franklin</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>DAL (14)</t>
+          <t>DEN (10)</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -5264,107 +5264,107 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>WR67</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="C171" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Kayshon Boutte</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>NE (11)</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>WR68</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="C172" s="4" t="n">
+        <v>203</v>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Ryan Flournoy</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>DAL (14)</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
           <t>WR69</t>
         </is>
       </c>
-      <c r="B171" s="3" t="n">
+      <c r="B173" s="3" t="n">
         <v>177</v>
       </c>
-      <c r="C171" s="11" t="n">
-        <v>146</v>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
+      <c r="C173" s="7" t="n">
+        <v>135</v>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
         <is>
           <t>Stefon Diggs</t>
         </is>
       </c>
-      <c r="E171" s="3" t="inlineStr">
+      <c r="E173" s="3" t="inlineStr">
         <is>
           <t>FA ()</t>
         </is>
       </c>
-      <c r="F171" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="5" t="inlineStr">
-        <is>
-          <t>RB56</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="n">
-        <v>178</v>
-      </c>
-      <c r="C172" s="4" t="n">
-        <v>219</v>
-      </c>
-      <c r="D172" s="3" t="inlineStr">
-        <is>
-          <t>James Conner</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="inlineStr">
-        <is>
-          <t>ARI (14)</t>
-        </is>
-      </c>
-      <c r="F172" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="10" t="inlineStr">
-        <is>
-          <t>QB27</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="n">
-        <v>179</v>
-      </c>
-      <c r="C173" s="6" t="n">
-        <v>172</v>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>Jacoby Brissett</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="inlineStr">
-        <is>
-          <t>ARI (14)</t>
-        </is>
-      </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>RB57</t>
+          <t>RB56</t>
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>186</v>
-      </c>
-      <c r="C174" s="6" t="n">
-        <v>190</v>
+        <v>178</v>
+      </c>
+      <c r="C174" s="4" t="n">
+        <v>276</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Emanuel Wilson</t>
+          <t>James Conner</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>ARI (14)</t>
         </is>
       </c>
       <c r="F174" s="3" t="inlineStr">
@@ -5374,305 +5374,305 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>WR71</t>
+      <c r="A175" s="10" t="inlineStr">
+        <is>
+          <t>QB27</t>
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="C175" s="11" t="n">
-        <v>156</v>
+        <v>179</v>
+      </c>
+      <c r="C175" s="4" t="n">
+        <v>245</v>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Calvin Ridley</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>TEN (9)</t>
+          <t>ARI (14)</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
+          <t>WR70</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="n">
+        <v>185</v>
+      </c>
+      <c r="C176" s="4" t="n">
+        <v>284</v>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>Jaylin Noel</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>HOU (8)</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="5" t="inlineStr">
+        <is>
+          <t>RB57</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="C177" s="4" t="n">
+        <v>273</v>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>Emanuel Wilson</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>WR71</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="n">
+        <v>187</v>
+      </c>
+      <c r="C178" s="6" t="n">
+        <v>206</v>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>Calvin Ridley</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>TEN (9)</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
           <t>WR72</t>
         </is>
       </c>
-      <c r="B176" s="3" t="n">
+      <c r="B179" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="C176" s="6" t="n">
-        <v>185</v>
-      </c>
-      <c r="D176" s="3" t="inlineStr">
+      <c r="C179" s="6" t="n">
+        <v>208</v>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
         <is>
           <t>Isaac TeSlaa</t>
         </is>
       </c>
-      <c r="E176" s="3" t="inlineStr">
+      <c r="E179" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F176" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="9" t="inlineStr">
+      <c r="F179" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="8" t="inlineStr">
         <is>
           <t>TE23</t>
         </is>
       </c>
-      <c r="B177" s="3" t="n">
+      <c r="B180" s="3" t="n">
         <v>191</v>
       </c>
-      <c r="C177" s="11" t="n">
-        <v>157</v>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
+      <c r="C180" s="6" t="n">
+        <v>216</v>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
         <is>
           <t>Kenyon Sadiq</t>
         </is>
       </c>
-      <c r="E177" s="3" t="inlineStr">
+      <c r="E180" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F177" s="3" t="inlineStr">
+      <c r="F180" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="5" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
         <is>
           <t>RB58</t>
         </is>
       </c>
-      <c r="B178" s="3" t="n">
+      <c r="B181" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="C178" s="6" t="n">
-        <v>189</v>
-      </c>
-      <c r="D178" s="3" t="inlineStr">
+      <c r="C181" s="4" t="n">
+        <v>264</v>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
         <is>
           <t>Emmett Johnson</t>
         </is>
       </c>
-      <c r="E178" s="3" t="inlineStr">
+      <c r="E181" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F178" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="5" t="inlineStr">
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
         <is>
           <t>RB59</t>
         </is>
       </c>
-      <c r="B179" s="3" t="n">
+      <c r="B182" s="3" t="n">
         <v>194</v>
       </c>
-      <c r="C179" s="6" t="n">
-        <v>210</v>
-      </c>
-      <c r="D179" s="3" t="inlineStr">
+      <c r="C182" s="4" t="n">
+        <v>271</v>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
         <is>
           <t>Kimani Vidal</t>
         </is>
       </c>
-      <c r="E179" s="3" t="inlineStr">
+      <c r="E182" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F179" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="5" t="inlineStr">
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr">
         <is>
           <t>RB60</t>
         </is>
       </c>
-      <c r="B180" s="3" t="n">
+      <c r="B183" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="C180" s="6" t="n">
-        <v>209</v>
-      </c>
-      <c r="D180" s="3" t="inlineStr">
+      <c r="C183" s="6" t="n">
+        <v>217</v>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
         <is>
           <t>Ray Davis</t>
         </is>
       </c>
-      <c r="E180" s="3" t="inlineStr">
+      <c r="E183" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F180" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="9" t="inlineStr">
+      <c r="F183" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="8" t="inlineStr">
         <is>
           <t>TE24</t>
         </is>
       </c>
-      <c r="B181" s="3" t="n">
+      <c r="B184" s="3" t="n">
         <v>196</v>
       </c>
-      <c r="C181" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
+      <c r="C184" s="6" t="n">
+        <v>184</v>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
         <is>
           <t>AJ Barner</t>
         </is>
       </c>
-      <c r="E181" s="3" t="inlineStr">
+      <c r="E184" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F181" s="3" t="inlineStr">
+      <c r="F184" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
-        <is>
-          <t>WR73</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="C182" s="6" t="n">
-        <v>223</v>
-      </c>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>Darnell Mooney</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="inlineStr">
-        <is>
-          <t>NYG (8)</t>
-        </is>
-      </c>
-      <c r="F182" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
-        <is>
-          <t>WR74</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="C183" s="7" t="n">
-        <v>137</v>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>Jalen Nailor</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>LV (13)</t>
-        </is>
-      </c>
-      <c r="F183" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
-        <is>
-          <t>WR75</t>
-        </is>
-      </c>
-      <c r="B184" s="3" t="n">
-        <v>201</v>
-      </c>
-      <c r="C184" s="11" t="n">
-        <v>148</v>
-      </c>
-      <c r="D184" s="3" t="inlineStr">
-        <is>
-          <t>Deebo Samuel</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="inlineStr">
-        <is>
-          <t>FA ()</t>
-        </is>
-      </c>
-      <c r="F184" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>WR76</t>
+          <t>WR73</t>
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="C185" s="6" t="n">
-        <v>204</v>
+        <v>197</v>
+      </c>
+      <c r="C185" s="4" t="n">
+        <v>235</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Malik Washington</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>NYG (8)</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -5682,20 +5682,20 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>RB61</t>
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>WR74</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>204</v>
-      </c>
-      <c r="C186" s="11" t="n">
-        <v>153</v>
+        <v>199</v>
+      </c>
+      <c r="C186" s="7" t="n">
+        <v>148</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Mike Washington</t>
+          <t>Jalen Nailor</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
@@ -5705,30 +5705,30 @@
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>WR77</t>
+          <t>WR75</t>
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C187" s="6" t="n">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Pat Bryant</t>
+          <t>Deebo Samuel</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>DEN (10)</t>
+          <t>FA ()</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -5740,23 +5740,23 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>WR78</t>
+          <t>WR76</t>
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>206</v>
-      </c>
-      <c r="C188" s="11" t="n">
-        <v>174</v>
+        <v>202</v>
+      </c>
+      <c r="C188" s="4" t="n">
+        <v>242</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Antonio Williams</t>
+          <t>Malik Washington</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
@@ -5766,53 +5766,53 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="9" t="inlineStr">
-        <is>
-          <t>TE25</t>
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>RB61</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C189" s="6" t="n">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Gunnar Helm</t>
+          <t>Mike Washington</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>TEN (9)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>WR79</t>
+          <t>WR77</t>
         </is>
       </c>
       <c r="B190" s="3" t="n">
-        <v>211</v>
-      </c>
-      <c r="C190" s="6" t="n">
-        <v>200</v>
+        <v>205</v>
+      </c>
+      <c r="C190" s="4" t="n">
+        <v>241</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks</t>
+          <t>Pat Bryant</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>PHI (10)</t>
+          <t>DEN (10)</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -5822,48 +5822,48 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="5" t="inlineStr">
-        <is>
-          <t>RB62</t>
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>WR78</t>
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C191" s="6" t="n">
-        <v>193</v>
+        <v>236</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Sean Tucker</t>
+          <t>Antonio Williams</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>TB (10)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="5" t="inlineStr">
-        <is>
-          <t>RB63</t>
+      <c r="A192" s="8" t="inlineStr">
+        <is>
+          <t>TE25</t>
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>213</v>
-      </c>
-      <c r="C192" s="6" t="n">
-        <v>212</v>
+        <v>207</v>
+      </c>
+      <c r="C192" s="4" t="n">
+        <v>239</v>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Nicholas Singleton</t>
+          <t>Gunnar Helm</t>
         </is>
       </c>
       <c r="E192" s="3" t="inlineStr">
@@ -5873,142 +5873,142 @@
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
+          <t>WR79</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="n">
+        <v>211</v>
+      </c>
+      <c r="C193" s="4" t="n">
+        <v>258</v>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>Dontayvion Wicks</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>PHI (10)</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="inlineStr">
+        <is>
+          <t>RB62</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="n">
+        <v>212</v>
+      </c>
+      <c r="C194" s="6" t="n">
+        <v>243</v>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>Sean Tucker</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>TB (10)</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="inlineStr">
+        <is>
+          <t>RB63</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="n">
+        <v>213</v>
+      </c>
+      <c r="C195" s="4" t="n">
+        <v>297</v>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>Nicholas Singleton</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>TEN (9)</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
           <t>WR80</t>
         </is>
       </c>
-      <c r="B193" s="3" t="n">
+      <c r="B196" s="3" t="n">
         <v>217</v>
       </c>
-      <c r="C193" s="6" t="n">
-        <v>224</v>
-      </c>
-      <c r="D193" s="3" t="inlineStr">
+      <c r="C196" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
         <is>
           <t>Tank Dell</t>
         </is>
       </c>
-      <c r="E193" s="3" t="inlineStr">
+      <c r="E196" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F193" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="10" t="inlineStr">
-        <is>
-          <t>QB28</t>
-        </is>
-      </c>
-      <c r="B194" s="3" t="n">
-        <v>219</v>
-      </c>
-      <c r="C194" s="11" t="n">
-        <v>173</v>
-      </c>
-      <c r="D194" s="3" t="inlineStr">
-        <is>
-          <t>Aaron Rodgers</t>
-        </is>
-      </c>
-      <c r="E194" s="3" t="inlineStr">
-        <is>
-          <t>PIT (9)</t>
-        </is>
-      </c>
-      <c r="F194" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>WR81</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="n">
-        <v>221</v>
-      </c>
-      <c r="C195" s="6" t="n">
-        <v>198</v>
-      </c>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>Cooper Kupp</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>SEA (11)</t>
-        </is>
-      </c>
-      <c r="F195" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="5" t="inlineStr">
-        <is>
-          <t>RB64</t>
-        </is>
-      </c>
-      <c r="B196" s="3" t="n">
-        <v>222</v>
-      </c>
-      <c r="C196" s="11" t="n">
-        <v>182</v>
-      </c>
-      <c r="D196" s="3" t="inlineStr">
-        <is>
-          <t>Kaytron Allen</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="inlineStr">
-        <is>
-          <t>WAS (7)</t>
-        </is>
-      </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="10" t="inlineStr">
         <is>
-          <t>QB29</t>
+          <t>QB28</t>
         </is>
       </c>
       <c r="B197" s="3" t="n">
-        <v>223</v>
-      </c>
-      <c r="C197" s="11" t="n">
-        <v>170</v>
+        <v>219</v>
+      </c>
+      <c r="C197" s="6" t="n">
+        <v>222</v>
       </c>
       <c r="D197" s="3" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>Aaron Rodgers</t>
         </is>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>NYJ (13)</t>
+          <t>PIT (9)</t>
         </is>
       </c>
       <c r="F197" s="3" t="inlineStr">
@@ -6020,23 +6020,23 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>WR83</t>
+          <t>WR81</t>
         </is>
       </c>
       <c r="B198" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="C198" s="11" t="n">
-        <v>175</v>
+        <v>221</v>
+      </c>
+      <c r="C198" s="6" t="n">
+        <v>233</v>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Cooper Kupp</t>
         </is>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
@@ -6046,76 +6046,76 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="inlineStr">
-        <is>
-          <t>WR84</t>
+      <c r="A199" s="5" t="inlineStr">
+        <is>
+          <t>RB64</t>
         </is>
       </c>
       <c r="B199" s="3" t="n">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C199" s="6" t="n">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="D199" s="3" t="inlineStr">
         <is>
-          <t>Germie Bernard</t>
+          <t>Kaytron Allen</t>
         </is>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>PIT (9)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>WR85</t>
+      <c r="A200" s="10" t="inlineStr">
+        <is>
+          <t>QB29</t>
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C200" s="6" t="n">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Rashod Bateman</t>
+          <t>Geno Smith</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>BAL (13)</t>
+          <t>NYJ (13)</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>WR86</t>
+          <t>WR83</t>
         </is>
       </c>
       <c r="B201" s="3" t="n">
-        <v>232</v>
-      </c>
-      <c r="C201" s="11" t="n">
-        <v>145</v>
+        <v>225</v>
+      </c>
+      <c r="C201" s="6" t="n">
+        <v>227</v>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>Brandon Aiyuk</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
@@ -6130,81 +6130,81 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="10" t="inlineStr">
-        <is>
-          <t>QB30</t>
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>WR84</t>
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>234</v>
-      </c>
-      <c r="C202" s="11" t="n">
-        <v>171</v>
+        <v>228</v>
+      </c>
+      <c r="C202" s="6" t="n">
+        <v>226</v>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Fernando Mendoza</t>
+          <t>Germie Bernard</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>PIT (9)</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="9" t="inlineStr">
-        <is>
-          <t>TE26</t>
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>WR85</t>
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>235</v>
-      </c>
-      <c r="C203" s="6" t="n">
-        <v>217</v>
+        <v>230</v>
+      </c>
+      <c r="C203" s="4" t="n">
+        <v>283</v>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>Pat Freiermuth</t>
+          <t>Rashod Bateman</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>PIT (9)</t>
+          <t>BAL (13)</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>WR87</t>
+          <t>WR86</t>
         </is>
       </c>
       <c r="B204" s="3" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C204" s="6" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Zachariah Branch</t>
+          <t>Brandon Aiyuk</t>
         </is>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>ATL (11)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
@@ -6214,109 +6214,109 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="9" t="inlineStr">
-        <is>
-          <t>TE27</t>
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>RB65</t>
         </is>
       </c>
       <c r="B205" s="3" t="n">
-        <v>238</v>
-      </c>
-      <c r="C205" s="11" t="n">
-        <v>164</v>
+        <v>233</v>
+      </c>
+      <c r="C205" s="4" t="n">
+        <v>289</v>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>Cade Otton</t>
+          <t>Jaylen Wright</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>TB (10)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="10" t="inlineStr">
+        <is>
+          <t>QB30</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="C206" s="6" t="n">
+        <v>205</v>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>Fernando Mendoza</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
+        <is>
+          <t>LV (13)</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="8" t="inlineStr">
+        <is>
+          <t>TE26</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="C207" s="4" t="n">
+        <v>275</v>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Pat Freiermuth</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>PIT (9)</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="9" t="inlineStr">
-        <is>
-          <t>TE28</t>
-        </is>
-      </c>
-      <c r="B206" s="3" t="n">
-        <v>239</v>
-      </c>
-      <c r="C206" s="11" t="n">
-        <v>194</v>
-      </c>
-      <c r="D206" s="3" t="inlineStr">
-        <is>
-          <t>David Njoku</t>
-        </is>
-      </c>
-      <c r="E206" s="3" t="inlineStr">
-        <is>
-          <t>LAC (7)</t>
-        </is>
-      </c>
-      <c r="F206" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="5" t="inlineStr">
-        <is>
-          <t>RB66</t>
-        </is>
-      </c>
-      <c r="B207" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="C207" s="11" t="n">
-        <v>184</v>
-      </c>
-      <c r="D207" s="3" t="inlineStr">
-        <is>
-          <t>Justice Hill</t>
-        </is>
-      </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>BAL (13)</t>
-        </is>
-      </c>
-      <c r="F207" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>WR88</t>
+          <t>WR87</t>
         </is>
       </c>
       <c r="B208" s="3" t="n">
-        <v>241</v>
-      </c>
-      <c r="C208" s="11" t="n">
-        <v>179</v>
+        <v>237</v>
+      </c>
+      <c r="C208" s="6" t="n">
+        <v>260</v>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Jack Bech</t>
+          <t>Zachariah Branch</t>
         </is>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>ATL (11)</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
@@ -6326,25 +6326,25 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="9" t="inlineStr">
-        <is>
-          <t>TE29</t>
+      <c r="A209" s="8" t="inlineStr">
+        <is>
+          <t>TE27</t>
         </is>
       </c>
       <c r="B209" s="3" t="n">
-        <v>243</v>
-      </c>
-      <c r="C209" s="11" t="n">
-        <v>195</v>
+        <v>238</v>
+      </c>
+      <c r="C209" s="6" t="n">
+        <v>224</v>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>Terrance Ferguson</t>
+          <t>Cade Otton</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>TB (10)</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -6354,81 +6354,81 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="inlineStr">
-        <is>
-          <t>WR91</t>
+      <c r="A210" s="8" t="inlineStr">
+        <is>
+          <t>TE28</t>
         </is>
       </c>
       <c r="B210" s="3" t="n">
-        <v>249</v>
-      </c>
-      <c r="C210" s="6" t="n">
-        <v>233</v>
+        <v>239</v>
+      </c>
+      <c r="C210" s="4" t="n">
+        <v>280</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Keon Coleman</t>
+          <t>David Njoku</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>WR92</t>
+      <c r="A211" s="5" t="inlineStr">
+        <is>
+          <t>RB66</t>
         </is>
       </c>
       <c r="B211" s="3" t="n">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C211" s="6" t="n">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Chris Bell</t>
+          <t>Justice Hill</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>BAL (13)</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>WR93</t>
+          <t>WR88</t>
         </is>
       </c>
       <c r="B212" s="3" t="n">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="C212" s="6" t="n">
-        <v>225</v>
+        <v>259</v>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Elijah Sarratt</t>
+          <t>Jack Bech</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>BAL (13)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -6440,23 +6440,23 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>WR94</t>
+          <t>WR89</t>
         </is>
       </c>
       <c r="B213" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="C213" s="6" t="n">
-        <v>222</v>
+        <v>242</v>
+      </c>
+      <c r="C213" s="4" t="n">
+        <v>298</v>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>Christian Kirk</t>
+          <t>Ted Hurst</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>TB (10)</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
@@ -6466,81 +6466,81 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="inlineStr">
-        <is>
-          <t>RB70</t>
+      <c r="A214" s="8" t="inlineStr">
+        <is>
+          <t>TE29</t>
         </is>
       </c>
       <c r="B214" s="3" t="n">
+        <v>243</v>
+      </c>
+      <c r="C214" s="6" t="n">
         <v>257</v>
       </c>
-      <c r="C214" s="6" t="n">
-        <v>220</v>
-      </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>DJ Giddens</t>
+          <t>Terrance Ferguson</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>IND (13)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="inlineStr">
-        <is>
-          <t>WR96</t>
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>RB68</t>
         </is>
       </c>
       <c r="B215" s="3" t="n">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="C215" s="6" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>Tyreek Hill</t>
+          <t>MarShawn Lloyd</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>FA ()</t>
+          <t>GB (11)</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="9" t="inlineStr">
-        <is>
-          <t>TE32</t>
+      <c r="A216" s="8" t="inlineStr">
+        <is>
+          <t>TE30</t>
         </is>
       </c>
       <c r="B216" s="3" t="n">
-        <v>259</v>
-      </c>
-      <c r="C216" s="11" t="n">
-        <v>196</v>
+        <v>248</v>
+      </c>
+      <c r="C216" s="6" t="n">
+        <v>238</v>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Eli Stowers</t>
+          <t>Colby Parkinson</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>PHI (10)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
@@ -6552,23 +6552,23 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>WR97</t>
+          <t>WR91</t>
         </is>
       </c>
       <c r="B217" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="C217" s="6" t="n">
-        <v>227</v>
+        <v>249</v>
+      </c>
+      <c r="C217" s="4" t="n">
+        <v>291</v>
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>Tory Horton</t>
+          <t>Keon Coleman</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
@@ -6578,364 +6578,924 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>WR99</t>
+      <c r="A218" s="5" t="inlineStr">
+        <is>
+          <t>RB69</t>
         </is>
       </c>
       <c r="B218" s="3" t="n">
-        <v>263</v>
-      </c>
-      <c r="C218" s="6" t="n">
-        <v>202</v>
+        <v>250</v>
+      </c>
+      <c r="C218" s="4" t="n">
+        <v>292</v>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Chris Brazzell</t>
+          <t>Ty Johnson</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>CAR (5)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="5" t="inlineStr">
-        <is>
-          <t>RB72</t>
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>WR92</t>
         </is>
       </c>
       <c r="B219" s="3" t="n">
+        <v>251</v>
+      </c>
+      <c r="C219" s="6" t="n">
+        <v>248</v>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>Chris Bell</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>WR93</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="n">
+        <v>252</v>
+      </c>
+      <c r="C220" s="6" t="n">
+        <v>269</v>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>Elijah Sarratt</t>
+        </is>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>BAL (13)</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="8" t="inlineStr">
+        <is>
+          <t>TE31</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="C221" s="6" t="n">
         <v>265</v>
       </c>
-      <c r="C219" s="11" t="n">
-        <v>192</v>
-      </c>
-      <c r="D219" s="3" t="inlineStr">
-        <is>
-          <t>Chris Brooks</t>
-        </is>
-      </c>
-      <c r="E219" s="3" t="inlineStr">
-        <is>
-          <t>GB (11)</t>
-        </is>
-      </c>
-      <c r="F219" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="10" t="inlineStr">
-        <is>
-          <t>QB31</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="n">
-        <v>266</v>
-      </c>
-      <c r="C220" s="6" t="n">
-        <v>205</v>
-      </c>
-      <c r="D220" s="3" t="inlineStr">
-        <is>
-          <t>Tua Tagovailoa</t>
-        </is>
-      </c>
-      <c r="E220" s="3" t="inlineStr">
-        <is>
-          <t>ATL (11)</t>
-        </is>
-      </c>
-      <c r="F220" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
-        <is>
-          <t>WR100</t>
-        </is>
-      </c>
-      <c r="B221" s="3" t="n">
-        <v>267</v>
-      </c>
-      <c r="C221" s="6" t="n">
-        <v>238</v>
-      </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
-          <t>Darius Slayton</t>
+          <t>Evan Engram</t>
         </is>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>NYG (8)</t>
+          <t>DEN (10)</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="10" t="inlineStr">
-        <is>
-          <t>QB32</t>
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>WR94</t>
         </is>
       </c>
       <c r="B222" s="3" t="n">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="C222" s="6" t="n">
-        <v>206</v>
+        <v>287</v>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Michael Penix</t>
+          <t>Christian Kirk</t>
         </is>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>ATL (11)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
+          <t>RB70</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="C223" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>DJ Giddens</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>IND (13)</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="8" t="inlineStr">
+        <is>
+          <t>TE32</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="C224" s="6" t="n">
+        <v>274</v>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>Eli Stowers</t>
+        </is>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
+        <is>
+          <t>PHI (10)</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>WR97</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="C225" s="6" t="n">
+        <v>290</v>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>Tory Horton</t>
+        </is>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="inlineStr">
+        <is>
+          <t>RB71</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="C226" s="6" t="n">
+        <v>254</v>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>Jaydon Blue</t>
+        </is>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
+        <is>
+          <t>DAL (14)</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>WR99</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="C227" s="6" t="n">
+        <v>268</v>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>Chris Brazzell</t>
+        </is>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
+        <is>
+          <t>CAR (5)</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="10" t="inlineStr">
+        <is>
+          <t>QB31</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="C228" s="6" t="n">
+        <v>256</v>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>Tua Tagovailoa</t>
+        </is>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
+        <is>
+          <t>ATL (11)</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>WR100</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="C229" s="6" t="n">
+        <v>282</v>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>Darius Slayton</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>NYG (8)</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="5" t="inlineStr">
+        <is>
+          <t>RB73</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="C230" s="6" t="n">
+        <v>293</v>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>Samaje Perine</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>CIN (6)</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="inlineStr">
+        <is>
+          <t>RB75</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="n">
+        <v>271</v>
+      </c>
+      <c r="C231" s="6" t="n">
+        <v>278</v>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>Demond Claiborne</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>MIN (6)</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="inlineStr">
+        <is>
+          <t>RB78</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="C232" s="6" t="n">
+        <v>299</v>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>Seth McGowan</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>IND (13)</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="10" t="inlineStr">
+        <is>
+          <t>QB32</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="C233" s="6" t="n">
+        <v>255</v>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>Michael Penix</t>
+        </is>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>ATL (11)</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="5" t="inlineStr">
+        <is>
           <t>RB79</t>
         </is>
       </c>
-      <c r="B223" s="3" t="n">
+      <c r="B234" s="3" t="n">
         <v>277</v>
       </c>
-      <c r="C223" s="6" t="n">
+      <c r="C234" s="6" t="n">
+        <v>272</v>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>Jordan James</t>
+        </is>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>SF (8)</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="8" t="inlineStr">
+        <is>
+          <t>TE35</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>278</v>
+      </c>
+      <c r="C235" s="6" t="n">
         <v>214</v>
       </c>
-      <c r="D223" s="3" t="inlineStr">
-        <is>
-          <t>Jordan James</t>
-        </is>
-      </c>
-      <c r="E223" s="3" t="inlineStr">
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Greg Dulcich</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>WR102</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="C236" s="6" t="n">
+        <v>247</v>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>Tyquan Thornton</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>KC (5)</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="inlineStr">
+        <is>
+          <t>RB82</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="n">
+        <v>283</v>
+      </c>
+      <c r="C237" s="6" t="n">
+        <v>294</v>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>George Holani</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>WR103</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="C238" s="6" t="n">
+        <v>281</v>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>Devaughn Vele</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>WR105</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="C239" s="6" t="n">
+        <v>261</v>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Keenan Allen</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>LAC (7)</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>RB85</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="n">
+        <v>293</v>
+      </c>
+      <c r="C240" s="6" t="n">
+        <v>253</v>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Kaelon Black</t>
+        </is>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F223" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="inlineStr">
-        <is>
-          <t>WR103</t>
-        </is>
-      </c>
-      <c r="B224" s="3" t="n">
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>WR106</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="n">
+        <v>294</v>
+      </c>
+      <c r="C241" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>Hollywood Brown</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>PHI (10)</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>RB87</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="n">
+        <v>298</v>
+      </c>
+      <c r="C242" s="6" t="n">
+        <v>263</v>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>Emari Demercado</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>KC (5)</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="10" t="inlineStr">
+        <is>
+          <t>QB34</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="n">
+        <v>299</v>
+      </c>
+      <c r="C243" s="6" t="n">
+        <v>246</v>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Deshaun Watson</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="8" t="inlineStr">
+        <is>
+          <t>TE37</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="C244" s="6" t="n">
+        <v>267</v>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>Mike Gesicki</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>CIN (6)</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="10" t="inlineStr">
+        <is>
+          <t>QB35</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="n">
+        <v>302</v>
+      </c>
+      <c r="C245" s="6" t="n">
+        <v>262</v>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>Kirk Cousins</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>LV (13)</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="inlineStr">
+        <is>
+          <t>RB90</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="C246" s="6" t="n">
+        <v>277</v>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>Najee Harris</t>
+        </is>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>LAC (7)</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>WR108</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="n">
+        <v>306</v>
+      </c>
+      <c r="C247" s="6" t="n">
+        <v>286</v>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>BAL (13)</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>WR111</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="C248" s="6" t="n">
+        <v>295</v>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>Andrei Iosivas</t>
+        </is>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
+        <is>
+          <t>CIN (6)</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>WR120</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="n">
+        <v>335</v>
+      </c>
+      <c r="C249" s="6" t="n">
         <v>285</v>
       </c>
-      <c r="C224" s="6" t="n">
-        <v>230</v>
-      </c>
-      <c r="D224" s="3" t="inlineStr">
-        <is>
-          <t>Devaughn Vele</t>
-        </is>
-      </c>
-      <c r="E224" s="3" t="inlineStr">
-        <is>
-          <t>NO (8)</t>
-        </is>
-      </c>
-      <c r="F224" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="10" t="inlineStr">
-        <is>
-          <t>QB33</t>
-        </is>
-      </c>
-      <c r="B225" s="3" t="n">
-        <v>289</v>
-      </c>
-      <c r="C225" s="6" t="n">
-        <v>218</v>
-      </c>
-      <c r="D225" s="3" t="inlineStr">
-        <is>
-          <t>Shedeur Sanders</t>
-        </is>
-      </c>
-      <c r="E225" s="3" t="inlineStr">
-        <is>
-          <t>CLE (11)</t>
-        </is>
-      </c>
-      <c r="F225" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>WR105</t>
-        </is>
-      </c>
-      <c r="B226" s="3" t="n">
-        <v>290</v>
-      </c>
-      <c r="C226" s="6" t="n">
-        <v>234</v>
-      </c>
-      <c r="D226" s="3" t="inlineStr">
-        <is>
-          <t>Keenan Allen</t>
-        </is>
-      </c>
-      <c r="E226" s="3" t="inlineStr">
-        <is>
-          <t>LAC (7)</t>
-        </is>
-      </c>
-      <c r="F226" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="5" t="inlineStr">
-        <is>
-          <t>RB85</t>
-        </is>
-      </c>
-      <c r="B227" s="3" t="n">
-        <v>293</v>
-      </c>
-      <c r="C227" s="11" t="n">
-        <v>183</v>
-      </c>
-      <c r="D227" s="3" t="inlineStr">
-        <is>
-          <t>Kaelon Black</t>
-        </is>
-      </c>
-      <c r="E227" s="3" t="inlineStr">
-        <is>
-          <t>SF (8)</t>
-        </is>
-      </c>
-      <c r="F227" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="inlineStr">
-        <is>
-          <t>WR106</t>
-        </is>
-      </c>
-      <c r="B228" s="3" t="n">
-        <v>294</v>
-      </c>
-      <c r="C228" s="6" t="n">
-        <v>229</v>
-      </c>
-      <c r="D228" s="3" t="inlineStr">
-        <is>
-          <t>Hollywood Brown</t>
-        </is>
-      </c>
-      <c r="E228" s="3" t="inlineStr">
-        <is>
-          <t>PHI (10)</t>
-        </is>
-      </c>
-      <c r="F228" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="10" t="inlineStr">
-        <is>
-          <t>QB34</t>
-        </is>
-      </c>
-      <c r="B229" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="C229" s="6" t="n">
-        <v>208</v>
-      </c>
-      <c r="D229" s="3" t="inlineStr">
-        <is>
-          <t>Deshaun Watson</t>
-        </is>
-      </c>
-      <c r="E229" s="3" t="inlineStr">
-        <is>
-          <t>CLE (11)</t>
-        </is>
-      </c>
-      <c r="F229" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="9" t="inlineStr">
-        <is>
-          <t>TE37</t>
-        </is>
-      </c>
-      <c r="B230" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="C230" s="6" t="n">
-        <v>216</v>
-      </c>
-      <c r="D230" s="3" t="inlineStr">
-        <is>
-          <t>Mike Gesicki</t>
-        </is>
-      </c>
-      <c r="E230" s="3" t="inlineStr">
-        <is>
-          <t>CIN (6)</t>
-        </is>
-      </c>
-      <c r="F230" s="3" t="inlineStr">
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>Jalen Tolbert</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="8" t="inlineStr">
+        <is>
+          <t>TE45</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="n">
+        <v>344</v>
+      </c>
+      <c r="C250" s="6" t="n">
+        <v>279</v>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>Dawson Knox</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>BUF (7)</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -108,10 +108,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F250"/>
+  <dimension ref="A1:F257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,8 +566,8 @@
       <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>4</v>
+      <c r="C3" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>RB1</t>
         </is>
@@ -594,8 +594,8 @@
       <c r="B4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="6" t="n">
-        <v>2</v>
+      <c r="C4" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>RB2</t>
         </is>
@@ -650,7 +650,7 @@
       <c r="B6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -678,7 +678,7 @@
       <c r="B7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="B8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="5" t="n">
         <v>11</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>RB3</t>
         </is>
@@ -734,7 +734,7 @@
       <c r="B9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="5" t="n">
         <v>5</v>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -762,7 +762,7 @@
       <c r="B10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>RB4</t>
         </is>
@@ -894,7 +894,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>RB5</t>
         </is>
@@ -902,8 +902,8 @@
       <c r="B15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C15" s="6" t="n">
-        <v>15</v>
+      <c r="C15" s="5" t="n">
+        <v>17</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>RB6</t>
         </is>
@@ -1006,7 +1006,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>RB7</t>
         </is>
@@ -1042,8 +1042,8 @@
       <c r="B20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="4" t="n">
-        <v>30</v>
+      <c r="C20" s="9" t="n">
+        <v>37</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>RB8</t>
         </is>
@@ -1071,7 +1071,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
       <c r="B22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="5" t="n">
         <v>18</v>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1126,8 +1126,8 @@
       <c r="B23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>31</v>
+      <c r="C23" s="9" t="n">
+        <v>43</v>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>RB9</t>
         </is>
@@ -1182,7 +1182,7 @@
       <c r="B25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C25" s="5" t="n">
         <v>22</v>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1210,8 +1210,8 @@
       <c r="B26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C26" s="6" t="n">
-        <v>25</v>
+      <c r="C26" s="5" t="n">
+        <v>26</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>RB10</t>
         </is>
@@ -1267,7 +1267,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>RB11</t>
         </is>
@@ -1351,7 +1351,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -1378,8 +1378,8 @@
       <c r="B32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="C32" s="6" t="n">
-        <v>26</v>
+      <c r="C32" s="5" t="n">
+        <v>29</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="9" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>RB12</t>
         </is>
@@ -1491,7 +1491,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
@@ -1518,8 +1518,8 @@
       <c r="B37" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="C37" s="4" t="n">
-        <v>43</v>
+      <c r="C37" s="7" t="n">
+        <v>24</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -1546,8 +1546,8 @@
       <c r="B38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="C38" s="6" t="n">
-        <v>41</v>
+      <c r="C38" s="5" t="n">
+        <v>44</v>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
@@ -1574,8 +1574,8 @@
       <c r="B39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="C39" s="6" t="n">
-        <v>32</v>
+      <c r="C39" s="11" t="n">
+        <v>27</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>RB13</t>
         </is>
@@ -1630,8 +1630,8 @@
       <c r="B41" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="C41" s="6" t="n">
-        <v>38</v>
+      <c r="C41" s="5" t="n">
+        <v>36</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>RB14</t>
         </is>
@@ -1659,7 +1659,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>RB15</t>
         </is>
@@ -1687,7 +1687,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
@@ -1714,8 +1714,8 @@
       <c r="B44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="C44" s="6" t="n">
-        <v>46</v>
+      <c r="C44" s="4" t="n">
+        <v>48</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
@@ -1742,8 +1742,8 @@
       <c r="B45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="C45" s="4" t="n">
-        <v>55</v>
+      <c r="C45" s="9" t="n">
+        <v>59</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>RB16</t>
         </is>
@@ -1771,7 +1771,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="6" t="inlineStr">
         <is>
           <t>RB17</t>
         </is>
@@ -1827,7 +1827,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>RB18</t>
         </is>
@@ -1855,7 +1855,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -1882,8 +1882,8 @@
       <c r="B50" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="C50" s="6" t="n">
-        <v>50</v>
+      <c r="C50" s="4" t="n">
+        <v>53</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
@@ -1910,8 +1910,8 @@
       <c r="B51" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="C51" s="4" t="n">
-        <v>54</v>
+      <c r="C51" s="5" t="n">
+        <v>51</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
@@ -1938,8 +1938,8 @@
       <c r="B52" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="C52" s="6" t="n">
-        <v>48</v>
+      <c r="C52" s="5" t="n">
+        <v>46</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
@@ -1966,8 +1966,8 @@
       <c r="B53" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="C53" s="6" t="n">
-        <v>68</v>
+      <c r="C53" s="5" t="n">
+        <v>58</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
@@ -1994,8 +1994,8 @@
       <c r="B54" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="C54" s="6" t="n">
-        <v>49</v>
+      <c r="C54" s="5" t="n">
+        <v>52</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>RB19</t>
         </is>
@@ -2050,8 +2050,8 @@
       <c r="B56" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="C56" s="6" t="n">
-        <v>56</v>
+      <c r="C56" s="5" t="n">
+        <v>60</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       <c r="B57" s="3" t="n">
         <v>56</v>
       </c>
-      <c r="C57" s="6" t="n">
+      <c r="C57" s="5" t="n">
         <v>47</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>RB20</t>
         </is>
@@ -2106,8 +2106,8 @@
       <c r="B58" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="C58" s="6" t="n">
-        <v>60</v>
+      <c r="C58" s="5" t="n">
+        <v>68</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
@@ -2134,8 +2134,8 @@
       <c r="B59" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="C59" s="6" t="n">
-        <v>64</v>
+      <c r="C59" s="5" t="n">
+        <v>62</v>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
@@ -2162,8 +2162,8 @@
       <c r="B60" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="C60" s="6" t="n">
-        <v>62</v>
+      <c r="C60" s="5" t="n">
+        <v>50</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>RB21</t>
         </is>
@@ -2190,8 +2190,8 @@
       <c r="B61" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="C61" s="6" t="n">
-        <v>59</v>
+      <c r="C61" s="5" t="n">
+        <v>63</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>RB22</t>
         </is>
@@ -2218,8 +2218,8 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="7" t="n">
-        <v>52</v>
+      <c r="C62" s="11" t="n">
+        <v>56</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="inlineStr">
+      <c r="A63" s="6" t="inlineStr">
         <is>
           <t>RB23</t>
         </is>
@@ -2247,7 +2247,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>RB24</t>
         </is>
@@ -2303,7 +2303,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       <c r="B66" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="C66" s="6" t="n">
+      <c r="C66" s="5" t="n">
         <v>71</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -2359,7 +2359,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
@@ -2386,8 +2386,8 @@
       <c r="B68" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="C68" s="6" t="n">
-        <v>75</v>
+      <c r="C68" s="5" t="n">
+        <v>77</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
@@ -2414,8 +2414,8 @@
       <c r="B69" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="C69" s="6" t="n">
-        <v>81</v>
+      <c r="C69" s="5" t="n">
+        <v>79</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>RB25</t>
         </is>
@@ -2442,8 +2442,8 @@
       <c r="B70" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="C70" s="6" t="n">
-        <v>67</v>
+      <c r="C70" s="11" t="n">
+        <v>64</v>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>RB26</t>
         </is>
@@ -2471,7 +2471,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
@@ -2498,8 +2498,8 @@
       <c r="B72" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="C72" s="6" t="n">
-        <v>95</v>
+      <c r="C72" s="5" t="n">
+        <v>81</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
@@ -2526,8 +2526,8 @@
       <c r="B73" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="C73" s="6" t="n">
-        <v>72</v>
+      <c r="C73" s="5" t="n">
+        <v>65</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="9" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>RB27</t>
         </is>
@@ -2610,8 +2610,8 @@
       <c r="B76" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="C76" s="11" t="n">
-        <v>69</v>
+      <c r="C76" s="7" t="n">
+        <v>67</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
@@ -2638,8 +2638,8 @@
       <c r="B77" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C77" s="6" t="n">
-        <v>86</v>
+      <c r="C77" s="9" t="n">
+        <v>94</v>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
@@ -2666,8 +2666,8 @@
       <c r="B78" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="C78" s="6" t="n">
-        <v>61</v>
+      <c r="C78" s="5" t="n">
+        <v>75</v>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
@@ -2694,8 +2694,8 @@
       <c r="B79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C79" s="6" t="n">
-        <v>76</v>
+      <c r="C79" s="5" t="n">
+        <v>78</v>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
@@ -2722,8 +2722,8 @@
       <c r="B80" s="3" t="n">
         <v>79</v>
       </c>
-      <c r="C80" s="6" t="n">
-        <v>74</v>
+      <c r="C80" s="5" t="n">
+        <v>72</v>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="9" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>RB28</t>
         </is>
@@ -2779,7 +2779,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="inlineStr">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>RB29</t>
         </is>
@@ -2806,8 +2806,8 @@
       <c r="B83" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="C83" s="7" t="n">
-        <v>66</v>
+      <c r="C83" s="5" t="n">
+        <v>82</v>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>83</v>
       </c>
       <c r="C84" s="9" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="inlineStr">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>RB30</t>
         </is>
@@ -2882,7 +2882,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>RB31</t>
         </is>
@@ -2890,8 +2890,8 @@
       <c r="B86" s="3" t="n">
         <v>85</v>
       </c>
-      <c r="C86" s="6" t="n">
-        <v>103</v>
+      <c r="C86" s="5" t="n">
+        <v>96</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
@@ -2918,8 +2918,8 @@
       <c r="B87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="C87" s="6" t="n">
-        <v>79</v>
+      <c r="C87" s="5" t="n">
+        <v>76</v>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="9" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="inlineStr">
+      <c r="A90" s="6" t="inlineStr">
         <is>
           <t>RB32</t>
         </is>
@@ -3002,8 +3002,8 @@
       <c r="B90" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="C90" s="6" t="n">
-        <v>94</v>
+      <c r="C90" s="5" t="n">
+        <v>107</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="9" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
@@ -3058,8 +3058,8 @@
       <c r="B92" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="C92" s="9" t="n">
-        <v>112</v>
+      <c r="C92" s="5" t="n">
+        <v>98</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
@@ -3086,8 +3086,8 @@
       <c r="B93" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="C93" s="6" t="n">
-        <v>84</v>
+      <c r="C93" s="11" t="n">
+        <v>66</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="9" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
@@ -3142,8 +3142,8 @@
       <c r="B95" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="C95" s="6" t="n">
-        <v>96</v>
+      <c r="C95" s="5" t="n">
+        <v>99</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
@@ -3170,8 +3170,8 @@
       <c r="B96" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="C96" s="6" t="n">
-        <v>90</v>
+      <c r="C96" s="5" t="n">
+        <v>85</v>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
@@ -3198,8 +3198,8 @@
       <c r="B97" s="3" t="n">
         <v>96</v>
       </c>
-      <c r="C97" s="6" t="n">
-        <v>78</v>
+      <c r="C97" s="5" t="n">
+        <v>84</v>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
@@ -3226,8 +3226,8 @@
       <c r="B98" s="3" t="n">
         <v>97</v>
       </c>
-      <c r="C98" s="6" t="n">
-        <v>121</v>
+      <c r="C98" s="5" t="n">
+        <v>129</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>RB33</t>
         </is>
@@ -3255,7 +3255,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
@@ -3282,521 +3282,521 @@
       <c r="B100" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="C100" s="6" t="n">
+      <c r="C100" s="9" t="n">
+        <v>117</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Patrick Mahomes</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>KC (5)</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>QB14</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="C101" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Bo Nix</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>DEN (10)</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>RB34</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="C102" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Kenny Gainwell</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>TB (10)</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>QB15</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>97</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Matthew Stafford</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>LAR (11)</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>WR46</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="n">
         <v>104</v>
       </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>Patrick Mahomes</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>KC (5)</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="inlineStr">
+      <c r="C104" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>Quentin Johnston</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>LAC (7)</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>TE10</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="C105" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Jake Ferguson</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>DAL (14)</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>WR47</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="C106" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Jordan Addison</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>MIN (6)</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>RB35</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="C107" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>J.K. Dobbins</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>DEN (10)</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>RB36</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="C108" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Aaron Jones</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>MIN (6)</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>QB16</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="C109" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>Jared Goff</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>DET (6)</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>WR45</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="C101" s="6" t="n">
-        <v>91</v>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>Ricky Pearsall</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>RB37</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="C110" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Blake Corum</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>LAR (11)</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>TE11</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="C111" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>George Kittle</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F101" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="10" t="inlineStr">
-        <is>
-          <t>QB14</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="n">
-        <v>101</v>
-      </c>
-      <c r="C102" s="6" t="n">
-        <v>97</v>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>Bo Nix</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>DEN (10)</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>WR48</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="C112" s="5" t="n">
+        <v>104</v>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>Jayden Reed</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>GB (11)</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>RB38</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="C113" s="7" t="n">
+        <v>92</v>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Rachaad White</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>WAS (7)</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>QB17</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="C114" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Kyler Murray</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>MIN (6)</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>RB34</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="n">
-        <v>102</v>
-      </c>
-      <c r="C103" s="6" t="n">
-        <v>142</v>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>Kenny Gainwell</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>TB (10)</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="10" t="inlineStr">
-        <is>
-          <t>QB15</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="n">
-        <v>103</v>
-      </c>
-      <c r="C104" s="6" t="n">
-        <v>102</v>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>Matthew Stafford</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>LAR (11)</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>TE12</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="C115" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Dalton Kincaid</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>BUF (7)</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>WR49</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="C116" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Khalil Shakir</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>BUF (7)</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>QB18</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="C117" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Jordan Love</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>GB (11)</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
         <is>
           <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>WR46</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="n">
-        <v>104</v>
-      </c>
-      <c r="C105" s="6" t="n">
-        <v>85</v>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>Quentin Johnston</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>LAC (7)</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="8" t="inlineStr">
-        <is>
-          <t>TE10</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="C106" s="6" t="n">
-        <v>140</v>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>Jake Ferguson</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>DAL (14)</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>WR47</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="n">
-        <v>106</v>
-      </c>
-      <c r="C107" s="6" t="n">
-        <v>83</v>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>Jordan Addison</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>MIN (6)</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="inlineStr">
-        <is>
-          <t>RB35</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="n">
-        <v>107</v>
-      </c>
-      <c r="C108" s="7" t="n">
-        <v>88</v>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>J.K. Dobbins</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>DEN (10)</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
-        <is>
-          <t>RB36</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="n">
-        <v>108</v>
-      </c>
-      <c r="C109" s="6" t="n">
-        <v>141</v>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>Aaron Jones</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>MIN (6)</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="10" t="inlineStr">
-        <is>
-          <t>QB16</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="n">
-        <v>109</v>
-      </c>
-      <c r="C110" s="6" t="n">
-        <v>114</v>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>Jared Goff</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>DET (6)</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="inlineStr">
-        <is>
-          <t>RB37</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="n">
-        <v>110</v>
-      </c>
-      <c r="C111" s="7" t="n">
-        <v>87</v>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>Blake Corum</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>LAR (11)</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="8" t="inlineStr">
-        <is>
-          <t>TE11</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="n">
-        <v>111</v>
-      </c>
-      <c r="C112" s="6" t="n">
-        <v>139</v>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>George Kittle</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>SF (8)</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>WR48</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="C113" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>Jayden Reed</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>GB (11)</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>RB38</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="C114" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>Rachaad White</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>WAS (7)</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="10" t="inlineStr">
-        <is>
-          <t>QB17</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="n">
-        <v>114</v>
-      </c>
-      <c r="C115" s="6" t="n">
-        <v>105</v>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>Kyler Murray</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>MIN (6)</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="8" t="inlineStr">
-        <is>
-          <t>TE12</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="n">
-        <v>115</v>
-      </c>
-      <c r="C116" s="11" t="n">
-        <v>106</v>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>Dalton Kincaid</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>BUF (7)</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>WR49</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="C117" s="9" t="n">
-        <v>150</v>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>Khalil Shakir</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>BUF (7)</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="10" t="inlineStr">
         <is>
-          <t>QB18</t>
+          <t>QB19</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>117</v>
-      </c>
-      <c r="C118" s="6" t="n">
-        <v>113</v>
+        <v>118</v>
+      </c>
+      <c r="C118" s="5" t="n">
+        <v>118</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Jordan Love</t>
+          <t>Baker Mayfield</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>GB (11)</t>
+          <t>TB (10)</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
@@ -3806,81 +3806,81 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="10" t="inlineStr">
-        <is>
-          <t>QB19</t>
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>TE13</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="C119" s="6" t="n">
-        <v>115</v>
+        <v>119</v>
+      </c>
+      <c r="C119" s="5" t="n">
+        <v>127</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Baker Mayfield</t>
+          <t>Isaiah Likely</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>TB (10)</t>
+          <t>NYG (8)</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="8" t="inlineStr">
-        <is>
-          <t>TE13</t>
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>WR50</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>119</v>
-      </c>
-      <c r="C120" s="6" t="n">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>132</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Isaiah Likely</t>
+          <t>Jayden Higgins</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>NYG (8)</t>
+          <t>HOU (8)</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>WR50</t>
+          <t>WR51</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="C121" s="4" t="n">
-        <v>131</v>
+        <v>121</v>
+      </c>
+      <c r="C121" s="11" t="n">
+        <v>86</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Jayden Higgins</t>
+          <t>Xavier Worthy</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>HOU (8)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -3890,109 +3890,109 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>WR51</t>
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>QB20</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="C122" s="9" t="n">
+        <v>165</v>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>Tyler Shough</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>TE14</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="C123" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="C122" s="11" t="n">
-        <v>89</v>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>Xavier Worthy</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>KC (5)</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="10" t="inlineStr">
-        <is>
-          <t>QB20</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="n">
-        <v>122</v>
-      </c>
-      <c r="C123" s="9" t="n">
-        <v>164</v>
-      </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Tyler Shough</t>
+          <t>Dallas Goedert</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>PHI (10)</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="8" t="inlineStr">
-        <is>
-          <t>TE14</t>
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>RB39</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="C124" s="5" t="n">
         <v>123</v>
       </c>
-      <c r="C124" s="11" t="n">
-        <v>118</v>
-      </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Dallas Goedert</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>PHI (10)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>RB39</t>
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>RB40</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>124</v>
-      </c>
-      <c r="C125" s="6" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="C125" s="7" t="n">
+        <v>106</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -4002,669 +4002,669 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="inlineStr">
-        <is>
-          <t>RB40</t>
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>WR52</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="C126" s="7" t="n">
-        <v>111</v>
+        <v>126</v>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>119</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>WR52</t>
+          <t>WR53</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="C127" s="6" t="n">
+        <v>127</v>
+      </c>
+      <c r="C127" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>Romeo Doubs</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>NE (11)</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>RB41</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="C128" s="7" t="n">
+        <v>93</v>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Jonathon Brooks</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>CAR (5)</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>RB42</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Tyrone Tracy</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>NYG (8)</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
+          <t>TE15</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="C130" s="11" t="n">
         <v>122</v>
       </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>KC Concepcion</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>CLE (11)</t>
-        </is>
-      </c>
-      <c r="F127" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>WR53</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="C128" s="4" t="n">
-        <v>136</v>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>Romeo Doubs</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="inlineStr">
-        <is>
-          <t>NE (11)</t>
-        </is>
-      </c>
-      <c r="F128" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="5" t="inlineStr">
-        <is>
-          <t>RB41</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="C129" s="11" t="n">
-        <v>123</v>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>Jonathon Brooks</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Mark Andrews</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>BAL (13)</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>QB21</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Malik Willis</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>WR54</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="C132" s="5" t="n">
+        <v>111</v>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Jalen Coker</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
         <is>
           <t>CAR (5)</t>
         </is>
       </c>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>RB42</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="C130" s="6" t="n">
-        <v>143</v>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>Tyrone Tracy</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>NYG (8)</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="8" t="inlineStr">
-        <is>
-          <t>TE15</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="C131" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>Mark Andrews</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>BAL (13)</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="10" t="inlineStr">
-        <is>
-          <t>QB21</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="n">
-        <v>131</v>
-      </c>
-      <c r="C132" s="6" t="n">
-        <v>132</v>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>Malik Willis</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="inlineStr">
-        <is>
-          <t>MIA (6)</t>
-        </is>
-      </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>WR54</t>
+          <t>WR55</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>132</v>
-      </c>
-      <c r="C133" s="6" t="n">
+        <v>133</v>
+      </c>
+      <c r="C133" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Matthew Golden</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>GB (11)</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="inlineStr">
+        <is>
+          <t>QB22</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>Jalen Coker</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>CAR (5)</t>
-        </is>
-      </c>
-      <c r="F133" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>WR55</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="n">
+      <c r="C134" s="9" t="n">
+        <v>164</v>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>C.J. Stroud</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>HOU (8)</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>RB43</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="C135" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Woody Marks</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>HOU (8)</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>RB44</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="C136" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>Tyler Allgeier</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>ARI (14)</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>RB45</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="C137" s="9" t="n">
+        <v>238</v>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Zach Charbonnet</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>QB23</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="C138" s="9" t="n">
+        <v>166</v>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>Sam Darnold</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>RB46</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="C139" s="7" t="n">
+        <v>108</v>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Chris Rodriguez</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>JAC (7)</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>RB47</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="C140" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>Tyjae Spears</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>TEN (9)</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>TE16</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="C141" s="5" t="n">
+        <v>173</v>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Juwan Johnson</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>RB48</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="n">
+        <v>142</v>
+      </c>
+      <c r="C142" s="5" t="n">
+        <v>182</v>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Dylan Sampson</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>RB49</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="C143" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Isiah Pacheco</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>DET (6)</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>RB50</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="C144" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Alvin Kamara</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>QB24</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="C145" s="9" t="n">
+        <v>199</v>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Cam Ward</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>TEN (9)</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>WR56</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="C146" s="5" t="n">
         <v>133</v>
       </c>
-      <c r="C134" s="11" t="n">
-        <v>99</v>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>Matthew Golden</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>GB (11)</t>
-        </is>
-      </c>
-      <c r="F134" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="10" t="inlineStr">
-        <is>
-          <t>QB22</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="n">
-        <v>134</v>
-      </c>
-      <c r="C135" s="9" t="n">
-        <v>163</v>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>C.J. Stroud</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>HOU (8)</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="5" t="inlineStr">
-        <is>
-          <t>RB43</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="n">
-        <v>135</v>
-      </c>
-      <c r="C136" s="6" t="n">
-        <v>151</v>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>Woody Marks</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>HOU (8)</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="5" t="inlineStr">
-        <is>
-          <t>RB44</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="n">
-        <v>136</v>
-      </c>
-      <c r="C137" s="6" t="n">
-        <v>168</v>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>Tyler Allgeier</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>ARI (14)</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="5" t="inlineStr">
-        <is>
-          <t>RB45</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="C138" s="9" t="n">
-        <v>244</v>
-      </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>Zach Charbonnet</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="inlineStr">
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Rashid Shaheed</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F138" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="10" t="inlineStr">
-        <is>
-          <t>QB23</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="n">
-        <v>138</v>
-      </c>
-      <c r="C139" s="9" t="n">
-        <v>165</v>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>Sam Darnold</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>SEA (11)</t>
-        </is>
-      </c>
-      <c r="F139" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>RB46</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="n">
-        <v>139</v>
-      </c>
-      <c r="C140" s="7" t="n">
-        <v>110</v>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>Chris Rodriguez</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t>TE17</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="C147" s="5" t="n">
+        <v>180</v>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Brenton Strange</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F140" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="5" t="inlineStr">
-        <is>
-          <t>RB47</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="C141" s="6" t="n">
-        <v>152</v>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>Tyjae Spears</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>TEN (9)</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="8" t="inlineStr">
-        <is>
-          <t>TE16</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="n">
-        <v>141</v>
-      </c>
-      <c r="C142" s="6" t="n">
-        <v>185</v>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t>Juwan Johnson</t>
-        </is>
-      </c>
-      <c r="E142" s="3" t="inlineStr">
-        <is>
-          <t>NO (8)</t>
-        </is>
-      </c>
-      <c r="F142" s="3" t="inlineStr">
+      <c r="F147" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="5" t="inlineStr">
-        <is>
-          <t>RB48</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="C143" s="6" t="n">
-        <v>183</v>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>Dylan Sampson</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>CLE (11)</t>
-        </is>
-      </c>
-      <c r="F143" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="5" t="inlineStr">
-        <is>
-          <t>RB49</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="n">
-        <v>143</v>
-      </c>
-      <c r="C144" s="6" t="n">
-        <v>169</v>
-      </c>
-      <c r="D144" s="3" t="inlineStr">
-        <is>
-          <t>Isiah Pacheco</t>
-        </is>
-      </c>
-      <c r="E144" s="3" t="inlineStr">
-        <is>
-          <t>DET (6)</t>
-        </is>
-      </c>
-      <c r="F144" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="5" t="inlineStr">
-        <is>
-          <t>RB50</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="n">
-        <v>144</v>
-      </c>
-      <c r="C145" s="6" t="n">
-        <v>171</v>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>Alvin Kamara</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>NO (8)</t>
-        </is>
-      </c>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="10" t="inlineStr">
-        <is>
-          <t>QB24</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="C146" s="9" t="n">
-        <v>204</v>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>Cam Ward</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>TEN (9)</t>
-        </is>
-      </c>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>WR56</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="n">
-        <v>146</v>
-      </c>
-      <c r="C147" s="6" t="n">
-        <v>133</v>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>Rashid Shaheed</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="inlineStr">
-        <is>
-          <t>SEA (11)</t>
-        </is>
-      </c>
-      <c r="F147" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
     <row r="148">
-      <c r="A148" s="8" t="inlineStr">
-        <is>
-          <t>TE17</t>
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>WR57</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>147</v>
-      </c>
-      <c r="C148" s="6" t="n">
-        <v>186</v>
+        <v>148</v>
+      </c>
+      <c r="C148" s="9" t="n">
+        <v>190</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Brenton Strange</t>
+          <t>Omar Cooper</t>
         </is>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>JAC (7)</t>
+          <t>NYJ (13)</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>WR57</t>
+          <t>WR58</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C149" s="9" t="n">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Omar Cooper</t>
+          <t>Denzel Boston</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>NYJ (13)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -4676,18 +4676,18 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>WR58</t>
+          <t>WR59</t>
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>149</v>
-      </c>
-      <c r="C150" s="9" t="n">
-        <v>225</v>
+        <v>150</v>
+      </c>
+      <c r="C150" s="4" t="n">
+        <v>189</v>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Denzel Boston</t>
+          <t>Jerry Jeudy</t>
         </is>
       </c>
       <c r="E150" s="3" t="inlineStr">
@@ -4702,53 +4702,53 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>WR59</t>
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t>QB25</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Jerry Jeudy</t>
+          <t>Daniel Jones</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>IND (13)</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="10" t="inlineStr">
         <is>
-          <t>QB25</t>
+          <t>QB26</t>
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C152" s="4" t="n">
         <v>177</v>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Daniel Jones</t>
+          <t>Bryce Young</t>
         </is>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>IND (13)</t>
+          <t>CAR (5)</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
@@ -4758,81 +4758,81 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="10" t="inlineStr">
-        <is>
-          <t>QB26</t>
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>WR60</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Jauan Jennings</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>CAR (5)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>WR60</t>
+      <c r="A154" s="8" t="inlineStr">
+        <is>
+          <t>TE18</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>153</v>
-      </c>
-      <c r="C154" s="4" t="n">
-        <v>201</v>
+        <v>154</v>
+      </c>
+      <c r="C154" s="5" t="n">
+        <v>172</v>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Jauan Jennings</t>
+          <t>Chig Okonkwo</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>TE18</t>
+          <t>TE19</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>154</v>
-      </c>
-      <c r="C155" s="6" t="n">
-        <v>166</v>
+        <v>155</v>
+      </c>
+      <c r="C155" s="5" t="n">
+        <v>187</v>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Chig Okonkwo</t>
+          <t>Oronde Gadsden</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -4844,81 +4844,81 @@
     <row r="156">
       <c r="A156" s="8" t="inlineStr">
         <is>
-          <t>TE19</t>
+          <t>TE20</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>155</v>
-      </c>
-      <c r="C156" s="6" t="n">
-        <v>196</v>
+        <v>156</v>
+      </c>
+      <c r="C156" s="5" t="n">
+        <v>186</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Oronde Gadsden</t>
+          <t>Hunter Henry</t>
         </is>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
+          <t>NE (11)</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>RB51</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="C157" s="5" t="n">
+        <v>228</v>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Jonah Coleman</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>DEN (10)</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>RB52</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="C158" s="7" t="n">
+        <v>124</v>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Keaton Mitchell</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F156" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="8" t="inlineStr">
-        <is>
-          <t>TE20</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="C157" s="6" t="n">
-        <v>195</v>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>Hunter Henry</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>NE (11)</t>
-        </is>
-      </c>
-      <c r="F157" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="5" t="inlineStr">
-        <is>
-          <t>RB51</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="C158" s="6" t="n">
-        <v>228</v>
-      </c>
-      <c r="D158" s="3" t="inlineStr">
-        <is>
-          <t>Jonah Coleman</t>
-        </is>
-      </c>
-      <c r="E158" s="3" t="inlineStr">
-        <is>
-          <t>DEN (10)</t>
-        </is>
-      </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
           <t>RB</t>
@@ -4926,53 +4926,53 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="inlineStr">
-        <is>
-          <t>RB52</t>
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>WR61</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>159</v>
-      </c>
-      <c r="C159" s="7" t="n">
-        <v>125</v>
+        <v>160</v>
+      </c>
+      <c r="C159" s="4" t="n">
+        <v>188</v>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Keaton Mitchell</t>
+          <t>Adonai Mitchell</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>NYJ (13)</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>WR61</t>
+          <t>WR62</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="C160" s="4" t="n">
-        <v>179</v>
+        <v>161</v>
+      </c>
+      <c r="C160" s="5" t="n">
+        <v>155</v>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Adonai Mitchell</t>
+          <t>Jalen McMillan</t>
         </is>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>NYJ (13)</t>
+          <t>TB (10)</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
@@ -4984,23 +4984,23 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>WR62</t>
+          <t>WR63</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="C161" s="6" t="n">
-        <v>181</v>
+        <v>162</v>
+      </c>
+      <c r="C161" s="4" t="n">
+        <v>208</v>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Tre Tucker</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>TB (10)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -5010,249 +5010,249 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>WR63</t>
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>RB53</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="C162" s="4" t="n">
-        <v>207</v>
+        <v>164</v>
+      </c>
+      <c r="C162" s="5" t="n">
+        <v>169</v>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Tre Tucker</t>
+          <t>Brian Robinson</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>ATL (11)</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="5" t="inlineStr">
-        <is>
-          <t>RB53</t>
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>RB54</t>
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>164</v>
-      </c>
-      <c r="C163" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="C163" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Tank Bigsby</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>PHI (10)</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="8" t="inlineStr">
+        <is>
+          <t>TE21</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="C164" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Dalton Schultz</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>HOU (8)</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>WR64</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="C165" s="5" t="n">
+        <v>157</v>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Travis Hunter</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>JAC (7)</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>RB55</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="C166" s="4" t="n">
+        <v>218</v>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Braelon Allen</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>NYJ (13)</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>WR65</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="n">
         <v>170</v>
       </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>Brian Robinson</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="inlineStr">
-        <is>
-          <t>ATL (11)</t>
-        </is>
-      </c>
-      <c r="F163" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="5" t="inlineStr">
-        <is>
-          <t>RB54</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="n">
-        <v>165</v>
-      </c>
-      <c r="C164" s="6" t="n">
-        <v>167</v>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>Tank Bigsby</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>PHI (10)</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="8" t="inlineStr">
-        <is>
-          <t>TE21</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="C165" s="4" t="n">
-        <v>215</v>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>Dalton Schultz</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>HOU (8)</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="inlineStr">
+      <c r="C167" s="5" t="n">
+        <v>193</v>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Tre' Harris</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>LAC (7)</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="8" t="inlineStr">
+        <is>
+          <t>TE22</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="C168" s="4" t="n">
+        <v>213</v>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>T.J. Hockenson</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>MIN (6)</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>WR64</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="C166" s="6" t="n">
-        <v>147</v>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>Travis Hunter</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>JAC (7)</t>
-        </is>
-      </c>
-      <c r="F166" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="5" t="inlineStr">
-        <is>
-          <t>RB55</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="n">
-        <v>169</v>
-      </c>
-      <c r="C167" s="6" t="n">
-        <v>182</v>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>Braelon Allen</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="inlineStr">
-        <is>
-          <t>NYJ (13)</t>
-        </is>
-      </c>
-      <c r="F167" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>WR65</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="C168" s="6" t="n">
-        <v>178</v>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>Tre' Harris</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="inlineStr">
-        <is>
-          <t>LAC (7)</t>
-        </is>
-      </c>
-      <c r="F168" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
     <row r="169">
-      <c r="A169" s="8" t="inlineStr">
-        <is>
-          <t>TE22</t>
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>WR66</t>
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C169" s="4" t="n">
-        <v>213</v>
+        <v>271</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
-          <t>T.J. Hockenson</t>
+          <t>Troy Franklin</t>
         </is>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>DEN (10)</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>WR66</t>
+          <t>WR67</t>
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>296</v>
+        <v>235</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Troy Franklin</t>
+          <t>Kayshon Boutte</t>
         </is>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>DEN (10)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
@@ -5264,23 +5264,23 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>WR67</t>
+          <t>WR68</t>
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="C171" s="4" t="n">
-        <v>240</v>
+        <v>176</v>
+      </c>
+      <c r="C171" s="5" t="n">
+        <v>191</v>
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Kayshon Boutte</t>
+          <t>Ryan Flournoy</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>DAL (14)</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
@@ -5292,23 +5292,23 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>WR68</t>
+          <t>WR69</t>
         </is>
       </c>
       <c r="B172" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="C172" s="4" t="n">
-        <v>203</v>
+        <v>177</v>
+      </c>
+      <c r="C172" s="7" t="n">
+        <v>134</v>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Ryan Flournoy</t>
+          <t>Stefon Diggs</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>DAL (14)</t>
+          <t>FA ()</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
@@ -5318,48 +5318,48 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>WR69</t>
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>RB56</t>
         </is>
       </c>
       <c r="B173" s="3" t="n">
-        <v>177</v>
-      </c>
-      <c r="C173" s="7" t="n">
-        <v>135</v>
+        <v>178</v>
+      </c>
+      <c r="C173" s="4" t="n">
+        <v>242</v>
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>Stefon Diggs</t>
+          <t>James Conner</t>
         </is>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>FA ()</t>
+          <t>ARI (14)</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="5" t="inlineStr">
-        <is>
-          <t>RB56</t>
+      <c r="A174" s="10" t="inlineStr">
+        <is>
+          <t>QB27</t>
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C174" s="4" t="n">
-        <v>276</v>
+        <v>239</v>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>James Conner</t>
+          <t>Jacoby Brissett</t>
         </is>
       </c>
       <c r="E174" s="3" t="inlineStr">
@@ -5369,114 +5369,114 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="10" t="inlineStr">
-        <is>
-          <t>QB27</t>
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>WR70</t>
         </is>
       </c>
       <c r="B175" s="3" t="n">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>Jacoby Brissett</t>
+          <t>Jaylin Noel</t>
         </is>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>ARI (14)</t>
+          <t>HOU (8)</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>WR70</t>
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>RB57</t>
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Jaylin Noel</t>
+          <t>Emanuel Wilson</t>
         </is>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>HOU (8)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="inlineStr">
-        <is>
-          <t>RB57</t>
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>WR71</t>
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>186</v>
-      </c>
-      <c r="C177" s="4" t="n">
-        <v>273</v>
+        <v>187</v>
+      </c>
+      <c r="C177" s="5" t="n">
+        <v>211</v>
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>Emanuel Wilson</t>
+          <t>Calvin Ridley</t>
         </is>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>TEN (9)</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>WR71</t>
+          <t>WR72</t>
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="C178" s="6" t="n">
-        <v>206</v>
+        <v>188</v>
+      </c>
+      <c r="C178" s="5" t="n">
+        <v>209</v>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Calvin Ridley</t>
+          <t>Isaac TeSlaa</t>
         </is>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>TEN (9)</t>
+          <t>DET (6)</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
@@ -5486,193 +5486,193 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>WR72</t>
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t>TE23</t>
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>188</v>
-      </c>
-      <c r="C179" s="6" t="n">
-        <v>208</v>
+        <v>191</v>
+      </c>
+      <c r="C179" s="5" t="n">
+        <v>212</v>
       </c>
       <c r="D179" s="3" t="inlineStr">
         <is>
-          <t>Isaac TeSlaa</t>
+          <t>Kenyon Sadiq</t>
         </is>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>DET (6)</t>
+          <t>NYJ (13)</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="8" t="inlineStr">
-        <is>
-          <t>TE23</t>
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>RB58</t>
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>191</v>
-      </c>
-      <c r="C180" s="6" t="n">
-        <v>216</v>
+        <v>192</v>
+      </c>
+      <c r="C180" s="4" t="n">
+        <v>262</v>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq</t>
+          <t>Emmett Johnson</t>
         </is>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>NYJ (13)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>RB59</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="n">
+        <v>194</v>
+      </c>
+      <c r="C181" s="4" t="n">
+        <v>263</v>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Kimani Vidal</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>LAC (7)</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>RB60</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="C182" s="5" t="n">
+        <v>204</v>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>Ray Davis</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>BUF (7)</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="8" t="inlineStr">
+        <is>
+          <t>TE24</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="C183" s="5" t="n">
+        <v>179</v>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>AJ Barner</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="inlineStr">
+        <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="5" t="inlineStr">
-        <is>
-          <t>RB58</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="C181" s="4" t="n">
-        <v>264</v>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>Emmett Johnson</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="inlineStr">
-        <is>
-          <t>KC (5)</t>
-        </is>
-      </c>
-      <c r="F181" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="5" t="inlineStr">
-        <is>
-          <t>RB59</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="C182" s="4" t="n">
-        <v>271</v>
-      </c>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>Kimani Vidal</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="inlineStr">
-        <is>
-          <t>LAC (7)</t>
-        </is>
-      </c>
-      <c r="F182" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="5" t="inlineStr">
-        <is>
-          <t>RB60</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="n">
-        <v>195</v>
-      </c>
-      <c r="C183" s="6" t="n">
-        <v>217</v>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>Ray Davis</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>BUF (7)</t>
-        </is>
-      </c>
-      <c r="F183" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
     <row r="184">
-      <c r="A184" s="8" t="inlineStr">
-        <is>
-          <t>TE24</t>
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>WR73</t>
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="C184" s="6" t="n">
-        <v>184</v>
+        <v>197</v>
+      </c>
+      <c r="C184" s="4" t="n">
+        <v>259</v>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>AJ Barner</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>NYG (8)</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>WR73</t>
+          <t>WR74</t>
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="C185" s="4" t="n">
-        <v>235</v>
+        <v>199</v>
+      </c>
+      <c r="C185" s="7" t="n">
+        <v>154</v>
       </c>
       <c r="D185" s="3" t="inlineStr">
         <is>
-          <t>Darnell Mooney</t>
+          <t>Jalen Nailor</t>
         </is>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>NYG (8)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
@@ -5684,23 +5684,23 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>WR74</t>
+          <t>WR75</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="C186" s="7" t="n">
-        <v>148</v>
+        <v>201</v>
+      </c>
+      <c r="C186" s="11" t="n">
+        <v>156</v>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Jalen Nailor</t>
+          <t>Deebo Samuel</t>
         </is>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>FA ()</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
@@ -5712,23 +5712,23 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>WR75</t>
+          <t>WR76</t>
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>201</v>
-      </c>
-      <c r="C187" s="6" t="n">
         <v>202</v>
       </c>
+      <c r="C187" s="5" t="n">
+        <v>206</v>
+      </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>Deebo Samuel</t>
+          <t>Malik Washington</t>
         </is>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>FA ()</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
@@ -5738,81 +5738,81 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>WR76</t>
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>RB61</t>
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="C188" s="4" t="n">
-        <v>242</v>
+        <v>204</v>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>217</v>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Malik Washington</t>
+          <t>Mike Washington</t>
         </is>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="inlineStr">
-        <is>
-          <t>RB61</t>
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>WR77</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>204</v>
-      </c>
-      <c r="C189" s="6" t="n">
-        <v>219</v>
+        <v>205</v>
+      </c>
+      <c r="C189" s="4" t="n">
+        <v>245</v>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>Mike Washington</t>
+          <t>Pat Bryant</t>
         </is>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>DEN (10)</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>WR77</t>
+          <t>WR78</t>
         </is>
       </c>
       <c r="B190" s="3" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C190" s="4" t="n">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Pat Bryant</t>
+          <t>Antonio Williams</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>DEN (10)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
@@ -5822,305 +5822,305 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="inlineStr">
-        <is>
-          <t>WR78</t>
+      <c r="A191" s="8" t="inlineStr">
+        <is>
+          <t>TE25</t>
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>206</v>
-      </c>
-      <c r="C191" s="6" t="n">
-        <v>236</v>
+        <v>207</v>
+      </c>
+      <c r="C191" s="5" t="n">
+        <v>233</v>
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Antonio Williams</t>
+          <t>Gunnar Helm</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
+          <t>TEN (9)</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>WR79</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="n">
+        <v>211</v>
+      </c>
+      <c r="C192" s="4" t="n">
+        <v>243</v>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>Dontayvion Wicks</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>PHI (10)</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t>RB62</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="n">
+        <v>212</v>
+      </c>
+      <c r="C193" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>Sean Tucker</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>TB (10)</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>RB63</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="n">
+        <v>213</v>
+      </c>
+      <c r="C194" s="4" t="n">
+        <v>272</v>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>Nicholas Singleton</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>TEN (9)</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>WR80</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="C195" s="4" t="n">
+        <v>274</v>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>Tank Dell</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>HOU (8)</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="10" t="inlineStr">
+        <is>
+          <t>QB28</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="n">
+        <v>219</v>
+      </c>
+      <c r="C196" s="5" t="n">
+        <v>216</v>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>Aaron Rodgers</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>PIT (9)</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>WR81</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="n">
+        <v>221</v>
+      </c>
+      <c r="C197" s="5" t="n">
+        <v>234</v>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>Cooper Kupp</t>
+        </is>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>RB64</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="C198" s="5" t="n">
+        <v>227</v>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>Kaytron Allen</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F191" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="8" t="inlineStr">
-        <is>
-          <t>TE25</t>
-        </is>
-      </c>
-      <c r="B192" s="3" t="n">
-        <v>207</v>
-      </c>
-      <c r="C192" s="4" t="n">
-        <v>239</v>
-      </c>
-      <c r="D192" s="3" t="inlineStr">
-        <is>
-          <t>Gunnar Helm</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>TEN (9)</t>
-        </is>
-      </c>
-      <c r="F192" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="inlineStr">
-        <is>
-          <t>WR79</t>
-        </is>
-      </c>
-      <c r="B193" s="3" t="n">
-        <v>211</v>
-      </c>
-      <c r="C193" s="4" t="n">
-        <v>258</v>
-      </c>
-      <c r="D193" s="3" t="inlineStr">
-        <is>
-          <t>Dontayvion Wicks</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="inlineStr">
-        <is>
-          <t>PHI (10)</t>
-        </is>
-      </c>
-      <c r="F193" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="5" t="inlineStr">
-        <is>
-          <t>RB62</t>
-        </is>
-      </c>
-      <c r="B194" s="3" t="n">
-        <v>212</v>
-      </c>
-      <c r="C194" s="6" t="n">
-        <v>243</v>
-      </c>
-      <c r="D194" s="3" t="inlineStr">
-        <is>
-          <t>Sean Tucker</t>
-        </is>
-      </c>
-      <c r="E194" s="3" t="inlineStr">
-        <is>
-          <t>TB (10)</t>
-        </is>
-      </c>
-      <c r="F194" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="5" t="inlineStr">
-        <is>
-          <t>RB63</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="n">
-        <v>213</v>
-      </c>
-      <c r="C195" s="4" t="n">
-        <v>297</v>
-      </c>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>Nicholas Singleton</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>TEN (9)</t>
-        </is>
-      </c>
-      <c r="F195" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="inlineStr">
-        <is>
-          <t>WR80</t>
-        </is>
-      </c>
-      <c r="B196" s="3" t="n">
-        <v>217</v>
-      </c>
-      <c r="C196" s="4" t="n">
-        <v>288</v>
-      </c>
-      <c r="D196" s="3" t="inlineStr">
-        <is>
-          <t>Tank Dell</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="inlineStr">
-        <is>
-          <t>HOU (8)</t>
-        </is>
-      </c>
-      <c r="F196" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="10" t="inlineStr">
-        <is>
-          <t>QB28</t>
-        </is>
-      </c>
-      <c r="B197" s="3" t="n">
-        <v>219</v>
-      </c>
-      <c r="C197" s="6" t="n">
-        <v>222</v>
-      </c>
-      <c r="D197" s="3" t="inlineStr">
-        <is>
-          <t>Aaron Rodgers</t>
-        </is>
-      </c>
-      <c r="E197" s="3" t="inlineStr">
-        <is>
-          <t>PIT (9)</t>
-        </is>
-      </c>
-      <c r="F197" s="3" t="inlineStr">
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="10" t="inlineStr">
+        <is>
+          <t>QB29</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="n">
+        <v>223</v>
+      </c>
+      <c r="C199" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>Geno Smith</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>NYJ (13)</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="2" t="inlineStr">
-        <is>
-          <t>WR81</t>
-        </is>
-      </c>
-      <c r="B198" s="3" t="n">
-        <v>221</v>
-      </c>
-      <c r="C198" s="6" t="n">
-        <v>233</v>
-      </c>
-      <c r="D198" s="3" t="inlineStr">
-        <is>
-          <t>Cooper Kupp</t>
-        </is>
-      </c>
-      <c r="E198" s="3" t="inlineStr">
-        <is>
-          <t>SEA (11)</t>
-        </is>
-      </c>
-      <c r="F198" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="5" t="inlineStr">
-        <is>
-          <t>RB64</t>
-        </is>
-      </c>
-      <c r="B199" s="3" t="n">
-        <v>222</v>
-      </c>
-      <c r="C199" s="6" t="n">
-        <v>229</v>
-      </c>
-      <c r="D199" s="3" t="inlineStr">
-        <is>
-          <t>Kaytron Allen</t>
-        </is>
-      </c>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>WAS (7)</t>
-        </is>
-      </c>
-      <c r="F199" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
     <row r="200">
-      <c r="A200" s="10" t="inlineStr">
-        <is>
-          <t>QB29</t>
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>WR83</t>
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>223</v>
-      </c>
-      <c r="C200" s="6" t="n">
-        <v>211</v>
+        <v>225</v>
+      </c>
+      <c r="C200" s="11" t="n">
+        <v>120</v>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Geno Smith</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>NYJ (13)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>WR83</t>
+          <t>WR84</t>
         </is>
       </c>
       <c r="B201" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="C201" s="6" t="n">
-        <v>227</v>
+        <v>228</v>
+      </c>
+      <c r="C201" s="5" t="n">
+        <v>226</v>
       </c>
       <c r="D201" s="3" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Germie Bernard</t>
         </is>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>PIT (9)</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
@@ -6132,23 +6132,23 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>WR84</t>
+          <t>WR85</t>
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>228</v>
-      </c>
-      <c r="C202" s="6" t="n">
-        <v>226</v>
+        <v>230</v>
+      </c>
+      <c r="C202" s="5" t="n">
+        <v>210</v>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Germie Bernard</t>
+          <t>Rashod Bateman</t>
         </is>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>PIT (9)</t>
+          <t>BAL (13)</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
@@ -6160,23 +6160,23 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>WR85</t>
+          <t>WR86</t>
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>230</v>
-      </c>
-      <c r="C203" s="4" t="n">
-        <v>283</v>
+        <v>232</v>
+      </c>
+      <c r="C203" s="5" t="n">
+        <v>236</v>
       </c>
       <c r="D203" s="3" t="inlineStr">
         <is>
-          <t>Rashod Bateman</t>
+          <t>Brandon Aiyuk</t>
         </is>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>BAL (13)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
@@ -6186,165 +6186,165 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>WR86</t>
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>RB65</t>
         </is>
       </c>
       <c r="B204" s="3" t="n">
-        <v>232</v>
-      </c>
-      <c r="C204" s="6" t="n">
+        <v>233</v>
+      </c>
+      <c r="C204" s="4" t="n">
+        <v>273</v>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>Jaylen Wright</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="10" t="inlineStr">
+        <is>
+          <t>QB30</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="n">
         <v>234</v>
       </c>
-      <c r="D204" s="3" t="inlineStr">
-        <is>
-          <t>Brandon Aiyuk</t>
-        </is>
-      </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>SF (8)</t>
-        </is>
-      </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="5" t="inlineStr">
-        <is>
-          <t>RB65</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="n">
-        <v>233</v>
-      </c>
-      <c r="C205" s="4" t="n">
-        <v>289</v>
+      <c r="C205" s="5" t="n">
+        <v>201</v>
       </c>
       <c r="D205" s="3" t="inlineStr">
         <is>
-          <t>Jaylen Wright</t>
+          <t>Fernando Mendoza</t>
         </is>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="10" t="inlineStr">
-        <is>
-          <t>QB30</t>
+      <c r="A206" s="8" t="inlineStr">
+        <is>
+          <t>TE26</t>
         </is>
       </c>
       <c r="B206" s="3" t="n">
-        <v>234</v>
-      </c>
-      <c r="C206" s="6" t="n">
-        <v>205</v>
+        <v>235</v>
+      </c>
+      <c r="C206" s="5" t="n">
+        <v>265</v>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Fernando Mendoza</t>
+          <t>Pat Freiermuth</t>
         </is>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>PIT (9)</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="8" t="inlineStr">
-        <is>
-          <t>TE26</t>
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>WR87</t>
         </is>
       </c>
       <c r="B207" s="3" t="n">
-        <v>235</v>
-      </c>
-      <c r="C207" s="4" t="n">
-        <v>275</v>
+        <v>237</v>
+      </c>
+      <c r="C207" s="5" t="n">
+        <v>256</v>
       </c>
       <c r="D207" s="3" t="inlineStr">
         <is>
-          <t>Pat Freiermuth</t>
+          <t>Zachariah Branch</t>
         </is>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>PIT (9)</t>
+          <t>ATL (11)</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="8" t="inlineStr">
+        <is>
+          <t>TE27</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="C208" s="5" t="n">
+        <v>220</v>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Cade Otton</t>
+        </is>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>TB (10)</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>WR87</t>
-        </is>
-      </c>
-      <c r="B208" s="3" t="n">
-        <v>237</v>
-      </c>
-      <c r="C208" s="6" t="n">
-        <v>260</v>
-      </c>
-      <c r="D208" s="3" t="inlineStr">
-        <is>
-          <t>Zachariah Branch</t>
-        </is>
-      </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>ATL (11)</t>
-        </is>
-      </c>
-      <c r="F208" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="8" t="inlineStr">
         <is>
-          <t>TE27</t>
+          <t>TE28</t>
         </is>
       </c>
       <c r="B209" s="3" t="n">
-        <v>238</v>
-      </c>
-      <c r="C209" s="6" t="n">
-        <v>224</v>
+        <v>239</v>
+      </c>
+      <c r="C209" s="5" t="n">
+        <v>267</v>
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>Cade Otton</t>
+          <t>David Njoku</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>TB (10)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
@@ -6354,81 +6354,81 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="8" t="inlineStr">
-        <is>
-          <t>TE28</t>
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>RB66</t>
         </is>
       </c>
       <c r="B210" s="3" t="n">
-        <v>239</v>
-      </c>
-      <c r="C210" s="4" t="n">
-        <v>280</v>
+        <v>240</v>
+      </c>
+      <c r="C210" s="5" t="n">
+        <v>237</v>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>David Njoku</t>
+          <t>Justice Hill</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>BAL (13)</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="5" t="inlineStr">
-        <is>
-          <t>RB66</t>
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>WR88</t>
         </is>
       </c>
       <c r="B211" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="C211" s="6" t="n">
-        <v>237</v>
+        <v>241</v>
+      </c>
+      <c r="C211" s="5" t="n">
+        <v>244</v>
       </c>
       <c r="D211" s="3" t="inlineStr">
         <is>
-          <t>Justice Hill</t>
+          <t>Jack Bech</t>
         </is>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>BAL (13)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>WR88</t>
+          <t>WR89</t>
         </is>
       </c>
       <c r="B212" s="3" t="n">
-        <v>241</v>
-      </c>
-      <c r="C212" s="6" t="n">
-        <v>259</v>
+        <v>242</v>
+      </c>
+      <c r="C212" s="5" t="n">
+        <v>276</v>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Jack Bech</t>
+          <t>Ted Hurst</t>
         </is>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>TB (10)</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
@@ -6438,63 +6438,63 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>WR89</t>
+      <c r="A213" s="8" t="inlineStr">
+        <is>
+          <t>TE29</t>
         </is>
       </c>
       <c r="B213" s="3" t="n">
-        <v>242</v>
-      </c>
-      <c r="C213" s="4" t="n">
-        <v>298</v>
+        <v>243</v>
+      </c>
+      <c r="C213" s="5" t="n">
+        <v>232</v>
       </c>
       <c r="D213" s="3" t="inlineStr">
         <is>
-          <t>Ted Hurst</t>
+          <t>Terrance Ferguson</t>
         </is>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>TB (10)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="8" t="inlineStr">
-        <is>
-          <t>TE29</t>
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>RB67</t>
         </is>
       </c>
       <c r="B214" s="3" t="n">
-        <v>243</v>
-      </c>
-      <c r="C214" s="6" t="n">
-        <v>257</v>
+        <v>244</v>
+      </c>
+      <c r="C214" s="5" t="n">
+        <v>275</v>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Terrance Ferguson</t>
+          <t>Ollie Gordon</t>
         </is>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="5" t="inlineStr">
+      <c r="A215" s="6" t="inlineStr">
         <is>
           <t>RB68</t>
         </is>
@@ -6502,8 +6502,8 @@
       <c r="B215" s="3" t="n">
         <v>245</v>
       </c>
-      <c r="C215" s="6" t="n">
-        <v>218</v>
+      <c r="C215" s="5" t="n">
+        <v>202</v>
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
@@ -6522,86 +6522,86 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="8" t="inlineStr">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>WR90</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="C216" s="5" t="n">
+        <v>277</v>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>Elic Ayomanor</t>
+        </is>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>TEN (9)</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="8" t="inlineStr">
         <is>
           <t>TE30</t>
         </is>
       </c>
-      <c r="B216" s="3" t="n">
+      <c r="B217" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="C216" s="6" t="n">
-        <v>238</v>
-      </c>
-      <c r="D216" s="3" t="inlineStr">
+      <c r="C217" s="5" t="n">
+        <v>219</v>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
         <is>
           <t>Colby Parkinson</t>
         </is>
       </c>
-      <c r="E216" s="3" t="inlineStr">
+      <c r="E217" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="F216" s="3" t="inlineStr">
+      <c r="F217" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>WR91</t>
         </is>
       </c>
-      <c r="B217" s="3" t="n">
+      <c r="B218" s="3" t="n">
         <v>249</v>
       </c>
-      <c r="C217" s="4" t="n">
-        <v>291</v>
-      </c>
-      <c r="D217" s="3" t="inlineStr">
+      <c r="C218" s="5" t="n">
+        <v>278</v>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
         <is>
           <t>Keon Coleman</t>
         </is>
       </c>
-      <c r="E217" s="3" t="inlineStr">
+      <c r="E218" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F217" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="5" t="inlineStr">
-        <is>
-          <t>RB69</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="C218" s="4" t="n">
-        <v>292</v>
-      </c>
-      <c r="D218" s="3" t="inlineStr">
-        <is>
-          <t>Ty Johnson</t>
-        </is>
-      </c>
-      <c r="E218" s="3" t="inlineStr">
-        <is>
-          <t>BUF (7)</t>
-        </is>
-      </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
@@ -6614,8 +6614,8 @@
       <c r="B219" s="3" t="n">
         <v>251</v>
       </c>
-      <c r="C219" s="6" t="n">
-        <v>248</v>
+      <c r="C219" s="5" t="n">
+        <v>258</v>
       </c>
       <c r="D219" s="3" t="inlineStr">
         <is>
@@ -6642,8 +6642,8 @@
       <c r="B220" s="3" t="n">
         <v>252</v>
       </c>
-      <c r="C220" s="6" t="n">
-        <v>269</v>
+      <c r="C220" s="5" t="n">
+        <v>246</v>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
@@ -6670,8 +6670,8 @@
       <c r="B221" s="3" t="n">
         <v>254</v>
       </c>
-      <c r="C221" s="6" t="n">
-        <v>265</v>
+      <c r="C221" s="5" t="n">
+        <v>253</v>
       </c>
       <c r="D221" s="3" t="inlineStr">
         <is>
@@ -6698,8 +6698,8 @@
       <c r="B222" s="3" t="n">
         <v>255</v>
       </c>
-      <c r="C222" s="6" t="n">
-        <v>287</v>
+      <c r="C222" s="4" t="n">
+        <v>299</v>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
@@ -6718,137 +6718,137 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="5" t="inlineStr">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>WR95</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="n">
+        <v>256</v>
+      </c>
+      <c r="C223" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>Malachi Fields</t>
+        </is>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>NYG (8)</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="6" t="inlineStr">
         <is>
           <t>RB70</t>
         </is>
       </c>
-      <c r="B223" s="3" t="n">
+      <c r="B224" s="3" t="n">
         <v>257</v>
       </c>
-      <c r="C223" s="6" t="n">
-        <v>270</v>
-      </c>
-      <c r="D223" s="3" t="inlineStr">
+      <c r="C224" s="5" t="n">
+        <v>266</v>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
         <is>
           <t>DJ Giddens</t>
         </is>
       </c>
-      <c r="E223" s="3" t="inlineStr">
+      <c r="E224" s="3" t="inlineStr">
         <is>
           <t>IND (13)</t>
         </is>
       </c>
-      <c r="F223" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="8" t="inlineStr">
+      <c r="F224" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="8" t="inlineStr">
         <is>
           <t>TE32</t>
         </is>
       </c>
-      <c r="B224" s="3" t="n">
+      <c r="B225" s="3" t="n">
         <v>259</v>
       </c>
-      <c r="C224" s="6" t="n">
-        <v>274</v>
-      </c>
-      <c r="D224" s="3" t="inlineStr">
+      <c r="C225" s="5" t="n">
+        <v>264</v>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
         <is>
           <t>Eli Stowers</t>
         </is>
       </c>
-      <c r="E224" s="3" t="inlineStr">
+      <c r="E225" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F224" s="3" t="inlineStr">
+      <c r="F225" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>WR97</t>
         </is>
       </c>
-      <c r="B225" s="3" t="n">
+      <c r="B226" s="3" t="n">
         <v>260</v>
       </c>
-      <c r="C225" s="6" t="n">
-        <v>290</v>
-      </c>
-      <c r="D225" s="3" t="inlineStr">
+      <c r="C226" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
         <is>
           <t>Tory Horton</t>
         </is>
       </c>
-      <c r="E225" s="3" t="inlineStr">
+      <c r="E226" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F225" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="5" t="inlineStr">
-        <is>
-          <t>RB71</t>
-        </is>
-      </c>
-      <c r="B226" s="3" t="n">
-        <v>262</v>
-      </c>
-      <c r="C226" s="6" t="n">
-        <v>254</v>
-      </c>
-      <c r="D226" s="3" t="inlineStr">
-        <is>
-          <t>Jaydon Blue</t>
-        </is>
-      </c>
-      <c r="E226" s="3" t="inlineStr">
-        <is>
-          <t>DAL (14)</t>
-        </is>
-      </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>WR99</t>
+          <t>WR98</t>
         </is>
       </c>
       <c r="B227" s="3" t="n">
-        <v>263</v>
-      </c>
-      <c r="C227" s="6" t="n">
-        <v>268</v>
+        <v>261</v>
+      </c>
+      <c r="C227" s="5" t="n">
+        <v>284</v>
       </c>
       <c r="D227" s="3" t="inlineStr">
         <is>
-          <t>Chris Brazzell</t>
+          <t>Marvin Mims</t>
         </is>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>CAR (5)</t>
+          <t>DEN (10)</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
@@ -6858,557 +6858,557 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="10" t="inlineStr">
-        <is>
-          <t>QB31</t>
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>RB71</t>
         </is>
       </c>
       <c r="B228" s="3" t="n">
-        <v>266</v>
-      </c>
-      <c r="C228" s="6" t="n">
-        <v>256</v>
+        <v>262</v>
+      </c>
+      <c r="C228" s="5" t="n">
+        <v>250</v>
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa</t>
+          <t>Jaydon Blue</t>
         </is>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>ATL (11)</t>
+          <t>DAL (14)</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
+          <t>WR99</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="C229" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>Chris Brazzell</t>
+        </is>
+      </c>
+      <c r="E229" s="3" t="inlineStr">
+        <is>
+          <t>CAR (5)</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="8" t="inlineStr">
+        <is>
+          <t>TE33</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="C230" s="5" t="n">
+        <v>297</v>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>Mason Taylor</t>
+        </is>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>NYJ (13)</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="6" t="inlineStr">
+        <is>
+          <t>RB72</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="C231" s="5" t="n">
+        <v>283</v>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>Chris Brooks</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>GB (11)</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="10" t="inlineStr">
+        <is>
+          <t>QB31</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="C232" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>Tua Tagovailoa</t>
+        </is>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>ATL (11)</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
           <t>WR100</t>
         </is>
       </c>
-      <c r="B229" s="3" t="n">
+      <c r="B233" s="3" t="n">
         <v>267</v>
       </c>
-      <c r="C229" s="6" t="n">
-        <v>282</v>
-      </c>
-      <c r="D229" s="3" t="inlineStr">
+      <c r="C233" s="5" t="n">
+        <v>207</v>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
         <is>
           <t>Darius Slayton</t>
         </is>
       </c>
-      <c r="E229" s="3" t="inlineStr">
+      <c r="E233" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F229" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="5" t="inlineStr">
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="6" t="inlineStr">
         <is>
           <t>RB73</t>
         </is>
       </c>
-      <c r="B230" s="3" t="n">
+      <c r="B234" s="3" t="n">
         <v>269</v>
       </c>
-      <c r="C230" s="6" t="n">
-        <v>293</v>
-      </c>
-      <c r="D230" s="3" t="inlineStr">
+      <c r="C234" s="5" t="n">
+        <v>286</v>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
         <is>
           <t>Samaje Perine</t>
         </is>
       </c>
-      <c r="E230" s="3" t="inlineStr">
+      <c r="E234" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="F230" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="5" t="inlineStr">
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="6" t="inlineStr">
+        <is>
+          <t>RB74</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="C235" s="5" t="n">
+        <v>281</v>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>Isaiah Davis</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>NYJ (13)</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="6" t="inlineStr">
         <is>
           <t>RB75</t>
         </is>
       </c>
-      <c r="B231" s="3" t="n">
+      <c r="B236" s="3" t="n">
         <v>271</v>
       </c>
-      <c r="C231" s="6" t="n">
+      <c r="C236" s="5" t="n">
+        <v>279</v>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>Demond Claiborne</t>
+        </is>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>MIN (6)</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="6" t="inlineStr">
+        <is>
+          <t>RB76</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="C237" s="5" t="n">
+        <v>287</v>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>LeQuint Allen</t>
+        </is>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>JAC (7)</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="10" t="inlineStr">
+        <is>
+          <t>QB32</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="C238" s="5" t="n">
+        <v>252</v>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>Michael Penix</t>
+        </is>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
+        <is>
+          <t>ATL (11)</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>RB79</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="n">
+        <v>277</v>
+      </c>
+      <c r="C239" s="5" t="n">
+        <v>249</v>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Jordan James</t>
+        </is>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
+        <is>
+          <t>SF (8)</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="8" t="inlineStr">
+        <is>
+          <t>TE35</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="n">
         <v>278</v>
       </c>
-      <c r="D231" s="3" t="inlineStr">
-        <is>
-          <t>Demond Claiborne</t>
-        </is>
-      </c>
-      <c r="E231" s="3" t="inlineStr">
-        <is>
-          <t>MIN (6)</t>
-        </is>
-      </c>
-      <c r="F231" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="5" t="inlineStr">
-        <is>
-          <t>RB78</t>
-        </is>
-      </c>
-      <c r="B232" s="3" t="n">
-        <v>275</v>
-      </c>
-      <c r="C232" s="6" t="n">
-        <v>299</v>
-      </c>
-      <c r="D232" s="3" t="inlineStr">
-        <is>
-          <t>Seth McGowan</t>
-        </is>
-      </c>
-      <c r="E232" s="3" t="inlineStr">
-        <is>
-          <t>IND (13)</t>
-        </is>
-      </c>
-      <c r="F232" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="10" t="inlineStr">
-        <is>
-          <t>QB32</t>
-        </is>
-      </c>
-      <c r="B233" s="3" t="n">
-        <v>276</v>
-      </c>
-      <c r="C233" s="6" t="n">
-        <v>255</v>
-      </c>
-      <c r="D233" s="3" t="inlineStr">
-        <is>
-          <t>Michael Penix</t>
-        </is>
-      </c>
-      <c r="E233" s="3" t="inlineStr">
-        <is>
-          <t>ATL (11)</t>
-        </is>
-      </c>
-      <c r="F233" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="5" t="inlineStr">
-        <is>
-          <t>RB79</t>
-        </is>
-      </c>
-      <c r="B234" s="3" t="n">
-        <v>277</v>
-      </c>
-      <c r="C234" s="6" t="n">
-        <v>272</v>
-      </c>
-      <c r="D234" s="3" t="inlineStr">
-        <is>
-          <t>Jordan James</t>
-        </is>
-      </c>
-      <c r="E234" s="3" t="inlineStr">
-        <is>
-          <t>SF (8)</t>
-        </is>
-      </c>
-      <c r="F234" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="8" t="inlineStr">
-        <is>
-          <t>TE35</t>
-        </is>
-      </c>
-      <c r="B235" s="3" t="n">
-        <v>278</v>
-      </c>
-      <c r="C235" s="6" t="n">
+      <c r="C240" s="5" t="n">
         <v>214</v>
       </c>
-      <c r="D235" s="3" t="inlineStr">
+      <c r="D240" s="3" t="inlineStr">
         <is>
           <t>Greg Dulcich</t>
         </is>
       </c>
-      <c r="E235" s="3" t="inlineStr">
+      <c r="E240" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="F235" s="3" t="inlineStr">
+      <c r="F240" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>WR102</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="n">
-        <v>282</v>
-      </c>
-      <c r="C236" s="6" t="n">
-        <v>247</v>
-      </c>
-      <c r="D236" s="3" t="inlineStr">
-        <is>
-          <t>Tyquan Thornton</t>
-        </is>
-      </c>
-      <c r="E236" s="3" t="inlineStr">
-        <is>
-          <t>KC (5)</t>
-        </is>
-      </c>
-      <c r="F236" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="5" t="inlineStr">
-        <is>
-          <t>RB82</t>
-        </is>
-      </c>
-      <c r="B237" s="3" t="n">
-        <v>283</v>
-      </c>
-      <c r="C237" s="6" t="n">
-        <v>294</v>
-      </c>
-      <c r="D237" s="3" t="inlineStr">
-        <is>
-          <t>George Holani</t>
-        </is>
-      </c>
-      <c r="E237" s="3" t="inlineStr">
-        <is>
-          <t>SEA (11)</t>
-        </is>
-      </c>
-      <c r="F237" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>WR103</t>
-        </is>
-      </c>
-      <c r="B238" s="3" t="n">
-        <v>285</v>
-      </c>
-      <c r="C238" s="6" t="n">
-        <v>281</v>
-      </c>
-      <c r="D238" s="3" t="inlineStr">
-        <is>
-          <t>Devaughn Vele</t>
-        </is>
-      </c>
-      <c r="E238" s="3" t="inlineStr">
-        <is>
-          <t>NO (8)</t>
-        </is>
-      </c>
-      <c r="F238" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>WR105</t>
-        </is>
-      </c>
-      <c r="B239" s="3" t="n">
-        <v>290</v>
-      </c>
-      <c r="C239" s="6" t="n">
-        <v>261</v>
-      </c>
-      <c r="D239" s="3" t="inlineStr">
-        <is>
-          <t>Keenan Allen</t>
-        </is>
-      </c>
-      <c r="E239" s="3" t="inlineStr">
-        <is>
-          <t>LAC (7)</t>
-        </is>
-      </c>
-      <c r="F239" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="5" t="inlineStr">
-        <is>
-          <t>RB85</t>
-        </is>
-      </c>
-      <c r="B240" s="3" t="n">
-        <v>293</v>
-      </c>
-      <c r="C240" s="6" t="n">
-        <v>253</v>
-      </c>
-      <c r="D240" s="3" t="inlineStr">
-        <is>
-          <t>Kaelon Black</t>
-        </is>
-      </c>
-      <c r="E240" s="3" t="inlineStr">
-        <is>
-          <t>SF (8)</t>
-        </is>
-      </c>
-      <c r="F240" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
+          <t>WR102</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="C241" s="5" t="n">
+        <v>248</v>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>Tyquan Thornton</t>
+        </is>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>KC (5)</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>RB82</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="n">
+        <v>283</v>
+      </c>
+      <c r="C242" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>George Holani</t>
+        </is>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>WR103</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="C243" s="5" t="n">
+        <v>296</v>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Devaughn Vele</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>WR105</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="C244" s="5" t="n">
+        <v>257</v>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>Keenan Allen</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>LAC (7)</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="6" t="inlineStr">
+        <is>
+          <t>RB85</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="n">
+        <v>293</v>
+      </c>
+      <c r="C245" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>Kaelon Black</t>
+        </is>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>SF (8)</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
           <t>WR106</t>
         </is>
       </c>
-      <c r="B241" s="3" t="n">
+      <c r="B246" s="3" t="n">
         <v>294</v>
       </c>
-      <c r="C241" s="6" t="n">
-        <v>300</v>
-      </c>
-      <c r="D241" s="3" t="inlineStr">
+      <c r="C246" s="5" t="n">
+        <v>298</v>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
         <is>
           <t>Hollywood Brown</t>
         </is>
       </c>
-      <c r="E241" s="3" t="inlineStr">
+      <c r="E246" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F241" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="5" t="inlineStr">
-        <is>
-          <t>RB87</t>
-        </is>
-      </c>
-      <c r="B242" s="3" t="n">
-        <v>298</v>
-      </c>
-      <c r="C242" s="6" t="n">
-        <v>263</v>
-      </c>
-      <c r="D242" s="3" t="inlineStr">
-        <is>
-          <t>Emari Demercado</t>
-        </is>
-      </c>
-      <c r="E242" s="3" t="inlineStr">
-        <is>
-          <t>KC (5)</t>
-        </is>
-      </c>
-      <c r="F242" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="10" t="inlineStr">
-        <is>
-          <t>QB34</t>
-        </is>
-      </c>
-      <c r="B243" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="C243" s="6" t="n">
-        <v>246</v>
-      </c>
-      <c r="D243" s="3" t="inlineStr">
-        <is>
-          <t>Deshaun Watson</t>
-        </is>
-      </c>
-      <c r="E243" s="3" t="inlineStr">
-        <is>
-          <t>CLE (11)</t>
-        </is>
-      </c>
-      <c r="F243" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="8" t="inlineStr">
-        <is>
-          <t>TE37</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="C244" s="6" t="n">
-        <v>267</v>
-      </c>
-      <c r="D244" s="3" t="inlineStr">
-        <is>
-          <t>Mike Gesicki</t>
-        </is>
-      </c>
-      <c r="E244" s="3" t="inlineStr">
-        <is>
-          <t>CIN (6)</t>
-        </is>
-      </c>
-      <c r="F244" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="10" t="inlineStr">
-        <is>
-          <t>QB35</t>
-        </is>
-      </c>
-      <c r="B245" s="3" t="n">
-        <v>302</v>
-      </c>
-      <c r="C245" s="6" t="n">
-        <v>262</v>
-      </c>
-      <c r="D245" s="3" t="inlineStr">
-        <is>
-          <t>Kirk Cousins</t>
-        </is>
-      </c>
-      <c r="E245" s="3" t="inlineStr">
-        <is>
-          <t>LV (13)</t>
-        </is>
-      </c>
-      <c r="F245" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="5" t="inlineStr">
-        <is>
-          <t>RB90</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="n">
-        <v>304</v>
-      </c>
-      <c r="C246" s="6" t="n">
-        <v>277</v>
-      </c>
-      <c r="D246" s="3" t="inlineStr">
-        <is>
-          <t>Najee Harris</t>
-        </is>
-      </c>
-      <c r="E246" s="3" t="inlineStr">
-        <is>
-          <t>LAC (7)</t>
-        </is>
-      </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>WR108</t>
+          <t>WR107</t>
         </is>
       </c>
       <c r="B247" s="3" t="n">
-        <v>306</v>
-      </c>
-      <c r="C247" s="6" t="n">
-        <v>286</v>
+        <v>295</v>
+      </c>
+      <c r="C247" s="5" t="n">
+        <v>288</v>
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Mack Hollins</t>
         </is>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>BAL (13)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
@@ -7418,86 +7418,282 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>WR111</t>
+      <c r="A248" s="6" t="inlineStr">
+        <is>
+          <t>RB87</t>
         </is>
       </c>
       <c r="B248" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="C248" s="6" t="n">
-        <v>295</v>
+        <v>298</v>
+      </c>
+      <c r="C248" s="5" t="n">
+        <v>261</v>
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>Andrei Iosivas</t>
+          <t>Emari Demercado</t>
         </is>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>CIN (6)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>WR120</t>
+      <c r="A249" s="10" t="inlineStr">
+        <is>
+          <t>QB34</t>
         </is>
       </c>
       <c r="B249" s="3" t="n">
-        <v>335</v>
-      </c>
-      <c r="C249" s="6" t="n">
-        <v>285</v>
+        <v>299</v>
+      </c>
+      <c r="C249" s="5" t="n">
+        <v>241</v>
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Deshaun Watson</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="8" t="inlineStr">
         <is>
-          <t>TE45</t>
+          <t>TE37</t>
         </is>
       </c>
       <c r="B250" s="3" t="n">
-        <v>344</v>
-      </c>
-      <c r="C250" s="6" t="n">
-        <v>279</v>
+        <v>300</v>
+      </c>
+      <c r="C250" s="5" t="n">
+        <v>255</v>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>Dawson Knox</t>
+          <t>Mike Gesicki</t>
         </is>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>CIN (6)</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
           <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="10" t="inlineStr">
+        <is>
+          <t>QB35</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="n">
+        <v>302</v>
+      </c>
+      <c r="C251" s="5" t="n">
+        <v>251</v>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>Kirk Cousins</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>LV (13)</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>WR108</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="n">
+        <v>306</v>
+      </c>
+      <c r="C252" s="5" t="n">
+        <v>291</v>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
+        <is>
+          <t>BAL (13)</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>WR111</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="C253" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>Andrei Iosivas</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
+        <is>
+          <t>CIN (6)</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>WR119</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="n">
+        <v>334</v>
+      </c>
+      <c r="C254" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>Calvin Austin</t>
+        </is>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
+        <is>
+          <t>NYG (8)</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>WR120</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="n">
+        <v>335</v>
+      </c>
+      <c r="C255" s="5" t="n">
+        <v>269</v>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>Jalen Tolbert</t>
+        </is>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>WR123</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="n">
+        <v>347</v>
+      </c>
+      <c r="C256" s="5" t="n">
+        <v>294</v>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>Kendrick Bourne</t>
+        </is>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>ARI (14)</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>WR130</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="n">
+        <v>363</v>
+      </c>
+      <c r="C257" s="5" t="n">
+        <v>293</v>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>Treylon Burks</t>
+        </is>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>WAS (7)</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
         </is>
       </c>
     </row>

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F257"/>
+  <dimension ref="A1:G257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,15 +515,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Adjusted Rank Half PPR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Team (Bye)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Position Category</t>
         </is>
@@ -541,17 +546,20 @@
       <c r="C2" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Ja'Marr Chase</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -569,17 +577,20 @@
       <c r="C3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Puka Nacua</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -597,17 +608,20 @@
       <c r="C4" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Bijan Robinson</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>ATL (11)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -625,17 +639,20 @@
       <c r="C5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Jahmyr Gibbs</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -653,17 +670,20 @@
       <c r="C6" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Jaxon Smith-Njigba</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -681,17 +701,20 @@
       <c r="C7" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Amon-Ra St. Brown</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -709,17 +732,20 @@
       <c r="C8" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>CeeDee Lamb</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>DAL (14)</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -737,17 +763,20 @@
       <c r="C9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>Christian McCaffrey</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -765,17 +794,20 @@
       <c r="C10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>Justin Jefferson</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -793,17 +825,20 @@
       <c r="C11" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>Jonathan Taylor</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>IND (13)</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -821,17 +856,20 @@
       <c r="C12" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Drake London</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>ATL (11)</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -849,17 +887,20 @@
       <c r="C13" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>Nico Collins</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -877,17 +918,20 @@
       <c r="C14" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>A.J. Brown</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>NE (11)</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -905,17 +949,20 @@
       <c r="C15" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Ashton Jeanty</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -933,17 +980,20 @@
       <c r="C16" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>George Pickens</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>DAL (14)</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -961,17 +1011,20 @@
       <c r="C17" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Trey McBride</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -989,17 +1042,20 @@
       <c r="C18" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>De'Von Achane</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -1017,17 +1073,20 @@
       <c r="C19" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>James Cook</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -1045,17 +1104,20 @@
       <c r="C20" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Chris Olave</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1073,17 +1135,20 @@
       <c r="C21" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Chase Brown</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -1101,17 +1166,20 @@
       <c r="C22" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>Brock Bowers</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -1129,17 +1197,20 @@
       <c r="C23" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>Rashee Rice</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1157,17 +1228,20 @@
       <c r="C24" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Josh Allen</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -1185,17 +1259,20 @@
       <c r="C25" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Omarion Hampton</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -1213,17 +1290,20 @@
       <c r="C26" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>DeVonta Smith</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1241,17 +1321,20 @@
       <c r="C27" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Saquon Barkley</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -1269,17 +1352,20 @@
       <c r="C28" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Tetairoa McMillan</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>CAR (5)</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1297,17 +1383,20 @@
       <c r="C29" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Garrett Wilson</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1325,17 +1414,20 @@
       <c r="C30" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Kenneth Walker</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -1353,17 +1445,20 @@
       <c r="C31" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Zay Flowers</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1381,17 +1476,20 @@
       <c r="C32" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D32" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Tee Higgins</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1409,17 +1507,20 @@
       <c r="C33" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>Lamar Jackson</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -1437,17 +1538,20 @@
       <c r="C34" s="9" t="n">
         <v>61</v>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Drake Maye</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>NE (11)</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -1465,17 +1569,20 @@
       <c r="C35" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t>Ladd McConkey</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1493,17 +1600,20 @@
       <c r="C36" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Jeremiyah Love</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -1521,17 +1631,20 @@
       <c r="C37" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D37" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>Malik Nabers</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1549,17 +1662,20 @@
       <c r="C38" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D38" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Colston Loveland</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>CHI (10)</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -1577,17 +1693,20 @@
       <c r="C39" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Jaylen Waddle</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1605,17 +1724,20 @@
       <c r="C40" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="D40" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Derrick Henry</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -1633,17 +1755,20 @@
       <c r="C41" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="D41" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>Emeka Egbuka</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1661,17 +1786,20 @@
       <c r="C42" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="D42" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>Breece Hall</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -1689,17 +1817,20 @@
       <c r="C43" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Kyren Williams</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -1717,17 +1848,20 @@
       <c r="C44" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Terry McLaurin</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1745,17 +1879,20 @@
       <c r="C45" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Joe Burrow</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -1773,17 +1910,20 @@
       <c r="C46" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D46" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Josh Jacobs</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -1801,17 +1941,20 @@
       <c r="C47" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Luther Burden</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>CHI (10)</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1829,17 +1972,20 @@
       <c r="C48" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D48" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>Javonte Williams</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>DAL (14)</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -1857,17 +2003,20 @@
       <c r="C49" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Travis Etienne</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -1885,17 +2034,20 @@
       <c r="C50" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="D50" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>Davante Adams</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1913,17 +2065,20 @@
       <c r="C51" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>DJ Moore</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1941,17 +2096,20 @@
       <c r="C52" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>Jameson Williams</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -1969,17 +2127,20 @@
       <c r="C53" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D53" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Tyler Warren</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>IND (13)</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -1997,17 +2158,20 @@
       <c r="C54" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Mike Evans</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2025,17 +2189,20 @@
       <c r="C55" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
         <is>
           <t>Cam Skattebo</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="G55" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -2053,17 +2220,20 @@
       <c r="C56" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
         <is>
           <t>Jayden Daniels</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="G56" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -2081,17 +2251,20 @@
       <c r="C57" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Christian Watson</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2109,17 +2282,20 @@
       <c r="C58" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>Bucky Irving</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -2137,17 +2313,20 @@
       <c r="C59" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Jalen Hurts</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -2165,17 +2344,20 @@
       <c r="C60" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D60" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>Rome Odunze</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>CHI (10)</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="G60" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2193,17 +2375,20 @@
       <c r="C61" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="D61" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
         <is>
           <t>TreVeyon Henderson</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>NE (11)</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -2221,17 +2406,20 @@
       <c r="C62" s="11" t="n">
         <v>56</v>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D62" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>Quinshon Judkins</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr">
+      <c r="G62" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -2249,17 +2437,20 @@
       <c r="C63" s="7" t="n">
         <v>49</v>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="D63" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>D'Andre Swift</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>CHI (10)</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr">
+      <c r="G63" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -2277,17 +2468,20 @@
       <c r="C64" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>Carnell Tate</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr">
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2305,17 +2499,20 @@
       <c r="C65" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D65" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>David Montgomery</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F65" s="3" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -2333,17 +2530,20 @@
       <c r="C66" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Caleb Williams</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>CHI (10)</t>
         </is>
       </c>
-      <c r="F66" s="3" t="inlineStr">
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -2361,17 +2561,20 @@
       <c r="C67" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>Marvin Harrison</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F67" s="3" t="inlineStr">
+      <c r="G67" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2389,17 +2592,20 @@
       <c r="C68" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D68" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>Justin Herbert</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F68" s="3" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -2417,17 +2623,20 @@
       <c r="C69" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D69" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Tucker Kraft</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F69" s="3" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -2445,17 +2654,20 @@
       <c r="C70" s="11" t="n">
         <v>64</v>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D70" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>Jaylen Warren</t>
         </is>
       </c>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="F70" s="3" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -2473,17 +2685,20 @@
       <c r="C71" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D71" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Bhayshul Tuten</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F71" s="3" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -2501,17 +2716,20 @@
       <c r="C72" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="D72" s="3" t="inlineStr">
+      <c r="D72" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
         <is>
           <t>Harold Fannin</t>
         </is>
       </c>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F72" s="3" t="inlineStr">
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -2529,17 +2747,20 @@
       <c r="C73" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D73" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Alec Pierce</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>IND (13)</t>
         </is>
       </c>
-      <c r="F73" s="3" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2557,17 +2778,20 @@
       <c r="C74" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D74" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>DK Metcalf</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2585,17 +2809,20 @@
       <c r="C75" s="9" t="n">
         <v>102</v>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D75" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>Courtland Sutton</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2613,17 +2840,20 @@
       <c r="C76" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D76" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>Jadarian Price</t>
         </is>
       </c>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F76" s="3" t="inlineStr">
+      <c r="G76" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -2641,17 +2871,20 @@
       <c r="C77" s="9" t="n">
         <v>94</v>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D77" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>Trevor Lawrence</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F77" s="3" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -2669,17 +2902,20 @@
       <c r="C78" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D78" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>Brian Thomas</t>
         </is>
       </c>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F78" s="3" t="inlineStr">
+      <c r="G78" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2697,17 +2933,20 @@
       <c r="C79" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D79" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>Kyle Pitts</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>ATL (11)</t>
         </is>
       </c>
-      <c r="F79" s="3" t="inlineStr">
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -2725,17 +2964,20 @@
       <c r="C80" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D80" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
         <is>
           <t>Dak Prescott</t>
         </is>
       </c>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>DAL (14)</t>
         </is>
       </c>
-      <c r="F80" s="3" t="inlineStr">
+      <c r="G80" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -2753,17 +2995,20 @@
       <c r="C81" s="9" t="n">
         <v>105</v>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D81" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>Chris Godwin</t>
         </is>
       </c>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F81" s="3" t="inlineStr">
+      <c r="G81" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2781,17 +3026,20 @@
       <c r="C82" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="D82" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>Rhamondre Stevenson</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t>NE (11)</t>
         </is>
       </c>
-      <c r="F82" s="3" t="inlineStr">
+      <c r="G82" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -2809,17 +3057,20 @@
       <c r="C83" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D83" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>Chuba Hubbard</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t>CAR (5)</t>
         </is>
       </c>
-      <c r="F83" s="3" t="inlineStr">
+      <c r="G83" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -2837,17 +3088,20 @@
       <c r="C84" s="9" t="n">
         <v>110</v>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D84" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>Michael Pittman</t>
         </is>
       </c>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="F84" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr">
+      <c r="G84" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2865,17 +3119,20 @@
       <c r="C85" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D85" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>Tony Pollard</t>
         </is>
       </c>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr">
+      <c r="G85" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -2893,17 +3150,20 @@
       <c r="C86" s="5" t="n">
         <v>96</v>
       </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="D86" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>RJ Harvey</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F86" s="3" t="inlineStr">
+      <c r="G86" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -2921,17 +3181,20 @@
       <c r="C87" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="D87" s="3" t="inlineStr">
+      <c r="D87" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>Jordyn Tyson</t>
         </is>
       </c>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr">
+      <c r="G87" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2949,17 +3212,20 @@
       <c r="C88" s="9" t="n">
         <v>136</v>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D88" s="3" t="n">
+        <v>136</v>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>Wan'Dale Robinson</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
+      <c r="G88" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -2977,17 +3243,20 @@
       <c r="C89" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D89" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>Sam LaPorta</t>
         </is>
       </c>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F89" s="3" t="inlineStr">
+      <c r="G89" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -3005,17 +3274,20 @@
       <c r="C90" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D90" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>Rico Dowdle</t>
         </is>
       </c>
-      <c r="E90" s="3" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="F90" s="3" t="inlineStr">
+      <c r="G90" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -3033,17 +3305,20 @@
       <c r="C91" s="9" t="n">
         <v>103</v>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D91" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>Michael Wilson</t>
         </is>
       </c>
-      <c r="E91" s="3" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F91" s="3" t="inlineStr">
+      <c r="G91" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3061,17 +3336,20 @@
       <c r="C92" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D92" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>Jaxson Dart</t>
         </is>
       </c>
-      <c r="E92" s="3" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F92" s="3" t="inlineStr">
+      <c r="G92" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3089,17 +3367,20 @@
       <c r="C93" s="11" t="n">
         <v>66</v>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D93" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>Parker Washington</t>
         </is>
       </c>
-      <c r="E93" s="3" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F93" s="3" t="inlineStr">
+      <c r="G93" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3117,17 +3398,20 @@
       <c r="C94" s="9" t="n">
         <v>146</v>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D94" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
         <is>
           <t>Jakobi Meyers</t>
         </is>
       </c>
-      <c r="E94" s="3" t="inlineStr">
+      <c r="F94" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F94" s="3" t="inlineStr">
+      <c r="G94" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3145,17 +3429,20 @@
       <c r="C95" s="5" t="n">
         <v>99</v>
       </c>
-      <c r="D95" s="3" t="inlineStr">
+      <c r="D95" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>Brock Purdy</t>
         </is>
       </c>
-      <c r="E95" s="3" t="inlineStr">
+      <c r="F95" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F95" s="3" t="inlineStr">
+      <c r="G95" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3173,17 +3460,20 @@
       <c r="C96" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="D96" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>Josh Downs</t>
         </is>
       </c>
-      <c r="E96" s="3" t="inlineStr">
+      <c r="F96" s="3" t="inlineStr">
         <is>
           <t>IND (13)</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
+      <c r="G96" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3201,17 +3491,20 @@
       <c r="C97" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="D97" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>Makai Lemon</t>
         </is>
       </c>
-      <c r="E97" s="3" t="inlineStr">
+      <c r="F97" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F97" s="3" t="inlineStr">
+      <c r="G97" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3229,17 +3522,20 @@
       <c r="C98" s="5" t="n">
         <v>129</v>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D98" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>Travis Kelce</t>
         </is>
       </c>
-      <c r="E98" s="3" t="inlineStr">
+      <c r="F98" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F98" s="3" t="inlineStr">
+      <c r="G98" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -3257,17 +3553,20 @@
       <c r="C99" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="D99" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>Kyle Monangai</t>
         </is>
       </c>
-      <c r="E99" s="3" t="inlineStr">
+      <c r="F99" s="3" t="inlineStr">
         <is>
           <t>CHI (10)</t>
         </is>
       </c>
-      <c r="F99" s="3" t="inlineStr">
+      <c r="G99" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -3285,17 +3584,20 @@
       <c r="C100" s="9" t="n">
         <v>117</v>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D100" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>Patrick Mahomes</t>
         </is>
       </c>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="F100" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr">
+      <c r="G100" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3313,17 +3615,20 @@
       <c r="C101" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D101" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>Bo Nix</t>
         </is>
       </c>
-      <c r="E101" s="3" t="inlineStr">
+      <c r="F101" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F101" s="3" t="inlineStr">
+      <c r="G101" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3341,17 +3646,20 @@
       <c r="C102" s="5" t="n">
         <v>147</v>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D102" s="3" t="n">
+        <v>137</v>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>Kenny Gainwell</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="F102" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
+      <c r="G102" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -3369,17 +3677,20 @@
       <c r="C103" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="D103" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>Matthew Stafford</t>
         </is>
       </c>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr">
+      <c r="G103" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3397,17 +3708,20 @@
       <c r="C104" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="D104" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>Quentin Johnston</t>
         </is>
       </c>
-      <c r="E104" s="3" t="inlineStr">
+      <c r="F104" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F104" s="3" t="inlineStr">
+      <c r="G104" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3425,17 +3739,20 @@
       <c r="C105" s="5" t="n">
         <v>149</v>
       </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="D105" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>Jake Ferguson</t>
         </is>
       </c>
-      <c r="E105" s="3" t="inlineStr">
+      <c r="F105" s="3" t="inlineStr">
         <is>
           <t>DAL (14)</t>
         </is>
       </c>
-      <c r="F105" s="3" t="inlineStr">
+      <c r="G105" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -3453,17 +3770,20 @@
       <c r="C106" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="D106" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>Jordan Addison</t>
         </is>
       </c>
-      <c r="E106" s="3" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr">
+      <c r="G106" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3481,17 +3801,20 @@
       <c r="C107" s="7" t="n">
         <v>89</v>
       </c>
-      <c r="D107" s="3" t="inlineStr">
+      <c r="D107" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>J.K. Dobbins</t>
         </is>
       </c>
-      <c r="E107" s="3" t="inlineStr">
+      <c r="F107" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F107" s="3" t="inlineStr">
+      <c r="G107" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -3509,17 +3832,20 @@
       <c r="C108" s="5" t="n">
         <v>148</v>
       </c>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="D108" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>Aaron Jones</t>
         </is>
       </c>
-      <c r="E108" s="3" t="inlineStr">
+      <c r="F108" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F108" s="3" t="inlineStr">
+      <c r="G108" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -3537,17 +3863,20 @@
       <c r="C109" s="5" t="n">
         <v>115</v>
       </c>
-      <c r="D109" s="3" t="inlineStr">
+      <c r="D109" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
         <is>
           <t>Jared Goff</t>
         </is>
       </c>
-      <c r="E109" s="3" t="inlineStr">
+      <c r="F109" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F109" s="3" t="inlineStr">
+      <c r="G109" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3565,17 +3894,20 @@
       <c r="C110" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="D110" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>Blake Corum</t>
         </is>
       </c>
-      <c r="E110" s="3" t="inlineStr">
+      <c r="F110" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr">
+      <c r="G110" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -3593,17 +3925,20 @@
       <c r="C111" s="5" t="n">
         <v>128</v>
       </c>
-      <c r="D111" s="3" t="inlineStr">
+      <c r="D111" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>George Kittle</t>
         </is>
       </c>
-      <c r="E111" s="3" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F111" s="3" t="inlineStr">
+      <c r="G111" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -3621,17 +3956,20 @@
       <c r="C112" s="5" t="n">
         <v>104</v>
       </c>
-      <c r="D112" s="3" t="inlineStr">
+      <c r="D112" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>Jayden Reed</t>
         </is>
       </c>
-      <c r="E112" s="3" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F112" s="3" t="inlineStr">
+      <c r="G112" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3649,17 +3987,20 @@
       <c r="C113" s="7" t="n">
         <v>92</v>
       </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="D113" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>Rachaad White</t>
         </is>
       </c>
-      <c r="E113" s="3" t="inlineStr">
+      <c r="F113" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F113" s="3" t="inlineStr">
+      <c r="G113" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -3677,17 +4018,20 @@
       <c r="C114" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="D114" s="3" t="inlineStr">
+      <c r="D114" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>Kyler Murray</t>
         </is>
       </c>
-      <c r="E114" s="3" t="inlineStr">
+      <c r="F114" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F114" s="3" t="inlineStr">
+      <c r="G114" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3705,17 +4049,20 @@
       <c r="C115" s="5" t="n">
         <v>112</v>
       </c>
-      <c r="D115" s="3" t="inlineStr">
+      <c r="D115" s="3" t="n">
+        <v>116</v>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
         <is>
           <t>Dalton Kincaid</t>
         </is>
       </c>
-      <c r="E115" s="3" t="inlineStr">
+      <c r="F115" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F115" s="3" t="inlineStr">
+      <c r="G115" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -3733,17 +4080,20 @@
       <c r="C116" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="D116" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>Khalil Shakir</t>
         </is>
       </c>
-      <c r="E116" s="3" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr">
+      <c r="G116" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3761,17 +4111,20 @@
       <c r="C117" s="5" t="n">
         <v>116</v>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D117" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>Jordan Love</t>
         </is>
       </c>
-      <c r="E117" s="3" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
+      <c r="G117" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3789,17 +4142,20 @@
       <c r="C118" s="5" t="n">
         <v>118</v>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D118" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>Baker Mayfield</t>
         </is>
       </c>
-      <c r="E118" s="3" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
+      <c r="G118" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3817,17 +4173,20 @@
       <c r="C119" s="5" t="n">
         <v>127</v>
       </c>
-      <c r="D119" s="3" t="inlineStr">
+      <c r="D119" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>Isaiah Likely</t>
         </is>
       </c>
-      <c r="E119" s="3" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F119" s="3" t="inlineStr">
+      <c r="G119" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -3845,17 +4204,20 @@
       <c r="C120" s="4" t="n">
         <v>132</v>
       </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="D120" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>Jayden Higgins</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr">
+      <c r="G120" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3873,17 +4235,20 @@
       <c r="C121" s="11" t="n">
         <v>86</v>
       </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="D121" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>Xavier Worthy</t>
         </is>
       </c>
-      <c r="E121" s="3" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F121" s="3" t="inlineStr">
+      <c r="G121" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -3901,17 +4266,20 @@
       <c r="C122" s="9" t="n">
         <v>165</v>
       </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D122" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>Tyler Shough</t>
         </is>
       </c>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="F122" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr">
+      <c r="G122" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -3929,17 +4297,20 @@
       <c r="C123" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="D123" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>Dallas Goedert</t>
         </is>
       </c>
-      <c r="E123" s="3" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F123" s="3" t="inlineStr">
+      <c r="G123" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -3957,17 +4328,20 @@
       <c r="C124" s="5" t="n">
         <v>123</v>
       </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D124" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
-      <c r="E124" s="3" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F124" s="3" t="inlineStr">
+      <c r="G124" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -3985,17 +4359,20 @@
       <c r="C125" s="7" t="n">
         <v>106</v>
       </c>
-      <c r="D125" s="3" t="inlineStr">
+      <c r="D125" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>Jordan Mason</t>
         </is>
       </c>
-      <c r="E125" s="3" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F125" s="3" t="inlineStr">
+      <c r="G125" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -4013,17 +4390,20 @@
       <c r="C126" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="D126" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>KC Concepcion</t>
         </is>
       </c>
-      <c r="E126" s="3" t="inlineStr">
+      <c r="F126" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F126" s="3" t="inlineStr">
+      <c r="G126" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -4041,17 +4421,20 @@
       <c r="C127" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="D127" s="3" t="inlineStr">
+      <c r="D127" s="3" t="n">
+        <v>135</v>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>Romeo Doubs</t>
         </is>
       </c>
-      <c r="E127" s="3" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr">
         <is>
           <t>NE (11)</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr">
+      <c r="G127" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -4069,17 +4452,20 @@
       <c r="C128" s="7" t="n">
         <v>93</v>
       </c>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="D128" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
         <is>
           <t>Jonathon Brooks</t>
         </is>
       </c>
-      <c r="E128" s="3" t="inlineStr">
+      <c r="F128" s="3" t="inlineStr">
         <is>
           <t>CAR (5)</t>
         </is>
       </c>
-      <c r="F128" s="3" t="inlineStr">
+      <c r="G128" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -4097,17 +4483,20 @@
       <c r="C129" s="5" t="n">
         <v>153</v>
       </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="D129" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
         <is>
           <t>Tyrone Tracy</t>
         </is>
       </c>
-      <c r="E129" s="3" t="inlineStr">
+      <c r="F129" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F129" s="3" t="inlineStr">
+      <c r="G129" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -4125,17 +4514,20 @@
       <c r="C130" s="11" t="n">
         <v>122</v>
       </c>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="D130" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>Mark Andrews</t>
         </is>
       </c>
-      <c r="E130" s="3" t="inlineStr">
+      <c r="F130" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="F130" s="3" t="inlineStr">
+      <c r="G130" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -4153,17 +4545,20 @@
       <c r="C131" s="5" t="n">
         <v>131</v>
       </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="D131" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>Malik Willis</t>
         </is>
       </c>
-      <c r="E131" s="3" t="inlineStr">
+      <c r="F131" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="F131" s="3" t="inlineStr">
+      <c r="G131" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -4181,17 +4576,20 @@
       <c r="C132" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="D132" s="3" t="inlineStr">
+      <c r="D132" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
         <is>
           <t>Jalen Coker</t>
         </is>
       </c>
-      <c r="E132" s="3" t="inlineStr">
+      <c r="F132" s="3" t="inlineStr">
         <is>
           <t>CAR (5)</t>
         </is>
       </c>
-      <c r="F132" s="3" t="inlineStr">
+      <c r="G132" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -4209,17 +4607,20 @@
       <c r="C133" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="D133" s="3" t="inlineStr">
+      <c r="D133" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>Matthew Golden</t>
         </is>
       </c>
-      <c r="E133" s="3" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F133" s="3" t="inlineStr">
+      <c r="G133" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -4237,17 +4638,20 @@
       <c r="C134" s="9" t="n">
         <v>164</v>
       </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="D134" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>C.J. Stroud</t>
         </is>
       </c>
-      <c r="E134" s="3" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr">
+      <c r="G134" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -4265,17 +4669,20 @@
       <c r="C135" s="5" t="n">
         <v>152</v>
       </c>
-      <c r="D135" s="3" t="inlineStr">
+      <c r="D135" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>Woody Marks</t>
         </is>
       </c>
-      <c r="E135" s="3" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F135" s="3" t="inlineStr">
+      <c r="G135" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -4293,17 +4700,20 @@
       <c r="C136" s="5" t="n">
         <v>168</v>
       </c>
-      <c r="D136" s="3" t="inlineStr">
+      <c r="D136" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>Tyler Allgeier</t>
         </is>
       </c>
-      <c r="E136" s="3" t="inlineStr">
+      <c r="F136" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F136" s="3" t="inlineStr">
+      <c r="G136" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -4321,17 +4731,20 @@
       <c r="C137" s="9" t="n">
         <v>238</v>
       </c>
-      <c r="D137" s="3" t="inlineStr">
+      <c r="D137" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
         <is>
           <t>Zach Charbonnet</t>
         </is>
       </c>
-      <c r="E137" s="3" t="inlineStr">
+      <c r="F137" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F137" s="3" t="inlineStr">
+      <c r="G137" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -4349,17 +4762,20 @@
       <c r="C138" s="9" t="n">
         <v>166</v>
       </c>
-      <c r="D138" s="3" t="inlineStr">
+      <c r="D138" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
         <is>
           <t>Sam Darnold</t>
         </is>
       </c>
-      <c r="E138" s="3" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F138" s="3" t="inlineStr">
+      <c r="G138" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -4377,17 +4793,20 @@
       <c r="C139" s="7" t="n">
         <v>108</v>
       </c>
-      <c r="D139" s="3" t="inlineStr">
+      <c r="D139" s="3" t="n">
+        <v>112</v>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
         <is>
           <t>Chris Rodriguez</t>
         </is>
       </c>
-      <c r="E139" s="3" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F139" s="3" t="inlineStr">
+      <c r="G139" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -4405,17 +4824,20 @@
       <c r="C140" s="5" t="n">
         <v>171</v>
       </c>
-      <c r="D140" s="3" t="inlineStr">
+      <c r="D140" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
         <is>
           <t>Tyjae Spears</t>
         </is>
       </c>
-      <c r="E140" s="3" t="inlineStr">
+      <c r="F140" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F140" s="3" t="inlineStr">
+      <c r="G140" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -4433,17 +4855,20 @@
       <c r="C141" s="5" t="n">
         <v>173</v>
       </c>
-      <c r="D141" s="3" t="inlineStr">
+      <c r="D141" s="3" t="n">
+        <v>172</v>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>Juwan Johnson</t>
         </is>
       </c>
-      <c r="E141" s="3" t="inlineStr">
+      <c r="F141" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="F141" s="3" t="inlineStr">
+      <c r="G141" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -4461,17 +4886,20 @@
       <c r="C142" s="5" t="n">
         <v>182</v>
       </c>
-      <c r="D142" s="3" t="inlineStr">
+      <c r="D142" s="3" t="n">
+        <v>194</v>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
         <is>
           <t>Dylan Sampson</t>
         </is>
       </c>
-      <c r="E142" s="3" t="inlineStr">
+      <c r="F142" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F142" s="3" t="inlineStr">
+      <c r="G142" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -4489,17 +4917,20 @@
       <c r="C143" s="5" t="n">
         <v>170</v>
       </c>
-      <c r="D143" s="3" t="inlineStr">
+      <c r="D143" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>Isiah Pacheco</t>
         </is>
       </c>
-      <c r="E143" s="3" t="inlineStr">
+      <c r="F143" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F143" s="3" t="inlineStr">
+      <c r="G143" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -4517,17 +4948,20 @@
       <c r="C144" s="5" t="n">
         <v>181</v>
       </c>
-      <c r="D144" s="3" t="inlineStr">
+      <c r="D144" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
         <is>
           <t>Alvin Kamara</t>
         </is>
       </c>
-      <c r="E144" s="3" t="inlineStr">
+      <c r="F144" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="F144" s="3" t="inlineStr">
+      <c r="G144" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -4545,17 +4979,20 @@
       <c r="C145" s="9" t="n">
         <v>199</v>
       </c>
-      <c r="D145" s="3" t="inlineStr">
+      <c r="D145" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>Cam Ward</t>
         </is>
       </c>
-      <c r="E145" s="3" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F145" s="3" t="inlineStr">
+      <c r="G145" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -4573,17 +5010,20 @@
       <c r="C146" s="5" t="n">
         <v>133</v>
       </c>
-      <c r="D146" s="3" t="inlineStr">
+      <c r="D146" s="3" t="n">
+        <v>134</v>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>Rashid Shaheed</t>
         </is>
       </c>
-      <c r="E146" s="3" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F146" s="3" t="inlineStr">
+      <c r="G146" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -4601,17 +5041,20 @@
       <c r="C147" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="D147" s="3" t="inlineStr">
+      <c r="D147" s="3" t="n">
+        <v>185</v>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
         <is>
           <t>Brenton Strange</t>
         </is>
       </c>
-      <c r="E147" s="3" t="inlineStr">
+      <c r="F147" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F147" s="3" t="inlineStr">
+      <c r="G147" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -4629,17 +5072,20 @@
       <c r="C148" s="9" t="n">
         <v>190</v>
       </c>
-      <c r="D148" s="3" t="inlineStr">
+      <c r="D148" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
         <is>
           <t>Omar Cooper</t>
         </is>
       </c>
-      <c r="E148" s="3" t="inlineStr">
+      <c r="F148" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F148" s="3" t="inlineStr">
+      <c r="G148" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -4657,17 +5103,20 @@
       <c r="C149" s="9" t="n">
         <v>225</v>
       </c>
-      <c r="D149" s="3" t="inlineStr">
+      <c r="D149" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
         <is>
           <t>Denzel Boston</t>
         </is>
       </c>
-      <c r="E149" s="3" t="inlineStr">
+      <c r="F149" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F149" s="3" t="inlineStr">
+      <c r="G149" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -4685,17 +5134,20 @@
       <c r="C150" s="4" t="n">
         <v>189</v>
       </c>
-      <c r="D150" s="3" t="inlineStr">
+      <c r="D150" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
         <is>
           <t>Jerry Jeudy</t>
         </is>
       </c>
-      <c r="E150" s="3" t="inlineStr">
+      <c r="F150" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F150" s="3" t="inlineStr">
+      <c r="G150" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -4713,17 +5165,20 @@
       <c r="C151" s="4" t="n">
         <v>178</v>
       </c>
-      <c r="D151" s="3" t="inlineStr">
+      <c r="D151" s="3" t="n">
+        <v>178</v>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
         <is>
           <t>Daniel Jones</t>
         </is>
       </c>
-      <c r="E151" s="3" t="inlineStr">
+      <c r="F151" s="3" t="inlineStr">
         <is>
           <t>IND (13)</t>
         </is>
       </c>
-      <c r="F151" s="3" t="inlineStr">
+      <c r="G151" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -4741,17 +5196,20 @@
       <c r="C152" s="4" t="n">
         <v>177</v>
       </c>
-      <c r="D152" s="3" t="inlineStr">
+      <c r="D152" s="3" t="n">
+        <v>177</v>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
         <is>
           <t>Bryce Young</t>
         </is>
       </c>
-      <c r="E152" s="3" t="inlineStr">
+      <c r="F152" s="3" t="inlineStr">
         <is>
           <t>CAR (5)</t>
         </is>
       </c>
-      <c r="F152" s="3" t="inlineStr">
+      <c r="G152" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -4769,17 +5227,20 @@
       <c r="C153" s="4" t="n">
         <v>192</v>
       </c>
-      <c r="D153" s="3" t="inlineStr">
+      <c r="D153" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
         <is>
           <t>Jauan Jennings</t>
         </is>
       </c>
-      <c r="E153" s="3" t="inlineStr">
+      <c r="F153" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F153" s="3" t="inlineStr">
+      <c r="G153" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -4797,17 +5258,20 @@
       <c r="C154" s="5" t="n">
         <v>172</v>
       </c>
-      <c r="D154" s="3" t="inlineStr">
+      <c r="D154" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
         <is>
           <t>Chig Okonkwo</t>
         </is>
       </c>
-      <c r="E154" s="3" t="inlineStr">
+      <c r="F154" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F154" s="3" t="inlineStr">
+      <c r="G154" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -4825,17 +5289,20 @@
       <c r="C155" s="5" t="n">
         <v>187</v>
       </c>
-      <c r="D155" s="3" t="inlineStr">
+      <c r="D155" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
         <is>
           <t>Oronde Gadsden</t>
         </is>
       </c>
-      <c r="E155" s="3" t="inlineStr">
+      <c r="F155" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F155" s="3" t="inlineStr">
+      <c r="G155" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -4853,17 +5320,20 @@
       <c r="C156" s="5" t="n">
         <v>186</v>
       </c>
-      <c r="D156" s="3" t="inlineStr">
+      <c r="D156" s="3" t="n">
+        <v>183</v>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
         <is>
           <t>Hunter Henry</t>
         </is>
       </c>
-      <c r="E156" s="3" t="inlineStr">
+      <c r="F156" s="3" t="inlineStr">
         <is>
           <t>NE (11)</t>
         </is>
       </c>
-      <c r="F156" s="3" t="inlineStr">
+      <c r="G156" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -4881,17 +5351,20 @@
       <c r="C157" s="5" t="n">
         <v>228</v>
       </c>
-      <c r="D157" s="3" t="inlineStr">
+      <c r="D157" s="3" t="n">
+        <v>210</v>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
         <is>
           <t>Jonah Coleman</t>
         </is>
       </c>
-      <c r="E157" s="3" t="inlineStr">
+      <c r="F157" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F157" s="3" t="inlineStr">
+      <c r="G157" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -4909,17 +5382,20 @@
       <c r="C158" s="7" t="n">
         <v>124</v>
       </c>
-      <c r="D158" s="3" t="inlineStr">
+      <c r="D158" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
         <is>
           <t>Keaton Mitchell</t>
         </is>
       </c>
-      <c r="E158" s="3" t="inlineStr">
+      <c r="F158" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F158" s="3" t="inlineStr">
+      <c r="G158" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -4937,17 +5413,20 @@
       <c r="C159" s="4" t="n">
         <v>188</v>
       </c>
-      <c r="D159" s="3" t="inlineStr">
+      <c r="D159" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
         <is>
           <t>Adonai Mitchell</t>
         </is>
       </c>
-      <c r="E159" s="3" t="inlineStr">
+      <c r="F159" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F159" s="3" t="inlineStr">
+      <c r="G159" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -4965,17 +5444,20 @@
       <c r="C160" s="5" t="n">
         <v>155</v>
       </c>
-      <c r="D160" s="3" t="inlineStr">
+      <c r="D160" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
         <is>
           <t>Jalen McMillan</t>
         </is>
       </c>
-      <c r="E160" s="3" t="inlineStr">
+      <c r="F160" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F160" s="3" t="inlineStr">
+      <c r="G160" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -4993,17 +5475,20 @@
       <c r="C161" s="4" t="n">
         <v>208</v>
       </c>
-      <c r="D161" s="3" t="inlineStr">
+      <c r="D161" s="3" t="n">
+        <v>213</v>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
         <is>
           <t>Tre Tucker</t>
         </is>
       </c>
-      <c r="E161" s="3" t="inlineStr">
+      <c r="F161" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F161" s="3" t="inlineStr">
+      <c r="G161" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5021,17 +5506,20 @@
       <c r="C162" s="5" t="n">
         <v>169</v>
       </c>
-      <c r="D162" s="3" t="inlineStr">
+      <c r="D162" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
         <is>
           <t>Brian Robinson</t>
         </is>
       </c>
-      <c r="E162" s="3" t="inlineStr">
+      <c r="F162" s="3" t="inlineStr">
         <is>
           <t>ATL (11)</t>
         </is>
       </c>
-      <c r="F162" s="3" t="inlineStr">
+      <c r="G162" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -5049,17 +5537,20 @@
       <c r="C163" s="5" t="n">
         <v>167</v>
       </c>
-      <c r="D163" s="3" t="inlineStr">
+      <c r="D163" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
         <is>
           <t>Tank Bigsby</t>
         </is>
       </c>
-      <c r="E163" s="3" t="inlineStr">
+      <c r="F163" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F163" s="3" t="inlineStr">
+      <c r="G163" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -5077,17 +5568,20 @@
       <c r="C164" s="4" t="n">
         <v>215</v>
       </c>
-      <c r="D164" s="3" t="inlineStr">
+      <c r="D164" s="3" t="n">
+        <v>219</v>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
         <is>
           <t>Dalton Schultz</t>
         </is>
       </c>
-      <c r="E164" s="3" t="inlineStr">
+      <c r="F164" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F164" s="3" t="inlineStr">
+      <c r="G164" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -5105,17 +5599,20 @@
       <c r="C165" s="5" t="n">
         <v>157</v>
       </c>
-      <c r="D165" s="3" t="inlineStr">
+      <c r="D165" s="3" t="n">
+        <v>151</v>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
         <is>
           <t>Travis Hunter</t>
         </is>
       </c>
-      <c r="E165" s="3" t="inlineStr">
+      <c r="F165" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F165" s="3" t="inlineStr">
+      <c r="G165" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5133,17 +5630,20 @@
       <c r="C166" s="4" t="n">
         <v>218</v>
       </c>
-      <c r="D166" s="3" t="inlineStr">
+      <c r="D166" s="3" t="n">
+        <v>225</v>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
         <is>
           <t>Braelon Allen</t>
         </is>
       </c>
-      <c r="E166" s="3" t="inlineStr">
+      <c r="F166" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F166" s="3" t="inlineStr">
+      <c r="G166" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -5161,17 +5661,20 @@
       <c r="C167" s="5" t="n">
         <v>193</v>
       </c>
-      <c r="D167" s="3" t="inlineStr">
+      <c r="D167" s="3" t="n">
+        <v>182</v>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
         <is>
           <t>Tre' Harris</t>
         </is>
       </c>
-      <c r="E167" s="3" t="inlineStr">
+      <c r="F167" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F167" s="3" t="inlineStr">
+      <c r="G167" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5189,17 +5692,20 @@
       <c r="C168" s="4" t="n">
         <v>213</v>
       </c>
-      <c r="D168" s="3" t="inlineStr">
+      <c r="D168" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
         <is>
           <t>T.J. Hockenson</t>
         </is>
       </c>
-      <c r="E168" s="3" t="inlineStr">
+      <c r="F168" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F168" s="3" t="inlineStr">
+      <c r="G168" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -5217,17 +5723,20 @@
       <c r="C169" s="4" t="n">
         <v>271</v>
       </c>
-      <c r="D169" s="3" t="inlineStr">
+      <c r="D169" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
         <is>
           <t>Troy Franklin</t>
         </is>
       </c>
-      <c r="E169" s="3" t="inlineStr">
+      <c r="F169" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F169" s="3" t="inlineStr">
+      <c r="G169" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5245,17 +5754,20 @@
       <c r="C170" s="4" t="n">
         <v>235</v>
       </c>
-      <c r="D170" s="3" t="inlineStr">
+      <c r="D170" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
         <is>
           <t>Kayshon Boutte</t>
         </is>
       </c>
-      <c r="E170" s="3" t="inlineStr">
+      <c r="F170" s="3" t="inlineStr">
         <is>
           <t>NE (11)</t>
         </is>
       </c>
-      <c r="F170" s="3" t="inlineStr">
+      <c r="G170" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5273,17 +5785,20 @@
       <c r="C171" s="5" t="n">
         <v>191</v>
       </c>
-      <c r="D171" s="3" t="inlineStr">
+      <c r="D171" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
         <is>
           <t>Ryan Flournoy</t>
         </is>
       </c>
-      <c r="E171" s="3" t="inlineStr">
+      <c r="F171" s="3" t="inlineStr">
         <is>
           <t>DAL (14)</t>
         </is>
       </c>
-      <c r="F171" s="3" t="inlineStr">
+      <c r="G171" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5301,17 +5816,20 @@
       <c r="C172" s="7" t="n">
         <v>134</v>
       </c>
-      <c r="D172" s="3" t="inlineStr">
+      <c r="D172" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
         <is>
           <t>Stefon Diggs</t>
         </is>
       </c>
-      <c r="E172" s="3" t="inlineStr">
+      <c r="F172" s="3" t="inlineStr">
         <is>
           <t>FA ()</t>
         </is>
       </c>
-      <c r="F172" s="3" t="inlineStr">
+      <c r="G172" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5329,17 +5847,20 @@
       <c r="C173" s="4" t="n">
         <v>242</v>
       </c>
-      <c r="D173" s="3" t="inlineStr">
+      <c r="D173" s="3" t="n">
+        <v>243</v>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
         <is>
           <t>James Conner</t>
         </is>
       </c>
-      <c r="E173" s="3" t="inlineStr">
+      <c r="F173" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F173" s="3" t="inlineStr">
+      <c r="G173" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -5357,17 +5878,20 @@
       <c r="C174" s="4" t="n">
         <v>239</v>
       </c>
-      <c r="D174" s="3" t="inlineStr">
+      <c r="D174" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
         <is>
           <t>Jacoby Brissett</t>
         </is>
       </c>
-      <c r="E174" s="3" t="inlineStr">
+      <c r="F174" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F174" s="3" t="inlineStr">
+      <c r="G174" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -5385,17 +5909,20 @@
       <c r="C175" s="4" t="n">
         <v>268</v>
       </c>
-      <c r="D175" s="3" t="inlineStr">
+      <c r="D175" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
         <is>
           <t>Jaylin Noel</t>
         </is>
       </c>
-      <c r="E175" s="3" t="inlineStr">
+      <c r="F175" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F175" s="3" t="inlineStr">
+      <c r="G175" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5413,17 +5940,20 @@
       <c r="C176" s="4" t="n">
         <v>270</v>
       </c>
-      <c r="D176" s="3" t="inlineStr">
+      <c r="D176" s="3" t="n">
+        <v>277</v>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
         <is>
           <t>Emanuel Wilson</t>
         </is>
       </c>
-      <c r="E176" s="3" t="inlineStr">
+      <c r="F176" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F176" s="3" t="inlineStr">
+      <c r="G176" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -5441,17 +5971,20 @@
       <c r="C177" s="5" t="n">
         <v>211</v>
       </c>
-      <c r="D177" s="3" t="inlineStr">
+      <c r="D177" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
         <is>
           <t>Calvin Ridley</t>
         </is>
       </c>
-      <c r="E177" s="3" t="inlineStr">
+      <c r="F177" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F177" s="3" t="inlineStr">
+      <c r="G177" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5469,17 +6002,20 @@
       <c r="C178" s="5" t="n">
         <v>209</v>
       </c>
-      <c r="D178" s="3" t="inlineStr">
+      <c r="D178" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
         <is>
           <t>Isaac TeSlaa</t>
         </is>
       </c>
-      <c r="E178" s="3" t="inlineStr">
+      <c r="F178" s="3" t="inlineStr">
         <is>
           <t>DET (6)</t>
         </is>
       </c>
-      <c r="F178" s="3" t="inlineStr">
+      <c r="G178" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5497,17 +6033,20 @@
       <c r="C179" s="5" t="n">
         <v>212</v>
       </c>
-      <c r="D179" s="3" t="inlineStr">
+      <c r="D179" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
         <is>
           <t>Kenyon Sadiq</t>
         </is>
       </c>
-      <c r="E179" s="3" t="inlineStr">
+      <c r="F179" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F179" s="3" t="inlineStr">
+      <c r="G179" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -5525,17 +6064,20 @@
       <c r="C180" s="4" t="n">
         <v>262</v>
       </c>
-      <c r="D180" s="3" t="inlineStr">
+      <c r="D180" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
         <is>
           <t>Emmett Johnson</t>
         </is>
       </c>
-      <c r="E180" s="3" t="inlineStr">
+      <c r="F180" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F180" s="3" t="inlineStr">
+      <c r="G180" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -5553,17 +6095,20 @@
       <c r="C181" s="4" t="n">
         <v>263</v>
       </c>
-      <c r="D181" s="3" t="inlineStr">
+      <c r="D181" s="3" t="n">
+        <v>252</v>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
         <is>
           <t>Kimani Vidal</t>
         </is>
       </c>
-      <c r="E181" s="3" t="inlineStr">
+      <c r="F181" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F181" s="3" t="inlineStr">
+      <c r="G181" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -5581,17 +6126,20 @@
       <c r="C182" s="5" t="n">
         <v>204</v>
       </c>
-      <c r="D182" s="3" t="inlineStr">
+      <c r="D182" s="3" t="n">
+        <v>192</v>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
         <is>
           <t>Ray Davis</t>
         </is>
       </c>
-      <c r="E182" s="3" t="inlineStr">
+      <c r="F182" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F182" s="3" t="inlineStr">
+      <c r="G182" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -5609,17 +6157,20 @@
       <c r="C183" s="5" t="n">
         <v>179</v>
       </c>
-      <c r="D183" s="3" t="inlineStr">
+      <c r="D183" s="3" t="n">
+        <v>184</v>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
         <is>
           <t>AJ Barner</t>
         </is>
       </c>
-      <c r="E183" s="3" t="inlineStr">
+      <c r="F183" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F183" s="3" t="inlineStr">
+      <c r="G183" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -5637,17 +6188,20 @@
       <c r="C184" s="4" t="n">
         <v>259</v>
       </c>
-      <c r="D184" s="3" t="inlineStr">
+      <c r="D184" s="3" t="n">
+        <v>274</v>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
         <is>
           <t>Darnell Mooney</t>
         </is>
       </c>
-      <c r="E184" s="3" t="inlineStr">
+      <c r="F184" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F184" s="3" t="inlineStr">
+      <c r="G184" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5665,17 +6219,20 @@
       <c r="C185" s="7" t="n">
         <v>154</v>
       </c>
-      <c r="D185" s="3" t="inlineStr">
+      <c r="D185" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
         <is>
           <t>Jalen Nailor</t>
         </is>
       </c>
-      <c r="E185" s="3" t="inlineStr">
+      <c r="F185" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F185" s="3" t="inlineStr">
+      <c r="G185" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5693,17 +6250,20 @@
       <c r="C186" s="11" t="n">
         <v>156</v>
       </c>
-      <c r="D186" s="3" t="inlineStr">
+      <c r="D186" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
         <is>
           <t>Deebo Samuel</t>
         </is>
       </c>
-      <c r="E186" s="3" t="inlineStr">
+      <c r="F186" s="3" t="inlineStr">
         <is>
           <t>FA ()</t>
         </is>
       </c>
-      <c r="F186" s="3" t="inlineStr">
+      <c r="G186" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5721,17 +6281,20 @@
       <c r="C187" s="5" t="n">
         <v>206</v>
       </c>
-      <c r="D187" s="3" t="inlineStr">
+      <c r="D187" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
         <is>
           <t>Malik Washington</t>
         </is>
       </c>
-      <c r="E187" s="3" t="inlineStr">
+      <c r="F187" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="F187" s="3" t="inlineStr">
+      <c r="G187" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5749,17 +6312,20 @@
       <c r="C188" s="5" t="n">
         <v>217</v>
       </c>
-      <c r="D188" s="3" t="inlineStr">
+      <c r="D188" s="3" t="n">
+        <v>209</v>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
         <is>
           <t>Mike Washington</t>
         </is>
       </c>
-      <c r="E188" s="3" t="inlineStr">
+      <c r="F188" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F188" s="3" t="inlineStr">
+      <c r="G188" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -5777,17 +6343,20 @@
       <c r="C189" s="4" t="n">
         <v>245</v>
       </c>
-      <c r="D189" s="3" t="inlineStr">
+      <c r="D189" s="3" t="n">
+        <v>245</v>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
         <is>
           <t>Pat Bryant</t>
         </is>
       </c>
-      <c r="E189" s="3" t="inlineStr">
+      <c r="F189" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F189" s="3" t="inlineStr">
+      <c r="G189" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5805,17 +6374,20 @@
       <c r="C190" s="4" t="n">
         <v>247</v>
       </c>
-      <c r="D190" s="3" t="inlineStr">
+      <c r="D190" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
         <is>
           <t>Antonio Williams</t>
         </is>
       </c>
-      <c r="E190" s="3" t="inlineStr">
+      <c r="F190" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F190" s="3" t="inlineStr">
+      <c r="G190" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5833,17 +6405,20 @@
       <c r="C191" s="5" t="n">
         <v>233</v>
       </c>
-      <c r="D191" s="3" t="inlineStr">
+      <c r="D191" s="3" t="n">
+        <v>236</v>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
         <is>
           <t>Gunnar Helm</t>
         </is>
       </c>
-      <c r="E191" s="3" t="inlineStr">
+      <c r="F191" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F191" s="3" t="inlineStr">
+      <c r="G191" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -5861,17 +6436,20 @@
       <c r="C192" s="4" t="n">
         <v>243</v>
       </c>
-      <c r="D192" s="3" t="inlineStr">
+      <c r="D192" s="3" t="n">
+        <v>179</v>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
         <is>
           <t>Dontayvion Wicks</t>
         </is>
       </c>
-      <c r="E192" s="3" t="inlineStr">
+      <c r="F192" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F192" s="3" t="inlineStr">
+      <c r="G192" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5889,17 +6467,20 @@
       <c r="C193" s="5" t="n">
         <v>203</v>
       </c>
-      <c r="D193" s="3" t="inlineStr">
+      <c r="D193" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
         <is>
           <t>Sean Tucker</t>
         </is>
       </c>
-      <c r="E193" s="3" t="inlineStr">
+      <c r="F193" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F193" s="3" t="inlineStr">
+      <c r="G193" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -5917,17 +6498,20 @@
       <c r="C194" s="4" t="n">
         <v>272</v>
       </c>
-      <c r="D194" s="3" t="inlineStr">
+      <c r="D194" s="3" t="n">
+        <v>279</v>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
         <is>
           <t>Nicholas Singleton</t>
         </is>
       </c>
-      <c r="E194" s="3" t="inlineStr">
+      <c r="F194" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F194" s="3" t="inlineStr">
+      <c r="G194" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -5945,17 +6529,20 @@
       <c r="C195" s="4" t="n">
         <v>274</v>
       </c>
-      <c r="D195" s="3" t="inlineStr">
+      <c r="D195" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
         <is>
           <t>Tank Dell</t>
         </is>
       </c>
-      <c r="E195" s="3" t="inlineStr">
+      <c r="F195" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="F195" s="3" t="inlineStr">
+      <c r="G195" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -5973,17 +6560,20 @@
       <c r="C196" s="5" t="n">
         <v>216</v>
       </c>
-      <c r="D196" s="3" t="inlineStr">
+      <c r="D196" s="3" t="n">
+        <v>221</v>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
         <is>
           <t>Aaron Rodgers</t>
         </is>
       </c>
-      <c r="E196" s="3" t="inlineStr">
+      <c r="F196" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="F196" s="3" t="inlineStr">
+      <c r="G196" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -6001,17 +6591,20 @@
       <c r="C197" s="5" t="n">
         <v>234</v>
       </c>
-      <c r="D197" s="3" t="inlineStr">
+      <c r="D197" s="3" t="n">
+        <v>237</v>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
         <is>
           <t>Cooper Kupp</t>
         </is>
       </c>
-      <c r="E197" s="3" t="inlineStr">
+      <c r="F197" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F197" s="3" t="inlineStr">
+      <c r="G197" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6029,17 +6622,20 @@
       <c r="C198" s="5" t="n">
         <v>227</v>
       </c>
-      <c r="D198" s="3" t="inlineStr">
+      <c r="D198" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
         <is>
           <t>Kaytron Allen</t>
         </is>
       </c>
-      <c r="E198" s="3" t="inlineStr">
+      <c r="F198" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F198" s="3" t="inlineStr">
+      <c r="G198" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -6057,17 +6653,20 @@
       <c r="C199" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="D199" s="3" t="inlineStr">
+      <c r="D199" s="3" t="n">
+        <v>207</v>
+      </c>
+      <c r="E199" s="3" t="inlineStr">
         <is>
           <t>Geno Smith</t>
         </is>
       </c>
-      <c r="E199" s="3" t="inlineStr">
+      <c r="F199" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F199" s="3" t="inlineStr">
+      <c r="G199" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -6085,17 +6684,20 @@
       <c r="C200" s="11" t="n">
         <v>120</v>
       </c>
-      <c r="D200" s="3" t="inlineStr">
+      <c r="D200" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="E200" s="3" t="inlineStr">
         <is>
           <t>De'Zhaun Stribling</t>
         </is>
       </c>
-      <c r="E200" s="3" t="inlineStr">
+      <c r="F200" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F200" s="3" t="inlineStr">
+      <c r="G200" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6113,17 +6715,20 @@
       <c r="C201" s="5" t="n">
         <v>226</v>
       </c>
-      <c r="D201" s="3" t="inlineStr">
+      <c r="D201" s="3" t="n">
+        <v>223</v>
+      </c>
+      <c r="E201" s="3" t="inlineStr">
         <is>
           <t>Germie Bernard</t>
         </is>
       </c>
-      <c r="E201" s="3" t="inlineStr">
+      <c r="F201" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="F201" s="3" t="inlineStr">
+      <c r="G201" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6141,17 +6746,20 @@
       <c r="C202" s="5" t="n">
         <v>210</v>
       </c>
-      <c r="D202" s="3" t="inlineStr">
+      <c r="D202" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="E202" s="3" t="inlineStr">
         <is>
           <t>Rashod Bateman</t>
         </is>
       </c>
-      <c r="E202" s="3" t="inlineStr">
+      <c r="F202" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="F202" s="3" t="inlineStr">
+      <c r="G202" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6169,17 +6777,20 @@
       <c r="C203" s="5" t="n">
         <v>236</v>
       </c>
-      <c r="D203" s="3" t="inlineStr">
+      <c r="D203" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
         <is>
           <t>Brandon Aiyuk</t>
         </is>
       </c>
-      <c r="E203" s="3" t="inlineStr">
+      <c r="F203" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F203" s="3" t="inlineStr">
+      <c r="G203" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6197,17 +6808,20 @@
       <c r="C204" s="4" t="n">
         <v>273</v>
       </c>
-      <c r="D204" s="3" t="inlineStr">
+      <c r="D204" s="3" t="n">
+        <v>280</v>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
         <is>
           <t>Jaylen Wright</t>
         </is>
       </c>
-      <c r="E204" s="3" t="inlineStr">
+      <c r="F204" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="F204" s="3" t="inlineStr">
+      <c r="G204" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -6225,17 +6839,20 @@
       <c r="C205" s="5" t="n">
         <v>201</v>
       </c>
-      <c r="D205" s="3" t="inlineStr">
+      <c r="D205" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="E205" s="3" t="inlineStr">
         <is>
           <t>Fernando Mendoza</t>
         </is>
       </c>
-      <c r="E205" s="3" t="inlineStr">
+      <c r="F205" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F205" s="3" t="inlineStr">
+      <c r="G205" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -6253,17 +6870,20 @@
       <c r="C206" s="5" t="n">
         <v>265</v>
       </c>
-      <c r="D206" s="3" t="inlineStr">
+      <c r="D206" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="E206" s="3" t="inlineStr">
         <is>
           <t>Pat Freiermuth</t>
         </is>
       </c>
-      <c r="E206" s="3" t="inlineStr">
+      <c r="F206" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="F206" s="3" t="inlineStr">
+      <c r="G206" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -6281,17 +6901,20 @@
       <c r="C207" s="5" t="n">
         <v>256</v>
       </c>
-      <c r="D207" s="3" t="inlineStr">
+      <c r="D207" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
         <is>
           <t>Zachariah Branch</t>
         </is>
       </c>
-      <c r="E207" s="3" t="inlineStr">
+      <c r="F207" s="3" t="inlineStr">
         <is>
           <t>ATL (11)</t>
         </is>
       </c>
-      <c r="F207" s="3" t="inlineStr">
+      <c r="G207" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6309,17 +6932,20 @@
       <c r="C208" s="5" t="n">
         <v>220</v>
       </c>
-      <c r="D208" s="3" t="inlineStr">
+      <c r="D208" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
         <is>
           <t>Cade Otton</t>
         </is>
       </c>
-      <c r="E208" s="3" t="inlineStr">
+      <c r="F208" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F208" s="3" t="inlineStr">
+      <c r="G208" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -6337,17 +6963,20 @@
       <c r="C209" s="5" t="n">
         <v>267</v>
       </c>
-      <c r="D209" s="3" t="inlineStr">
+      <c r="D209" s="3" t="n">
+        <v>256</v>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
         <is>
           <t>David Njoku</t>
         </is>
       </c>
-      <c r="E209" s="3" t="inlineStr">
+      <c r="F209" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F209" s="3" t="inlineStr">
+      <c r="G209" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -6365,17 +6994,20 @@
       <c r="C210" s="5" t="n">
         <v>237</v>
       </c>
-      <c r="D210" s="3" t="inlineStr">
+      <c r="D210" s="3" t="n">
+        <v>239</v>
+      </c>
+      <c r="E210" s="3" t="inlineStr">
         <is>
           <t>Justice Hill</t>
         </is>
       </c>
-      <c r="E210" s="3" t="inlineStr">
+      <c r="F210" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="F210" s="3" t="inlineStr">
+      <c r="G210" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -6393,17 +7025,20 @@
       <c r="C211" s="5" t="n">
         <v>244</v>
       </c>
-      <c r="D211" s="3" t="inlineStr">
+      <c r="D211" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
         <is>
           <t>Jack Bech</t>
         </is>
       </c>
-      <c r="E211" s="3" t="inlineStr">
+      <c r="F211" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F211" s="3" t="inlineStr">
+      <c r="G211" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6421,17 +7056,20 @@
       <c r="C212" s="5" t="n">
         <v>276</v>
       </c>
-      <c r="D212" s="3" t="inlineStr">
+      <c r="D212" s="3" t="n">
+        <v>283</v>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
         <is>
           <t>Ted Hurst</t>
         </is>
       </c>
-      <c r="E212" s="3" t="inlineStr">
+      <c r="F212" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="F212" s="3" t="inlineStr">
+      <c r="G212" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6449,17 +7087,20 @@
       <c r="C213" s="5" t="n">
         <v>232</v>
       </c>
-      <c r="D213" s="3" t="inlineStr">
+      <c r="D213" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="E213" s="3" t="inlineStr">
         <is>
           <t>Terrance Ferguson</t>
         </is>
       </c>
-      <c r="E213" s="3" t="inlineStr">
+      <c r="F213" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="F213" s="3" t="inlineStr">
+      <c r="G213" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -6477,17 +7118,20 @@
       <c r="C214" s="5" t="n">
         <v>275</v>
       </c>
-      <c r="D214" s="3" t="inlineStr">
+      <c r="D214" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="E214" s="3" t="inlineStr">
         <is>
           <t>Ollie Gordon</t>
         </is>
       </c>
-      <c r="E214" s="3" t="inlineStr">
+      <c r="F214" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="F214" s="3" t="inlineStr">
+      <c r="G214" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -6505,17 +7149,20 @@
       <c r="C215" s="5" t="n">
         <v>202</v>
       </c>
-      <c r="D215" s="3" t="inlineStr">
+      <c r="D215" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
         <is>
           <t>MarShawn Lloyd</t>
         </is>
       </c>
-      <c r="E215" s="3" t="inlineStr">
+      <c r="F215" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F215" s="3" t="inlineStr">
+      <c r="G215" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -6533,17 +7180,20 @@
       <c r="C216" s="5" t="n">
         <v>277</v>
       </c>
-      <c r="D216" s="3" t="inlineStr">
+      <c r="D216" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
         <is>
           <t>Elic Ayomanor</t>
         </is>
       </c>
-      <c r="E216" s="3" t="inlineStr">
+      <c r="F216" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="F216" s="3" t="inlineStr">
+      <c r="G216" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6561,17 +7211,20 @@
       <c r="C217" s="5" t="n">
         <v>219</v>
       </c>
-      <c r="D217" s="3" t="inlineStr">
+      <c r="D217" s="3" t="n">
+        <v>226</v>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
         <is>
           <t>Colby Parkinson</t>
         </is>
       </c>
-      <c r="E217" s="3" t="inlineStr">
+      <c r="F217" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="F217" s="3" t="inlineStr">
+      <c r="G217" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -6589,17 +7242,20 @@
       <c r="C218" s="5" t="n">
         <v>278</v>
       </c>
-      <c r="D218" s="3" t="inlineStr">
+      <c r="D218" s="3" t="n">
+        <v>288</v>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
         <is>
           <t>Keon Coleman</t>
         </is>
       </c>
-      <c r="E218" s="3" t="inlineStr">
+      <c r="F218" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="F218" s="3" t="inlineStr">
+      <c r="G218" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6617,17 +7273,20 @@
       <c r="C219" s="5" t="n">
         <v>258</v>
       </c>
-      <c r="D219" s="3" t="inlineStr">
+      <c r="D219" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
         <is>
           <t>Chris Bell</t>
         </is>
       </c>
-      <c r="E219" s="3" t="inlineStr">
+      <c r="F219" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="F219" s="3" t="inlineStr">
+      <c r="G219" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6645,17 +7304,20 @@
       <c r="C220" s="5" t="n">
         <v>246</v>
       </c>
-      <c r="D220" s="3" t="inlineStr">
+      <c r="D220" s="3" t="n">
+        <v>249</v>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
         <is>
           <t>Elijah Sarratt</t>
         </is>
       </c>
-      <c r="E220" s="3" t="inlineStr">
+      <c r="F220" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="F220" s="3" t="inlineStr">
+      <c r="G220" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6673,17 +7335,20 @@
       <c r="C221" s="5" t="n">
         <v>253</v>
       </c>
-      <c r="D221" s="3" t="inlineStr">
+      <c r="D221" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
         <is>
           <t>Evan Engram</t>
         </is>
       </c>
-      <c r="E221" s="3" t="inlineStr">
+      <c r="F221" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F221" s="3" t="inlineStr">
+      <c r="G221" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -6701,17 +7366,18 @@
       <c r="C222" s="4" t="n">
         <v>299</v>
       </c>
-      <c r="D222" s="3" t="inlineStr">
+      <c r="D222" s="3" t="inlineStr"/>
+      <c r="E222" s="3" t="inlineStr">
         <is>
           <t>Christian Kirk</t>
         </is>
       </c>
-      <c r="E222" s="3" t="inlineStr">
+      <c r="F222" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F222" s="3" t="inlineStr">
+      <c r="G222" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6729,17 +7395,20 @@
       <c r="C223" s="5" t="n">
         <v>285</v>
       </c>
-      <c r="D223" s="3" t="inlineStr">
+      <c r="D223" s="3" t="n">
+        <v>294</v>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
         <is>
           <t>Malachi Fields</t>
         </is>
       </c>
-      <c r="E223" s="3" t="inlineStr">
+      <c r="F223" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F223" s="3" t="inlineStr">
+      <c r="G223" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6757,17 +7426,20 @@
       <c r="C224" s="5" t="n">
         <v>266</v>
       </c>
-      <c r="D224" s="3" t="inlineStr">
+      <c r="D224" s="3" t="n">
+        <v>273</v>
+      </c>
+      <c r="E224" s="3" t="inlineStr">
         <is>
           <t>DJ Giddens</t>
         </is>
       </c>
-      <c r="E224" s="3" t="inlineStr">
+      <c r="F224" s="3" t="inlineStr">
         <is>
           <t>IND (13)</t>
         </is>
       </c>
-      <c r="F224" s="3" t="inlineStr">
+      <c r="G224" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -6785,17 +7457,20 @@
       <c r="C225" s="5" t="n">
         <v>264</v>
       </c>
-      <c r="D225" s="3" t="inlineStr">
+      <c r="D225" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="E225" s="3" t="inlineStr">
         <is>
           <t>Eli Stowers</t>
         </is>
       </c>
-      <c r="E225" s="3" t="inlineStr">
+      <c r="F225" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F225" s="3" t="inlineStr">
+      <c r="G225" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -6813,17 +7488,20 @@
       <c r="C226" s="5" t="n">
         <v>280</v>
       </c>
-      <c r="D226" s="3" t="inlineStr">
+      <c r="D226" s="3" t="n">
+        <v>291</v>
+      </c>
+      <c r="E226" s="3" t="inlineStr">
         <is>
           <t>Tory Horton</t>
         </is>
       </c>
-      <c r="E226" s="3" t="inlineStr">
+      <c r="F226" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F226" s="3" t="inlineStr">
+      <c r="G226" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6841,17 +7519,20 @@
       <c r="C227" s="5" t="n">
         <v>284</v>
       </c>
-      <c r="D227" s="3" t="inlineStr">
+      <c r="D227" s="3" t="n">
+        <v>292</v>
+      </c>
+      <c r="E227" s="3" t="inlineStr">
         <is>
           <t>Marvin Mims</t>
         </is>
       </c>
-      <c r="E227" s="3" t="inlineStr">
+      <c r="F227" s="3" t="inlineStr">
         <is>
           <t>DEN (10)</t>
         </is>
       </c>
-      <c r="F227" s="3" t="inlineStr">
+      <c r="G227" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6869,17 +7550,20 @@
       <c r="C228" s="5" t="n">
         <v>250</v>
       </c>
-      <c r="D228" s="3" t="inlineStr">
+      <c r="D228" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="E228" s="3" t="inlineStr">
         <is>
           <t>Jaydon Blue</t>
         </is>
       </c>
-      <c r="E228" s="3" t="inlineStr">
+      <c r="F228" s="3" t="inlineStr">
         <is>
           <t>DAL (14)</t>
         </is>
       </c>
-      <c r="F228" s="3" t="inlineStr">
+      <c r="G228" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -6897,17 +7581,18 @@
       <c r="C229" s="5" t="n">
         <v>260</v>
       </c>
-      <c r="D229" s="3" t="inlineStr">
+      <c r="D229" s="3" t="inlineStr"/>
+      <c r="E229" s="3" t="inlineStr">
         <is>
           <t>Chris Brazzell</t>
         </is>
       </c>
-      <c r="E229" s="3" t="inlineStr">
+      <c r="F229" s="3" t="inlineStr">
         <is>
           <t>CAR (5)</t>
         </is>
       </c>
-      <c r="F229" s="3" t="inlineStr">
+      <c r="G229" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -6925,17 +7610,20 @@
       <c r="C230" s="5" t="n">
         <v>297</v>
       </c>
-      <c r="D230" s="3" t="inlineStr">
+      <c r="D230" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
         <is>
           <t>Mason Taylor</t>
         </is>
       </c>
-      <c r="E230" s="3" t="inlineStr">
+      <c r="F230" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F230" s="3" t="inlineStr">
+      <c r="G230" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -6953,17 +7641,20 @@
       <c r="C231" s="5" t="n">
         <v>283</v>
       </c>
-      <c r="D231" s="3" t="inlineStr">
+      <c r="D231" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
         <is>
           <t>Chris Brooks</t>
         </is>
       </c>
-      <c r="E231" s="3" t="inlineStr">
+      <c r="F231" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="F231" s="3" t="inlineStr">
+      <c r="G231" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -6981,17 +7672,20 @@
       <c r="C232" s="5" t="n">
         <v>240</v>
       </c>
-      <c r="D232" s="3" t="inlineStr">
+      <c r="D232" s="3" t="n">
+        <v>241</v>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
         <is>
           <t>Tua Tagovailoa</t>
         </is>
       </c>
-      <c r="E232" s="3" t="inlineStr">
+      <c r="F232" s="3" t="inlineStr">
         <is>
           <t>ATL (11)</t>
         </is>
       </c>
-      <c r="F232" s="3" t="inlineStr">
+      <c r="G232" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -7009,17 +7703,20 @@
       <c r="C233" s="5" t="n">
         <v>207</v>
       </c>
-      <c r="D233" s="3" t="inlineStr">
+      <c r="D233" s="3" t="n">
+        <v>212</v>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
         <is>
           <t>Darius Slayton</t>
         </is>
       </c>
-      <c r="E233" s="3" t="inlineStr">
+      <c r="F233" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F233" s="3" t="inlineStr">
+      <c r="G233" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7037,17 +7734,20 @@
       <c r="C234" s="5" t="n">
         <v>286</v>
       </c>
-      <c r="D234" s="3" t="inlineStr">
+      <c r="D234" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
         <is>
           <t>Samaje Perine</t>
         </is>
       </c>
-      <c r="E234" s="3" t="inlineStr">
+      <c r="F234" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="F234" s="3" t="inlineStr">
+      <c r="G234" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -7065,17 +7765,20 @@
       <c r="C235" s="5" t="n">
         <v>281</v>
       </c>
-      <c r="D235" s="3" t="inlineStr">
+      <c r="D235" s="3" t="n">
+        <v>289</v>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
         <is>
           <t>Isaiah Davis</t>
         </is>
       </c>
-      <c r="E235" s="3" t="inlineStr">
+      <c r="F235" s="3" t="inlineStr">
         <is>
           <t>NYJ (13)</t>
         </is>
       </c>
-      <c r="F235" s="3" t="inlineStr">
+      <c r="G235" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -7093,17 +7796,20 @@
       <c r="C236" s="5" t="n">
         <v>279</v>
       </c>
-      <c r="D236" s="3" t="inlineStr">
+      <c r="D236" s="3" t="n">
+        <v>287</v>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
         <is>
           <t>Demond Claiborne</t>
         </is>
       </c>
-      <c r="E236" s="3" t="inlineStr">
+      <c r="F236" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="F236" s="3" t="inlineStr">
+      <c r="G236" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -7121,17 +7827,20 @@
       <c r="C237" s="5" t="n">
         <v>287</v>
       </c>
-      <c r="D237" s="3" t="inlineStr">
+      <c r="D237" s="3" t="n">
+        <v>286</v>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
         <is>
           <t>LeQuint Allen</t>
         </is>
       </c>
-      <c r="E237" s="3" t="inlineStr">
+      <c r="F237" s="3" t="inlineStr">
         <is>
           <t>JAC (7)</t>
         </is>
       </c>
-      <c r="F237" s="3" t="inlineStr">
+      <c r="G237" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -7149,17 +7858,20 @@
       <c r="C238" s="5" t="n">
         <v>252</v>
       </c>
-      <c r="D238" s="3" t="inlineStr">
+      <c r="D238" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="E238" s="3" t="inlineStr">
         <is>
           <t>Michael Penix</t>
         </is>
       </c>
-      <c r="E238" s="3" t="inlineStr">
+      <c r="F238" s="3" t="inlineStr">
         <is>
           <t>ATL (11)</t>
         </is>
       </c>
-      <c r="F238" s="3" t="inlineStr">
+      <c r="G238" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -7177,17 +7889,20 @@
       <c r="C239" s="5" t="n">
         <v>249</v>
       </c>
-      <c r="D239" s="3" t="inlineStr">
+      <c r="D239" s="3" t="n">
+        <v>253</v>
+      </c>
+      <c r="E239" s="3" t="inlineStr">
         <is>
           <t>Jordan James</t>
         </is>
       </c>
-      <c r="E239" s="3" t="inlineStr">
+      <c r="F239" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F239" s="3" t="inlineStr">
+      <c r="G239" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -7205,17 +7920,20 @@
       <c r="C240" s="5" t="n">
         <v>214</v>
       </c>
-      <c r="D240" s="3" t="inlineStr">
+      <c r="D240" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="E240" s="3" t="inlineStr">
         <is>
           <t>Greg Dulcich</t>
         </is>
       </c>
-      <c r="E240" s="3" t="inlineStr">
+      <c r="F240" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="F240" s="3" t="inlineStr">
+      <c r="G240" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -7233,17 +7951,20 @@
       <c r="C241" s="5" t="n">
         <v>248</v>
       </c>
-      <c r="D241" s="3" t="inlineStr">
+      <c r="D241" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
         <is>
           <t>Tyquan Thornton</t>
         </is>
       </c>
-      <c r="E241" s="3" t="inlineStr">
+      <c r="F241" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F241" s="3" t="inlineStr">
+      <c r="G241" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7261,17 +7982,20 @@
       <c r="C242" s="5" t="n">
         <v>282</v>
       </c>
-      <c r="D242" s="3" t="inlineStr">
+      <c r="D242" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
         <is>
           <t>George Holani</t>
         </is>
       </c>
-      <c r="E242" s="3" t="inlineStr">
+      <c r="F242" s="3" t="inlineStr">
         <is>
           <t>SEA (11)</t>
         </is>
       </c>
-      <c r="F242" s="3" t="inlineStr">
+      <c r="G242" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -7289,17 +8013,20 @@
       <c r="C243" s="5" t="n">
         <v>296</v>
       </c>
-      <c r="D243" s="3" t="inlineStr">
+      <c r="D243" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
         <is>
           <t>Devaughn Vele</t>
         </is>
       </c>
-      <c r="E243" s="3" t="inlineStr">
+      <c r="F243" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="F243" s="3" t="inlineStr">
+      <c r="G243" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7317,17 +8044,20 @@
       <c r="C244" s="5" t="n">
         <v>257</v>
       </c>
-      <c r="D244" s="3" t="inlineStr">
+      <c r="D244" s="3" t="n">
+        <v>251</v>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
         <is>
           <t>Keenan Allen</t>
         </is>
       </c>
-      <c r="E244" s="3" t="inlineStr">
+      <c r="F244" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="F244" s="3" t="inlineStr">
+      <c r="G244" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7345,17 +8075,20 @@
       <c r="C245" s="5" t="n">
         <v>205</v>
       </c>
-      <c r="D245" s="3" t="inlineStr">
+      <c r="D245" s="3" t="n">
+        <v>211</v>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
         <is>
           <t>Kaelon Black</t>
         </is>
       </c>
-      <c r="E245" s="3" t="inlineStr">
+      <c r="F245" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="F245" s="3" t="inlineStr">
+      <c r="G245" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -7373,17 +8106,18 @@
       <c r="C246" s="5" t="n">
         <v>298</v>
       </c>
-      <c r="D246" s="3" t="inlineStr">
+      <c r="D246" s="3" t="inlineStr"/>
+      <c r="E246" s="3" t="inlineStr">
         <is>
           <t>Hollywood Brown</t>
         </is>
       </c>
-      <c r="E246" s="3" t="inlineStr">
+      <c r="F246" s="3" t="inlineStr">
         <is>
           <t>PHI (10)</t>
         </is>
       </c>
-      <c r="F246" s="3" t="inlineStr">
+      <c r="G246" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7401,17 +8135,20 @@
       <c r="C247" s="5" t="n">
         <v>288</v>
       </c>
-      <c r="D247" s="3" t="inlineStr">
+      <c r="D247" s="3" t="n">
+        <v>296</v>
+      </c>
+      <c r="E247" s="3" t="inlineStr">
         <is>
           <t>Mack Hollins</t>
         </is>
       </c>
-      <c r="E247" s="3" t="inlineStr">
+      <c r="F247" s="3" t="inlineStr">
         <is>
           <t>NE (11)</t>
         </is>
       </c>
-      <c r="F247" s="3" t="inlineStr">
+      <c r="G247" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7429,17 +8166,20 @@
       <c r="C248" s="5" t="n">
         <v>261</v>
       </c>
-      <c r="D248" s="3" t="inlineStr">
+      <c r="D248" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="E248" s="3" t="inlineStr">
         <is>
           <t>Emari Demercado</t>
         </is>
       </c>
-      <c r="E248" s="3" t="inlineStr">
+      <c r="F248" s="3" t="inlineStr">
         <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="F248" s="3" t="inlineStr">
+      <c r="G248" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
@@ -7457,17 +8197,20 @@
       <c r="C249" s="5" t="n">
         <v>241</v>
       </c>
-      <c r="D249" s="3" t="inlineStr">
+      <c r="D249" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
         <is>
           <t>Deshaun Watson</t>
         </is>
       </c>
-      <c r="E249" s="3" t="inlineStr">
+      <c r="F249" s="3" t="inlineStr">
         <is>
           <t>CLE (11)</t>
         </is>
       </c>
-      <c r="F249" s="3" t="inlineStr">
+      <c r="G249" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -7485,17 +8228,20 @@
       <c r="C250" s="5" t="n">
         <v>255</v>
       </c>
-      <c r="D250" s="3" t="inlineStr">
+      <c r="D250" s="3" t="n">
+        <v>261</v>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
         <is>
           <t>Mike Gesicki</t>
         </is>
       </c>
-      <c r="E250" s="3" t="inlineStr">
+      <c r="F250" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="F250" s="3" t="inlineStr">
+      <c r="G250" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
@@ -7513,17 +8259,20 @@
       <c r="C251" s="5" t="n">
         <v>251</v>
       </c>
-      <c r="D251" s="3" t="inlineStr">
+      <c r="D251" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
         <is>
           <t>Kirk Cousins</t>
         </is>
       </c>
-      <c r="E251" s="3" t="inlineStr">
+      <c r="F251" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="F251" s="3" t="inlineStr">
+      <c r="G251" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
@@ -7541,17 +8290,20 @@
       <c r="C252" s="5" t="n">
         <v>291</v>
       </c>
-      <c r="D252" s="3" t="inlineStr">
+      <c r="D252" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="E252" s="3" t="inlineStr">
         <is>
           <t>Ja'Kobi Lane</t>
         </is>
       </c>
-      <c r="E252" s="3" t="inlineStr">
+      <c r="F252" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="F252" s="3" t="inlineStr">
+      <c r="G252" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7569,17 +8321,20 @@
       <c r="C253" s="5" t="n">
         <v>290</v>
       </c>
-      <c r="D253" s="3" t="inlineStr">
+      <c r="D253" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="E253" s="3" t="inlineStr">
         <is>
           <t>Andrei Iosivas</t>
         </is>
       </c>
-      <c r="E253" s="3" t="inlineStr">
+      <c r="F253" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="F253" s="3" t="inlineStr">
+      <c r="G253" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7597,17 +8352,20 @@
       <c r="C254" s="5" t="n">
         <v>292</v>
       </c>
-      <c r="D254" s="3" t="inlineStr">
+      <c r="D254" s="3" t="n">
+        <v>297</v>
+      </c>
+      <c r="E254" s="3" t="inlineStr">
         <is>
           <t>Calvin Austin</t>
         </is>
       </c>
-      <c r="E254" s="3" t="inlineStr">
+      <c r="F254" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="F254" s="3" t="inlineStr">
+      <c r="G254" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7625,17 +8383,20 @@
       <c r="C255" s="5" t="n">
         <v>269</v>
       </c>
-      <c r="D255" s="3" t="inlineStr">
+      <c r="D255" s="3" t="n">
+        <v>278</v>
+      </c>
+      <c r="E255" s="3" t="inlineStr">
         <is>
           <t>Jalen Tolbert</t>
         </is>
       </c>
-      <c r="E255" s="3" t="inlineStr">
+      <c r="F255" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="F255" s="3" t="inlineStr">
+      <c r="G255" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7653,17 +8414,20 @@
       <c r="C256" s="5" t="n">
         <v>294</v>
       </c>
-      <c r="D256" s="3" t="inlineStr">
+      <c r="D256" s="3" t="n">
+        <v>299</v>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
         <is>
           <t>Kendrick Bourne</t>
         </is>
       </c>
-      <c r="E256" s="3" t="inlineStr">
+      <c r="F256" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="F256" s="3" t="inlineStr">
+      <c r="G256" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>
@@ -7681,17 +8445,20 @@
       <c r="C257" s="5" t="n">
         <v>293</v>
       </c>
-      <c r="D257" s="3" t="inlineStr">
+      <c r="D257" s="3" t="n">
+        <v>293</v>
+      </c>
+      <c r="E257" s="3" t="inlineStr">
         <is>
           <t>Treylon Burks</t>
         </is>
       </c>
-      <c r="E257" s="3" t="inlineStr">
+      <c r="F257" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="F257" s="3" t="inlineStr">
+      <c r="G257" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G257"/>
+  <dimension ref="A1:G305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>8</v>
@@ -699,7 +699,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>7</v>
@@ -730,7 +730,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>10</v>
@@ -761,7 +761,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>5</v>
@@ -791,8 +791,8 @@
       <c r="B10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>9</v>
+      <c r="C10" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>17</v>
@@ -822,8 +822,8 @@
       <c r="B11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="7" t="n">
-        <v>7</v>
+      <c r="C11" s="5" t="n">
+        <v>9</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>6</v>
@@ -885,7 +885,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>21</v>
@@ -916,7 +916,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>23</v>
@@ -947,7 +947,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>15</v>
@@ -978,7 +978,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>22</v>
@@ -1009,7 +1009,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>28</v>
@@ -1040,7 +1040,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>12</v>
@@ -1071,7 +1071,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>13</v>
@@ -1102,7 +1102,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>37</v>
@@ -1133,7 +1133,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>14</v>
@@ -1195,7 +1195,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>44</v>
@@ -1225,8 +1225,8 @@
       <c r="B24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C24" s="4" t="n">
-        <v>28</v>
+      <c r="C24" s="9" t="n">
+        <v>36</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>29</v>
@@ -1257,7 +1257,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>19</v>
@@ -1288,7 +1288,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>26</v>
@@ -1319,7 +1319,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>11</v>
@@ -1350,7 +1350,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>39</v>
@@ -1381,7 +1381,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>40</v>
@@ -1412,7 +1412,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>9</v>
@@ -1442,8 +1442,8 @@
       <c r="B31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C31" s="4" t="n">
-        <v>35</v>
+      <c r="C31" s="5" t="n">
+        <v>28</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>33</v>
@@ -1474,7 +1474,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>31</v>
@@ -1505,7 +1505,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="9" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>45</v>
@@ -1536,7 +1536,7 @@
         <v>33</v>
       </c>
       <c r="C34" s="9" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>61</v>
@@ -1567,7 +1567,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>42</v>
@@ -1597,8 +1597,8 @@
       <c r="B36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="C36" s="7" t="n">
-        <v>30</v>
+      <c r="C36" s="5" t="n">
+        <v>35</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>30</v>
@@ -1629,7 +1629,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>24</v>
@@ -1660,7 +1660,7 @@
         <v>37</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>41</v>
@@ -1690,8 +1690,8 @@
       <c r="B39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="C39" s="11" t="n">
-        <v>27</v>
+      <c r="C39" s="7" t="n">
+        <v>26</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>27</v>
@@ -1722,7 +1722,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>16</v>
@@ -1753,7 +1753,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>34</v>
@@ -1784,7 +1784,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>25</v>
@@ -1814,8 +1814,8 @@
       <c r="B43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="7" t="n">
-        <v>33</v>
+      <c r="C43" s="5" t="n">
+        <v>43</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>35</v>
@@ -1846,7 +1846,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>48</v>
@@ -1877,7 +1877,7 @@
         <v>44</v>
       </c>
       <c r="C45" s="9" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>60</v>
@@ -1908,7 +1908,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>36</v>
@@ -1938,8 +1938,8 @@
       <c r="B47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="C47" s="4" t="n">
-        <v>54</v>
+      <c r="C47" s="5" t="n">
+        <v>46</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>51</v>
@@ -1970,7 +1970,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>32</v>
@@ -2001,7 +2001,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>38</v>
@@ -2063,7 +2063,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>52</v>
@@ -2094,7 +2094,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D52" s="3" t="n">
         <v>46</v>
@@ -2125,7 +2125,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>58</v>
@@ -2218,7 +2218,7 @@
         <v>55</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D56" s="3" t="n">
         <v>59</v>
@@ -2249,7 +2249,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>47</v>
@@ -2310,8 +2310,8 @@
       <c r="B59" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="C59" s="5" t="n">
-        <v>62</v>
+      <c r="C59" s="9" t="n">
+        <v>71</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>62</v>
@@ -2342,7 +2342,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D60" s="3" t="n">
         <v>50</v>
@@ -2373,7 +2373,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>72</v>
@@ -2403,8 +2403,8 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="11" t="n">
-        <v>56</v>
+      <c r="C62" s="5" t="n">
+        <v>58</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>56</v>
@@ -2435,7 +2435,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>49</v>
@@ -2465,8 +2465,8 @@
       <c r="B64" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="C64" s="4" t="n">
-        <v>73</v>
+      <c r="C64" s="9" t="n">
+        <v>76</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>74</v>
@@ -2497,7 +2497,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>55</v>
@@ -2528,7 +2528,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>67</v>
@@ -2559,7 +2559,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>75</v>
@@ -2589,8 +2589,8 @@
       <c r="B68" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="C68" s="5" t="n">
-        <v>77</v>
+      <c r="C68" s="9" t="n">
+        <v>82</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>77</v>
@@ -2621,7 +2621,7 @@
         <v>68</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>80</v>
@@ -2651,8 +2651,8 @@
       <c r="B70" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="C70" s="11" t="n">
-        <v>64</v>
+      <c r="C70" s="7" t="n">
+        <v>59</v>
       </c>
       <c r="D70" s="3" t="n">
         <v>64</v>
@@ -2745,7 +2745,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>65</v>
@@ -2776,7 +2776,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D74" s="3" t="n">
         <v>84</v>
@@ -2807,7 +2807,7 @@
         <v>74</v>
       </c>
       <c r="C75" s="9" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>108</v>
@@ -2838,7 +2838,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D76" s="3" t="n">
         <v>63</v>
@@ -2869,7 +2869,7 @@
         <v>76</v>
       </c>
       <c r="C77" s="9" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>97</v>
@@ -2900,7 +2900,7 @@
         <v>77</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D78" s="3" t="n">
         <v>73</v>
@@ -2930,8 +2930,8 @@
       <c r="B79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C79" s="5" t="n">
-        <v>78</v>
+      <c r="C79" s="11" t="n">
+        <v>72</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>78</v>
@@ -2962,7 +2962,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D80" s="3" t="n">
         <v>68</v>
@@ -2993,7 +2993,7 @@
         <v>80</v>
       </c>
       <c r="C81" s="9" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>101</v>
@@ -3024,7 +3024,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D82" s="3" t="n">
         <v>70</v>
@@ -3055,7 +3055,7 @@
         <v>82</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>86</v>
@@ -3086,7 +3086,7 @@
         <v>83</v>
       </c>
       <c r="C84" s="9" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D84" s="3" t="n">
         <v>109</v>
@@ -3117,7 +3117,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>71</v>
@@ -3148,7 +3148,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D86" s="3" t="n">
         <v>103</v>
@@ -3179,7 +3179,7 @@
         <v>86</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>76</v>
@@ -3210,7 +3210,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="9" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>136</v>
@@ -3241,7 +3241,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>79</v>
@@ -3272,7 +3272,7 @@
         <v>89</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D90" s="3" t="n">
         <v>111</v>
@@ -3303,7 +3303,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="9" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>99</v>
@@ -3333,8 +3333,8 @@
       <c r="B92" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="C92" s="5" t="n">
-        <v>98</v>
+      <c r="C92" s="9" t="n">
+        <v>108</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>105</v>
@@ -3364,8 +3364,8 @@
       <c r="B93" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="C93" s="11" t="n">
-        <v>66</v>
+      <c r="C93" s="7" t="n">
+        <v>54</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>66</v>
@@ -3396,7 +3396,7 @@
         <v>93</v>
       </c>
       <c r="C94" s="9" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D94" s="3" t="n">
         <v>149</v>
@@ -3426,8 +3426,8 @@
       <c r="B95" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="C95" s="5" t="n">
-        <v>99</v>
+      <c r="C95" s="9" t="n">
+        <v>109</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>106</v>
@@ -3458,7 +3458,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D96" s="3" t="n">
         <v>85</v>
@@ -3489,7 +3489,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>91</v>
@@ -3520,7 +3520,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D98" s="3" t="n">
         <v>131</v>
@@ -3550,8 +3550,8 @@
       <c r="B99" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="C99" s="11" t="n">
-        <v>91</v>
+      <c r="C99" s="5" t="n">
+        <v>99</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>95</v>
@@ -3582,7 +3582,7 @@
         <v>99</v>
       </c>
       <c r="C100" s="9" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>118</v>
@@ -3613,7 +3613,7 @@
         <v>101</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>96</v>
@@ -3644,7 +3644,7 @@
         <v>102</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>137</v>
@@ -3675,7 +3675,7 @@
         <v>103</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>98</v>
@@ -3705,8 +3705,8 @@
       <c r="B104" s="3" t="n">
         <v>104</v>
       </c>
-      <c r="C104" s="5" t="n">
-        <v>88</v>
+      <c r="C104" s="11" t="n">
+        <v>77</v>
       </c>
       <c r="D104" s="3" t="n">
         <v>83</v>
@@ -3737,7 +3737,7 @@
         <v>105</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>152</v>
@@ -3768,7 +3768,7 @@
         <v>106</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>89</v>
@@ -3799,7 +3799,7 @@
         <v>107</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>82</v>
@@ -3830,7 +3830,7 @@
         <v>108</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>138</v>
@@ -3861,7 +3861,7 @@
         <v>109</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>114</v>
@@ -3892,7 +3892,7 @@
         <v>110</v>
       </c>
       <c r="C110" s="7" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>94</v>
@@ -3923,7 +3923,7 @@
         <v>111</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>130</v>
@@ -3954,7 +3954,7 @@
         <v>112</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>102</v>
@@ -3985,7 +3985,7 @@
         <v>113</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>87</v>
@@ -4016,7 +4016,7 @@
         <v>114</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>120</v>
@@ -4046,8 +4046,8 @@
       <c r="B115" s="3" t="n">
         <v>115</v>
       </c>
-      <c r="C115" s="5" t="n">
-        <v>112</v>
+      <c r="C115" s="11" t="n">
+        <v>111</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>116</v>
@@ -4078,7 +4078,7 @@
         <v>116</v>
       </c>
       <c r="C116" s="9" t="n">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>148</v>
@@ -4109,7 +4109,7 @@
         <v>117</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>115</v>
@@ -4140,7 +4140,7 @@
         <v>118</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>119</v>
@@ -4171,7 +4171,7 @@
         <v>119</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>129</v>
@@ -4202,7 +4202,7 @@
         <v>120</v>
       </c>
       <c r="C120" s="4" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>124</v>
@@ -4264,7 +4264,7 @@
         <v>122</v>
       </c>
       <c r="C122" s="9" t="n">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>166</v>
@@ -4294,8 +4294,8 @@
       <c r="B123" s="3" t="n">
         <v>123</v>
       </c>
-      <c r="C123" s="5" t="n">
-        <v>121</v>
+      <c r="C123" s="7" t="n">
+        <v>101</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>121</v>
@@ -4325,8 +4325,8 @@
       <c r="B124" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="C124" s="5" t="n">
-        <v>123</v>
+      <c r="C124" s="7" t="n">
+        <v>91</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>88</v>
@@ -4357,7 +4357,7 @@
         <v>125</v>
       </c>
       <c r="C125" s="7" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>104</v>
@@ -4388,7 +4388,7 @@
         <v>126</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D126" s="3" t="n">
         <v>125</v>
@@ -4419,7 +4419,7 @@
         <v>127</v>
       </c>
       <c r="C127" s="4" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>135</v>
@@ -4450,7 +4450,7 @@
         <v>128</v>
       </c>
       <c r="C128" s="7" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D128" s="3" t="n">
         <v>93</v>
@@ -4481,7 +4481,7 @@
         <v>129</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>155</v>
@@ -4511,8 +4511,8 @@
       <c r="B130" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="C130" s="11" t="n">
-        <v>122</v>
+      <c r="C130" s="7" t="n">
+        <v>117</v>
       </c>
       <c r="D130" s="3" t="n">
         <v>122</v>
@@ -4543,7 +4543,7 @@
         <v>131</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>133</v>
@@ -4574,7 +4574,7 @@
         <v>132</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D132" s="3" t="n">
         <v>110</v>
@@ -4604,8 +4604,8 @@
       <c r="B133" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="C133" s="5" t="n">
-        <v>101</v>
+      <c r="C133" s="11" t="n">
+        <v>94</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>100</v>
@@ -4636,7 +4636,7 @@
         <v>134</v>
       </c>
       <c r="C134" s="9" t="n">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>165</v>
@@ -4667,7 +4667,7 @@
         <v>135</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>147</v>
@@ -4698,7 +4698,7 @@
         <v>136</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D136" s="3" t="n">
         <v>169</v>
@@ -4728,8 +4728,8 @@
       <c r="B137" s="3" t="n">
         <v>137</v>
       </c>
-      <c r="C137" s="9" t="n">
-        <v>238</v>
+      <c r="C137" s="5" t="n">
+        <v>174</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>190</v>
@@ -4760,7 +4760,7 @@
         <v>138</v>
       </c>
       <c r="C138" s="9" t="n">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="D138" s="3" t="n">
         <v>167</v>
@@ -4791,7 +4791,7 @@
         <v>139</v>
       </c>
       <c r="C139" s="7" t="n">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>112</v>
@@ -4822,7 +4822,7 @@
         <v>140</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="D140" s="3" t="n">
         <v>195</v>
@@ -4853,7 +4853,7 @@
         <v>141</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>172</v>
@@ -4884,7 +4884,7 @@
         <v>142</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="D142" s="3" t="n">
         <v>194</v>
@@ -4915,7 +4915,7 @@
         <v>143</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>171</v>
@@ -4946,7 +4946,7 @@
         <v>144</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="D144" s="3" t="n">
         <v>186</v>
@@ -4977,7 +4977,7 @@
         <v>145</v>
       </c>
       <c r="C145" s="9" t="n">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>206</v>
@@ -5008,7 +5008,7 @@
         <v>146</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D146" s="3" t="n">
         <v>134</v>
@@ -5039,7 +5039,7 @@
         <v>147</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>185</v>
@@ -5070,7 +5070,7 @@
         <v>148</v>
       </c>
       <c r="C148" s="9" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D148" s="3" t="n">
         <v>199</v>
@@ -5100,8 +5100,8 @@
       <c r="B149" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="C149" s="9" t="n">
-        <v>225</v>
+      <c r="C149" s="5" t="n">
+        <v>146</v>
       </c>
       <c r="D149" s="3" t="n">
         <v>181</v>
@@ -5132,7 +5132,7 @@
         <v>150</v>
       </c>
       <c r="C150" s="4" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D150" s="3" t="n">
         <v>198</v>
@@ -5163,7 +5163,7 @@
         <v>151</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="D151" s="3" t="n">
         <v>178</v>
@@ -5194,7 +5194,7 @@
         <v>152</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="D152" s="3" t="n">
         <v>177</v>
@@ -5225,7 +5225,7 @@
         <v>153</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D153" s="3" t="n">
         <v>200</v>
@@ -5256,7 +5256,7 @@
         <v>154</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D154" s="3" t="n">
         <v>173</v>
@@ -5287,7 +5287,7 @@
         <v>155</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>220</v>
@@ -5317,8 +5317,8 @@
       <c r="B156" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="C156" s="5" t="n">
-        <v>186</v>
+      <c r="C156" s="7" t="n">
+        <v>144</v>
       </c>
       <c r="D156" s="3" t="n">
         <v>183</v>
@@ -5349,7 +5349,7 @@
         <v>158</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>210</v>
@@ -5380,7 +5380,7 @@
         <v>159</v>
       </c>
       <c r="C158" s="7" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D158" s="3" t="n">
         <v>123</v>
@@ -5411,7 +5411,7 @@
         <v>160</v>
       </c>
       <c r="C159" s="4" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D159" s="3" t="n">
         <v>197</v>
@@ -5442,7 +5442,7 @@
         <v>161</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="D160" s="3" t="n">
         <v>158</v>
@@ -5473,7 +5473,7 @@
         <v>162</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>213</v>
@@ -5504,7 +5504,7 @@
         <v>164</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D162" s="3" t="n">
         <v>170</v>
@@ -5566,7 +5566,7 @@
         <v>166</v>
       </c>
       <c r="C164" s="4" t="n">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D164" s="3" t="n">
         <v>219</v>
@@ -5597,7 +5597,7 @@
         <v>167</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D165" s="3" t="n">
         <v>151</v>
@@ -5628,7 +5628,7 @@
         <v>169</v>
       </c>
       <c r="C166" s="4" t="n">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="D166" s="3" t="n">
         <v>225</v>
@@ -5659,7 +5659,7 @@
         <v>170</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D167" s="3" t="n">
         <v>182</v>
@@ -5689,8 +5689,8 @@
       <c r="B168" s="3" t="n">
         <v>173</v>
       </c>
-      <c r="C168" s="4" t="n">
-        <v>213</v>
+      <c r="C168" s="5" t="n">
+        <v>197</v>
       </c>
       <c r="D168" s="3" t="n">
         <v>217</v>
@@ -5721,7 +5721,7 @@
         <v>174</v>
       </c>
       <c r="C169" s="4" t="n">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D169" s="3" t="n">
         <v>282</v>
@@ -5752,7 +5752,7 @@
         <v>175</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>235</v>
+        <v>267</v>
       </c>
       <c r="D170" s="3" t="n">
         <v>238</v>
@@ -5783,7 +5783,7 @@
         <v>176</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="D171" s="3" t="n">
         <v>180</v>
@@ -5814,7 +5814,7 @@
         <v>177</v>
       </c>
       <c r="C172" s="7" t="n">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="D172" s="3" t="n">
         <v>92</v>
@@ -5845,7 +5845,7 @@
         <v>178</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="D173" s="3" t="n">
         <v>243</v>
@@ -5876,7 +5876,7 @@
         <v>179</v>
       </c>
       <c r="C174" s="4" t="n">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D174" s="3" t="n">
         <v>240</v>
@@ -5907,7 +5907,7 @@
         <v>185</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="D175" s="3" t="n">
         <v>275</v>
@@ -5938,7 +5938,7 @@
         <v>186</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>270</v>
+        <v>298</v>
       </c>
       <c r="D176" s="3" t="n">
         <v>277</v>
@@ -5968,8 +5968,8 @@
       <c r="B177" s="3" t="n">
         <v>187</v>
       </c>
-      <c r="C177" s="5" t="n">
-        <v>211</v>
+      <c r="C177" s="4" t="n">
+        <v>231</v>
       </c>
       <c r="D177" s="3" t="n">
         <v>216</v>
@@ -6000,7 +6000,7 @@
         <v>188</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D178" s="3" t="n">
         <v>214</v>
@@ -6030,8 +6030,8 @@
       <c r="B179" s="3" t="n">
         <v>191</v>
       </c>
-      <c r="C179" s="5" t="n">
-        <v>212</v>
+      <c r="C179" s="4" t="n">
+        <v>280</v>
       </c>
       <c r="D179" s="3" t="n">
         <v>260</v>
@@ -6062,7 +6062,7 @@
         <v>192</v>
       </c>
       <c r="C180" s="4" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="D180" s="3" t="n">
         <v>265</v>
@@ -6093,7 +6093,7 @@
         <v>194</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="D181" s="3" t="n">
         <v>252</v>
@@ -6124,7 +6124,7 @@
         <v>195</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="D182" s="3" t="n">
         <v>192</v>
@@ -6155,7 +6155,7 @@
         <v>196</v>
       </c>
       <c r="C183" s="5" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D183" s="3" t="n">
         <v>184</v>
@@ -6186,7 +6186,7 @@
         <v>197</v>
       </c>
       <c r="C184" s="4" t="n">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="D184" s="3" t="n">
         <v>274</v>
@@ -6217,7 +6217,7 @@
         <v>199</v>
       </c>
       <c r="C185" s="7" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D185" s="3" t="n">
         <v>157</v>
@@ -6248,7 +6248,7 @@
         <v>201</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D186" s="3" t="n">
         <v>150</v>
@@ -6278,8 +6278,8 @@
       <c r="B187" s="3" t="n">
         <v>202</v>
       </c>
-      <c r="C187" s="5" t="n">
-        <v>206</v>
+      <c r="C187" s="11" t="n">
+        <v>170</v>
       </c>
       <c r="D187" s="3" t="n">
         <v>196</v>
@@ -6310,7 +6310,7 @@
         <v>204</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D188" s="3" t="n">
         <v>209</v>
@@ -6340,8 +6340,8 @@
       <c r="B189" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C189" s="4" t="n">
-        <v>245</v>
+      <c r="C189" s="5" t="n">
+        <v>234</v>
       </c>
       <c r="D189" s="3" t="n">
         <v>245</v>
@@ -6372,7 +6372,7 @@
         <v>206</v>
       </c>
       <c r="C190" s="4" t="n">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="D190" s="3" t="n">
         <v>268</v>
@@ -6403,7 +6403,7 @@
         <v>207</v>
       </c>
       <c r="C191" s="5" t="n">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D191" s="3" t="n">
         <v>236</v>
@@ -6433,8 +6433,8 @@
       <c r="B192" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="C192" s="4" t="n">
-        <v>243</v>
+      <c r="C192" s="11" t="n">
+        <v>173</v>
       </c>
       <c r="D192" s="3" t="n">
         <v>179</v>
@@ -6465,7 +6465,7 @@
         <v>212</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D193" s="3" t="n">
         <v>191</v>
@@ -6496,7 +6496,7 @@
         <v>213</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="D194" s="3" t="n">
         <v>279</v>
@@ -6527,7 +6527,7 @@
         <v>217</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="D195" s="3" t="n">
         <v>262</v>
@@ -6558,7 +6558,7 @@
         <v>219</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="D196" s="3" t="n">
         <v>221</v>
@@ -6588,8 +6588,8 @@
       <c r="B197" s="3" t="n">
         <v>221</v>
       </c>
-      <c r="C197" s="5" t="n">
-        <v>234</v>
+      <c r="C197" s="4" t="n">
+        <v>265</v>
       </c>
       <c r="D197" s="3" t="n">
         <v>237</v>
@@ -6620,7 +6620,7 @@
         <v>222</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="D198" s="3" t="n">
         <v>224</v>
@@ -6651,7 +6651,7 @@
         <v>223</v>
       </c>
       <c r="C199" s="5" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="D199" s="3" t="n">
         <v>207</v>
@@ -6675,26 +6675,24 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>WR83</t>
+          <t>WR82</t>
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="C200" s="11" t="n">
-        <v>120</v>
-      </c>
-      <c r="D200" s="3" t="n">
-        <v>126</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C200" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D200" s="3" t="inlineStr"/>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Chimere Dike</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>TEN (9)</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -6706,26 +6704,26 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>WR84</t>
+          <t>WR83</t>
         </is>
       </c>
       <c r="B201" s="3" t="n">
-        <v>228</v>
-      </c>
-      <c r="C201" s="5" t="n">
-        <v>226</v>
+        <v>225</v>
+      </c>
+      <c r="C201" s="11" t="n">
+        <v>129</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>223</v>
+        <v>126</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>Germie Bernard</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>PIT (9)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -6737,26 +6735,26 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>WR85</t>
+          <t>WR84</t>
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C202" s="5" t="n">
-        <v>210</v>
+        <v>255</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>Rashod Bateman</t>
+          <t>Germie Bernard</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>BAL (13)</t>
+          <t>PIT (9)</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -6768,768 +6766,764 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
+          <t>WR85</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="C203" s="5" t="n">
+        <v>235</v>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>215</v>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>Rashod Bateman</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>BAL (13)</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
           <t>WR86</t>
         </is>
       </c>
-      <c r="B203" s="3" t="n">
+      <c r="B204" s="3" t="n">
         <v>232</v>
       </c>
-      <c r="C203" s="5" t="n">
-        <v>236</v>
-      </c>
-      <c r="D203" s="3" t="n">
+      <c r="C204" s="5" t="n">
+        <v>262</v>
+      </c>
+      <c r="D204" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="E203" s="3" t="inlineStr">
+      <c r="E204" s="3" t="inlineStr">
         <is>
           <t>Brandon Aiyuk</t>
         </is>
       </c>
-      <c r="F203" s="3" t="inlineStr">
+      <c r="F204" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="G203" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="6" t="inlineStr">
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="inlineStr">
         <is>
           <t>RB65</t>
         </is>
       </c>
-      <c r="B204" s="3" t="n">
+      <c r="B205" s="3" t="n">
         <v>233</v>
       </c>
-      <c r="C204" s="4" t="n">
-        <v>273</v>
-      </c>
-      <c r="D204" s="3" t="n">
+      <c r="C205" s="4" t="n">
+        <v>296</v>
+      </c>
+      <c r="D205" s="3" t="n">
         <v>280</v>
       </c>
-      <c r="E204" s="3" t="inlineStr">
+      <c r="E205" s="3" t="inlineStr">
         <is>
           <t>Jaylen Wright</t>
         </is>
       </c>
-      <c r="F204" s="3" t="inlineStr">
+      <c r="F205" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="G204" s="3" t="inlineStr">
+      <c r="G205" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="10" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="10" t="inlineStr">
         <is>
           <t>QB30</t>
         </is>
       </c>
-      <c r="B205" s="3" t="n">
+      <c r="B206" s="3" t="n">
         <v>234</v>
       </c>
-      <c r="C205" s="5" t="n">
-        <v>201</v>
-      </c>
-      <c r="D205" s="3" t="n">
+      <c r="C206" s="5" t="n">
+        <v>227</v>
+      </c>
+      <c r="D206" s="3" t="n">
         <v>208</v>
       </c>
-      <c r="E205" s="3" t="inlineStr">
+      <c r="E206" s="3" t="inlineStr">
         <is>
           <t>Fernando Mendoza</t>
         </is>
       </c>
-      <c r="F205" s="3" t="inlineStr">
+      <c r="F206" s="3" t="inlineStr">
         <is>
           <t>LV (13)</t>
         </is>
       </c>
-      <c r="G205" s="3" t="inlineStr">
+      <c r="G206" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="8" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="8" t="inlineStr">
         <is>
           <t>TE26</t>
         </is>
       </c>
-      <c r="B206" s="3" t="n">
+      <c r="B207" s="3" t="n">
         <v>235</v>
       </c>
-      <c r="C206" s="5" t="n">
-        <v>265</v>
-      </c>
-      <c r="D206" s="3" t="n">
+      <c r="C207" s="5" t="n">
+        <v>259</v>
+      </c>
+      <c r="D207" s="3" t="n">
         <v>272</v>
       </c>
-      <c r="E206" s="3" t="inlineStr">
+      <c r="E207" s="3" t="inlineStr">
         <is>
           <t>Pat Freiermuth</t>
         </is>
       </c>
-      <c r="F206" s="3" t="inlineStr">
+      <c r="F207" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="G206" s="3" t="inlineStr">
+      <c r="G207" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>WR87</t>
         </is>
       </c>
-      <c r="B207" s="3" t="n">
+      <c r="B208" s="3" t="n">
         <v>237</v>
       </c>
-      <c r="C207" s="5" t="n">
-        <v>256</v>
-      </c>
-      <c r="D207" s="3" t="n">
+      <c r="C208" s="5" t="n">
+        <v>261</v>
+      </c>
+      <c r="D208" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="E207" s="3" t="inlineStr">
+      <c r="E208" s="3" t="inlineStr">
         <is>
           <t>Zachariah Branch</t>
         </is>
       </c>
-      <c r="F207" s="3" t="inlineStr">
+      <c r="F208" s="3" t="inlineStr">
         <is>
           <t>ATL (11)</t>
         </is>
       </c>
-      <c r="G207" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="8" t="inlineStr">
-        <is>
-          <t>TE27</t>
-        </is>
-      </c>
-      <c r="B208" s="3" t="n">
-        <v>238</v>
-      </c>
-      <c r="C208" s="5" t="n">
-        <v>220</v>
-      </c>
-      <c r="D208" s="3" t="n">
-        <v>227</v>
-      </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>Cade Otton</t>
-        </is>
-      </c>
-      <c r="F208" s="3" t="inlineStr">
-        <is>
-          <t>TB (10)</t>
-        </is>
-      </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="8" t="inlineStr">
         <is>
+          <t>TE27</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="C209" s="5" t="n">
+        <v>208</v>
+      </c>
+      <c r="D209" s="3" t="n">
+        <v>227</v>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>Cade Otton</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>TB (10)</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="8" t="inlineStr">
+        <is>
           <t>TE28</t>
         </is>
       </c>
-      <c r="B209" s="3" t="n">
+      <c r="B210" s="3" t="n">
         <v>239</v>
       </c>
-      <c r="C209" s="5" t="n">
-        <v>267</v>
-      </c>
-      <c r="D209" s="3" t="n">
+      <c r="C210" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="D210" s="3" t="n">
         <v>256</v>
       </c>
-      <c r="E209" s="3" t="inlineStr">
+      <c r="E210" s="3" t="inlineStr">
         <is>
           <t>David Njoku</t>
         </is>
       </c>
-      <c r="F209" s="3" t="inlineStr">
+      <c r="F210" s="3" t="inlineStr">
         <is>
           <t>LAC (7)</t>
         </is>
       </c>
-      <c r="G209" s="3" t="inlineStr">
+      <c r="G210" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="6" t="inlineStr">
+    <row r="211">
+      <c r="A211" s="6" t="inlineStr">
         <is>
           <t>RB66</t>
         </is>
       </c>
-      <c r="B210" s="3" t="n">
+      <c r="B211" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="C210" s="5" t="n">
+      <c r="C211" s="5" t="n">
         <v>237</v>
       </c>
-      <c r="D210" s="3" t="n">
+      <c r="D211" s="3" t="n">
         <v>239</v>
       </c>
-      <c r="E210" s="3" t="inlineStr">
+      <c r="E211" s="3" t="inlineStr">
         <is>
           <t>Justice Hill</t>
         </is>
       </c>
-      <c r="F210" s="3" t="inlineStr">
+      <c r="F211" s="3" t="inlineStr">
         <is>
           <t>BAL (13)</t>
         </is>
       </c>
-      <c r="G210" s="3" t="inlineStr">
+      <c r="G211" s="3" t="inlineStr">
         <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="inlineStr">
-        <is>
-          <t>WR88</t>
-        </is>
-      </c>
-      <c r="B211" s="3" t="n">
-        <v>241</v>
-      </c>
-      <c r="C211" s="5" t="n">
-        <v>244</v>
-      </c>
-      <c r="D211" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="E211" s="3" t="inlineStr">
-        <is>
-          <t>Jack Bech</t>
-        </is>
-      </c>
-      <c r="F211" s="3" t="inlineStr">
-        <is>
-          <t>LV (13)</t>
-        </is>
-      </c>
-      <c r="G211" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
+          <t>WR88</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="n">
+        <v>241</v>
+      </c>
+      <c r="C212" s="5" t="n">
+        <v>266</v>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>Jack Bech</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr">
+        <is>
+          <t>LV (13)</t>
+        </is>
+      </c>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
           <t>WR89</t>
         </is>
       </c>
-      <c r="B212" s="3" t="n">
+      <c r="B213" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="C212" s="5" t="n">
-        <v>276</v>
-      </c>
-      <c r="D212" s="3" t="n">
+      <c r="C213" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="D213" s="3" t="n">
         <v>283</v>
       </c>
-      <c r="E212" s="3" t="inlineStr">
+      <c r="E213" s="3" t="inlineStr">
         <is>
           <t>Ted Hurst</t>
         </is>
       </c>
-      <c r="F212" s="3" t="inlineStr">
+      <c r="F213" s="3" t="inlineStr">
         <is>
           <t>TB (10)</t>
         </is>
       </c>
-      <c r="G212" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="8" t="inlineStr">
+      <c r="G213" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="8" t="inlineStr">
         <is>
           <t>TE29</t>
         </is>
       </c>
-      <c r="B213" s="3" t="n">
+      <c r="B214" s="3" t="n">
         <v>243</v>
       </c>
-      <c r="C213" s="5" t="n">
-        <v>232</v>
-      </c>
-      <c r="D213" s="3" t="n">
+      <c r="C214" s="5" t="n">
+        <v>230</v>
+      </c>
+      <c r="D214" s="3" t="n">
         <v>235</v>
       </c>
-      <c r="E213" s="3" t="inlineStr">
+      <c r="E214" s="3" t="inlineStr">
         <is>
           <t>Terrance Ferguson</t>
         </is>
       </c>
-      <c r="F213" s="3" t="inlineStr">
+      <c r="F214" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="G213" s="3" t="inlineStr">
+      <c r="G214" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="6" t="inlineStr">
-        <is>
-          <t>RB67</t>
-        </is>
-      </c>
-      <c r="B214" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="C214" s="5" t="n">
-        <v>275</v>
-      </c>
-      <c r="D214" s="3" t="n">
-        <v>281</v>
-      </c>
-      <c r="E214" s="3" t="inlineStr">
-        <is>
-          <t>Ollie Gordon</t>
-        </is>
-      </c>
-      <c r="F214" s="3" t="inlineStr">
-        <is>
-          <t>MIA (6)</t>
-        </is>
-      </c>
-      <c r="G214" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
+          <t>RB67</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="C215" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="D215" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>Ollie Gordon</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
           <t>RB68</t>
         </is>
       </c>
-      <c r="B215" s="3" t="n">
+      <c r="B216" s="3" t="n">
         <v>245</v>
       </c>
-      <c r="C215" s="5" t="n">
-        <v>202</v>
-      </c>
-      <c r="D215" s="3" t="n">
+      <c r="C216" s="11" t="n">
+        <v>166</v>
+      </c>
+      <c r="D216" s="3" t="n">
         <v>168</v>
       </c>
-      <c r="E215" s="3" t="inlineStr">
+      <c r="E216" s="3" t="inlineStr">
         <is>
           <t>MarShawn Lloyd</t>
         </is>
       </c>
-      <c r="F215" s="3" t="inlineStr">
+      <c r="F216" s="3" t="inlineStr">
         <is>
           <t>GB (11)</t>
         </is>
       </c>
-      <c r="G215" s="3" t="inlineStr">
+      <c r="G216" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="2" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>WR90</t>
         </is>
       </c>
-      <c r="B216" s="3" t="n">
+      <c r="B217" s="3" t="n">
         <v>246</v>
       </c>
-      <c r="C216" s="5" t="n">
-        <v>277</v>
-      </c>
-      <c r="D216" s="3" t="n">
+      <c r="C217" s="5" t="n">
+        <v>278</v>
+      </c>
+      <c r="D217" s="3" t="n">
         <v>284</v>
       </c>
-      <c r="E216" s="3" t="inlineStr">
+      <c r="E217" s="3" t="inlineStr">
         <is>
           <t>Elic Ayomanor</t>
         </is>
       </c>
-      <c r="F216" s="3" t="inlineStr">
+      <c r="F217" s="3" t="inlineStr">
         <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="G216" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="8" t="inlineStr">
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="8" t="inlineStr">
         <is>
           <t>TE30</t>
         </is>
       </c>
-      <c r="B217" s="3" t="n">
+      <c r="B218" s="3" t="n">
         <v>248</v>
       </c>
-      <c r="C217" s="5" t="n">
-        <v>219</v>
-      </c>
-      <c r="D217" s="3" t="n">
+      <c r="C218" s="5" t="n">
+        <v>221</v>
+      </c>
+      <c r="D218" s="3" t="n">
         <v>226</v>
       </c>
-      <c r="E217" s="3" t="inlineStr">
+      <c r="E218" s="3" t="inlineStr">
         <is>
           <t>Colby Parkinson</t>
         </is>
       </c>
-      <c r="F217" s="3" t="inlineStr">
+      <c r="F218" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="G217" s="3" t="inlineStr">
+      <c r="G218" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="inlineStr">
-        <is>
-          <t>WR91</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="n">
-        <v>249</v>
-      </c>
-      <c r="C218" s="5" t="n">
-        <v>278</v>
-      </c>
-      <c r="D218" s="3" t="n">
-        <v>288</v>
-      </c>
-      <c r="E218" s="3" t="inlineStr">
-        <is>
-          <t>Keon Coleman</t>
-        </is>
-      </c>
-      <c r="F218" s="3" t="inlineStr">
-        <is>
-          <t>BUF (7)</t>
-        </is>
-      </c>
-      <c r="G218" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
+          <t>WR91</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="n">
+        <v>249</v>
+      </c>
+      <c r="C219" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="D219" s="3" t="n">
+        <v>288</v>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>Keon Coleman</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>BUF (7)</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="6" t="inlineStr">
+        <is>
+          <t>RB69</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="C220" s="4" t="n">
+        <v>293</v>
+      </c>
+      <c r="D220" s="3" t="inlineStr"/>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>Ty Johnson</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
+        <is>
+          <t>BUF (7)</t>
+        </is>
+      </c>
+      <c r="G220" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
           <t>WR92</t>
         </is>
       </c>
-      <c r="B219" s="3" t="n">
+      <c r="B221" s="3" t="n">
         <v>251</v>
       </c>
-      <c r="C219" s="5" t="n">
-        <v>258</v>
-      </c>
-      <c r="D219" s="3" t="n">
+      <c r="C221" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="D221" s="3" t="n">
         <v>269</v>
       </c>
-      <c r="E219" s="3" t="inlineStr">
+      <c r="E221" s="3" t="inlineStr">
         <is>
           <t>Chris Bell</t>
         </is>
       </c>
-      <c r="F219" s="3" t="inlineStr">
+      <c r="F221" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="G219" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="inlineStr">
-        <is>
-          <t>WR93</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="n">
-        <v>252</v>
-      </c>
-      <c r="C220" s="5" t="n">
-        <v>246</v>
-      </c>
-      <c r="D220" s="3" t="n">
-        <v>249</v>
-      </c>
-      <c r="E220" s="3" t="inlineStr">
-        <is>
-          <t>Elijah Sarratt</t>
-        </is>
-      </c>
-      <c r="F220" s="3" t="inlineStr">
-        <is>
-          <t>BAL (13)</t>
-        </is>
-      </c>
-      <c r="G220" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="8" t="inlineStr">
-        <is>
-          <t>TE31</t>
-        </is>
-      </c>
-      <c r="B221" s="3" t="n">
-        <v>254</v>
-      </c>
-      <c r="C221" s="5" t="n">
-        <v>253</v>
-      </c>
-      <c r="D221" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="E221" s="3" t="inlineStr">
-        <is>
-          <t>Evan Engram</t>
-        </is>
-      </c>
-      <c r="F221" s="3" t="inlineStr">
-        <is>
-          <t>DEN (10)</t>
-        </is>
-      </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
+          <t>WR93</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="n">
+        <v>252</v>
+      </c>
+      <c r="C222" s="5" t="n">
+        <v>264</v>
+      </c>
+      <c r="D222" s="3" t="n">
+        <v>249</v>
+      </c>
+      <c r="E222" s="3" t="inlineStr">
+        <is>
+          <t>Elijah Sarratt</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="inlineStr">
+        <is>
+          <t>BAL (13)</t>
+        </is>
+      </c>
+      <c r="G222" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="8" t="inlineStr">
+        <is>
+          <t>TE31</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="C223" s="5" t="n">
+        <v>258</v>
+      </c>
+      <c r="D223" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="E223" s="3" t="inlineStr">
+        <is>
+          <t>Evan Engram</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="inlineStr">
+        <is>
+          <t>DEN (10)</t>
+        </is>
+      </c>
+      <c r="G223" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
           <t>WR94</t>
         </is>
       </c>
-      <c r="B222" s="3" t="n">
+      <c r="B224" s="3" t="n">
         <v>255</v>
       </c>
-      <c r="C222" s="4" t="n">
+      <c r="C224" s="4" t="n">
         <v>299</v>
       </c>
-      <c r="D222" s="3" t="inlineStr"/>
-      <c r="E222" s="3" t="inlineStr">
+      <c r="D224" s="3" t="inlineStr"/>
+      <c r="E224" s="3" t="inlineStr">
         <is>
           <t>Christian Kirk</t>
         </is>
       </c>
-      <c r="F222" s="3" t="inlineStr">
+      <c r="F224" s="3" t="inlineStr">
         <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="G222" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+      <c r="G224" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>WR95</t>
         </is>
       </c>
-      <c r="B223" s="3" t="n">
+      <c r="B225" s="3" t="n">
         <v>256</v>
       </c>
-      <c r="C223" s="5" t="n">
-        <v>285</v>
-      </c>
-      <c r="D223" s="3" t="n">
+      <c r="C225" s="5" t="n">
+        <v>257</v>
+      </c>
+      <c r="D225" s="3" t="n">
         <v>294</v>
       </c>
-      <c r="E223" s="3" t="inlineStr">
+      <c r="E225" s="3" t="inlineStr">
         <is>
           <t>Malachi Fields</t>
         </is>
       </c>
-      <c r="F223" s="3" t="inlineStr">
+      <c r="F225" s="3" t="inlineStr">
         <is>
           <t>NYG (8)</t>
         </is>
       </c>
-      <c r="G223" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="6" t="inlineStr">
+      <c r="G225" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="6" t="inlineStr">
         <is>
           <t>RB70</t>
         </is>
       </c>
-      <c r="B224" s="3" t="n">
+      <c r="B226" s="3" t="n">
         <v>257</v>
       </c>
-      <c r="C224" s="5" t="n">
-        <v>266</v>
-      </c>
-      <c r="D224" s="3" t="n">
+      <c r="C226" s="5" t="n">
+        <v>269</v>
+      </c>
+      <c r="D226" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="E224" s="3" t="inlineStr">
+      <c r="E226" s="3" t="inlineStr">
         <is>
           <t>DJ Giddens</t>
         </is>
       </c>
-      <c r="F224" s="3" t="inlineStr">
+      <c r="F226" s="3" t="inlineStr">
         <is>
           <t>IND (13)</t>
         </is>
       </c>
-      <c r="G224" s="3" t="inlineStr">
+      <c r="G226" s="3" t="inlineStr">
         <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="8" t="inlineStr">
-        <is>
-          <t>TE32</t>
-        </is>
-      </c>
-      <c r="B225" s="3" t="n">
-        <v>259</v>
-      </c>
-      <c r="C225" s="5" t="n">
-        <v>264</v>
-      </c>
-      <c r="D225" s="3" t="n">
-        <v>270</v>
-      </c>
-      <c r="E225" s="3" t="inlineStr">
-        <is>
-          <t>Eli Stowers</t>
-        </is>
-      </c>
-      <c r="F225" s="3" t="inlineStr">
-        <is>
-          <t>PHI (10)</t>
-        </is>
-      </c>
-      <c r="G225" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="inlineStr">
-        <is>
-          <t>WR97</t>
-        </is>
-      </c>
-      <c r="B226" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="C226" s="5" t="n">
-        <v>280</v>
-      </c>
-      <c r="D226" s="3" t="n">
-        <v>291</v>
-      </c>
-      <c r="E226" s="3" t="inlineStr">
-        <is>
-          <t>Tory Horton</t>
-        </is>
-      </c>
-      <c r="F226" s="3" t="inlineStr">
-        <is>
-          <t>SEA (11)</t>
-        </is>
-      </c>
-      <c r="G226" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>WR98</t>
+          <t>WR96</t>
         </is>
       </c>
       <c r="B227" s="3" t="n">
-        <v>261</v>
-      </c>
-      <c r="C227" s="5" t="n">
-        <v>284</v>
-      </c>
-      <c r="D227" s="3" t="n">
-        <v>292</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="C227" s="4" t="n">
+        <v>322</v>
+      </c>
+      <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>Marvin Mims</t>
+          <t>Tyreek Hill</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>DEN (10)</t>
+          <t>FA ()</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -7539,57 +7533,59 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="6" t="inlineStr">
-        <is>
-          <t>RB71</t>
+      <c r="A228" s="8" t="inlineStr">
+        <is>
+          <t>TE32</t>
         </is>
       </c>
       <c r="B228" s="3" t="n">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="D228" s="3" t="n">
-        <v>193</v>
+        <v>270</v>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>Jaydon Blue</t>
+          <t>Eli Stowers</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>DAL (14)</t>
+          <t>PHI (10)</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>WR99</t>
+          <t>WR97</t>
         </is>
       </c>
       <c r="B229" s="3" t="n">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C229" s="5" t="n">
-        <v>260</v>
-      </c>
-      <c r="D229" s="3" t="inlineStr"/>
+        <v>268</v>
+      </c>
+      <c r="D229" s="3" t="n">
+        <v>291</v>
+      </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>Chris Brazzell</t>
+          <t>Tory Horton</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>CAR (5)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -7599,59 +7595,59 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="8" t="inlineStr">
-        <is>
-          <t>TE33</t>
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>WR98</t>
         </is>
       </c>
       <c r="B230" s="3" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C230" s="5" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D230" s="3" t="n">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>Mason Taylor</t>
+          <t>Marvin Mims</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>NYJ (13)</t>
+          <t>DEN (10)</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>RB72</t>
+          <t>RB71</t>
         </is>
       </c>
       <c r="B231" s="3" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>283</v>
+        <v>203</v>
       </c>
       <c r="D231" s="3" t="n">
-        <v>290</v>
+        <v>193</v>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>Chris Brooks</t>
+          <t>Jaydon Blue</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>GB (11)</t>
+          <t>DAL (14)</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
@@ -7661,245 +7657,241 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="10" t="inlineStr">
-        <is>
-          <t>QB31</t>
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>WR99</t>
         </is>
       </c>
       <c r="B232" s="3" t="n">
-        <v>266</v>
-      </c>
-      <c r="C232" s="5" t="n">
-        <v>240</v>
-      </c>
-      <c r="D232" s="3" t="n">
-        <v>241</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="C232" s="4" t="n">
+        <v>325</v>
+      </c>
+      <c r="D232" s="3" t="inlineStr"/>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>Tua Tagovailoa</t>
+          <t>Chris Brazzell</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>ATL (11)</t>
+          <t>CAR (5)</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="inlineStr">
-        <is>
-          <t>WR100</t>
+      <c r="A233" s="8" t="inlineStr">
+        <is>
+          <t>TE33</t>
         </is>
       </c>
       <c r="B233" s="3" t="n">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>207</v>
+        <v>279</v>
       </c>
       <c r="D233" s="3" t="n">
-        <v>212</v>
+        <v>259</v>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>Darius Slayton</t>
+          <t>Mason Taylor</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>NYG (8)</t>
+          <t>NYJ (13)</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
         <is>
+          <t>RB72</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="C234" s="5" t="n">
+        <v>299</v>
+      </c>
+      <c r="D234" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>Chris Brooks</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>GB (11)</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="10" t="inlineStr">
+        <is>
+          <t>QB31</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="C235" s="5" t="n">
+        <v>240</v>
+      </c>
+      <c r="D235" s="3" t="n">
+        <v>241</v>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>Tua Tagovailoa</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>ATL (11)</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>WR100</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="C236" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D236" s="3" t="n">
+        <v>212</v>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>Darius Slayton</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>NYG (8)</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="8" t="inlineStr">
+        <is>
+          <t>TE34</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="C237" s="4" t="n">
+        <v>346</v>
+      </c>
+      <c r="D237" s="3" t="inlineStr"/>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>Theo Johnson</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>NYG (8)</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="6" t="inlineStr">
+        <is>
           <t>RB73</t>
         </is>
       </c>
-      <c r="B234" s="3" t="n">
+      <c r="B238" s="3" t="n">
         <v>269</v>
       </c>
-      <c r="C234" s="5" t="n">
-        <v>286</v>
-      </c>
-      <c r="D234" s="3" t="n">
+      <c r="C238" s="4" t="n">
+        <v>326</v>
+      </c>
+      <c r="D238" s="3" t="n">
         <v>285</v>
       </c>
-      <c r="E234" s="3" t="inlineStr">
+      <c r="E238" s="3" t="inlineStr">
         <is>
           <t>Samaje Perine</t>
         </is>
       </c>
-      <c r="F234" s="3" t="inlineStr">
+      <c r="F238" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="G234" s="3" t="inlineStr">
+      <c r="G238" s="3" t="inlineStr">
         <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="6" t="inlineStr">
-        <is>
-          <t>RB74</t>
-        </is>
-      </c>
-      <c r="B235" s="3" t="n">
-        <v>270</v>
-      </c>
-      <c r="C235" s="5" t="n">
-        <v>281</v>
-      </c>
-      <c r="D235" s="3" t="n">
-        <v>289</v>
-      </c>
-      <c r="E235" s="3" t="inlineStr">
-        <is>
-          <t>Isaiah Davis</t>
-        </is>
-      </c>
-      <c r="F235" s="3" t="inlineStr">
-        <is>
-          <t>NYJ (13)</t>
-        </is>
-      </c>
-      <c r="G235" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="6" t="inlineStr">
-        <is>
-          <t>RB75</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="n">
-        <v>271</v>
-      </c>
-      <c r="C236" s="5" t="n">
-        <v>279</v>
-      </c>
-      <c r="D236" s="3" t="n">
-        <v>287</v>
-      </c>
-      <c r="E236" s="3" t="inlineStr">
-        <is>
-          <t>Demond Claiborne</t>
-        </is>
-      </c>
-      <c r="F236" s="3" t="inlineStr">
-        <is>
-          <t>MIN (6)</t>
-        </is>
-      </c>
-      <c r="G236" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="6" t="inlineStr">
-        <is>
-          <t>RB76</t>
-        </is>
-      </c>
-      <c r="B237" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="C237" s="5" t="n">
-        <v>287</v>
-      </c>
-      <c r="D237" s="3" t="n">
-        <v>286</v>
-      </c>
-      <c r="E237" s="3" t="inlineStr">
-        <is>
-          <t>LeQuint Allen</t>
-        </is>
-      </c>
-      <c r="F237" s="3" t="inlineStr">
-        <is>
-          <t>JAC (7)</t>
-        </is>
-      </c>
-      <c r="G237" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="10" t="inlineStr">
-        <is>
-          <t>QB32</t>
-        </is>
-      </c>
-      <c r="B238" s="3" t="n">
-        <v>276</v>
-      </c>
-      <c r="C238" s="5" t="n">
-        <v>252</v>
-      </c>
-      <c r="D238" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="E238" s="3" t="inlineStr">
-        <is>
-          <t>Michael Penix</t>
-        </is>
-      </c>
-      <c r="F238" s="3" t="inlineStr">
-        <is>
-          <t>ATL (11)</t>
-        </is>
-      </c>
-      <c r="G238" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>RB79</t>
+          <t>RB74</t>
         </is>
       </c>
       <c r="B239" s="3" t="n">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="D239" s="3" t="n">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>Jordan James</t>
+          <t>Isaiah Davis</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>NYJ (13)</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -7909,90 +7901,88 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="8" t="inlineStr">
-        <is>
-          <t>TE35</t>
+      <c r="A240" s="6" t="inlineStr">
+        <is>
+          <t>RB75</t>
         </is>
       </c>
       <c r="B240" s="3" t="n">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="C240" s="5" t="n">
-        <v>214</v>
+        <v>266</v>
       </c>
       <c r="D240" s="3" t="n">
-        <v>218</v>
+        <v>287</v>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>Greg Dulcich</t>
+          <t>Demond Claiborne</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>WR102</t>
+      <c r="A241" s="6" t="inlineStr">
+        <is>
+          <t>RB76</t>
         </is>
       </c>
       <c r="B241" s="3" t="n">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>248</v>
+        <v>288</v>
       </c>
       <c r="D241" s="3" t="n">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>Tyquan Thornton</t>
+          <t>LeQuint Allen</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>KC (5)</t>
+          <t>JAC (7)</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
         <is>
-          <t>RB82</t>
+          <t>RB77</t>
         </is>
       </c>
       <c r="B242" s="3" t="n">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>282</v>
-      </c>
-      <c r="D242" s="3" t="n">
-        <v>276</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="D242" s="3" t="inlineStr"/>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>George Holani</t>
+          <t>Devin Neal</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -8004,26 +7994,24 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>WR103</t>
+          <t>WR101</t>
         </is>
       </c>
       <c r="B243" s="3" t="n">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>296</v>
-      </c>
-      <c r="D243" s="3" t="n">
-        <v>300</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="D243" s="3" t="inlineStr"/>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>Devaughn Vele</t>
+          <t>Xavier Legette</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>CAR (5)</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -8033,305 +8021,299 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>WR105</t>
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>RB78</t>
         </is>
       </c>
       <c r="B244" s="3" t="n">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="C244" s="5" t="n">
-        <v>257</v>
-      </c>
-      <c r="D244" s="3" t="n">
-        <v>251</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="D244" s="3" t="inlineStr"/>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>Keenan Allen</t>
+          <t>Seth McGowan</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>IND (13)</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="6" t="inlineStr">
-        <is>
-          <t>RB85</t>
+      <c r="A245" s="10" t="inlineStr">
+        <is>
+          <t>QB32</t>
         </is>
       </c>
       <c r="B245" s="3" t="n">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="C245" s="5" t="n">
-        <v>205</v>
+        <v>275</v>
       </c>
       <c r="D245" s="3" t="n">
-        <v>211</v>
+        <v>255</v>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>Kaelon Black</t>
+          <t>Michael Penix</t>
         </is>
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
+          <t>ATL (11)</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="6" t="inlineStr">
+        <is>
+          <t>RB79</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="n">
+        <v>277</v>
+      </c>
+      <c r="C246" s="5" t="n">
+        <v>272</v>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>253</v>
+      </c>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>Jordan James</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
           <t>SF (8)</t>
         </is>
       </c>
-      <c r="G245" s="3" t="inlineStr">
+      <c r="G246" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>WR106</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="n">
-        <v>294</v>
-      </c>
-      <c r="C246" s="5" t="n">
-        <v>298</v>
-      </c>
-      <c r="D246" s="3" t="inlineStr"/>
-      <c r="E246" s="3" t="inlineStr">
-        <is>
-          <t>Hollywood Brown</t>
-        </is>
-      </c>
-      <c r="F246" s="3" t="inlineStr">
-        <is>
-          <t>PHI (10)</t>
-        </is>
-      </c>
-      <c r="G246" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
     <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>WR107</t>
+      <c r="A247" s="8" t="inlineStr">
+        <is>
+          <t>TE35</t>
         </is>
       </c>
       <c r="B247" s="3" t="n">
-        <v>295</v>
-      </c>
-      <c r="C247" s="5" t="n">
-        <v>288</v>
+        <v>278</v>
+      </c>
+      <c r="C247" s="11" t="n">
+        <v>198</v>
       </c>
       <c r="D247" s="3" t="n">
-        <v>296</v>
+        <v>218</v>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>Mack Hollins</t>
+          <t>Greg Dulcich</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
         <is>
-          <t>RB87</t>
+          <t>RB80</t>
         </is>
       </c>
       <c r="B248" s="3" t="n">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>261</v>
-      </c>
-      <c r="D248" s="3" t="n">
-        <v>266</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="D248" s="3" t="inlineStr"/>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>Emari Demercado</t>
+          <t>Kaleb Johnson</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
+          <t>PIT (9)</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="6" t="inlineStr">
+        <is>
+          <t>RB81</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="C249" s="4" t="n">
+        <v>338</v>
+      </c>
+      <c r="D249" s="3" t="inlineStr"/>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>Trey Benson</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>ARI (14)</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>WR102</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="C250" s="5" t="n">
+        <v>285</v>
+      </c>
+      <c r="D250" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>Tyquan Thornton</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
           <t>KC (5)</t>
         </is>
       </c>
-      <c r="G248" s="3" t="inlineStr">
+      <c r="G250" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="6" t="inlineStr">
+        <is>
+          <t>RB82</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="n">
+        <v>283</v>
+      </c>
+      <c r="C251" s="5" t="n">
+        <v>289</v>
+      </c>
+      <c r="D251" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="E251" s="3" t="inlineStr">
+        <is>
+          <t>George Holani</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="10" t="inlineStr">
-        <is>
-          <t>QB34</t>
-        </is>
-      </c>
-      <c r="B249" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="C249" s="5" t="n">
-        <v>241</v>
-      </c>
-      <c r="D249" s="3" t="n">
-        <v>242</v>
-      </c>
-      <c r="E249" s="3" t="inlineStr">
-        <is>
-          <t>Deshaun Watson</t>
-        </is>
-      </c>
-      <c r="F249" s="3" t="inlineStr">
-        <is>
-          <t>CLE (11)</t>
-        </is>
-      </c>
-      <c r="G249" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="8" t="inlineStr">
-        <is>
-          <t>TE37</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="C250" s="5" t="n">
-        <v>255</v>
-      </c>
-      <c r="D250" s="3" t="n">
-        <v>261</v>
-      </c>
-      <c r="E250" s="3" t="inlineStr">
-        <is>
-          <t>Mike Gesicki</t>
-        </is>
-      </c>
-      <c r="F250" s="3" t="inlineStr">
-        <is>
-          <t>CIN (6)</t>
-        </is>
-      </c>
-      <c r="G250" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="10" t="inlineStr">
-        <is>
-          <t>QB35</t>
-        </is>
-      </c>
-      <c r="B251" s="3" t="n">
-        <v>302</v>
-      </c>
-      <c r="C251" s="5" t="n">
-        <v>251</v>
-      </c>
-      <c r="D251" s="3" t="n">
-        <v>254</v>
-      </c>
-      <c r="E251" s="3" t="inlineStr">
-        <is>
-          <t>Kirk Cousins</t>
-        </is>
-      </c>
-      <c r="F251" s="3" t="inlineStr">
-        <is>
-          <t>LV (13)</t>
-        </is>
-      </c>
-      <c r="G251" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
     <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>WR108</t>
+      <c r="A252" s="6" t="inlineStr">
+        <is>
+          <t>RB83</t>
         </is>
       </c>
       <c r="B252" s="3" t="n">
-        <v>306</v>
-      </c>
-      <c r="C252" s="5" t="n">
-        <v>291</v>
-      </c>
-      <c r="D252" s="3" t="n">
-        <v>246</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="C252" s="4" t="n">
+        <v>343</v>
+      </c>
+      <c r="D252" s="3" t="inlineStr"/>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>Ja'Kobi Lane</t>
+          <t>Malik Davis</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>BAL (13)</t>
+          <t>DAL (14)</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>WR111</t>
+          <t>WR103</t>
         </is>
       </c>
       <c r="B253" s="3" t="n">
-        <v>316</v>
+        <v>285</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D253" s="3" t="n">
-        <v>263</v>
+        <v>300</v>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>Andrei Iosivas</t>
+          <t>Devaughn Vele</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>CIN (6)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -8343,26 +8325,24 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>WR119</t>
+          <t>WR104</t>
         </is>
       </c>
       <c r="B254" s="3" t="n">
-        <v>334</v>
-      </c>
-      <c r="C254" s="5" t="n">
-        <v>292</v>
-      </c>
-      <c r="D254" s="3" t="n">
-        <v>297</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="C254" s="4" t="n">
+        <v>335</v>
+      </c>
+      <c r="D254" s="3" t="inlineStr"/>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>Calvin Austin</t>
+          <t>Kyle Williams</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>NYG (8)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -8372,93 +8352,1507 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>WR120</t>
+      <c r="A255" s="10" t="inlineStr">
+        <is>
+          <t>QB33</t>
         </is>
       </c>
       <c r="B255" s="3" t="n">
-        <v>335</v>
+        <v>289</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>269</v>
-      </c>
-      <c r="D255" s="3" t="n">
-        <v>278</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="D255" s="3" t="inlineStr"/>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Shedeur Sanders</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>WR123</t>
+          <t>WR105</t>
         </is>
       </c>
       <c r="B256" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="C256" s="5" t="n">
+        <v>283</v>
+      </c>
+      <c r="D256" s="3" t="n">
+        <v>251</v>
+      </c>
+      <c r="E256" s="3" t="inlineStr">
+        <is>
+          <t>Keenan Allen</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>LAC (7)</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="6" t="inlineStr">
+        <is>
+          <t>RB84</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="n">
+        <v>292</v>
+      </c>
+      <c r="C257" s="5" t="n">
+        <v>318</v>
+      </c>
+      <c r="D257" s="3" t="inlineStr"/>
+      <c r="E257" s="3" t="inlineStr">
+        <is>
+          <t>Brashard Smith</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>KC (5)</t>
+        </is>
+      </c>
+      <c r="G257" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="6" t="inlineStr">
+        <is>
+          <t>RB85</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="n">
+        <v>293</v>
+      </c>
+      <c r="C258" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="D258" s="3" t="n">
+        <v>211</v>
+      </c>
+      <c r="E258" s="3" t="inlineStr">
+        <is>
+          <t>Kaelon Black</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>SF (8)</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>WR106</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="n">
+        <v>294</v>
+      </c>
+      <c r="C259" s="4" t="n">
+        <v>345</v>
+      </c>
+      <c r="D259" s="3" t="inlineStr"/>
+      <c r="E259" s="3" t="inlineStr">
+        <is>
+          <t>Hollywood Brown</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>PHI (10)</t>
+        </is>
+      </c>
+      <c r="G259" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="6" t="inlineStr">
+        <is>
+          <t>RB86</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="n">
+        <v>296</v>
+      </c>
+      <c r="C260" s="5" t="n">
+        <v>267</v>
+      </c>
+      <c r="D260" s="3" t="inlineStr"/>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>Devin Singletary</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>NYG (8)</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="8" t="inlineStr">
+        <is>
+          <t>TE36</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="n">
+        <v>297</v>
+      </c>
+      <c r="C261" s="5" t="n">
+        <v>336</v>
+      </c>
+      <c r="D261" s="3" t="inlineStr"/>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>Oscar Delp</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="6" t="inlineStr">
+        <is>
+          <t>RB87</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="n">
+        <v>298</v>
+      </c>
+      <c r="C262" s="5" t="n">
+        <v>273</v>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>Emari Demercado</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>KC (5)</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="10" t="inlineStr">
+        <is>
+          <t>QB34</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="n">
+        <v>299</v>
+      </c>
+      <c r="C263" s="5" t="n">
+        <v>251</v>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>Deshaun Watson</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="G263" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="8" t="inlineStr">
+        <is>
+          <t>TE37</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="C264" s="5" t="n">
+        <v>281</v>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>261</v>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>Mike Gesicki</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>CIN (6)</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>RB88</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C265" s="5" t="n">
+        <v>317</v>
+      </c>
+      <c r="D265" s="3" t="inlineStr"/>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>Kendre Miller</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="10" t="inlineStr">
+        <is>
+          <t>QB35</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="n">
+        <v>302</v>
+      </c>
+      <c r="C266" s="5" t="n">
+        <v>252</v>
+      </c>
+      <c r="D266" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>Kirk Cousins</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>LV (13)</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="6" t="inlineStr">
+        <is>
+          <t>RB90</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="C267" s="5" t="n">
+        <v>307</v>
+      </c>
+      <c r="D267" s="3" t="inlineStr"/>
+      <c r="E267" s="3" t="inlineStr">
+        <is>
+          <t>Najee Harris</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>LAC (7)</t>
+        </is>
+      </c>
+      <c r="G267" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="6" t="inlineStr">
+        <is>
+          <t>RB91</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="n">
+        <v>305</v>
+      </c>
+      <c r="C268" s="5" t="n">
+        <v>297</v>
+      </c>
+      <c r="D268" s="3" t="inlineStr"/>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>Adam Randall</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>BAL (13)</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>WR108</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="n">
+        <v>306</v>
+      </c>
+      <c r="C269" s="5" t="n">
+        <v>256</v>
+      </c>
+      <c r="D269" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>Ja'Kobi Lane</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>BAL (13)</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>RB93</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="n">
+        <v>309</v>
+      </c>
+      <c r="C270" s="5" t="n">
+        <v>321</v>
+      </c>
+      <c r="D270" s="3" t="inlineStr"/>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>Trevor Etienne</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="inlineStr">
+        <is>
+          <t>CAR (5)</t>
+        </is>
+      </c>
+      <c r="G270" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>WR109</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="n">
+        <v>310</v>
+      </c>
+      <c r="C271" s="5" t="n">
+        <v>331</v>
+      </c>
+      <c r="D271" s="3" t="inlineStr"/>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>Isaiah Bond</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="G271" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>WR110</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="n">
+        <v>311</v>
+      </c>
+      <c r="C272" s="5" t="n">
+        <v>288</v>
+      </c>
+      <c r="D272" s="3" t="inlineStr"/>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>Skyler Bell</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="inlineStr">
+        <is>
+          <t>BUF (7)</t>
+        </is>
+      </c>
+      <c r="G272" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="8" t="inlineStr">
+        <is>
+          <t>TE38</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="n">
+        <v>312</v>
+      </c>
+      <c r="C273" s="5" t="n">
+        <v>340</v>
+      </c>
+      <c r="D273" s="3" t="inlineStr"/>
+      <c r="E273" s="3" t="inlineStr">
+        <is>
+          <t>Jake Tonges</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="inlineStr">
+        <is>
+          <t>SF (8)</t>
+        </is>
+      </c>
+      <c r="G273" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="6" t="inlineStr">
+        <is>
+          <t>RB95</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="n">
+        <v>314</v>
+      </c>
+      <c r="C274" s="5" t="n">
+        <v>298</v>
+      </c>
+      <c r="D274" s="3" t="inlineStr"/>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>Tahj Brooks</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="inlineStr">
+        <is>
+          <t>CIN (6)</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>WR111</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>253</v>
+      </c>
+      <c r="D275" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>Andrei Iosivas</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>CIN (6)</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="6" t="inlineStr">
+        <is>
+          <t>RB96</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="n">
+        <v>317</v>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>287</v>
+      </c>
+      <c r="D276" s="3" t="inlineStr"/>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>Jarquez Hunter</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>LAR (11)</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="8" t="inlineStr">
+        <is>
+          <t>TE39</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="n">
+        <v>322</v>
+      </c>
+      <c r="C277" s="5" t="n">
+        <v>275</v>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>271</v>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
+        <is>
+          <t>Darnell Washington</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="inlineStr">
+        <is>
+          <t>PIT (9)</t>
+        </is>
+      </c>
+      <c r="G277" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>WR113</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="n">
+        <v>325</v>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>332</v>
+      </c>
+      <c r="D278" s="3" t="inlineStr"/>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
+          <t>Konata Mumpfield</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="inlineStr">
+        <is>
+          <t>LAR (11)</t>
+        </is>
+      </c>
+      <c r="G278" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="10" t="inlineStr">
+        <is>
+          <t>QB36</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="n">
+        <v>327</v>
+      </c>
+      <c r="C279" s="5" t="n">
+        <v>362</v>
+      </c>
+      <c r="D279" s="3" t="inlineStr"/>
+      <c r="E279" s="3" t="inlineStr">
+        <is>
+          <t>J.J. McCarthy</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>MIN (6)</t>
+        </is>
+      </c>
+      <c r="G279" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>WR114</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="n">
+        <v>328</v>
+      </c>
+      <c r="C280" s="5" t="n">
+        <v>284</v>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="E280" s="3" t="inlineStr">
+        <is>
+          <t>Luke McCaffrey</t>
+        </is>
+      </c>
+      <c r="F280" s="3" t="inlineStr">
+        <is>
+          <t>WAS (7)</t>
+        </is>
+      </c>
+      <c r="G280" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>WR116</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="C281" s="5" t="n">
+        <v>264</v>
+      </c>
+      <c r="D281" s="3" t="inlineStr"/>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>Jahan Dotson</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>ATL (11)</t>
+        </is>
+      </c>
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>WR117</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="n">
+        <v>331</v>
+      </c>
+      <c r="C282" s="5" t="n">
         <v>347</v>
       </c>
-      <c r="C256" s="5" t="n">
-        <v>294</v>
-      </c>
-      <c r="D256" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="E256" s="3" t="inlineStr">
-        <is>
-          <t>Kendrick Bourne</t>
-        </is>
-      </c>
-      <c r="F256" s="3" t="inlineStr">
+      <c r="D282" s="3" t="inlineStr"/>
+      <c r="E282" s="3" t="inlineStr">
+        <is>
+          <t>Jalen Royals</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>KC (5)</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="8" t="inlineStr">
+        <is>
+          <t>TE40</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="n">
+        <v>332</v>
+      </c>
+      <c r="C283" s="5" t="n">
+        <v>363</v>
+      </c>
+      <c r="D283" s="3" t="inlineStr"/>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
+          <t>Max Klare</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="inlineStr">
+        <is>
+          <t>LAR (11)</t>
+        </is>
+      </c>
+      <c r="G283" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>WR118</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="n">
+        <v>333</v>
+      </c>
+      <c r="C284" s="5" t="n">
+        <v>233</v>
+      </c>
+      <c r="D284" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="E284" s="3" t="inlineStr">
+        <is>
+          <t>Caleb Douglas</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="G284" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>WR120</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="n">
+        <v>335</v>
+      </c>
+      <c r="C285" s="5" t="n">
+        <v>291</v>
+      </c>
+      <c r="D285" s="3" t="n">
+        <v>278</v>
+      </c>
+      <c r="E285" s="3" t="inlineStr">
+        <is>
+          <t>Jalen Tolbert</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="G285" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="8" t="inlineStr">
+        <is>
+          <t>TE41</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="n">
+        <v>338</v>
+      </c>
+      <c r="C286" s="5" t="n">
+        <v>361</v>
+      </c>
+      <c r="D286" s="3" t="inlineStr"/>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>Michael Mayer</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>LV (13)</t>
+        </is>
+      </c>
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="8" t="inlineStr">
+        <is>
+          <t>TE42</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="n">
+        <v>340</v>
+      </c>
+      <c r="C287" s="5" t="n">
+        <v>354</v>
+      </c>
+      <c r="D287" s="3" t="inlineStr"/>
+      <c r="E287" s="3" t="inlineStr">
+        <is>
+          <t>Elijah Arroyo</t>
+        </is>
+      </c>
+      <c r="F287" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="G287" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="8" t="inlineStr">
+        <is>
+          <t>TE43</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="n">
+        <v>341</v>
+      </c>
+      <c r="C288" s="5" t="n">
+        <v>312</v>
+      </c>
+      <c r="D288" s="3" t="inlineStr"/>
+      <c r="E288" s="3" t="inlineStr">
+        <is>
+          <t>Tyler Higbee</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="inlineStr">
+        <is>
+          <t>LAR (11)</t>
+        </is>
+      </c>
+      <c r="G288" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="8" t="inlineStr">
+        <is>
+          <t>TE45</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="n">
+        <v>344</v>
+      </c>
+      <c r="C289" s="5" t="n">
+        <v>365</v>
+      </c>
+      <c r="D289" s="3" t="inlineStr"/>
+      <c r="E289" s="3" t="inlineStr">
+        <is>
+          <t>Dawson Knox</t>
+        </is>
+      </c>
+      <c r="F289" s="3" t="inlineStr">
+        <is>
+          <t>BUF (7)</t>
+        </is>
+      </c>
+      <c r="G289" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="10" t="inlineStr">
+        <is>
+          <t>QB38</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="n">
+        <v>348</v>
+      </c>
+      <c r="C290" s="5" t="n">
+        <v>341</v>
+      </c>
+      <c r="D290" s="3" t="inlineStr"/>
+      <c r="E290" s="3" t="inlineStr">
+        <is>
+          <t>Carson Beck</t>
+        </is>
+      </c>
+      <c r="F290" s="3" t="inlineStr">
         <is>
           <t>ARI (14)</t>
         </is>
       </c>
-      <c r="G256" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
+      <c r="G290" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="8" t="inlineStr">
+        <is>
+          <t>TE47</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="n">
+        <v>349</v>
+      </c>
+      <c r="C291" s="5" t="n">
+        <v>355</v>
+      </c>
+      <c r="D291" s="3" t="inlineStr"/>
+      <c r="E291" s="3" t="inlineStr">
+        <is>
+          <t>Cole Kmet</t>
+        </is>
+      </c>
+      <c r="F291" s="3" t="inlineStr">
+        <is>
+          <t>CHI (10)</t>
+        </is>
+      </c>
+      <c r="G291" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>WR124</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="C292" s="5" t="n">
+        <v>337</v>
+      </c>
+      <c r="D292" s="3" t="inlineStr"/>
+      <c r="E292" s="3" t="inlineStr">
+        <is>
+          <t>Brenen Thompson</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="inlineStr">
+        <is>
+          <t>LAC (7)</t>
+        </is>
+      </c>
+      <c r="G292" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>WR125</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="n">
+        <v>351</v>
+      </c>
+      <c r="C293" s="5" t="n">
+        <v>358</v>
+      </c>
+      <c r="D293" s="3" t="inlineStr"/>
+      <c r="E293" s="3" t="inlineStr">
+        <is>
+          <t>DeMario Douglas</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="inlineStr">
+        <is>
+          <t>NE (11)</t>
+        </is>
+      </c>
+      <c r="G293" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>WR129</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="n">
+        <v>359</v>
+      </c>
+      <c r="C294" s="5" t="n">
+        <v>357</v>
+      </c>
+      <c r="D294" s="3" t="inlineStr"/>
+      <c r="E294" s="3" t="inlineStr">
+        <is>
+          <t>Kalif Raymond</t>
+        </is>
+      </c>
+      <c r="F294" s="3" t="inlineStr">
+        <is>
+          <t>CHI (10)</t>
+        </is>
+      </c>
+      <c r="G294" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="6" t="inlineStr">
+        <is>
+          <t>RB104</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="C295" s="5" t="n">
+        <v>349</v>
+      </c>
+      <c r="D295" s="3" t="inlineStr"/>
+      <c r="E295" s="3" t="inlineStr">
+        <is>
+          <t>Jawhar Jordan</t>
+        </is>
+      </c>
+      <c r="F295" s="3" t="inlineStr">
+        <is>
+          <t>HOU (8)</t>
+        </is>
+      </c>
+      <c r="G295" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="6" t="inlineStr">
+        <is>
+          <t>RB105</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="n">
+        <v>362</v>
+      </c>
+      <c r="C296" s="5" t="n">
+        <v>313</v>
+      </c>
+      <c r="D296" s="3" t="inlineStr"/>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>Nick Chubb</t>
+        </is>
+      </c>
+      <c r="F296" s="3" t="inlineStr">
+        <is>
+          <t>FA ()</t>
+        </is>
+      </c>
+      <c r="G296" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
         <is>
           <t>WR130</t>
         </is>
       </c>
-      <c r="B257" s="3" t="n">
+      <c r="B297" s="3" t="n">
         <v>363</v>
       </c>
-      <c r="C257" s="5" t="n">
+      <c r="C297" s="5" t="n">
+        <v>310</v>
+      </c>
+      <c r="D297" s="3" t="n">
         <v>293</v>
       </c>
-      <c r="D257" s="3" t="n">
-        <v>293</v>
-      </c>
-      <c r="E257" s="3" t="inlineStr">
+      <c r="E297" s="3" t="inlineStr">
         <is>
           <t>Treylon Burks</t>
         </is>
       </c>
-      <c r="F257" s="3" t="inlineStr">
+      <c r="F297" s="3" t="inlineStr">
         <is>
           <t>WAS (7)</t>
         </is>
       </c>
-      <c r="G257" s="3" t="inlineStr">
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>WR133</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="n">
+        <v>367</v>
+      </c>
+      <c r="C298" s="5" t="n">
+        <v>353</v>
+      </c>
+      <c r="D298" s="3" t="inlineStr"/>
+      <c r="E298" s="3" t="inlineStr">
+        <is>
+          <t>Savion Williams</t>
+        </is>
+      </c>
+      <c r="F298" s="3" t="inlineStr">
+        <is>
+          <t>GB (11)</t>
+        </is>
+      </c>
+      <c r="G298" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="8" t="inlineStr">
+        <is>
+          <t>TE49</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="n">
+        <v>373</v>
+      </c>
+      <c r="C299" s="5" t="n">
+        <v>364</v>
+      </c>
+      <c r="D299" s="3" t="inlineStr"/>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
+          <t>Noah Fant</t>
+        </is>
+      </c>
+      <c r="F299" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="G299" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="6" t="inlineStr">
+        <is>
+          <t>RB107</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="n">
+        <v>374</v>
+      </c>
+      <c r="C300" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="D300" s="3" t="inlineStr"/>
+      <c r="E300" s="3" t="inlineStr">
+        <is>
+          <t>Raheim Sanders</t>
+        </is>
+      </c>
+      <c r="F300" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="G300" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="8" t="inlineStr">
+        <is>
+          <t>TE50</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="n">
+        <v>377</v>
+      </c>
+      <c r="C301" s="5" t="n">
+        <v>339</v>
+      </c>
+      <c r="D301" s="3" t="inlineStr"/>
+      <c r="E301" s="3" t="inlineStr">
+        <is>
+          <t>Eli Raridon</t>
+        </is>
+      </c>
+      <c r="F301" s="3" t="inlineStr">
+        <is>
+          <t>NE (11)</t>
+        </is>
+      </c>
+      <c r="G301" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>WR137</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="n">
+        <v>380</v>
+      </c>
+      <c r="C302" s="5" t="n">
+        <v>356</v>
+      </c>
+      <c r="D302" s="3" t="inlineStr"/>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>Kevin Coleman</t>
+        </is>
+      </c>
+      <c r="F302" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="G302" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="6" t="inlineStr">
+        <is>
+          <t>RB109</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="n">
+        <v>386</v>
+      </c>
+      <c r="C303" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="D303" s="3" t="inlineStr"/>
+      <c r="E303" s="3" t="inlineStr">
+        <is>
+          <t>Phil Mafah</t>
+        </is>
+      </c>
+      <c r="F303" s="3" t="inlineStr">
+        <is>
+          <t>DAL (14)</t>
+        </is>
+      </c>
+      <c r="G303" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="8" t="inlineStr">
+        <is>
+          <t>TE52</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="n">
+        <v>387</v>
+      </c>
+      <c r="C304" s="5" t="n">
+        <v>319</v>
+      </c>
+      <c r="D304" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="E304" s="3" t="inlineStr">
+        <is>
+          <t>Erick All</t>
+        </is>
+      </c>
+      <c r="F304" s="3" t="inlineStr">
+        <is>
+          <t>CIN (6)</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>WR140</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="n">
+        <v>390</v>
+      </c>
+      <c r="C305" s="5" t="n">
+        <v>359</v>
+      </c>
+      <c r="D305" s="3" t="inlineStr"/>
+      <c r="E305" s="3" t="inlineStr">
+        <is>
+          <t>Devontez Walker</t>
+        </is>
+      </c>
+      <c r="F305" s="3" t="inlineStr">
+        <is>
+          <t>BAL (13)</t>
+        </is>
+      </c>
+      <c r="G305" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -7207,7 +7207,7 @@
         <v>246</v>
       </c>
       <c r="C217" s="5" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D217" s="3" t="n">
         <v>284</v>
@@ -7422,7 +7422,7 @@
         <v>255</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D224" s="3" t="inlineStr"/>
       <c r="E224" s="3" t="inlineStr">
@@ -7451,7 +7451,7 @@
         <v>256</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D225" s="3" t="n">
         <v>294</v>
@@ -7513,7 +7513,7 @@
         <v>258</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
@@ -7666,7 +7666,7 @@
         <v>263</v>
       </c>
       <c r="C232" s="4" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D232" s="3" t="inlineStr"/>
       <c r="E232" s="3" t="inlineStr">
@@ -7910,7 +7910,7 @@
         <v>271</v>
       </c>
       <c r="C240" s="5" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D240" s="3" t="n">
         <v>287</v>
@@ -8750,7 +8750,7 @@
         <v>305</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D268" s="3" t="inlineStr"/>
       <c r="E268" s="3" t="inlineStr">
@@ -8926,7 +8926,7 @@
         <v>314</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D274" s="3" t="inlineStr"/>
       <c r="E274" s="3" t="inlineStr">
@@ -9135,7 +9135,7 @@
         <v>330</v>
       </c>
       <c r="C281" s="5" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D281" s="3" t="inlineStr"/>
       <c r="E281" s="3" t="inlineStr">

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G305"/>
+  <dimension ref="A1:G304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,11 +791,11 @@
       <c r="B10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="D10" s="3" t="n">
         <v>15</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>17</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>19</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         <v>13</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>14</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -978,10 +978,10 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -1008,11 +1008,11 @@
       <c r="B17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C17" s="9" t="n">
-        <v>29</v>
+      <c r="C17" s="4" t="n">
+        <v>26</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>13</v>
@@ -1102,10 +1102,10 @@
         <v>19</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>44</v>
@@ -1226,10 +1226,10 @@
         <v>23</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
         <v>24</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -1287,11 +1287,11 @@
       <c r="B26" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="C26" s="5" t="n">
-        <v>27</v>
+      <c r="C26" s="4" t="n">
+        <v>29</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
         <v>30</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>31</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>45</v>
@@ -1536,10 +1536,10 @@
         <v>33</v>
       </c>
       <c r="C34" s="9" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1566,11 +1566,11 @@
       <c r="B35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="C35" s="4" t="n">
-        <v>44</v>
+      <c r="C35" s="5" t="n">
+        <v>36</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -1597,11 +1597,11 @@
       <c r="B36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="C36" s="5" t="n">
-        <v>35</v>
+      <c r="C36" s="7" t="n">
+        <v>27</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -1629,10 +1629,10 @@
         <v>36</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -1690,11 +1690,11 @@
       <c r="B39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="C39" s="7" t="n">
-        <v>26</v>
+      <c r="C39" s="11" t="n">
+        <v>28</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>17</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>34</v>
@@ -1784,7 +1784,7 @@
         <v>41</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>25</v>
@@ -1815,10 +1815,10 @@
         <v>42</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         <v>43</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>44</v>
       </c>
       <c r="C45" s="9" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -1908,7 +1908,7 @@
         <v>45</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>36</v>
@@ -1938,11 +1938,11 @@
       <c r="B47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="C47" s="5" t="n">
-        <v>46</v>
+      <c r="C47" s="4" t="n">
+        <v>52</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -1970,10 +1970,10 @@
         <v>47</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         <v>48</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
         <v>49</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D52" s="3" t="n">
         <v>46</v>
@@ -2125,10 +2125,10 @@
         <v>52</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>53</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D54" s="3" t="n">
         <v>53</v>
@@ -2190,7 +2190,7 @@
         <v>42</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -2217,11 +2217,11 @@
       <c r="B56" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C56" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="D56" s="3" t="n">
         <v>61</v>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>59</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>47</v>
@@ -2280,10 +2280,10 @@
         <v>57</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -2310,8 +2310,8 @@
       <c r="B59" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="C59" s="9" t="n">
-        <v>71</v>
+      <c r="C59" s="4" t="n">
+        <v>69</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>62</v>
@@ -2342,10 +2342,10 @@
         <v>59</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -2373,10 +2373,10 @@
         <v>60</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
@@ -2403,11 +2403,11 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="5" t="n">
-        <v>58</v>
+      <c r="C62" s="7" t="n">
+        <v>43</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
@@ -2435,10 +2435,10 @@
         <v>62</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -2465,11 +2465,11 @@
       <c r="B64" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="C64" s="9" t="n">
-        <v>76</v>
+      <c r="C64" s="4" t="n">
+        <v>75</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -2559,10 +2559,10 @@
         <v>66</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
         <v>67</v>
       </c>
       <c r="C68" s="9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
         <v>68</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -2651,8 +2651,8 @@
       <c r="B70" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="C70" s="7" t="n">
-        <v>59</v>
+      <c r="C70" s="11" t="n">
+        <v>64</v>
       </c>
       <c r="D70" s="3" t="n">
         <v>64</v>
@@ -2682,11 +2682,11 @@
       <c r="B71" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C71" s="7" t="n">
-        <v>57</v>
+      <c r="C71" s="11" t="n">
+        <v>63</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -2714,10 +2714,10 @@
         <v>71</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -2744,11 +2744,11 @@
       <c r="B73" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="C73" s="5" t="n">
-        <v>63</v>
+      <c r="C73" s="9" t="n">
+        <v>93</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -2775,8 +2775,8 @@
       <c r="B74" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="C74" s="4" t="n">
-        <v>85</v>
+      <c r="C74" s="9" t="n">
+        <v>88</v>
       </c>
       <c r="D74" s="3" t="n">
         <v>84</v>
@@ -2807,10 +2807,10 @@
         <v>74</v>
       </c>
       <c r="C75" s="9" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D76" s="3" t="n">
         <v>63</v>
@@ -2869,10 +2869,10 @@
         <v>76</v>
       </c>
       <c r="C77" s="9" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         <v>77</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -2931,10 +2931,10 @@
         <v>78</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D80" s="3" t="n">
         <v>68</v>
@@ -2992,11 +2992,11 @@
       <c r="B81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="C81" s="9" t="n">
-        <v>93</v>
+      <c r="C81" s="4" t="n">
+        <v>92</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>81</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>82</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>86</v>
@@ -3086,10 +3086,10 @@
         <v>83</v>
       </c>
       <c r="C84" s="9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="7" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>71</v>
@@ -3148,10 +3148,10 @@
         <v>85</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -3178,11 +3178,11 @@
       <c r="B87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="C87" s="5" t="n">
+      <c r="C87" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="D87" s="3" t="n">
         <v>74</v>
-      </c>
-      <c r="D87" s="3" t="n">
-        <v>76</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         <v>87</v>
       </c>
       <c r="C88" s="9" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
@@ -3240,11 +3240,11 @@
       <c r="B89" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="C89" s="11" t="n">
-        <v>79</v>
+      <c r="C89" s="7" t="n">
+        <v>72</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
@@ -3272,10 +3272,10 @@
         <v>89</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
@@ -3302,11 +3302,11 @@
       <c r="B91" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="C91" s="9" t="n">
-        <v>106</v>
+      <c r="C91" s="5" t="n">
+        <v>94</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -3334,10 +3334,10 @@
         <v>91</v>
       </c>
       <c r="C92" s="9" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -3365,10 +3365,10 @@
         <v>92</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>147</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
@@ -3427,10 +3427,10 @@
         <v>94</v>
       </c>
       <c r="C95" s="9" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
@@ -3458,10 +3458,10 @@
         <v>95</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         <v>96</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>91</v>
@@ -3520,10 +3520,10 @@
         <v>97</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         <v>98</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
@@ -3582,10 +3582,10 @@
         <v>99</v>
       </c>
       <c r="C100" s="9" t="n">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         <v>101</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>137</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
         <v>103</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
@@ -3705,8 +3705,8 @@
       <c r="B104" s="3" t="n">
         <v>104</v>
       </c>
-      <c r="C104" s="11" t="n">
-        <v>77</v>
+      <c r="C104" s="5" t="n">
+        <v>84</v>
       </c>
       <c r="D104" s="3" t="n">
         <v>83</v>
@@ -3740,7 +3740,7 @@
         <v>136</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
@@ -3768,10 +3768,10 @@
         <v>106</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         <v>107</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>138</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
@@ -3861,10 +3861,10 @@
         <v>109</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
@@ -3892,10 +3892,10 @@
         <v>110</v>
       </c>
       <c r="C110" s="7" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -3923,10 +3923,10 @@
         <v>111</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
@@ -3954,10 +3954,10 @@
         <v>112</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
         <v>113</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
         <v>114</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
@@ -4046,11 +4046,11 @@
       <c r="B115" s="3" t="n">
         <v>115</v>
       </c>
-      <c r="C115" s="11" t="n">
-        <v>111</v>
+      <c r="C115" s="7" t="n">
+        <v>102</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
@@ -4078,10 +4078,10 @@
         <v>116</v>
       </c>
       <c r="C116" s="9" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
@@ -4109,10 +4109,10 @@
         <v>117</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
@@ -4140,10 +4140,10 @@
         <v>118</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
@@ -4170,11 +4170,11 @@
       <c r="B119" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="C119" s="5" t="n">
-        <v>118</v>
+      <c r="C119" s="7" t="n">
+        <v>108</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
@@ -4201,11 +4201,11 @@
       <c r="B120" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="C120" s="4" t="n">
-        <v>130</v>
+      <c r="C120" s="9" t="n">
+        <v>133</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
@@ -4232,11 +4232,11 @@
       <c r="B121" s="3" t="n">
         <v>121</v>
       </c>
-      <c r="C121" s="11" t="n">
-        <v>86</v>
+      <c r="C121" s="5" t="n">
+        <v>105</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>193</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
@@ -4295,10 +4295,10 @@
         <v>123</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>124</v>
       </c>
       <c r="C124" s="7" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>88</v>
@@ -4357,10 +4357,10 @@
         <v>125</v>
       </c>
       <c r="C125" s="7" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
@@ -4388,10 +4388,10 @@
         <v>126</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
@@ -4418,11 +4418,11 @@
       <c r="B127" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="C127" s="4" t="n">
-        <v>134</v>
+      <c r="C127" s="5" t="n">
+        <v>119</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>96</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>148</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
@@ -4511,11 +4511,11 @@
       <c r="B130" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="C130" s="7" t="n">
-        <v>117</v>
+      <c r="C130" s="11" t="n">
+        <v>123</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>145</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
@@ -4574,10 +4574,10 @@
         <v>132</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
@@ -4604,11 +4604,11 @@
       <c r="B133" s="3" t="n">
         <v>133</v>
       </c>
-      <c r="C133" s="11" t="n">
-        <v>94</v>
+      <c r="C133" s="7" t="n">
+        <v>78</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>192</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>149</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>169</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
@@ -4729,10 +4729,10 @@
         <v>137</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>194</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
@@ -4791,10 +4791,10 @@
         <v>139</v>
       </c>
       <c r="C139" s="7" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>156</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>175</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
@@ -4946,10 +4946,10 @@
         <v>144</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>218</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
@@ -5008,10 +5008,10 @@
         <v>146</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
@@ -5039,10 +5039,10 @@
         <v>147</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
         <v>148</v>
       </c>
       <c r="C148" s="9" t="n">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
@@ -5101,10 +5101,10 @@
         <v>149</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
@@ -5132,10 +5132,10 @@
         <v>150</v>
       </c>
       <c r="C150" s="4" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>206</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>205</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
@@ -5225,10 +5225,10 @@
         <v>153</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>157</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
@@ -5287,10 +5287,10 @@
         <v>155</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>144</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>211</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         <v>159</v>
       </c>
       <c r="C158" s="7" t="n">
+        <v>116</v>
+      </c>
+      <c r="D158" s="3" t="n">
         <v>114</v>
-      </c>
-      <c r="D158" s="3" t="n">
-        <v>123</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
@@ -5442,10 +5442,10 @@
         <v>161</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>232</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
@@ -5503,11 +5503,11 @@
       <c r="B162" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="C162" s="5" t="n">
-        <v>176</v>
+      <c r="C162" s="4" t="n">
+        <v>195</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>167</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>207</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
         <v>167</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>239</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>189</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>197</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>174</v>
       </c>
       <c r="C169" s="4" t="n">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D169" s="3" t="n">
         <v>282</v>
@@ -5752,10 +5752,10 @@
         <v>175</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>171</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>177</v>
       </c>
       <c r="C172" s="7" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D172" s="3" t="n">
         <v>92</v>
@@ -5845,10 +5845,10 @@
         <v>178</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>236</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
@@ -5907,7 +5907,7 @@
         <v>185</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="D175" s="3" t="n">
         <v>275</v>
@@ -5938,7 +5938,7 @@
         <v>186</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D176" s="3" t="n">
         <v>277</v>
@@ -5968,11 +5968,11 @@
       <c r="B177" s="3" t="n">
         <v>187</v>
       </c>
-      <c r="C177" s="4" t="n">
-        <v>231</v>
+      <c r="C177" s="5" t="n">
+        <v>202</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -5999,11 +5999,11 @@
       <c r="B178" s="3" t="n">
         <v>188</v>
       </c>
-      <c r="C178" s="5" t="n">
-        <v>202</v>
+      <c r="C178" s="4" t="n">
+        <v>254</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>191</v>
       </c>
       <c r="C179" s="4" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D179" s="3" t="n">
         <v>260</v>
@@ -6096,7 +6096,7 @@
         <v>274</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
@@ -6124,10 +6124,10 @@
         <v>195</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
@@ -6155,10 +6155,10 @@
         <v>196</v>
       </c>
       <c r="C183" s="5" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>159</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
@@ -6248,10 +6248,10 @@
         <v>201</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
@@ -6278,8 +6278,8 @@
       <c r="B187" s="3" t="n">
         <v>202</v>
       </c>
-      <c r="C187" s="11" t="n">
-        <v>170</v>
+      <c r="C187" s="5" t="n">
+        <v>172</v>
       </c>
       <c r="D187" s="3" t="n">
         <v>196</v>
@@ -6310,10 +6310,10 @@
         <v>204</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
@@ -6341,10 +6341,10 @@
         <v>205</v>
       </c>
       <c r="C189" s="5" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>206</v>
       </c>
       <c r="C190" s="4" t="n">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="D190" s="3" t="n">
         <v>268</v>
@@ -6402,11 +6402,11 @@
       <c r="B191" s="3" t="n">
         <v>207</v>
       </c>
-      <c r="C191" s="5" t="n">
-        <v>229</v>
+      <c r="C191" s="4" t="n">
+        <v>257</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>173</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
@@ -6465,10 +6465,10 @@
         <v>212</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>213</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D194" s="3" t="n">
         <v>279</v>
@@ -6527,7 +6527,7 @@
         <v>217</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D195" s="3" t="n">
         <v>262</v>
@@ -6561,7 +6561,7 @@
         <v>228</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
@@ -6589,10 +6589,10 @@
         <v>221</v>
       </c>
       <c r="C197" s="4" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>238</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>219</v>
       </c>
       <c r="D199" s="3" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>224</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D200" s="3" t="inlineStr"/>
       <c r="E200" s="3" t="inlineStr">
@@ -6711,10 +6711,10 @@
         <v>225</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
@@ -6742,10 +6742,10 @@
         <v>228</v>
       </c>
       <c r="C202" s="5" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
@@ -6773,10 +6773,10 @@
         <v>230</v>
       </c>
       <c r="C203" s="5" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D203" s="3" t="n">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
@@ -6804,10 +6804,10 @@
         <v>232</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D204" s="3" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>233</v>
       </c>
       <c r="C205" s="4" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D205" s="3" t="n">
         <v>280</v>
@@ -6869,7 +6869,7 @@
         <v>227</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>235</v>
       </c>
       <c r="C207" s="5" t="n">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="D207" s="3" t="n">
         <v>272</v>
@@ -6928,10 +6928,10 @@
         <v>237</v>
       </c>
       <c r="C208" s="5" t="n">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
@@ -6959,10 +6959,10 @@
         <v>238</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
@@ -6990,10 +6990,10 @@
         <v>239</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>237</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
@@ -7051,11 +7051,11 @@
       <c r="B212" s="3" t="n">
         <v>241</v>
       </c>
-      <c r="C212" s="5" t="n">
-        <v>266</v>
+      <c r="C212" s="4" t="n">
+        <v>285</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>230</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
@@ -7144,8 +7144,8 @@
       <c r="B215" s="3" t="n">
         <v>244</v>
       </c>
-      <c r="C215" s="5" t="n">
-        <v>215</v>
+      <c r="C215" s="4" t="n">
+        <v>298</v>
       </c>
       <c r="D215" s="3" t="n">
         <v>281</v>
@@ -7179,7 +7179,7 @@
         <v>166</v>
       </c>
       <c r="D216" s="3" t="n">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>246</v>
       </c>
       <c r="C217" s="5" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D217" s="3" t="n">
         <v>284</v>
@@ -7238,10 +7238,10 @@
         <v>248</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>249</v>
       </c>
       <c r="C219" s="5" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D219" s="3" t="n">
         <v>288</v>
@@ -7300,7 +7300,7 @@
         <v>250</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D220" s="3" t="inlineStr"/>
       <c r="E220" s="3" t="inlineStr">
@@ -7391,10 +7391,10 @@
         <v>254</v>
       </c>
       <c r="C223" s="5" t="n">
-        <v>258</v>
+        <v>221</v>
       </c>
       <c r="D223" s="3" t="n">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>255</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D224" s="3" t="inlineStr"/>
       <c r="E224" s="3" t="inlineStr">
@@ -7451,7 +7451,7 @@
         <v>256</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D225" s="3" t="n">
         <v>294</v>
@@ -7482,7 +7482,7 @@
         <v>257</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D226" s="3" t="n">
         <v>273</v>
@@ -7542,7 +7542,7 @@
         <v>259</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D228" s="3" t="n">
         <v>270</v>
@@ -7573,7 +7573,7 @@
         <v>260</v>
       </c>
       <c r="C229" s="5" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D229" s="3" t="n">
         <v>291</v>
@@ -7603,8 +7603,8 @@
       <c r="B230" s="3" t="n">
         <v>261</v>
       </c>
-      <c r="C230" s="5" t="n">
-        <v>295</v>
+      <c r="C230" s="4" t="n">
+        <v>317</v>
       </c>
       <c r="D230" s="3" t="n">
         <v>292</v>
@@ -7634,11 +7634,11 @@
       <c r="B231" s="3" t="n">
         <v>262</v>
       </c>
-      <c r="C231" s="5" t="n">
-        <v>203</v>
+      <c r="C231" s="11" t="n">
+        <v>174</v>
       </c>
       <c r="D231" s="3" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>264</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="D233" s="3" t="n">
         <v>259</v>
@@ -7726,7 +7726,7 @@
         <v>265</v>
       </c>
       <c r="C234" s="5" t="n">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="D234" s="3" t="n">
         <v>290</v>
@@ -7760,7 +7760,7 @@
         <v>240</v>
       </c>
       <c r="D235" s="3" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
@@ -7788,10 +7788,10 @@
         <v>267</v>
       </c>
       <c r="C236" s="5" t="n">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="D236" s="3" t="n">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>268</v>
       </c>
       <c r="C237" s="4" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D237" s="3" t="inlineStr"/>
       <c r="E237" s="3" t="inlineStr">
@@ -7847,8 +7847,8 @@
       <c r="B238" s="3" t="n">
         <v>269</v>
       </c>
-      <c r="C238" s="4" t="n">
-        <v>326</v>
+      <c r="C238" s="5" t="n">
+        <v>288</v>
       </c>
       <c r="D238" s="3" t="n">
         <v>285</v>
@@ -7879,7 +7879,7 @@
         <v>270</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D239" s="3" t="n">
         <v>289</v>
@@ -7910,7 +7910,7 @@
         <v>271</v>
       </c>
       <c r="C240" s="5" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D240" s="3" t="n">
         <v>287</v>
@@ -7941,7 +7941,7 @@
         <v>272</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D241" s="3" t="n">
         <v>286</v>
@@ -7972,7 +7972,7 @@
         <v>273</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="D242" s="3" t="inlineStr"/>
       <c r="E242" s="3" t="inlineStr">
@@ -8001,7 +8001,7 @@
         <v>274</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D243" s="3" t="inlineStr"/>
       <c r="E243" s="3" t="inlineStr">
@@ -8030,7 +8030,7 @@
         <v>275</v>
       </c>
       <c r="C244" s="5" t="n">
-        <v>308</v>
+        <v>270</v>
       </c>
       <c r="D244" s="3" t="inlineStr"/>
       <c r="E244" s="3" t="inlineStr">
@@ -8062,7 +8062,7 @@
         <v>275</v>
       </c>
       <c r="D245" s="3" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>272</v>
       </c>
       <c r="D246" s="3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>198</v>
       </c>
       <c r="D247" s="3" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>281</v>
       </c>
       <c r="C249" s="4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D249" s="3" t="inlineStr"/>
       <c r="E249" s="3" t="inlineStr">
@@ -8210,7 +8210,7 @@
         <v>282</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="D250" s="3" t="n">
         <v>264</v>
@@ -8272,7 +8272,7 @@
         <v>284</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D252" s="3" t="inlineStr"/>
       <c r="E252" s="3" t="inlineStr">
@@ -8301,7 +8301,7 @@
         <v>285</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="D253" s="3" t="n">
         <v>300</v>
@@ -8390,10 +8390,10 @@
         <v>290</v>
       </c>
       <c r="C256" s="5" t="n">
-        <v>283</v>
+        <v>265</v>
       </c>
       <c r="D256" s="3" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>292</v>
       </c>
       <c r="C257" s="5" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D257" s="3" t="inlineStr"/>
       <c r="E257" s="3" t="inlineStr">
@@ -8453,7 +8453,7 @@
         <v>212</v>
       </c>
       <c r="D258" s="3" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>294</v>
       </c>
       <c r="C259" s="4" t="n">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
@@ -8510,7 +8510,7 @@
         <v>296</v>
       </c>
       <c r="C260" s="5" t="n">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="D260" s="3" t="inlineStr"/>
       <c r="E260" s="3" t="inlineStr">
@@ -8602,7 +8602,7 @@
         <v>251</v>
       </c>
       <c r="D263" s="3" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>300</v>
       </c>
       <c r="C264" s="5" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D264" s="3" t="n">
         <v>261</v>
@@ -8661,7 +8661,7 @@
         <v>301</v>
       </c>
       <c r="C265" s="5" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D265" s="3" t="inlineStr"/>
       <c r="E265" s="3" t="inlineStr">
@@ -8693,7 +8693,7 @@
         <v>252</v>
       </c>
       <c r="D266" s="3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E266" s="3" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>304</v>
       </c>
       <c r="C267" s="5" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D267" s="3" t="inlineStr"/>
       <c r="E267" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
         <v>305</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D268" s="3" t="inlineStr"/>
       <c r="E268" s="3" t="inlineStr">
@@ -8779,10 +8779,10 @@
         <v>306</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>256</v>
+        <v>201</v>
       </c>
       <c r="D269" s="3" t="n">
-        <v>246</v>
+        <v>200</v>
       </c>
       <c r="E269" s="3" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>310</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr">
@@ -8868,7 +8868,7 @@
         <v>311</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
@@ -8897,7 +8897,7 @@
         <v>312</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D273" s="3" t="inlineStr"/>
       <c r="E273" s="3" t="inlineStr">
@@ -8926,7 +8926,7 @@
         <v>314</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D274" s="3" t="inlineStr"/>
       <c r="E274" s="3" t="inlineStr">
@@ -8986,7 +8986,7 @@
         <v>317</v>
       </c>
       <c r="C276" s="5" t="n">
-        <v>287</v>
+        <v>341</v>
       </c>
       <c r="D276" s="3" t="inlineStr"/>
       <c r="E276" s="3" t="inlineStr">
@@ -9015,7 +9015,7 @@
         <v>322</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D277" s="3" t="n">
         <v>271</v>
@@ -9037,86 +9037,86 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>WR113</t>
+      <c r="A278" s="10" t="inlineStr">
+        <is>
+          <t>QB36</t>
         </is>
       </c>
       <c r="B278" s="3" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C278" s="5" t="n">
-        <v>332</v>
+        <v>365</v>
       </c>
       <c r="D278" s="3" t="inlineStr"/>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>Konata Mumpfield</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="10" t="inlineStr">
-        <is>
-          <t>QB36</t>
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>WR114</t>
         </is>
       </c>
       <c r="B279" s="3" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>362</v>
-      </c>
-      <c r="D279" s="3" t="inlineStr"/>
+        <v>283</v>
+      </c>
+      <c r="D279" s="3" t="n">
+        <v>267</v>
+      </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Luke McCaffrey</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>WR114</t>
+          <t>WR116</t>
         </is>
       </c>
       <c r="B280" s="3" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>284</v>
-      </c>
-      <c r="D280" s="3" t="n">
-        <v>267</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="D280" s="3" t="inlineStr"/>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Luke McCaffrey</t>
+          <t>Jahan Dotson</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>ATL (11)</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -9128,24 +9128,24 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>WR116</t>
+          <t>WR117</t>
         </is>
       </c>
       <c r="B281" s="3" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C281" s="5" t="n">
-        <v>266</v>
+        <v>349</v>
       </c>
       <c r="D281" s="3" t="inlineStr"/>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>Jalen Royals</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>ATL (11)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -9155,81 +9155,83 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>WR117</t>
+      <c r="A282" s="8" t="inlineStr">
+        <is>
+          <t>TE40</t>
         </is>
       </c>
       <c r="B282" s="3" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C282" s="5" t="n">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="D282" s="3" t="inlineStr"/>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>Jalen Royals</t>
+          <t>Max Klare</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>KC (5)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="8" t="inlineStr">
-        <is>
-          <t>TE40</t>
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>WR118</t>
         </is>
       </c>
       <c r="B283" s="3" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C283" s="5" t="n">
-        <v>363</v>
-      </c>
-      <c r="D283" s="3" t="inlineStr"/>
+        <v>231</v>
+      </c>
+      <c r="D283" s="3" t="n">
+        <v>223</v>
+      </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>Max Klare</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>WR118</t>
+          <t>WR120</t>
         </is>
       </c>
       <c r="B284" s="3" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="D284" s="3" t="n">
-        <v>222</v>
+        <v>278</v>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Caleb Douglas</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
@@ -9246,26 +9248,24 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>WR120</t>
+          <t>WR122</t>
         </is>
       </c>
       <c r="B285" s="3" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>291</v>
-      </c>
-      <c r="D285" s="3" t="n">
-        <v>278</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="D285" s="3" t="inlineStr"/>
       <c r="E285" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Joshua Palmer</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -9284,7 +9284,7 @@
         <v>338</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D286" s="3" t="inlineStr"/>
       <c r="E286" s="3" t="inlineStr">
@@ -9313,7 +9313,7 @@
         <v>340</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D287" s="3" t="inlineStr"/>
       <c r="E287" s="3" t="inlineStr">
@@ -9342,7 +9342,7 @@
         <v>341</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
@@ -9371,7 +9371,7 @@
         <v>344</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr">
@@ -9400,7 +9400,7 @@
         <v>348</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D290" s="3" t="inlineStr"/>
       <c r="E290" s="3" t="inlineStr">
@@ -9429,7 +9429,7 @@
         <v>349</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
@@ -9458,7 +9458,7 @@
         <v>350</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
@@ -9487,7 +9487,7 @@
         <v>351</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr">
@@ -9507,55 +9507,55 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="inlineStr">
-        <is>
-          <t>WR129</t>
+      <c r="A294" s="6" t="inlineStr">
+        <is>
+          <t>RB104</t>
         </is>
       </c>
       <c r="B294" s="3" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>Kalif Raymond</t>
+          <t>Jawhar Jordan</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>CHI (10)</t>
+          <t>HOU (8)</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>RB104</t>
+          <t>RB105</t>
         </is>
       </c>
       <c r="B295" s="3" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>349</v>
+        <v>309</v>
       </c>
       <c r="D295" s="3" t="inlineStr"/>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>Jawhar Jordan</t>
+          <t>Nick Chubb</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>HOU (8)</t>
+          <t>FA ()</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -9565,57 +9565,57 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="6" t="inlineStr">
-        <is>
-          <t>RB105</t>
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>WR130</t>
         </is>
       </c>
       <c r="B296" s="3" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>313</v>
-      </c>
-      <c r="D296" s="3" t="inlineStr"/>
+        <v>338</v>
+      </c>
+      <c r="D296" s="3" t="n">
+        <v>293</v>
+      </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>Nick Chubb</t>
+          <t>Treylon Burks</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>FA ()</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>WR130</t>
+          <t>WR133</t>
         </is>
       </c>
       <c r="B297" s="3" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="D297" s="3" t="n">
-        <v>293</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="D297" s="3" t="inlineStr"/>
       <c r="E297" s="3" t="inlineStr">
         <is>
-          <t>Treylon Burks</t>
+          <t>Savion Williams</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>GB (11)</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -9625,234 +9625,205 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="inlineStr">
-        <is>
-          <t>WR133</t>
+      <c r="A298" s="8" t="inlineStr">
+        <is>
+          <t>TE49</t>
         </is>
       </c>
       <c r="B298" s="3" t="n">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="D298" s="3" t="inlineStr"/>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>Savion Williams</t>
+          <t>Noah Fant</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>GB (11)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="8" t="inlineStr">
-        <is>
-          <t>TE49</t>
+      <c r="A299" s="6" t="inlineStr">
+        <is>
+          <t>RB107</t>
         </is>
       </c>
       <c r="B299" s="3" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="D299" s="3" t="inlineStr"/>
       <c r="E299" s="3" t="inlineStr">
         <is>
-          <t>Noah Fant</t>
+          <t>Raheim Sanders</t>
         </is>
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="6" t="inlineStr">
-        <is>
-          <t>RB107</t>
+      <c r="A300" s="8" t="inlineStr">
+        <is>
+          <t>TE50</t>
         </is>
       </c>
       <c r="B300" s="3" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C300" s="5" t="n">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="D300" s="3" t="inlineStr"/>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>Raheim Sanders</t>
+          <t>Eli Raridon</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="8" t="inlineStr">
-        <is>
-          <t>TE50</t>
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>WR138</t>
         </is>
       </c>
       <c r="B301" s="3" t="n">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C301" s="5" t="n">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="D301" s="3" t="inlineStr"/>
       <c r="E301" s="3" t="inlineStr">
         <is>
-          <t>Eli Raridon</t>
+          <t>Zavion Thomas</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>CHI (10)</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="inlineStr">
-        <is>
-          <t>WR137</t>
+      <c r="A302" s="6" t="inlineStr">
+        <is>
+          <t>RB109</t>
         </is>
       </c>
       <c r="B302" s="3" t="n">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>356</v>
+        <v>319</v>
       </c>
       <c r="D302" s="3" t="inlineStr"/>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>Kevin Coleman</t>
+          <t>Phil Mafah</t>
         </is>
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>DAL (14)</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="6" t="inlineStr">
-        <is>
-          <t>RB109</t>
+      <c r="A303" s="8" t="inlineStr">
+        <is>
+          <t>TE52</t>
         </is>
       </c>
       <c r="B303" s="3" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>320</v>
-      </c>
-      <c r="D303" s="3" t="inlineStr"/>
+        <v>318</v>
+      </c>
+      <c r="D303" s="3" t="n">
+        <v>301</v>
+      </c>
       <c r="E303" s="3" t="inlineStr">
         <is>
-          <t>Phil Mafah</t>
+          <t>Erick All</t>
         </is>
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>DAL (14)</t>
+          <t>CIN (6)</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="8" t="inlineStr">
-        <is>
-          <t>TE52</t>
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>WR142</t>
         </is>
       </c>
       <c r="B304" s="3" t="n">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C304" s="5" t="n">
-        <v>319</v>
-      </c>
-      <c r="D304" s="3" t="n">
-        <v>301</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="D304" s="3" t="inlineStr"/>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>Erick All</t>
+          <t>Jordan Whittington</t>
         </is>
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
-          <t>CIN (6)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>WR140</t>
-        </is>
-      </c>
-      <c r="B305" s="3" t="n">
-        <v>390</v>
-      </c>
-      <c r="C305" s="5" t="n">
-        <v>359</v>
-      </c>
-      <c r="D305" s="3" t="inlineStr"/>
-      <c r="E305" s="3" t="inlineStr">
-        <is>
-          <t>Devontez Walker</t>
-        </is>
-      </c>
-      <c r="F305" s="3" t="inlineStr">
-        <is>
-          <t>BAL (13)</t>
-        </is>
-      </c>
-      <c r="G305" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G304"/>
+  <dimension ref="A1:G303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
         <v>9</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>20</v>
@@ -916,7 +916,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>22</v>
@@ -947,10 +947,10 @@
         <v>14</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>21</v>
@@ -1009,7 +1009,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>27</v>
@@ -1043,7 +1043,7 @@
         <v>11</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
         <v>18</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -1102,10 +1102,10 @@
         <v>19</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -1133,10 +1133,10 @@
         <v>20</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         <v>22</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -1319,10 +1319,10 @@
         <v>26</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>30</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>31</v>
@@ -1474,7 +1474,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>30</v>
@@ -1505,7 +1505,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>45</v>
@@ -1566,11 +1566,11 @@
       <c r="B35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="C35" s="5" t="n">
-        <v>36</v>
+      <c r="C35" s="4" t="n">
+        <v>42</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
         <v>35</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>36</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>23</v>
@@ -1690,11 +1690,11 @@
       <c r="B39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="C39" s="11" t="n">
-        <v>28</v>
+      <c r="C39" s="5" t="n">
+        <v>33</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>17</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -1753,10 +1753,10 @@
         <v>40</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         <v>41</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1815,10 +1815,10 @@
         <v>42</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         <v>43</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         <v>45</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         <v>46</v>
       </c>
       <c r="C47" s="4" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -1970,10 +1970,10 @@
         <v>47</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>38</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>58</v>
@@ -2066,7 +2066,7 @@
         <v>47</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>56</v>
@@ -2155,11 +2155,11 @@
       <c r="B54" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="C54" s="5" t="n">
-        <v>50</v>
+      <c r="C54" s="4" t="n">
+        <v>57</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -2187,10 +2187,10 @@
         <v>54</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -2217,11 +2217,11 @@
       <c r="B56" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="C56" s="9" t="n">
-        <v>68</v>
+      <c r="C56" s="4" t="n">
+        <v>66</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -2310,11 +2310,11 @@
       <c r="B59" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="C59" s="4" t="n">
-        <v>69</v>
+      <c r="C59" s="5" t="n">
+        <v>65</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>70</v>
@@ -2404,7 +2404,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>54</v>
@@ -2435,7 +2435,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>48</v>
@@ -2497,7 +2497,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>55</v>
@@ -2562,7 +2562,7 @@
         <v>76</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -2745,10 +2745,10 @@
         <v>72</v>
       </c>
       <c r="C73" s="9" t="n">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -2775,11 +2775,11 @@
       <c r="B74" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="C74" s="9" t="n">
-        <v>88</v>
+      <c r="C74" s="4" t="n">
+        <v>84</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
         <v>74</v>
       </c>
       <c r="C75" s="9" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D76" s="3" t="n">
         <v>63</v>
@@ -2869,10 +2869,10 @@
         <v>76</v>
       </c>
       <c r="C77" s="9" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>77</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D78" s="3" t="n">
         <v>75</v>
@@ -2993,10 +2993,10 @@
         <v>80</v>
       </c>
       <c r="C81" s="4" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D82" s="3" t="n">
         <v>69</v>
@@ -3058,7 +3058,7 @@
         <v>80</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -3086,10 +3086,10 @@
         <v>83</v>
       </c>
       <c r="C84" s="9" t="n">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D86" s="3" t="n">
         <v>105</v>
@@ -3179,10 +3179,10 @@
         <v>86</v>
       </c>
       <c r="C87" s="7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="9" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>137</v>
@@ -3275,7 +3275,7 @@
         <v>101</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
@@ -3302,11 +3302,11 @@
       <c r="B91" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="C91" s="5" t="n">
-        <v>94</v>
+      <c r="C91" s="4" t="n">
+        <v>95</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -3334,10 +3334,10 @@
         <v>91</v>
       </c>
       <c r="C92" s="9" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -3396,10 +3396,10 @@
         <v>93</v>
       </c>
       <c r="C94" s="9" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
@@ -3427,10 +3427,10 @@
         <v>94</v>
       </c>
       <c r="C95" s="9" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D96" s="3" t="n">
         <v>82</v>
@@ -3489,10 +3489,10 @@
         <v>96</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D98" s="3" t="n">
         <v>132</v>
@@ -3551,10 +3551,10 @@
         <v>98</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
@@ -3582,10 +3582,10 @@
         <v>99</v>
       </c>
       <c r="C100" s="9" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         <v>101</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>102</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>138</v>
@@ -3678,7 +3678,7 @@
         <v>110</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
@@ -3706,10 +3706,10 @@
         <v>104</v>
       </c>
       <c r="C104" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="D104" s="3" t="n">
         <v>84</v>
-      </c>
-      <c r="D104" s="3" t="n">
-        <v>83</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
@@ -3737,10 +3737,10 @@
         <v>105</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>87</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         <v>107</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>108</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>139</v>
@@ -3864,7 +3864,7 @@
         <v>114</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
@@ -3892,10 +3892,10 @@
         <v>110</v>
       </c>
       <c r="C110" s="7" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -3923,10 +3923,10 @@
         <v>111</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>112</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>104</v>
@@ -3985,10 +3985,10 @@
         <v>113</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
         <v>114</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>115</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>112</v>
@@ -4112,7 +4112,7 @@
         <v>115</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
@@ -4140,10 +4140,10 @@
         <v>118</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
@@ -4201,8 +4201,8 @@
       <c r="B120" s="3" t="n">
         <v>120</v>
       </c>
-      <c r="C120" s="9" t="n">
-        <v>133</v>
+      <c r="C120" s="5" t="n">
+        <v>120</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>126</v>
@@ -4233,10 +4233,10 @@
         <v>121</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>122</v>
       </c>
       <c r="C122" s="9" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>169</v>
@@ -4326,10 +4326,10 @@
         <v>124</v>
       </c>
       <c r="C124" s="7" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
@@ -4357,10 +4357,10 @@
         <v>125</v>
       </c>
       <c r="C125" s="7" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
@@ -4388,7 +4388,7 @@
         <v>126</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D126" s="3" t="n">
         <v>127</v>
@@ -4419,10 +4419,10 @@
         <v>127</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
@@ -4450,10 +4450,10 @@
         <v>128</v>
       </c>
       <c r="C128" s="7" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
         <v>129</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         <v>130</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D130" s="3" t="n">
         <v>131</v>
@@ -4542,8 +4542,8 @@
       <c r="B131" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="C131" s="5" t="n">
-        <v>145</v>
+      <c r="C131" s="9" t="n">
+        <v>147</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>134</v>
@@ -4574,10 +4574,10 @@
         <v>132</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         <v>133</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>81</v>
@@ -4636,7 +4636,7 @@
         <v>134</v>
       </c>
       <c r="C134" s="9" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>168</v>
@@ -4667,7 +4667,7 @@
         <v>135</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>148</v>
@@ -4698,7 +4698,7 @@
         <v>136</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D136" s="3" t="n">
         <v>159</v>
@@ -4729,7 +4729,7 @@
         <v>137</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>171</v>
@@ -4760,7 +4760,7 @@
         <v>138</v>
       </c>
       <c r="C138" s="9" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D138" s="3" t="n">
         <v>170</v>
@@ -4791,7 +4791,7 @@
         <v>139</v>
       </c>
       <c r="C139" s="7" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>113</v>
@@ -4822,7 +4822,7 @@
         <v>140</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D140" s="3" t="n">
         <v>195</v>
@@ -4915,7 +4915,7 @@
         <v>143</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>173</v>
@@ -4946,7 +4946,7 @@
         <v>144</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D144" s="3" t="n">
         <v>189</v>
@@ -4977,7 +4977,7 @@
         <v>145</v>
       </c>
       <c r="C145" s="9" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D145" s="3" t="n">
         <v>208</v>
@@ -5008,7 +5008,7 @@
         <v>146</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D146" s="3" t="n">
         <v>135</v>
@@ -5039,7 +5039,7 @@
         <v>147</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>186</v>
@@ -5101,10 +5101,10 @@
         <v>149</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
@@ -5286,11 +5286,11 @@
       <c r="B155" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="C155" s="5" t="n">
-        <v>208</v>
+      <c r="C155" s="4" t="n">
+        <v>234</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
@@ -5317,8 +5317,8 @@
       <c r="B156" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="C156" s="7" t="n">
-        <v>144</v>
+      <c r="C156" s="11" t="n">
+        <v>146</v>
       </c>
       <c r="D156" s="3" t="n">
         <v>184</v>
@@ -5473,7 +5473,7 @@
         <v>162</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>214</v>
@@ -5503,8 +5503,8 @@
       <c r="B162" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="C162" s="4" t="n">
-        <v>195</v>
+      <c r="C162" s="5" t="n">
+        <v>178</v>
       </c>
       <c r="D162" s="3" t="n">
         <v>172</v>
@@ -5535,7 +5535,7 @@
         <v>165</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D163" s="3" t="n">
         <v>157</v>
@@ -5597,10 +5597,10 @@
         <v>167</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>169</v>
       </c>
       <c r="C166" s="4" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D166" s="3" t="n">
         <v>230</v>
@@ -5690,7 +5690,7 @@
         <v>173</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D168" s="3" t="n">
         <v>216</v>
@@ -5721,7 +5721,7 @@
         <v>174</v>
       </c>
       <c r="C169" s="4" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D169" s="3" t="n">
         <v>282</v>
@@ -5752,7 +5752,7 @@
         <v>175</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="D170" s="3" t="n">
         <v>226</v>
@@ -5783,7 +5783,7 @@
         <v>176</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D171" s="3" t="n">
         <v>182</v>
@@ -5814,10 +5814,10 @@
         <v>177</v>
       </c>
       <c r="C172" s="7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>179</v>
       </c>
       <c r="C174" s="4" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D174" s="3" t="n">
         <v>242</v>
@@ -5938,7 +5938,7 @@
         <v>186</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="D176" s="3" t="n">
         <v>277</v>
@@ -6000,7 +6000,7 @@
         <v>188</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D178" s="3" t="n">
         <v>228</v>
@@ -6062,7 +6062,7 @@
         <v>192</v>
       </c>
       <c r="C180" s="4" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D180" s="3" t="n">
         <v>265</v>
@@ -6093,7 +6093,7 @@
         <v>194</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D181" s="3" t="n">
         <v>253</v>
@@ -6123,11 +6123,11 @@
       <c r="B182" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="C182" s="5" t="n">
-        <v>176</v>
+      <c r="C182" s="11" t="n">
+        <v>162</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>196</v>
       </c>
       <c r="C183" s="5" t="n">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D183" s="3" t="n">
         <v>185</v>
@@ -6186,7 +6186,7 @@
         <v>197</v>
       </c>
       <c r="C184" s="4" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D184" s="3" t="n">
         <v>274</v>
@@ -6248,10 +6248,10 @@
         <v>201</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
@@ -6278,8 +6278,8 @@
       <c r="B187" s="3" t="n">
         <v>202</v>
       </c>
-      <c r="C187" s="5" t="n">
-        <v>172</v>
+      <c r="C187" s="11" t="n">
+        <v>171</v>
       </c>
       <c r="D187" s="3" t="n">
         <v>196</v>
@@ -6340,8 +6340,8 @@
       <c r="B189" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C189" s="5" t="n">
-        <v>235</v>
+      <c r="C189" s="4" t="n">
+        <v>236</v>
       </c>
       <c r="D189" s="3" t="n">
         <v>246</v>
@@ -6403,7 +6403,7 @@
         <v>207</v>
       </c>
       <c r="C191" s="4" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D191" s="3" t="n">
         <v>240</v>
@@ -6465,7 +6465,7 @@
         <v>212</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D193" s="3" t="n">
         <v>193</v>
@@ -6496,7 +6496,7 @@
         <v>213</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D194" s="3" t="n">
         <v>279</v>
@@ -6527,7 +6527,7 @@
         <v>217</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D195" s="3" t="n">
         <v>262</v>
@@ -6558,7 +6558,7 @@
         <v>219</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D196" s="3" t="n">
         <v>222</v>
@@ -6589,7 +6589,7 @@
         <v>221</v>
       </c>
       <c r="C197" s="4" t="n">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D197" s="3" t="n">
         <v>227</v>
@@ -6620,7 +6620,7 @@
         <v>222</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D198" s="3" t="n">
         <v>229</v>
@@ -6651,7 +6651,7 @@
         <v>223</v>
       </c>
       <c r="C199" s="5" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D199" s="3" t="n">
         <v>209</v>
@@ -6682,7 +6682,7 @@
         <v>224</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D200" s="3" t="inlineStr"/>
       <c r="E200" s="3" t="inlineStr">
@@ -6711,7 +6711,7 @@
         <v>225</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D201" s="3" t="n">
         <v>128</v>
@@ -6773,7 +6773,7 @@
         <v>230</v>
       </c>
       <c r="C203" s="5" t="n">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="D203" s="3" t="n">
         <v>201</v>
@@ -6804,7 +6804,7 @@
         <v>232</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D204" s="3" t="n">
         <v>252</v>
@@ -6835,7 +6835,7 @@
         <v>233</v>
       </c>
       <c r="C205" s="4" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="D205" s="3" t="n">
         <v>280</v>
@@ -6866,7 +6866,7 @@
         <v>234</v>
       </c>
       <c r="C206" s="5" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D206" s="3" t="n">
         <v>210</v>
@@ -6897,7 +6897,7 @@
         <v>235</v>
       </c>
       <c r="C207" s="5" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D207" s="3" t="n">
         <v>272</v>
@@ -6928,7 +6928,7 @@
         <v>237</v>
       </c>
       <c r="C208" s="5" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D208" s="3" t="n">
         <v>247</v>
@@ -6959,7 +6959,7 @@
         <v>238</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D209" s="3" t="n">
         <v>239</v>
@@ -6990,7 +6990,7 @@
         <v>239</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D210" s="3" t="n">
         <v>257</v>
@@ -7021,7 +7021,7 @@
         <v>240</v>
       </c>
       <c r="C211" s="5" t="n">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="D211" s="3" t="n">
         <v>241</v>
@@ -7052,7 +7052,7 @@
         <v>241</v>
       </c>
       <c r="C212" s="4" t="n">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="D212" s="3" t="n">
         <v>251</v>
@@ -7114,10 +7114,10 @@
         <v>243</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>244</v>
       </c>
       <c r="C215" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D215" s="3" t="n">
         <v>281</v>
@@ -7176,7 +7176,7 @@
         <v>245</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D216" s="3" t="n">
         <v>158</v>
@@ -7207,7 +7207,7 @@
         <v>246</v>
       </c>
       <c r="C217" s="5" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D217" s="3" t="n">
         <v>284</v>
@@ -7241,7 +7241,7 @@
         <v>220</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>249</v>
       </c>
       <c r="C219" s="5" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D219" s="3" t="n">
         <v>288</v>
@@ -7300,7 +7300,7 @@
         <v>250</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="D220" s="3" t="inlineStr"/>
       <c r="E220" s="3" t="inlineStr">
@@ -7328,8 +7328,8 @@
       <c r="B221" s="3" t="n">
         <v>251</v>
       </c>
-      <c r="C221" s="4" t="n">
-        <v>294</v>
+      <c r="C221" s="5" t="n">
+        <v>285</v>
       </c>
       <c r="D221" s="3" t="n">
         <v>269</v>
@@ -7360,7 +7360,7 @@
         <v>252</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D222" s="3" t="n">
         <v>249</v>
@@ -7422,7 +7422,7 @@
         <v>255</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="D224" s="3" t="inlineStr"/>
       <c r="E224" s="3" t="inlineStr">
@@ -7451,7 +7451,7 @@
         <v>256</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="D225" s="3" t="n">
         <v>294</v>
@@ -7482,7 +7482,7 @@
         <v>257</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D226" s="3" t="n">
         <v>273</v>
@@ -7513,7 +7513,7 @@
         <v>258</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>325</v>
+        <v>363</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
@@ -7573,7 +7573,7 @@
         <v>260</v>
       </c>
       <c r="C229" s="5" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D229" s="3" t="n">
         <v>291</v>
@@ -7604,7 +7604,7 @@
         <v>261</v>
       </c>
       <c r="C230" s="4" t="n">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D230" s="3" t="n">
         <v>292</v>
@@ -7635,10 +7635,10 @@
         <v>262</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D231" s="3" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
@@ -7657,210 +7657,212 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="inlineStr">
-        <is>
-          <t>WR99</t>
+      <c r="A232" s="8" t="inlineStr">
+        <is>
+          <t>TE33</t>
         </is>
       </c>
       <c r="B232" s="3" t="n">
-        <v>263</v>
-      </c>
-      <c r="C232" s="4" t="n">
-        <v>324</v>
-      </c>
-      <c r="D232" s="3" t="inlineStr"/>
+        <v>264</v>
+      </c>
+      <c r="C232" s="5" t="n">
+        <v>261</v>
+      </c>
+      <c r="D232" s="3" t="n">
+        <v>259</v>
+      </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>Chris Brazzell</t>
+          <t>Mason Taylor</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>CAR (5)</t>
+          <t>NYJ (13)</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="8" t="inlineStr">
-        <is>
-          <t>TE33</t>
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>RB72</t>
         </is>
       </c>
       <c r="B233" s="3" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="D233" s="3" t="n">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>Mason Taylor</t>
+          <t>Chris Brooks</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>NYJ (13)</t>
+          <t>GB (11)</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="10" t="inlineStr">
+        <is>
+          <t>QB31</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="C234" s="5" t="n">
+        <v>241</v>
+      </c>
+      <c r="D234" s="3" t="n">
+        <v>243</v>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>Tua Tagovailoa</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>ATL (11)</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>WR100</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="C235" s="5" t="n">
+        <v>225</v>
+      </c>
+      <c r="D235" s="3" t="n">
+        <v>225</v>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>Darius Slayton</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>NYG (8)</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="8" t="inlineStr">
+        <is>
+          <t>TE34</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="C236" s="4" t="n">
+        <v>341</v>
+      </c>
+      <c r="D236" s="3" t="inlineStr"/>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>Theo Johnson</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>NYG (8)</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
+        <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="6" t="inlineStr">
-        <is>
-          <t>RB72</t>
-        </is>
-      </c>
-      <c r="B234" s="3" t="n">
-        <v>265</v>
-      </c>
-      <c r="C234" s="5" t="n">
-        <v>280</v>
-      </c>
-      <c r="D234" s="3" t="n">
-        <v>290</v>
-      </c>
-      <c r="E234" s="3" t="inlineStr">
-        <is>
-          <t>Chris Brooks</t>
-        </is>
-      </c>
-      <c r="F234" s="3" t="inlineStr">
-        <is>
-          <t>GB (11)</t>
-        </is>
-      </c>
-      <c r="G234" s="3" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="6" t="inlineStr">
+        <is>
+          <t>RB73</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="C237" s="5" t="n">
+        <v>293</v>
+      </c>
+      <c r="D237" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="E237" s="3" t="inlineStr">
+        <is>
+          <t>Samaje Perine</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>CIN (6)</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr">
         <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="10" t="inlineStr">
-        <is>
-          <t>QB31</t>
-        </is>
-      </c>
-      <c r="B235" s="3" t="n">
-        <v>266</v>
-      </c>
-      <c r="C235" s="5" t="n">
-        <v>240</v>
-      </c>
-      <c r="D235" s="3" t="n">
-        <v>243</v>
-      </c>
-      <c r="E235" s="3" t="inlineStr">
-        <is>
-          <t>Tua Tagovailoa</t>
-        </is>
-      </c>
-      <c r="F235" s="3" t="inlineStr">
-        <is>
-          <t>ATL (11)</t>
-        </is>
-      </c>
-      <c r="G235" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
-        <is>
-          <t>WR100</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="n">
-        <v>267</v>
-      </c>
-      <c r="C236" s="5" t="n">
-        <v>233</v>
-      </c>
-      <c r="D236" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="E236" s="3" t="inlineStr">
-        <is>
-          <t>Darius Slayton</t>
-        </is>
-      </c>
-      <c r="F236" s="3" t="inlineStr">
-        <is>
-          <t>NYG (8)</t>
-        </is>
-      </c>
-      <c r="G236" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="8" t="inlineStr">
-        <is>
-          <t>TE34</t>
-        </is>
-      </c>
-      <c r="B237" s="3" t="n">
-        <v>268</v>
-      </c>
-      <c r="C237" s="4" t="n">
-        <v>350</v>
-      </c>
-      <c r="D237" s="3" t="inlineStr"/>
-      <c r="E237" s="3" t="inlineStr">
-        <is>
-          <t>Theo Johnson</t>
-        </is>
-      </c>
-      <c r="F237" s="3" t="inlineStr">
-        <is>
-          <t>NYG (8)</t>
-        </is>
-      </c>
-      <c r="G237" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
         <is>
-          <t>RB73</t>
+          <t>RB74</t>
         </is>
       </c>
       <c r="B238" s="3" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="D238" s="3" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>Samaje Perine</t>
+          <t>Isaiah Davis</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>CIN (6)</t>
+          <t>NYJ (13)</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -7872,26 +7874,26 @@
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>RB74</t>
+          <t>RB75</t>
         </is>
       </c>
       <c r="B239" s="3" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="D239" s="3" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>Isaiah Davis</t>
+          <t>Demond Claiborne</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>NYJ (13)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -7903,26 +7905,26 @@
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
         <is>
-          <t>RB75</t>
+          <t>RB76</t>
         </is>
       </c>
       <c r="B240" s="3" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C240" s="5" t="n">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="D240" s="3" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>Demond Claiborne</t>
+          <t>LeQuint Allen</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>JAC (7)</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -7934,26 +7936,24 @@
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>RB76</t>
+          <t>RB77</t>
         </is>
       </c>
       <c r="B241" s="3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>287</v>
-      </c>
-      <c r="D241" s="3" t="n">
-        <v>286</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="D241" s="3" t="inlineStr"/>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>LeQuint Allen</t>
+          <t>Devin Neal</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>JAC (7)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -7963,206 +7963,206 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="6" t="inlineStr">
-        <is>
-          <t>RB77</t>
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>WR101</t>
         </is>
       </c>
       <c r="B242" s="3" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="D242" s="3" t="inlineStr"/>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>Devin Neal</t>
+          <t>Xavier Legette</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>CAR (5)</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="inlineStr">
-        <is>
-          <t>WR101</t>
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>RB78</t>
         </is>
       </c>
       <c r="B243" s="3" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="D243" s="3" t="inlineStr"/>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>Xavier Legette</t>
+          <t>Seth McGowan</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>CAR (5)</t>
+          <t>IND (13)</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="6" t="inlineStr">
-        <is>
-          <t>RB78</t>
+      <c r="A244" s="10" t="inlineStr">
+        <is>
+          <t>QB32</t>
         </is>
       </c>
       <c r="B244" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="C244" s="5" t="n">
         <v>275</v>
       </c>
-      <c r="C244" s="5" t="n">
-        <v>270</v>
-      </c>
-      <c r="D244" s="3" t="inlineStr"/>
+      <c r="D244" s="3" t="n">
+        <v>256</v>
+      </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>Seth McGowan</t>
+          <t>Michael Penix</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>IND (13)</t>
+          <t>ATL (11)</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="6" t="inlineStr">
+        <is>
+          <t>RB79</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="n">
+        <v>277</v>
+      </c>
+      <c r="C245" s="5" t="n">
+        <v>271</v>
+      </c>
+      <c r="D245" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>Jordan James</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>SF (8)</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr">
+        <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="10" t="inlineStr">
-        <is>
-          <t>QB32</t>
-        </is>
-      </c>
-      <c r="B245" s="3" t="n">
-        <v>276</v>
-      </c>
-      <c r="C245" s="5" t="n">
-        <v>275</v>
-      </c>
-      <c r="D245" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="E245" s="3" t="inlineStr">
-        <is>
-          <t>Michael Penix</t>
-        </is>
-      </c>
-      <c r="F245" s="3" t="inlineStr">
-        <is>
-          <t>ATL (11)</t>
-        </is>
-      </c>
-      <c r="G245" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
     <row r="246">
-      <c r="A246" s="6" t="inlineStr">
-        <is>
-          <t>RB79</t>
+      <c r="A246" s="8" t="inlineStr">
+        <is>
+          <t>TE35</t>
         </is>
       </c>
       <c r="B246" s="3" t="n">
-        <v>277</v>
-      </c>
-      <c r="C246" s="5" t="n">
-        <v>272</v>
+        <v>278</v>
+      </c>
+      <c r="C246" s="11" t="n">
+        <v>193</v>
       </c>
       <c r="D246" s="3" t="n">
-        <v>254</v>
+        <v>217</v>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>Jordan James</t>
+          <t>Greg Dulcich</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="6" t="inlineStr">
+        <is>
+          <t>RB80</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="n">
+        <v>280</v>
+      </c>
+      <c r="C247" s="5" t="n">
+        <v>320</v>
+      </c>
+      <c r="D247" s="3" t="inlineStr"/>
+      <c r="E247" s="3" t="inlineStr">
+        <is>
+          <t>Kaleb Johnson</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>PIT (9)</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr">
+        <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="8" t="inlineStr">
-        <is>
-          <t>TE35</t>
-        </is>
-      </c>
-      <c r="B247" s="3" t="n">
-        <v>278</v>
-      </c>
-      <c r="C247" s="11" t="n">
-        <v>198</v>
-      </c>
-      <c r="D247" s="3" t="n">
-        <v>217</v>
-      </c>
-      <c r="E247" s="3" t="inlineStr">
-        <is>
-          <t>Greg Dulcich</t>
-        </is>
-      </c>
-      <c r="F247" s="3" t="inlineStr">
-        <is>
-          <t>MIA (6)</t>
-        </is>
-      </c>
-      <c r="G247" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
         <is>
-          <t>RB80</t>
+          <t>RB81</t>
         </is>
       </c>
       <c r="B248" s="3" t="n">
-        <v>280</v>
-      </c>
-      <c r="C248" s="5" t="n">
-        <v>285</v>
+        <v>281</v>
+      </c>
+      <c r="C248" s="4" t="n">
+        <v>337</v>
       </c>
       <c r="D248" s="3" t="inlineStr"/>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>Kaleb Johnson</t>
+          <t>Trey Benson</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>PIT (9)</t>
+          <t>ARI (14)</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -8172,88 +8172,88 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="6" t="inlineStr">
-        <is>
-          <t>RB81</t>
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>WR102</t>
         </is>
       </c>
       <c r="B249" s="3" t="n">
-        <v>281</v>
-      </c>
-      <c r="C249" s="4" t="n">
-        <v>339</v>
-      </c>
-      <c r="D249" s="3" t="inlineStr"/>
+        <v>282</v>
+      </c>
+      <c r="C249" s="5" t="n">
+        <v>268</v>
+      </c>
+      <c r="D249" s="3" t="n">
+        <v>264</v>
+      </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>Trey Benson</t>
+          <t>Tyquan Thornton</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>ARI (14)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="6" t="inlineStr">
+        <is>
+          <t>RB82</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="n">
+        <v>283</v>
+      </c>
+      <c r="C250" s="5" t="n">
+        <v>287</v>
+      </c>
+      <c r="D250" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="E250" s="3" t="inlineStr">
+        <is>
+          <t>George Holani</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr">
+        <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>WR102</t>
-        </is>
-      </c>
-      <c r="B250" s="3" t="n">
-        <v>282</v>
-      </c>
-      <c r="C250" s="5" t="n">
-        <v>268</v>
-      </c>
-      <c r="D250" s="3" t="n">
-        <v>264</v>
-      </c>
-      <c r="E250" s="3" t="inlineStr">
-        <is>
-          <t>Tyquan Thornton</t>
-        </is>
-      </c>
-      <c r="F250" s="3" t="inlineStr">
-        <is>
-          <t>KC (5)</t>
-        </is>
-      </c>
-      <c r="G250" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>RB82</t>
+          <t>RB83</t>
         </is>
       </c>
       <c r="B251" s="3" t="n">
-        <v>283</v>
-      </c>
-      <c r="C251" s="5" t="n">
-        <v>289</v>
-      </c>
-      <c r="D251" s="3" t="n">
-        <v>276</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="C251" s="4" t="n">
+        <v>338</v>
+      </c>
+      <c r="D251" s="3" t="inlineStr"/>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>George Holani</t>
+          <t>Malik Davis</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>DAL (14)</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
@@ -8263,57 +8263,57 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="6" t="inlineStr">
-        <is>
-          <t>RB83</t>
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>WR103</t>
         </is>
       </c>
       <c r="B252" s="3" t="n">
-        <v>284</v>
-      </c>
-      <c r="C252" s="4" t="n">
-        <v>345</v>
-      </c>
-      <c r="D252" s="3" t="inlineStr"/>
+        <v>285</v>
+      </c>
+      <c r="C252" s="5" t="n">
+        <v>293</v>
+      </c>
+      <c r="D252" s="3" t="n">
+        <v>300</v>
+      </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>Malik Davis</t>
+          <t>Devaughn Vele</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>DAL (14)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>WR103</t>
+          <t>WR104</t>
         </is>
       </c>
       <c r="B253" s="3" t="n">
-        <v>285</v>
-      </c>
-      <c r="C253" s="5" t="n">
-        <v>293</v>
-      </c>
-      <c r="D253" s="3" t="n">
-        <v>300</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="C253" s="4" t="n">
+        <v>349</v>
+      </c>
+      <c r="D253" s="3" t="inlineStr"/>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>Devaughn Vele</t>
+          <t>Kyle Williams</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -8323,115 +8323,117 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>WR104</t>
+      <c r="A254" s="10" t="inlineStr">
+        <is>
+          <t>QB33</t>
         </is>
       </c>
       <c r="B254" s="3" t="n">
-        <v>288</v>
-      </c>
-      <c r="C254" s="4" t="n">
-        <v>335</v>
+        <v>289</v>
+      </c>
+      <c r="C254" s="5" t="n">
+        <v>284</v>
       </c>
       <c r="D254" s="3" t="inlineStr"/>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>Kyle Williams</t>
+          <t>Shedeur Sanders</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="10" t="inlineStr">
-        <is>
-          <t>QB33</t>
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>WR105</t>
         </is>
       </c>
       <c r="B255" s="3" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>287</v>
-      </c>
-      <c r="D255" s="3" t="inlineStr"/>
+        <v>267</v>
+      </c>
+      <c r="D255" s="3" t="n">
+        <v>250</v>
+      </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>Shedeur Sanders</t>
+          <t>Keenan Allen</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>WR105</t>
+      <c r="A256" s="6" t="inlineStr">
+        <is>
+          <t>RB84</t>
         </is>
       </c>
       <c r="B256" s="3" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C256" s="5" t="n">
-        <v>265</v>
-      </c>
-      <c r="D256" s="3" t="n">
-        <v>250</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="D256" s="3" t="inlineStr"/>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>Keenan Allen</t>
+          <t>Brashard Smith</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>RB84</t>
+          <t>RB85</t>
         </is>
       </c>
       <c r="B257" s="3" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C257" s="5" t="n">
-        <v>320</v>
-      </c>
-      <c r="D257" s="3" t="inlineStr"/>
+        <v>240</v>
+      </c>
+      <c r="D257" s="3" t="n">
+        <v>213</v>
+      </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>Brashard Smith</t>
+          <t>Kaelon Black</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>KC (5)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
@@ -8441,297 +8443,295 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="6" t="inlineStr">
-        <is>
-          <t>RB85</t>
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>WR106</t>
         </is>
       </c>
       <c r="B258" s="3" t="n">
-        <v>293</v>
-      </c>
-      <c r="C258" s="5" t="n">
-        <v>212</v>
-      </c>
-      <c r="D258" s="3" t="n">
-        <v>213</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="C258" s="4" t="n">
+        <v>346</v>
+      </c>
+      <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>Kaelon Black</t>
+          <t>Hollywood Brown</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>PHI (10)</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>WR106</t>
+      <c r="A259" s="6" t="inlineStr">
+        <is>
+          <t>RB86</t>
         </is>
       </c>
       <c r="B259" s="3" t="n">
+        <v>296</v>
+      </c>
+      <c r="C259" s="5" t="n">
         <v>294</v>
-      </c>
-      <c r="C259" s="4" t="n">
-        <v>356</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>Hollywood Brown</t>
+          <t>Devin Singletary</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>PHI (10)</t>
+          <t>NYG (8)</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="6" t="inlineStr">
-        <is>
-          <t>RB86</t>
+      <c r="A260" s="8" t="inlineStr">
+        <is>
+          <t>TE36</t>
         </is>
       </c>
       <c r="B260" s="3" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C260" s="5" t="n">
-        <v>294</v>
+        <v>332</v>
       </c>
       <c r="D260" s="3" t="inlineStr"/>
       <c r="E260" s="3" t="inlineStr">
         <is>
-          <t>Devin Singletary</t>
+          <t>Oscar Delp</t>
         </is>
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>NYG (8)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="6" t="inlineStr">
+        <is>
+          <t>RB87</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="n">
+        <v>298</v>
+      </c>
+      <c r="C261" s="5" t="n">
+        <v>274</v>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>Emari Demercado</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>KC (5)</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="inlineStr">
+        <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" s="8" t="inlineStr">
-        <is>
-          <t>TE36</t>
-        </is>
-      </c>
-      <c r="B261" s="3" t="n">
-        <v>297</v>
-      </c>
-      <c r="C261" s="5" t="n">
-        <v>336</v>
-      </c>
-      <c r="D261" s="3" t="inlineStr"/>
-      <c r="E261" s="3" t="inlineStr">
-        <is>
-          <t>Oscar Delp</t>
-        </is>
-      </c>
-      <c r="F261" s="3" t="inlineStr">
+    <row r="262">
+      <c r="A262" s="10" t="inlineStr">
+        <is>
+          <t>QB34</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="n">
+        <v>299</v>
+      </c>
+      <c r="C262" s="5" t="n">
+        <v>252</v>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>244</v>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>Deshaun Watson</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="8" t="inlineStr">
+        <is>
+          <t>TE37</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="C263" s="5" t="n">
+        <v>280</v>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>261</v>
+      </c>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>Mike Gesicki</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>CIN (6)</t>
+        </is>
+      </c>
+      <c r="G263" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="6" t="inlineStr">
+        <is>
+          <t>RB88</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C264" s="5" t="n">
+        <v>306</v>
+      </c>
+      <c r="D264" s="3" t="inlineStr"/>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>Kendre Miller</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="G261" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="6" t="inlineStr">
-        <is>
-          <t>RB87</t>
-        </is>
-      </c>
-      <c r="B262" s="3" t="n">
-        <v>298</v>
-      </c>
-      <c r="C262" s="5" t="n">
-        <v>273</v>
-      </c>
-      <c r="D262" s="3" t="n">
-        <v>266</v>
-      </c>
-      <c r="E262" s="3" t="inlineStr">
-        <is>
-          <t>Emari Demercado</t>
-        </is>
-      </c>
-      <c r="F262" s="3" t="inlineStr">
-        <is>
-          <t>KC (5)</t>
-        </is>
-      </c>
-      <c r="G262" s="3" t="inlineStr">
+      <c r="G264" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="10" t="inlineStr">
-        <is>
-          <t>QB34</t>
-        </is>
-      </c>
-      <c r="B263" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="C263" s="5" t="n">
-        <v>251</v>
-      </c>
-      <c r="D263" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="E263" s="3" t="inlineStr">
-        <is>
-          <t>Deshaun Watson</t>
-        </is>
-      </c>
-      <c r="F263" s="3" t="inlineStr">
-        <is>
-          <t>CLE (11)</t>
-        </is>
-      </c>
-      <c r="G263" s="3" t="inlineStr">
+    <row r="265">
+      <c r="A265" s="10" t="inlineStr">
+        <is>
+          <t>QB35</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="n">
+        <v>302</v>
+      </c>
+      <c r="C265" s="5" t="n">
+        <v>253</v>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>Kirk Cousins</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>LV (13)</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="8" t="inlineStr">
-        <is>
-          <t>TE37</t>
-        </is>
-      </c>
-      <c r="B264" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="C264" s="5" t="n">
-        <v>280</v>
-      </c>
-      <c r="D264" s="3" t="n">
-        <v>261</v>
-      </c>
-      <c r="E264" s="3" t="inlineStr">
-        <is>
-          <t>Mike Gesicki</t>
-        </is>
-      </c>
-      <c r="F264" s="3" t="inlineStr">
-        <is>
-          <t>CIN (6)</t>
-        </is>
-      </c>
-      <c r="G264" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="6" t="inlineStr">
-        <is>
-          <t>RB88</t>
-        </is>
-      </c>
-      <c r="B265" s="3" t="n">
-        <v>301</v>
-      </c>
-      <c r="C265" s="5" t="n">
-        <v>316</v>
-      </c>
-      <c r="D265" s="3" t="inlineStr"/>
-      <c r="E265" s="3" t="inlineStr">
-        <is>
-          <t>Kendre Miller</t>
-        </is>
-      </c>
-      <c r="F265" s="3" t="inlineStr">
-        <is>
-          <t>NO (8)</t>
-        </is>
-      </c>
-      <c r="G265" s="3" t="inlineStr">
+    <row r="266">
+      <c r="A266" s="6" t="inlineStr">
+        <is>
+          <t>RB90</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="C266" s="5" t="n">
+        <v>311</v>
+      </c>
+      <c r="D266" s="3" t="inlineStr"/>
+      <c r="E266" s="3" t="inlineStr">
+        <is>
+          <t>Najee Harris</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>LAC (7)</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr">
         <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="10" t="inlineStr">
-        <is>
-          <t>QB35</t>
-        </is>
-      </c>
-      <c r="B266" s="3" t="n">
-        <v>302</v>
-      </c>
-      <c r="C266" s="5" t="n">
-        <v>252</v>
-      </c>
-      <c r="D266" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="E266" s="3" t="inlineStr">
-        <is>
-          <t>Kirk Cousins</t>
-        </is>
-      </c>
-      <c r="F266" s="3" t="inlineStr">
-        <is>
-          <t>LV (13)</t>
-        </is>
-      </c>
-      <c r="G266" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>RB90</t>
+          <t>RB91</t>
         </is>
       </c>
       <c r="B267" s="3" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C267" s="5" t="n">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="D267" s="3" t="inlineStr"/>
       <c r="E267" s="3" t="inlineStr">
         <is>
-          <t>Najee Harris</t>
+          <t>Adam Randall</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>BAL (13)</t>
         </is>
       </c>
       <c r="G267" s="3" t="inlineStr">
@@ -8741,21 +8741,23 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="6" t="inlineStr">
-        <is>
-          <t>RB91</t>
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>WR108</t>
         </is>
       </c>
       <c r="B268" s="3" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>297</v>
-      </c>
-      <c r="D268" s="3" t="inlineStr"/>
+        <v>201</v>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>200</v>
+      </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
-          <t>Adam Randall</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="F268" s="3" t="inlineStr">
@@ -8765,91 +8767,89 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>RB93</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="n">
+        <v>309</v>
+      </c>
+      <c r="C269" s="5" t="n">
+        <v>314</v>
+      </c>
+      <c r="D269" s="3" t="inlineStr"/>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>Trevor Etienne</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="inlineStr">
+        <is>
+          <t>CAR (5)</t>
+        </is>
+      </c>
+      <c r="G269" s="3" t="inlineStr">
+        <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
-        <is>
-          <t>WR108</t>
-        </is>
-      </c>
-      <c r="B269" s="3" t="n">
-        <v>306</v>
-      </c>
-      <c r="C269" s="5" t="n">
-        <v>201</v>
-      </c>
-      <c r="D269" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="E269" s="3" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
-      <c r="F269" s="3" t="inlineStr">
-        <is>
-          <t>BAL (13)</t>
-        </is>
-      </c>
-      <c r="G269" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
     <row r="270">
-      <c r="A270" s="6" t="inlineStr">
-        <is>
-          <t>RB93</t>
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>WR109</t>
         </is>
       </c>
       <c r="B270" s="3" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>Trevor Etienne</t>
+          <t>Isaiah Bond</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>CAR (5)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>WR109</t>
+          <t>WR110</t>
         </is>
       </c>
       <c r="B271" s="3" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>Isaiah Bond</t>
+          <t>Skyler Bell</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
@@ -8859,235 +8859,235 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="inlineStr">
-        <is>
-          <t>WR110</t>
+      <c r="A272" s="8" t="inlineStr">
+        <is>
+          <t>TE38</t>
         </is>
       </c>
       <c r="B272" s="3" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>291</v>
+        <v>339</v>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>Skyler Bell</t>
+          <t>Jake Tonges</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="8" t="inlineStr">
-        <is>
-          <t>TE38</t>
+      <c r="A273" s="6" t="inlineStr">
+        <is>
+          <t>RB95</t>
         </is>
       </c>
       <c r="B273" s="3" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>342</v>
+        <v>288</v>
       </c>
       <c r="D273" s="3" t="inlineStr"/>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>Jake Tonges</t>
+          <t>Tahj Brooks</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>CIN (6)</t>
         </is>
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>WR111</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="n">
+        <v>316</v>
+      </c>
+      <c r="C274" s="5" t="n">
+        <v>254</v>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>Andrei Iosivas</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="inlineStr">
+        <is>
+          <t>CIN (6)</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="6" t="inlineStr">
+        <is>
+          <t>RB96</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="n">
+        <v>317</v>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>292</v>
+      </c>
+      <c r="D275" s="3" t="inlineStr"/>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>Jarquez Hunter</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>LAR (11)</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="8" t="inlineStr">
+        <is>
+          <t>TE39</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="n">
+        <v>322</v>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>282</v>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>271</v>
+      </c>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>Darnell Washington</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>PIT (9)</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="6" t="inlineStr">
-        <is>
-          <t>RB95</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="n">
-        <v>314</v>
-      </c>
-      <c r="C274" s="5" t="n">
-        <v>298</v>
-      </c>
-      <c r="D274" s="3" t="inlineStr"/>
-      <c r="E274" s="3" t="inlineStr">
-        <is>
-          <t>Tahj Brooks</t>
-        </is>
-      </c>
-      <c r="F274" s="3" t="inlineStr">
-        <is>
-          <t>CIN (6)</t>
-        </is>
-      </c>
-      <c r="G274" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
-        <is>
-          <t>WR111</t>
-        </is>
-      </c>
-      <c r="B275" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="C275" s="5" t="n">
-        <v>253</v>
-      </c>
-      <c r="D275" s="3" t="n">
-        <v>263</v>
-      </c>
-      <c r="E275" s="3" t="inlineStr">
-        <is>
-          <t>Andrei Iosivas</t>
-        </is>
-      </c>
-      <c r="F275" s="3" t="inlineStr">
-        <is>
-          <t>CIN (6)</t>
-        </is>
-      </c>
-      <c r="G275" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="6" t="inlineStr">
-        <is>
-          <t>RB96</t>
-        </is>
-      </c>
-      <c r="B276" s="3" t="n">
-        <v>317</v>
-      </c>
-      <c r="C276" s="5" t="n">
-        <v>341</v>
-      </c>
-      <c r="D276" s="3" t="inlineStr"/>
-      <c r="E276" s="3" t="inlineStr">
-        <is>
-          <t>Jarquez Hunter</t>
-        </is>
-      </c>
-      <c r="F276" s="3" t="inlineStr">
-        <is>
-          <t>LAR (11)</t>
-        </is>
-      </c>
-      <c r="G276" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
     <row r="277">
-      <c r="A277" s="8" t="inlineStr">
-        <is>
-          <t>TE39</t>
+      <c r="A277" s="10" t="inlineStr">
+        <is>
+          <t>QB36</t>
         </is>
       </c>
       <c r="B277" s="3" t="n">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>282</v>
-      </c>
-      <c r="D277" s="3" t="n">
-        <v>271</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="D277" s="3" t="inlineStr"/>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>Darnell Washington</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>PIT (9)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="10" t="inlineStr">
-        <is>
-          <t>QB36</t>
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>WR114</t>
         </is>
       </c>
       <c r="B278" s="3" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C278" s="5" t="n">
-        <v>365</v>
-      </c>
-      <c r="D278" s="3" t="inlineStr"/>
+        <v>283</v>
+      </c>
+      <c r="D278" s="3" t="n">
+        <v>267</v>
+      </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Luke McCaffrey</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>WR114</t>
+          <t>WR116</t>
         </is>
       </c>
       <c r="B279" s="3" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>283</v>
-      </c>
-      <c r="D279" s="3" t="n">
-        <v>267</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="D279" s="3" t="inlineStr"/>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>Luke McCaffrey</t>
+          <t>Jahan Dotson</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>ATL (11)</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -9099,24 +9099,24 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>WR116</t>
+          <t>WR117</t>
         </is>
       </c>
       <c r="B280" s="3" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>265</v>
+        <v>352</v>
       </c>
       <c r="D280" s="3" t="inlineStr"/>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>Jalen Royals</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>ATL (11)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -9126,81 +9126,83 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="inlineStr">
-        <is>
-          <t>WR117</t>
+      <c r="A281" s="8" t="inlineStr">
+        <is>
+          <t>TE40</t>
         </is>
       </c>
       <c r="B281" s="3" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C281" s="5" t="n">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="D281" s="3" t="inlineStr"/>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>Jalen Royals</t>
+          <t>Max Klare</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>KC (5)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="8" t="inlineStr">
-        <is>
-          <t>TE40</t>
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>WR118</t>
         </is>
       </c>
       <c r="B282" s="3" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C282" s="5" t="n">
-        <v>367</v>
-      </c>
-      <c r="D282" s="3" t="inlineStr"/>
+        <v>223</v>
+      </c>
+      <c r="D282" s="3" t="n">
+        <v>223</v>
+      </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>Max Klare</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>WR118</t>
+          <t>WR120</t>
         </is>
       </c>
       <c r="B283" s="3" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C283" s="5" t="n">
-        <v>231</v>
+        <v>291</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>223</v>
+        <v>278</v>
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>Caleb Douglas</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
@@ -9217,26 +9219,24 @@
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>WR120</t>
+          <t>WR122</t>
         </is>
       </c>
       <c r="B284" s="3" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>295</v>
-      </c>
-      <c r="D284" s="3" t="n">
-        <v>278</v>
-      </c>
+        <v>348</v>
+      </c>
+      <c r="D284" s="3" t="inlineStr"/>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Joshua Palmer</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -9246,55 +9246,55 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="inlineStr">
-        <is>
-          <t>WR122</t>
+      <c r="A285" s="8" t="inlineStr">
+        <is>
+          <t>TE41</t>
         </is>
       </c>
       <c r="B285" s="3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="D285" s="3" t="inlineStr"/>
       <c r="E285" s="3" t="inlineStr">
         <is>
-          <t>Joshua Palmer</t>
+          <t>Michael Mayer</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="8" t="inlineStr">
         <is>
-          <t>TE41</t>
+          <t>TE42</t>
         </is>
       </c>
       <c r="B286" s="3" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="D286" s="3" t="inlineStr"/>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>Michael Mayer</t>
+          <t>Elijah Arroyo</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -9306,24 +9306,24 @@
     <row r="287">
       <c r="A287" s="8" t="inlineStr">
         <is>
-          <t>TE42</t>
+          <t>TE43</t>
         </is>
       </c>
       <c r="B287" s="3" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>358</v>
+        <v>312</v>
       </c>
       <c r="D287" s="3" t="inlineStr"/>
       <c r="E287" s="3" t="inlineStr">
         <is>
-          <t>Elijah Arroyo</t>
+          <t>Tyler Higbee</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -9333,31 +9333,31 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="8" t="inlineStr">
-        <is>
-          <t>TE43</t>
+      <c r="A288" s="10" t="inlineStr">
+        <is>
+          <t>QB37</t>
         </is>
       </c>
       <c r="B288" s="3" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>308</v>
+        <v>365</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Tyler Higbee</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
@@ -9400,7 +9400,7 @@
         <v>348</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D290" s="3" t="inlineStr"/>
       <c r="E290" s="3" t="inlineStr">
@@ -9429,7 +9429,7 @@
         <v>349</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
@@ -9458,7 +9458,7 @@
         <v>350</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
@@ -9487,7 +9487,7 @@
         <v>351</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr">
@@ -9516,7 +9516,7 @@
         <v>360</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
@@ -9536,57 +9536,57 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="6" t="inlineStr">
-        <is>
-          <t>RB105</t>
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>WR130</t>
         </is>
       </c>
       <c r="B295" s="3" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>309</v>
-      </c>
-      <c r="D295" s="3" t="inlineStr"/>
+        <v>335</v>
+      </c>
+      <c r="D295" s="3" t="n">
+        <v>293</v>
+      </c>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>Nick Chubb</t>
+          <t>Treylon Burks</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>FA ()</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>WR130</t>
+          <t>WR133</t>
         </is>
       </c>
       <c r="B296" s="3" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>338</v>
-      </c>
-      <c r="D296" s="3" t="n">
-        <v>293</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="D296" s="3" t="inlineStr"/>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>Treylon Burks</t>
+          <t>Savion Williams</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>GB (11)</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -9596,234 +9596,205 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="inlineStr">
-        <is>
-          <t>WR133</t>
+      <c r="A297" s="8" t="inlineStr">
+        <is>
+          <t>TE49</t>
         </is>
       </c>
       <c r="B297" s="3" t="n">
+        <v>373</v>
+      </c>
+      <c r="C297" s="5" t="n">
         <v>367</v>
-      </c>
-      <c r="C297" s="5" t="n">
-        <v>361</v>
       </c>
       <c r="D297" s="3" t="inlineStr"/>
       <c r="E297" s="3" t="inlineStr">
         <is>
-          <t>Savion Williams</t>
+          <t>Noah Fant</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>GB (11)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="8" t="inlineStr">
-        <is>
-          <t>TE49</t>
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>RB107</t>
         </is>
       </c>
       <c r="B298" s="3" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>368</v>
+        <v>347</v>
       </c>
       <c r="D298" s="3" t="inlineStr"/>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>Noah Fant</t>
+          <t>Raheim Sanders</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="6" t="inlineStr">
-        <is>
-          <t>RB107</t>
+      <c r="A299" s="8" t="inlineStr">
+        <is>
+          <t>TE50</t>
         </is>
       </c>
       <c r="B299" s="3" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c r="D299" s="3" t="inlineStr"/>
       <c r="E299" s="3" t="inlineStr">
         <is>
-          <t>Raheim Sanders</t>
+          <t>Eli Raridon</t>
         </is>
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="8" t="inlineStr">
-        <is>
-          <t>TE50</t>
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>WR138</t>
         </is>
       </c>
       <c r="B300" s="3" t="n">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C300" s="5" t="n">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="D300" s="3" t="inlineStr"/>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>Eli Raridon</t>
+          <t>Zavion Thomas</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>CHI (10)</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="inlineStr">
-        <is>
-          <t>WR138</t>
+      <c r="A301" s="6" t="inlineStr">
+        <is>
+          <t>RB109</t>
         </is>
       </c>
       <c r="B301" s="3" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C301" s="5" t="n">
-        <v>362</v>
+        <v>321</v>
       </c>
       <c r="D301" s="3" t="inlineStr"/>
       <c r="E301" s="3" t="inlineStr">
         <is>
-          <t>Zavion Thomas</t>
+          <t>Phil Mafah</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>CHI (10)</t>
+          <t>DAL (14)</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="6" t="inlineStr">
-        <is>
-          <t>RB109</t>
+      <c r="A302" s="8" t="inlineStr">
+        <is>
+          <t>TE52</t>
         </is>
       </c>
       <c r="B302" s="3" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>319</v>
-      </c>
-      <c r="D302" s="3" t="inlineStr"/>
+        <v>318</v>
+      </c>
+      <c r="D302" s="3" t="n">
+        <v>301</v>
+      </c>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>Phil Mafah</t>
+          <t>Erick All</t>
         </is>
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
-          <t>DAL (14)</t>
+          <t>CIN (6)</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="8" t="inlineStr">
-        <is>
-          <t>TE52</t>
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>WR142</t>
         </is>
       </c>
       <c r="B303" s="3" t="n">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>318</v>
-      </c>
-      <c r="D303" s="3" t="n">
-        <v>301</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="D303" s="3" t="inlineStr"/>
       <c r="E303" s="3" t="inlineStr">
         <is>
-          <t>Erick All</t>
+          <t>Jordan Whittington</t>
         </is>
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>CIN (6)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>WR142</t>
-        </is>
-      </c>
-      <c r="B304" s="3" t="n">
-        <v>395</v>
-      </c>
-      <c r="C304" s="5" t="n">
-        <v>364</v>
-      </c>
-      <c r="D304" s="3" t="inlineStr"/>
-      <c r="E304" s="3" t="inlineStr">
-        <is>
-          <t>Jordan Whittington</t>
-        </is>
-      </c>
-      <c r="F304" s="3" t="inlineStr">
-        <is>
-          <t>LAR (11)</t>
-        </is>
-      </c>
-      <c r="G304" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -578,7 +578,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>12</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>19</v>
@@ -885,10 +885,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         <v>13</v>
       </c>
       <c r="C14" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D14" s="3" t="n">
         <v>23</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>22</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>21</v>
@@ -1008,11 +1008,11 @@
       <c r="B17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>27</v>
+      <c r="C17" s="9" t="n">
+        <v>41</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>11</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -1102,10 +1102,10 @@
         <v>19</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>43</v>
@@ -1229,7 +1229,7 @@
         <v>37</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>29</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>28</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>30</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>55</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -1536,10 +1536,10 @@
         <v>33</v>
       </c>
       <c r="C34" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="D34" s="3" t="n">
         <v>61</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>60</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1566,8 +1566,8 @@
       <c r="B35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="C35" s="4" t="n">
-        <v>42</v>
+      <c r="C35" s="5" t="n">
+        <v>36</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>42</v>
@@ -1629,10 +1629,10 @@
         <v>36</v>
       </c>
       <c r="C37" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="D37" s="3" t="n">
         <v>20</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>23</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -1659,11 +1659,11 @@
       <c r="B38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="C38" s="5" t="n">
-        <v>41</v>
+      <c r="C38" s="7" t="n">
+        <v>27</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
         <v>38</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1753,10 +1753,10 @@
         <v>40</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>43</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         <v>43</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>44</v>
       </c>
       <c r="C45" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="D45" s="3" t="n">
         <v>60</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>59</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>40</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -1938,11 +1938,11 @@
       <c r="B47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="C47" s="4" t="n">
-        <v>51</v>
+      <c r="C47" s="5" t="n">
+        <v>49</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>39</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>38</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D52" s="3" t="n">
         <v>46</v>
@@ -2128,7 +2128,7 @@
         <v>56</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>47</v>
@@ -2311,10 +2311,10 @@
         <v>58</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>48</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>53</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>52</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>54</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>83</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>81</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>69</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D70" s="3" t="n">
         <v>64</v>
@@ -2683,7 +2683,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>66</v>
@@ -2717,7 +2717,7 @@
         <v>71</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -2745,10 +2745,10 @@
         <v>72</v>
       </c>
       <c r="C73" s="9" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
         <v>74</v>
       </c>
       <c r="C75" s="9" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>79</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>78</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>77</v>
@@ -2993,10 +2993,10 @@
         <v>80</v>
       </c>
       <c r="C81" s="4" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
@@ -3085,11 +3085,11 @@
       <c r="B84" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="C84" s="9" t="n">
-        <v>97</v>
+      <c r="C84" s="4" t="n">
+        <v>94</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>98</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         <v>87</v>
       </c>
       <c r="C88" s="9" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
@@ -3241,10 +3241,10 @@
         <v>88</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
@@ -3272,10 +3272,10 @@
         <v>89</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
@@ -3303,10 +3303,10 @@
         <v>90</v>
       </c>
       <c r="C91" s="4" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>112</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>50</v>
@@ -3399,7 +3399,7 @@
         <v>158</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>113</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>92</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="D98" s="3" t="n">
         <v>132</v>
@@ -3551,10 +3551,10 @@
         <v>98</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>129</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
@@ -3644,10 +3644,10 @@
         <v>102</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
         <v>103</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>104</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D104" s="3" t="n">
         <v>84</v>
@@ -3737,7 +3737,7 @@
         <v>105</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>154</v>
@@ -3768,10 +3768,10 @@
         <v>106</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>128</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>114</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
@@ -3891,11 +3891,11 @@
       <c r="B110" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="C110" s="7" t="n">
-        <v>99</v>
+      <c r="C110" s="11" t="n">
+        <v>100</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -3923,10 +3923,10 @@
         <v>111</v>
       </c>
       <c r="C111" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="D111" s="3" t="n">
         <v>119</v>
-      </c>
-      <c r="D111" s="3" t="n">
-        <v>123</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
@@ -3954,10 +3954,10 @@
         <v>112</v>
       </c>
       <c r="C112" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="D112" s="3" t="n">
         <v>106</v>
-      </c>
-      <c r="D112" s="3" t="n">
-        <v>104</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>90</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
         <v>114</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
@@ -4046,11 +4046,11 @@
       <c r="B115" s="3" t="n">
         <v>115</v>
       </c>
-      <c r="C115" s="7" t="n">
+      <c r="C115" s="11" t="n">
+        <v>108</v>
+      </c>
+      <c r="D115" s="3" t="n">
         <v>103</v>
-      </c>
-      <c r="D115" s="3" t="n">
-        <v>112</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>134</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>115</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>130</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
@@ -4170,11 +4170,11 @@
       <c r="B119" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="C119" s="7" t="n">
-        <v>108</v>
+      <c r="C119" s="5" t="n">
+        <v>119</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         <v>120</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
@@ -4233,10 +4233,10 @@
         <v>121</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
@@ -4295,7 +4295,7 @@
         <v>123</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>117</v>
@@ -4356,11 +4356,11 @@
       <c r="B125" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="C125" s="7" t="n">
-        <v>102</v>
+      <c r="C125" s="11" t="n">
+        <v>116</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>123</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>107</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>91</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>144</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
@@ -4511,11 +4511,11 @@
       <c r="B130" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="C130" s="11" t="n">
-        <v>126</v>
+      <c r="C130" s="5" t="n">
+        <v>138</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>147</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
@@ -4574,10 +4574,10 @@
         <v>132</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>77</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>145</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>136</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="D136" s="3" t="n">
         <v>159</v>
@@ -4791,10 +4791,10 @@
         <v>139</v>
       </c>
       <c r="C139" s="7" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>140</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D140" s="3" t="n">
         <v>195</v>
@@ -4884,7 +4884,7 @@
         <v>142</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D142" s="3" t="n">
         <v>194</v>
@@ -4915,7 +4915,7 @@
         <v>143</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>173</v>
@@ -4946,7 +4946,7 @@
         <v>144</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D144" s="3" t="n">
         <v>189</v>
@@ -5008,10 +5008,10 @@
         <v>146</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
@@ -5101,10 +5101,10 @@
         <v>149</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>234</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>158</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>212</v>
@@ -5380,10 +5380,10 @@
         <v>159</v>
       </c>
       <c r="C158" s="7" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
@@ -5473,10 +5473,10 @@
         <v>162</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>224</v>
+        <v>254</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
@@ -5503,8 +5503,8 @@
       <c r="B162" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="C162" s="5" t="n">
-        <v>178</v>
+      <c r="C162" s="4" t="n">
+        <v>197</v>
       </c>
       <c r="D162" s="3" t="n">
         <v>172</v>
@@ -5569,7 +5569,7 @@
         <v>207</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>148</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
@@ -5628,10 +5628,10 @@
         <v>169</v>
       </c>
       <c r="C166" s="4" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>192</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
@@ -5752,10 +5752,10 @@
         <v>175</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
@@ -5814,10 +5814,10 @@
         <v>177</v>
       </c>
       <c r="C172" s="7" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>269</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>237</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>186</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D176" s="3" t="n">
         <v>277</v>
@@ -5968,11 +5968,11 @@
       <c r="B177" s="3" t="n">
         <v>187</v>
       </c>
-      <c r="C177" s="5" t="n">
-        <v>202</v>
+      <c r="C177" s="4" t="n">
+        <v>225</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>188</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>192</v>
       </c>
       <c r="C180" s="4" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D180" s="3" t="n">
         <v>265</v>
@@ -6093,7 +6093,7 @@
         <v>194</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D181" s="3" t="n">
         <v>253</v>
@@ -6123,8 +6123,8 @@
       <c r="B182" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="C182" s="11" t="n">
-        <v>162</v>
+      <c r="C182" s="5" t="n">
+        <v>176</v>
       </c>
       <c r="D182" s="3" t="n">
         <v>187</v>
@@ -6310,7 +6310,7 @@
         <v>204</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D188" s="3" t="n">
         <v>211</v>
@@ -6340,11 +6340,11 @@
       <c r="B189" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C189" s="4" t="n">
-        <v>236</v>
+      <c r="C189" s="5" t="n">
+        <v>201</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>246</v>
+        <v>215</v>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>258</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
         <v>212</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D193" s="3" t="n">
         <v>193</v>
@@ -6496,7 +6496,7 @@
         <v>213</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D194" s="3" t="n">
         <v>279</v>
@@ -6527,7 +6527,7 @@
         <v>217</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D195" s="3" t="n">
         <v>262</v>
@@ -6561,7 +6561,7 @@
         <v>232</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
@@ -6589,10 +6589,10 @@
         <v>221</v>
       </c>
       <c r="C197" s="4" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>239</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
@@ -6711,10 +6711,10 @@
         <v>225</v>
       </c>
       <c r="C201" s="11" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
@@ -6745,7 +6745,7 @@
         <v>262</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>230</v>
       </c>
       <c r="C203" s="5" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D203" s="3" t="n">
         <v>201</v>
@@ -6804,7 +6804,7 @@
         <v>232</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D204" s="3" t="n">
         <v>252</v>
@@ -6931,7 +6931,7 @@
         <v>256</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
@@ -6959,10 +6959,10 @@
         <v>238</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
@@ -7021,10 +7021,10 @@
         <v>240</v>
       </c>
       <c r="C211" s="5" t="n">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>219</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>245</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D216" s="3" t="n">
         <v>158</v>
@@ -7241,7 +7241,7 @@
         <v>220</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>249</v>
       </c>
       <c r="C219" s="5" t="n">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="D219" s="3" t="n">
         <v>288</v>
@@ -7300,7 +7300,7 @@
         <v>250</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D220" s="3" t="inlineStr"/>
       <c r="E220" s="3" t="inlineStr">
@@ -7360,7 +7360,7 @@
         <v>252</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D222" s="3" t="n">
         <v>249</v>
@@ -7391,10 +7391,10 @@
         <v>254</v>
       </c>
       <c r="C223" s="5" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D223" s="3" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>255</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D224" s="3" t="inlineStr"/>
       <c r="E224" s="3" t="inlineStr">
@@ -7451,7 +7451,7 @@
         <v>256</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D225" s="3" t="n">
         <v>294</v>
@@ -7482,7 +7482,7 @@
         <v>257</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D226" s="3" t="n">
         <v>273</v>
@@ -7573,7 +7573,7 @@
         <v>260</v>
       </c>
       <c r="C229" s="5" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D229" s="3" t="n">
         <v>291</v>
@@ -7604,7 +7604,7 @@
         <v>261</v>
       </c>
       <c r="C230" s="4" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D230" s="3" t="n">
         <v>292</v>
@@ -7635,7 +7635,7 @@
         <v>262</v>
       </c>
       <c r="C231" s="11" t="n">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="D231" s="3" t="n">
         <v>188</v>
@@ -7697,7 +7697,7 @@
         <v>265</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="D233" s="3" t="n">
         <v>290</v>
@@ -7731,7 +7731,7 @@
         <v>241</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
@@ -7759,10 +7759,10 @@
         <v>267</v>
       </c>
       <c r="C235" s="5" t="n">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D235" s="3" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>270</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="D238" s="3" t="n">
         <v>289</v>
@@ -7881,7 +7881,7 @@
         <v>271</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="D239" s="3" t="n">
         <v>287</v>
@@ -7912,7 +7912,7 @@
         <v>272</v>
       </c>
       <c r="C240" s="5" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D240" s="3" t="n">
         <v>286</v>
@@ -7972,7 +7972,7 @@
         <v>274</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D242" s="3" t="inlineStr"/>
       <c r="E242" s="3" t="inlineStr">
@@ -8001,7 +8001,7 @@
         <v>275</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D243" s="3" t="inlineStr"/>
       <c r="E243" s="3" t="inlineStr">
@@ -8061,7 +8061,7 @@
         <v>277</v>
       </c>
       <c r="C245" s="5" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D245" s="3" t="n">
         <v>254</v>
@@ -8095,7 +8095,7 @@
         <v>193</v>
       </c>
       <c r="D246" s="3" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>281</v>
       </c>
       <c r="C248" s="4" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D248" s="3" t="inlineStr"/>
       <c r="E248" s="3" t="inlineStr">
@@ -8212,7 +8212,7 @@
         <v>283</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D250" s="3" t="n">
         <v>276</v>
@@ -8243,7 +8243,7 @@
         <v>284</v>
       </c>
       <c r="C251" s="4" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D251" s="3" t="inlineStr"/>
       <c r="E251" s="3" t="inlineStr">
@@ -8272,7 +8272,7 @@
         <v>285</v>
       </c>
       <c r="C252" s="5" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D252" s="3" t="n">
         <v>300</v>
@@ -8303,7 +8303,7 @@
         <v>288</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D253" s="3" t="inlineStr"/>
       <c r="E253" s="3" t="inlineStr">
@@ -8332,7 +8332,7 @@
         <v>289</v>
       </c>
       <c r="C254" s="5" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D254" s="3" t="inlineStr"/>
       <c r="E254" s="3" t="inlineStr">
@@ -8361,7 +8361,7 @@
         <v>290</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D255" s="3" t="n">
         <v>250</v>
@@ -8392,7 +8392,7 @@
         <v>292</v>
       </c>
       <c r="C256" s="5" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D256" s="3" t="inlineStr"/>
       <c r="E256" s="3" t="inlineStr">
@@ -8421,7 +8421,7 @@
         <v>293</v>
       </c>
       <c r="C257" s="5" t="n">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="D257" s="3" t="n">
         <v>213</v>
@@ -8452,7 +8452,7 @@
         <v>294</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
@@ -8481,7 +8481,7 @@
         <v>296</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
@@ -8573,7 +8573,7 @@
         <v>252</v>
       </c>
       <c r="D262" s="3" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>304</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D266" s="3" t="inlineStr"/>
       <c r="E266" s="3" t="inlineStr">
@@ -8721,7 +8721,7 @@
         <v>305</v>
       </c>
       <c r="C267" s="5" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D267" s="3" t="inlineStr"/>
       <c r="E267" s="3" t="inlineStr">
@@ -8750,7 +8750,7 @@
         <v>306</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D268" s="3" t="n">
         <v>200</v>
@@ -8810,7 +8810,7 @@
         <v>310</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
@@ -8839,7 +8839,7 @@
         <v>311</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr">
@@ -8897,7 +8897,7 @@
         <v>314</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="D273" s="3" t="inlineStr"/>
       <c r="E273" s="3" t="inlineStr">
@@ -8926,7 +8926,7 @@
         <v>316</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D274" s="3" t="n">
         <v>263</v>
@@ -8957,7 +8957,7 @@
         <v>317</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>292</v>
+        <v>322</v>
       </c>
       <c r="D275" s="3" t="inlineStr"/>
       <c r="E275" s="3" t="inlineStr">
@@ -9017,7 +9017,7 @@
         <v>327</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D277" s="3" t="inlineStr"/>
       <c r="E277" s="3" t="inlineStr">
@@ -9077,7 +9077,7 @@
         <v>330</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D279" s="3" t="inlineStr"/>
       <c r="E279" s="3" t="inlineStr">
@@ -9106,7 +9106,7 @@
         <v>331</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D280" s="3" t="inlineStr"/>
       <c r="E280" s="3" t="inlineStr">
@@ -9164,10 +9164,10 @@
         <v>333</v>
       </c>
       <c r="C282" s="5" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D282" s="3" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>337</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D284" s="3" t="inlineStr"/>
       <c r="E284" s="3" t="inlineStr">
@@ -9255,7 +9255,7 @@
         <v>338</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D285" s="3" t="inlineStr"/>
       <c r="E285" s="3" t="inlineStr">
@@ -9284,7 +9284,7 @@
         <v>340</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D286" s="3" t="inlineStr"/>
       <c r="E286" s="3" t="inlineStr">
@@ -9313,7 +9313,7 @@
         <v>341</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D287" s="3" t="inlineStr"/>
       <c r="E287" s="3" t="inlineStr">
@@ -9342,7 +9342,7 @@
         <v>342</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
@@ -9371,7 +9371,7 @@
         <v>344</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr">
@@ -9429,7 +9429,7 @@
         <v>349</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
@@ -9487,7 +9487,7 @@
         <v>351</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr">
@@ -9516,7 +9516,7 @@
         <v>360</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
@@ -9545,7 +9545,7 @@
         <v>363</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D295" s="3" t="n">
         <v>293</v>
@@ -9663,7 +9663,7 @@
         <v>377</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D299" s="3" t="inlineStr"/>
       <c r="E299" s="3" t="inlineStr">
@@ -9692,7 +9692,7 @@
         <v>383</v>
       </c>
       <c r="C300" s="5" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D300" s="3" t="inlineStr"/>
       <c r="E300" s="3" t="inlineStr">
@@ -9721,7 +9721,7 @@
         <v>386</v>
       </c>
       <c r="C301" s="5" t="n">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D301" s="3" t="inlineStr"/>
       <c r="E301" s="3" t="inlineStr">
@@ -9750,7 +9750,7 @@
         <v>387</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D302" s="3" t="n">
         <v>301</v>
@@ -9781,7 +9781,7 @@
         <v>395</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D303" s="3" t="inlineStr"/>
       <c r="E303" s="3" t="inlineStr">

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -857,7 +857,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>23</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>22</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         <v>14</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>21</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>18</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
         <v>24</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>40</v>
@@ -1381,7 +1381,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>39</v>
@@ -1539,7 +1539,7 @@
         <v>65</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
         <v>35</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>19</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>34</v>
@@ -1722,7 +1722,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>16</v>
@@ -1753,7 +1753,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>37</v>
@@ -1845,8 +1845,8 @@
       <c r="B44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="C44" s="4" t="n">
-        <v>51</v>
+      <c r="C44" s="9" t="n">
+        <v>57</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>56</v>
@@ -1880,7 +1880,7 @@
         <v>61</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -2031,11 +2031,11 @@
       <c r="B50" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="C50" s="4" t="n">
-        <v>58</v>
+      <c r="C50" s="5" t="n">
+        <v>51</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>51</v>
@@ -2094,10 +2094,10 @@
         <v>51</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -2156,10 +2156,10 @@
         <v>53</v>
       </c>
       <c r="C54" s="4" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>66</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
         <v>56</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>65</v>
@@ -2314,7 +2314,7 @@
         <v>60</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -2342,10 +2342,10 @@
         <v>59</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>61</v>
       </c>
       <c r="C62" s="7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>52</v>
@@ -2465,11 +2465,11 @@
       <c r="B64" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="C64" s="4" t="n">
-        <v>75</v>
+      <c r="C64" s="9" t="n">
+        <v>96</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>53</v>
@@ -2559,10 +2559,10 @@
         <v>66</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>83</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>81</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -2651,8 +2651,8 @@
       <c r="B70" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="C70" s="11" t="n">
-        <v>63</v>
+      <c r="C70" s="7" t="n">
+        <v>62</v>
       </c>
       <c r="D70" s="3" t="n">
         <v>64</v>
@@ -2683,7 +2683,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>66</v>
@@ -2717,7 +2717,7 @@
         <v>71</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>122</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         <v>73</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
         <v>74</v>
       </c>
       <c r="C75" s="9" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>67</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>105</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         <v>77</v>
       </c>
       <c r="C78" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="D78" s="3" t="n">
         <v>79</v>
-      </c>
-      <c r="D78" s="3" t="n">
-        <v>81</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>72</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -2993,10 +2993,10 @@
         <v>80</v>
       </c>
       <c r="C81" s="4" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
@@ -3054,11 +3054,11 @@
       <c r="B83" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="C83" s="5" t="n">
-        <v>80</v>
+      <c r="C83" s="9" t="n">
+        <v>127</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -3085,11 +3085,11 @@
       <c r="B84" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="C84" s="4" t="n">
-        <v>94</v>
+      <c r="C84" s="9" t="n">
+        <v>121</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>74</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
@@ -3148,10 +3148,10 @@
         <v>85</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -3178,11 +3178,11 @@
       <c r="B87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="C87" s="7" t="n">
-        <v>59</v>
+      <c r="C87" s="5" t="n">
+        <v>77</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         <v>87</v>
       </c>
       <c r="C88" s="9" t="n">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>70</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
@@ -3302,11 +3302,11 @@
       <c r="B91" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="C91" s="4" t="n">
-        <v>97</v>
+      <c r="C91" s="5" t="n">
+        <v>86</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>112</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -3396,10 +3396,10 @@
         <v>93</v>
       </c>
       <c r="C94" s="9" t="n">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>113</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
@@ -3458,10 +3458,10 @@
         <v>95</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
@@ -3489,10 +3489,10 @@
         <v>96</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>109</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>94</v>
@@ -3585,7 +3585,7 @@
         <v>129</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>104</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
@@ -3644,10 +3644,10 @@
         <v>102</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>111</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
@@ -3706,10 +3706,10 @@
         <v>104</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
@@ -3768,10 +3768,10 @@
         <v>106</v>
       </c>
       <c r="C106" s="5" t="n">
+        <v>84</v>
+      </c>
+      <c r="D106" s="3" t="n">
         <v>86</v>
-      </c>
-      <c r="D106" s="3" t="n">
-        <v>88</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         <v>107</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
@@ -3830,10 +3830,10 @@
         <v>108</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>114</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
@@ -3891,8 +3891,8 @@
       <c r="B110" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="C110" s="11" t="n">
-        <v>100</v>
+      <c r="C110" s="7" t="n">
+        <v>98</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>93</v>
@@ -3926,7 +3926,7 @@
         <v>125</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>93</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>110</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>108</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
@@ -4077,11 +4077,11 @@
       <c r="B116" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="C116" s="9" t="n">
-        <v>134</v>
+      <c r="C116" s="4" t="n">
+        <v>124</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>115</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>130</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>119</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         <v>120</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
@@ -4233,10 +4233,10 @@
         <v>121</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>195</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>103</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
@@ -4326,10 +4326,10 @@
         <v>124</v>
       </c>
       <c r="C124" s="7" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
@@ -4356,11 +4356,11 @@
       <c r="B125" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="C125" s="11" t="n">
-        <v>116</v>
+      <c r="C125" s="7" t="n">
+        <v>102</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
@@ -4387,11 +4387,11 @@
       <c r="B126" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="C126" s="5" t="n">
-        <v>123</v>
+      <c r="C126" s="4" t="n">
+        <v>135</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
         <v>127</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
@@ -4450,10 +4450,10 @@
         <v>128</v>
       </c>
       <c r="C128" s="7" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
@@ -4480,11 +4480,11 @@
       <c r="B129" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="C129" s="5" t="n">
-        <v>144</v>
+      <c r="C129" s="7" t="n">
+        <v>117</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>138</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>147</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>136</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
@@ -4605,10 +4605,10 @@
         <v>133</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>194</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>145</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
@@ -4698,10 +4698,10 @@
         <v>136</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
@@ -4729,10 +4729,10 @@
         <v>137</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>196</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
@@ -4790,11 +4790,11 @@
       <c r="B139" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C139" s="7" t="n">
-        <v>127</v>
+      <c r="C139" s="5" t="n">
+        <v>161</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
@@ -4821,11 +4821,11 @@
       <c r="B140" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="C140" s="5" t="n">
-        <v>208</v>
+      <c r="C140" s="7" t="n">
+        <v>128</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>195</v>
+        <v>152</v>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>156</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
@@ -4884,10 +4884,10 @@
         <v>142</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
@@ -4915,10 +4915,10 @@
         <v>143</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>178</v>
+        <v>204</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>198</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>145</v>
       </c>
       <c r="C145" s="9" t="n">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
@@ -5008,10 +5008,10 @@
         <v>146</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>175</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>191</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
@@ -5100,11 +5100,11 @@
       <c r="B149" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="C149" s="5" t="n">
-        <v>120</v>
+      <c r="C149" s="11" t="n">
+        <v>106</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
@@ -5132,10 +5132,10 @@
         <v>150</v>
       </c>
       <c r="C150" s="4" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>206</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>205</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>200</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>157</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>234</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>146</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         <v>159</v>
       </c>
       <c r="C158" s="7" t="n">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>190</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
@@ -5442,10 +5442,10 @@
         <v>161</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
@@ -5473,10 +5473,10 @@
         <v>162</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>197</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>207</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>148</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
@@ -5628,10 +5628,10 @@
         <v>169</v>
       </c>
       <c r="C166" s="4" t="n">
-        <v>240</v>
+        <v>269</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>189</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>192</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
@@ -5721,10 +5721,10 @@
         <v>174</v>
       </c>
       <c r="C169" s="4" t="n">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
@@ -5752,10 +5752,10 @@
         <v>175</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
@@ -5783,10 +5783,10 @@
         <v>176</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
@@ -5814,10 +5814,10 @@
         <v>177</v>
       </c>
       <c r="C172" s="7" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -5845,10 +5845,10 @@
         <v>178</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>237</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>286</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
@@ -5938,10 +5938,10 @@
         <v>186</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>225</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>188</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>279</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
@@ -6062,10 +6062,10 @@
         <v>192</v>
       </c>
       <c r="C180" s="4" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
@@ -6093,10 +6093,10 @@
         <v>194</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
@@ -6123,11 +6123,11 @@
       <c r="B182" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="C182" s="5" t="n">
-        <v>176</v>
+      <c r="C182" s="11" t="n">
+        <v>163</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>174</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
@@ -6186,10 +6186,10 @@
         <v>197</v>
       </c>
       <c r="C184" s="4" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
@@ -6216,11 +6216,11 @@
       <c r="B185" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="C185" s="7" t="n">
-        <v>159</v>
+      <c r="C185" s="5" t="n">
+        <v>170</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
@@ -6248,10 +6248,10 @@
         <v>201</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
@@ -6278,11 +6278,11 @@
       <c r="B187" s="3" t="n">
         <v>202</v>
       </c>
-      <c r="C187" s="11" t="n">
-        <v>171</v>
+      <c r="C187" s="5" t="n">
+        <v>172</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
@@ -6309,11 +6309,11 @@
       <c r="B188" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="C188" s="5" t="n">
-        <v>204</v>
+      <c r="C188" s="11" t="n">
+        <v>162</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>211</v>
+        <v>159</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
@@ -6341,10 +6341,10 @@
         <v>205</v>
       </c>
       <c r="C189" s="5" t="n">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
@@ -6372,10 +6372,10 @@
         <v>206</v>
       </c>
       <c r="C190" s="4" t="n">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>258</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>173</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
@@ -6465,10 +6465,10 @@
         <v>212</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
@@ -6496,10 +6496,10 @@
         <v>213</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
@@ -6527,10 +6527,10 @@
         <v>217</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>232</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
@@ -6589,10 +6589,10 @@
         <v>221</v>
       </c>
       <c r="C197" s="4" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
@@ -6620,10 +6620,10 @@
         <v>222</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>218</v>
       </c>
       <c r="D199" s="3" t="n">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>224</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="D200" s="3" t="inlineStr"/>
       <c r="E200" s="3" t="inlineStr">
@@ -6710,11 +6710,11 @@
       <c r="B201" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="C201" s="11" t="n">
-        <v>137</v>
+      <c r="C201" s="7" t="n">
+        <v>87</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
@@ -6742,10 +6742,10 @@
         <v>228</v>
       </c>
       <c r="C202" s="5" t="n">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
@@ -6773,10 +6773,10 @@
         <v>230</v>
       </c>
       <c r="C203" s="5" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D203" s="3" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
@@ -6804,10 +6804,10 @@
         <v>232</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D204" s="3" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
@@ -6835,10 +6835,10 @@
         <v>233</v>
       </c>
       <c r="C205" s="4" t="n">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
@@ -6866,10 +6866,10 @@
         <v>234</v>
       </c>
       <c r="C206" s="5" t="n">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
@@ -6897,10 +6897,10 @@
         <v>235</v>
       </c>
       <c r="C207" s="5" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>256</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>221</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>260</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>238</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
@@ -7052,10 +7052,10 @@
         <v>241</v>
       </c>
       <c r="C212" s="4" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>300</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>219</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
@@ -7145,10 +7145,10 @@
         <v>244</v>
       </c>
       <c r="C215" s="4" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D215" s="3" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>245</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="D216" s="3" t="n">
         <v>158</v>
@@ -7210,7 +7210,7 @@
         <v>281</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>220</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>249</v>
       </c>
       <c r="C219" s="5" t="n">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="D219" s="3" t="n">
         <v>288</v>
@@ -7300,7 +7300,7 @@
         <v>250</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="D220" s="3" t="inlineStr"/>
       <c r="E220" s="3" t="inlineStr">
@@ -7332,7 +7332,7 @@
         <v>285</v>
       </c>
       <c r="D221" s="3" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
@@ -7360,10 +7360,10 @@
         <v>252</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D222" s="3" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>233</v>
       </c>
       <c r="D223" s="3" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>255</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D224" s="3" t="inlineStr"/>
       <c r="E224" s="3" t="inlineStr">
@@ -7451,7 +7451,7 @@
         <v>256</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D225" s="3" t="n">
         <v>294</v>
@@ -7482,10 +7482,10 @@
         <v>257</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D226" s="3" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>258</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
@@ -7545,7 +7545,7 @@
         <v>281</v>
       </c>
       <c r="D228" s="3" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>260</v>
       </c>
       <c r="C229" s="5" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D229" s="3" t="n">
         <v>291</v>
@@ -7604,7 +7604,7 @@
         <v>261</v>
       </c>
       <c r="C230" s="4" t="n">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="D230" s="3" t="n">
         <v>292</v>
@@ -7634,11 +7634,11 @@
       <c r="B231" s="3" t="n">
         <v>262</v>
       </c>
-      <c r="C231" s="11" t="n">
-        <v>177</v>
+      <c r="C231" s="5" t="n">
+        <v>203</v>
       </c>
       <c r="D231" s="3" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>261</v>
       </c>
       <c r="D232" s="3" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>265</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="D233" s="3" t="n">
         <v>290</v>
@@ -7731,7 +7731,7 @@
         <v>241</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
@@ -7759,10 +7759,10 @@
         <v>267</v>
       </c>
       <c r="C235" s="5" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D235" s="3" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>268</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D236" s="3" t="inlineStr"/>
       <c r="E236" s="3" t="inlineStr">
@@ -7819,10 +7819,10 @@
         <v>269</v>
       </c>
       <c r="C237" s="5" t="n">
-        <v>293</v>
+        <v>209</v>
       </c>
       <c r="D237" s="3" t="n">
-        <v>285</v>
+        <v>213</v>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>270</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="D238" s="3" t="n">
         <v>289</v>
@@ -7881,7 +7881,7 @@
         <v>271</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>298</v>
+        <v>254</v>
       </c>
       <c r="D239" s="3" t="n">
         <v>287</v>
@@ -7912,7 +7912,7 @@
         <v>272</v>
       </c>
       <c r="C240" s="5" t="n">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="D240" s="3" t="n">
         <v>286</v>
@@ -7943,7 +7943,7 @@
         <v>273</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="D241" s="3" t="inlineStr"/>
       <c r="E241" s="3" t="inlineStr">
@@ -7972,7 +7972,7 @@
         <v>274</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D242" s="3" t="inlineStr"/>
       <c r="E242" s="3" t="inlineStr">
@@ -8001,7 +8001,7 @@
         <v>275</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D243" s="3" t="inlineStr"/>
       <c r="E243" s="3" t="inlineStr">
@@ -8033,7 +8033,7 @@
         <v>275</v>
       </c>
       <c r="D244" s="3" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
@@ -8061,10 +8061,10 @@
         <v>277</v>
       </c>
       <c r="C245" s="5" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D245" s="3" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>193</v>
       </c>
       <c r="D246" s="3" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
@@ -8122,8 +8122,8 @@
       <c r="B247" s="3" t="n">
         <v>280</v>
       </c>
-      <c r="C247" s="5" t="n">
-        <v>320</v>
+      <c r="C247" s="4" t="n">
+        <v>337</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
@@ -8151,8 +8151,8 @@
       <c r="B248" s="3" t="n">
         <v>281</v>
       </c>
-      <c r="C248" s="4" t="n">
-        <v>338</v>
+      <c r="C248" s="5" t="n">
+        <v>293</v>
       </c>
       <c r="D248" s="3" t="inlineStr"/>
       <c r="E248" s="3" t="inlineStr">
@@ -8181,10 +8181,10 @@
         <v>282</v>
       </c>
       <c r="C249" s="5" t="n">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="D249" s="3" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>288</v>
       </c>
       <c r="D250" s="3" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
@@ -8242,8 +8242,8 @@
       <c r="B251" s="3" t="n">
         <v>284</v>
       </c>
-      <c r="C251" s="4" t="n">
-        <v>334</v>
+      <c r="C251" s="5" t="n">
+        <v>312</v>
       </c>
       <c r="D251" s="3" t="inlineStr"/>
       <c r="E251" s="3" t="inlineStr">
@@ -8272,7 +8272,7 @@
         <v>285</v>
       </c>
       <c r="C252" s="5" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D252" s="3" t="n">
         <v>300</v>
@@ -8303,7 +8303,7 @@
         <v>288</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D253" s="3" t="inlineStr"/>
       <c r="E253" s="3" t="inlineStr">
@@ -8332,7 +8332,7 @@
         <v>289</v>
       </c>
       <c r="C254" s="5" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D254" s="3" t="inlineStr"/>
       <c r="E254" s="3" t="inlineStr">
@@ -8361,10 +8361,10 @@
         <v>290</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D255" s="3" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
@@ -8392,7 +8392,7 @@
         <v>292</v>
       </c>
       <c r="C256" s="5" t="n">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="D256" s="3" t="inlineStr"/>
       <c r="E256" s="3" t="inlineStr">
@@ -8421,10 +8421,10 @@
         <v>293</v>
       </c>
       <c r="C257" s="5" t="n">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="D257" s="3" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>294</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
@@ -8481,7 +8481,7 @@
         <v>296</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
@@ -8539,10 +8539,10 @@
         <v>298</v>
       </c>
       <c r="C261" s="5" t="n">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="D261" s="3" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>252</v>
       </c>
       <c r="D262" s="3" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>280</v>
       </c>
       <c r="D263" s="3" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>301</v>
       </c>
       <c r="C264" s="5" t="n">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="D264" s="3" t="inlineStr"/>
       <c r="E264" s="3" t="inlineStr">
@@ -8664,7 +8664,7 @@
         <v>253</v>
       </c>
       <c r="D265" s="3" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>304</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D266" s="3" t="inlineStr"/>
       <c r="E266" s="3" t="inlineStr">
@@ -8721,7 +8721,7 @@
         <v>305</v>
       </c>
       <c r="C267" s="5" t="n">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D267" s="3" t="inlineStr"/>
       <c r="E267" s="3" t="inlineStr">
@@ -8749,11 +8749,11 @@
       <c r="B268" s="3" t="n">
         <v>306</v>
       </c>
-      <c r="C268" s="5" t="n">
-        <v>202</v>
+      <c r="C268" s="11" t="n">
+        <v>199</v>
       </c>
       <c r="D268" s="3" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>309</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D269" s="3" t="inlineStr"/>
       <c r="E269" s="3" t="inlineStr">
@@ -8810,7 +8810,7 @@
         <v>310</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
@@ -8839,7 +8839,7 @@
         <v>311</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr">
@@ -8868,7 +8868,7 @@
         <v>312</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
@@ -8897,7 +8897,7 @@
         <v>314</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>270</v>
+        <v>298</v>
       </c>
       <c r="D273" s="3" t="inlineStr"/>
       <c r="E273" s="3" t="inlineStr">
@@ -8929,7 +8929,7 @@
         <v>255</v>
       </c>
       <c r="D274" s="3" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>317</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>322</v>
+        <v>296</v>
       </c>
       <c r="D275" s="3" t="inlineStr"/>
       <c r="E275" s="3" t="inlineStr">
@@ -8989,7 +8989,7 @@
         <v>282</v>
       </c>
       <c r="D276" s="3" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
@@ -9017,7 +9017,7 @@
         <v>327</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D277" s="3" t="inlineStr"/>
       <c r="E277" s="3" t="inlineStr">
@@ -9046,10 +9046,10 @@
         <v>328</v>
       </c>
       <c r="C278" s="5" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D278" s="3" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>330</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D279" s="3" t="inlineStr"/>
       <c r="E279" s="3" t="inlineStr">
@@ -9106,7 +9106,7 @@
         <v>331</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D280" s="3" t="inlineStr"/>
       <c r="E280" s="3" t="inlineStr">
@@ -9135,7 +9135,7 @@
         <v>332</v>
       </c>
       <c r="C281" s="5" t="n">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="D281" s="3" t="inlineStr"/>
       <c r="E281" s="3" t="inlineStr">
@@ -9164,10 +9164,10 @@
         <v>333</v>
       </c>
       <c r="C282" s="5" t="n">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="D282" s="3" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
@@ -9195,10 +9195,10 @@
         <v>335</v>
       </c>
       <c r="C283" s="5" t="n">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>337</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D284" s="3" t="inlineStr"/>
       <c r="E284" s="3" t="inlineStr">
@@ -9255,7 +9255,7 @@
         <v>338</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D285" s="3" t="inlineStr"/>
       <c r="E285" s="3" t="inlineStr">
@@ -9284,7 +9284,7 @@
         <v>340</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D286" s="3" t="inlineStr"/>
       <c r="E286" s="3" t="inlineStr">
@@ -9313,7 +9313,7 @@
         <v>341</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D287" s="3" t="inlineStr"/>
       <c r="E287" s="3" t="inlineStr">
@@ -9342,7 +9342,7 @@
         <v>342</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
@@ -9371,7 +9371,7 @@
         <v>344</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr">
@@ -9400,7 +9400,7 @@
         <v>348</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D290" s="3" t="inlineStr"/>
       <c r="E290" s="3" t="inlineStr">
@@ -9429,7 +9429,7 @@
         <v>349</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
@@ -9458,7 +9458,7 @@
         <v>350</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
@@ -9487,7 +9487,7 @@
         <v>351</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr">
@@ -9516,7 +9516,7 @@
         <v>360</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
@@ -9545,7 +9545,7 @@
         <v>363</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D295" s="3" t="n">
         <v>293</v>
@@ -9576,7 +9576,7 @@
         <v>367</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D296" s="3" t="inlineStr"/>
       <c r="E296" s="3" t="inlineStr">
@@ -9605,7 +9605,7 @@
         <v>373</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D297" s="3" t="inlineStr"/>
       <c r="E297" s="3" t="inlineStr">
@@ -9634,7 +9634,7 @@
         <v>374</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D298" s="3" t="inlineStr"/>
       <c r="E298" s="3" t="inlineStr">
@@ -9663,7 +9663,7 @@
         <v>377</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D299" s="3" t="inlineStr"/>
       <c r="E299" s="3" t="inlineStr">
@@ -9692,7 +9692,7 @@
         <v>383</v>
       </c>
       <c r="C300" s="5" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D300" s="3" t="inlineStr"/>
       <c r="E300" s="3" t="inlineStr">
@@ -9721,7 +9721,7 @@
         <v>386</v>
       </c>
       <c r="C301" s="5" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D301" s="3" t="inlineStr"/>
       <c r="E301" s="3" t="inlineStr">
@@ -9750,7 +9750,7 @@
         <v>387</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D302" s="3" t="n">
         <v>301</v>
@@ -9781,7 +9781,7 @@
         <v>395</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D303" s="3" t="inlineStr"/>
       <c r="E303" s="3" t="inlineStr">

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -6682,7 +6682,7 @@
         <v>224</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D200" s="3" t="inlineStr"/>
       <c r="E200" s="3" t="inlineStr">
@@ -6897,7 +6897,7 @@
         <v>235</v>
       </c>
       <c r="C207" s="5" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D207" s="3" t="n">
         <v>273</v>
@@ -7207,7 +7207,7 @@
         <v>246</v>
       </c>
       <c r="C217" s="5" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D217" s="3" t="n">
         <v>285</v>
@@ -7300,7 +7300,7 @@
         <v>250</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D220" s="3" t="inlineStr"/>
       <c r="E220" s="3" t="inlineStr">
@@ -7422,7 +7422,7 @@
         <v>255</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D224" s="3" t="inlineStr"/>
       <c r="E224" s="3" t="inlineStr">
@@ -7513,7 +7513,7 @@
         <v>258</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
@@ -7790,7 +7790,7 @@
         <v>268</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D236" s="3" t="inlineStr"/>
       <c r="E236" s="3" t="inlineStr">
@@ -7881,7 +7881,7 @@
         <v>271</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D239" s="3" t="n">
         <v>287</v>
@@ -7972,7 +7972,7 @@
         <v>274</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D242" s="3" t="inlineStr"/>
       <c r="E242" s="3" t="inlineStr">
@@ -8123,7 +8123,7 @@
         <v>280</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
@@ -8152,7 +8152,7 @@
         <v>281</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D248" s="3" t="inlineStr"/>
       <c r="E248" s="3" t="inlineStr">
@@ -8303,7 +8303,7 @@
         <v>288</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D253" s="3" t="inlineStr"/>
       <c r="E253" s="3" t="inlineStr">
@@ -8392,7 +8392,7 @@
         <v>292</v>
       </c>
       <c r="C256" s="5" t="n">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="D256" s="3" t="inlineStr"/>
       <c r="E256" s="3" t="inlineStr">
@@ -8452,7 +8452,7 @@
         <v>294</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
@@ -8481,7 +8481,7 @@
         <v>296</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
@@ -8510,7 +8510,7 @@
         <v>297</v>
       </c>
       <c r="C260" s="5" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D260" s="3" t="inlineStr"/>
       <c r="E260" s="3" t="inlineStr">
@@ -8721,7 +8721,7 @@
         <v>305</v>
       </c>
       <c r="C267" s="5" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D267" s="3" t="inlineStr"/>
       <c r="E267" s="3" t="inlineStr">
@@ -8839,7 +8839,7 @@
         <v>311</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr">
@@ -8868,7 +8868,7 @@
         <v>312</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
@@ -8897,7 +8897,7 @@
         <v>314</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D273" s="3" t="inlineStr"/>
       <c r="E273" s="3" t="inlineStr">
@@ -9017,7 +9017,7 @@
         <v>327</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D277" s="3" t="inlineStr"/>
       <c r="E277" s="3" t="inlineStr">
@@ -9106,7 +9106,7 @@
         <v>331</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D280" s="3" t="inlineStr"/>
       <c r="E280" s="3" t="inlineStr">
@@ -9135,7 +9135,7 @@
         <v>332</v>
       </c>
       <c r="C281" s="5" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D281" s="3" t="inlineStr"/>
       <c r="E281" s="3" t="inlineStr">
@@ -9226,7 +9226,7 @@
         <v>337</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D284" s="3" t="inlineStr"/>
       <c r="E284" s="3" t="inlineStr">
@@ -9255,7 +9255,7 @@
         <v>338</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D285" s="3" t="inlineStr"/>
       <c r="E285" s="3" t="inlineStr">
@@ -9284,7 +9284,7 @@
         <v>340</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>363</v>
+        <v>328</v>
       </c>
       <c r="D286" s="3" t="inlineStr"/>
       <c r="E286" s="3" t="inlineStr">
@@ -9342,7 +9342,7 @@
         <v>342</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
@@ -9371,7 +9371,7 @@
         <v>344</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr">
@@ -9400,7 +9400,7 @@
         <v>348</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D290" s="3" t="inlineStr"/>
       <c r="E290" s="3" t="inlineStr">
@@ -9429,7 +9429,7 @@
         <v>349</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
@@ -9458,7 +9458,7 @@
         <v>350</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
@@ -9487,7 +9487,7 @@
         <v>351</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr">
@@ -9516,7 +9516,7 @@
         <v>360</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
@@ -9545,7 +9545,7 @@
         <v>363</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D295" s="3" t="n">
         <v>293</v>
@@ -9576,7 +9576,7 @@
         <v>367</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D296" s="3" t="inlineStr"/>
       <c r="E296" s="3" t="inlineStr">
@@ -9605,7 +9605,7 @@
         <v>373</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D297" s="3" t="inlineStr"/>
       <c r="E297" s="3" t="inlineStr">
@@ -9634,7 +9634,7 @@
         <v>374</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D298" s="3" t="inlineStr"/>
       <c r="E298" s="3" t="inlineStr">
@@ -9663,7 +9663,7 @@
         <v>377</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D299" s="3" t="inlineStr"/>
       <c r="E299" s="3" t="inlineStr">
@@ -9692,7 +9692,7 @@
         <v>383</v>
       </c>
       <c r="C300" s="5" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D300" s="3" t="inlineStr"/>
       <c r="E300" s="3" t="inlineStr">
@@ -9750,7 +9750,7 @@
         <v>387</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D302" s="3" t="n">
         <v>301</v>
@@ -9781,7 +9781,7 @@
         <v>395</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D303" s="3" t="inlineStr"/>
       <c r="E303" s="3" t="inlineStr">

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -764,7 +764,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>12</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>17</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>41</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>14</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>42</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>33</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>34</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>28</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>30</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>55</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>65</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>24</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>27</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>32</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>31</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>61</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>51</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>48</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>50</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>59</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>66</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>60</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>47</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>96</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>81</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>122</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>78</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>95</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>67</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>76</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>72</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>127</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>121</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>74</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>91</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>77</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>99</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>86</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>112</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>46</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>113</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>79</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>94</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>109</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>97</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>84</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>88</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>114</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>125</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>93</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>90</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>115</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>119</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>107</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>195</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>103</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>102</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>135</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>120</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>80</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>117</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>136</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>194</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>145</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>176</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>196</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>161</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>128</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>156</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>208</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>204</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>198</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>231</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>191</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>106</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>202</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>234</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>146</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>210</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>144</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>159</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>235</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>197</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>160</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>207</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>269</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>233</v>
+        <v>196</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>189</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>192</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         <v>295</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>254</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>171</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>92</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>270</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>237</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>286</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>289</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>225</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>263</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>279</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>273</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>266</v>
+        <v>213</v>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>272</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>174</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>294</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>170</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>158</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>162</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>222</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>258</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>173</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>211</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>290</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>262</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>232</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>265</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>240</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>224</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D200" s="3" t="inlineStr"/>
       <c r="E200" s="3" t="inlineStr">
@@ -6714,7 +6714,7 @@
         <v>87</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>224</v>
       </c>
       <c r="D203" s="3" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>292</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>256</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>221</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>260</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>238</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>300</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>219</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>298</v>
       </c>
       <c r="D215" s="3" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>178</v>
       </c>
       <c r="D216" s="3" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
@@ -7207,10 +7207,10 @@
         <v>246</v>
       </c>
       <c r="C217" s="5" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>220</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>277</v>
       </c>
       <c r="D219" s="3" t="n">
-        <v>288</v>
+        <v>204</v>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>250</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D220" s="3" t="inlineStr"/>
       <c r="E220" s="3" t="inlineStr">
@@ -7332,7 +7332,7 @@
         <v>285</v>
       </c>
       <c r="D221" s="3" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>267</v>
       </c>
       <c r="D222" s="3" t="n">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>233</v>
       </c>
       <c r="D223" s="3" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>256</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D225" s="3" t="n">
         <v>294</v>
@@ -7485,7 +7485,7 @@
         <v>274</v>
       </c>
       <c r="D226" s="3" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>281</v>
       </c>
       <c r="D228" s="3" t="n">
-        <v>271</v>
+        <v>301</v>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>261</v>
       </c>
       <c r="D232" s="3" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>265</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D233" s="3" t="n">
         <v>290</v>
@@ -7731,7 +7731,7 @@
         <v>241</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>236</v>
       </c>
       <c r="D235" s="3" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>268</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D236" s="3" t="inlineStr"/>
       <c r="E236" s="3" t="inlineStr">
@@ -7822,7 +7822,7 @@
         <v>209</v>
       </c>
       <c r="D237" s="3" t="n">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
@@ -7881,10 +7881,10 @@
         <v>271</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D239" s="3" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
         <v>293</v>
       </c>
       <c r="D240" s="3" t="n">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>275</v>
       </c>
       <c r="D244" s="3" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>271</v>
       </c>
       <c r="D245" s="3" t="n">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>193</v>
       </c>
       <c r="D246" s="3" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>280</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
@@ -8215,7 +8215,7 @@
         <v>288</v>
       </c>
       <c r="D250" s="3" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>285</v>
       </c>
       <c r="C252" s="5" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D252" s="3" t="n">
         <v>300</v>
@@ -8392,7 +8392,7 @@
         <v>292</v>
       </c>
       <c r="C256" s="5" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D256" s="3" t="inlineStr"/>
       <c r="E256" s="3" t="inlineStr">
@@ -8424,7 +8424,7 @@
         <v>239</v>
       </c>
       <c r="D257" s="3" t="n">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
@@ -8542,7 +8542,7 @@
         <v>287</v>
       </c>
       <c r="D261" s="3" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>280</v>
       </c>
       <c r="D263" s="3" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>301</v>
       </c>
       <c r="C264" s="5" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D264" s="3" t="inlineStr"/>
       <c r="E264" s="3" t="inlineStr">
@@ -8664,7 +8664,7 @@
         <v>253</v>
       </c>
       <c r="D265" s="3" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>305</v>
       </c>
       <c r="C267" s="5" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D267" s="3" t="inlineStr"/>
       <c r="E267" s="3" t="inlineStr">
@@ -8753,7 +8753,7 @@
         <v>199</v>
       </c>
       <c r="D268" s="3" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>309</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D269" s="3" t="inlineStr"/>
       <c r="E269" s="3" t="inlineStr">
@@ -8839,7 +8839,7 @@
         <v>311</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr">
@@ -8868,7 +8868,7 @@
         <v>312</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
@@ -9049,7 +9049,7 @@
         <v>284</v>
       </c>
       <c r="D278" s="3" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         <v>330</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D279" s="3" t="inlineStr"/>
       <c r="E279" s="3" t="inlineStr">
@@ -9135,7 +9135,7 @@
         <v>332</v>
       </c>
       <c r="C281" s="5" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D281" s="3" t="inlineStr"/>
       <c r="E281" s="3" t="inlineStr">
@@ -9167,7 +9167,7 @@
         <v>201</v>
       </c>
       <c r="D282" s="3" t="n">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="E282" s="3" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>297</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>338</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D285" s="3" t="inlineStr"/>
       <c r="E285" s="3" t="inlineStr">
@@ -9284,7 +9284,7 @@
         <v>340</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D286" s="3" t="inlineStr"/>
       <c r="E286" s="3" t="inlineStr">
@@ -9313,7 +9313,7 @@
         <v>341</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D287" s="3" t="inlineStr"/>
       <c r="E287" s="3" t="inlineStr">
@@ -9342,7 +9342,7 @@
         <v>342</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
@@ -9487,7 +9487,7 @@
         <v>351</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr">
@@ -9516,7 +9516,7 @@
         <v>360</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
@@ -9545,7 +9545,7 @@
         <v>363</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D295" s="3" t="n">
         <v>293</v>
@@ -9605,7 +9605,7 @@
         <v>373</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D297" s="3" t="inlineStr"/>
       <c r="E297" s="3" t="inlineStr">
@@ -9634,7 +9634,7 @@
         <v>374</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D298" s="3" t="inlineStr"/>
       <c r="E298" s="3" t="inlineStr">
@@ -9663,7 +9663,7 @@
         <v>377</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D299" s="3" t="inlineStr"/>
       <c r="E299" s="3" t="inlineStr">
@@ -9753,7 +9753,7 @@
         <v>319</v>
       </c>
       <c r="D302" s="3" t="n">
-        <v>301</v>
+        <v>274</v>
       </c>
       <c r="E302" s="3" t="inlineStr">
         <is>

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G303"/>
+  <dimension ref="A1:G307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>8</v>
@@ -761,7 +761,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>6</v>
@@ -795,7 +795,7 @@
         <v>12</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>23</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>22</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>17</v>
@@ -981,7 +981,7 @@
         <v>21</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -1008,11 +1008,11 @@
       <c r="B17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C17" s="9" t="n">
-        <v>41</v>
+      <c r="C17" s="4" t="n">
+        <v>28</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>11</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -1101,11 +1101,11 @@
       <c r="B20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="9" t="n">
-        <v>42</v>
+      <c r="C20" s="4" t="n">
+        <v>26</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>13</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>18</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>43</v>
@@ -1226,7 +1226,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>27</v>
@@ -1257,10 +1257,10 @@
         <v>24</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>29</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -1349,11 +1349,11 @@
       <c r="B28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C28" s="4" t="n">
-        <v>33</v>
+      <c r="C28" s="5" t="n">
+        <v>27</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
         <v>30</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
         <v>31</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="9" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>51</v>
@@ -1539,7 +1539,7 @@
         <v>65</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>42</v>
@@ -1598,10 +1598,10 @@
         <v>35</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>19</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -1659,11 +1659,11 @@
       <c r="B38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="C38" s="7" t="n">
-        <v>27</v>
+      <c r="C38" s="11" t="n">
+        <v>32</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>35</v>
@@ -1722,10 +1722,10 @@
         <v>39</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -1753,10 +1753,10 @@
         <v>40</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -1783,11 +1783,11 @@
       <c r="B42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="C42" s="7" t="n">
-        <v>26</v>
+      <c r="C42" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>43</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1845,11 +1845,11 @@
       <c r="B44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="C44" s="9" t="n">
-        <v>57</v>
+      <c r="C44" s="4" t="n">
+        <v>53</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>44</v>
       </c>
       <c r="C45" s="9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -1907,8 +1907,8 @@
       <c r="B46" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="C46" s="7" t="n">
-        <v>40</v>
+      <c r="C46" s="5" t="n">
+        <v>42</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>33</v>
@@ -1942,7 +1942,7 @@
         <v>49</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -1970,10 +1970,10 @@
         <v>47</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         <v>48</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -2031,11 +2031,11 @@
       <c r="B50" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="C50" s="5" t="n">
-        <v>51</v>
+      <c r="C50" s="4" t="n">
+        <v>57</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>48</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -2094,10 +2094,10 @@
         <v>51</v>
       </c>
       <c r="C52" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="D52" s="3" t="n">
         <v>50</v>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>49</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -2125,10 +2125,10 @@
         <v>52</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -2155,11 +2155,11 @@
       <c r="B54" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="C54" s="4" t="n">
-        <v>59</v>
+      <c r="C54" s="5" t="n">
+        <v>54</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -2187,10 +2187,10 @@
         <v>54</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>66</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
         <v>56</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
         <v>57</v>
       </c>
       <c r="C58" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="D58" s="3" t="n">
         <v>64</v>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>65</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         <v>58</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D60" s="3" t="n">
         <v>46</v>
@@ -2373,7 +2373,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>70</v>
@@ -2403,8 +2403,8 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="7" t="n">
-        <v>54</v>
+      <c r="C62" s="11" t="n">
+        <v>56</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>52</v>
@@ -2435,10 +2435,10 @@
         <v>62</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         <v>63</v>
       </c>
       <c r="C64" s="9" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>87</v>
@@ -2497,10 +2497,10 @@
         <v>64</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>67</v>
@@ -2562,7 +2562,7 @@
         <v>75</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
         <v>67</v>
       </c>
       <c r="C68" s="9" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
         <v>68</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>62</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
@@ -2682,8 +2682,8 @@
       <c r="B71" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C71" s="11" t="n">
-        <v>63</v>
+      <c r="C71" s="7" t="n">
+        <v>61</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>66</v>
@@ -2714,10 +2714,10 @@
         <v>71</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -2745,10 +2745,10 @@
         <v>72</v>
       </c>
       <c r="C73" s="9" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -2775,11 +2775,11 @@
       <c r="B74" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="C74" s="4" t="n">
-        <v>78</v>
+      <c r="C74" s="5" t="n">
+        <v>76</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -2806,11 +2806,11 @@
       <c r="B75" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="C75" s="9" t="n">
-        <v>95</v>
+      <c r="C75" s="4" t="n">
+        <v>86</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D76" s="3" t="n">
         <v>63</v>
@@ -2869,10 +2869,10 @@
         <v>76</v>
       </c>
       <c r="C77" s="9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         <v>77</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -2930,11 +2930,11 @@
       <c r="B79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C79" s="11" t="n">
-        <v>72</v>
+      <c r="C79" s="5" t="n">
+        <v>78</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D80" s="3" t="n">
         <v>68</v>
@@ -2992,11 +2992,11 @@
       <c r="B81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="C81" s="4" t="n">
-        <v>85</v>
+      <c r="C81" s="9" t="n">
+        <v>94</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D82" s="3" t="n">
         <v>69</v>
@@ -3054,11 +3054,11 @@
       <c r="B83" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="C83" s="9" t="n">
-        <v>127</v>
+      <c r="C83" s="5" t="n">
+        <v>99</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -3086,10 +3086,10 @@
         <v>83</v>
       </c>
       <c r="C84" s="9" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -3116,8 +3116,8 @@
       <c r="B85" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="C85" s="7" t="n">
-        <v>74</v>
+      <c r="C85" s="5" t="n">
+        <v>92</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>84</v>
@@ -3148,10 +3148,10 @@
         <v>85</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -3178,11 +3178,11 @@
       <c r="B87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="C87" s="5" t="n">
-        <v>77</v>
+      <c r="C87" s="9" t="n">
+        <v>107</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         <v>87</v>
       </c>
       <c r="C88" s="9" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
@@ -3241,10 +3241,10 @@
         <v>88</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
@@ -3272,10 +3272,10 @@
         <v>89</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
@@ -3303,10 +3303,10 @@
         <v>90</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -3334,10 +3334,10 @@
         <v>91</v>
       </c>
       <c r="C92" s="9" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>47</v>
@@ -3396,10 +3396,10 @@
         <v>93</v>
       </c>
       <c r="C94" s="9" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
@@ -3427,10 +3427,10 @@
         <v>94</v>
       </c>
       <c r="C95" s="9" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
@@ -3458,10 +3458,10 @@
         <v>95</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
@@ -3489,10 +3489,10 @@
         <v>96</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>97</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         <v>98</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
@@ -3582,10 +3582,10 @@
         <v>99</v>
       </c>
       <c r="C100" s="9" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         <v>101</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
@@ -3644,10 +3644,10 @@
         <v>102</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
         <v>103</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
@@ -3706,10 +3706,10 @@
         <v>104</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
@@ -3737,10 +3737,10 @@
         <v>105</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
@@ -3768,10 +3768,10 @@
         <v>106</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         <v>107</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
@@ -3830,10 +3830,10 @@
         <v>108</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
@@ -3860,8 +3860,8 @@
       <c r="B109" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="C109" s="5" t="n">
-        <v>114</v>
+      <c r="C109" s="9" t="n">
+        <v>123</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>121</v>
@@ -3891,11 +3891,11 @@
       <c r="B110" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="C110" s="7" t="n">
-        <v>98</v>
+      <c r="C110" s="11" t="n">
+        <v>104</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -3922,11 +3922,11 @@
       <c r="B111" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="C111" s="5" t="n">
-        <v>125</v>
+      <c r="C111" s="7" t="n">
+        <v>97</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>93</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
         <v>113</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
         <v>114</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
@@ -4046,11 +4046,11 @@
       <c r="B115" s="3" t="n">
         <v>115</v>
       </c>
-      <c r="C115" s="11" t="n">
-        <v>108</v>
+      <c r="C115" s="7" t="n">
+        <v>96</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
@@ -4077,11 +4077,11 @@
       <c r="B116" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="C116" s="4" t="n">
-        <v>124</v>
+      <c r="C116" s="9" t="n">
+        <v>137</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
@@ -4109,10 +4109,10 @@
         <v>117</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
@@ -4140,10 +4140,10 @@
         <v>118</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
@@ -4170,11 +4170,11 @@
       <c r="B119" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="C119" s="5" t="n">
-        <v>119</v>
+      <c r="C119" s="11" t="n">
+        <v>113</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         <v>120</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
@@ -4233,10 +4233,10 @@
         <v>121</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
@@ -4264,10 +4264,10 @@
         <v>122</v>
       </c>
       <c r="C122" s="9" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
@@ -4295,10 +4295,10 @@
         <v>123</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>124</v>
       </c>
       <c r="C124" s="7" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>85</v>
@@ -4356,11 +4356,11 @@
       <c r="B125" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="C125" s="7" t="n">
-        <v>102</v>
+      <c r="C125" s="5" t="n">
+        <v>126</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
@@ -4387,11 +4387,11 @@
       <c r="B126" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="C126" s="4" t="n">
-        <v>135</v>
+      <c r="C126" s="7" t="n">
+        <v>82</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>120</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
@@ -4450,10 +4450,10 @@
         <v>128</v>
       </c>
       <c r="C128" s="7" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
@@ -4480,11 +4480,11 @@
       <c r="B129" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="C129" s="7" t="n">
-        <v>117</v>
+      <c r="C129" s="9" t="n">
+        <v>201</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
@@ -4512,10 +4512,10 @@
         <v>130</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
@@ -4543,10 +4543,10 @@
         <v>131</v>
       </c>
       <c r="C131" s="9" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
@@ -4573,11 +4573,11 @@
       <c r="B132" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="C132" s="5" t="n">
-        <v>136</v>
+      <c r="C132" s="4" t="n">
+        <v>141</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
@@ -4605,10 +4605,10 @@
         <v>133</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
@@ -4636,10 +4636,10 @@
         <v>134</v>
       </c>
       <c r="C134" s="9" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
@@ -4667,10 +4667,10 @@
         <v>135</v>
       </c>
       <c r="C135" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="D135" s="3" t="n">
         <v>145</v>
-      </c>
-      <c r="D135" s="3" t="n">
-        <v>152</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
@@ -4698,10 +4698,10 @@
         <v>136</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
@@ -4729,7 +4729,7 @@
         <v>137</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="D137" s="3" t="n">
         <v>159</v>
@@ -4760,10 +4760,10 @@
         <v>138</v>
       </c>
       <c r="C138" s="9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
@@ -4790,11 +4790,11 @@
       <c r="B139" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C139" s="5" t="n">
-        <v>161</v>
+      <c r="C139" s="7" t="n">
+        <v>125</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
@@ -4821,11 +4821,11 @@
       <c r="B140" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="C140" s="7" t="n">
-        <v>128</v>
+      <c r="C140" s="5" t="n">
+        <v>148</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
@@ -4853,10 +4853,10 @@
         <v>141</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
@@ -4884,10 +4884,10 @@
         <v>142</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
@@ -4915,10 +4915,10 @@
         <v>143</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
@@ -4946,10 +4946,10 @@
         <v>144</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>145</v>
       </c>
       <c r="C145" s="9" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
@@ -5008,10 +5008,10 @@
         <v>146</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>175</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
         <v>148</v>
       </c>
       <c r="C148" s="9" t="n">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
@@ -5100,11 +5100,11 @@
       <c r="B149" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="C149" s="11" t="n">
-        <v>106</v>
+      <c r="C149" s="5" t="n">
+        <v>151</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
@@ -5132,10 +5132,10 @@
         <v>150</v>
       </c>
       <c r="C150" s="4" t="n">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         <v>151</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
@@ -5194,10 +5194,10 @@
         <v>152</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
@@ -5225,10 +5225,10 @@
         <v>153</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
@@ -5256,10 +5256,10 @@
         <v>154</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
@@ -5287,10 +5287,10 @@
         <v>155</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
@@ -5317,11 +5317,11 @@
       <c r="B156" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="C156" s="11" t="n">
-        <v>146</v>
+      <c r="C156" s="5" t="n">
+        <v>174</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
@@ -5349,10 +5349,10 @@
         <v>158</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         <v>159</v>
       </c>
       <c r="C158" s="7" t="n">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>190</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>198</v>
+        <v>166</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>161</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D160" s="3" t="n">
         <v>161</v>
@@ -5473,10 +5473,10 @@
         <v>162</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         <v>164</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
@@ -5535,10 +5535,10 @@
         <v>165</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
@@ -5566,10 +5566,10 @@
         <v>166</v>
       </c>
       <c r="C164" s="4" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
         <v>167</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
@@ -5627,11 +5627,11 @@
       <c r="B166" s="3" t="n">
         <v>169</v>
       </c>
-      <c r="C166" s="4" t="n">
-        <v>269</v>
+      <c r="C166" s="5" t="n">
+        <v>177</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
@@ -5659,10 +5659,10 @@
         <v>170</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
@@ -5690,10 +5690,10 @@
         <v>173</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
@@ -5721,10 +5721,10 @@
         <v>174</v>
       </c>
       <c r="C169" s="4" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
@@ -5752,10 +5752,10 @@
         <v>175</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>171</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
@@ -5814,10 +5814,10 @@
         <v>177</v>
       </c>
       <c r="C172" s="7" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -5845,10 +5845,10 @@
         <v>178</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>237</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
@@ -5907,10 +5907,10 @@
         <v>185</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
@@ -5938,10 +5938,10 @@
         <v>186</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
@@ -5969,10 +5969,10 @@
         <v>187</v>
       </c>
       <c r="C177" s="4" t="n">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>188</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>279</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
@@ -6061,11 +6061,11 @@
       <c r="B180" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="C180" s="4" t="n">
-        <v>273</v>
+      <c r="C180" s="5" t="n">
+        <v>195</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
@@ -6093,10 +6093,10 @@
         <v>194</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
@@ -6123,11 +6123,11 @@
       <c r="B182" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="C182" s="11" t="n">
-        <v>163</v>
+      <c r="C182" s="5" t="n">
+        <v>176</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
@@ -6154,11 +6154,11 @@
       <c r="B183" s="3" t="n">
         <v>196</v>
       </c>
-      <c r="C183" s="5" t="n">
-        <v>174</v>
+      <c r="C183" s="11" t="n">
+        <v>159</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
@@ -6186,10 +6186,10 @@
         <v>197</v>
       </c>
       <c r="C184" s="4" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
@@ -6216,11 +6216,11 @@
       <c r="B185" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="C185" s="5" t="n">
-        <v>170</v>
+      <c r="C185" s="11" t="n">
+        <v>161</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
@@ -6248,10 +6248,10 @@
         <v>201</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
@@ -6279,10 +6279,10 @@
         <v>202</v>
       </c>
       <c r="C187" s="5" t="n">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
@@ -6310,10 +6310,10 @@
         <v>204</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
@@ -6341,10 +6341,10 @@
         <v>205</v>
       </c>
       <c r="C189" s="5" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
@@ -6372,10 +6372,10 @@
         <v>206</v>
       </c>
       <c r="C190" s="4" t="n">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
@@ -6403,10 +6403,10 @@
         <v>207</v>
       </c>
       <c r="C191" s="4" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>173</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
@@ -6465,10 +6465,10 @@
         <v>212</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
@@ -6496,10 +6496,10 @@
         <v>213</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
@@ -6527,10 +6527,10 @@
         <v>217</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
@@ -6558,10 +6558,10 @@
         <v>219</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
@@ -6589,10 +6589,10 @@
         <v>221</v>
       </c>
       <c r="C197" s="4" t="n">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
@@ -6619,11 +6619,11 @@
       <c r="B198" s="3" t="n">
         <v>222</v>
       </c>
-      <c r="C198" s="5" t="n">
-        <v>240</v>
+      <c r="C198" s="4" t="n">
+        <v>269</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>218</v>
       </c>
       <c r="D199" s="3" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>224</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D200" s="3" t="inlineStr"/>
       <c r="E200" s="3" t="inlineStr">
@@ -6711,7 +6711,7 @@
         <v>225</v>
       </c>
       <c r="C201" s="7" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D201" s="3" t="n">
         <v>89</v>
@@ -6741,11 +6741,11 @@
       <c r="B202" s="3" t="n">
         <v>228</v>
       </c>
-      <c r="C202" s="5" t="n">
-        <v>257</v>
+      <c r="C202" s="4" t="n">
+        <v>263</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
@@ -6772,8 +6772,8 @@
       <c r="B203" s="3" t="n">
         <v>230</v>
       </c>
-      <c r="C203" s="5" t="n">
-        <v>224</v>
+      <c r="C203" s="11" t="n">
+        <v>192</v>
       </c>
       <c r="D203" s="3" t="n">
         <v>203</v>
@@ -6803,11 +6803,11 @@
       <c r="B204" s="3" t="n">
         <v>232</v>
       </c>
-      <c r="C204" s="5" t="n">
-        <v>266</v>
+      <c r="C204" s="4" t="n">
+        <v>303</v>
       </c>
       <c r="D204" s="3" t="n">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
@@ -6835,10 +6835,10 @@
         <v>233</v>
       </c>
       <c r="C205" s="4" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
@@ -6866,10 +6866,10 @@
         <v>234</v>
       </c>
       <c r="C206" s="5" t="n">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
@@ -6897,10 +6897,10 @@
         <v>235</v>
       </c>
       <c r="C207" s="5" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         <v>237</v>
       </c>
       <c r="C208" s="5" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
@@ -6959,10 +6959,10 @@
         <v>238</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
@@ -6989,11 +6989,11 @@
       <c r="B210" s="3" t="n">
         <v>239</v>
       </c>
-      <c r="C210" s="5" t="n">
-        <v>260</v>
+      <c r="C210" s="4" t="n">
+        <v>281</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
@@ -7021,10 +7021,10 @@
         <v>240</v>
       </c>
       <c r="C211" s="5" t="n">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>291</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
@@ -7082,11 +7082,11 @@
       <c r="B213" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="C213" s="4" t="n">
-        <v>300</v>
+      <c r="C213" s="5" t="n">
+        <v>260</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
@@ -7114,10 +7114,10 @@
         <v>243</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
@@ -7145,10 +7145,10 @@
         <v>244</v>
       </c>
       <c r="C215" s="4" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D215" s="3" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
@@ -7176,10 +7176,10 @@
         <v>245</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="D216" s="3" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
@@ -7206,11 +7206,11 @@
       <c r="B217" s="3" t="n">
         <v>246</v>
       </c>
-      <c r="C217" s="5" t="n">
-        <v>281</v>
+      <c r="C217" s="4" t="n">
+        <v>288</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
@@ -7238,10 +7238,10 @@
         <v>248</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
@@ -7269,10 +7269,10 @@
         <v>249</v>
       </c>
       <c r="C219" s="5" t="n">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="D219" s="3" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
@@ -7299,8 +7299,8 @@
       <c r="B220" s="3" t="n">
         <v>250</v>
       </c>
-      <c r="C220" s="4" t="n">
-        <v>301</v>
+      <c r="C220" s="5" t="n">
+        <v>287</v>
       </c>
       <c r="D220" s="3" t="inlineStr"/>
       <c r="E220" s="3" t="inlineStr">
@@ -7329,10 +7329,10 @@
         <v>251</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>285</v>
+        <v>203</v>
       </c>
       <c r="D221" s="3" t="n">
-        <v>271</v>
+        <v>204</v>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
@@ -7360,10 +7360,10 @@
         <v>252</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D222" s="3" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
@@ -7391,10 +7391,10 @@
         <v>254</v>
       </c>
       <c r="C223" s="5" t="n">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="D223" s="3" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>255</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D224" s="3" t="inlineStr"/>
       <c r="E224" s="3" t="inlineStr">
@@ -7451,10 +7451,10 @@
         <v>256</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="D225" s="3" t="n">
-        <v>294</v>
+        <v>231</v>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
@@ -7482,10 +7482,10 @@
         <v>257</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="D226" s="3" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>258</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
@@ -7542,11 +7542,9 @@
         <v>259</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>281</v>
-      </c>
-      <c r="D228" s="3" t="n">
-        <v>301</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="D228" s="3" t="inlineStr"/>
       <c r="E228" s="3" t="inlineStr">
         <is>
           <t>Eli Stowers</t>
@@ -7573,10 +7571,10 @@
         <v>260</v>
       </c>
       <c r="C229" s="5" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D229" s="3" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
@@ -7604,10 +7602,10 @@
         <v>261</v>
       </c>
       <c r="C230" s="4" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="D230" s="3" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
@@ -7634,11 +7632,11 @@
       <c r="B231" s="3" t="n">
         <v>262</v>
       </c>
-      <c r="C231" s="5" t="n">
-        <v>203</v>
+      <c r="C231" s="11" t="n">
+        <v>196</v>
       </c>
       <c r="D231" s="3" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
@@ -7669,7 +7667,7 @@
         <v>261</v>
       </c>
       <c r="D232" s="3" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
@@ -7697,10 +7695,10 @@
         <v>265</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="D233" s="3" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
@@ -7728,10 +7726,10 @@
         <v>266</v>
       </c>
       <c r="C234" s="5" t="n">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
@@ -7759,10 +7757,10 @@
         <v>267</v>
       </c>
       <c r="C235" s="5" t="n">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="D235" s="3" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
@@ -7790,7 +7788,7 @@
         <v>268</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D236" s="3" t="inlineStr"/>
       <c r="E236" s="3" t="inlineStr">
@@ -7819,10 +7817,10 @@
         <v>269</v>
       </c>
       <c r="C237" s="5" t="n">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="D237" s="3" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
@@ -7850,10 +7848,10 @@
         <v>270</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D238" s="3" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
@@ -7881,10 +7879,10 @@
         <v>271</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>255</v>
+        <v>299</v>
       </c>
       <c r="D239" s="3" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
@@ -7912,10 +7910,10 @@
         <v>272</v>
       </c>
       <c r="C240" s="5" t="n">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="D240" s="3" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
@@ -7942,8 +7940,8 @@
       <c r="B241" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="C241" s="5" t="n">
-        <v>313</v>
+      <c r="C241" s="4" t="n">
+        <v>324</v>
       </c>
       <c r="D241" s="3" t="inlineStr"/>
       <c r="E241" s="3" t="inlineStr">
@@ -7972,7 +7970,7 @@
         <v>274</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="D242" s="3" t="inlineStr"/>
       <c r="E242" s="3" t="inlineStr">
@@ -8001,7 +7999,7 @@
         <v>275</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="D243" s="3" t="inlineStr"/>
       <c r="E243" s="3" t="inlineStr">
@@ -8033,7 +8031,7 @@
         <v>275</v>
       </c>
       <c r="D244" s="3" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
@@ -8061,10 +8059,10 @@
         <v>277</v>
       </c>
       <c r="C245" s="5" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D245" s="3" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
@@ -8091,11 +8089,11 @@
       <c r="B246" s="3" t="n">
         <v>278</v>
       </c>
-      <c r="C246" s="11" t="n">
-        <v>193</v>
+      <c r="C246" s="5" t="n">
+        <v>219</v>
       </c>
       <c r="D246" s="3" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
@@ -8123,7 +8121,7 @@
         <v>280</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
@@ -8152,7 +8150,7 @@
         <v>281</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="D248" s="3" t="inlineStr"/>
       <c r="E248" s="3" t="inlineStr">
@@ -8181,10 +8179,10 @@
         <v>282</v>
       </c>
       <c r="C249" s="5" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D249" s="3" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
@@ -8212,10 +8210,10 @@
         <v>283</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D250" s="3" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
@@ -8243,7 +8241,7 @@
         <v>284</v>
       </c>
       <c r="C251" s="5" t="n">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="D251" s="3" t="inlineStr"/>
       <c r="E251" s="3" t="inlineStr">
@@ -8272,10 +8270,10 @@
         <v>285</v>
       </c>
       <c r="C252" s="5" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="D252" s="3" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
@@ -8303,7 +8301,7 @@
         <v>288</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D253" s="3" t="inlineStr"/>
       <c r="E253" s="3" t="inlineStr">
@@ -8332,7 +8330,7 @@
         <v>289</v>
       </c>
       <c r="C254" s="5" t="n">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D254" s="3" t="inlineStr"/>
       <c r="E254" s="3" t="inlineStr">
@@ -8361,10 +8359,10 @@
         <v>290</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D255" s="3" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
@@ -8392,7 +8390,7 @@
         <v>292</v>
       </c>
       <c r="C256" s="5" t="n">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="D256" s="3" t="inlineStr"/>
       <c r="E256" s="3" t="inlineStr">
@@ -8424,7 +8422,7 @@
         <v>239</v>
       </c>
       <c r="D257" s="3" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
@@ -8452,7 +8450,7 @@
         <v>294</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
@@ -8481,7 +8479,7 @@
         <v>296</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
@@ -8510,7 +8508,7 @@
         <v>297</v>
       </c>
       <c r="C260" s="5" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D260" s="3" t="inlineStr"/>
       <c r="E260" s="3" t="inlineStr">
@@ -8539,10 +8537,10 @@
         <v>298</v>
       </c>
       <c r="C261" s="5" t="n">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D261" s="3" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
@@ -8570,10 +8568,10 @@
         <v>299</v>
       </c>
       <c r="C262" s="5" t="n">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="D262" s="3" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
@@ -8604,7 +8602,7 @@
         <v>280</v>
       </c>
       <c r="D263" s="3" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
@@ -8632,7 +8630,7 @@
         <v>301</v>
       </c>
       <c r="C264" s="5" t="n">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D264" s="3" t="inlineStr"/>
       <c r="E264" s="3" t="inlineStr">
@@ -8664,7 +8662,7 @@
         <v>253</v>
       </c>
       <c r="D265" s="3" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
@@ -8692,7 +8690,7 @@
         <v>304</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D266" s="3" t="inlineStr"/>
       <c r="E266" s="3" t="inlineStr">
@@ -8721,7 +8719,7 @@
         <v>305</v>
       </c>
       <c r="C267" s="5" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D267" s="3" t="inlineStr"/>
       <c r="E267" s="3" t="inlineStr">
@@ -8750,10 +8748,10 @@
         <v>306</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D268" s="3" t="n">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
@@ -8781,7 +8779,7 @@
         <v>309</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="D269" s="3" t="inlineStr"/>
       <c r="E269" s="3" t="inlineStr">
@@ -8810,7 +8808,7 @@
         <v>310</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
@@ -8839,7 +8837,7 @@
         <v>311</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr">
@@ -8868,7 +8866,7 @@
         <v>312</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
@@ -8897,7 +8895,7 @@
         <v>314</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D273" s="3" t="inlineStr"/>
       <c r="E273" s="3" t="inlineStr">
@@ -8926,10 +8924,10 @@
         <v>316</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D274" s="3" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
@@ -8957,7 +8955,7 @@
         <v>317</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>296</v>
+        <v>364</v>
       </c>
       <c r="D275" s="3" t="inlineStr"/>
       <c r="E275" s="3" t="inlineStr">
@@ -8977,88 +8975,86 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="8" t="inlineStr">
+      <c r="A276" s="6" t="inlineStr">
+        <is>
+          <t>RB98</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="n">
+        <v>321</v>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>349</v>
+      </c>
+      <c r="D276" s="3" t="inlineStr"/>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>Audric Estime</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="8" t="inlineStr">
         <is>
           <t>TE39</t>
         </is>
       </c>
-      <c r="B276" s="3" t="n">
+      <c r="B277" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="C276" s="5" t="n">
+      <c r="C277" s="5" t="n">
         <v>282</v>
       </c>
-      <c r="D276" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="E276" s="3" t="inlineStr">
+      <c r="D277" s="3" t="n">
+        <v>277</v>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
         <is>
           <t>Darnell Washington</t>
         </is>
       </c>
-      <c r="F276" s="3" t="inlineStr">
+      <c r="F277" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="G276" s="3" t="inlineStr">
+      <c r="G277" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="10" t="inlineStr">
-        <is>
-          <t>QB36</t>
-        </is>
-      </c>
-      <c r="B277" s="3" t="n">
-        <v>327</v>
-      </c>
-      <c r="C277" s="5" t="n">
-        <v>368</v>
-      </c>
-      <c r="D277" s="3" t="inlineStr"/>
-      <c r="E277" s="3" t="inlineStr">
-        <is>
-          <t>J.J. McCarthy</t>
-        </is>
-      </c>
-      <c r="F277" s="3" t="inlineStr">
-        <is>
-          <t>MIN (6)</t>
-        </is>
-      </c>
-      <c r="G277" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>WR114</t>
+          <t>WR112</t>
         </is>
       </c>
       <c r="B278" s="3" t="n">
-        <v>328</v>
-      </c>
-      <c r="C278" s="5" t="n">
-        <v>284</v>
-      </c>
-      <c r="D278" s="3" t="n">
-        <v>266</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="C278" s="4" t="n">
+        <v>375</v>
+      </c>
+      <c r="D278" s="3" t="inlineStr"/>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>Luke McCaffrey</t>
+          <t>Cedric Tillman</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -9068,55 +9064,57 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="inlineStr">
-        <is>
-          <t>WR116</t>
+      <c r="A279" s="10" t="inlineStr">
+        <is>
+          <t>QB36</t>
         </is>
       </c>
       <c r="B279" s="3" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>266</v>
+        <v>368</v>
       </c>
       <c r="D279" s="3" t="inlineStr"/>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>ATL (11)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>WR117</t>
+          <t>WR114</t>
         </is>
       </c>
       <c r="B280" s="3" t="n">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>352</v>
-      </c>
-      <c r="D280" s="3" t="inlineStr"/>
+        <v>294</v>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>270</v>
+      </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Jalen Royals</t>
+          <t>Luke McCaffrey</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>KC (5)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -9126,57 +9124,55 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="8" t="inlineStr">
-        <is>
-          <t>TE40</t>
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>WR115</t>
         </is>
       </c>
       <c r="B281" s="3" t="n">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C281" s="5" t="n">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D281" s="3" t="inlineStr"/>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>Max Klare</t>
+          <t>Tez Johnson</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>TB (10)</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>WR118</t>
+          <t>WR116</t>
         </is>
       </c>
       <c r="B282" s="3" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C282" s="5" t="n">
-        <v>201</v>
-      </c>
-      <c r="D282" s="3" t="n">
-        <v>207</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="D282" s="3" t="inlineStr"/>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>Caleb Douglas</t>
+          <t>Jahan Dotson</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>ATL (11)</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -9188,26 +9184,24 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>WR120</t>
+          <t>WR117</t>
         </is>
       </c>
       <c r="B283" s="3" t="n">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C283" s="5" t="n">
-        <v>297</v>
-      </c>
-      <c r="D283" s="3" t="n">
-        <v>280</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="D283" s="3" t="inlineStr"/>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Jalen Royals</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -9217,171 +9211,177 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="inlineStr">
-        <is>
-          <t>WR122</t>
+      <c r="A284" s="8" t="inlineStr">
+        <is>
+          <t>TE40</t>
         </is>
       </c>
       <c r="B284" s="3" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="D284" s="3" t="inlineStr"/>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Joshua Palmer</t>
+          <t>Max Klare</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="8" t="inlineStr">
-        <is>
-          <t>TE41</t>
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>WR118</t>
         </is>
       </c>
       <c r="B285" s="3" t="n">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>362</v>
-      </c>
-      <c r="D285" s="3" t="inlineStr"/>
+        <v>224</v>
+      </c>
+      <c r="D285" s="3" t="n">
+        <v>213</v>
+      </c>
       <c r="E285" s="3" t="inlineStr">
         <is>
-          <t>Michael Mayer</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="8" t="inlineStr">
-        <is>
-          <t>TE42</t>
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>WR119</t>
         </is>
       </c>
       <c r="B286" s="3" t="n">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>330</v>
-      </c>
-      <c r="D286" s="3" t="inlineStr"/>
+        <v>286</v>
+      </c>
+      <c r="D286" s="3" t="n">
+        <v>269</v>
+      </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>Elijah Arroyo</t>
+          <t>Calvin Austin</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>NYG (8)</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="8" t="inlineStr">
-        <is>
-          <t>TE43</t>
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>WR120</t>
         </is>
       </c>
       <c r="B287" s="3" t="n">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>307</v>
-      </c>
-      <c r="D287" s="3" t="inlineStr"/>
+        <v>360</v>
+      </c>
+      <c r="D287" s="3" t="n">
+        <v>299</v>
+      </c>
       <c r="E287" s="3" t="inlineStr">
         <is>
-          <t>Tyler Higbee</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="10" t="inlineStr">
-        <is>
-          <t>QB37</t>
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>WR122</t>
         </is>
       </c>
       <c r="B288" s="3" t="n">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>372</v>
+        <v>334</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Joshua Palmer</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="8" t="inlineStr">
         <is>
-          <t>TE45</t>
+          <t>TE41</t>
         </is>
       </c>
       <c r="B289" s="3" t="n">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>Dawson Knox</t>
+          <t>Michael Mayer</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -9391,55 +9391,55 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="10" t="inlineStr">
-        <is>
-          <t>QB38</t>
+      <c r="A290" s="8" t="inlineStr">
+        <is>
+          <t>TE42</t>
         </is>
       </c>
       <c r="B290" s="3" t="n">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D290" s="3" t="inlineStr"/>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Carson Beck</t>
+          <t>Elijah Arroyo</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>ARI (14)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="8" t="inlineStr">
         <is>
-          <t>TE47</t>
+          <t>TE43</t>
         </is>
       </c>
       <c r="B291" s="3" t="n">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>366</v>
+        <v>307</v>
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>Cole Kmet</t>
+          <t>Tyler Higbee</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>CHI (10)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -9449,144 +9449,142 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="inlineStr">
-        <is>
-          <t>WR124</t>
+      <c r="A292" s="10" t="inlineStr">
+        <is>
+          <t>QB37</t>
         </is>
       </c>
       <c r="B292" s="3" t="n">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>331</v>
+        <v>378</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>Brenen Thompson</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="inlineStr">
-        <is>
-          <t>WR125</t>
+      <c r="A293" s="8" t="inlineStr">
+        <is>
+          <t>TE45</t>
         </is>
       </c>
       <c r="B293" s="3" t="n">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>339</v>
+        <v>376</v>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr">
         <is>
-          <t>DeMario Douglas</t>
+          <t>Dawson Knox</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="6" t="inlineStr">
-        <is>
-          <t>RB104</t>
+      <c r="A294" s="10" t="inlineStr">
+        <is>
+          <t>QB38</t>
         </is>
       </c>
       <c r="B294" s="3" t="n">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>Jawhar Jordan</t>
+          <t>Carson Beck</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>HOU (8)</t>
+          <t>ARI (14)</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="inlineStr">
-        <is>
-          <t>WR130</t>
+      <c r="A295" s="8" t="inlineStr">
+        <is>
+          <t>TE47</t>
         </is>
       </c>
       <c r="B295" s="3" t="n">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>338</v>
-      </c>
-      <c r="D295" s="3" t="n">
-        <v>293</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="D295" s="3" t="inlineStr"/>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>Treylon Burks</t>
+          <t>Cole Kmet</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>CHI (10)</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>WR133</t>
+          <t>WR124</t>
         </is>
       </c>
       <c r="B296" s="3" t="n">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="D296" s="3" t="inlineStr"/>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>Savion Williams</t>
+          <t>Brenen Thompson</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>GB (11)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -9596,55 +9594,55 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="8" t="inlineStr">
-        <is>
-          <t>TE49</t>
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>WR125</t>
         </is>
       </c>
       <c r="B297" s="3" t="n">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>371</v>
+        <v>325</v>
       </c>
       <c r="D297" s="3" t="inlineStr"/>
       <c r="E297" s="3" t="inlineStr">
         <is>
-          <t>Noah Fant</t>
+          <t>DeMario Douglas</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>RB107</t>
+          <t>RB104</t>
         </is>
       </c>
       <c r="B298" s="3" t="n">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D298" s="3" t="inlineStr"/>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>Raheim Sanders</t>
+          <t>Jawhar Jordan</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>HOU (8)</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -9654,55 +9652,57 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="8" t="inlineStr">
-        <is>
-          <t>TE50</t>
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>WR130</t>
         </is>
       </c>
       <c r="B299" s="3" t="n">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>337</v>
-      </c>
-      <c r="D299" s="3" t="inlineStr"/>
+        <v>340</v>
+      </c>
+      <c r="D299" s="3" t="n">
+        <v>294</v>
+      </c>
       <c r="E299" s="3" t="inlineStr">
         <is>
-          <t>Eli Raridon</t>
+          <t>Treylon Burks</t>
         </is>
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>WR138</t>
+          <t>WR132</t>
         </is>
       </c>
       <c r="B300" s="3" t="n">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="C300" s="5" t="n">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="D300" s="3" t="inlineStr"/>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>Zavion Thomas</t>
+          <t>Nick Westbrook-Ikhine</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>CHI (10)</t>
+          <t>IND (13)</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -9712,89 +9712,205 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="6" t="inlineStr">
-        <is>
-          <t>RB109</t>
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>WR133</t>
         </is>
       </c>
       <c r="B301" s="3" t="n">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="C301" s="5" t="n">
-        <v>317</v>
+        <v>359</v>
       </c>
       <c r="D301" s="3" t="inlineStr"/>
       <c r="E301" s="3" t="inlineStr">
         <is>
-          <t>Phil Mafah</t>
+          <t>Savion Williams</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>DAL (14)</t>
+          <t>GB (11)</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="6" t="inlineStr">
+        <is>
+          <t>RB107</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="n">
+        <v>374</v>
+      </c>
+      <c r="C302" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="D302" s="3" t="inlineStr"/>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>Raheim Sanders</t>
+        </is>
+      </c>
+      <c r="F302" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="G302" s="3" t="inlineStr">
+        <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" s="8" t="inlineStr">
-        <is>
-          <t>TE52</t>
-        </is>
-      </c>
-      <c r="B302" s="3" t="n">
-        <v>387</v>
-      </c>
-      <c r="C302" s="5" t="n">
-        <v>319</v>
-      </c>
-      <c r="D302" s="3" t="n">
-        <v>274</v>
-      </c>
-      <c r="E302" s="3" t="inlineStr">
-        <is>
-          <t>Erick All</t>
-        </is>
-      </c>
-      <c r="F302" s="3" t="inlineStr">
-        <is>
-          <t>CIN (6)</t>
-        </is>
-      </c>
-      <c r="G302" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
     <row r="303">
-      <c r="A303" s="2" t="inlineStr">
-        <is>
-          <t>WR142</t>
+      <c r="A303" s="8" t="inlineStr">
+        <is>
+          <t>TE50</t>
         </is>
       </c>
       <c r="B303" s="3" t="n">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>364</v>
+        <v>310</v>
       </c>
       <c r="D303" s="3" t="inlineStr"/>
       <c r="E303" s="3" t="inlineStr">
         <is>
+          <t>Eli Raridon</t>
+        </is>
+      </c>
+      <c r="F303" s="3" t="inlineStr">
+        <is>
+          <t>NE (11)</t>
+        </is>
+      </c>
+      <c r="G303" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>WR138</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="n">
+        <v>383</v>
+      </c>
+      <c r="C304" s="5" t="n">
+        <v>361</v>
+      </c>
+      <c r="D304" s="3" t="inlineStr"/>
+      <c r="E304" s="3" t="inlineStr">
+        <is>
+          <t>Zavion Thomas</t>
+        </is>
+      </c>
+      <c r="F304" s="3" t="inlineStr">
+        <is>
+          <t>CHI (10)</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="6" t="inlineStr">
+        <is>
+          <t>RB109</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="n">
+        <v>386</v>
+      </c>
+      <c r="C305" s="5" t="n">
+        <v>318</v>
+      </c>
+      <c r="D305" s="3" t="inlineStr"/>
+      <c r="E305" s="3" t="inlineStr">
+        <is>
+          <t>Phil Mafah</t>
+        </is>
+      </c>
+      <c r="F305" s="3" t="inlineStr">
+        <is>
+          <t>DAL (14)</t>
+        </is>
+      </c>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="8" t="inlineStr">
+        <is>
+          <t>TE52</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="n">
+        <v>387</v>
+      </c>
+      <c r="C306" s="5" t="n">
+        <v>327</v>
+      </c>
+      <c r="D306" s="3" t="n">
+        <v>278</v>
+      </c>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>Erick All</t>
+        </is>
+      </c>
+      <c r="F306" s="3" t="inlineStr">
+        <is>
+          <t>CIN (6)</t>
+        </is>
+      </c>
+      <c r="G306" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>WR142</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="n">
+        <v>395</v>
+      </c>
+      <c r="C307" s="5" t="n">
+        <v>365</v>
+      </c>
+      <c r="D307" s="3" t="inlineStr"/>
+      <c r="E307" s="3" t="inlineStr">
+        <is>
           <t>Jordan Whittington</t>
         </is>
       </c>
-      <c r="F303" s="3" t="inlineStr">
+      <c r="F307" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="G303" s="3" t="inlineStr">
+      <c r="G307" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G303"/>
+  <dimension ref="A1:G307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>8</v>
@@ -761,7 +761,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>6</v>
@@ -795,7 +795,7 @@
         <v>12</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>23</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>22</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>17</v>
@@ -981,7 +981,7 @@
         <v>21</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -1008,11 +1008,11 @@
       <c r="B17" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="C17" s="9" t="n">
-        <v>41</v>
+      <c r="C17" s="4" t="n">
+        <v>28</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>11</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -1101,11 +1101,11 @@
       <c r="B20" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="C20" s="9" t="n">
-        <v>42</v>
+      <c r="C20" s="4" t="n">
+        <v>26</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>13</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>18</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         <v>22</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>23</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>27</v>
@@ -1257,10 +1257,10 @@
         <v>24</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>29</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -1349,11 +1349,11 @@
       <c r="B28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C28" s="4" t="n">
-        <v>33</v>
+      <c r="C28" s="5" t="n">
+        <v>27</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -1443,10 +1443,10 @@
         <v>30</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
         <v>31</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>32</v>
       </c>
       <c r="C33" s="9" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>51</v>
@@ -1539,7 +1539,7 @@
         <v>65</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1567,10 +1567,10 @@
         <v>34</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -1598,10 +1598,10 @@
         <v>35</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>19</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -1659,11 +1659,11 @@
       <c r="B38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="C38" s="7" t="n">
-        <v>27</v>
+      <c r="C38" s="11" t="n">
+        <v>32</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>35</v>
@@ -1722,10 +1722,10 @@
         <v>39</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -1753,10 +1753,10 @@
         <v>40</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -1783,11 +1783,11 @@
       <c r="B42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="C42" s="7" t="n">
-        <v>26</v>
+      <c r="C42" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>43</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1845,11 +1845,11 @@
       <c r="B44" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="C44" s="9" t="n">
-        <v>57</v>
+      <c r="C44" s="4" t="n">
+        <v>53</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>44</v>
       </c>
       <c r="C45" s="9" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -1907,8 +1907,8 @@
       <c r="B46" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="C46" s="7" t="n">
-        <v>40</v>
+      <c r="C46" s="5" t="n">
+        <v>42</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>33</v>
@@ -1942,7 +1942,7 @@
         <v>49</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -1970,10 +1970,10 @@
         <v>47</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         <v>48</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -2031,11 +2031,11 @@
       <c r="B50" s="3" t="n">
         <v>49</v>
       </c>
-      <c r="C50" s="5" t="n">
-        <v>51</v>
+      <c r="C50" s="4" t="n">
+        <v>57</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>48</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -2094,10 +2094,10 @@
         <v>51</v>
       </c>
       <c r="C52" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="D52" s="3" t="n">
         <v>50</v>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>49</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -2125,10 +2125,10 @@
         <v>52</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -2155,11 +2155,11 @@
       <c r="B54" s="3" t="n">
         <v>53</v>
       </c>
-      <c r="C54" s="4" t="n">
-        <v>59</v>
+      <c r="C54" s="5" t="n">
+        <v>54</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -2187,10 +2187,10 @@
         <v>54</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>66</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
         <v>56</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
         <v>57</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         <v>58</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D60" s="3" t="n">
         <v>46</v>
@@ -2373,7 +2373,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>70</v>
@@ -2403,8 +2403,8 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="7" t="n">
-        <v>54</v>
+      <c r="C62" s="11" t="n">
+        <v>56</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>52</v>
@@ -2435,10 +2435,10 @@
         <v>62</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -2466,10 +2466,10 @@
         <v>63</v>
       </c>
       <c r="C64" s="9" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -2497,10 +2497,10 @@
         <v>64</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>67</v>
@@ -2562,7 +2562,7 @@
         <v>75</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
         <v>67</v>
       </c>
       <c r="C68" s="9" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
         <v>68</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -2682,11 +2682,11 @@
       <c r="B71" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C71" s="11" t="n">
-        <v>63</v>
+      <c r="C71" s="7" t="n">
+        <v>61</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -2714,10 +2714,10 @@
         <v>71</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -2745,10 +2745,10 @@
         <v>72</v>
       </c>
       <c r="C73" s="9" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -2775,11 +2775,11 @@
       <c r="B74" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="C74" s="4" t="n">
+      <c r="C74" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="D74" s="3" t="n">
         <v>78</v>
-      </c>
-      <c r="D74" s="3" t="n">
-        <v>81</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -2806,11 +2806,11 @@
       <c r="B75" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="C75" s="9" t="n">
-        <v>95</v>
+      <c r="C75" s="4" t="n">
+        <v>86</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -2838,10 +2838,10 @@
         <v>75</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
@@ -2869,10 +2869,10 @@
         <v>76</v>
       </c>
       <c r="C77" s="9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>77</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D78" s="3" t="n">
         <v>80</v>
@@ -2930,11 +2930,11 @@
       <c r="B79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C79" s="11" t="n">
-        <v>72</v>
+      <c r="C79" s="5" t="n">
+        <v>78</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D80" s="3" t="n">
         <v>68</v>
@@ -2992,11 +2992,11 @@
       <c r="B81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="C81" s="4" t="n">
-        <v>85</v>
+      <c r="C81" s="9" t="n">
+        <v>94</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D82" s="3" t="n">
         <v>69</v>
@@ -3054,11 +3054,11 @@
       <c r="B83" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="C83" s="9" t="n">
-        <v>127</v>
+      <c r="C83" s="5" t="n">
+        <v>99</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -3086,10 +3086,10 @@
         <v>83</v>
       </c>
       <c r="C84" s="9" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -3116,11 +3116,11 @@
       <c r="B85" s="3" t="n">
         <v>84</v>
       </c>
-      <c r="C85" s="7" t="n">
-        <v>74</v>
+      <c r="C85" s="5" t="n">
+        <v>92</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
@@ -3148,10 +3148,10 @@
         <v>85</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -3178,11 +3178,11 @@
       <c r="B87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="C87" s="5" t="n">
-        <v>77</v>
+      <c r="C87" s="9" t="n">
+        <v>107</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -3210,10 +3210,10 @@
         <v>87</v>
       </c>
       <c r="C88" s="9" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
@@ -3241,10 +3241,10 @@
         <v>88</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
@@ -3272,10 +3272,10 @@
         <v>89</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
@@ -3303,10 +3303,10 @@
         <v>90</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -3334,10 +3334,10 @@
         <v>91</v>
       </c>
       <c r="C92" s="9" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>47</v>
@@ -3396,10 +3396,10 @@
         <v>93</v>
       </c>
       <c r="C94" s="9" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
@@ -3427,10 +3427,10 @@
         <v>94</v>
       </c>
       <c r="C95" s="9" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
@@ -3458,10 +3458,10 @@
         <v>95</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
@@ -3489,10 +3489,10 @@
         <v>96</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>97</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         <v>98</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
@@ -3582,10 +3582,10 @@
         <v>99</v>
       </c>
       <c r="C100" s="9" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
@@ -3613,10 +3613,10 @@
         <v>101</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
@@ -3644,10 +3644,10 @@
         <v>102</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
         <v>103</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
@@ -3706,10 +3706,10 @@
         <v>104</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>105</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>154</v>
@@ -3768,10 +3768,10 @@
         <v>106</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         <v>107</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
@@ -3830,10 +3830,10 @@
         <v>108</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
@@ -3860,11 +3860,11 @@
       <c r="B109" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="C109" s="5" t="n">
-        <v>114</v>
+      <c r="C109" s="9" t="n">
+        <v>123</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
@@ -3891,11 +3891,11 @@
       <c r="B110" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="C110" s="7" t="n">
-        <v>98</v>
+      <c r="C110" s="11" t="n">
+        <v>104</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -3922,11 +3922,11 @@
       <c r="B111" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="C111" s="5" t="n">
-        <v>125</v>
+      <c r="C111" s="7" t="n">
+        <v>97</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>93</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
@@ -3985,10 +3985,10 @@
         <v>113</v>
       </c>
       <c r="C113" s="7" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
@@ -4016,10 +4016,10 @@
         <v>114</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
@@ -4046,11 +4046,11 @@
       <c r="B115" s="3" t="n">
         <v>115</v>
       </c>
-      <c r="C115" s="11" t="n">
-        <v>108</v>
+      <c r="C115" s="7" t="n">
+        <v>96</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
@@ -4077,11 +4077,11 @@
       <c r="B116" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="C116" s="4" t="n">
-        <v>124</v>
+      <c r="C116" s="9" t="n">
+        <v>137</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
@@ -4109,10 +4109,10 @@
         <v>117</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
@@ -4140,10 +4140,10 @@
         <v>118</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
@@ -4170,11 +4170,11 @@
       <c r="B119" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="C119" s="5" t="n">
-        <v>119</v>
+      <c r="C119" s="11" t="n">
+        <v>113</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         <v>120</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
@@ -4233,10 +4233,10 @@
         <v>121</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
@@ -4264,10 +4264,10 @@
         <v>122</v>
       </c>
       <c r="C122" s="9" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
@@ -4295,10 +4295,10 @@
         <v>123</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
@@ -4326,10 +4326,10 @@
         <v>124</v>
       </c>
       <c r="C124" s="7" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
@@ -4356,11 +4356,11 @@
       <c r="B125" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="C125" s="7" t="n">
-        <v>102</v>
+      <c r="C125" s="5" t="n">
+        <v>126</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
@@ -4387,11 +4387,11 @@
       <c r="B126" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="C126" s="4" t="n">
-        <v>135</v>
+      <c r="C126" s="7" t="n">
+        <v>82</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>120</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>128</v>
       </c>
       <c r="C128" s="7" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D128" s="3" t="n">
         <v>76</v>
@@ -4480,11 +4480,11 @@
       <c r="B129" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="C129" s="7" t="n">
-        <v>117</v>
+      <c r="C129" s="9" t="n">
+        <v>201</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
@@ -4512,10 +4512,10 @@
         <v>130</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
@@ -4543,10 +4543,10 @@
         <v>131</v>
       </c>
       <c r="C131" s="9" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
@@ -4573,11 +4573,11 @@
       <c r="B132" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="C132" s="5" t="n">
-        <v>136</v>
+      <c r="C132" s="4" t="n">
+        <v>141</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
@@ -4605,10 +4605,10 @@
         <v>133</v>
       </c>
       <c r="C133" s="7" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
@@ -4636,10 +4636,10 @@
         <v>134</v>
       </c>
       <c r="C134" s="9" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
@@ -4667,10 +4667,10 @@
         <v>135</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
@@ -4698,10 +4698,10 @@
         <v>136</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
@@ -4729,10 +4729,10 @@
         <v>137</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
@@ -4760,10 +4760,10 @@
         <v>138</v>
       </c>
       <c r="C138" s="9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
@@ -4790,11 +4790,11 @@
       <c r="B139" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C139" s="5" t="n">
-        <v>161</v>
+      <c r="C139" s="7" t="n">
+        <v>125</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
@@ -4821,11 +4821,11 @@
       <c r="B140" s="3" t="n">
         <v>140</v>
       </c>
-      <c r="C140" s="7" t="n">
-        <v>128</v>
+      <c r="C140" s="5" t="n">
+        <v>148</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
@@ -4853,10 +4853,10 @@
         <v>141</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
@@ -4884,10 +4884,10 @@
         <v>142</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
@@ -4915,10 +4915,10 @@
         <v>143</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
@@ -4946,10 +4946,10 @@
         <v>144</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>145</v>
       </c>
       <c r="C145" s="9" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
@@ -5008,10 +5008,10 @@
         <v>146</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
         <v>148</v>
       </c>
       <c r="C148" s="9" t="n">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
@@ -5100,11 +5100,11 @@
       <c r="B149" s="3" t="n">
         <v>149</v>
       </c>
-      <c r="C149" s="11" t="n">
-        <v>106</v>
+      <c r="C149" s="5" t="n">
+        <v>151</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
@@ -5132,10 +5132,10 @@
         <v>150</v>
       </c>
       <c r="C150" s="4" t="n">
-        <v>202</v>
+        <v>255</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         <v>151</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
@@ -5194,10 +5194,10 @@
         <v>152</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
@@ -5225,10 +5225,10 @@
         <v>153</v>
       </c>
       <c r="C153" s="4" t="n">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
@@ -5256,10 +5256,10 @@
         <v>154</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
@@ -5287,10 +5287,10 @@
         <v>155</v>
       </c>
       <c r="C155" s="4" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
@@ -5317,11 +5317,11 @@
       <c r="B156" s="3" t="n">
         <v>156</v>
       </c>
-      <c r="C156" s="11" t="n">
-        <v>146</v>
+      <c r="C156" s="5" t="n">
+        <v>174</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
@@ -5349,10 +5349,10 @@
         <v>158</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         <v>159</v>
       </c>
       <c r="C158" s="7" t="n">
-        <v>144</v>
+        <v>101</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>190</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
@@ -5442,10 +5442,10 @@
         <v>161</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
@@ -5473,10 +5473,10 @@
         <v>162</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         <v>164</v>
       </c>
       <c r="C162" s="4" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
@@ -5535,10 +5535,10 @@
         <v>165</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
@@ -5566,10 +5566,10 @@
         <v>166</v>
       </c>
       <c r="C164" s="4" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
         <v>167</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
@@ -5627,11 +5627,11 @@
       <c r="B166" s="3" t="n">
         <v>169</v>
       </c>
-      <c r="C166" s="4" t="n">
-        <v>269</v>
+      <c r="C166" s="5" t="n">
+        <v>177</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
@@ -5659,10 +5659,10 @@
         <v>170</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
@@ -5690,10 +5690,10 @@
         <v>173</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D168" s="3" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
@@ -5721,10 +5721,10 @@
         <v>174</v>
       </c>
       <c r="C169" s="4" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
@@ -5752,10 +5752,10 @@
         <v>175</v>
       </c>
       <c r="C170" s="4" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>171</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
@@ -5814,10 +5814,10 @@
         <v>177</v>
       </c>
       <c r="C172" s="7" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -5845,10 +5845,10 @@
         <v>178</v>
       </c>
       <c r="C173" s="4" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
@@ -5879,7 +5879,7 @@
         <v>237</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
@@ -5907,10 +5907,10 @@
         <v>185</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
@@ -5938,10 +5938,10 @@
         <v>186</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
@@ -5969,10 +5969,10 @@
         <v>187</v>
       </c>
       <c r="C177" s="4" t="n">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -6000,10 +6000,10 @@
         <v>188</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>279</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
@@ -6061,11 +6061,11 @@
       <c r="B180" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="C180" s="4" t="n">
-        <v>273</v>
+      <c r="C180" s="5" t="n">
+        <v>195</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
@@ -6093,10 +6093,10 @@
         <v>194</v>
       </c>
       <c r="C181" s="4" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
@@ -6123,11 +6123,11 @@
       <c r="B182" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="C182" s="11" t="n">
-        <v>163</v>
+      <c r="C182" s="5" t="n">
+        <v>176</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
@@ -6154,11 +6154,11 @@
       <c r="B183" s="3" t="n">
         <v>196</v>
       </c>
-      <c r="C183" s="5" t="n">
-        <v>174</v>
+      <c r="C183" s="11" t="n">
+        <v>159</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
@@ -6186,10 +6186,10 @@
         <v>197</v>
       </c>
       <c r="C184" s="4" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
@@ -6216,11 +6216,11 @@
       <c r="B185" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="C185" s="5" t="n">
-        <v>170</v>
+      <c r="C185" s="11" t="n">
+        <v>161</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
@@ -6248,10 +6248,10 @@
         <v>201</v>
       </c>
       <c r="C186" s="11" t="n">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
@@ -6279,10 +6279,10 @@
         <v>202</v>
       </c>
       <c r="C187" s="5" t="n">
-        <v>172</v>
+        <v>202</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
@@ -6310,10 +6310,10 @@
         <v>204</v>
       </c>
       <c r="C188" s="11" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
@@ -6341,10 +6341,10 @@
         <v>205</v>
       </c>
       <c r="C189" s="5" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
@@ -6372,10 +6372,10 @@
         <v>206</v>
       </c>
       <c r="C190" s="4" t="n">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
@@ -6403,10 +6403,10 @@
         <v>207</v>
       </c>
       <c r="C191" s="4" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>173</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
@@ -6465,10 +6465,10 @@
         <v>212</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>211</v>
+        <v>240</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
@@ -6496,10 +6496,10 @@
         <v>213</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
@@ -6527,10 +6527,10 @@
         <v>217</v>
       </c>
       <c r="C195" s="4" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
@@ -6558,10 +6558,10 @@
         <v>219</v>
       </c>
       <c r="C196" s="5" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
@@ -6589,10 +6589,10 @@
         <v>221</v>
       </c>
       <c r="C197" s="4" t="n">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
@@ -6619,11 +6619,11 @@
       <c r="B198" s="3" t="n">
         <v>222</v>
       </c>
-      <c r="C198" s="5" t="n">
-        <v>240</v>
+      <c r="C198" s="4" t="n">
+        <v>269</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>218</v>
       </c>
       <c r="D199" s="3" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>224</v>
       </c>
       <c r="C200" s="4" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D200" s="3" t="inlineStr"/>
       <c r="E200" s="3" t="inlineStr">
@@ -6711,10 +6711,10 @@
         <v>225</v>
       </c>
       <c r="C201" s="7" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
@@ -6741,11 +6741,11 @@
       <c r="B202" s="3" t="n">
         <v>228</v>
       </c>
-      <c r="C202" s="5" t="n">
-        <v>257</v>
+      <c r="C202" s="4" t="n">
+        <v>263</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
@@ -6772,11 +6772,11 @@
       <c r="B203" s="3" t="n">
         <v>230</v>
       </c>
-      <c r="C203" s="5" t="n">
-        <v>224</v>
+      <c r="C203" s="11" t="n">
+        <v>192</v>
       </c>
       <c r="D203" s="3" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
@@ -6803,11 +6803,11 @@
       <c r="B204" s="3" t="n">
         <v>232</v>
       </c>
-      <c r="C204" s="5" t="n">
-        <v>266</v>
+      <c r="C204" s="4" t="n">
+        <v>299</v>
       </c>
       <c r="D204" s="3" t="n">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
@@ -6835,10 +6835,10 @@
         <v>233</v>
       </c>
       <c r="C205" s="4" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
@@ -6866,10 +6866,10 @@
         <v>234</v>
       </c>
       <c r="C206" s="5" t="n">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
@@ -6897,10 +6897,10 @@
         <v>235</v>
       </c>
       <c r="C207" s="5" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         <v>237</v>
       </c>
       <c r="C208" s="5" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
@@ -6959,10 +6959,10 @@
         <v>238</v>
       </c>
       <c r="C209" s="5" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
@@ -6989,11 +6989,11 @@
       <c r="B210" s="3" t="n">
         <v>239</v>
       </c>
-      <c r="C210" s="5" t="n">
-        <v>260</v>
+      <c r="C210" s="4" t="n">
+        <v>281</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
@@ -7021,10 +7021,10 @@
         <v>240</v>
       </c>
       <c r="C211" s="5" t="n">
-        <v>238</v>
+        <v>270</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>291</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
@@ -7082,11 +7082,11 @@
       <c r="B213" s="3" t="n">
         <v>242</v>
       </c>
-      <c r="C213" s="4" t="n">
-        <v>300</v>
+      <c r="C213" s="5" t="n">
+        <v>264</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
@@ -7114,10 +7114,10 @@
         <v>243</v>
       </c>
       <c r="C214" s="5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
@@ -7145,10 +7145,10 @@
         <v>244</v>
       </c>
       <c r="C215" s="4" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D215" s="3" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
@@ -7176,10 +7176,10 @@
         <v>245</v>
       </c>
       <c r="C216" s="11" t="n">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="D216" s="3" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
@@ -7206,11 +7206,11 @@
       <c r="B217" s="3" t="n">
         <v>246</v>
       </c>
-      <c r="C217" s="5" t="n">
-        <v>281</v>
+      <c r="C217" s="4" t="n">
+        <v>288</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
@@ -7238,10 +7238,10 @@
         <v>248</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
@@ -7269,10 +7269,10 @@
         <v>249</v>
       </c>
       <c r="C219" s="5" t="n">
-        <v>277</v>
+        <v>204</v>
       </c>
       <c r="D219" s="3" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>250</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="D220" s="3" t="inlineStr"/>
       <c r="E220" s="3" t="inlineStr">
@@ -7329,10 +7329,10 @@
         <v>251</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>285</v>
+        <v>203</v>
       </c>
       <c r="D221" s="3" t="n">
-        <v>271</v>
+        <v>208</v>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
@@ -7360,10 +7360,10 @@
         <v>252</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D222" s="3" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
@@ -7391,10 +7391,10 @@
         <v>254</v>
       </c>
       <c r="C223" s="5" t="n">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="D223" s="3" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
@@ -7451,10 +7451,10 @@
         <v>256</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="D225" s="3" t="n">
-        <v>294</v>
+        <v>232</v>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
@@ -7482,10 +7482,10 @@
         <v>257</v>
       </c>
       <c r="C226" s="5" t="n">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="D226" s="3" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>258</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
@@ -7542,11 +7542,9 @@
         <v>259</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>281</v>
-      </c>
-      <c r="D228" s="3" t="n">
-        <v>301</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="D228" s="3" t="inlineStr"/>
       <c r="E228" s="3" t="inlineStr">
         <is>
           <t>Eli Stowers</t>
@@ -7573,10 +7571,10 @@
         <v>260</v>
       </c>
       <c r="C229" s="5" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="D229" s="3" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
@@ -7604,10 +7602,10 @@
         <v>261</v>
       </c>
       <c r="C230" s="4" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D230" s="3" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
@@ -7634,11 +7632,11 @@
       <c r="B231" s="3" t="n">
         <v>262</v>
       </c>
-      <c r="C231" s="5" t="n">
-        <v>203</v>
+      <c r="C231" s="11" t="n">
+        <v>196</v>
       </c>
       <c r="D231" s="3" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
@@ -7669,7 +7667,7 @@
         <v>261</v>
       </c>
       <c r="D232" s="3" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
@@ -7697,10 +7695,10 @@
         <v>265</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D233" s="3" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
@@ -7728,10 +7726,10 @@
         <v>266</v>
       </c>
       <c r="C234" s="5" t="n">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
@@ -7759,10 +7757,10 @@
         <v>267</v>
       </c>
       <c r="C235" s="5" t="n">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="D235" s="3" t="n">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
@@ -7790,7 +7788,7 @@
         <v>268</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="D236" s="3" t="inlineStr"/>
       <c r="E236" s="3" t="inlineStr">
@@ -7819,10 +7817,10 @@
         <v>269</v>
       </c>
       <c r="C237" s="5" t="n">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="D237" s="3" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
@@ -7850,10 +7848,10 @@
         <v>270</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D238" s="3" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
@@ -7881,10 +7879,10 @@
         <v>271</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>255</v>
+        <v>299</v>
       </c>
       <c r="D239" s="3" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
@@ -7912,10 +7910,10 @@
         <v>272</v>
       </c>
       <c r="C240" s="5" t="n">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="D240" s="3" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
@@ -7942,8 +7940,8 @@
       <c r="B241" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="C241" s="5" t="n">
-        <v>313</v>
+      <c r="C241" s="4" t="n">
+        <v>341</v>
       </c>
       <c r="D241" s="3" t="inlineStr"/>
       <c r="E241" s="3" t="inlineStr">
@@ -7972,7 +7970,7 @@
         <v>274</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D242" s="3" t="inlineStr"/>
       <c r="E242" s="3" t="inlineStr">
@@ -8001,7 +7999,7 @@
         <v>275</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D243" s="3" t="inlineStr"/>
       <c r="E243" s="3" t="inlineStr">
@@ -8033,7 +8031,7 @@
         <v>275</v>
       </c>
       <c r="D244" s="3" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
@@ -8061,10 +8059,10 @@
         <v>277</v>
       </c>
       <c r="C245" s="5" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D245" s="3" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
@@ -8091,11 +8089,11 @@
       <c r="B246" s="3" t="n">
         <v>278</v>
       </c>
-      <c r="C246" s="11" t="n">
-        <v>193</v>
+      <c r="C246" s="5" t="n">
+        <v>219</v>
       </c>
       <c r="D246" s="3" t="n">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
@@ -8123,7 +8121,7 @@
         <v>280</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
@@ -8152,7 +8150,7 @@
         <v>281</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D248" s="3" t="inlineStr"/>
       <c r="E248" s="3" t="inlineStr">
@@ -8181,10 +8179,10 @@
         <v>282</v>
       </c>
       <c r="C249" s="5" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D249" s="3" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
@@ -8212,10 +8210,10 @@
         <v>283</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D250" s="3" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
@@ -8243,7 +8241,7 @@
         <v>284</v>
       </c>
       <c r="C251" s="5" t="n">
-        <v>312</v>
+        <v>287</v>
       </c>
       <c r="D251" s="3" t="inlineStr"/>
       <c r="E251" s="3" t="inlineStr">
@@ -8272,10 +8270,10 @@
         <v>285</v>
       </c>
       <c r="C252" s="5" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="D252" s="3" t="n">
-        <v>300</v>
+        <v>218</v>
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
@@ -8303,7 +8301,7 @@
         <v>288</v>
       </c>
       <c r="C253" s="4" t="n">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="D253" s="3" t="inlineStr"/>
       <c r="E253" s="3" t="inlineStr">
@@ -8332,7 +8330,7 @@
         <v>289</v>
       </c>
       <c r="C254" s="5" t="n">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D254" s="3" t="inlineStr"/>
       <c r="E254" s="3" t="inlineStr">
@@ -8361,10 +8359,10 @@
         <v>290</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D255" s="3" t="n">
-        <v>251</v>
+        <v>147</v>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
@@ -8391,8 +8389,8 @@
       <c r="B256" s="3" t="n">
         <v>292</v>
       </c>
-      <c r="C256" s="5" t="n">
-        <v>335</v>
+      <c r="C256" s="4" t="n">
+        <v>337</v>
       </c>
       <c r="D256" s="3" t="inlineStr"/>
       <c r="E256" s="3" t="inlineStr">
@@ -8424,7 +8422,7 @@
         <v>239</v>
       </c>
       <c r="D257" s="3" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
@@ -8452,7 +8450,7 @@
         <v>294</v>
       </c>
       <c r="C258" s="4" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
@@ -8481,7 +8479,7 @@
         <v>296</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
@@ -8510,7 +8508,7 @@
         <v>297</v>
       </c>
       <c r="C260" s="5" t="n">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D260" s="3" t="inlineStr"/>
       <c r="E260" s="3" t="inlineStr">
@@ -8539,10 +8537,10 @@
         <v>298</v>
       </c>
       <c r="C261" s="5" t="n">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="D261" s="3" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
@@ -8570,10 +8568,10 @@
         <v>299</v>
       </c>
       <c r="C262" s="5" t="n">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="D262" s="3" t="n">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
@@ -8604,7 +8602,7 @@
         <v>280</v>
       </c>
       <c r="D263" s="3" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
@@ -8631,8 +8629,8 @@
       <c r="B264" s="3" t="n">
         <v>301</v>
       </c>
-      <c r="C264" s="5" t="n">
-        <v>323</v>
+      <c r="C264" s="4" t="n">
+        <v>367</v>
       </c>
       <c r="D264" s="3" t="inlineStr"/>
       <c r="E264" s="3" t="inlineStr">
@@ -8664,7 +8662,7 @@
         <v>253</v>
       </c>
       <c r="D265" s="3" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
@@ -8692,7 +8690,7 @@
         <v>304</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D266" s="3" t="inlineStr"/>
       <c r="E266" s="3" t="inlineStr">
@@ -8721,7 +8719,7 @@
         <v>305</v>
       </c>
       <c r="C267" s="5" t="n">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D267" s="3" t="inlineStr"/>
       <c r="E267" s="3" t="inlineStr">
@@ -8750,10 +8748,10 @@
         <v>306</v>
       </c>
       <c r="C268" s="11" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="D268" s="3" t="n">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="E268" s="3" t="inlineStr">
         <is>
@@ -8781,7 +8779,7 @@
         <v>309</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D269" s="3" t="inlineStr"/>
       <c r="E269" s="3" t="inlineStr">
@@ -8810,7 +8808,7 @@
         <v>310</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
@@ -8839,7 +8837,7 @@
         <v>311</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>294</v>
+        <v>320</v>
       </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr">
@@ -8868,7 +8866,7 @@
         <v>312</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
@@ -8897,7 +8895,7 @@
         <v>314</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="D273" s="3" t="inlineStr"/>
       <c r="E273" s="3" t="inlineStr">
@@ -8926,10 +8924,10 @@
         <v>316</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D274" s="3" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E274" s="3" t="inlineStr">
         <is>
@@ -8957,7 +8955,7 @@
         <v>317</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>296</v>
+        <v>352</v>
       </c>
       <c r="D275" s="3" t="inlineStr"/>
       <c r="E275" s="3" t="inlineStr">
@@ -8977,88 +8975,86 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="8" t="inlineStr">
+      <c r="A276" s="6" t="inlineStr">
+        <is>
+          <t>RB98</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="n">
+        <v>321</v>
+      </c>
+      <c r="C276" s="5" t="n">
+        <v>348</v>
+      </c>
+      <c r="D276" s="3" t="inlineStr"/>
+      <c r="E276" s="3" t="inlineStr">
+        <is>
+          <t>Audric Estime</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="G276" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="8" t="inlineStr">
         <is>
           <t>TE39</t>
         </is>
       </c>
-      <c r="B276" s="3" t="n">
+      <c r="B277" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="C276" s="5" t="n">
+      <c r="C277" s="5" t="n">
         <v>282</v>
       </c>
-      <c r="D276" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="E276" s="3" t="inlineStr">
+      <c r="D277" s="3" t="n">
+        <v>277</v>
+      </c>
+      <c r="E277" s="3" t="inlineStr">
         <is>
           <t>Darnell Washington</t>
         </is>
       </c>
-      <c r="F276" s="3" t="inlineStr">
+      <c r="F277" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="G276" s="3" t="inlineStr">
+      <c r="G277" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="10" t="inlineStr">
-        <is>
-          <t>QB36</t>
-        </is>
-      </c>
-      <c r="B277" s="3" t="n">
-        <v>327</v>
-      </c>
-      <c r="C277" s="5" t="n">
-        <v>368</v>
-      </c>
-      <c r="D277" s="3" t="inlineStr"/>
-      <c r="E277" s="3" t="inlineStr">
-        <is>
-          <t>J.J. McCarthy</t>
-        </is>
-      </c>
-      <c r="F277" s="3" t="inlineStr">
-        <is>
-          <t>MIN (6)</t>
-        </is>
-      </c>
-      <c r="G277" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>WR114</t>
+          <t>WR112</t>
         </is>
       </c>
       <c r="B278" s="3" t="n">
-        <v>328</v>
-      </c>
-      <c r="C278" s="5" t="n">
-        <v>284</v>
-      </c>
-      <c r="D278" s="3" t="n">
-        <v>266</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="C278" s="4" t="n">
+        <v>375</v>
+      </c>
+      <c r="D278" s="3" t="inlineStr"/>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>Luke McCaffrey</t>
+          <t>Cedric Tillman</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
@@ -9068,55 +9064,57 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="inlineStr">
-        <is>
-          <t>WR116</t>
+      <c r="A279" s="10" t="inlineStr">
+        <is>
+          <t>QB36</t>
         </is>
       </c>
       <c r="B279" s="3" t="n">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>266</v>
+        <v>369</v>
       </c>
       <c r="D279" s="3" t="inlineStr"/>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>ATL (11)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>WR117</t>
+          <t>WR114</t>
         </is>
       </c>
       <c r="B280" s="3" t="n">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>352</v>
-      </c>
-      <c r="D280" s="3" t="inlineStr"/>
+        <v>294</v>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>270</v>
+      </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Jalen Royals</t>
+          <t>Luke McCaffrey</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>KC (5)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -9126,13 +9124,13 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="8" t="inlineStr">
-        <is>
-          <t>TE40</t>
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>WR115</t>
         </is>
       </c>
       <c r="B281" s="3" t="n">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C281" s="5" t="n">
         <v>370</v>
@@ -9140,43 +9138,41 @@
       <c r="D281" s="3" t="inlineStr"/>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>Max Klare</t>
+          <t>Tez Johnson</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>TB (10)</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>WR118</t>
+          <t>WR116</t>
         </is>
       </c>
       <c r="B282" s="3" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C282" s="5" t="n">
-        <v>201</v>
-      </c>
-      <c r="D282" s="3" t="n">
-        <v>207</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="D282" s="3" t="inlineStr"/>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>Caleb Douglas</t>
+          <t>Jahan Dotson</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>ATL (11)</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -9188,26 +9184,24 @@
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>WR120</t>
+          <t>WR117</t>
         </is>
       </c>
       <c r="B283" s="3" t="n">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C283" s="5" t="n">
-        <v>297</v>
-      </c>
-      <c r="D283" s="3" t="n">
-        <v>280</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="D283" s="3" t="inlineStr"/>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Jalen Royals</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
@@ -9217,171 +9211,177 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="inlineStr">
-        <is>
-          <t>WR122</t>
+      <c r="A284" s="8" t="inlineStr">
+        <is>
+          <t>TE40</t>
         </is>
       </c>
       <c r="B284" s="3" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="D284" s="3" t="inlineStr"/>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Joshua Palmer</t>
+          <t>Max Klare</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="8" t="inlineStr">
-        <is>
-          <t>TE41</t>
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>WR118</t>
         </is>
       </c>
       <c r="B285" s="3" t="n">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>362</v>
-      </c>
-      <c r="D285" s="3" t="inlineStr"/>
+        <v>224</v>
+      </c>
+      <c r="D285" s="3" t="n">
+        <v>209</v>
+      </c>
       <c r="E285" s="3" t="inlineStr">
         <is>
-          <t>Michael Mayer</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="8" t="inlineStr">
-        <is>
-          <t>TE42</t>
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>WR119</t>
         </is>
       </c>
       <c r="B286" s="3" t="n">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>330</v>
-      </c>
-      <c r="D286" s="3" t="inlineStr"/>
+        <v>286</v>
+      </c>
+      <c r="D286" s="3" t="n">
+        <v>269</v>
+      </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>Elijah Arroyo</t>
+          <t>Calvin Austin</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>NYG (8)</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="8" t="inlineStr">
-        <is>
-          <t>TE43</t>
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>WR120</t>
         </is>
       </c>
       <c r="B287" s="3" t="n">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>307</v>
-      </c>
-      <c r="D287" s="3" t="inlineStr"/>
+        <v>359</v>
+      </c>
+      <c r="D287" s="3" t="n">
+        <v>299</v>
+      </c>
       <c r="E287" s="3" t="inlineStr">
         <is>
-          <t>Tyler Higbee</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="10" t="inlineStr">
-        <is>
-          <t>QB37</t>
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>WR122</t>
         </is>
       </c>
       <c r="B288" s="3" t="n">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>372</v>
+        <v>331</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Joshua Palmer</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="8" t="inlineStr">
         <is>
-          <t>TE45</t>
+          <t>TE41</t>
         </is>
       </c>
       <c r="B289" s="3" t="n">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>367</v>
+        <v>328</v>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>Dawson Knox</t>
+          <t>Michael Mayer</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -9391,55 +9391,55 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="10" t="inlineStr">
-        <is>
-          <t>QB38</t>
+      <c r="A290" s="8" t="inlineStr">
+        <is>
+          <t>TE42</t>
         </is>
       </c>
       <c r="B290" s="3" t="n">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="D290" s="3" t="inlineStr"/>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Carson Beck</t>
+          <t>Elijah Arroyo</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>ARI (14)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="8" t="inlineStr">
         <is>
-          <t>TE47</t>
+          <t>TE43</t>
         </is>
       </c>
       <c r="B291" s="3" t="n">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>366</v>
+        <v>310</v>
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>Cole Kmet</t>
+          <t>Tyler Higbee</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>CHI (10)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -9449,144 +9449,142 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="inlineStr">
-        <is>
-          <t>WR124</t>
+      <c r="A292" s="10" t="inlineStr">
+        <is>
+          <t>QB37</t>
         </is>
       </c>
       <c r="B292" s="3" t="n">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>331</v>
+        <v>378</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>Brenen Thompson</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="inlineStr">
-        <is>
-          <t>WR125</t>
+      <c r="A293" s="8" t="inlineStr">
+        <is>
+          <t>TE45</t>
         </is>
       </c>
       <c r="B293" s="3" t="n">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>339</v>
+        <v>376</v>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr">
         <is>
-          <t>DeMario Douglas</t>
+          <t>Dawson Knox</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="6" t="inlineStr">
-        <is>
-          <t>RB104</t>
+      <c r="A294" s="10" t="inlineStr">
+        <is>
+          <t>QB38</t>
         </is>
       </c>
       <c r="B294" s="3" t="n">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>Jawhar Jordan</t>
+          <t>Carson Beck</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>HOU (8)</t>
+          <t>ARI (14)</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="inlineStr">
-        <is>
-          <t>WR130</t>
+      <c r="A295" s="8" t="inlineStr">
+        <is>
+          <t>TE47</t>
         </is>
       </c>
       <c r="B295" s="3" t="n">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>338</v>
-      </c>
-      <c r="D295" s="3" t="n">
-        <v>293</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="D295" s="3" t="inlineStr"/>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>Treylon Burks</t>
+          <t>Cole Kmet</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>CHI (10)</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>WR133</t>
+          <t>WR124</t>
         </is>
       </c>
       <c r="B296" s="3" t="n">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="D296" s="3" t="inlineStr"/>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>Savion Williams</t>
+          <t>Brenen Thompson</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>GB (11)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -9596,55 +9594,55 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="8" t="inlineStr">
-        <is>
-          <t>TE49</t>
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>WR125</t>
         </is>
       </c>
       <c r="B297" s="3" t="n">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="D297" s="3" t="inlineStr"/>
       <c r="E297" s="3" t="inlineStr">
         <is>
-          <t>Noah Fant</t>
+          <t>DeMario Douglas</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>RB107</t>
+          <t>RB104</t>
         </is>
       </c>
       <c r="B298" s="3" t="n">
-        <v>374</v>
+        <v>360</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D298" s="3" t="inlineStr"/>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>Raheim Sanders</t>
+          <t>Jawhar Jordan</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>HOU (8)</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -9654,55 +9652,57 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="8" t="inlineStr">
-        <is>
-          <t>TE50</t>
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>WR130</t>
         </is>
       </c>
       <c r="B299" s="3" t="n">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>337</v>
-      </c>
-      <c r="D299" s="3" t="inlineStr"/>
+        <v>338</v>
+      </c>
+      <c r="D299" s="3" t="n">
+        <v>294</v>
+      </c>
       <c r="E299" s="3" t="inlineStr">
         <is>
-          <t>Eli Raridon</t>
+          <t>Treylon Burks</t>
         </is>
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>WR138</t>
+          <t>WR132</t>
         </is>
       </c>
       <c r="B300" s="3" t="n">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="C300" s="5" t="n">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="D300" s="3" t="inlineStr"/>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>Zavion Thomas</t>
+          <t>Nick Westbrook-Ikhine</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>CHI (10)</t>
+          <t>IND (13)</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -9712,89 +9712,205 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="6" t="inlineStr">
-        <is>
-          <t>RB109</t>
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>WR133</t>
         </is>
       </c>
       <c r="B301" s="3" t="n">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="C301" s="5" t="n">
-        <v>317</v>
+        <v>358</v>
       </c>
       <c r="D301" s="3" t="inlineStr"/>
       <c r="E301" s="3" t="inlineStr">
         <is>
-          <t>Phil Mafah</t>
+          <t>Savion Williams</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>DAL (14)</t>
+          <t>GB (11)</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="6" t="inlineStr">
+        <is>
+          <t>RB107</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="n">
+        <v>374</v>
+      </c>
+      <c r="C302" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="D302" s="3" t="inlineStr"/>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>Raheim Sanders</t>
+        </is>
+      </c>
+      <c r="F302" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="G302" s="3" t="inlineStr">
+        <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" s="8" t="inlineStr">
-        <is>
-          <t>TE52</t>
-        </is>
-      </c>
-      <c r="B302" s="3" t="n">
-        <v>387</v>
-      </c>
-      <c r="C302" s="5" t="n">
-        <v>319</v>
-      </c>
-      <c r="D302" s="3" t="n">
-        <v>274</v>
-      </c>
-      <c r="E302" s="3" t="inlineStr">
-        <is>
-          <t>Erick All</t>
-        </is>
-      </c>
-      <c r="F302" s="3" t="inlineStr">
-        <is>
-          <t>CIN (6)</t>
-        </is>
-      </c>
-      <c r="G302" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
     <row r="303">
-      <c r="A303" s="2" t="inlineStr">
-        <is>
-          <t>WR142</t>
+      <c r="A303" s="8" t="inlineStr">
+        <is>
+          <t>TE50</t>
         </is>
       </c>
       <c r="B303" s="3" t="n">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>364</v>
+        <v>313</v>
       </c>
       <c r="D303" s="3" t="inlineStr"/>
       <c r="E303" s="3" t="inlineStr">
         <is>
+          <t>Eli Raridon</t>
+        </is>
+      </c>
+      <c r="F303" s="3" t="inlineStr">
+        <is>
+          <t>NE (11)</t>
+        </is>
+      </c>
+      <c r="G303" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>WR138</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="n">
+        <v>383</v>
+      </c>
+      <c r="C304" s="5" t="n">
+        <v>360</v>
+      </c>
+      <c r="D304" s="3" t="inlineStr"/>
+      <c r="E304" s="3" t="inlineStr">
+        <is>
+          <t>Zavion Thomas</t>
+        </is>
+      </c>
+      <c r="F304" s="3" t="inlineStr">
+        <is>
+          <t>CHI (10)</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="6" t="inlineStr">
+        <is>
+          <t>RB109</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="n">
+        <v>386</v>
+      </c>
+      <c r="C305" s="5" t="n">
+        <v>318</v>
+      </c>
+      <c r="D305" s="3" t="inlineStr"/>
+      <c r="E305" s="3" t="inlineStr">
+        <is>
+          <t>Phil Mafah</t>
+        </is>
+      </c>
+      <c r="F305" s="3" t="inlineStr">
+        <is>
+          <t>DAL (14)</t>
+        </is>
+      </c>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="8" t="inlineStr">
+        <is>
+          <t>TE52</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="n">
+        <v>387</v>
+      </c>
+      <c r="C306" s="5" t="n">
+        <v>322</v>
+      </c>
+      <c r="D306" s="3" t="n">
+        <v>278</v>
+      </c>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
+          <t>Erick All</t>
+        </is>
+      </c>
+      <c r="F306" s="3" t="inlineStr">
+        <is>
+          <t>CIN (6)</t>
+        </is>
+      </c>
+      <c r="G306" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>WR142</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="n">
+        <v>395</v>
+      </c>
+      <c r="C307" s="5" t="n">
+        <v>363</v>
+      </c>
+      <c r="D307" s="3" t="inlineStr"/>
+      <c r="E307" s="3" t="inlineStr">
+        <is>
           <t>Jordan Whittington</t>
         </is>
       </c>
-      <c r="F303" s="3" t="inlineStr">
+      <c r="F307" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="G303" s="3" t="inlineStr">
+      <c r="G307" s="3" t="inlineStr">
         <is>
           <t>WR</t>
         </is>

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -7083,7 +7083,7 @@
         <v>242</v>
       </c>
       <c r="C213" s="5" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D213" s="3" t="n">
         <v>286</v>
@@ -7300,7 +7300,7 @@
         <v>250</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="D220" s="3" t="inlineStr"/>
       <c r="E220" s="3" t="inlineStr">
@@ -7422,7 +7422,7 @@
         <v>255</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D224" s="3" t="inlineStr"/>
       <c r="E224" s="3" t="inlineStr">
@@ -7513,7 +7513,7 @@
         <v>258</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
@@ -7542,7 +7542,7 @@
         <v>259</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D228" s="3" t="inlineStr"/>
       <c r="E228" s="3" t="inlineStr">
@@ -7571,7 +7571,7 @@
         <v>260</v>
       </c>
       <c r="C229" s="5" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D229" s="3" t="n">
         <v>292</v>
@@ -7941,7 +7941,7 @@
         <v>273</v>
       </c>
       <c r="C241" s="4" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D241" s="3" t="inlineStr"/>
       <c r="E241" s="3" t="inlineStr">
@@ -7999,7 +7999,7 @@
         <v>275</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="D243" s="3" t="inlineStr"/>
       <c r="E243" s="3" t="inlineStr">
@@ -8121,7 +8121,7 @@
         <v>280</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
@@ -8150,7 +8150,7 @@
         <v>281</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="D248" s="3" t="inlineStr"/>
       <c r="E248" s="3" t="inlineStr">
@@ -8241,7 +8241,7 @@
         <v>284</v>
       </c>
       <c r="C251" s="5" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D251" s="3" t="inlineStr"/>
       <c r="E251" s="3" t="inlineStr">
@@ -8330,7 +8330,7 @@
         <v>289</v>
       </c>
       <c r="C254" s="5" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D254" s="3" t="inlineStr"/>
       <c r="E254" s="3" t="inlineStr">
@@ -8479,7 +8479,7 @@
         <v>296</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
@@ -8508,7 +8508,7 @@
         <v>297</v>
       </c>
       <c r="C260" s="5" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D260" s="3" t="inlineStr"/>
       <c r="E260" s="3" t="inlineStr">
@@ -8630,7 +8630,7 @@
         <v>301</v>
       </c>
       <c r="C264" s="4" t="n">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="D264" s="3" t="inlineStr"/>
       <c r="E264" s="3" t="inlineStr">
@@ -8719,7 +8719,7 @@
         <v>305</v>
       </c>
       <c r="C267" s="5" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D267" s="3" t="inlineStr"/>
       <c r="E267" s="3" t="inlineStr">
@@ -8779,7 +8779,7 @@
         <v>309</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="D269" s="3" t="inlineStr"/>
       <c r="E269" s="3" t="inlineStr">
@@ -8895,7 +8895,7 @@
         <v>314</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="D273" s="3" t="inlineStr"/>
       <c r="E273" s="3" t="inlineStr">
@@ -8955,7 +8955,7 @@
         <v>317</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D275" s="3" t="inlineStr"/>
       <c r="E275" s="3" t="inlineStr">
@@ -9191,7 +9191,7 @@
         <v>331</v>
       </c>
       <c r="C283" s="5" t="n">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D283" s="3" t="inlineStr"/>
       <c r="E283" s="3" t="inlineStr">
@@ -9342,7 +9342,7 @@
         <v>337</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
@@ -9371,7 +9371,7 @@
         <v>338</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr">
@@ -9429,7 +9429,7 @@
         <v>341</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
@@ -9574,7 +9574,7 @@
         <v>350</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D296" s="3" t="inlineStr"/>
       <c r="E296" s="3" t="inlineStr">
@@ -9603,7 +9603,7 @@
         <v>351</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D297" s="3" t="inlineStr"/>
       <c r="E297" s="3" t="inlineStr">
@@ -9632,7 +9632,7 @@
         <v>360</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D298" s="3" t="inlineStr"/>
       <c r="E298" s="3" t="inlineStr">
@@ -9661,7 +9661,7 @@
         <v>363</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D299" s="3" t="n">
         <v>294</v>
@@ -9866,7 +9866,7 @@
         <v>387</v>
       </c>
       <c r="C306" s="5" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D306" s="3" t="n">
         <v>278</v>
@@ -9897,7 +9897,7 @@
         <v>395</v>
       </c>
       <c r="C307" s="5" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D307" s="3" t="inlineStr"/>
       <c r="E307" s="3" t="inlineStr">

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -120,13 +120,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -792,7 +792,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>16</v>
@@ -854,10 +854,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
         <v>12</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         <v>14</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -978,10 +978,10 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>39</v>
@@ -1071,7 +1071,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>13</v>
@@ -1102,7 +1102,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>25</v>
@@ -1133,7 +1133,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>14</v>
@@ -1163,11 +1163,11 @@
       <c r="B22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C22" s="5" t="n">
-        <v>18</v>
+      <c r="C22" s="9" t="n">
+        <v>17</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -1194,8 +1194,8 @@
       <c r="B23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="9" t="n">
-        <v>36</v>
+      <c r="C23" s="10" t="n">
+        <v>43</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>44</v>
@@ -1217,7 +1217,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>QB1</t>
         </is>
@@ -1225,8 +1225,8 @@
       <c r="B24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C24" s="9" t="n">
-        <v>40</v>
+      <c r="C24" s="10" t="n">
+        <v>37</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>27</v>
@@ -1257,10 +1257,10 @@
         <v>24</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
         <v>25</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>29</v>
@@ -1319,7 +1319,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>12</v>
@@ -1350,7 +1350,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>28</v>
@@ -1381,7 +1381,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>40</v>
@@ -1412,7 +1412,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>9</v>
@@ -1473,8 +1473,8 @@
       <c r="B32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="C32" s="5" t="n">
-        <v>34</v>
+      <c r="C32" s="4" t="n">
+        <v>35</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>37</v>
@@ -1496,7 +1496,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>QB2</t>
         </is>
@@ -1504,7 +1504,7 @@
       <c r="B33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="C33" s="9" t="n">
+      <c r="C33" s="10" t="n">
         <v>58</v>
       </c>
       <c r="D33" s="3" t="n">
@@ -1527,7 +1527,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>QB3</t>
         </is>
@@ -1535,8 +1535,8 @@
       <c r="B34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="C34" s="9" t="n">
-        <v>65</v>
+      <c r="C34" s="10" t="n">
+        <v>68</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>59</v>
@@ -1566,8 +1566,8 @@
       <c r="B35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="C35" s="5" t="n">
-        <v>37</v>
+      <c r="C35" s="4" t="n">
+        <v>42</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>43</v>
@@ -1598,7 +1598,7 @@
         <v>35</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>26</v>
@@ -1629,10 +1629,10 @@
         <v>36</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -1659,8 +1659,8 @@
       <c r="B38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="C38" s="11" t="n">
-        <v>32</v>
+      <c r="C38" s="9" t="n">
+        <v>33</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>38</v>
@@ -1691,7 +1691,7 @@
         <v>38</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>35</v>
@@ -1722,7 +1722,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>15</v>
@@ -1753,7 +1753,7 @@
         <v>40</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>42</v>
@@ -1783,8 +1783,8 @@
       <c r="B42" s="3" t="n">
         <v>41</v>
       </c>
-      <c r="C42" s="5" t="n">
-        <v>38</v>
+      <c r="C42" s="7" t="n">
+        <v>32</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>32</v>
@@ -1815,7 +1815,7 @@
         <v>42</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>34</v>
@@ -1846,7 +1846,7 @@
         <v>43</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>54</v>
@@ -1868,7 +1868,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>QB4</t>
         </is>
@@ -1876,8 +1876,8 @@
       <c r="B45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="C45" s="9" t="n">
-        <v>64</v>
+      <c r="C45" s="10" t="n">
+        <v>67</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>58</v>
@@ -1907,8 +1907,8 @@
       <c r="B46" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="C46" s="5" t="n">
-        <v>42</v>
+      <c r="C46" s="7" t="n">
+        <v>39</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>33</v>
@@ -1938,8 +1938,8 @@
       <c r="B47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="C47" s="5" t="n">
-        <v>49</v>
+      <c r="C47" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>53</v>
@@ -1970,7 +1970,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>30</v>
@@ -2001,7 +2001,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>31</v>
@@ -2032,7 +2032,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>61</v>
@@ -2063,7 +2063,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>48</v>
@@ -2125,7 +2125,7 @@
         <v>52</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>66</v>
@@ -2187,7 +2187,7 @@
         <v>54</v>
       </c>
       <c r="C55" s="7" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>45</v>
@@ -2209,7 +2209,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>QB5</t>
         </is>
@@ -2217,8 +2217,8 @@
       <c r="B56" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="C56" s="4" t="n">
-        <v>66</v>
+      <c r="C56" s="10" t="n">
+        <v>69</v>
       </c>
       <c r="D56" s="3" t="n">
         <v>60</v>
@@ -2249,7 +2249,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>49</v>
@@ -2280,7 +2280,7 @@
         <v>57</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>63</v>
@@ -2302,7 +2302,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>QB6</t>
         </is>
@@ -2311,7 +2311,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>57</v>
@@ -2342,7 +2342,7 @@
         <v>59</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D60" s="3" t="n">
         <v>46</v>
@@ -2373,7 +2373,7 @@
         <v>60</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>70</v>
@@ -2403,7 +2403,7 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="11" t="n">
+      <c r="C62" s="9" t="n">
         <v>56</v>
       </c>
       <c r="D62" s="3" t="n">
@@ -2465,8 +2465,8 @@
       <c r="B64" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="C64" s="9" t="n">
-        <v>88</v>
+      <c r="C64" s="10" t="n">
+        <v>79</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>86</v>
@@ -2497,7 +2497,7 @@
         <v>64</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>56</v>
@@ -2519,7 +2519,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>QB7</t>
         </is>
@@ -2528,7 +2528,7 @@
         <v>65</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>67</v>
@@ -2559,7 +2559,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>74</v>
@@ -2581,7 +2581,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>QB8</t>
         </is>
@@ -2589,8 +2589,8 @@
       <c r="B68" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="C68" s="9" t="n">
-        <v>81</v>
+      <c r="C68" s="10" t="n">
+        <v>86</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>73</v>
@@ -2620,8 +2620,8 @@
       <c r="B69" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="C69" s="5" t="n">
-        <v>70</v>
+      <c r="C69" s="9" t="n">
+        <v>64</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>72</v>
@@ -2683,7 +2683,7 @@
         <v>70</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>65</v>
@@ -2714,10 +2714,10 @@
         <v>71</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -2744,8 +2744,8 @@
       <c r="B73" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="C73" s="9" t="n">
-        <v>117</v>
+      <c r="C73" s="10" t="n">
+        <v>103</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>110</v>
@@ -2776,7 +2776,7 @@
         <v>73</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D74" s="3" t="n">
         <v>78</v>
@@ -2806,11 +2806,11 @@
       <c r="B75" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="C75" s="4" t="n">
-        <v>86</v>
+      <c r="C75" s="10" t="n">
+        <v>87</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D76" s="3" t="n">
         <v>62</v>
@@ -2860,7 +2860,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t>QB9</t>
         </is>
@@ -2868,8 +2868,8 @@
       <c r="B77" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C77" s="9" t="n">
-        <v>106</v>
+      <c r="C77" s="10" t="n">
+        <v>112</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>100</v>
@@ -2930,8 +2930,8 @@
       <c r="B79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C79" s="5" t="n">
-        <v>78</v>
+      <c r="C79" s="9" t="n">
+        <v>72</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>82</v>
@@ -2953,7 +2953,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="10" t="inlineStr">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t>QB10</t>
         </is>
@@ -2962,7 +2962,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D80" s="3" t="n">
         <v>68</v>
@@ -2992,8 +2992,8 @@
       <c r="B81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="C81" s="9" t="n">
-        <v>94</v>
+      <c r="C81" s="10" t="n">
+        <v>95</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>98</v>
@@ -3024,7 +3024,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D82" s="3" t="n">
         <v>69</v>
@@ -3058,7 +3058,7 @@
         <v>99</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -3085,8 +3085,8 @@
       <c r="B84" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="C84" s="9" t="n">
-        <v>119</v>
+      <c r="C84" s="10" t="n">
+        <v>108</v>
       </c>
       <c r="D84" s="3" t="n">
         <v>125</v>
@@ -3117,7 +3117,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>83</v>
@@ -3148,7 +3148,7 @@
         <v>85</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="D86" s="3" t="n">
         <v>116</v>
@@ -3178,11 +3178,11 @@
       <c r="B87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="C87" s="9" t="n">
-        <v>107</v>
+      <c r="C87" s="10" t="n">
+        <v>122</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -3209,11 +3209,11 @@
       <c r="B88" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="C88" s="9" t="n">
-        <v>139</v>
+      <c r="C88" s="10" t="n">
+        <v>123</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>71</v>
@@ -3303,7 +3303,7 @@
         <v>90</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>81</v>
@@ -3325,7 +3325,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="10" t="inlineStr">
+      <c r="A92" s="11" t="inlineStr">
         <is>
           <t>QB11</t>
         </is>
@@ -3333,8 +3333,8 @@
       <c r="B92" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="C92" s="9" t="n">
-        <v>122</v>
+      <c r="C92" s="10" t="n">
+        <v>129</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>121</v>
@@ -3365,7 +3365,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>47</v>
@@ -3395,11 +3395,11 @@
       <c r="B94" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="C94" s="9" t="n">
-        <v>140</v>
+      <c r="C94" s="10" t="n">
+        <v>124</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="10" t="inlineStr">
+      <c r="A95" s="11" t="inlineStr">
         <is>
           <t>QB12</t>
         </is>
@@ -3426,8 +3426,8 @@
       <c r="B95" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="C95" s="9" t="n">
-        <v>124</v>
+      <c r="C95" s="10" t="n">
+        <v>130</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>122</v>
@@ -3458,7 +3458,7 @@
         <v>95</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D96" s="3" t="n">
         <v>96</v>
@@ -3489,10 +3489,10 @@
         <v>96</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>97</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D98" s="3" t="n">
         <v>124</v>
@@ -3551,7 +3551,7 @@
         <v>98</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>115</v>
@@ -3573,7 +3573,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t>QB13</t>
         </is>
@@ -3581,8 +3581,8 @@
       <c r="B100" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="C100" s="9" t="n">
-        <v>130</v>
+      <c r="C100" s="10" t="n">
+        <v>138</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>138</v>
@@ -3604,7 +3604,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="10" t="inlineStr">
+      <c r="A101" s="11" t="inlineStr">
         <is>
           <t>QB14</t>
         </is>
@@ -3613,7 +3613,7 @@
         <v>101</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>99</v>
@@ -3644,10 +3644,10 @@
         <v>102</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="10" t="inlineStr">
+      <c r="A103" s="11" t="inlineStr">
         <is>
           <t>QB15</t>
         </is>
@@ -3675,7 +3675,7 @@
         <v>103</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>102</v>
@@ -3706,10 +3706,10 @@
         <v>104</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
@@ -3737,10 +3737,10 @@
         <v>105</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
@@ -3768,7 +3768,7 @@
         <v>106</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>79</v>
@@ -3799,7 +3799,7 @@
         <v>107</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>77</v>
@@ -3830,10 +3830,10 @@
         <v>108</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="10" t="inlineStr">
+      <c r="A109" s="11" t="inlineStr">
         <is>
           <t>QB16</t>
         </is>
@@ -3860,11 +3860,11 @@
       <c r="B109" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="C109" s="9" t="n">
-        <v>123</v>
+      <c r="C109" s="10" t="n">
+        <v>128</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
@@ -3891,11 +3891,11 @@
       <c r="B110" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="C110" s="11" t="n">
-        <v>104</v>
+      <c r="C110" s="9" t="n">
+        <v>106</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>112</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>97</v>
@@ -3984,8 +3984,8 @@
       <c r="B113" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="C113" s="7" t="n">
-        <v>102</v>
+      <c r="C113" s="9" t="n">
+        <v>105</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>112</v>
@@ -4007,7 +4007,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="10" t="inlineStr">
+      <c r="A114" s="11" t="inlineStr">
         <is>
           <t>QB17</t>
         </is>
@@ -4016,7 +4016,7 @@
         <v>114</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>101</v>
@@ -4047,7 +4047,7 @@
         <v>115</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>103</v>
@@ -4077,11 +4077,11 @@
       <c r="B116" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="C116" s="9" t="n">
-        <v>137</v>
+      <c r="C116" s="5" t="n">
+        <v>110</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="10" t="inlineStr">
+      <c r="A117" s="11" t="inlineStr">
         <is>
           <t>QB18</t>
         </is>
@@ -4109,10 +4109,10 @@
         <v>117</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="10" t="inlineStr">
+      <c r="A118" s="11" t="inlineStr">
         <is>
           <t>QB19</t>
         </is>
@@ -4139,8 +4139,8 @@
       <c r="B118" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="C118" s="5" t="n">
-        <v>131</v>
+      <c r="C118" s="10" t="n">
+        <v>139</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>139</v>
@@ -4170,8 +4170,8 @@
       <c r="B119" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="C119" s="11" t="n">
-        <v>113</v>
+      <c r="C119" s="5" t="n">
+        <v>116</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>123</v>
@@ -4195,26 +4195,26 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>WR50</t>
+          <t>WR51</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Jayden Higgins</t>
+          <t>Xavier Worthy</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>HOU (8)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -4224,121 +4224,121 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>WR51</t>
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>QB20</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>121</v>
-      </c>
-      <c r="C121" s="5" t="n">
-        <v>108</v>
+        <v>122</v>
+      </c>
+      <c r="C121" s="10" t="n">
+        <v>206</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>108</v>
+        <v>184</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Xavier Worthy</t>
+          <t>Tyler Shough</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>KC (5)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="10" t="inlineStr">
-        <is>
-          <t>QB20</t>
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>TE14</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>122</v>
-      </c>
-      <c r="C122" s="9" t="n">
-        <v>198</v>
+        <v>123</v>
+      </c>
+      <c r="C122" s="7" t="n">
+        <v>98</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>185</v>
+        <v>105</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>Tyler Shough</t>
+          <t>Dallas Goedert</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>PHI (10)</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="8" t="inlineStr">
-        <is>
-          <t>TE14</t>
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>RB39</t>
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Dallas Goedert</t>
+          <t>Jacory Croskey-Merritt</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>PHI (10)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>RB39</t>
+          <t>RB40</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C124" s="7" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>Jacory Croskey-Merritt</t>
+          <t>Jordan Mason</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -4348,59 +4348,59 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>RB40</t>
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>WR52</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="C125" s="5" t="n">
         <v>126</v>
       </c>
+      <c r="C125" s="7" t="n">
+        <v>78</v>
+      </c>
       <c r="D125" s="3" t="n">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Jordan Mason</t>
+          <t>KC Concepcion</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>WR52</t>
+          <t>WR53</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="C126" s="7" t="n">
-        <v>82</v>
+        <v>127</v>
+      </c>
+      <c r="C126" s="5" t="n">
+        <v>109</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>KC Concepcion</t>
+          <t>Romeo Doubs</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -4410,183 +4410,183 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>WR53</t>
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>RB41</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="C127" s="5" t="n">
-        <v>120</v>
+        <v>128</v>
+      </c>
+      <c r="C127" s="7" t="n">
+        <v>75</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>Romeo Doubs</t>
+          <t>Jonathon Brooks</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>CAR (5)</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>RB41</t>
+          <t>RB42</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="C128" s="7" t="n">
-        <v>72</v>
+        <v>129</v>
+      </c>
+      <c r="C128" s="10" t="n">
+        <v>229</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>76</v>
+        <v>243</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>Jonathon Brooks</t>
+          <t>Tyrone Tracy</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
+          <t>NYG (8)</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>TE15</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="C129" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>Mark Andrews</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>BAL (13)</t>
+        </is>
+      </c>
+      <c r="G129" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>QB21</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="C130" s="10" t="n">
+        <v>151</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>Malik Willis</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>WR54</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="C131" s="5" t="n">
+        <v>121</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>Jalen Coker</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
           <t>CAR (5)</t>
         </is>
       </c>
-      <c r="G128" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>RB42</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="n">
-        <v>129</v>
-      </c>
-      <c r="C129" s="9" t="n">
-        <v>201</v>
-      </c>
-      <c r="D129" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>Tyrone Tracy</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t>NYG (8)</t>
-        </is>
-      </c>
-      <c r="G129" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="8" t="inlineStr">
-        <is>
-          <t>TE15</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="C130" s="5" t="n">
-        <v>129</v>
-      </c>
-      <c r="D130" s="3" t="n">
-        <v>130</v>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>Mark Andrews</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t>BAL (13)</t>
-        </is>
-      </c>
-      <c r="G130" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="10" t="inlineStr">
-        <is>
-          <t>QB21</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="n">
-        <v>131</v>
-      </c>
-      <c r="C131" s="9" t="n">
-        <v>149</v>
-      </c>
-      <c r="D131" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>Malik Willis</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="inlineStr">
-        <is>
-          <t>MIA (6)</t>
-        </is>
-      </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>WR54</t>
+          <t>WR55</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>132</v>
-      </c>
-      <c r="C132" s="4" t="n">
-        <v>141</v>
+        <v>133</v>
+      </c>
+      <c r="C132" s="7" t="n">
+        <v>82</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>Jalen Coker</t>
+          <t>Matthew Golden</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>CAR (5)</t>
+          <t>GB (11)</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
@@ -4596,54 +4596,54 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>WR55</t>
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>QB22</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>133</v>
-      </c>
-      <c r="C133" s="7" t="n">
-        <v>73</v>
+        <v>134</v>
+      </c>
+      <c r="C133" s="10" t="n">
+        <v>208</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>75</v>
+        <v>186</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Matthew Golden</t>
+          <t>C.J. Stroud</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>GB (11)</t>
+          <t>HOU (8)</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="10" t="inlineStr">
-        <is>
-          <t>QB22</t>
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>RB43</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>134</v>
-      </c>
-      <c r="C134" s="9" t="n">
-        <v>197</v>
+        <v>135</v>
+      </c>
+      <c r="C134" s="5" t="n">
+        <v>149</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>184</v>
+        <v>137</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>C.J. Stroud</t>
+          <t>Woody Marks</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -4653,33 +4653,33 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>RB43</t>
+          <t>RB44</t>
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Woody Marks</t>
+          <t>Tyler Allgeier</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>HOU (8)</t>
+          <t>ARI (14)</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -4691,26 +4691,26 @@
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>RB44</t>
+          <t>RB45</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>Tyler Allgeier</t>
+          <t>Zach Charbonnet</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>ARI (14)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -4720,23 +4720,23 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="6" t="inlineStr">
-        <is>
-          <t>RB45</t>
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>QB23</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="C137" s="5" t="n">
-        <v>147</v>
+        <v>138</v>
+      </c>
+      <c r="C137" s="10" t="n">
+        <v>207</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Zach Charbonnet</t>
+          <t>Sam Darnold</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -4746,64 +4746,64 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>RB46</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="C138" s="9" t="n">
+        <v>131</v>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>114</v>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>Chris Rodriguez</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>JAC (7)</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="10" t="inlineStr">
-        <is>
-          <t>QB23</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="n">
-        <v>138</v>
-      </c>
-      <c r="C138" s="9" t="n">
-        <v>199</v>
-      </c>
-      <c r="D138" s="3" t="n">
-        <v>186</v>
-      </c>
-      <c r="E138" s="3" t="inlineStr">
-        <is>
-          <t>Sam Darnold</t>
-        </is>
-      </c>
-      <c r="F138" s="3" t="inlineStr">
-        <is>
-          <t>SEA (11)</t>
-        </is>
-      </c>
-      <c r="G138" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>RB46</t>
+          <t>RB47</t>
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>139</v>
-      </c>
-      <c r="C139" s="7" t="n">
-        <v>125</v>
+        <v>140</v>
+      </c>
+      <c r="C139" s="5" t="n">
+        <v>148</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Chris Rodriguez</t>
+          <t>Tyjae Spears</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>JAC (7)</t>
+          <t>TEN (9)</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -4813,90 +4813,90 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="6" t="inlineStr">
-        <is>
-          <t>RB47</t>
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t>TE16</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="C140" s="5" t="n">
-        <v>148</v>
+        <v>141</v>
+      </c>
+      <c r="C140" s="7" t="n">
+        <v>118</v>
       </c>
       <c r="D140" s="3" t="n">
+        <v>152</v>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>Juwan Johnson</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>RB48</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="n">
         <v>142</v>
       </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>Tyjae Spears</t>
-        </is>
-      </c>
-      <c r="F140" s="3" t="inlineStr">
-        <is>
-          <t>TEN (9)</t>
-        </is>
-      </c>
-      <c r="G140" s="3" t="inlineStr">
+      <c r="C141" s="5" t="n">
+        <v>198</v>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>Dylan Sampson</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
         <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="8" t="inlineStr">
-        <is>
-          <t>TE16</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="n">
-        <v>141</v>
-      </c>
-      <c r="C141" s="5" t="n">
-        <v>145</v>
-      </c>
-      <c r="D141" s="3" t="n">
-        <v>153</v>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>Juwan Johnson</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t>NO (8)</t>
-        </is>
-      </c>
-      <c r="G141" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>RB48</t>
+          <t>RB49</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>142</v>
-      </c>
-      <c r="C142" s="5" t="n">
-        <v>209</v>
+        <v>143</v>
+      </c>
+      <c r="C142" s="10" t="n">
+        <v>228</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>Dylan Sampson</t>
+          <t>Isiah Pacheco</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>DET (6)</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -4908,26 +4908,26 @@
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>RB49</t>
+          <t>RB50</t>
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>143</v>
-      </c>
-      <c r="C143" s="5" t="n">
-        <v>211</v>
+        <v>144</v>
+      </c>
+      <c r="C143" s="10" t="n">
+        <v>225</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Isiah Pacheco</t>
+          <t>Alvin Kamara</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>DET (6)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -4937,152 +4937,152 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="6" t="inlineStr">
-        <is>
-          <t>RB50</t>
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>QB24</t>
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>144</v>
-      </c>
-      <c r="C144" s="5" t="n">
-        <v>210</v>
+        <v>145</v>
+      </c>
+      <c r="C144" s="10" t="n">
+        <v>243</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Alvin Kamara</t>
+          <t>Cam Ward</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>TEN (9)</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="10" t="inlineStr">
-        <is>
-          <t>QB24</t>
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>WR56</t>
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="C145" s="9" t="n">
-        <v>232</v>
+        <v>146</v>
+      </c>
+      <c r="C145" s="5" t="n">
+        <v>134</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>226</v>
+        <v>142</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Cam Ward</t>
+          <t>Rashid Shaheed</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>TEN (9)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>WR56</t>
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t>TE17</t>
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Rashid Shaheed</t>
+          <t>Brenton Strange</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>JAC (7)</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="8" t="inlineStr">
-        <is>
-          <t>TE17</t>
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>WR57</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>147</v>
-      </c>
-      <c r="C147" s="5" t="n">
-        <v>175</v>
+        <v>148</v>
+      </c>
+      <c r="C147" s="10" t="n">
+        <v>266</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Brenton Strange</t>
+          <t>Omar Cooper</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>JAC (7)</t>
+          <t>NYJ (13)</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>WR57</t>
+          <t>WR58</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>148</v>
-      </c>
-      <c r="C148" s="9" t="n">
-        <v>223</v>
+        <v>149</v>
+      </c>
+      <c r="C148" s="5" t="n">
+        <v>136</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>217</v>
+        <v>126</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>Omar Cooper</t>
+          <t>Denzel Boston</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>NYJ (13)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -5094,181 +5094,181 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>WR58</t>
+          <t>WR59</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>149</v>
-      </c>
-      <c r="C149" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C149" s="4" t="n">
+        <v>268</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>233</v>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>Jerry Jeudy</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="11" t="inlineStr">
+        <is>
+          <t>QB25</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="D149" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>Denzel Boston</t>
-        </is>
-      </c>
-      <c r="F149" s="3" t="inlineStr">
-        <is>
-          <t>CLE (11)</t>
-        </is>
-      </c>
-      <c r="G149" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>WR59</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="n">
-        <v>150</v>
-      </c>
       <c r="C150" s="4" t="n">
-        <v>255</v>
+        <v>217</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>229</v>
+        <v>194</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Jerry Jeudy</t>
+          <t>Daniel Jones</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>IND (13)</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="10" t="inlineStr">
-        <is>
-          <t>QB25</t>
+      <c r="A151" s="11" t="inlineStr">
+        <is>
+          <t>QB26</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C151" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>193</v>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>Bryce Young</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>CAR (5)</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>WR60</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="C152" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="D152" s="3" t="n">
         <v>217</v>
       </c>
-      <c r="D151" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>Daniel Jones</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="inlineStr">
-        <is>
-          <t>IND (13)</t>
-        </is>
-      </c>
-      <c r="G151" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="10" t="inlineStr">
-        <is>
-          <t>QB26</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="n">
-        <v>152</v>
-      </c>
-      <c r="C152" s="4" t="n">
-        <v>207</v>
-      </c>
-      <c r="D152" s="3" t="n">
-        <v>193</v>
-      </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>Bryce Young</t>
+          <t>Jauan Jennings</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>CAR (5)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>WR60</t>
+      <c r="A153" s="8" t="inlineStr">
+        <is>
+          <t>TE18</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>153</v>
-      </c>
-      <c r="C153" s="4" t="n">
-        <v>222</v>
+        <v>154</v>
+      </c>
+      <c r="C153" s="5" t="n">
+        <v>172</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Jauan Jennings</t>
+          <t>Chig Okonkwo</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="8" t="inlineStr">
         <is>
-          <t>TE18</t>
+          <t>TE19</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>158</v>
+        <v>213</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>179</v>
+        <v>252</v>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Chig Okonkwo</t>
+          <t>Oronde Gadsden</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -5280,26 +5280,26 @@
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>TE19</t>
+          <t>TE20</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>155</v>
-      </c>
-      <c r="C155" s="4" t="n">
-        <v>233</v>
+        <v>156</v>
+      </c>
+      <c r="C155" s="5" t="n">
+        <v>185</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>248</v>
+        <v>188</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Oronde Gadsden</t>
+          <t>Hunter Henry</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -5309,59 +5309,59 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="8" t="inlineStr">
-        <is>
-          <t>TE20</t>
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>RB51</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Hunter Henry</t>
+          <t>Jonah Coleman</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>DEN (10)</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>RB51</t>
+          <t>RB52</t>
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>158</v>
-      </c>
-      <c r="C157" s="5" t="n">
-        <v>179</v>
+        <v>159</v>
+      </c>
+      <c r="C157" s="7" t="n">
+        <v>104</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>177</v>
+        <v>111</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Jonah Coleman</t>
+          <t>Keaton Mitchell</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>DEN (10)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -5371,59 +5371,59 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="6" t="inlineStr">
-        <is>
-          <t>RB52</t>
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>WR61</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>159</v>
-      </c>
-      <c r="C158" s="7" t="n">
-        <v>101</v>
+        <v>160</v>
+      </c>
+      <c r="C158" s="4" t="n">
+        <v>176</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>111</v>
+        <v>180</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Keaton Mitchell</t>
+          <t>Adonai Mitchell</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>NYJ (13)</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>WR61</t>
+          <t>WR62</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>160</v>
-      </c>
-      <c r="C159" s="4" t="n">
-        <v>190</v>
+        <v>161</v>
+      </c>
+      <c r="C159" s="5" t="n">
+        <v>164</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Adonai Mitchell</t>
+          <t>Jalen McMillan</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>NYJ (13)</t>
+          <t>TB (10)</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -5435,26 +5435,26 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>WR62</t>
+          <t>WR63</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="C160" s="5" t="n">
-        <v>160</v>
+        <v>162</v>
+      </c>
+      <c r="C160" s="4" t="n">
+        <v>247</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Jalen McMillan</t>
+          <t>Tre Tucker</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>TB (10)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -5464,276 +5464,274 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>WR63</t>
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>RB53</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Tre Tucker</t>
+          <t>Brian Robinson</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>ATL (11)</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>RB53</t>
+          <t>RB54</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>164</v>
-      </c>
-      <c r="C162" s="4" t="n">
+        <v>165</v>
+      </c>
+      <c r="C162" s="5" t="n">
+        <v>159</v>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>Tank Bigsby</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>PHI (10)</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="8" t="inlineStr">
+        <is>
+          <t>TE21</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="C163" s="5" t="n">
+        <v>158</v>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>177</v>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>Dalton Schultz</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>HOU (8)</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>WR64</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="C164" s="9" t="n">
+        <v>135</v>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>Travis Hunter</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>JAC (7)</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>RB55</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="C165" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="D162" s="3" t="n">
-        <v>169</v>
-      </c>
-      <c r="E162" s="3" t="inlineStr">
-        <is>
-          <t>Brian Robinson</t>
-        </is>
-      </c>
-      <c r="F162" s="3" t="inlineStr">
-        <is>
-          <t>ATL (11)</t>
-        </is>
-      </c>
-      <c r="G162" s="3" t="inlineStr">
+      <c r="D165" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>Braelon Allen</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>NYJ (13)</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>RB54</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="n">
-        <v>165</v>
-      </c>
-      <c r="C163" s="5" t="n">
-        <v>162</v>
-      </c>
-      <c r="D163" s="3" t="n">
-        <v>155</v>
-      </c>
-      <c r="E163" s="3" t="inlineStr">
-        <is>
-          <t>Tank Bigsby</t>
-        </is>
-      </c>
-      <c r="F163" s="3" t="inlineStr">
-        <is>
-          <t>PHI (10)</t>
-        </is>
-      </c>
-      <c r="G163" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="8" t="inlineStr">
-        <is>
-          <t>TE21</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="C164" s="4" t="n">
-        <v>208</v>
-      </c>
-      <c r="D164" s="3" t="n">
-        <v>211</v>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>Dalton Schultz</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>HOU (8)</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>WR64</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="C165" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="D165" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>Travis Hunter</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="inlineStr">
-        <is>
-          <t>JAC (7)</t>
-        </is>
-      </c>
-      <c r="G165" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
     <row r="166">
-      <c r="A166" s="6" t="inlineStr">
-        <is>
-          <t>RB55</t>
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>WR65</t>
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C166" s="5" t="n">
         <v>177</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>Braelon Allen</t>
+          <t>Tre' Harris</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>NYJ (13)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>WR65</t>
+      <c r="A167" s="8" t="inlineStr">
+        <is>
+          <t>TE22</t>
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="C167" s="5" t="n">
-        <v>172</v>
+        <v>173</v>
+      </c>
+      <c r="C167" s="4" t="n">
+        <v>211</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Tre' Harris</t>
+          <t>T.J. Hockenson</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="8" t="inlineStr">
-        <is>
-          <t>TE22</t>
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>WR66</t>
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>173</v>
-      </c>
-      <c r="C168" s="5" t="n">
-        <v>193</v>
-      </c>
-      <c r="D168" s="3" t="n">
-        <v>205</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="C168" s="4" t="n">
+        <v>269</v>
+      </c>
+      <c r="D168" s="3" t="inlineStr"/>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>T.J. Hockenson</t>
+          <t>Troy Franklin</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>DEN (10)</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>WR66</t>
+          <t>WR67</t>
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="C169" s="4" t="n">
-        <v>297</v>
+        <v>175</v>
+      </c>
+      <c r="C169" s="5" t="n">
+        <v>184</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>285</v>
+        <v>210</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>Troy Franklin</t>
+          <t>Kayshon Boutte</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>DEN (10)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
@@ -5745,26 +5743,26 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>WR67</t>
+          <t>WR68</t>
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>175</v>
-      </c>
-      <c r="C170" s="4" t="n">
-        <v>257</v>
+        <v>176</v>
+      </c>
+      <c r="C170" s="5" t="n">
+        <v>174</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>234</v>
+        <v>182</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>Kayshon Boutte</t>
+          <t>Ryan Flournoy</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>DAL (14)</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
@@ -5776,212 +5774,212 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>WR68</t>
+          <t>WR69</t>
         </is>
       </c>
       <c r="B171" s="3" t="n">
-        <v>176</v>
-      </c>
-      <c r="C171" s="5" t="n">
-        <v>171</v>
+        <v>177</v>
+      </c>
+      <c r="C171" s="7" t="n">
+        <v>89</v>
       </c>
       <c r="D171" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>Stefon Diggs</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>FA ()</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>RB56</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="n">
+        <v>178</v>
+      </c>
+      <c r="C172" s="4" t="n">
+        <v>273</v>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>257</v>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>James Conner</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>ARI (14)</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="11" t="inlineStr">
+        <is>
+          <t>QB27</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="n">
+        <v>179</v>
+      </c>
+      <c r="C173" s="4" t="n">
+        <v>244</v>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>Jacoby Brissett</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>ARI (14)</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>WR70</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="n">
+        <v>185</v>
+      </c>
+      <c r="C174" s="5" t="n">
         <v>182</v>
       </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>Ryan Flournoy</t>
-        </is>
-      </c>
-      <c r="F171" s="3" t="inlineStr">
-        <is>
-          <t>DAL (14)</t>
-        </is>
-      </c>
-      <c r="G171" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>WR69</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="n">
-        <v>177</v>
-      </c>
-      <c r="C172" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="D172" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="E172" s="3" t="inlineStr">
-        <is>
-          <t>Stefon Diggs</t>
-        </is>
-      </c>
-      <c r="F172" s="3" t="inlineStr">
-        <is>
-          <t>FA ()</t>
-        </is>
-      </c>
-      <c r="G172" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="6" t="inlineStr">
-        <is>
-          <t>RB56</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="n">
-        <v>178</v>
-      </c>
-      <c r="C173" s="4" t="n">
-        <v>271</v>
-      </c>
-      <c r="D173" s="3" t="n">
-        <v>253</v>
-      </c>
-      <c r="E173" s="3" t="inlineStr">
-        <is>
-          <t>James Conner</t>
-        </is>
-      </c>
-      <c r="F173" s="3" t="inlineStr">
-        <is>
-          <t>ARI (14)</t>
-        </is>
-      </c>
-      <c r="G173" s="3" t="inlineStr">
+      <c r="D174" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>Jaylin Noel</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="inlineStr">
+        <is>
+          <t>HOU (8)</t>
+        </is>
+      </c>
+      <c r="G174" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>RB57</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="C175" s="4" t="n">
+        <v>291</v>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>283</v>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>Emanuel Wilson</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="G175" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="10" t="inlineStr">
-        <is>
-          <t>QB27</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="n">
-        <v>179</v>
-      </c>
-      <c r="C174" s="4" t="n">
-        <v>237</v>
-      </c>
-      <c r="D174" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="E174" s="3" t="inlineStr">
-        <is>
-          <t>Jacoby Brissett</t>
-        </is>
-      </c>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>ARI (14)</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>WR70</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="n">
-        <v>185</v>
-      </c>
-      <c r="C175" s="4" t="n">
-        <v>285</v>
-      </c>
-      <c r="D175" s="3" t="n">
-        <v>268</v>
-      </c>
-      <c r="E175" s="3" t="inlineStr">
-        <is>
-          <t>Jaylin Noel</t>
-        </is>
-      </c>
-      <c r="F175" s="3" t="inlineStr">
-        <is>
-          <t>HOU (8)</t>
-        </is>
-      </c>
-      <c r="G175" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
     <row r="176">
-      <c r="A176" s="6" t="inlineStr">
-        <is>
-          <t>RB57</t>
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>WR71</t>
         </is>
       </c>
       <c r="B176" s="3" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>281</v>
+        <v>235</v>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>Emanuel Wilson</t>
+          <t>Calvin Ridley</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>TEN (9)</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>WR71</t>
+          <t>WR72</t>
         </is>
       </c>
       <c r="B177" s="3" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C177" s="4" t="n">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Calvin Ridley</t>
+          <t>Isaac TeSlaa</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>TEN (9)</t>
+          <t>DET (6)</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -5991,90 +5989,90 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="inlineStr">
-        <is>
-          <t>WR72</t>
+      <c r="A178" s="8" t="inlineStr">
+        <is>
+          <t>TE23</t>
         </is>
       </c>
       <c r="B178" s="3" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C178" s="4" t="n">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>Isaac TeSlaa</t>
+          <t>Kenyon Sadiq</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>DET (6)</t>
+          <t>NYJ (13)</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="8" t="inlineStr">
-        <is>
-          <t>TE23</t>
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>RB58</t>
         </is>
       </c>
       <c r="B179" s="3" t="n">
-        <v>191</v>
-      </c>
-      <c r="C179" s="4" t="n">
-        <v>279</v>
+        <v>192</v>
+      </c>
+      <c r="C179" s="5" t="n">
+        <v>201</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>264</v>
+        <v>200</v>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Kenyon Sadiq</t>
+          <t>Emmett Johnson</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>NYJ (13)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>RB58</t>
+          <t>RB59</t>
         </is>
       </c>
       <c r="B180" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="C180" s="5" t="n">
-        <v>195</v>
+        <v>194</v>
+      </c>
+      <c r="C180" s="4" t="n">
+        <v>288</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>201</v>
+        <v>272</v>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>Emmett Johnson</t>
+          <t>Kimani Vidal</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>KC (5)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
@@ -6086,26 +6084,26 @@
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>RB59</t>
+          <t>RB60</t>
         </is>
       </c>
       <c r="B181" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="C181" s="4" t="n">
-        <v>273</v>
+        <v>195</v>
+      </c>
+      <c r="C181" s="9" t="n">
+        <v>162</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>271</v>
+        <v>167</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Kimani Vidal</t>
+          <t>Ray Davis</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -6115,90 +6113,90 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="6" t="inlineStr">
-        <is>
-          <t>RB60</t>
+      <c r="A182" s="8" t="inlineStr">
+        <is>
+          <t>TE24</t>
         </is>
       </c>
       <c r="B182" s="3" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>Ray Davis</t>
+          <t>AJ Barner</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="8" t="inlineStr">
-        <is>
-          <t>TE24</t>
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>WR73</t>
         </is>
       </c>
       <c r="B183" s="3" t="n">
-        <v>196</v>
-      </c>
-      <c r="C183" s="11" t="n">
-        <v>159</v>
+        <v>197</v>
+      </c>
+      <c r="C183" s="4" t="n">
+        <v>299</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>178</v>
+        <v>275</v>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>AJ Barner</t>
+          <t>Darnell Mooney</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>NYG (8)</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>WR73</t>
+          <t>WR74</t>
         </is>
       </c>
       <c r="B184" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="C184" s="4" t="n">
-        <v>300</v>
+        <v>199</v>
+      </c>
+      <c r="C184" s="9" t="n">
+        <v>165</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>274</v>
+        <v>164</v>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>Darnell Mooney</t>
+          <t>Jalen Nailor</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>NYG (8)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -6210,26 +6208,26 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>WR74</t>
+          <t>WR75</t>
         </is>
       </c>
       <c r="B185" s="3" t="n">
-        <v>199</v>
-      </c>
-      <c r="C185" s="11" t="n">
-        <v>161</v>
+        <v>201</v>
+      </c>
+      <c r="C185" s="5" t="n">
+        <v>179</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Jalen Nailor</t>
+          <t>Deebo Samuel</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>FA ()</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -6241,26 +6239,26 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>WR75</t>
+          <t>WR76</t>
         </is>
       </c>
       <c r="B186" s="3" t="n">
-        <v>201</v>
-      </c>
-      <c r="C186" s="11" t="n">
-        <v>170</v>
+        <v>202</v>
+      </c>
+      <c r="C186" s="4" t="n">
+        <v>270</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Deebo Samuel</t>
+          <t>Malik Washington</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>FA ()</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -6270,90 +6268,90 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="inlineStr">
-        <is>
-          <t>WR76</t>
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>RB61</t>
         </is>
       </c>
       <c r="B187" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="C187" s="5" t="n">
-        <v>202</v>
+        <v>204</v>
+      </c>
+      <c r="C187" s="9" t="n">
+        <v>161</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>Malik Washington</t>
+          <t>Mike Washington</t>
         </is>
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>RB61</t>
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>WR77</t>
         </is>
       </c>
       <c r="B188" s="3" t="n">
-        <v>204</v>
-      </c>
-      <c r="C188" s="11" t="n">
-        <v>164</v>
+        <v>205</v>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>222</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Mike Washington</t>
+          <t>Pat Bryant</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>DEN (10)</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>WR77</t>
+          <t>WR78</t>
         </is>
       </c>
       <c r="B189" s="3" t="n">
-        <v>205</v>
-      </c>
-      <c r="C189" s="5" t="n">
-        <v>205</v>
+        <v>206</v>
+      </c>
+      <c r="C189" s="4" t="n">
+        <v>297</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>219</v>
+        <v>276</v>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Pat Bryant</t>
+          <t>Antonio Williams</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>DEN (10)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
@@ -6363,121 +6361,121 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr">
-        <is>
-          <t>WR78</t>
+      <c r="A190" s="8" t="inlineStr">
+        <is>
+          <t>TE25</t>
         </is>
       </c>
       <c r="B190" s="3" t="n">
-        <v>206</v>
-      </c>
-      <c r="C190" s="4" t="n">
-        <v>295</v>
+        <v>207</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>236</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Antonio Williams</t>
+          <t>Gunnar Helm</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>TEN (9)</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="8" t="inlineStr">
-        <is>
-          <t>TE25</t>
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>WR79</t>
         </is>
       </c>
       <c r="B191" s="3" t="n">
-        <v>207</v>
-      </c>
-      <c r="C191" s="4" t="n">
-        <v>260</v>
+        <v>211</v>
+      </c>
+      <c r="C191" s="9" t="n">
+        <v>178</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>261</v>
+        <v>166</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Gunnar Helm</t>
+          <t>Dontayvion Wicks</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>TEN (9)</t>
+          <t>PHI (10)</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="inlineStr">
-        <is>
-          <t>WR79</t>
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t>RB62</t>
         </is>
       </c>
       <c r="B192" s="3" t="n">
-        <v>211</v>
-      </c>
-      <c r="C192" s="11" t="n">
-        <v>173</v>
+        <v>212</v>
+      </c>
+      <c r="C192" s="5" t="n">
+        <v>224</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Dontayvion Wicks</t>
+          <t>Sean Tucker</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>PHI (10)</t>
+          <t>TB (10)</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>RB62</t>
+          <t>RB63</t>
         </is>
       </c>
       <c r="B193" s="3" t="n">
-        <v>212</v>
-      </c>
-      <c r="C193" s="5" t="n">
-        <v>240</v>
+        <v>213</v>
+      </c>
+      <c r="C193" s="4" t="n">
+        <v>292</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>228</v>
+        <v>285</v>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Sean Tucker</t>
+          <t>Nicholas Singleton</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>TB (10)</t>
+          <t>TEN (9)</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
@@ -6487,212 +6485,212 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="6" t="inlineStr">
-        <is>
-          <t>RB63</t>
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>WR80</t>
         </is>
       </c>
       <c r="B194" s="3" t="n">
-        <v>213</v>
-      </c>
-      <c r="C194" s="4" t="n">
-        <v>292</v>
+        <v>217</v>
+      </c>
+      <c r="C194" s="5" t="n">
+        <v>223</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>283</v>
+        <v>221</v>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Nicholas Singleton</t>
+          <t>Tank Dell</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
+          <t>HOU (8)</t>
+        </is>
+      </c>
+      <c r="G194" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="11" t="inlineStr">
+        <is>
+          <t>QB28</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="n">
+        <v>219</v>
+      </c>
+      <c r="C195" s="5" t="n">
+        <v>242</v>
+      </c>
+      <c r="D195" s="3" t="n">
+        <v>203</v>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
+        <is>
+          <t>Aaron Rodgers</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="inlineStr">
+        <is>
+          <t>PIT (9)</t>
+        </is>
+      </c>
+      <c r="G195" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>WR81</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="n">
+        <v>221</v>
+      </c>
+      <c r="C196" s="4" t="n">
+        <v>287</v>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>Cooper Kupp</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="G196" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>RB64</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="C197" s="4" t="n">
+        <v>272</v>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="E197" s="3" t="inlineStr">
+        <is>
+          <t>Kaytron Allen</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="inlineStr">
+        <is>
+          <t>WAS (7)</t>
+        </is>
+      </c>
+      <c r="G197" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="11" t="inlineStr">
+        <is>
+          <t>QB29</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="n">
+        <v>223</v>
+      </c>
+      <c r="C198" s="5" t="n">
+        <v>218</v>
+      </c>
+      <c r="D198" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>Geno Smith</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>NYJ (13)</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>WR82</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="C199" s="4" t="n">
+        <v>294</v>
+      </c>
+      <c r="D199" s="3" t="inlineStr"/>
+      <c r="E199" s="3" t="inlineStr">
+        <is>
+          <t>Chimere Dike</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
           <t>TEN (9)</t>
         </is>
       </c>
-      <c r="G194" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="inlineStr">
-        <is>
-          <t>WR80</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="n">
-        <v>217</v>
-      </c>
-      <c r="C195" s="4" t="n">
-        <v>266</v>
-      </c>
-      <c r="D195" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>Tank Dell</t>
-        </is>
-      </c>
-      <c r="F195" s="3" t="inlineStr">
-        <is>
-          <t>HOU (8)</t>
-        </is>
-      </c>
-      <c r="G195" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="10" t="inlineStr">
-        <is>
-          <t>QB28</t>
-        </is>
-      </c>
-      <c r="B196" s="3" t="n">
-        <v>219</v>
-      </c>
-      <c r="C196" s="5" t="n">
-        <v>231</v>
-      </c>
-      <c r="D196" s="3" t="n">
-        <v>204</v>
-      </c>
-      <c r="E196" s="3" t="inlineStr">
-        <is>
-          <t>Aaron Rodgers</t>
-        </is>
-      </c>
-      <c r="F196" s="3" t="inlineStr">
-        <is>
-          <t>PIT (9)</t>
-        </is>
-      </c>
-      <c r="G196" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="inlineStr">
-        <is>
-          <t>WR81</t>
-        </is>
-      </c>
-      <c r="B197" s="3" t="n">
-        <v>221</v>
-      </c>
-      <c r="C197" s="4" t="n">
-        <v>283</v>
-      </c>
-      <c r="D197" s="3" t="n">
-        <v>235</v>
-      </c>
-      <c r="E197" s="3" t="inlineStr">
-        <is>
-          <t>Cooper Kupp</t>
-        </is>
-      </c>
-      <c r="F197" s="3" t="inlineStr">
-        <is>
-          <t>SEA (11)</t>
-        </is>
-      </c>
-      <c r="G197" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="6" t="inlineStr">
-        <is>
-          <t>RB64</t>
-        </is>
-      </c>
-      <c r="B198" s="3" t="n">
-        <v>222</v>
-      </c>
-      <c r="C198" s="4" t="n">
-        <v>269</v>
-      </c>
-      <c r="D198" s="3" t="n">
-        <v>239</v>
-      </c>
-      <c r="E198" s="3" t="inlineStr">
-        <is>
-          <t>Kaytron Allen</t>
-        </is>
-      </c>
-      <c r="F198" s="3" t="inlineStr">
-        <is>
-          <t>WAS (7)</t>
-        </is>
-      </c>
-      <c r="G198" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="10" t="inlineStr">
-        <is>
-          <t>QB29</t>
-        </is>
-      </c>
-      <c r="B199" s="3" t="n">
-        <v>223</v>
-      </c>
-      <c r="C199" s="5" t="n">
-        <v>218</v>
-      </c>
-      <c r="D199" s="3" t="n">
-        <v>203</v>
-      </c>
-      <c r="E199" s="3" t="inlineStr">
-        <is>
-          <t>Geno Smith</t>
-        </is>
-      </c>
-      <c r="F199" s="3" t="inlineStr">
-        <is>
-          <t>NYJ (13)</t>
-        </is>
-      </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>WR82</t>
+          <t>WR83</t>
         </is>
       </c>
       <c r="B200" s="3" t="n">
-        <v>224</v>
-      </c>
-      <c r="C200" s="4" t="n">
-        <v>294</v>
-      </c>
-      <c r="D200" s="3" t="inlineStr"/>
+        <v>225</v>
+      </c>
+      <c r="C200" s="7" t="n">
+        <v>96</v>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>94</v>
+      </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>Chimere Dike</t>
+          <t>De'Zhaun Stribling</t>
         </is>
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>TEN (9)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -6704,26 +6702,26 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>WR83</t>
+          <t>WR84</t>
         </is>
       </c>
       <c r="B201" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="C201" s="7" t="n">
-        <v>84</v>
+        <v>228</v>
+      </c>
+      <c r="C201" s="5" t="n">
+        <v>221</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>88</v>
+        <v>223</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>De'Zhaun Stribling</t>
+          <t>Germie Bernard</t>
         </is>
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>PIT (9)</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -6735,26 +6733,26 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>WR84</t>
+          <t>WR85</t>
         </is>
       </c>
       <c r="B202" s="3" t="n">
-        <v>228</v>
-      </c>
-      <c r="C202" s="4" t="n">
-        <v>263</v>
+        <v>230</v>
+      </c>
+      <c r="C202" s="5" t="n">
+        <v>219</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>Germie Bernard</t>
+          <t>Rashod Bateman</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>PIT (9)</t>
+          <t>BAL (13)</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
@@ -6766,305 +6764,303 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>WR85</t>
+          <t>WR86</t>
         </is>
       </c>
       <c r="B203" s="3" t="n">
-        <v>230</v>
-      </c>
-      <c r="C203" s="11" t="n">
+        <v>232</v>
+      </c>
+      <c r="C203" s="4" t="n">
+        <v>299</v>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>299</v>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>Brandon Aiyuk</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>SF (8)</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>RB65</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="n">
+        <v>233</v>
+      </c>
+      <c r="C204" s="5" t="n">
+        <v>264</v>
+      </c>
+      <c r="D204" s="3" t="inlineStr"/>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>Jaylen Wright</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="11" t="inlineStr">
+        <is>
+          <t>QB30</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="C205" s="5" t="n">
+        <v>209</v>
+      </c>
+      <c r="D205" s="3" t="n">
         <v>192</v>
       </c>
-      <c r="D203" s="3" t="n">
-        <v>207</v>
-      </c>
-      <c r="E203" s="3" t="inlineStr">
-        <is>
-          <t>Rashod Bateman</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="inlineStr">
-        <is>
-          <t>BAL (13)</t>
-        </is>
-      </c>
-      <c r="G203" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
-        <is>
-          <t>WR86</t>
-        </is>
-      </c>
-      <c r="B204" s="3" t="n">
-        <v>232</v>
-      </c>
-      <c r="C204" s="4" t="n">
-        <v>299</v>
-      </c>
-      <c r="D204" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="E204" s="3" t="inlineStr">
-        <is>
-          <t>Brandon Aiyuk</t>
-        </is>
-      </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>SF (8)</t>
-        </is>
-      </c>
-      <c r="G204" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="6" t="inlineStr">
-        <is>
-          <t>RB65</t>
-        </is>
-      </c>
-      <c r="B205" s="3" t="n">
-        <v>233</v>
-      </c>
-      <c r="C205" s="4" t="n">
-        <v>296</v>
-      </c>
-      <c r="D205" s="3" t="n">
-        <v>284</v>
-      </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Jaylen Wright</t>
+          <t>Fernando Mendoza</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="10" t="inlineStr">
-        <is>
-          <t>QB30</t>
+      <c r="A206" s="8" t="inlineStr">
+        <is>
+          <t>TE26</t>
         </is>
       </c>
       <c r="B206" s="3" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C206" s="5" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>192</v>
+        <v>263</v>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>Fernando Mendoza</t>
+          <t>Pat Freiermuth</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>PIT (9)</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="8" t="inlineStr">
-        <is>
-          <t>TE26</t>
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>WR87</t>
         </is>
       </c>
       <c r="B207" s="3" t="n">
+        <v>237</v>
+      </c>
+      <c r="C207" s="4" t="n">
+        <v>283</v>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="E207" s="3" t="inlineStr">
+        <is>
+          <t>Zachariah Branch</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>ATL (11)</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="8" t="inlineStr">
+        <is>
+          <t>TE27</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="n">
+        <v>238</v>
+      </c>
+      <c r="C208" s="5" t="n">
         <v>235</v>
       </c>
-      <c r="C207" s="5" t="n">
-        <v>259</v>
-      </c>
-      <c r="D207" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="E207" s="3" t="inlineStr">
-        <is>
-          <t>Pat Freiermuth</t>
-        </is>
-      </c>
-      <c r="F207" s="3" t="inlineStr">
-        <is>
-          <t>PIT (9)</t>
-        </is>
-      </c>
-      <c r="G207" s="3" t="inlineStr">
+      <c r="D208" s="3" t="n">
+        <v>253</v>
+      </c>
+      <c r="E208" s="3" t="inlineStr">
+        <is>
+          <t>Cade Otton</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="inlineStr">
+        <is>
+          <t>TB (10)</t>
+        </is>
+      </c>
+      <c r="G208" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
-        <is>
-          <t>WR87</t>
-        </is>
-      </c>
-      <c r="B208" s="3" t="n">
-        <v>237</v>
-      </c>
-      <c r="C208" s="5" t="n">
-        <v>265</v>
-      </c>
-      <c r="D208" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="E208" s="3" t="inlineStr">
-        <is>
-          <t>Zachariah Branch</t>
-        </is>
-      </c>
-      <c r="F208" s="3" t="inlineStr">
-        <is>
-          <t>ATL (11)</t>
-        </is>
-      </c>
-      <c r="G208" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="8" t="inlineStr">
         <is>
-          <t>TE27</t>
+          <t>TE28</t>
         </is>
       </c>
       <c r="B209" s="3" t="n">
-        <v>238</v>
-      </c>
-      <c r="C209" s="5" t="n">
-        <v>234</v>
+        <v>239</v>
+      </c>
+      <c r="C209" s="4" t="n">
+        <v>280</v>
       </c>
       <c r="D209" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="E209" s="3" t="inlineStr">
+        <is>
+          <t>David Njoku</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="inlineStr">
+        <is>
+          <t>LAC (7)</t>
+        </is>
+      </c>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>RB66</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="C210" s="5" t="n">
         <v>249</v>
       </c>
-      <c r="E209" s="3" t="inlineStr">
-        <is>
-          <t>Cade Otton</t>
-        </is>
-      </c>
-      <c r="F209" s="3" t="inlineStr">
-        <is>
-          <t>TB (10)</t>
-        </is>
-      </c>
-      <c r="G209" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="8" t="inlineStr">
-        <is>
-          <t>TE28</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="n">
-        <v>239</v>
-      </c>
-      <c r="C210" s="4" t="n">
-        <v>281</v>
-      </c>
       <c r="D210" s="3" t="n">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>David Njoku</t>
+          <t>Justice Hill</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>BAL (13)</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="6" t="inlineStr">
-        <is>
-          <t>RB66</t>
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>WR88</t>
         </is>
       </c>
       <c r="B211" s="3" t="n">
-        <v>240</v>
-      </c>
-      <c r="C211" s="5" t="n">
-        <v>270</v>
+        <v>241</v>
+      </c>
+      <c r="C211" s="4" t="n">
+        <v>286</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>Justice Hill</t>
+          <t>Jack Bech</t>
         </is>
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>BAL (13)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>WR88</t>
+          <t>WR89</t>
         </is>
       </c>
       <c r="B212" s="3" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C212" s="4" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>Jack Bech</t>
+          <t>Ted Hurst</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>TB (10)</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -7074,365 +7070,365 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="inlineStr">
-        <is>
-          <t>WR89</t>
+      <c r="A213" s="8" t="inlineStr">
+        <is>
+          <t>TE29</t>
         </is>
       </c>
       <c r="B213" s="3" t="n">
-        <v>242</v>
-      </c>
-      <c r="C213" s="5" t="n">
-        <v>261</v>
+        <v>243</v>
+      </c>
+      <c r="C213" s="9" t="n">
+        <v>187</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>286</v>
+        <v>213</v>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>Ted Hurst</t>
+          <t>Terrance Ferguson</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>TB (10)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="8" t="inlineStr">
-        <is>
-          <t>TE29</t>
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>RB67</t>
         </is>
       </c>
       <c r="B214" s="3" t="n">
-        <v>243</v>
-      </c>
-      <c r="C214" s="5" t="n">
-        <v>220</v>
+        <v>244</v>
+      </c>
+      <c r="C214" s="4" t="n">
+        <v>293</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>213</v>
+        <v>288</v>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>Terrance Ferguson</t>
+          <t>Ollie Gordon</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>RB67</t>
+          <t>RB68</t>
         </is>
       </c>
       <c r="B215" s="3" t="n">
-        <v>244</v>
-      </c>
-      <c r="C215" s="4" t="n">
+        <v>245</v>
+      </c>
+      <c r="C215" s="9" t="n">
+        <v>160</v>
+      </c>
+      <c r="D215" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="E215" s="3" t="inlineStr">
+        <is>
+          <t>MarShawn Lloyd</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="inlineStr">
+        <is>
+          <t>GB (11)</t>
+        </is>
+      </c>
+      <c r="G215" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>WR90</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="C216" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="D216" s="3" t="n">
+        <v>287</v>
+      </c>
+      <c r="E216" s="3" t="inlineStr">
+        <is>
+          <t>Elic Ayomanor</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="inlineStr">
+        <is>
+          <t>TEN (9)</t>
+        </is>
+      </c>
+      <c r="G216" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="8" t="inlineStr">
+        <is>
+          <t>TE30</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="C217" s="5" t="n">
+        <v>212</v>
+      </c>
+      <c r="D217" s="3" t="n">
+        <v>212</v>
+      </c>
+      <c r="E217" s="3" t="inlineStr">
+        <is>
+          <t>Colby Parkinson</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="inlineStr">
+        <is>
+          <t>LAR (11)</t>
+        </is>
+      </c>
+      <c r="G217" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>WR91</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="n">
+        <v>249</v>
+      </c>
+      <c r="C218" s="5" t="n">
+        <v>204</v>
+      </c>
+      <c r="D218" s="3" t="n">
+        <v>211</v>
+      </c>
+      <c r="E218" s="3" t="inlineStr">
+        <is>
+          <t>Keon Coleman</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="inlineStr">
+        <is>
+          <t>BUF (7)</t>
+        </is>
+      </c>
+      <c r="G218" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>RB69</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="C219" s="4" t="n">
         <v>293</v>
       </c>
-      <c r="D215" s="3" t="n">
-        <v>288</v>
-      </c>
-      <c r="E215" s="3" t="inlineStr">
-        <is>
-          <t>Ollie Gordon</t>
-        </is>
-      </c>
-      <c r="F215" s="3" t="inlineStr">
+      <c r="D219" s="3" t="inlineStr"/>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>Ty Johnson</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="inlineStr">
+        <is>
+          <t>BUF (7)</t>
+        </is>
+      </c>
+      <c r="G219" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>WR92</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="n">
+        <v>251</v>
+      </c>
+      <c r="C220" s="5" t="n">
+        <v>205</v>
+      </c>
+      <c r="D220" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="E220" s="3" t="inlineStr">
+        <is>
+          <t>Chris Bell</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="inlineStr">
         <is>
           <t>MIA (6)</t>
         </is>
       </c>
-      <c r="G215" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="6" t="inlineStr">
-        <is>
-          <t>RB68</t>
-        </is>
-      </c>
-      <c r="B216" s="3" t="n">
-        <v>245</v>
-      </c>
-      <c r="C216" s="11" t="n">
-        <v>163</v>
-      </c>
-      <c r="D216" s="3" t="n">
-        <v>156</v>
-      </c>
-      <c r="E216" s="3" t="inlineStr">
-        <is>
-          <t>MarShawn Lloyd</t>
-        </is>
-      </c>
-      <c r="F216" s="3" t="inlineStr">
-        <is>
-          <t>GB (11)</t>
-        </is>
-      </c>
-      <c r="G216" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="inlineStr">
-        <is>
-          <t>WR90</t>
-        </is>
-      </c>
-      <c r="B217" s="3" t="n">
-        <v>246</v>
-      </c>
-      <c r="C217" s="4" t="n">
-        <v>288</v>
-      </c>
-      <c r="D217" s="3" t="n">
-        <v>287</v>
-      </c>
-      <c r="E217" s="3" t="inlineStr">
-        <is>
-          <t>Elic Ayomanor</t>
-        </is>
-      </c>
-      <c r="F217" s="3" t="inlineStr">
-        <is>
-          <t>TEN (9)</t>
-        </is>
-      </c>
-      <c r="G217" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="8" t="inlineStr">
-        <is>
-          <t>TE30</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="n">
-        <v>248</v>
-      </c>
-      <c r="C218" s="5" t="n">
-        <v>221</v>
-      </c>
-      <c r="D218" s="3" t="n">
-        <v>212</v>
-      </c>
-      <c r="E218" s="3" t="inlineStr">
-        <is>
-          <t>Colby Parkinson</t>
-        </is>
-      </c>
-      <c r="F218" s="3" t="inlineStr">
-        <is>
-          <t>LAR (11)</t>
-        </is>
-      </c>
-      <c r="G218" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="inlineStr">
-        <is>
-          <t>WR91</t>
-        </is>
-      </c>
-      <c r="B219" s="3" t="n">
-        <v>249</v>
-      </c>
-      <c r="C219" s="5" t="n">
-        <v>204</v>
-      </c>
-      <c r="D219" s="3" t="n">
-        <v>210</v>
-      </c>
-      <c r="E219" s="3" t="inlineStr">
-        <is>
-          <t>Keon Coleman</t>
-        </is>
-      </c>
-      <c r="F219" s="3" t="inlineStr">
-        <is>
-          <t>BUF (7)</t>
-        </is>
-      </c>
-      <c r="G219" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="6" t="inlineStr">
-        <is>
-          <t>RB69</t>
-        </is>
-      </c>
-      <c r="B220" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="C220" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="D220" s="3" t="inlineStr"/>
-      <c r="E220" s="3" t="inlineStr">
-        <is>
-          <t>Ty Johnson</t>
-        </is>
-      </c>
-      <c r="F220" s="3" t="inlineStr">
-        <is>
-          <t>BUF (7)</t>
-        </is>
-      </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>WR92</t>
+          <t>WR93</t>
         </is>
       </c>
       <c r="B221" s="3" t="n">
+        <v>252</v>
+      </c>
+      <c r="C221" s="5" t="n">
+        <v>274</v>
+      </c>
+      <c r="D221" s="3" t="n">
+        <v>277</v>
+      </c>
+      <c r="E221" s="3" t="inlineStr">
+        <is>
+          <t>Elijah Sarratt</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="inlineStr">
+        <is>
+          <t>BAL (13)</t>
+        </is>
+      </c>
+      <c r="G221" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="8" t="inlineStr">
+        <is>
+          <t>TE31</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="n">
+        <v>254</v>
+      </c>
+      <c r="C222" s="5" t="n">
+        <v>215</v>
+      </c>
+      <c r="D222" s="3" t="n">
         <v>251</v>
       </c>
-      <c r="C221" s="5" t="n">
-        <v>203</v>
-      </c>
-      <c r="D221" s="3" t="n">
-        <v>208</v>
-      </c>
-      <c r="E221" s="3" t="inlineStr">
-        <is>
-          <t>Chris Bell</t>
-        </is>
-      </c>
-      <c r="F221" s="3" t="inlineStr">
-        <is>
-          <t>MIA (6)</t>
-        </is>
-      </c>
-      <c r="G221" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="inlineStr">
-        <is>
-          <t>WR93</t>
-        </is>
-      </c>
-      <c r="B222" s="3" t="n">
-        <v>252</v>
-      </c>
-      <c r="C222" s="5" t="n">
-        <v>270</v>
-      </c>
-      <c r="D222" s="3" t="n">
-        <v>276</v>
-      </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>Elijah Sarratt</t>
+          <t>Evan Engram</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>BAL (13)</t>
+          <t>DEN (10)</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="8" t="inlineStr">
-        <is>
-          <t>TE31</t>
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>WR94</t>
         </is>
       </c>
       <c r="B223" s="3" t="n">
-        <v>254</v>
-      </c>
-      <c r="C223" s="5" t="n">
-        <v>258</v>
-      </c>
-      <c r="D223" s="3" t="n">
-        <v>247</v>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="C223" s="4" t="n">
+        <v>298</v>
+      </c>
+      <c r="D223" s="3" t="inlineStr"/>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>Evan Engram</t>
+          <t>Christian Kirk</t>
         </is>
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>DEN (10)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>WR94</t>
+          <t>WR95</t>
         </is>
       </c>
       <c r="B224" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="C224" s="4" t="n">
-        <v>297</v>
-      </c>
-      <c r="D224" s="3" t="inlineStr"/>
+        <v>256</v>
+      </c>
+      <c r="C224" s="5" t="n">
+        <v>248</v>
+      </c>
+      <c r="D224" s="3" t="n">
+        <v>236</v>
+      </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>Christian Kirk</t>
+          <t>Malachi Fields</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>NYG (8)</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -7442,148 +7438,148 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>WR95</t>
+      <c r="A225" s="6" t="inlineStr">
+        <is>
+          <t>RB70</t>
         </is>
       </c>
       <c r="B225" s="3" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>236</v>
+        <v>275</v>
       </c>
       <c r="D225" s="3" t="n">
-        <v>232</v>
+        <v>281</v>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>Malachi Fields</t>
+          <t>DJ Giddens</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>NYG (8)</t>
+          <t>IND (13)</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="6" t="inlineStr">
-        <is>
-          <t>RB70</t>
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>WR96</t>
         </is>
       </c>
       <c r="B226" s="3" t="n">
-        <v>257</v>
-      </c>
-      <c r="C226" s="5" t="n">
-        <v>287</v>
-      </c>
-      <c r="D226" s="3" t="n">
-        <v>279</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="C226" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="D226" s="3" t="inlineStr"/>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>DJ Giddens</t>
+          <t>Tyreek Hill</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>IND (13)</t>
+          <t>FA ()</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="inlineStr">
-        <is>
-          <t>WR96</t>
+      <c r="A227" s="8" t="inlineStr">
+        <is>
+          <t>TE32</t>
         </is>
       </c>
       <c r="B227" s="3" t="n">
-        <v>258</v>
-      </c>
-      <c r="C227" s="4" t="n">
-        <v>366</v>
+        <v>259</v>
+      </c>
+      <c r="C227" s="5" t="n">
+        <v>277</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>Tyreek Hill</t>
+          <t>Eli Stowers</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>FA ()</t>
+          <t>PHI (10)</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="8" t="inlineStr">
-        <is>
-          <t>TE32</t>
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>WR97</t>
         </is>
       </c>
       <c r="B228" s="3" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>276</v>
-      </c>
-      <c r="D228" s="3" t="inlineStr"/>
+        <v>278</v>
+      </c>
+      <c r="D228" s="3" t="n">
+        <v>291</v>
+      </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>Eli Stowers</t>
+          <t>Tory Horton</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>PHI (10)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>WR97</t>
+          <t>WR98</t>
         </is>
       </c>
       <c r="B229" s="3" t="n">
-        <v>260</v>
-      </c>
-      <c r="C229" s="5" t="n">
-        <v>279</v>
+        <v>261</v>
+      </c>
+      <c r="C229" s="4" t="n">
+        <v>306</v>
       </c>
       <c r="D229" s="3" t="n">
         <v>292</v>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>Tory Horton</t>
+          <t>Marvin Mims</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>DEN (10)</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
@@ -7593,243 +7589,243 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="inlineStr">
-        <is>
-          <t>WR98</t>
+      <c r="A230" s="6" t="inlineStr">
+        <is>
+          <t>RB71</t>
         </is>
       </c>
       <c r="B230" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="C230" s="5" t="n">
+        <v>202</v>
+      </c>
+      <c r="D230" s="3" t="n">
+        <v>195</v>
+      </c>
+      <c r="E230" s="3" t="inlineStr">
+        <is>
+          <t>Jaydon Blue</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="inlineStr">
+        <is>
+          <t>DAL (14)</t>
+        </is>
+      </c>
+      <c r="G230" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="8" t="inlineStr">
+        <is>
+          <t>TE33</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="C231" s="5" t="n">
+        <v>264</v>
+      </c>
+      <c r="D231" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>Mason Taylor</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="inlineStr">
+        <is>
+          <t>NYJ (13)</t>
+        </is>
+      </c>
+      <c r="G231" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="6" t="inlineStr">
+        <is>
+          <t>RB72</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="C232" s="5" t="n">
+        <v>276</v>
+      </c>
+      <c r="D232" s="3" t="n">
+        <v>290</v>
+      </c>
+      <c r="E232" s="3" t="inlineStr">
+        <is>
+          <t>Chris Brooks</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="inlineStr">
+        <is>
+          <t>GB (11)</t>
+        </is>
+      </c>
+      <c r="G232" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="11" t="inlineStr">
+        <is>
+          <t>QB31</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="C233" s="5" t="n">
         <v>261</v>
       </c>
-      <c r="C230" s="4" t="n">
-        <v>311</v>
-      </c>
-      <c r="D230" s="3" t="n">
-        <v>293</v>
-      </c>
-      <c r="E230" s="3" t="inlineStr">
-        <is>
-          <t>Marvin Mims</t>
-        </is>
-      </c>
-      <c r="F230" s="3" t="inlineStr">
-        <is>
-          <t>DEN (10)</t>
-        </is>
-      </c>
-      <c r="G230" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="6" t="inlineStr">
-        <is>
-          <t>RB71</t>
-        </is>
-      </c>
-      <c r="B231" s="3" t="n">
-        <v>262</v>
-      </c>
-      <c r="C231" s="11" t="n">
-        <v>196</v>
-      </c>
-      <c r="D231" s="3" t="n">
-        <v>195</v>
-      </c>
-      <c r="E231" s="3" t="inlineStr">
-        <is>
-          <t>Jaydon Blue</t>
-        </is>
-      </c>
-      <c r="F231" s="3" t="inlineStr">
-        <is>
-          <t>DAL (14)</t>
-        </is>
-      </c>
-      <c r="G231" s="3" t="inlineStr">
+      <c r="D233" s="3" t="n">
+        <v>256</v>
+      </c>
+      <c r="E233" s="3" t="inlineStr">
+        <is>
+          <t>Tua Tagovailoa</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="inlineStr">
+        <is>
+          <t>ATL (11)</t>
+        </is>
+      </c>
+      <c r="G233" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>WR100</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="C234" s="5" t="n">
+        <v>271</v>
+      </c>
+      <c r="D234" s="3" t="n">
+        <v>237</v>
+      </c>
+      <c r="E234" s="3" t="inlineStr">
+        <is>
+          <t>Darius Slayton</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>NYG (8)</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="8" t="inlineStr">
+        <is>
+          <t>TE34</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="C235" s="4" t="n">
+        <v>320</v>
+      </c>
+      <c r="D235" s="3" t="inlineStr"/>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>Theo Johnson</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>NYG (8)</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="6" t="inlineStr">
+        <is>
+          <t>RB73</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="C236" s="5" t="n">
+        <v>226</v>
+      </c>
+      <c r="D236" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="E236" s="3" t="inlineStr">
+        <is>
+          <t>Samaje Perine</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>CIN (6)</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr">
         <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="8" t="inlineStr">
-        <is>
-          <t>TE33</t>
-        </is>
-      </c>
-      <c r="B232" s="3" t="n">
-        <v>264</v>
-      </c>
-      <c r="C232" s="5" t="n">
-        <v>261</v>
-      </c>
-      <c r="D232" s="3" t="n">
-        <v>263</v>
-      </c>
-      <c r="E232" s="3" t="inlineStr">
-        <is>
-          <t>Mason Taylor</t>
-        </is>
-      </c>
-      <c r="F232" s="3" t="inlineStr">
-        <is>
-          <t>NYJ (13)</t>
-        </is>
-      </c>
-      <c r="G232" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="6" t="inlineStr">
-        <is>
-          <t>RB72</t>
-        </is>
-      </c>
-      <c r="B233" s="3" t="n">
-        <v>265</v>
-      </c>
-      <c r="C233" s="5" t="n">
-        <v>273</v>
-      </c>
-      <c r="D233" s="3" t="n">
-        <v>291</v>
-      </c>
-      <c r="E233" s="3" t="inlineStr">
-        <is>
-          <t>Chris Brooks</t>
-        </is>
-      </c>
-      <c r="F233" s="3" t="inlineStr">
-        <is>
-          <t>GB (11)</t>
-        </is>
-      </c>
-      <c r="G233" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="10" t="inlineStr">
-        <is>
-          <t>QB31</t>
-        </is>
-      </c>
-      <c r="B234" s="3" t="n">
-        <v>266</v>
-      </c>
-      <c r="C234" s="5" t="n">
-        <v>252</v>
-      </c>
-      <c r="D234" s="3" t="n">
-        <v>252</v>
-      </c>
-      <c r="E234" s="3" t="inlineStr">
-        <is>
-          <t>Tua Tagovailoa</t>
-        </is>
-      </c>
-      <c r="F234" s="3" t="inlineStr">
-        <is>
-          <t>ATL (11)</t>
-        </is>
-      </c>
-      <c r="G234" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
-        <is>
-          <t>WR100</t>
-        </is>
-      </c>
-      <c r="B235" s="3" t="n">
-        <v>267</v>
-      </c>
-      <c r="C235" s="5" t="n">
-        <v>256</v>
-      </c>
-      <c r="D235" s="3" t="n">
-        <v>233</v>
-      </c>
-      <c r="E235" s="3" t="inlineStr">
-        <is>
-          <t>Darius Slayton</t>
-        </is>
-      </c>
-      <c r="F235" s="3" t="inlineStr">
-        <is>
-          <t>NYG (8)</t>
-        </is>
-      </c>
-      <c r="G235" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="8" t="inlineStr">
-        <is>
-          <t>TE34</t>
-        </is>
-      </c>
-      <c r="B236" s="3" t="n">
-        <v>268</v>
-      </c>
-      <c r="C236" s="4" t="n">
-        <v>319</v>
-      </c>
-      <c r="D236" s="3" t="inlineStr"/>
-      <c r="E236" s="3" t="inlineStr">
-        <is>
-          <t>Theo Johnson</t>
-        </is>
-      </c>
-      <c r="F236" s="3" t="inlineStr">
-        <is>
-          <t>NYG (8)</t>
-        </is>
-      </c>
-      <c r="G236" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>RB73</t>
+          <t>RB74</t>
         </is>
       </c>
       <c r="B237" s="3" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C237" s="5" t="n">
-        <v>238</v>
+        <v>296</v>
       </c>
       <c r="D237" s="3" t="n">
-        <v>237</v>
+        <v>289</v>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>Samaje Perine</t>
+          <t>Isaiah Davis</t>
         </is>
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>CIN (6)</t>
+          <t>NYJ (13)</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -7841,26 +7837,24 @@
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
         <is>
-          <t>RB74</t>
+          <t>RB75</t>
         </is>
       </c>
       <c r="B238" s="3" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>298</v>
-      </c>
-      <c r="D238" s="3" t="n">
-        <v>290</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="D238" s="3" t="inlineStr"/>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>Isaiah Davis</t>
+          <t>Demond Claiborne</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>NYJ (13)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -7872,26 +7866,26 @@
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>RB75</t>
+          <t>RB76</t>
         </is>
       </c>
       <c r="B239" s="3" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D239" s="3" t="n">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>Demond Claiborne</t>
+          <t>LeQuint Allen</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>JAC (7)</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -7903,26 +7897,24 @@
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
         <is>
-          <t>RB76</t>
+          <t>RB77</t>
         </is>
       </c>
       <c r="B240" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="C240" s="5" t="n">
-        <v>288</v>
-      </c>
-      <c r="D240" s="3" t="n">
-        <v>282</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="C240" s="4" t="n">
+        <v>351</v>
+      </c>
+      <c r="D240" s="3" t="inlineStr"/>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>LeQuint Allen</t>
+          <t>Devin Neal</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>JAC (7)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -7932,206 +7924,210 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="6" t="inlineStr">
-        <is>
-          <t>RB77</t>
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>WR101</t>
         </is>
       </c>
       <c r="B241" s="3" t="n">
+        <v>274</v>
+      </c>
+      <c r="C241" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D241" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E241" s="3" t="inlineStr">
+        <is>
+          <t>Xavier Legette</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>CAR (5)</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>RB78</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="C242" s="5" t="n">
+        <v>301</v>
+      </c>
+      <c r="D242" s="3" t="n">
+        <v>280</v>
+      </c>
+      <c r="E242" s="3" t="inlineStr">
+        <is>
+          <t>Seth McGowan</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>IND (13)</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="11" t="inlineStr">
+        <is>
+          <t>QB32</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="C243" s="5" t="n">
+        <v>277</v>
+      </c>
+      <c r="D243" s="3" t="n">
+        <v>262</v>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>Michael Penix</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>ATL (11)</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>RB79</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="n">
+        <v>277</v>
+      </c>
+      <c r="C244" s="5" t="n">
+        <v>274</v>
+      </c>
+      <c r="D244" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="C241" s="4" t="n">
-        <v>343</v>
-      </c>
-      <c r="D241" s="3" t="inlineStr"/>
-      <c r="E241" s="3" t="inlineStr">
-        <is>
-          <t>Devin Neal</t>
-        </is>
-      </c>
-      <c r="F241" s="3" t="inlineStr">
-        <is>
-          <t>NO (8)</t>
-        </is>
-      </c>
-      <c r="G241" s="3" t="inlineStr">
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>Jordan James</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>SF (8)</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>WR101</t>
-        </is>
-      </c>
-      <c r="B242" s="3" t="n">
-        <v>274</v>
-      </c>
-      <c r="C242" s="5" t="n">
-        <v>291</v>
-      </c>
-      <c r="D242" s="3" t="inlineStr"/>
-      <c r="E242" s="3" t="inlineStr">
-        <is>
-          <t>Xavier Legette</t>
-        </is>
-      </c>
-      <c r="F242" s="3" t="inlineStr">
-        <is>
-          <t>CAR (5)</t>
-        </is>
-      </c>
-      <c r="G242" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="6" t="inlineStr">
-        <is>
-          <t>RB78</t>
-        </is>
-      </c>
-      <c r="B243" s="3" t="n">
-        <v>275</v>
-      </c>
-      <c r="C243" s="5" t="n">
-        <v>286</v>
-      </c>
-      <c r="D243" s="3" t="inlineStr"/>
-      <c r="E243" s="3" t="inlineStr">
-        <is>
-          <t>Seth McGowan</t>
-        </is>
-      </c>
-      <c r="F243" s="3" t="inlineStr">
-        <is>
-          <t>IND (13)</t>
-        </is>
-      </c>
-      <c r="G243" s="3" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="8" t="inlineStr">
+        <is>
+          <t>TE35</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="n">
+        <v>278</v>
+      </c>
+      <c r="C245" s="9" t="n">
+        <v>186</v>
+      </c>
+      <c r="D245" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="E245" s="3" t="inlineStr">
+        <is>
+          <t>Greg Dulcich</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="6" t="inlineStr">
+        <is>
+          <t>RB80</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="n">
+        <v>280</v>
+      </c>
+      <c r="C246" s="4" t="n">
+        <v>327</v>
+      </c>
+      <c r="D246" s="3" t="inlineStr"/>
+      <c r="E246" s="3" t="inlineStr">
+        <is>
+          <t>Kaleb Johnson</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>PIT (9)</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr">
         <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="10" t="inlineStr">
-        <is>
-          <t>QB32</t>
-        </is>
-      </c>
-      <c r="B244" s="3" t="n">
-        <v>276</v>
-      </c>
-      <c r="C244" s="5" t="n">
-        <v>275</v>
-      </c>
-      <c r="D244" s="3" t="n">
-        <v>259</v>
-      </c>
-      <c r="E244" s="3" t="inlineStr">
-        <is>
-          <t>Michael Penix</t>
-        </is>
-      </c>
-      <c r="F244" s="3" t="inlineStr">
-        <is>
-          <t>ATL (11)</t>
-        </is>
-      </c>
-      <c r="G244" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="6" t="inlineStr">
-        <is>
-          <t>RB79</t>
-        </is>
-      </c>
-      <c r="B245" s="3" t="n">
-        <v>277</v>
-      </c>
-      <c r="C245" s="5" t="n">
-        <v>272</v>
-      </c>
-      <c r="D245" s="3" t="n">
-        <v>272</v>
-      </c>
-      <c r="E245" s="3" t="inlineStr">
-        <is>
-          <t>Jordan James</t>
-        </is>
-      </c>
-      <c r="F245" s="3" t="inlineStr">
-        <is>
-          <t>SF (8)</t>
-        </is>
-      </c>
-      <c r="G245" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="8" t="inlineStr">
-        <is>
-          <t>TE35</t>
-        </is>
-      </c>
-      <c r="B246" s="3" t="n">
-        <v>278</v>
-      </c>
-      <c r="C246" s="5" t="n">
-        <v>219</v>
-      </c>
-      <c r="D246" s="3" t="n">
-        <v>206</v>
-      </c>
-      <c r="E246" s="3" t="inlineStr">
-        <is>
-          <t>Greg Dulcich</t>
-        </is>
-      </c>
-      <c r="F246" s="3" t="inlineStr">
-        <is>
-          <t>MIA (6)</t>
-        </is>
-      </c>
-      <c r="G246" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>RB80</t>
+          <t>RB81</t>
         </is>
       </c>
       <c r="B247" s="3" t="n">
-        <v>280</v>
-      </c>
-      <c r="C247" s="4" t="n">
-        <v>333</v>
+        <v>281</v>
+      </c>
+      <c r="C247" s="5" t="n">
+        <v>284</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>Kaleb Johnson</t>
+          <t>Trey Benson</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>PIT (9)</t>
+          <t>ARI (14)</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -8141,88 +8137,88 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="6" t="inlineStr">
-        <is>
-          <t>RB81</t>
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>WR102</t>
         </is>
       </c>
       <c r="B248" s="3" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>277</v>
-      </c>
-      <c r="D248" s="3" t="inlineStr"/>
+        <v>284</v>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>269</v>
+      </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>Trey Benson</t>
+          <t>Tyquan Thornton</t>
         </is>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>ARI (14)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="6" t="inlineStr">
+        <is>
+          <t>RB82</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="n">
+        <v>283</v>
+      </c>
+      <c r="C249" s="5" t="n">
+        <v>290</v>
+      </c>
+      <c r="D249" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="E249" s="3" t="inlineStr">
+        <is>
+          <t>George Holani</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>SEA (11)</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr">
+        <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>WR102</t>
-        </is>
-      </c>
-      <c r="B249" s="3" t="n">
-        <v>282</v>
-      </c>
-      <c r="C249" s="5" t="n">
-        <v>284</v>
-      </c>
-      <c r="D249" s="3" t="n">
-        <v>267</v>
-      </c>
-      <c r="E249" s="3" t="inlineStr">
-        <is>
-          <t>Tyquan Thornton</t>
-        </is>
-      </c>
-      <c r="F249" s="3" t="inlineStr">
-        <is>
-          <t>KC (5)</t>
-        </is>
-      </c>
-      <c r="G249" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
         <is>
-          <t>RB82</t>
+          <t>RB83</t>
         </is>
       </c>
       <c r="B250" s="3" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>289</v>
-      </c>
-      <c r="D250" s="3" t="n">
-        <v>280</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="D250" s="3" t="inlineStr"/>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>George Holani</t>
+          <t>Malik Davis</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>DAL (14)</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -8232,57 +8228,57 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="6" t="inlineStr">
-        <is>
-          <t>RB83</t>
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>WR103</t>
         </is>
       </c>
       <c r="B251" s="3" t="n">
-        <v>284</v>
-      </c>
-      <c r="C251" s="5" t="n">
         <v>285</v>
       </c>
-      <c r="D251" s="3" t="inlineStr"/>
+      <c r="C251" s="9" t="n">
+        <v>183</v>
+      </c>
+      <c r="D251" s="3" t="n">
+        <v>219</v>
+      </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>Malik Davis</t>
+          <t>Devaughn Vele</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>DAL (14)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>WR103</t>
+          <t>WR104</t>
         </is>
       </c>
       <c r="B252" s="3" t="n">
-        <v>285</v>
-      </c>
-      <c r="C252" s="5" t="n">
-        <v>264</v>
-      </c>
-      <c r="D252" s="3" t="n">
-        <v>218</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="C252" s="4" t="n">
+        <v>341</v>
+      </c>
+      <c r="D252" s="3" t="inlineStr"/>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>Devaughn Vele</t>
+          <t>Kyle Williams</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -8292,115 +8288,117 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>WR104</t>
+      <c r="A253" s="11" t="inlineStr">
+        <is>
+          <t>QB33</t>
         </is>
       </c>
       <c r="B253" s="3" t="n">
-        <v>288</v>
-      </c>
-      <c r="C253" s="4" t="n">
-        <v>340</v>
+        <v>289</v>
+      </c>
+      <c r="C253" s="5" t="n">
+        <v>283</v>
       </c>
       <c r="D253" s="3" t="inlineStr"/>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>Kyle Williams</t>
+          <t>Shedeur Sanders</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="10" t="inlineStr">
-        <is>
-          <t>QB33</t>
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>WR105</t>
         </is>
       </c>
       <c r="B254" s="3" t="n">
-        <v>289</v>
-      </c>
-      <c r="C254" s="5" t="n">
-        <v>287</v>
-      </c>
-      <c r="D254" s="3" t="inlineStr"/>
+        <v>290</v>
+      </c>
+      <c r="C254" s="7" t="n">
+        <v>137</v>
+      </c>
+      <c r="D254" s="3" t="n">
+        <v>146</v>
+      </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>Shedeur Sanders</t>
+          <t>Keenan Allen</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>WR105</t>
+      <c r="A255" s="6" t="inlineStr">
+        <is>
+          <t>RB84</t>
         </is>
       </c>
       <c r="B255" s="3" t="n">
-        <v>290</v>
-      </c>
-      <c r="C255" s="5" t="n">
-        <v>267</v>
-      </c>
-      <c r="D255" s="3" t="n">
-        <v>147</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="C255" s="4" t="n">
+        <v>338</v>
+      </c>
+      <c r="D255" s="3" t="inlineStr"/>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>Keenan Allen</t>
+          <t>Brashard Smith</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>RB84</t>
+          <t>RB85</t>
         </is>
       </c>
       <c r="B256" s="3" t="n">
-        <v>292</v>
-      </c>
-      <c r="C256" s="4" t="n">
-        <v>337</v>
-      </c>
-      <c r="D256" s="3" t="inlineStr"/>
+        <v>293</v>
+      </c>
+      <c r="C256" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="D256" s="3" t="n">
+        <v>241</v>
+      </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>Brashard Smith</t>
+          <t>Kaelon Black</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>KC (5)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -8410,297 +8408,297 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="6" t="inlineStr">
-        <is>
-          <t>RB85</t>
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>WR106</t>
         </is>
       </c>
       <c r="B257" s="3" t="n">
-        <v>293</v>
-      </c>
-      <c r="C257" s="5" t="n">
-        <v>239</v>
-      </c>
-      <c r="D257" s="3" t="n">
-        <v>238</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="C257" s="4" t="n">
+        <v>346</v>
+      </c>
+      <c r="D257" s="3" t="inlineStr"/>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>Kaelon Black</t>
+          <t>Hollywood Brown</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>PHI (10)</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>WR106</t>
+      <c r="A258" s="6" t="inlineStr">
+        <is>
+          <t>RB86</t>
         </is>
       </c>
       <c r="B258" s="3" t="n">
-        <v>294</v>
-      </c>
-      <c r="C258" s="4" t="n">
-        <v>349</v>
+        <v>296</v>
+      </c>
+      <c r="C258" s="5" t="n">
+        <v>311</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>Hollywood Brown</t>
+          <t>Devin Singletary</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>PHI (10)</t>
+          <t>NYG (8)</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="6" t="inlineStr">
-        <is>
-          <t>RB86</t>
+      <c r="A259" s="8" t="inlineStr">
+        <is>
+          <t>TE36</t>
         </is>
       </c>
       <c r="B259" s="3" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>310</v>
+        <v>339</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>Devin Singletary</t>
+          <t>Oscar Delp</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>NYG (8)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="6" t="inlineStr">
+        <is>
+          <t>RB87</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="n">
+        <v>298</v>
+      </c>
+      <c r="C260" s="5" t="n">
+        <v>276</v>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>274</v>
+      </c>
+      <c r="E260" s="3" t="inlineStr">
+        <is>
+          <t>Emari Demercado</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>KC (5)</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr">
+        <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="8" t="inlineStr">
-        <is>
-          <t>TE36</t>
-        </is>
-      </c>
-      <c r="B260" s="3" t="n">
-        <v>297</v>
-      </c>
-      <c r="C260" s="5" t="n">
-        <v>338</v>
-      </c>
-      <c r="D260" s="3" t="inlineStr"/>
-      <c r="E260" s="3" t="inlineStr">
-        <is>
-          <t>Oscar Delp</t>
-        </is>
-      </c>
-      <c r="F260" s="3" t="inlineStr">
+    <row r="261">
+      <c r="A261" s="11" t="inlineStr">
+        <is>
+          <t>QB34</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="n">
+        <v>299</v>
+      </c>
+      <c r="C261" s="5" t="n">
+        <v>245</v>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="E261" s="3" t="inlineStr">
+        <is>
+          <t>Deshaun Watson</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="inlineStr">
+        <is>
+          <t>QB</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="8" t="inlineStr">
+        <is>
+          <t>TE37</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="C262" s="5" t="n">
+        <v>265</v>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="E262" s="3" t="inlineStr">
+        <is>
+          <t>Mike Gesicki</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>CIN (6)</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="6" t="inlineStr">
+        <is>
+          <t>RB88</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="n">
+        <v>301</v>
+      </c>
+      <c r="C263" s="4" t="n">
+        <v>366</v>
+      </c>
+      <c r="D263" s="3" t="inlineStr"/>
+      <c r="E263" s="3" t="inlineStr">
+        <is>
+          <t>Kendre Miller</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="inlineStr">
         <is>
           <t>NO (8)</t>
         </is>
       </c>
-      <c r="G260" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="6" t="inlineStr">
-        <is>
-          <t>RB87</t>
-        </is>
-      </c>
-      <c r="B261" s="3" t="n">
-        <v>298</v>
-      </c>
-      <c r="C261" s="5" t="n">
-        <v>274</v>
-      </c>
-      <c r="D261" s="3" t="n">
-        <v>273</v>
-      </c>
-      <c r="E261" s="3" t="inlineStr">
-        <is>
-          <t>Emari Demercado</t>
-        </is>
-      </c>
-      <c r="F261" s="3" t="inlineStr">
-        <is>
-          <t>KC (5)</t>
-        </is>
-      </c>
-      <c r="G261" s="3" t="inlineStr">
+      <c r="G263" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="10" t="inlineStr">
-        <is>
-          <t>QB34</t>
-        </is>
-      </c>
-      <c r="B262" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="C262" s="5" t="n">
-        <v>241</v>
-      </c>
-      <c r="D262" s="3" t="n">
-        <v>251</v>
-      </c>
-      <c r="E262" s="3" t="inlineStr">
-        <is>
-          <t>Deshaun Watson</t>
-        </is>
-      </c>
-      <c r="F262" s="3" t="inlineStr">
-        <is>
-          <t>CLE (11)</t>
-        </is>
-      </c>
-      <c r="G262" s="3" t="inlineStr">
+    <row r="264">
+      <c r="A264" s="11" t="inlineStr">
+        <is>
+          <t>QB35</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="n">
+        <v>302</v>
+      </c>
+      <c r="C264" s="5" t="n">
+        <v>262</v>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>261</v>
+      </c>
+      <c r="E264" s="3" t="inlineStr">
+        <is>
+          <t>Kirk Cousins</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>LV (13)</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr">
         <is>
           <t>QB</t>
         </is>
       </c>
     </row>
-    <row r="263">
-      <c r="A263" s="8" t="inlineStr">
-        <is>
-          <t>TE37</t>
-        </is>
-      </c>
-      <c r="B263" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="C263" s="5" t="n">
-        <v>280</v>
-      </c>
-      <c r="D263" s="3" t="n">
-        <v>265</v>
-      </c>
-      <c r="E263" s="3" t="inlineStr">
-        <is>
-          <t>Mike Gesicki</t>
-        </is>
-      </c>
-      <c r="F263" s="3" t="inlineStr">
-        <is>
-          <t>CIN (6)</t>
-        </is>
-      </c>
-      <c r="G263" s="3" t="inlineStr">
-        <is>
-          <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="6" t="inlineStr">
-        <is>
-          <t>RB88</t>
-        </is>
-      </c>
-      <c r="B264" s="3" t="n">
-        <v>301</v>
-      </c>
-      <c r="C264" s="4" t="n">
-        <v>363</v>
-      </c>
-      <c r="D264" s="3" t="inlineStr"/>
-      <c r="E264" s="3" t="inlineStr">
-        <is>
-          <t>Kendre Miller</t>
-        </is>
-      </c>
-      <c r="F264" s="3" t="inlineStr">
-        <is>
-          <t>NO (8)</t>
-        </is>
-      </c>
-      <c r="G264" s="3" t="inlineStr">
+    <row r="265">
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>RB90</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="C265" s="5" t="n">
+        <v>227</v>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="E265" s="3" t="inlineStr">
+        <is>
+          <t>Najee Harris</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>LAC (7)</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr">
         <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="10" t="inlineStr">
-        <is>
-          <t>QB35</t>
-        </is>
-      </c>
-      <c r="B265" s="3" t="n">
-        <v>302</v>
-      </c>
-      <c r="C265" s="5" t="n">
-        <v>253</v>
-      </c>
-      <c r="D265" s="3" t="n">
-        <v>258</v>
-      </c>
-      <c r="E265" s="3" t="inlineStr">
-        <is>
-          <t>Kirk Cousins</t>
-        </is>
-      </c>
-      <c r="F265" s="3" t="inlineStr">
-        <is>
-          <t>LV (13)</t>
-        </is>
-      </c>
-      <c r="G265" s="3" t="inlineStr">
-        <is>
-          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
         <is>
-          <t>RB90</t>
+          <t>RB91</t>
         </is>
       </c>
       <c r="B266" s="3" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="D266" s="3" t="inlineStr"/>
       <c r="E266" s="3" t="inlineStr">
         <is>
-          <t>Najee Harris</t>
+          <t>Adam Randall</t>
         </is>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>BAL (13)</t>
         </is>
       </c>
       <c r="G266" s="3" t="inlineStr">
@@ -8710,21 +8708,23 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="6" t="inlineStr">
-        <is>
-          <t>RB91</t>
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>WR108</t>
         </is>
       </c>
       <c r="B267" s="3" t="n">
-        <v>305</v>
-      </c>
-      <c r="C267" s="5" t="n">
-        <v>280</v>
-      </c>
-      <c r="D267" s="3" t="inlineStr"/>
+        <v>306</v>
+      </c>
+      <c r="C267" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="D267" s="3" t="n">
+        <v>181</v>
+      </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
-          <t>Adam Randall</t>
+          <t>Ja'Kobi Lane</t>
         </is>
       </c>
       <c r="F267" s="3" t="inlineStr">
@@ -8734,91 +8734,89 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="6" t="inlineStr">
+        <is>
+          <t>RB93</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="n">
+        <v>309</v>
+      </c>
+      <c r="C268" s="5" t="n">
+        <v>321</v>
+      </c>
+      <c r="D268" s="3" t="inlineStr"/>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>Trevor Etienne</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="inlineStr">
+        <is>
+          <t>CAR (5)</t>
+        </is>
+      </c>
+      <c r="G268" s="3" t="inlineStr">
+        <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
-        <is>
-          <t>WR108</t>
-        </is>
-      </c>
-      <c r="B268" s="3" t="n">
-        <v>306</v>
-      </c>
-      <c r="C268" s="11" t="n">
-        <v>191</v>
-      </c>
-      <c r="D268" s="3" t="n">
-        <v>181</v>
-      </c>
-      <c r="E268" s="3" t="inlineStr">
-        <is>
-          <t>Ja'Kobi Lane</t>
-        </is>
-      </c>
-      <c r="F268" s="3" t="inlineStr">
-        <is>
-          <t>BAL (13)</t>
-        </is>
-      </c>
-      <c r="G268" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
     <row r="269">
-      <c r="A269" s="6" t="inlineStr">
-        <is>
-          <t>RB93</t>
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>WR109</t>
         </is>
       </c>
       <c r="B269" s="3" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>336</v>
+        <v>302</v>
       </c>
       <c r="D269" s="3" t="inlineStr"/>
       <c r="E269" s="3" t="inlineStr">
         <is>
-          <t>Trevor Etienne</t>
+          <t>Isaiah Bond</t>
         </is>
       </c>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>CAR (5)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>WR109</t>
+          <t>WR110</t>
         </is>
       </c>
       <c r="B270" s="3" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
         <is>
-          <t>Isaiah Bond</t>
+          <t>Skyler Bell</t>
         </is>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G270" s="3" t="inlineStr">
@@ -8828,79 +8826,81 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="inlineStr">
-        <is>
-          <t>WR110</t>
+      <c r="A271" s="8" t="inlineStr">
+        <is>
+          <t>TE38</t>
         </is>
       </c>
       <c r="B271" s="3" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr">
         <is>
-          <t>Skyler Bell</t>
+          <t>Jake Tonges</t>
         </is>
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="8" t="inlineStr">
-        <is>
-          <t>TE38</t>
+      <c r="A272" s="6" t="inlineStr">
+        <is>
+          <t>RB95</t>
         </is>
       </c>
       <c r="B272" s="3" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
         <is>
-          <t>Jake Tonges</t>
+          <t>Tahj Brooks</t>
         </is>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>CIN (6)</t>
         </is>
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="6" t="inlineStr">
-        <is>
-          <t>RB95</t>
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>WR111</t>
         </is>
       </c>
       <c r="B273" s="3" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>298</v>
-      </c>
-      <c r="D273" s="3" t="inlineStr"/>
+        <v>267</v>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>268</v>
+      </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
-          <t>Tahj Brooks</t>
+          <t>Andrei Iosivas</t>
         </is>
       </c>
       <c r="F273" s="3" t="inlineStr">
@@ -8910,62 +8910,60 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="6" t="inlineStr">
+        <is>
+          <t>RB96</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="n">
+        <v>317</v>
+      </c>
+      <c r="C274" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="D274" s="3" t="inlineStr"/>
+      <c r="E274" s="3" t="inlineStr">
+        <is>
+          <t>Jarquez Hunter</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="inlineStr">
+        <is>
+          <t>LAR (11)</t>
+        </is>
+      </c>
+      <c r="G274" s="3" t="inlineStr">
+        <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
-        <is>
-          <t>WR111</t>
-        </is>
-      </c>
-      <c r="B274" s="3" t="n">
-        <v>316</v>
-      </c>
-      <c r="C274" s="5" t="n">
-        <v>262</v>
-      </c>
-      <c r="D274" s="3" t="n">
-        <v>266</v>
-      </c>
-      <c r="E274" s="3" t="inlineStr">
-        <is>
-          <t>Andrei Iosivas</t>
-        </is>
-      </c>
-      <c r="F274" s="3" t="inlineStr">
-        <is>
-          <t>CIN (6)</t>
-        </is>
-      </c>
-      <c r="G274" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>RB96</t>
+          <t>RB98</t>
         </is>
       </c>
       <c r="B275" s="3" t="n">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D275" s="3" t="inlineStr"/>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>Jarquez Hunter</t>
+          <t>Audric Estime</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
@@ -8975,146 +8973,146 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="6" t="inlineStr">
-        <is>
-          <t>RB98</t>
+      <c r="A276" s="8" t="inlineStr">
+        <is>
+          <t>TE39</t>
         </is>
       </c>
       <c r="B276" s="3" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C276" s="5" t="n">
-        <v>348</v>
-      </c>
-      <c r="D276" s="3" t="inlineStr"/>
+        <v>281</v>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>278</v>
+      </c>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>Audric Estime</t>
+          <t>Darnell Washington</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>PIT (9)</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="8" t="inlineStr">
-        <is>
-          <t>TE39</t>
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>WR112</t>
         </is>
       </c>
       <c r="B277" s="3" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>282</v>
-      </c>
-      <c r="D277" s="3" t="n">
-        <v>277</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="D277" s="3" t="inlineStr"/>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>Darnell Washington</t>
+          <t>Cedric Tillman</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>PIT (9)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>WR112</t>
+      <c r="A278" s="11" t="inlineStr">
+        <is>
+          <t>QB36</t>
         </is>
       </c>
       <c r="B278" s="3" t="n">
-        <v>324</v>
-      </c>
-      <c r="C278" s="4" t="n">
-        <v>375</v>
+        <v>327</v>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>369</v>
       </c>
       <c r="D278" s="3" t="inlineStr"/>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>Cedric Tillman</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="10" t="inlineStr">
-        <is>
-          <t>QB36</t>
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>WR114</t>
         </is>
       </c>
       <c r="B279" s="3" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>369</v>
-      </c>
-      <c r="D279" s="3" t="inlineStr"/>
+        <v>295</v>
+      </c>
+      <c r="D279" s="3" t="n">
+        <v>271</v>
+      </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Luke McCaffrey</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>WR114</t>
+          <t>WR115</t>
         </is>
       </c>
       <c r="B280" s="3" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>294</v>
-      </c>
-      <c r="D280" s="3" t="n">
-        <v>270</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="D280" s="3" t="inlineStr"/>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Luke McCaffrey</t>
+          <t>Tez Johnson</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>TB (10)</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -9126,24 +9124,26 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>WR115</t>
+          <t>WR116</t>
         </is>
       </c>
       <c r="B281" s="3" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C281" s="5" t="n">
-        <v>370</v>
-      </c>
-      <c r="D281" s="3" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="D281" s="3" t="n">
+        <v>222</v>
+      </c>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>Tez Johnson</t>
+          <t>Jahan Dotson</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>TB (10)</t>
+          <t>ATL (11)</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -9155,24 +9155,24 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>WR116</t>
+          <t>WR117</t>
         </is>
       </c>
       <c r="B282" s="3" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C282" s="5" t="n">
-        <v>269</v>
+        <v>345</v>
       </c>
       <c r="D282" s="3" t="inlineStr"/>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>Jalen Royals</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>ATL (11)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
@@ -9182,86 +9182,88 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="inlineStr">
-        <is>
-          <t>WR117</t>
+      <c r="A283" s="8" t="inlineStr">
+        <is>
+          <t>TE40</t>
         </is>
       </c>
       <c r="B283" s="3" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C283" s="5" t="n">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="D283" s="3" t="inlineStr"/>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>Jalen Royals</t>
+          <t>Max Klare</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>KC (5)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="8" t="inlineStr">
-        <is>
-          <t>TE40</t>
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>WR118</t>
         </is>
       </c>
       <c r="B284" s="3" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>374</v>
-      </c>
-      <c r="D284" s="3" t="inlineStr"/>
+        <v>203</v>
+      </c>
+      <c r="D284" s="3" t="n">
+        <v>209</v>
+      </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Max Klare</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>WR118</t>
+          <t>WR119</t>
         </is>
       </c>
       <c r="B285" s="3" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>224</v>
+        <v>294</v>
       </c>
       <c r="D285" s="3" t="n">
-        <v>209</v>
+        <v>270</v>
       </c>
       <c r="E285" s="3" t="inlineStr">
         <is>
-          <t>Caleb Douglas</t>
+          <t>Calvin Austin</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>NYG (8)</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -9273,26 +9275,26 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>WR119</t>
+          <t>WR120</t>
         </is>
       </c>
       <c r="B286" s="3" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>286</v>
+        <v>357</v>
       </c>
       <c r="D286" s="3" t="n">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>Calvin Austin</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>NYG (8)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -9304,26 +9306,24 @@
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>WR120</t>
+          <t>WR122</t>
         </is>
       </c>
       <c r="B287" s="3" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>359</v>
-      </c>
-      <c r="D287" s="3" t="n">
-        <v>299</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="D287" s="3" t="inlineStr"/>
       <c r="E287" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Joshua Palmer</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -9333,55 +9333,55 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="inlineStr">
-        <is>
-          <t>WR122</t>
+      <c r="A288" s="8" t="inlineStr">
+        <is>
+          <t>TE41</t>
         </is>
       </c>
       <c r="B288" s="3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Joshua Palmer</t>
+          <t>Michael Mayer</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="8" t="inlineStr">
         <is>
-          <t>TE41</t>
+          <t>TE42</t>
         </is>
       </c>
       <c r="B289" s="3" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>Michael Mayer</t>
+          <t>Elijah Arroyo</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -9393,24 +9393,24 @@
     <row r="290">
       <c r="A290" s="8" t="inlineStr">
         <is>
-          <t>TE42</t>
+          <t>TE43</t>
         </is>
       </c>
       <c r="B290" s="3" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>335</v>
+        <v>307</v>
       </c>
       <c r="D290" s="3" t="inlineStr"/>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Elijah Arroyo</t>
+          <t>Tyler Higbee</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -9420,171 +9420,171 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="8" t="inlineStr">
-        <is>
-          <t>TE43</t>
+      <c r="A291" s="11" t="inlineStr">
+        <is>
+          <t>QB37</t>
         </is>
       </c>
       <c r="B291" s="3" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>309</v>
+        <v>378</v>
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>Tyler Higbee</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="10" t="inlineStr">
-        <is>
-          <t>QB37</t>
+      <c r="A292" s="8" t="inlineStr">
+        <is>
+          <t>TE45</t>
         </is>
       </c>
       <c r="B292" s="3" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Dawson Knox</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="8" t="inlineStr">
-        <is>
-          <t>TE45</t>
+      <c r="A293" s="11" t="inlineStr">
+        <is>
+          <t>QB38</t>
         </is>
       </c>
       <c r="B293" s="3" t="n">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>376</v>
+        <v>342</v>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr">
         <is>
-          <t>Dawson Knox</t>
+          <t>Carson Beck</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>ARI (14)</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="10" t="inlineStr">
-        <is>
-          <t>QB38</t>
+      <c r="A294" s="8" t="inlineStr">
+        <is>
+          <t>TE47</t>
         </is>
       </c>
       <c r="B294" s="3" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>342</v>
+        <v>372</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>Carson Beck</t>
+          <t>Cole Kmet</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>ARI (14)</t>
+          <t>CHI (10)</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="8" t="inlineStr">
-        <is>
-          <t>TE47</t>
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>WR124</t>
         </is>
       </c>
       <c r="B295" s="3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>371</v>
+        <v>340</v>
       </c>
       <c r="D295" s="3" t="inlineStr"/>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>Cole Kmet</t>
+          <t>Brenen Thompson</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>CHI (10)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>WR124</t>
+          <t>WR125</t>
         </is>
       </c>
       <c r="B296" s="3" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="D296" s="3" t="inlineStr"/>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>Brenen Thompson</t>
+          <t>DeMario Douglas</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -9596,24 +9596,24 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>WR125</t>
+          <t>WR128</t>
         </is>
       </c>
       <c r="B297" s="3" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="D297" s="3" t="inlineStr"/>
       <c r="E297" s="3" t="inlineStr">
         <is>
-          <t>DeMario Douglas</t>
+          <t>Xavier Hutchinson</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>HOU (8)</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -9661,10 +9661,10 @@
         <v>363</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="D299" s="3" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E299" s="3" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>365</v>
       </c>
       <c r="C300" s="5" t="n">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="D300" s="3" t="inlineStr"/>
       <c r="E300" s="3" t="inlineStr">
@@ -9721,7 +9721,7 @@
         <v>367</v>
       </c>
       <c r="C301" s="5" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D301" s="3" t="inlineStr"/>
       <c r="E301" s="3" t="inlineStr">
@@ -9808,7 +9808,7 @@
         <v>383</v>
       </c>
       <c r="C304" s="5" t="n">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D304" s="3" t="inlineStr"/>
       <c r="E304" s="3" t="inlineStr">
@@ -9866,10 +9866,10 @@
         <v>387</v>
       </c>
       <c r="C306" s="5" t="n">
-        <v>321</v>
+        <v>282</v>
       </c>
       <c r="D306" s="3" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E306" s="3" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>395</v>
       </c>
       <c r="C307" s="5" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D307" s="3" t="inlineStr"/>
       <c r="E307" s="3" t="inlineStr">

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G307"/>
+  <dimension ref="A1:G306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4453,7 +4453,7 @@
         <v>229</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>266</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>220</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>213</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>247</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>174</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D168" s="3" t="inlineStr"/>
       <c r="E168" s="3" t="inlineStr">
@@ -5722,7 +5722,7 @@
         <v>184</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>273</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>244</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>182</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>285</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>222</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>236</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>223</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>221</v>
+        <v>271</v>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>287</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>272</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>224</v>
       </c>
       <c r="C199" s="4" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D199" s="3" t="inlineStr"/>
       <c r="E199" s="3" t="inlineStr">
@@ -6771,7 +6771,7 @@
         <v>232</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D203" s="3" t="n">
         <v>299</v>
@@ -6865,7 +6865,7 @@
         <v>216</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>283</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>235</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>280</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         <v>249</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>286</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>187</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>212</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>204</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>250</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D219" s="3" t="inlineStr"/>
       <c r="E219" s="3" t="inlineStr">
@@ -7297,7 +7297,7 @@
         <v>205</v>
       </c>
       <c r="D220" s="3" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>252</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D221" s="3" t="n">
         <v>277</v>
@@ -7359,7 +7359,7 @@
         <v>215</v>
       </c>
       <c r="D222" s="3" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         <v>255</v>
       </c>
       <c r="C223" s="4" t="n">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D223" s="3" t="inlineStr"/>
       <c r="E223" s="3" t="inlineStr">
@@ -7419,7 +7419,7 @@
         <v>248</v>
       </c>
       <c r="D224" s="3" t="n">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>258</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="D226" s="3" t="inlineStr"/>
       <c r="E226" s="3" t="inlineStr">
@@ -7536,7 +7536,7 @@
         <v>260</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D228" s="3" t="n">
         <v>291</v>
@@ -7567,7 +7567,7 @@
         <v>261</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D229" s="3" t="n">
         <v>292</v>
@@ -7632,7 +7632,7 @@
         <v>264</v>
       </c>
       <c r="D231" s="3" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>265</v>
       </c>
       <c r="C232" s="5" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D232" s="3" t="n">
         <v>290</v>
@@ -7694,7 +7694,7 @@
         <v>261</v>
       </c>
       <c r="D233" s="3" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>271</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         <v>268</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D235" s="3" t="inlineStr"/>
       <c r="E235" s="3" t="inlineStr">
@@ -7785,7 +7785,7 @@
         <v>226</v>
       </c>
       <c r="D236" s="3" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>271</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D238" s="3" t="inlineStr"/>
       <c r="E238" s="3" t="inlineStr">
@@ -7904,7 +7904,7 @@
         <v>273</v>
       </c>
       <c r="C240" s="4" t="n">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="D240" s="3" t="inlineStr"/>
       <c r="E240" s="3" t="inlineStr">
@@ -7998,7 +7998,7 @@
         <v>277</v>
       </c>
       <c r="D243" s="3" t="n">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>280</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D246" s="3" t="inlineStr"/>
       <c r="E246" s="3" t="inlineStr">
@@ -8117,7 +8117,7 @@
         <v>281</v>
       </c>
       <c r="C247" s="5" t="n">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
@@ -8149,7 +8149,7 @@
         <v>284</v>
       </c>
       <c r="D248" s="3" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>284</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D250" s="3" t="inlineStr"/>
       <c r="E250" s="3" t="inlineStr">
@@ -8240,7 +8240,7 @@
         <v>183</v>
       </c>
       <c r="D251" s="3" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>288</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D252" s="3" t="inlineStr"/>
       <c r="E252" s="3" t="inlineStr">
@@ -8297,7 +8297,7 @@
         <v>289</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D253" s="3" t="inlineStr"/>
       <c r="E253" s="3" t="inlineStr">
@@ -8357,7 +8357,7 @@
         <v>292</v>
       </c>
       <c r="C255" s="4" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D255" s="3" t="inlineStr"/>
       <c r="E255" s="3" t="inlineStr">
@@ -8389,7 +8389,7 @@
         <v>250</v>
       </c>
       <c r="D256" s="3" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>294</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="D257" s="3" t="inlineStr"/>
       <c r="E257" s="3" t="inlineStr">
@@ -8446,7 +8446,7 @@
         <v>296</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
@@ -8475,7 +8475,7 @@
         <v>297</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
@@ -8538,7 +8538,7 @@
         <v>245</v>
       </c>
       <c r="D261" s="3" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
@@ -8569,7 +8569,7 @@
         <v>265</v>
       </c>
       <c r="D262" s="3" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
@@ -8596,8 +8596,8 @@
       <c r="B263" s="3" t="n">
         <v>301</v>
       </c>
-      <c r="C263" s="4" t="n">
-        <v>366</v>
+      <c r="C263" s="5" t="n">
+        <v>311</v>
       </c>
       <c r="D263" s="3" t="inlineStr"/>
       <c r="E263" s="3" t="inlineStr">
@@ -8629,7 +8629,7 @@
         <v>262</v>
       </c>
       <c r="D264" s="3" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>305</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D266" s="3" t="inlineStr"/>
       <c r="E266" s="3" t="inlineStr">
@@ -8748,7 +8748,7 @@
         <v>309</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="D268" s="3" t="inlineStr"/>
       <c r="E268" s="3" t="inlineStr">
@@ -8777,7 +8777,7 @@
         <v>310</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D269" s="3" t="inlineStr"/>
       <c r="E269" s="3" t="inlineStr">
@@ -8806,7 +8806,7 @@
         <v>311</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
@@ -8835,7 +8835,7 @@
         <v>312</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr">
@@ -8864,7 +8864,7 @@
         <v>314</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
@@ -8896,7 +8896,7 @@
         <v>267</v>
       </c>
       <c r="D273" s="3" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>317</v>
       </c>
       <c r="C274" s="4" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D274" s="3" t="inlineStr"/>
       <c r="E274" s="3" t="inlineStr">
@@ -8944,73 +8944,73 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="6" t="inlineStr">
-        <is>
-          <t>RB98</t>
+      <c r="A275" s="8" t="inlineStr">
+        <is>
+          <t>TE39</t>
         </is>
       </c>
       <c r="B275" s="3" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>348</v>
-      </c>
-      <c r="D275" s="3" t="inlineStr"/>
+        <v>281</v>
+      </c>
+      <c r="D275" s="3" t="n">
+        <v>278</v>
+      </c>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>Audric Estime</t>
+          <t>Darnell Washington</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>PIT (9)</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="8" t="inlineStr">
-        <is>
-          <t>TE39</t>
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>WR112</t>
         </is>
       </c>
       <c r="B276" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="C276" s="5" t="n">
-        <v>281</v>
-      </c>
-      <c r="D276" s="3" t="n">
-        <v>278</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="C276" s="4" t="n">
+        <v>374</v>
+      </c>
+      <c r="D276" s="3" t="inlineStr"/>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>Darnell Washington</t>
+          <t>Cedric Tillman</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>PIT (9)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="inlineStr">
-        <is>
-          <t>WR112</t>
+      <c r="A277" s="11" t="inlineStr">
+        <is>
+          <t>QB36</t>
         </is>
       </c>
       <c r="B277" s="3" t="n">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C277" s="5" t="n">
         <v>368</v>
@@ -9018,72 +9018,72 @@
       <c r="D277" s="3" t="inlineStr"/>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>Cedric Tillman</t>
+          <t>J.J. McCarthy</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>MIN (6)</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="11" t="inlineStr">
-        <is>
-          <t>QB36</t>
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>WR114</t>
         </is>
       </c>
       <c r="B278" s="3" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C278" s="5" t="n">
-        <v>369</v>
-      </c>
-      <c r="D278" s="3" t="inlineStr"/>
+        <v>295</v>
+      </c>
+      <c r="D278" s="3" t="n">
+        <v>270</v>
+      </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Luke McCaffrey</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>WR114</t>
+          <t>WR115</t>
         </is>
       </c>
       <c r="B279" s="3" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>295</v>
-      </c>
-      <c r="D279" s="3" t="n">
-        <v>271</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="D279" s="3" t="inlineStr"/>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>Luke McCaffrey</t>
+          <t>Tez Johnson</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>TB (10)</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -9095,24 +9095,26 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>WR115</t>
+          <t>WR116</t>
         </is>
       </c>
       <c r="B280" s="3" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>374</v>
-      </c>
-      <c r="D280" s="3" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>222</v>
+      </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Tez Johnson</t>
+          <t>Jahan Dotson</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>TB (10)</t>
+          <t>ATL (11)</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -9124,26 +9126,24 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>WR116</t>
+          <t>WR117</t>
         </is>
       </c>
       <c r="B281" s="3" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C281" s="5" t="n">
-        <v>246</v>
-      </c>
-      <c r="D281" s="3" t="n">
-        <v>222</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="D281" s="3" t="inlineStr"/>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>Jalen Royals</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>ATL (11)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -9153,86 +9153,88 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>WR117</t>
+      <c r="A282" s="8" t="inlineStr">
+        <is>
+          <t>TE40</t>
         </is>
       </c>
       <c r="B282" s="3" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C282" s="5" t="n">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="D282" s="3" t="inlineStr"/>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>Jalen Royals</t>
+          <t>Max Klare</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>KC (5)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="8" t="inlineStr">
-        <is>
-          <t>TE40</t>
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>WR118</t>
         </is>
       </c>
       <c r="B283" s="3" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C283" s="5" t="n">
-        <v>375</v>
-      </c>
-      <c r="D283" s="3" t="inlineStr"/>
+        <v>203</v>
+      </c>
+      <c r="D283" s="3" t="n">
+        <v>210</v>
+      </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>Max Klare</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>WR118</t>
+          <t>WR119</t>
         </is>
       </c>
       <c r="B284" s="3" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>203</v>
+        <v>294</v>
       </c>
       <c r="D284" s="3" t="n">
-        <v>209</v>
+        <v>269</v>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Caleb Douglas</t>
+          <t>Calvin Austin</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>NYG (8)</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -9244,26 +9246,26 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>WR119</t>
+          <t>WR120</t>
         </is>
       </c>
       <c r="B285" s="3" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>294</v>
+        <v>358</v>
       </c>
       <c r="D285" s="3" t="n">
-        <v>270</v>
+        <v>298</v>
       </c>
       <c r="E285" s="3" t="inlineStr">
         <is>
-          <t>Calvin Austin</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>NYG (8)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -9275,26 +9277,24 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>WR120</t>
+          <t>WR122</t>
         </is>
       </c>
       <c r="B286" s="3" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>357</v>
-      </c>
-      <c r="D286" s="3" t="n">
-        <v>298</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="D286" s="3" t="inlineStr"/>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Joshua Palmer</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
@@ -9304,55 +9304,55 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="inlineStr">
-        <is>
-          <t>WR122</t>
+      <c r="A287" s="8" t="inlineStr">
+        <is>
+          <t>TE41</t>
         </is>
       </c>
       <c r="B287" s="3" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D287" s="3" t="inlineStr"/>
       <c r="E287" s="3" t="inlineStr">
         <is>
-          <t>Joshua Palmer</t>
+          <t>Michael Mayer</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="8" t="inlineStr">
         <is>
-          <t>TE41</t>
+          <t>TE42</t>
         </is>
       </c>
       <c r="B288" s="3" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Michael Mayer</t>
+          <t>Elijah Arroyo</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -9364,24 +9364,24 @@
     <row r="289">
       <c r="A289" s="8" t="inlineStr">
         <is>
-          <t>TE42</t>
+          <t>TE43</t>
         </is>
       </c>
       <c r="B289" s="3" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>335</v>
+        <v>308</v>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>Elijah Arroyo</t>
+          <t>Tyler Higbee</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -9391,171 +9391,171 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="8" t="inlineStr">
-        <is>
-          <t>TE43</t>
+      <c r="A290" s="11" t="inlineStr">
+        <is>
+          <t>QB37</t>
         </is>
       </c>
       <c r="B290" s="3" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>307</v>
+        <v>376</v>
       </c>
       <c r="D290" s="3" t="inlineStr"/>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Tyler Higbee</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="11" t="inlineStr">
-        <is>
-          <t>QB37</t>
+      <c r="A291" s="8" t="inlineStr">
+        <is>
+          <t>TE45</t>
         </is>
       </c>
       <c r="B291" s="3" t="n">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Dawson Knox</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="8" t="inlineStr">
-        <is>
-          <t>TE45</t>
+      <c r="A292" s="11" t="inlineStr">
+        <is>
+          <t>QB38</t>
         </is>
       </c>
       <c r="B292" s="3" t="n">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>376</v>
+        <v>343</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>Dawson Knox</t>
+          <t>Carson Beck</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>ARI (14)</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="11" t="inlineStr">
-        <is>
-          <t>QB38</t>
+      <c r="A293" s="8" t="inlineStr">
+        <is>
+          <t>TE47</t>
         </is>
       </c>
       <c r="B293" s="3" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>342</v>
+        <v>370</v>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr">
         <is>
-          <t>Carson Beck</t>
+          <t>Cole Kmet</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>ARI (14)</t>
+          <t>CHI (10)</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="8" t="inlineStr">
-        <is>
-          <t>TE47</t>
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>WR124</t>
         </is>
       </c>
       <c r="B294" s="3" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>Cole Kmet</t>
+          <t>Brenen Thompson</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>CHI (10)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>WR124</t>
+          <t>WR125</t>
         </is>
       </c>
       <c r="B295" s="3" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>340</v>
+        <v>307</v>
       </c>
       <c r="D295" s="3" t="inlineStr"/>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>Brenen Thompson</t>
+          <t>DeMario Douglas</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -9567,24 +9567,24 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>WR125</t>
+          <t>WR126</t>
         </is>
       </c>
       <c r="B296" s="3" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="D296" s="3" t="inlineStr"/>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>DeMario Douglas</t>
+          <t>Bryce Lance</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -9603,7 +9603,7 @@
         <v>358</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="D297" s="3" t="inlineStr"/>
       <c r="E297" s="3" t="inlineStr">
@@ -9661,7 +9661,7 @@
         <v>363</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D299" s="3" t="n">
         <v>293</v>
@@ -9721,7 +9721,7 @@
         <v>367</v>
       </c>
       <c r="C301" s="5" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D301" s="3" t="inlineStr"/>
       <c r="E301" s="3" t="inlineStr">
@@ -9779,7 +9779,7 @@
         <v>377</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D303" s="3" t="inlineStr"/>
       <c r="E303" s="3" t="inlineStr">
@@ -9808,7 +9808,7 @@
         <v>383</v>
       </c>
       <c r="C304" s="5" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D304" s="3" t="inlineStr"/>
       <c r="E304" s="3" t="inlineStr">
@@ -9837,7 +9837,7 @@
         <v>386</v>
       </c>
       <c r="C305" s="5" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D305" s="3" t="inlineStr"/>
       <c r="E305" s="3" t="inlineStr">
@@ -9884,35 +9884,6 @@
       <c r="G306" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="2" t="inlineStr">
-        <is>
-          <t>WR142</t>
-        </is>
-      </c>
-      <c r="B307" s="3" t="n">
-        <v>395</v>
-      </c>
-      <c r="C307" s="5" t="n">
-        <v>363</v>
-      </c>
-      <c r="D307" s="3" t="inlineStr"/>
-      <c r="E307" s="3" t="inlineStr">
-        <is>
-          <t>Jordan Whittington</t>
-        </is>
-      </c>
-      <c r="F307" s="3" t="inlineStr">
-        <is>
-          <t>LAR (11)</t>
-        </is>
-      </c>
-      <c r="G307" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -919,7 +919,7 @@
         <v>22</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>23</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>43</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>25</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>30</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>58</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>68</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>42</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>29</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>41</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>32</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>40</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>52</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>67</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>50</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>38</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>55</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>47</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>51</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>53</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         <v>48</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>69</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>49</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>59</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>66</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>45</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>71</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>56</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>44</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>57</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>74</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>76</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>86</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>64</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>60</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>73</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>103</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>65</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>87</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>61</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>77</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>72</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>85</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>70</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>99</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>108</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>94</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>101</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>122</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>123</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>63</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>100</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>88</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>129</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>46</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>124</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>130</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>80</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>117</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>115</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>119</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>84</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>83</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>92</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>120</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>128</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>106</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>97</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>105</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>91</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>110</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
@@ -4112,7 +4112,7 @@
         <v>127</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>116</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>102</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>98</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>93</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>107</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>78</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>109</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>75</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>132</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>121</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>82</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>149</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>180</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>150</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>131</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>148</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>118</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>134</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>136</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>181</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>104</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>164</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>199</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>159</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>158</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>135</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>200</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>177</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>211</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>174</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D168" s="3" t="inlineStr"/>
       <c r="E168" s="3" t="inlineStr">
@@ -5722,7 +5722,7 @@
         <v>184</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>182</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>263</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>162</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>165</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>161</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>178</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>242</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         <v>218</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>96</v>
       </c>
       <c r="D200" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>219</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>187</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>160</v>
       </c>
       <c r="D215" s="3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>212</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         <v>204</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>250</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D219" s="3" t="inlineStr"/>
       <c r="E219" s="3" t="inlineStr">
@@ -7297,7 +7297,7 @@
         <v>205</v>
       </c>
       <c r="D220" s="3" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
@@ -7325,7 +7325,7 @@
         <v>252</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D221" s="3" t="n">
         <v>277</v>
@@ -7419,7 +7419,7 @@
         <v>248</v>
       </c>
       <c r="D224" s="3" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>258</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D226" s="3" t="inlineStr"/>
       <c r="E226" s="3" t="inlineStr">
@@ -7536,7 +7536,7 @@
         <v>260</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D228" s="3" t="n">
         <v>291</v>
@@ -7567,7 +7567,7 @@
         <v>261</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D229" s="3" t="n">
         <v>292</v>
@@ -7844,7 +7844,7 @@
         <v>271</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D238" s="3" t="inlineStr"/>
       <c r="E238" s="3" t="inlineStr">
@@ -7904,7 +7904,7 @@
         <v>273</v>
       </c>
       <c r="C240" s="4" t="n">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="D240" s="3" t="inlineStr"/>
       <c r="E240" s="3" t="inlineStr">
@@ -8060,7 +8060,7 @@
         <v>186</v>
       </c>
       <c r="D245" s="3" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>280</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="D246" s="3" t="inlineStr"/>
       <c r="E246" s="3" t="inlineStr">
@@ -8208,7 +8208,7 @@
         <v>284</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D250" s="3" t="inlineStr"/>
       <c r="E250" s="3" t="inlineStr">
@@ -8268,7 +8268,7 @@
         <v>288</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D252" s="3" t="inlineStr"/>
       <c r="E252" s="3" t="inlineStr">
@@ -8329,7 +8329,7 @@
         <v>137</v>
       </c>
       <c r="D254" s="3" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>296</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
@@ -8597,7 +8597,7 @@
         <v>301</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D263" s="3" t="inlineStr"/>
       <c r="E263" s="3" t="inlineStr">
@@ -8688,7 +8688,7 @@
         <v>305</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D266" s="3" t="inlineStr"/>
       <c r="E266" s="3" t="inlineStr">
@@ -8748,7 +8748,7 @@
         <v>309</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D268" s="3" t="inlineStr"/>
       <c r="E268" s="3" t="inlineStr">
@@ -8806,7 +8806,7 @@
         <v>311</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
@@ -8864,7 +8864,7 @@
         <v>314</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
@@ -8923,8 +8923,8 @@
       <c r="B274" s="3" t="n">
         <v>317</v>
       </c>
-      <c r="C274" s="4" t="n">
-        <v>372</v>
+      <c r="C274" s="5" t="n">
+        <v>360</v>
       </c>
       <c r="D274" s="3" t="inlineStr"/>
       <c r="E274" s="3" t="inlineStr">
@@ -8983,8 +8983,8 @@
       <c r="B276" s="3" t="n">
         <v>324</v>
       </c>
-      <c r="C276" s="4" t="n">
-        <v>374</v>
+      <c r="C276" s="5" t="n">
+        <v>366</v>
       </c>
       <c r="D276" s="3" t="inlineStr"/>
       <c r="E276" s="3" t="inlineStr">
@@ -9073,7 +9073,7 @@
         <v>329</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D279" s="3" t="inlineStr"/>
       <c r="E279" s="3" t="inlineStr">
@@ -9133,7 +9133,7 @@
         <v>331</v>
       </c>
       <c r="C281" s="5" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D281" s="3" t="inlineStr"/>
       <c r="E281" s="3" t="inlineStr">
@@ -9162,7 +9162,7 @@
         <v>332</v>
       </c>
       <c r="C282" s="5" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D282" s="3" t="inlineStr"/>
       <c r="E282" s="3" t="inlineStr">
@@ -9194,7 +9194,7 @@
         <v>203</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>335</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D285" s="3" t="n">
         <v>298</v>
@@ -9371,7 +9371,7 @@
         <v>341</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr">
@@ -9400,7 +9400,7 @@
         <v>342</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D290" s="3" t="inlineStr"/>
       <c r="E290" s="3" t="inlineStr">
@@ -9429,7 +9429,7 @@
         <v>344</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
@@ -9458,7 +9458,7 @@
         <v>348</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
@@ -9516,7 +9516,7 @@
         <v>350</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
@@ -9632,7 +9632,7 @@
         <v>360</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D298" s="3" t="inlineStr"/>
       <c r="E298" s="3" t="inlineStr">
@@ -9661,7 +9661,7 @@
         <v>363</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D299" s="3" t="n">
         <v>293</v>
@@ -9692,7 +9692,7 @@
         <v>365</v>
       </c>
       <c r="C300" s="5" t="n">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D300" s="3" t="inlineStr"/>
       <c r="E300" s="3" t="inlineStr">
@@ -9721,7 +9721,7 @@
         <v>367</v>
       </c>
       <c r="C301" s="5" t="n">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D301" s="3" t="inlineStr"/>
       <c r="E301" s="3" t="inlineStr">
@@ -9750,7 +9750,7 @@
         <v>374</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D302" s="3" t="inlineStr"/>
       <c r="E302" s="3" t="inlineStr">
@@ -9779,7 +9779,7 @@
         <v>377</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D303" s="3" t="inlineStr"/>
       <c r="E303" s="3" t="inlineStr">
@@ -9808,7 +9808,7 @@
         <v>383</v>
       </c>
       <c r="C304" s="5" t="n">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D304" s="3" t="inlineStr"/>
       <c r="E304" s="3" t="inlineStr">
@@ -9837,7 +9837,7 @@
         <v>386</v>
       </c>
       <c r="C305" s="5" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D305" s="3" t="inlineStr"/>
       <c r="E305" s="3" t="inlineStr">

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -857,7 +857,7 @@
         <v>21</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>22</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>19</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>23</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>24</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>37</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>30</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>28</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>26</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>18</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>29</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>32</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>40</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>38</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>36</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>71</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>79</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>57</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>86</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>73</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>65</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>87</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>77</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>72</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>70</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>99</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>108</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>94</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>101</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>122</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>100</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>124</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>80</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>115</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>138</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>119</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>84</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>133</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>83</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>92</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>120</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>106</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>105</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>110</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>139</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>93</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>107</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>78</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>75</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>132</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>151</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>121</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>82</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>149</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>131</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
@@ -4794,7 +4794,7 @@
         <v>148</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>118</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>134</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>136</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>159</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>158</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>135</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>161</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>224</v>
       </c>
       <c r="C199" s="4" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D199" s="3" t="inlineStr"/>
       <c r="E199" s="3" t="inlineStr">
@@ -6681,7 +6681,7 @@
         <v>96</v>
       </c>
       <c r="D200" s="3" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>232</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D203" s="3" t="n">
         <v>299</v>
@@ -6802,7 +6802,7 @@
         <v>233</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D204" s="3" t="inlineStr"/>
       <c r="E204" s="3" t="inlineStr">
@@ -7144,7 +7144,7 @@
         <v>160</v>
       </c>
       <c r="D215" s="3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>246</v>
       </c>
       <c r="C216" s="4" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D216" s="3" t="n">
         <v>287</v>
@@ -7265,7 +7265,7 @@
         <v>250</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D219" s="3" t="inlineStr"/>
       <c r="E219" s="3" t="inlineStr">
@@ -7387,7 +7387,7 @@
         <v>255</v>
       </c>
       <c r="C223" s="4" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D223" s="3" t="inlineStr"/>
       <c r="E223" s="3" t="inlineStr">
@@ -7507,7 +7507,7 @@
         <v>259</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
@@ -7536,7 +7536,7 @@
         <v>260</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D228" s="3" t="n">
         <v>291</v>
@@ -7844,7 +7844,7 @@
         <v>271</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D238" s="3" t="inlineStr"/>
       <c r="E238" s="3" t="inlineStr">
@@ -7904,7 +7904,7 @@
         <v>273</v>
       </c>
       <c r="C240" s="4" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D240" s="3" t="inlineStr"/>
       <c r="E240" s="3" t="inlineStr">
@@ -8088,7 +8088,7 @@
         <v>280</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D246" s="3" t="inlineStr"/>
       <c r="E246" s="3" t="inlineStr">
@@ -8117,7 +8117,7 @@
         <v>281</v>
       </c>
       <c r="C247" s="5" t="n">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
@@ -8208,7 +8208,7 @@
         <v>284</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D250" s="3" t="inlineStr"/>
       <c r="E250" s="3" t="inlineStr">
@@ -8268,7 +8268,7 @@
         <v>288</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D252" s="3" t="inlineStr"/>
       <c r="E252" s="3" t="inlineStr">
@@ -8297,7 +8297,7 @@
         <v>289</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D253" s="3" t="inlineStr"/>
       <c r="E253" s="3" t="inlineStr">
@@ -8329,7 +8329,7 @@
         <v>137</v>
       </c>
       <c r="D254" s="3" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>292</v>
       </c>
       <c r="C255" s="4" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D255" s="3" t="inlineStr"/>
       <c r="E255" s="3" t="inlineStr">
@@ -8446,7 +8446,7 @@
         <v>296</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
@@ -8475,7 +8475,7 @@
         <v>297</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
@@ -8597,7 +8597,7 @@
         <v>301</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D263" s="3" t="inlineStr"/>
       <c r="E263" s="3" t="inlineStr">
@@ -8688,7 +8688,7 @@
         <v>305</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D266" s="3" t="inlineStr"/>
       <c r="E266" s="3" t="inlineStr">
@@ -8748,7 +8748,7 @@
         <v>309</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="D268" s="3" t="inlineStr"/>
       <c r="E268" s="3" t="inlineStr">
@@ -8777,7 +8777,7 @@
         <v>310</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D269" s="3" t="inlineStr"/>
       <c r="E269" s="3" t="inlineStr">
@@ -8806,7 +8806,7 @@
         <v>311</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
@@ -8864,7 +8864,7 @@
         <v>314</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
@@ -8924,7 +8924,7 @@
         <v>317</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>360</v>
+        <v>342</v>
       </c>
       <c r="D274" s="3" t="inlineStr"/>
       <c r="E274" s="3" t="inlineStr">
@@ -9133,7 +9133,7 @@
         <v>331</v>
       </c>
       <c r="C281" s="5" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D281" s="3" t="inlineStr"/>
       <c r="E281" s="3" t="inlineStr">
@@ -9253,7 +9253,7 @@
         <v>335</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D285" s="3" t="n">
         <v>298</v>
@@ -9284,7 +9284,7 @@
         <v>337</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D286" s="3" t="inlineStr"/>
       <c r="E286" s="3" t="inlineStr">
@@ -9313,7 +9313,7 @@
         <v>338</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D287" s="3" t="inlineStr"/>
       <c r="E287" s="3" t="inlineStr">
@@ -9458,7 +9458,7 @@
         <v>348</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
@@ -9516,7 +9516,7 @@
         <v>350</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
@@ -9632,7 +9632,7 @@
         <v>360</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D298" s="3" t="inlineStr"/>
       <c r="E298" s="3" t="inlineStr">
@@ -9661,7 +9661,7 @@
         <v>363</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D299" s="3" t="n">
         <v>293</v>
@@ -9721,7 +9721,7 @@
         <v>367</v>
       </c>
       <c r="C301" s="5" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D301" s="3" t="inlineStr"/>
       <c r="E301" s="3" t="inlineStr">
@@ -9750,7 +9750,7 @@
         <v>374</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D302" s="3" t="inlineStr"/>
       <c r="E302" s="3" t="inlineStr">
@@ -9808,7 +9808,7 @@
         <v>383</v>
       </c>
       <c r="C304" s="5" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D304" s="3" t="inlineStr"/>
       <c r="E304" s="3" t="inlineStr">
@@ -9837,7 +9837,7 @@
         <v>386</v>
       </c>
       <c r="C305" s="5" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D305" s="3" t="inlineStr"/>
       <c r="E305" s="3" t="inlineStr">

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -117,13 +117,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -544,7 +544,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>3</v>
@@ -575,7 +575,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>4</v>
@@ -764,7 +764,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>16</v>
@@ -826,7 +826,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D12" s="3" t="n">
         <v>21</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>20</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -884,8 +884,8 @@
       <c r="B13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>16</v>
+      <c r="C13" s="5" t="n">
+        <v>13</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>17</v>
@@ -916,10 +916,10 @@
         <v>13</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -946,11 +946,11 @@
       <c r="B15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C15" s="5" t="n">
-        <v>19</v>
+      <c r="C15" s="8" t="n">
+        <v>36</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>TE1</t>
         </is>
@@ -1040,7 +1040,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>11</v>
@@ -1133,7 +1133,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>14</v>
@@ -1155,7 +1155,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>TE2</t>
         </is>
@@ -1163,7 +1163,7 @@
       <c r="B22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="10" t="n">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="n">
@@ -1194,7 +1194,7 @@
       <c r="B23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="10" t="n">
+      <c r="C23" s="8" t="n">
         <v>43</v>
       </c>
       <c r="D23" s="3" t="n">
@@ -1225,11 +1225,11 @@
       <c r="B24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C24" s="10" t="n">
-        <v>37</v>
+      <c r="C24" s="8" t="n">
+        <v>40</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -1256,8 +1256,8 @@
       <c r="B25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C25" s="5" t="n">
-        <v>25</v>
+      <c r="C25" s="7" t="n">
+        <v>21</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>24</v>
@@ -1288,10 +1288,10 @@
         <v>25</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>26</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>12</v>
@@ -1349,11 +1349,11 @@
       <c r="B28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C28" s="5" t="n">
-        <v>28</v>
+      <c r="C28" s="4" t="n">
+        <v>31</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>40</v>
@@ -1412,7 +1412,7 @@
         <v>29</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>9</v>
@@ -1442,11 +1442,11 @@
       <c r="B31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C31" s="5" t="n">
-        <v>31</v>
+      <c r="C31" s="4" t="n">
+        <v>34</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -1473,11 +1473,11 @@
       <c r="B32" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="C32" s="4" t="n">
-        <v>35</v>
+      <c r="C32" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       <c r="B33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="C33" s="10" t="n">
+      <c r="C33" s="8" t="n">
         <v>58</v>
       </c>
       <c r="D33" s="3" t="n">
@@ -1535,7 +1535,7 @@
       <c r="B34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="C34" s="10" t="n">
+      <c r="C34" s="8" t="n">
         <v>68</v>
       </c>
       <c r="D34" s="3" t="n">
@@ -1651,7 +1651,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>TE3</t>
         </is>
@@ -1659,7 +1659,7 @@
       <c r="B38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="C38" s="9" t="n">
+      <c r="C38" s="10" t="n">
         <v>33</v>
       </c>
       <c r="D38" s="3" t="n">
@@ -1690,11 +1690,11 @@
       <c r="B39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="C39" s="5" t="n">
-        <v>29</v>
+      <c r="C39" s="10" t="n">
+        <v>28</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         <v>41</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1814,8 +1814,8 @@
       <c r="B43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="5" t="n">
-        <v>40</v>
+      <c r="C43" s="10" t="n">
+        <v>38</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>34</v>
@@ -1876,7 +1876,7 @@
       <c r="B45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="C45" s="10" t="n">
+      <c r="C45" s="8" t="n">
         <v>67</v>
       </c>
       <c r="D45" s="3" t="n">
@@ -1938,8 +1938,8 @@
       <c r="B47" s="3" t="n">
         <v>46</v>
       </c>
-      <c r="C47" s="4" t="n">
-        <v>50</v>
+      <c r="C47" s="5" t="n">
+        <v>49</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>51</v>
@@ -1970,7 +1970,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>33</v>
@@ -2001,7 +2001,7 @@
         <v>48</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>32</v>
@@ -2097,7 +2097,7 @@
         <v>51</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>TE4</t>
         </is>
@@ -2186,11 +2186,11 @@
       <c r="B55" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="C55" s="7" t="n">
-        <v>48</v>
+      <c r="C55" s="10" t="n">
+        <v>50</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
       <c r="B56" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="C56" s="10" t="n">
+      <c r="C56" s="8" t="n">
         <v>69</v>
       </c>
       <c r="D56" s="3" t="n">
@@ -2249,7 +2249,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>50</v>
@@ -2373,10 +2373,10 @@
         <v>60</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="9" t="n">
+      <c r="C62" s="10" t="n">
         <v>56</v>
       </c>
       <c r="D62" s="3" t="n">
@@ -2465,11 +2465,11 @@
       <c r="B64" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="C64" s="10" t="n">
-        <v>79</v>
+      <c r="C64" s="8" t="n">
+        <v>83</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -2496,11 +2496,11 @@
       <c r="B65" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="C65" s="7" t="n">
-        <v>57</v>
+      <c r="C65" s="5" t="n">
+        <v>61</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -2527,8 +2527,8 @@
       <c r="B66" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="C66" s="5" t="n">
-        <v>74</v>
+      <c r="C66" s="4" t="n">
+        <v>77</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>70</v>
@@ -2559,7 +2559,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>72</v>
@@ -2589,8 +2589,8 @@
       <c r="B68" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="C68" s="10" t="n">
-        <v>86</v>
+      <c r="C68" s="8" t="n">
+        <v>91</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>79</v>
@@ -2612,7 +2612,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+      <c r="A69" s="9" t="inlineStr">
         <is>
           <t>TE5</t>
         </is>
@@ -2620,8 +2620,8 @@
       <c r="B69" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="C69" s="9" t="n">
-        <v>64</v>
+      <c r="C69" s="10" t="n">
+        <v>63</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>69</v>
@@ -2651,11 +2651,11 @@
       <c r="B70" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="C70" s="7" t="n">
-        <v>62</v>
+      <c r="C70" s="10" t="n">
+        <v>65</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>60</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="8" t="inlineStr">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>TE6</t>
         </is>
@@ -2717,7 +2717,7 @@
         <v>73</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -2744,8 +2744,8 @@
       <c r="B73" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="C73" s="10" t="n">
-        <v>103</v>
+      <c r="C73" s="8" t="n">
+        <v>106</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>113</v>
@@ -2775,11 +2775,11 @@
       <c r="B74" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="C74" s="5" t="n">
-        <v>65</v>
+      <c r="C74" s="4" t="n">
+        <v>80</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -2806,11 +2806,11 @@
       <c r="B75" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="C75" s="10" t="n">
+      <c r="C75" s="8" t="n">
         <v>87</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>75</v>
       </c>
       <c r="C76" s="7" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D76" s="3" t="n">
         <v>57</v>
@@ -2868,8 +2868,8 @@
       <c r="B77" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C77" s="10" t="n">
-        <v>112</v>
+      <c r="C77" s="8" t="n">
+        <v>114</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>100</v>
@@ -2900,10 +2900,10 @@
         <v>77</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>TE7</t>
         </is>
@@ -2930,7 +2930,7 @@
       <c r="B79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C79" s="9" t="n">
+      <c r="C79" s="10" t="n">
         <v>72</v>
       </c>
       <c r="D79" s="3" t="n">
@@ -2962,7 +2962,7 @@
         <v>79</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D80" s="3" t="n">
         <v>71</v>
@@ -2992,8 +2992,8 @@
       <c r="B81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="C81" s="10" t="n">
-        <v>95</v>
+      <c r="C81" s="4" t="n">
+        <v>89</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>98</v>
@@ -3024,10 +3024,10 @@
         <v>81</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
@@ -3054,11 +3054,11 @@
       <c r="B83" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="C83" s="5" t="n">
-        <v>99</v>
+      <c r="C83" s="10" t="n">
+        <v>78</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -3085,8 +3085,8 @@
       <c r="B84" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="C84" s="10" t="n">
-        <v>108</v>
+      <c r="C84" s="8" t="n">
+        <v>104</v>
       </c>
       <c r="D84" s="3" t="n">
         <v>114</v>
@@ -3117,7 +3117,7 @@
         <v>84</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>81</v>
@@ -3148,10 +3148,10 @@
         <v>85</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -3178,11 +3178,11 @@
       <c r="B87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="C87" s="10" t="n">
-        <v>122</v>
+      <c r="C87" s="8" t="n">
+        <v>115</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -3209,11 +3209,11 @@
       <c r="B88" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="C88" s="10" t="n">
-        <v>123</v>
+      <c r="C88" s="5" t="n">
+        <v>88</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="8" t="inlineStr">
+      <c r="A89" s="9" t="inlineStr">
         <is>
           <t>TE8</t>
         </is>
@@ -3241,7 +3241,7 @@
         <v>88</v>
       </c>
       <c r="C89" s="7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>68</v>
@@ -3302,11 +3302,11 @@
       <c r="B91" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="C91" s="5" t="n">
-        <v>88</v>
+      <c r="C91" s="4" t="n">
+        <v>97</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -3333,11 +3333,11 @@
       <c r="B92" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="C92" s="10" t="n">
-        <v>129</v>
+      <c r="C92" s="8" t="n">
+        <v>130</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -3395,8 +3395,8 @@
       <c r="B94" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="C94" s="10" t="n">
-        <v>124</v>
+      <c r="C94" s="8" t="n">
+        <v>117</v>
       </c>
       <c r="D94" s="3" t="n">
         <v>147</v>
@@ -3426,8 +3426,8 @@
       <c r="B95" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="C95" s="10" t="n">
-        <v>130</v>
+      <c r="C95" s="8" t="n">
+        <v>123</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>103</v>
@@ -3458,10 +3458,10 @@
         <v>95</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
@@ -3489,10 +3489,10 @@
         <v>96</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="8" t="inlineStr">
+      <c r="A98" s="9" t="inlineStr">
         <is>
           <t>TE9</t>
         </is>
@@ -3520,10 +3520,10 @@
         <v>97</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         <v>98</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
@@ -3581,11 +3581,11 @@
       <c r="B100" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="C100" s="10" t="n">
-        <v>138</v>
+      <c r="C100" s="8" t="n">
+        <v>142</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>101</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>99</v>
@@ -3644,7 +3644,7 @@
         <v>102</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>132</v>
@@ -3674,8 +3674,8 @@
       <c r="B103" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="C103" s="5" t="n">
-        <v>114</v>
+      <c r="C103" s="8" t="n">
+        <v>122</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>102</v>
@@ -3709,7 +3709,7 @@
         <v>84</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="8" t="inlineStr">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>TE10</t>
         </is>
@@ -3737,10 +3737,10 @@
         <v>105</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
@@ -3768,10 +3768,10 @@
         <v>106</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>92</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
         <v>108</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>133</v>
@@ -3860,11 +3860,11 @@
       <c r="B109" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="C109" s="10" t="n">
-        <v>128</v>
+      <c r="C109" s="8" t="n">
+        <v>129</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
@@ -3891,11 +3891,11 @@
       <c r="B110" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="C110" s="9" t="n">
-        <v>106</v>
+      <c r="C110" s="5" t="n">
+        <v>110</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="8" t="inlineStr">
+      <c r="A111" s="9" t="inlineStr">
         <is>
           <t>TE11</t>
         </is>
@@ -3923,7 +3923,7 @@
         <v>111</v>
       </c>
       <c r="C111" s="7" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>105</v>
@@ -3954,10 +3954,10 @@
         <v>112</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
@@ -3984,8 +3984,8 @@
       <c r="B113" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="C113" s="9" t="n">
-        <v>105</v>
+      <c r="C113" s="10" t="n">
+        <v>108</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>115</v>
@@ -4016,7 +4016,7 @@
         <v>114</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>101</v>
@@ -4038,7 +4038,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="inlineStr">
+      <c r="A115" s="9" t="inlineStr">
         <is>
           <t>TE12</t>
         </is>
@@ -4047,7 +4047,7 @@
         <v>115</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>104</v>
@@ -4078,10 +4078,10 @@
         <v>116</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
@@ -4109,10 +4109,10 @@
         <v>117</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
@@ -4139,12 +4139,12 @@
       <c r="B118" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="C118" s="10" t="n">
+      <c r="C118" s="8" t="n">
+        <v>141</v>
+      </c>
+      <c r="D118" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="D118" s="3" t="n">
-        <v>140</v>
-      </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
           <t>Baker Mayfield</t>
@@ -4162,7 +4162,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="8" t="inlineStr">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>TE13</t>
         </is>
@@ -4171,7 +4171,7 @@
         <v>119</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D119" s="3" t="n">
         <v>107</v>
@@ -4202,7 +4202,7 @@
         <v>121</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>111</v>
@@ -4232,11 +4232,11 @@
       <c r="B121" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="C121" s="10" t="n">
-        <v>206</v>
+      <c r="C121" s="8" t="n">
+        <v>207</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="8" t="inlineStr">
+      <c r="A122" s="9" t="inlineStr">
         <is>
           <t>TE14</t>
         </is>
@@ -4264,7 +4264,7 @@
         <v>123</v>
       </c>
       <c r="C122" s="7" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>106</v>
@@ -4295,7 +4295,7 @@
         <v>124</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>82</v>
@@ -4326,7 +4326,7 @@
         <v>125</v>
       </c>
       <c r="C124" s="7" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>116</v>
@@ -4357,7 +4357,7 @@
         <v>126</v>
       </c>
       <c r="C125" s="7" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>83</v>
@@ -4388,7 +4388,7 @@
         <v>127</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D126" s="3" t="n">
         <v>112</v>
@@ -4419,10 +4419,10 @@
         <v>128</v>
       </c>
       <c r="C127" s="7" t="n">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
@@ -4449,11 +4449,11 @@
       <c r="B128" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="C128" s="10" t="n">
-        <v>229</v>
+      <c r="C128" s="8" t="n">
+        <v>227</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="8" t="inlineStr">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>TE15</t>
         </is>
@@ -4481,7 +4481,7 @@
         <v>130</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D129" s="3" t="n">
         <v>131</v>
@@ -4511,8 +4511,8 @@
       <c r="B130" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="C130" s="10" t="n">
-        <v>151</v>
+      <c r="C130" s="8" t="n">
+        <v>154</v>
       </c>
       <c r="D130" s="3" t="n">
         <v>141</v>
@@ -4543,10 +4543,10 @@
         <v>132</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
@@ -4574,10 +4574,10 @@
         <v>133</v>
       </c>
       <c r="C132" s="7" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
@@ -4604,11 +4604,11 @@
       <c r="B133" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="C133" s="10" t="n">
-        <v>208</v>
+      <c r="C133" s="8" t="n">
+        <v>209</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
@@ -4635,11 +4635,11 @@
       <c r="B134" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="C134" s="5" t="n">
-        <v>149</v>
+      <c r="C134" s="10" t="n">
+        <v>131</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
@@ -4666,8 +4666,8 @@
       <c r="B135" s="3" t="n">
         <v>136</v>
       </c>
-      <c r="C135" s="5" t="n">
-        <v>180</v>
+      <c r="C135" s="8" t="n">
+        <v>250</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>161</v>
@@ -4698,10 +4698,10 @@
         <v>137</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
@@ -4728,11 +4728,11 @@
       <c r="B137" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="C137" s="10" t="n">
-        <v>207</v>
+      <c r="C137" s="8" t="n">
+        <v>208</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
@@ -4759,11 +4759,11 @@
       <c r="B138" s="3" t="n">
         <v>139</v>
       </c>
-      <c r="C138" s="9" t="n">
-        <v>131</v>
+      <c r="C138" s="7" t="n">
+        <v>112</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>140</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D139" s="3" t="n">
         <v>143</v>
@@ -4813,7 +4813,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="8" t="inlineStr">
+      <c r="A140" s="9" t="inlineStr">
         <is>
           <t>TE16</t>
         </is>
@@ -4822,7 +4822,7 @@
         <v>141</v>
       </c>
       <c r="C140" s="7" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D140" s="3" t="n">
         <v>142</v>
@@ -4853,10 +4853,10 @@
         <v>142</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
@@ -4883,11 +4883,11 @@
       <c r="B142" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="C142" s="10" t="n">
-        <v>228</v>
+      <c r="C142" s="8" t="n">
+        <v>225</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
@@ -4914,11 +4914,11 @@
       <c r="B143" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="C143" s="10" t="n">
-        <v>225</v>
+      <c r="C143" s="5" t="n">
+        <v>184</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
       <c r="B144" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="C144" s="10" t="n">
+      <c r="C144" s="8" t="n">
         <v>243</v>
       </c>
       <c r="D144" s="3" t="n">
@@ -4980,7 +4980,7 @@
         <v>134</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="8" t="inlineStr">
+      <c r="A146" s="9" t="inlineStr">
         <is>
           <t>TE17</t>
         </is>
@@ -5008,10 +5008,10 @@
         <v>147</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
@@ -5038,11 +5038,11 @@
       <c r="B147" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="C147" s="10" t="n">
-        <v>266</v>
+      <c r="C147" s="8" t="n">
+        <v>178</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>219</v>
+        <v>184</v>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
         <v>149</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
@@ -5101,10 +5101,10 @@
         <v>150</v>
       </c>
       <c r="C149" s="4" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
@@ -5132,10 +5132,10 @@
         <v>151</v>
       </c>
       <c r="C150" s="4" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         <v>152</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
@@ -5194,10 +5194,10 @@
         <v>153</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="8" t="inlineStr">
+      <c r="A153" s="9" t="inlineStr">
         <is>
           <t>TE18</t>
         </is>
@@ -5225,10 +5225,10 @@
         <v>154</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="8" t="inlineStr">
+      <c r="A154" s="9" t="inlineStr">
         <is>
           <t>TE19</t>
         </is>
@@ -5255,11 +5255,11 @@
       <c r="B154" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="C154" s="5" t="n">
-        <v>213</v>
+      <c r="C154" s="4" t="n">
+        <v>235</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="8" t="inlineStr">
+      <c r="A155" s="9" t="inlineStr">
         <is>
           <t>TE20</t>
         </is>
@@ -5287,10 +5287,10 @@
         <v>156</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
@@ -5318,10 +5318,10 @@
         <v>158</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>159</v>
       </c>
       <c r="C157" s="7" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D157" s="3" t="n">
         <v>108</v>
@@ -5380,10 +5380,10 @@
         <v>160</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
@@ -5411,10 +5411,10 @@
         <v>161</v>
       </c>
       <c r="C159" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="D159" s="3" t="n">
         <v>164</v>
-      </c>
-      <c r="D159" s="3" t="n">
-        <v>162</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
@@ -5441,11 +5441,11 @@
       <c r="B160" s="3" t="n">
         <v>162</v>
       </c>
-      <c r="C160" s="4" t="n">
-        <v>247</v>
+      <c r="C160" s="5" t="n">
+        <v>152</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>217</v>
+        <v>149</v>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
@@ -5473,10 +5473,10 @@
         <v>164</v>
       </c>
       <c r="C161" s="4" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         <v>165</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
@@ -5526,7 +5526,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="8" t="inlineStr">
+      <c r="A163" s="9" t="inlineStr">
         <is>
           <t>TE21</t>
         </is>
@@ -5535,10 +5535,10 @@
         <v>166</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
@@ -5565,11 +5565,11 @@
       <c r="B164" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="C164" s="9" t="n">
-        <v>135</v>
+      <c r="C164" s="10" t="n">
+        <v>136</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
         <v>169</v>
       </c>
       <c r="C165" s="4" t="n">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
@@ -5628,10 +5628,10 @@
         <v>170</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="8" t="inlineStr">
+      <c r="A167" s="9" t="inlineStr">
         <is>
           <t>TE22</t>
         </is>
@@ -5659,10 +5659,10 @@
         <v>173</v>
       </c>
       <c r="C167" s="4" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>174</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D168" s="3" t="inlineStr"/>
       <c r="E168" s="3" t="inlineStr">
@@ -5719,10 +5719,10 @@
         <v>175</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>215</v>
+        <v>165</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
@@ -5750,10 +5750,10 @@
         <v>176</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
@@ -5781,10 +5781,10 @@
         <v>177</v>
       </c>
       <c r="C171" s="7" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
@@ -5812,10 +5812,10 @@
         <v>178</v>
       </c>
       <c r="C172" s="4" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -5873,11 +5873,11 @@
       <c r="B174" s="3" t="n">
         <v>185</v>
       </c>
-      <c r="C174" s="5" t="n">
-        <v>182</v>
+      <c r="C174" s="4" t="n">
+        <v>222</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         <v>186</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D175" s="3" t="n">
         <v>283</v>
@@ -5936,10 +5936,10 @@
         <v>187</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>269</v>
+        <v>220</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
@@ -5967,10 +5967,10 @@
         <v>188</v>
       </c>
       <c r="C177" s="4" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="8" t="inlineStr">
+      <c r="A178" s="9" t="inlineStr">
         <is>
           <t>TE23</t>
         </is>
@@ -5997,11 +5997,11 @@
       <c r="B178" s="3" t="n">
         <v>191</v>
       </c>
-      <c r="C178" s="4" t="n">
-        <v>263</v>
+      <c r="C178" s="5" t="n">
+        <v>212</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
@@ -6029,10 +6029,10 @@
         <v>192</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
@@ -6060,10 +6060,10 @@
         <v>194</v>
       </c>
       <c r="C180" s="4" t="n">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
@@ -6090,11 +6090,11 @@
       <c r="B181" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="C181" s="9" t="n">
+      <c r="C181" s="10" t="n">
         <v>162</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="8" t="inlineStr">
+      <c r="A182" s="9" t="inlineStr">
         <is>
           <t>TE24</t>
         </is>
@@ -6122,10 +6122,10 @@
         <v>196</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
@@ -6153,10 +6153,10 @@
         <v>197</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>299</v>
+        <v>261</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
@@ -6183,11 +6183,11 @@
       <c r="B184" s="3" t="n">
         <v>199</v>
       </c>
-      <c r="C184" s="9" t="n">
-        <v>165</v>
+      <c r="C184" s="5" t="n">
+        <v>186</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>165</v>
+        <v>213</v>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>201</v>
       </c>
       <c r="C185" s="5" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D185" s="3" t="n">
         <v>183</v>
@@ -6246,10 +6246,10 @@
         <v>202</v>
       </c>
       <c r="C186" s="4" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
@@ -6276,11 +6276,11 @@
       <c r="B187" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="C187" s="9" t="n">
-        <v>161</v>
+      <c r="C187" s="10" t="n">
+        <v>109</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
@@ -6308,10 +6308,10 @@
         <v>205</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>221</v>
+        <v>185</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
@@ -6339,10 +6339,10 @@
         <v>206</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D189" s="3" t="n">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
@@ -6361,7 +6361,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="8" t="inlineStr">
+      <c r="A190" s="9" t="inlineStr">
         <is>
           <t>TE25</t>
         </is>
@@ -6369,11 +6369,11 @@
       <c r="B190" s="3" t="n">
         <v>207</v>
       </c>
-      <c r="C190" s="5" t="n">
-        <v>236</v>
+      <c r="C190" s="4" t="n">
+        <v>264</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
@@ -6400,11 +6400,11 @@
       <c r="B191" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="C191" s="9" t="n">
-        <v>178</v>
+      <c r="C191" s="10" t="n">
+        <v>168</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
@@ -6432,10 +6432,10 @@
         <v>212</v>
       </c>
       <c r="C192" s="5" t="n">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
@@ -6462,11 +6462,11 @@
       <c r="B193" s="3" t="n">
         <v>213</v>
       </c>
-      <c r="C193" s="4" t="n">
-        <v>292</v>
+      <c r="C193" s="5" t="n">
+        <v>211</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
@@ -6493,11 +6493,11 @@
       <c r="B194" s="3" t="n">
         <v>217</v>
       </c>
-      <c r="C194" s="5" t="n">
-        <v>223</v>
+      <c r="C194" s="4" t="n">
+        <v>286</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>242</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>287</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
@@ -6586,11 +6586,11 @@
       <c r="B197" s="3" t="n">
         <v>222</v>
       </c>
-      <c r="C197" s="4" t="n">
-        <v>272</v>
+      <c r="C197" s="5" t="n">
+        <v>248</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
@@ -6618,10 +6618,10 @@
         <v>223</v>
       </c>
       <c r="C198" s="5" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>224</v>
       </c>
       <c r="C199" s="4" t="n">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="D199" s="3" t="inlineStr"/>
       <c r="E199" s="3" t="inlineStr">
@@ -6681,7 +6681,7 @@
         <v>96</v>
       </c>
       <c r="D200" s="3" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
@@ -6709,10 +6709,10 @@
         <v>228</v>
       </c>
       <c r="C201" s="5" t="n">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
@@ -6740,10 +6740,10 @@
         <v>230</v>
       </c>
       <c r="C202" s="5" t="n">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>232</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="D203" s="3" t="n">
         <v>299</v>
@@ -6802,7 +6802,7 @@
         <v>233</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="D204" s="3" t="inlineStr"/>
       <c r="E204" s="3" t="inlineStr">
@@ -6831,10 +6831,10 @@
         <v>234</v>
       </c>
       <c r="C205" s="5" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="8" t="inlineStr">
+      <c r="A206" s="9" t="inlineStr">
         <is>
           <t>TE26</t>
         </is>
@@ -6862,10 +6862,10 @@
         <v>235</v>
       </c>
       <c r="C206" s="5" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>283</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="8" t="inlineStr">
+      <c r="A208" s="9" t="inlineStr">
         <is>
           <t>TE27</t>
         </is>
@@ -6924,10 +6924,10 @@
         <v>238</v>
       </c>
       <c r="C208" s="5" t="n">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="8" t="inlineStr">
+      <c r="A209" s="9" t="inlineStr">
         <is>
           <t>TE28</t>
         </is>
@@ -6955,10 +6955,10 @@
         <v>239</v>
       </c>
       <c r="C209" s="4" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
@@ -6985,11 +6985,11 @@
       <c r="B210" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="C210" s="5" t="n">
-        <v>249</v>
+      <c r="C210" s="10" t="n">
+        <v>163</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
@@ -7017,10 +7017,10 @@
         <v>241</v>
       </c>
       <c r="C211" s="4" t="n">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
@@ -7048,10 +7048,10 @@
         <v>242</v>
       </c>
       <c r="C212" s="4" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="8" t="inlineStr">
+      <c r="A213" s="9" t="inlineStr">
         <is>
           <t>TE29</t>
         </is>
@@ -7078,11 +7078,11 @@
       <c r="B213" s="3" t="n">
         <v>243</v>
       </c>
-      <c r="C213" s="9" t="n">
-        <v>187</v>
+      <c r="C213" s="10" t="n">
+        <v>165</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
@@ -7110,10 +7110,10 @@
         <v>244</v>
       </c>
       <c r="C214" s="4" t="n">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
@@ -7140,11 +7140,11 @@
       <c r="B215" s="3" t="n">
         <v>245</v>
       </c>
-      <c r="C215" s="9" t="n">
-        <v>160</v>
+      <c r="C215" s="5" t="n">
+        <v>228</v>
       </c>
       <c r="D215" s="3" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
@@ -7172,10 +7172,10 @@
         <v>246</v>
       </c>
       <c r="C216" s="4" t="n">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="D216" s="3" t="n">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="8" t="inlineStr">
+      <c r="A217" s="9" t="inlineStr">
         <is>
           <t>TE30</t>
         </is>
@@ -7203,10 +7203,10 @@
         <v>248</v>
       </c>
       <c r="C217" s="5" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
@@ -7234,10 +7234,10 @@
         <v>249</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>250</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D219" s="3" t="inlineStr"/>
       <c r="E219" s="3" t="inlineStr">
@@ -7294,10 +7294,10 @@
         <v>251</v>
       </c>
       <c r="C220" s="5" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D220" s="3" t="n">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>274</v>
       </c>
       <c r="D221" s="3" t="n">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
@@ -7347,7 +7347,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="8" t="inlineStr">
+      <c r="A222" s="9" t="inlineStr">
         <is>
           <t>TE31</t>
         </is>
@@ -7356,7 +7356,7 @@
         <v>254</v>
       </c>
       <c r="C222" s="5" t="n">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="D222" s="3" t="n">
         <v>250</v>
@@ -7387,7 +7387,7 @@
         <v>255</v>
       </c>
       <c r="C223" s="4" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D223" s="3" t="inlineStr"/>
       <c r="E223" s="3" t="inlineStr">
@@ -7415,11 +7415,11 @@
       <c r="B224" s="3" t="n">
         <v>256</v>
       </c>
-      <c r="C224" s="5" t="n">
-        <v>248</v>
+      <c r="C224" s="10" t="n">
+        <v>185</v>
       </c>
       <c r="D224" s="3" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
@@ -7447,10 +7447,10 @@
         <v>257</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="D225" s="3" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>258</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D226" s="3" t="inlineStr"/>
       <c r="E226" s="3" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="8" t="inlineStr">
+      <c r="A227" s="9" t="inlineStr">
         <is>
           <t>TE32</t>
         </is>
@@ -7507,7 +7507,7 @@
         <v>259</v>
       </c>
       <c r="C227" s="5" t="n">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
@@ -7536,10 +7536,10 @@
         <v>260</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="D228" s="3" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
@@ -7567,10 +7567,10 @@
         <v>261</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="D229" s="3" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
@@ -7598,10 +7598,10 @@
         <v>262</v>
       </c>
       <c r="C230" s="5" t="n">
-        <v>202</v>
+        <v>249</v>
       </c>
       <c r="D230" s="3" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="8" t="inlineStr">
+      <c r="A231" s="9" t="inlineStr">
         <is>
           <t>TE33</t>
         </is>
@@ -7629,10 +7629,10 @@
         <v>264</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D231" s="3" t="n">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>265</v>
       </c>
       <c r="C232" s="5" t="n">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="D232" s="3" t="n">
         <v>290</v>
@@ -7722,10 +7722,10 @@
         <v>267</v>
       </c>
       <c r="C234" s="5" t="n">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="8" t="inlineStr">
+      <c r="A235" s="9" t="inlineStr">
         <is>
           <t>TE34</t>
         </is>
@@ -7753,7 +7753,7 @@
         <v>268</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="D235" s="3" t="inlineStr"/>
       <c r="E235" s="3" t="inlineStr">
@@ -7781,11 +7781,11 @@
       <c r="B236" s="3" t="n">
         <v>269</v>
       </c>
-      <c r="C236" s="5" t="n">
-        <v>226</v>
+      <c r="C236" s="10" t="n">
+        <v>199</v>
       </c>
       <c r="D236" s="3" t="n">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
@@ -7813,10 +7813,10 @@
         <v>270</v>
       </c>
       <c r="C237" s="5" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D237" s="3" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>271</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D238" s="3" t="inlineStr"/>
       <c r="E238" s="3" t="inlineStr">
@@ -7873,7 +7873,7 @@
         <v>272</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D239" s="3" t="n">
         <v>284</v>
@@ -7904,7 +7904,7 @@
         <v>273</v>
       </c>
       <c r="C240" s="4" t="n">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="D240" s="3" t="inlineStr"/>
       <c r="E240" s="3" t="inlineStr">
@@ -7933,7 +7933,7 @@
         <v>274</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="D241" s="3" t="n">
         <v>300</v>
@@ -7964,10 +7964,10 @@
         <v>275</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>301</v>
+        <v>272</v>
       </c>
       <c r="D242" s="3" t="n">
-        <v>280</v>
+        <v>241</v>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
@@ -8026,10 +8026,10 @@
         <v>277</v>
       </c>
       <c r="C244" s="5" t="n">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="D244" s="3" t="n">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="8" t="inlineStr">
+      <c r="A245" s="9" t="inlineStr">
         <is>
           <t>TE35</t>
         </is>
@@ -8056,11 +8056,11 @@
       <c r="B245" s="3" t="n">
         <v>278</v>
       </c>
-      <c r="C245" s="9" t="n">
-        <v>186</v>
+      <c r="C245" s="10" t="n">
+        <v>188</v>
       </c>
       <c r="D245" s="3" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
@@ -8087,8 +8087,8 @@
       <c r="B246" s="3" t="n">
         <v>280</v>
       </c>
-      <c r="C246" s="4" t="n">
-        <v>332</v>
+      <c r="C246" s="5" t="n">
+        <v>313</v>
       </c>
       <c r="D246" s="3" t="inlineStr"/>
       <c r="E246" s="3" t="inlineStr">
@@ -8116,8 +8116,8 @@
       <c r="B247" s="3" t="n">
         <v>281</v>
       </c>
-      <c r="C247" s="5" t="n">
-        <v>291</v>
+      <c r="C247" s="4" t="n">
+        <v>324</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
@@ -8146,10 +8146,10 @@
         <v>282</v>
       </c>
       <c r="C248" s="5" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D248" s="3" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
@@ -8177,10 +8177,10 @@
         <v>283</v>
       </c>
       <c r="C249" s="5" t="n">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="D249" s="3" t="n">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>284</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D250" s="3" t="inlineStr"/>
       <c r="E250" s="3" t="inlineStr">
@@ -8236,8 +8236,8 @@
       <c r="B251" s="3" t="n">
         <v>285</v>
       </c>
-      <c r="C251" s="9" t="n">
-        <v>183</v>
+      <c r="C251" s="5" t="n">
+        <v>205</v>
       </c>
       <c r="D251" s="3" t="n">
         <v>220</v>
@@ -8268,7 +8268,7 @@
         <v>288</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D252" s="3" t="inlineStr"/>
       <c r="E252" s="3" t="inlineStr">
@@ -8297,7 +8297,7 @@
         <v>289</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D253" s="3" t="inlineStr"/>
       <c r="E253" s="3" t="inlineStr">
@@ -8356,8 +8356,8 @@
       <c r="B255" s="3" t="n">
         <v>292</v>
       </c>
-      <c r="C255" s="4" t="n">
-        <v>341</v>
+      <c r="C255" s="5" t="n">
+        <v>299</v>
       </c>
       <c r="D255" s="3" t="inlineStr"/>
       <c r="E255" s="3" t="inlineStr">
@@ -8386,10 +8386,10 @@
         <v>293</v>
       </c>
       <c r="C256" s="5" t="n">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="D256" s="3" t="n">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>294</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D257" s="3" t="inlineStr"/>
       <c r="E257" s="3" t="inlineStr">
@@ -8446,7 +8446,7 @@
         <v>296</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>317</v>
+        <v>269</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="8" t="inlineStr">
+      <c r="A259" s="9" t="inlineStr">
         <is>
           <t>TE36</t>
         </is>
@@ -8504,10 +8504,10 @@
         <v>298</v>
       </c>
       <c r="C260" s="5" t="n">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="D260" s="3" t="n">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
@@ -8557,7 +8557,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="8" t="inlineStr">
+      <c r="A262" s="9" t="inlineStr">
         <is>
           <t>TE37</t>
         </is>
@@ -8597,7 +8597,7 @@
         <v>301</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D263" s="3" t="inlineStr"/>
       <c r="E263" s="3" t="inlineStr">
@@ -8657,10 +8657,10 @@
         <v>304</v>
       </c>
       <c r="C265" s="5" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D265" s="3" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>305</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="D266" s="3" t="inlineStr"/>
       <c r="E266" s="3" t="inlineStr">
@@ -8716,11 +8716,11 @@
       <c r="B267" s="3" t="n">
         <v>306</v>
       </c>
-      <c r="C267" s="9" t="n">
-        <v>175</v>
+      <c r="C267" s="7" t="n">
+        <v>151</v>
       </c>
       <c r="D267" s="3" t="n">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         <v>309</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="D268" s="3" t="inlineStr"/>
       <c r="E268" s="3" t="inlineStr">
@@ -8777,7 +8777,7 @@
         <v>310</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="D269" s="3" t="inlineStr"/>
       <c r="E269" s="3" t="inlineStr">
@@ -8806,7 +8806,7 @@
         <v>311</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="8" t="inlineStr">
+      <c r="A271" s="9" t="inlineStr">
         <is>
           <t>TE38</t>
         </is>
@@ -8835,7 +8835,7 @@
         <v>312</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr">
@@ -8893,10 +8893,10 @@
         <v>316</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D273" s="3" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>317</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>342</v>
+        <v>291</v>
       </c>
       <c r="D274" s="3" t="inlineStr"/>
       <c r="E274" s="3" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="8" t="inlineStr">
+      <c r="A275" s="9" t="inlineStr">
         <is>
           <t>TE39</t>
         </is>
@@ -8953,7 +8953,7 @@
         <v>322</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D275" s="3" t="n">
         <v>278</v>
@@ -8984,7 +8984,7 @@
         <v>324</v>
       </c>
       <c r="C276" s="5" t="n">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D276" s="3" t="inlineStr"/>
       <c r="E276" s="3" t="inlineStr">
@@ -9013,7 +9013,7 @@
         <v>327</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D277" s="3" t="inlineStr"/>
       <c r="E277" s="3" t="inlineStr">
@@ -9042,10 +9042,10 @@
         <v>328</v>
       </c>
       <c r="C278" s="5" t="n">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="D278" s="3" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>329</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D279" s="3" t="inlineStr"/>
       <c r="E279" s="3" t="inlineStr">
@@ -9102,10 +9102,10 @@
         <v>330</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="D280" s="3" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>331</v>
       </c>
       <c r="C281" s="5" t="n">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="D281" s="3" t="inlineStr"/>
       <c r="E281" s="3" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="8" t="inlineStr">
+      <c r="A282" s="9" t="inlineStr">
         <is>
           <t>TE40</t>
         </is>
@@ -9191,10 +9191,10 @@
         <v>333</v>
       </c>
       <c r="C283" s="5" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D283" s="3" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
         <v>334</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D284" s="3" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>335</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D285" s="3" t="n">
         <v>298</v>
@@ -9284,7 +9284,7 @@
         <v>337</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D286" s="3" t="inlineStr"/>
       <c r="E286" s="3" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="8" t="inlineStr">
+      <c r="A287" s="9" t="inlineStr">
         <is>
           <t>TE41</t>
         </is>
@@ -9313,7 +9313,7 @@
         <v>338</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D287" s="3" t="inlineStr"/>
       <c r="E287" s="3" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="8" t="inlineStr">
+      <c r="A288" s="9" t="inlineStr">
         <is>
           <t>TE42</t>
         </is>
@@ -9342,7 +9342,7 @@
         <v>340</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="8" t="inlineStr">
+      <c r="A289" s="9" t="inlineStr">
         <is>
           <t>TE43</t>
         </is>
@@ -9371,7 +9371,7 @@
         <v>341</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr">
@@ -9400,7 +9400,7 @@
         <v>342</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D290" s="3" t="inlineStr"/>
       <c r="E290" s="3" t="inlineStr">
@@ -9420,7 +9420,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="8" t="inlineStr">
+      <c r="A291" s="9" t="inlineStr">
         <is>
           <t>TE45</t>
         </is>
@@ -9429,7 +9429,7 @@
         <v>344</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
@@ -9458,7 +9458,7 @@
         <v>348</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="8" t="inlineStr">
+      <c r="A293" s="9" t="inlineStr">
         <is>
           <t>TE47</t>
         </is>
@@ -9487,7 +9487,7 @@
         <v>349</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr">
@@ -9516,7 +9516,7 @@
         <v>350</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
@@ -9545,7 +9545,7 @@
         <v>351</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D295" s="3" t="inlineStr"/>
       <c r="E295" s="3" t="inlineStr">
@@ -9574,7 +9574,7 @@
         <v>355</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="D296" s="3" t="inlineStr"/>
       <c r="E296" s="3" t="inlineStr">
@@ -9603,7 +9603,7 @@
         <v>358</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="D297" s="3" t="inlineStr"/>
       <c r="E297" s="3" t="inlineStr">
@@ -9632,7 +9632,7 @@
         <v>360</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D298" s="3" t="inlineStr"/>
       <c r="E298" s="3" t="inlineStr">
@@ -9661,10 +9661,10 @@
         <v>363</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>320</v>
+        <v>266</v>
       </c>
       <c r="D299" s="3" t="n">
-        <v>293</v>
+        <v>223</v>
       </c>
       <c r="E299" s="3" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>365</v>
       </c>
       <c r="C300" s="5" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D300" s="3" t="inlineStr"/>
       <c r="E300" s="3" t="inlineStr">
@@ -9750,7 +9750,7 @@
         <v>374</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D302" s="3" t="inlineStr"/>
       <c r="E302" s="3" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="8" t="inlineStr">
+      <c r="A303" s="9" t="inlineStr">
         <is>
           <t>TE50</t>
         </is>
@@ -9779,7 +9779,7 @@
         <v>377</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="D303" s="3" t="inlineStr"/>
       <c r="E303" s="3" t="inlineStr">
@@ -9837,7 +9837,7 @@
         <v>386</v>
       </c>
       <c r="C305" s="5" t="n">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="D305" s="3" t="inlineStr"/>
       <c r="E305" s="3" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="8" t="inlineStr">
+      <c r="A306" s="9" t="inlineStr">
         <is>
           <t>TE52</t>
         </is>
@@ -9866,7 +9866,7 @@
         <v>387</v>
       </c>
       <c r="C306" s="5" t="n">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D306" s="3" t="n">
         <v>279</v>

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -117,13 +117,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G306"/>
+  <dimension ref="A1:G307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -946,11 +946,11 @@
       <c r="B15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C15" s="8" t="n">
-        <v>36</v>
+      <c r="C15" s="5" t="n">
+        <v>20</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>TE1</t>
         </is>
@@ -1155,7 +1155,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>TE2</t>
         </is>
@@ -1163,7 +1163,7 @@
       <c r="B22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="9" t="n">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="n">
@@ -1194,8 +1194,8 @@
       <c r="B23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="8" t="n">
-        <v>43</v>
+      <c r="C23" s="10" t="n">
+        <v>42</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>43</v>
@@ -1225,11 +1225,11 @@
       <c r="B24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C24" s="10" t="n">
         <v>40</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -1256,11 +1256,11 @@
       <c r="B25" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="C25" s="7" t="n">
-        <v>21</v>
+      <c r="C25" s="5" t="n">
+        <v>26</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>29</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>31</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>30</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       <c r="B33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="C33" s="8" t="n">
+      <c r="C33" s="10" t="n">
         <v>58</v>
       </c>
       <c r="D33" s="3" t="n">
@@ -1535,11 +1535,11 @@
       <c r="B34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="C34" s="8" t="n">
+      <c r="C34" s="10" t="n">
         <v>68</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>34</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>42</v>
@@ -1598,10 +1598,10 @@
         <v>35</v>
       </c>
       <c r="C36" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="D36" s="3" t="n">
         <v>26</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>25</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>TE3</t>
         </is>
@@ -1659,7 +1659,7 @@
       <c r="B38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="C38" s="10" t="n">
+      <c r="C38" s="9" t="n">
         <v>33</v>
       </c>
       <c r="D38" s="3" t="n">
@@ -1690,11 +1690,11 @@
       <c r="B39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="C39" s="10" t="n">
+      <c r="C39" s="9" t="n">
         <v>28</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>15</v>
@@ -1784,10 +1784,10 @@
         <v>41</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
       <c r="B43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="10" t="n">
+      <c r="C43" s="9" t="n">
         <v>38</v>
       </c>
       <c r="D43" s="3" t="n">
@@ -1876,11 +1876,11 @@
       <c r="B45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="C45" s="8" t="n">
+      <c r="C45" s="10" t="n">
         <v>67</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>46</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>51</v>
@@ -1970,7 +1970,7 @@
         <v>47</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>33</v>
@@ -2001,10 +2001,10 @@
         <v>48</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
         <v>49</v>
       </c>
       <c r="C50" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="D50" s="3" t="n">
         <v>55</v>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>56</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D52" s="3" t="n">
         <v>48</v>
@@ -2116,7 +2116,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>TE4</t>
         </is>
@@ -2156,10 +2156,10 @@
         <v>53</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       <c r="B55" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="C55" s="10" t="n">
+      <c r="C55" s="9" t="n">
         <v>50</v>
       </c>
       <c r="D55" s="3" t="n">
@@ -2217,11 +2217,11 @@
       <c r="B56" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="C56" s="8" t="n">
+      <c r="C56" s="10" t="n">
         <v>69</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>56</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>50</v>
@@ -2280,10 +2280,10 @@
         <v>57</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>66</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>79</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="10" t="n">
+      <c r="C62" s="9" t="n">
         <v>56</v>
       </c>
       <c r="D62" s="3" t="n">
@@ -2465,11 +2465,11 @@
       <c r="B64" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="C64" s="8" t="n">
-        <v>83</v>
+      <c r="C64" s="10" t="n">
+        <v>89</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -2497,10 +2497,10 @@
         <v>64</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
         <v>66</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>72</v>
@@ -2589,11 +2589,11 @@
       <c r="B68" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="C68" s="8" t="n">
+      <c r="C68" s="10" t="n">
         <v>91</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="9" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>TE5</t>
         </is>
@@ -2620,7 +2620,7 @@
       <c r="B69" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="C69" s="10" t="n">
+      <c r="C69" s="9" t="n">
         <v>63</v>
       </c>
       <c r="D69" s="3" t="n">
@@ -2651,7 +2651,7 @@
       <c r="B70" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="C70" s="10" t="n">
+      <c r="C70" s="9" t="n">
         <v>65</v>
       </c>
       <c r="D70" s="3" t="n">
@@ -2683,10 +2683,10 @@
         <v>70</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>TE6</t>
         </is>
@@ -2717,7 +2717,7 @@
         <v>73</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -2744,11 +2744,11 @@
       <c r="B73" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="C73" s="8" t="n">
-        <v>106</v>
+      <c r="C73" s="4" t="n">
+        <v>80</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         <v>73</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -2806,11 +2806,11 @@
       <c r="B75" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="C75" s="8" t="n">
-        <v>87</v>
+      <c r="C75" s="10" t="n">
+        <v>88</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>57</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
@@ -2868,11 +2868,11 @@
       <c r="B77" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C77" s="8" t="n">
+      <c r="C77" s="10" t="n">
         <v>114</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         <v>77</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="9" t="inlineStr">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>TE7</t>
         </is>
@@ -2930,11 +2930,11 @@
       <c r="B79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C79" s="10" t="n">
+      <c r="C79" s="9" t="n">
         <v>72</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -2992,11 +2992,11 @@
       <c r="B81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="C81" s="4" t="n">
-        <v>89</v>
+      <c r="C81" s="10" t="n">
+        <v>96</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>81</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D82" s="3" t="n">
         <v>66</v>
@@ -3054,11 +3054,11 @@
       <c r="B83" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="C83" s="10" t="n">
+      <c r="C83" s="9" t="n">
         <v>78</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -3085,11 +3085,11 @@
       <c r="B84" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="C84" s="8" t="n">
+      <c r="C84" s="10" t="n">
         <v>104</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
       <c r="B87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="C87" s="8" t="n">
+      <c r="C87" s="10" t="n">
         <v>115</v>
       </c>
       <c r="D87" s="3" t="n">
@@ -3210,7 +3210,7 @@
         <v>87</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>129</v>
@@ -3232,7 +3232,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="9" t="inlineStr">
+      <c r="A89" s="8" t="inlineStr">
         <is>
           <t>TE8</t>
         </is>
@@ -3275,7 +3275,7 @@
         <v>100</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
@@ -3302,11 +3302,11 @@
       <c r="B91" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="C91" s="4" t="n">
-        <v>97</v>
+      <c r="C91" s="10" t="n">
+        <v>105</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -3333,11 +3333,11 @@
       <c r="B92" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="C92" s="8" t="n">
-        <v>130</v>
+      <c r="C92" s="10" t="n">
+        <v>128</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
       <c r="B94" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="C94" s="8" t="n">
+      <c r="C94" s="10" t="n">
         <v>117</v>
       </c>
       <c r="D94" s="3" t="n">
@@ -3426,11 +3426,11 @@
       <c r="B95" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="C95" s="8" t="n">
+      <c r="C95" s="10" t="n">
         <v>123</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
@@ -3458,10 +3458,10 @@
         <v>95</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
         <v>82</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="9" t="inlineStr">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>TE9</t>
         </is>
@@ -3523,7 +3523,7 @@
         <v>119</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         <v>98</v>
       </c>
       <c r="C99" s="5" t="n">
+        <v>112</v>
+      </c>
+      <c r="D99" s="3" t="n">
         <v>124</v>
-      </c>
-      <c r="D99" s="3" t="n">
-        <v>125</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
       <c r="B100" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="C100" s="8" t="n">
+      <c r="C100" s="10" t="n">
         <v>142</v>
       </c>
       <c r="D100" s="3" t="n">
@@ -3616,7 +3616,7 @@
         <v>113</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>102</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>132</v>
@@ -3674,11 +3674,11 @@
       <c r="B103" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="C103" s="8" t="n">
+      <c r="C103" s="10" t="n">
         <v>122</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>84</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="9" t="inlineStr">
+      <c r="A105" s="8" t="inlineStr">
         <is>
           <t>TE10</t>
         </is>
@@ -3771,7 +3771,7 @@
         <v>81</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>92</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
@@ -3829,11 +3829,11 @@
       <c r="B108" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="C108" s="5" t="n">
-        <v>138</v>
+      <c r="C108" s="9" t="n">
+        <v>102</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
@@ -3860,11 +3860,11 @@
       <c r="B109" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="C109" s="8" t="n">
-        <v>129</v>
+      <c r="C109" s="10" t="n">
+        <v>130</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>110</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="9" t="inlineStr">
+      <c r="A111" s="8" t="inlineStr">
         <is>
           <t>TE11</t>
         </is>
@@ -3926,7 +3926,7 @@
         <v>98</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
@@ -3984,11 +3984,11 @@
       <c r="B113" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="C113" s="10" t="n">
-        <v>108</v>
+      <c r="C113" s="9" t="n">
+        <v>109</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>121</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="9" t="inlineStr">
+      <c r="A115" s="8" t="inlineStr">
         <is>
           <t>TE12</t>
         </is>
@@ -4050,7 +4050,7 @@
         <v>85</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
@@ -4109,10 +4109,10 @@
         <v>117</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       <c r="B118" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="C118" s="8" t="n">
+      <c r="C118" s="10" t="n">
         <v>141</v>
       </c>
       <c r="D118" s="3" t="n">
@@ -4162,7 +4162,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="9" t="inlineStr">
+      <c r="A119" s="8" t="inlineStr">
         <is>
           <t>TE13</t>
         </is>
@@ -4174,7 +4174,7 @@
         <v>118</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>103</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
       <c r="B121" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="C121" s="8" t="n">
+      <c r="C121" s="10" t="n">
         <v>207</v>
       </c>
       <c r="D121" s="3" t="n">
@@ -4255,7 +4255,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="9" t="inlineStr">
+      <c r="A122" s="8" t="inlineStr">
         <is>
           <t>TE14</t>
         </is>
@@ -4267,7 +4267,7 @@
         <v>99</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>111</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
@@ -4388,10 +4388,10 @@
         <v>127</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>101</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
@@ -4449,8 +4449,8 @@
       <c r="B128" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="C128" s="8" t="n">
-        <v>227</v>
+      <c r="C128" s="10" t="n">
+        <v>272</v>
       </c>
       <c r="D128" s="3" t="n">
         <v>256</v>
@@ -4472,7 +4472,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="9" t="inlineStr">
+      <c r="A129" s="8" t="inlineStr">
         <is>
           <t>TE15</t>
         </is>
@@ -4511,7 +4511,7 @@
       <c r="B130" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="C130" s="8" t="n">
+      <c r="C130" s="10" t="n">
         <v>154</v>
       </c>
       <c r="D130" s="3" t="n">
@@ -4574,10 +4574,10 @@
         <v>133</v>
       </c>
       <c r="C132" s="7" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
       <c r="B133" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="C133" s="8" t="n">
+      <c r="C133" s="10" t="n">
         <v>209</v>
       </c>
       <c r="D133" s="3" t="n">
@@ -4635,7 +4635,7 @@
       <c r="B134" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="C134" s="10" t="n">
+      <c r="C134" s="9" t="n">
         <v>131</v>
       </c>
       <c r="D134" s="3" t="n">
@@ -4666,8 +4666,8 @@
       <c r="B135" s="3" t="n">
         <v>136</v>
       </c>
-      <c r="C135" s="8" t="n">
-        <v>250</v>
+      <c r="C135" s="5" t="n">
+        <v>199</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>161</v>
@@ -4728,7 +4728,7 @@
       <c r="B137" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="C137" s="8" t="n">
+      <c r="C137" s="10" t="n">
         <v>208</v>
       </c>
       <c r="D137" s="3" t="n">
@@ -4760,10 +4760,10 @@
         <v>139</v>
       </c>
       <c r="C138" s="7" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="9" t="inlineStr">
+      <c r="A140" s="8" t="inlineStr">
         <is>
           <t>TE16</t>
         </is>
@@ -4853,7 +4853,7 @@
         <v>142</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D141" s="3" t="n">
         <v>199</v>
@@ -4883,8 +4883,8 @@
       <c r="B142" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="C142" s="8" t="n">
-        <v>225</v>
+      <c r="C142" s="10" t="n">
+        <v>229</v>
       </c>
       <c r="D142" s="3" t="n">
         <v>239</v>
@@ -4915,7 +4915,7 @@
         <v>144</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="D143" s="3" t="n">
         <v>230</v>
@@ -4945,7 +4945,7 @@
       <c r="B144" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="C144" s="8" t="n">
+      <c r="C144" s="10" t="n">
         <v>243</v>
       </c>
       <c r="D144" s="3" t="n">
@@ -4999,7 +4999,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="9" t="inlineStr">
+      <c r="A146" s="8" t="inlineStr">
         <is>
           <t>TE17</t>
         </is>
@@ -5038,8 +5038,8 @@
       <c r="B147" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="C147" s="8" t="n">
-        <v>178</v>
+      <c r="C147" s="10" t="n">
+        <v>181</v>
       </c>
       <c r="D147" s="3" t="n">
         <v>184</v>
@@ -5194,7 +5194,7 @@
         <v>153</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D152" s="3" t="n">
         <v>219</v>
@@ -5216,7 +5216,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="9" t="inlineStr">
+      <c r="A153" s="8" t="inlineStr">
         <is>
           <t>TE18</t>
         </is>
@@ -5247,7 +5247,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="9" t="inlineStr">
+      <c r="A154" s="8" t="inlineStr">
         <is>
           <t>TE19</t>
         </is>
@@ -5278,7 +5278,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="9" t="inlineStr">
+      <c r="A155" s="8" t="inlineStr">
         <is>
           <t>TE20</t>
         </is>
@@ -5318,7 +5318,7 @@
         <v>158</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D156" s="3" t="n">
         <v>179</v>
@@ -5349,10 +5349,10 @@
         <v>159</v>
       </c>
       <c r="C157" s="7" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
@@ -5472,8 +5472,8 @@
       <c r="B161" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="C161" s="4" t="n">
-        <v>203</v>
+      <c r="C161" s="5" t="n">
+        <v>183</v>
       </c>
       <c r="D161" s="3" t="n">
         <v>171</v>
@@ -5504,7 +5504,7 @@
         <v>165</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="D162" s="3" t="n">
         <v>157</v>
@@ -5526,7 +5526,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="9" t="inlineStr">
+      <c r="A163" s="8" t="inlineStr">
         <is>
           <t>TE21</t>
         </is>
@@ -5565,7 +5565,7 @@
       <c r="B164" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="C164" s="10" t="n">
+      <c r="C164" s="9" t="n">
         <v>136</v>
       </c>
       <c r="D164" s="3" t="n">
@@ -5597,7 +5597,7 @@
         <v>169</v>
       </c>
       <c r="C165" s="4" t="n">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="D165" s="3" t="n">
         <v>178</v>
@@ -5628,7 +5628,7 @@
         <v>170</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D166" s="3" t="n">
         <v>182</v>
@@ -5650,7 +5650,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="9" t="inlineStr">
+      <c r="A167" s="8" t="inlineStr">
         <is>
           <t>TE22</t>
         </is>
@@ -5690,7 +5690,7 @@
         <v>174</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D168" s="3" t="inlineStr"/>
       <c r="E168" s="3" t="inlineStr">
@@ -5750,7 +5750,7 @@
         <v>176</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D170" s="3" t="n">
         <v>212</v>
@@ -5784,7 +5784,7 @@
         <v>95</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>178</v>
       </c>
       <c r="C172" s="4" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D172" s="3" t="n">
         <v>257</v>
@@ -5874,7 +5874,7 @@
         <v>185</v>
       </c>
       <c r="C174" s="4" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D174" s="3" t="n">
         <v>221</v>
@@ -5905,7 +5905,7 @@
         <v>186</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="D175" s="3" t="n">
         <v>283</v>
@@ -5936,7 +5936,7 @@
         <v>187</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D176" s="3" t="n">
         <v>222</v>
@@ -5989,7 +5989,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="9" t="inlineStr">
+      <c r="A178" s="8" t="inlineStr">
         <is>
           <t>TE23</t>
         </is>
@@ -6029,7 +6029,7 @@
         <v>192</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="D179" s="3" t="n">
         <v>203</v>
@@ -6090,7 +6090,7 @@
       <c r="B181" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="C181" s="10" t="n">
+      <c r="C181" s="9" t="n">
         <v>162</v>
       </c>
       <c r="D181" s="3" t="n">
@@ -6113,7 +6113,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="9" t="inlineStr">
+      <c r="A182" s="8" t="inlineStr">
         <is>
           <t>TE24</t>
         </is>
@@ -6153,7 +6153,7 @@
         <v>197</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D183" s="3" t="n">
         <v>277</v>
@@ -6215,7 +6215,7 @@
         <v>201</v>
       </c>
       <c r="C185" s="5" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D185" s="3" t="n">
         <v>183</v>
@@ -6276,11 +6276,11 @@
       <c r="B187" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="C187" s="10" t="n">
-        <v>109</v>
+      <c r="C187" s="9" t="n">
+        <v>139</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>205</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D188" s="3" t="n">
         <v>185</v>
@@ -6361,7 +6361,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="9" t="inlineStr">
+      <c r="A190" s="8" t="inlineStr">
         <is>
           <t>TE25</t>
         </is>
@@ -6400,7 +6400,7 @@
       <c r="B191" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="C191" s="10" t="n">
+      <c r="C191" s="9" t="n">
         <v>168</v>
       </c>
       <c r="D191" s="3" t="n">
@@ -6431,8 +6431,8 @@
       <c r="B192" s="3" t="n">
         <v>212</v>
       </c>
-      <c r="C192" s="5" t="n">
-        <v>201</v>
+      <c r="C192" s="4" t="n">
+        <v>249</v>
       </c>
       <c r="D192" s="3" t="n">
         <v>242</v>
@@ -6463,7 +6463,7 @@
         <v>213</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="D193" s="3" t="n">
         <v>289</v>
@@ -6556,7 +6556,7 @@
         <v>221</v>
       </c>
       <c r="C196" s="4" t="n">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D196" s="3" t="n">
         <v>238</v>
@@ -6587,7 +6587,7 @@
         <v>222</v>
       </c>
       <c r="C197" s="5" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D197" s="3" t="n">
         <v>240</v>
@@ -6649,7 +6649,7 @@
         <v>224</v>
       </c>
       <c r="C199" s="4" t="n">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="D199" s="3" t="inlineStr"/>
       <c r="E199" s="3" t="inlineStr">
@@ -6678,10 +6678,10 @@
         <v>225</v>
       </c>
       <c r="C200" s="7" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D200" s="3" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>232</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="D203" s="3" t="n">
         <v>299</v>
@@ -6802,7 +6802,7 @@
         <v>233</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>258</v>
+        <v>215</v>
       </c>
       <c r="D204" s="3" t="inlineStr"/>
       <c r="E204" s="3" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="9" t="inlineStr">
+      <c r="A206" s="8" t="inlineStr">
         <is>
           <t>TE26</t>
         </is>
@@ -6915,7 +6915,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="9" t="inlineStr">
+      <c r="A208" s="8" t="inlineStr">
         <is>
           <t>TE27</t>
         </is>
@@ -6946,7 +6946,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="9" t="inlineStr">
+      <c r="A209" s="8" t="inlineStr">
         <is>
           <t>TE28</t>
         </is>
@@ -6985,8 +6985,8 @@
       <c r="B210" s="3" t="n">
         <v>240</v>
       </c>
-      <c r="C210" s="10" t="n">
-        <v>163</v>
+      <c r="C210" s="5" t="n">
+        <v>248</v>
       </c>
       <c r="D210" s="3" t="n">
         <v>272</v>
@@ -7048,7 +7048,7 @@
         <v>242</v>
       </c>
       <c r="C212" s="4" t="n">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D212" s="3" t="n">
         <v>275</v>
@@ -7070,7 +7070,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="9" t="inlineStr">
+      <c r="A213" s="8" t="inlineStr">
         <is>
           <t>TE29</t>
         </is>
@@ -7078,7 +7078,7 @@
       <c r="B213" s="3" t="n">
         <v>243</v>
       </c>
-      <c r="C213" s="10" t="n">
+      <c r="C213" s="9" t="n">
         <v>165</v>
       </c>
       <c r="D213" s="3" t="n">
@@ -7140,8 +7140,8 @@
       <c r="B215" s="3" t="n">
         <v>245</v>
       </c>
-      <c r="C215" s="5" t="n">
-        <v>228</v>
+      <c r="C215" s="9" t="n">
+        <v>164</v>
       </c>
       <c r="D215" s="3" t="n">
         <v>158</v>
@@ -7194,7 +7194,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="9" t="inlineStr">
+      <c r="A217" s="8" t="inlineStr">
         <is>
           <t>TE30</t>
         </is>
@@ -7265,7 +7265,7 @@
         <v>250</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="D219" s="3" t="inlineStr"/>
       <c r="E219" s="3" t="inlineStr">
@@ -7325,7 +7325,7 @@
         <v>252</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D221" s="3" t="n">
         <v>287</v>
@@ -7347,7 +7347,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="9" t="inlineStr">
+      <c r="A222" s="8" t="inlineStr">
         <is>
           <t>TE31</t>
         </is>
@@ -7387,7 +7387,7 @@
         <v>255</v>
       </c>
       <c r="C223" s="4" t="n">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D223" s="3" t="inlineStr"/>
       <c r="E223" s="3" t="inlineStr">
@@ -7415,7 +7415,7 @@
       <c r="B224" s="3" t="n">
         <v>256</v>
       </c>
-      <c r="C224" s="10" t="n">
+      <c r="C224" s="9" t="n">
         <v>185</v>
       </c>
       <c r="D224" s="3" t="n">
@@ -7447,7 +7447,7 @@
         <v>257</v>
       </c>
       <c r="C225" s="5" t="n">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="D225" s="3" t="n">
         <v>282</v>
@@ -7498,7 +7498,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="9" t="inlineStr">
+      <c r="A227" s="8" t="inlineStr">
         <is>
           <t>TE32</t>
         </is>
@@ -7506,8 +7506,8 @@
       <c r="B227" s="3" t="n">
         <v>259</v>
       </c>
-      <c r="C227" s="5" t="n">
-        <v>276</v>
+      <c r="C227" s="4" t="n">
+        <v>309</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
@@ -7536,7 +7536,7 @@
         <v>260</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D228" s="3" t="n">
         <v>292</v>
@@ -7567,7 +7567,7 @@
         <v>261</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="D229" s="3" t="n">
         <v>293</v>
@@ -7598,7 +7598,7 @@
         <v>262</v>
       </c>
       <c r="C230" s="5" t="n">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="D230" s="3" t="n">
         <v>198</v>
@@ -7620,7 +7620,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="9" t="inlineStr">
+      <c r="A231" s="8" t="inlineStr">
         <is>
           <t>TE33</t>
         </is>
@@ -7660,7 +7660,7 @@
         <v>265</v>
       </c>
       <c r="C232" s="5" t="n">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D232" s="3" t="n">
         <v>290</v>
@@ -7744,7 +7744,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="9" t="inlineStr">
+      <c r="A235" s="8" t="inlineStr">
         <is>
           <t>TE34</t>
         </is>
@@ -7753,7 +7753,7 @@
         <v>268</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D235" s="3" t="inlineStr"/>
       <c r="E235" s="3" t="inlineStr">
@@ -7781,8 +7781,8 @@
       <c r="B236" s="3" t="n">
         <v>269</v>
       </c>
-      <c r="C236" s="10" t="n">
-        <v>199</v>
+      <c r="C236" s="5" t="n">
+        <v>227</v>
       </c>
       <c r="D236" s="3" t="n">
         <v>232</v>
@@ -7813,7 +7813,7 @@
         <v>270</v>
       </c>
       <c r="C237" s="5" t="n">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D237" s="3" t="n">
         <v>288</v>
@@ -7844,7 +7844,7 @@
         <v>271</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D238" s="3" t="inlineStr"/>
       <c r="E238" s="3" t="inlineStr">
@@ -7873,7 +7873,7 @@
         <v>272</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D239" s="3" t="n">
         <v>284</v>
@@ -7904,7 +7904,7 @@
         <v>273</v>
       </c>
       <c r="C240" s="4" t="n">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D240" s="3" t="inlineStr"/>
       <c r="E240" s="3" t="inlineStr">
@@ -7933,7 +7933,7 @@
         <v>274</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D241" s="3" t="n">
         <v>300</v>
@@ -7964,7 +7964,7 @@
         <v>275</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D242" s="3" t="n">
         <v>241</v>
@@ -8048,7 +8048,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="9" t="inlineStr">
+      <c r="A245" s="8" t="inlineStr">
         <is>
           <t>TE35</t>
         </is>
@@ -8056,7 +8056,7 @@
       <c r="B245" s="3" t="n">
         <v>278</v>
       </c>
-      <c r="C245" s="10" t="n">
+      <c r="C245" s="9" t="n">
         <v>188</v>
       </c>
       <c r="D245" s="3" t="n">
@@ -8087,8 +8087,8 @@
       <c r="B246" s="3" t="n">
         <v>280</v>
       </c>
-      <c r="C246" s="5" t="n">
-        <v>313</v>
+      <c r="C246" s="4" t="n">
+        <v>330</v>
       </c>
       <c r="D246" s="3" t="inlineStr"/>
       <c r="E246" s="3" t="inlineStr">
@@ -8116,8 +8116,8 @@
       <c r="B247" s="3" t="n">
         <v>281</v>
       </c>
-      <c r="C247" s="4" t="n">
-        <v>324</v>
+      <c r="C247" s="5" t="n">
+        <v>304</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
@@ -8177,7 +8177,7 @@
         <v>283</v>
       </c>
       <c r="C249" s="5" t="n">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="D249" s="3" t="n">
         <v>274</v>
@@ -8208,7 +8208,7 @@
         <v>284</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>296</v>
+        <v>251</v>
       </c>
       <c r="D250" s="3" t="inlineStr"/>
       <c r="E250" s="3" t="inlineStr">
@@ -8268,7 +8268,7 @@
         <v>288</v>
       </c>
       <c r="C252" s="4" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D252" s="3" t="inlineStr"/>
       <c r="E252" s="3" t="inlineStr">
@@ -8297,7 +8297,7 @@
         <v>289</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="D253" s="3" t="inlineStr"/>
       <c r="E253" s="3" t="inlineStr">
@@ -8386,7 +8386,7 @@
         <v>293</v>
       </c>
       <c r="C256" s="5" t="n">
-        <v>273</v>
+        <v>226</v>
       </c>
       <c r="D256" s="3" t="n">
         <v>204</v>
@@ -8417,7 +8417,7 @@
         <v>294</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D257" s="3" t="inlineStr"/>
       <c r="E257" s="3" t="inlineStr">
@@ -8446,7 +8446,7 @@
         <v>296</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="9" t="inlineStr">
+      <c r="A259" s="8" t="inlineStr">
         <is>
           <t>TE36</t>
         </is>
@@ -8475,7 +8475,7 @@
         <v>297</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
@@ -8504,7 +8504,7 @@
         <v>298</v>
       </c>
       <c r="C260" s="5" t="n">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="D260" s="3" t="n">
         <v>281</v>
@@ -8557,7 +8557,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="9" t="inlineStr">
+      <c r="A262" s="8" t="inlineStr">
         <is>
           <t>TE37</t>
         </is>
@@ -8597,7 +8597,7 @@
         <v>301</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D263" s="3" t="inlineStr"/>
       <c r="E263" s="3" t="inlineStr">
@@ -8657,7 +8657,7 @@
         <v>304</v>
       </c>
       <c r="C265" s="5" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D265" s="3" t="n">
         <v>231</v>
@@ -8688,7 +8688,7 @@
         <v>305</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D266" s="3" t="inlineStr"/>
       <c r="E266" s="3" t="inlineStr">
@@ -8748,7 +8748,7 @@
         <v>309</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D268" s="3" t="inlineStr"/>
       <c r="E268" s="3" t="inlineStr">
@@ -8777,7 +8777,7 @@
         <v>310</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D269" s="3" t="inlineStr"/>
       <c r="E269" s="3" t="inlineStr">
@@ -8806,7 +8806,7 @@
         <v>311</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="9" t="inlineStr">
+      <c r="A271" s="8" t="inlineStr">
         <is>
           <t>TE38</t>
         </is>
@@ -8835,7 +8835,7 @@
         <v>312</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr">
@@ -8924,7 +8924,7 @@
         <v>317</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D274" s="3" t="inlineStr"/>
       <c r="E274" s="3" t="inlineStr">
@@ -8944,73 +8944,73 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="9" t="inlineStr">
+      <c r="A275" s="6" t="inlineStr">
+        <is>
+          <t>RB98</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="n">
+        <v>321</v>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>329</v>
+      </c>
+      <c r="D275" s="3" t="inlineStr"/>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>Audric Estime</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="8" t="inlineStr">
         <is>
           <t>TE39</t>
         </is>
       </c>
-      <c r="B275" s="3" t="n">
+      <c r="B276" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="C275" s="5" t="n">
+      <c r="C276" s="5" t="n">
         <v>280</v>
       </c>
-      <c r="D275" s="3" t="n">
+      <c r="D276" s="3" t="n">
         <v>278</v>
       </c>
-      <c r="E275" s="3" t="inlineStr">
+      <c r="E276" s="3" t="inlineStr">
         <is>
           <t>Darnell Washington</t>
         </is>
       </c>
-      <c r="F275" s="3" t="inlineStr">
+      <c r="F276" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="G275" s="3" t="inlineStr">
+      <c r="G276" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
         <is>
           <t>WR112</t>
         </is>
       </c>
-      <c r="B276" s="3" t="n">
+      <c r="B277" s="3" t="n">
         <v>324</v>
-      </c>
-      <c r="C276" s="5" t="n">
-        <v>368</v>
-      </c>
-      <c r="D276" s="3" t="inlineStr"/>
-      <c r="E276" s="3" t="inlineStr">
-        <is>
-          <t>Cedric Tillman</t>
-        </is>
-      </c>
-      <c r="F276" s="3" t="inlineStr">
-        <is>
-          <t>CLE (11)</t>
-        </is>
-      </c>
-      <c r="G276" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="11" t="inlineStr">
-        <is>
-          <t>QB36</t>
-        </is>
-      </c>
-      <c r="B277" s="3" t="n">
-        <v>327</v>
       </c>
       <c r="C277" s="5" t="n">
         <v>367</v>
@@ -9018,72 +9018,72 @@
       <c r="D277" s="3" t="inlineStr"/>
       <c r="E277" s="3" t="inlineStr">
         <is>
+          <t>Cedric Tillman</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="G277" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="11" t="inlineStr">
+        <is>
+          <t>QB36</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="n">
+        <v>327</v>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>366</v>
+      </c>
+      <c r="D278" s="3" t="inlineStr"/>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
           <t>J.J. McCarthy</t>
         </is>
       </c>
-      <c r="F277" s="3" t="inlineStr">
+      <c r="F278" s="3" t="inlineStr">
         <is>
           <t>MIN (6)</t>
         </is>
       </c>
-      <c r="G277" s="3" t="inlineStr">
+      <c r="G278" s="3" t="inlineStr">
         <is>
           <t>QB</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>WR114</t>
-        </is>
-      </c>
-      <c r="B278" s="3" t="n">
-        <v>328</v>
-      </c>
-      <c r="C278" s="5" t="n">
-        <v>298</v>
-      </c>
-      <c r="D278" s="3" t="n">
-        <v>271</v>
-      </c>
-      <c r="E278" s="3" t="inlineStr">
-        <is>
-          <t>Luke McCaffrey</t>
-        </is>
-      </c>
-      <c r="F278" s="3" t="inlineStr">
-        <is>
-          <t>WAS (7)</t>
-        </is>
-      </c>
-      <c r="G278" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>WR115</t>
+          <t>WR114</t>
         </is>
       </c>
       <c r="B279" s="3" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>366</v>
-      </c>
-      <c r="D279" s="3" t="inlineStr"/>
+        <v>298</v>
+      </c>
+      <c r="D279" s="3" t="n">
+        <v>271</v>
+      </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>Tez Johnson</t>
+          <t>Luke McCaffrey</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>TB (10)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -9095,26 +9095,24 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>WR116</t>
+          <t>WR115</t>
         </is>
       </c>
       <c r="B280" s="3" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>267</v>
-      </c>
-      <c r="D280" s="3" t="n">
-        <v>233</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="D280" s="3" t="inlineStr"/>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>Tez Johnson</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>ATL (11)</t>
+          <t>TB (10)</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -9126,115 +9124,115 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
+          <t>WR116</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="C281" s="5" t="n">
+        <v>266</v>
+      </c>
+      <c r="D281" s="3" t="n">
+        <v>233</v>
+      </c>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>Jahan Dotson</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>ATL (11)</t>
+        </is>
+      </c>
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
           <t>WR117</t>
         </is>
       </c>
-      <c r="B281" s="3" t="n">
+      <c r="B282" s="3" t="n">
         <v>331</v>
       </c>
-      <c r="C281" s="5" t="n">
-        <v>354</v>
-      </c>
-      <c r="D281" s="3" t="inlineStr"/>
-      <c r="E281" s="3" t="inlineStr">
-        <is>
-          <t>Jalen Royals</t>
-        </is>
-      </c>
-      <c r="F281" s="3" t="inlineStr">
-        <is>
-          <t>KC (5)</t>
-        </is>
-      </c>
-      <c r="G281" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="9" t="inlineStr">
-        <is>
-          <t>TE40</t>
-        </is>
-      </c>
-      <c r="B282" s="3" t="n">
-        <v>332</v>
-      </c>
       <c r="C282" s="5" t="n">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="D282" s="3" t="inlineStr"/>
       <c r="E282" s="3" t="inlineStr">
         <is>
+          <t>Jalen Royals</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>KC (5)</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="8" t="inlineStr">
+        <is>
+          <t>TE40</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="n">
+        <v>332</v>
+      </c>
+      <c r="C283" s="5" t="n">
+        <v>372</v>
+      </c>
+      <c r="D283" s="3" t="inlineStr"/>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
           <t>Max Klare</t>
         </is>
       </c>
-      <c r="F282" s="3" t="inlineStr">
+      <c r="F283" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="G282" s="3" t="inlineStr">
+      <c r="G283" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="2" t="inlineStr">
-        <is>
-          <t>WR118</t>
-        </is>
-      </c>
-      <c r="B283" s="3" t="n">
-        <v>333</v>
-      </c>
-      <c r="C283" s="5" t="n">
-        <v>206</v>
-      </c>
-      <c r="D283" s="3" t="n">
-        <v>214</v>
-      </c>
-      <c r="E283" s="3" t="inlineStr">
-        <is>
-          <t>Caleb Douglas</t>
-        </is>
-      </c>
-      <c r="F283" s="3" t="inlineStr">
-        <is>
-          <t>MIA (6)</t>
-        </is>
-      </c>
-      <c r="G283" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>WR119</t>
+          <t>WR118</t>
         </is>
       </c>
       <c r="B284" s="3" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>297</v>
+        <v>206</v>
       </c>
       <c r="D284" s="3" t="n">
-        <v>270</v>
+        <v>214</v>
       </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Calvin Austin</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
         <is>
-          <t>NYG (8)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G284" s="3" t="inlineStr">
@@ -9246,26 +9244,26 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>WR120</t>
+          <t>WR119</t>
         </is>
       </c>
       <c r="B285" s="3" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>356</v>
+        <v>297</v>
       </c>
       <c r="D285" s="3" t="n">
-        <v>298</v>
+        <v>270</v>
       </c>
       <c r="E285" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Calvin Austin</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>NYG (8)</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -9277,82 +9275,84 @@
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
+          <t>WR120</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="n">
+        <v>335</v>
+      </c>
+      <c r="C286" s="5" t="n">
+        <v>355</v>
+      </c>
+      <c r="D286" s="3" t="n">
+        <v>298</v>
+      </c>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
+          <t>Jalen Tolbert</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="G286" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
           <t>WR122</t>
         </is>
       </c>
-      <c r="B286" s="3" t="n">
+      <c r="B287" s="3" t="n">
         <v>337</v>
       </c>
-      <c r="C286" s="5" t="n">
-        <v>331</v>
-      </c>
-      <c r="D286" s="3" t="inlineStr"/>
-      <c r="E286" s="3" t="inlineStr">
-        <is>
-          <t>Joshua Palmer</t>
-        </is>
-      </c>
-      <c r="F286" s="3" t="inlineStr">
-        <is>
-          <t>BUF (7)</t>
-        </is>
-      </c>
-      <c r="G286" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="9" t="inlineStr">
-        <is>
-          <t>TE41</t>
-        </is>
-      </c>
-      <c r="B287" s="3" t="n">
-        <v>338</v>
-      </c>
       <c r="C287" s="5" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D287" s="3" t="inlineStr"/>
       <c r="E287" s="3" t="inlineStr">
         <is>
-          <t>Michael Mayer</t>
+          <t>Joshua Palmer</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="9" t="inlineStr">
-        <is>
-          <t>TE42</t>
+      <c r="A288" s="8" t="inlineStr">
+        <is>
+          <t>TE41</t>
         </is>
       </c>
       <c r="B288" s="3" t="n">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Elijah Arroyo</t>
+          <t>Michael Mayer</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -9362,26 +9362,26 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="9" t="inlineStr">
-        <is>
-          <t>TE43</t>
+      <c r="A289" s="8" t="inlineStr">
+        <is>
+          <t>TE42</t>
         </is>
       </c>
       <c r="B289" s="3" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>Tyler Higbee</t>
+          <t>Elijah Arroyo</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
@@ -9391,171 +9391,171 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="11" t="inlineStr">
-        <is>
-          <t>QB37</t>
+      <c r="A290" s="8" t="inlineStr">
+        <is>
+          <t>TE43</t>
         </is>
       </c>
       <c r="B290" s="3" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="D290" s="3" t="inlineStr"/>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Tyler Higbee</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="9" t="inlineStr">
-        <is>
-          <t>TE45</t>
+      <c r="A291" s="11" t="inlineStr">
+        <is>
+          <t>QB37</t>
         </is>
       </c>
       <c r="B291" s="3" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>Dawson Knox</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="11" t="inlineStr">
-        <is>
-          <t>QB38</t>
+      <c r="A292" s="8" t="inlineStr">
+        <is>
+          <t>TE45</t>
         </is>
       </c>
       <c r="B292" s="3" t="n">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>342</v>
+        <v>377</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>Carson Beck</t>
+          <t>Dawson Knox</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>ARI (14)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="9" t="inlineStr">
-        <is>
-          <t>TE47</t>
+      <c r="A293" s="11" t="inlineStr">
+        <is>
+          <t>QB38</t>
         </is>
       </c>
       <c r="B293" s="3" t="n">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>369</v>
+        <v>341</v>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr">
         <is>
-          <t>Cole Kmet</t>
+          <t>Carson Beck</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>CHI (10)</t>
+          <t>ARI (14)</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="inlineStr">
-        <is>
-          <t>WR124</t>
+      <c r="A294" s="8" t="inlineStr">
+        <is>
+          <t>TE47</t>
         </is>
       </c>
       <c r="B294" s="3" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>Brenen Thompson</t>
+          <t>Cole Kmet</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>CHI (10)</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>WR125</t>
+          <t>WR124</t>
         </is>
       </c>
       <c r="B295" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="C295" s="5" t="n">
         <v>351</v>
-      </c>
-      <c r="C295" s="5" t="n">
-        <v>311</v>
       </c>
       <c r="D295" s="3" t="inlineStr"/>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>DeMario Douglas</t>
+          <t>Brenen Thompson</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -9567,24 +9567,24 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>WR126</t>
+          <t>WR125</t>
         </is>
       </c>
       <c r="B296" s="3" t="n">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="D296" s="3" t="inlineStr"/>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>Bryce Lance</t>
+          <t>DeMario Douglas</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -9596,24 +9596,24 @@
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>WR128</t>
+          <t>WR126</t>
         </is>
       </c>
       <c r="B297" s="3" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>294</v>
+        <v>326</v>
       </c>
       <c r="D297" s="3" t="inlineStr"/>
       <c r="E297" s="3" t="inlineStr">
         <is>
-          <t>Xavier Hutchinson</t>
+          <t>Bryce Lance</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>HOU (8)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
@@ -9623,86 +9623,86 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="6" t="inlineStr">
-        <is>
-          <t>RB104</t>
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>WR128</t>
         </is>
       </c>
       <c r="B298" s="3" t="n">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="D298" s="3" t="inlineStr"/>
       <c r="E298" s="3" t="inlineStr">
         <is>
+          <t>Xavier Hutchinson</t>
+        </is>
+      </c>
+      <c r="F298" s="3" t="inlineStr">
+        <is>
+          <t>HOU (8)</t>
+        </is>
+      </c>
+      <c r="G298" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="6" t="inlineStr">
+        <is>
+          <t>RB104</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="n">
+        <v>360</v>
+      </c>
+      <c r="C299" s="5" t="n">
+        <v>348</v>
+      </c>
+      <c r="D299" s="3" t="inlineStr"/>
+      <c r="E299" s="3" t="inlineStr">
+        <is>
           <t>Jawhar Jordan</t>
         </is>
       </c>
-      <c r="F298" s="3" t="inlineStr">
+      <c r="F299" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="G298" s="3" t="inlineStr">
+      <c r="G299" s="3" t="inlineStr">
         <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="2" t="inlineStr">
-        <is>
-          <t>WR130</t>
-        </is>
-      </c>
-      <c r="B299" s="3" t="n">
-        <v>363</v>
-      </c>
-      <c r="C299" s="5" t="n">
-        <v>266</v>
-      </c>
-      <c r="D299" s="3" t="n">
-        <v>223</v>
-      </c>
-      <c r="E299" s="3" t="inlineStr">
-        <is>
-          <t>Treylon Burks</t>
-        </is>
-      </c>
-      <c r="F299" s="3" t="inlineStr">
-        <is>
-          <t>WAS (7)</t>
-        </is>
-      </c>
-      <c r="G299" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>WR132</t>
+          <t>WR130</t>
         </is>
       </c>
       <c r="B300" s="3" t="n">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C300" s="5" t="n">
-        <v>374</v>
-      </c>
-      <c r="D300" s="3" t="inlineStr"/>
+        <v>267</v>
+      </c>
+      <c r="D300" s="3" t="n">
+        <v>223</v>
+      </c>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>Nick Westbrook-Ikhine</t>
+          <t>Treylon Burks</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>IND (13)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -9714,24 +9714,24 @@
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>WR133</t>
+          <t>WR132</t>
         </is>
       </c>
       <c r="B301" s="3" t="n">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C301" s="5" t="n">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="D301" s="3" t="inlineStr"/>
       <c r="E301" s="3" t="inlineStr">
         <is>
-          <t>Savion Williams</t>
+          <t>Nick Westbrook-Ikhine</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>GB (11)</t>
+          <t>IND (13)</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
@@ -9741,147 +9741,176 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="6" t="inlineStr">
-        <is>
-          <t>RB107</t>
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>WR133</t>
         </is>
       </c>
       <c r="B302" s="3" t="n">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="D302" s="3" t="inlineStr"/>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>Raheim Sanders</t>
+          <t>Savion Williams</t>
         </is>
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>GB (11)</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="9" t="inlineStr">
-        <is>
-          <t>TE50</t>
+      <c r="A303" s="6" t="inlineStr">
+        <is>
+          <t>RB107</t>
         </is>
       </c>
       <c r="B303" s="3" t="n">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>310</v>
+        <v>347</v>
       </c>
       <c r="D303" s="3" t="inlineStr"/>
       <c r="E303" s="3" t="inlineStr">
         <is>
-          <t>Eli Raridon</t>
+          <t>Raheim Sanders</t>
         </is>
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="inlineStr">
-        <is>
-          <t>WR138</t>
+      <c r="A304" s="8" t="inlineStr">
+        <is>
+          <t>TE50</t>
         </is>
       </c>
       <c r="B304" s="3" t="n">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C304" s="5" t="n">
-        <v>359</v>
+        <v>303</v>
       </c>
       <c r="D304" s="3" t="inlineStr"/>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>Zavion Thomas</t>
+          <t>Eli Raridon</t>
         </is>
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
-          <t>CHI (10)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="6" t="inlineStr">
-        <is>
-          <t>RB109</t>
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>WR138</t>
         </is>
       </c>
       <c r="B305" s="3" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C305" s="5" t="n">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="D305" s="3" t="inlineStr"/>
       <c r="E305" s="3" t="inlineStr">
         <is>
+          <t>Zavion Thomas</t>
+        </is>
+      </c>
+      <c r="F305" s="3" t="inlineStr">
+        <is>
+          <t>CHI (10)</t>
+        </is>
+      </c>
+      <c r="G305" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="6" t="inlineStr">
+        <is>
+          <t>RB109</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="n">
+        <v>386</v>
+      </c>
+      <c r="C306" s="5" t="n">
+        <v>349</v>
+      </c>
+      <c r="D306" s="3" t="inlineStr"/>
+      <c r="E306" s="3" t="inlineStr">
+        <is>
           <t>Phil Mafah</t>
         </is>
       </c>
-      <c r="F305" s="3" t="inlineStr">
+      <c r="F306" s="3" t="inlineStr">
         <is>
           <t>DAL (14)</t>
         </is>
       </c>
-      <c r="G305" s="3" t="inlineStr">
+      <c r="G306" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" s="9" t="inlineStr">
+    <row r="307">
+      <c r="A307" s="8" t="inlineStr">
         <is>
           <t>TE52</t>
         </is>
       </c>
-      <c r="B306" s="3" t="n">
+      <c r="B307" s="3" t="n">
         <v>387</v>
       </c>
-      <c r="C306" s="5" t="n">
+      <c r="C307" s="5" t="n">
         <v>281</v>
       </c>
-      <c r="D306" s="3" t="n">
+      <c r="D307" s="3" t="n">
         <v>279</v>
       </c>
-      <c r="E306" s="3" t="inlineStr">
+      <c r="E307" s="3" t="inlineStr">
         <is>
           <t>Erick All</t>
         </is>
       </c>
-      <c r="F306" s="3" t="inlineStr">
+      <c r="F307" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="G306" s="3" t="inlineStr">
+      <c r="G307" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -120,13 +120,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G307"/>
+  <dimension ref="A1:G305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,10 +668,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>16</v>
@@ -826,7 +826,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         <v>11</v>
       </c>
       <c r="C12" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="3" t="n">
         <v>22</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>21</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -884,8 +884,8 @@
       <c r="B13" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>13</v>
+      <c r="C13" s="4" t="n">
+        <v>17</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>17</v>
@@ -916,10 +916,10 @@
         <v>13</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -946,8 +946,8 @@
       <c r="B15" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="C15" s="5" t="n">
-        <v>20</v>
+      <c r="C15" s="4" t="n">
+        <v>24</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>24</v>
@@ -978,10 +978,10 @@
         <v>15</v>
       </c>
       <c r="C16" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>23</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>22</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>27</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         <v>17</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -1102,10 +1102,10 @@
         <v>19</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>14</v>
@@ -1163,11 +1163,11 @@
       <c r="B22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C22" s="9" t="n">
-        <v>17</v>
+      <c r="C22" s="5" t="n">
+        <v>18</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -1194,8 +1194,8 @@
       <c r="B23" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="C23" s="10" t="n">
-        <v>42</v>
+      <c r="C23" s="9" t="n">
+        <v>35</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>43</v>
@@ -1217,7 +1217,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>QB1</t>
         </is>
@@ -1225,11 +1225,11 @@
       <c r="B24" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="C24" s="10" t="n">
-        <v>40</v>
+      <c r="C24" s="9" t="n">
+        <v>43</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
         <v>24</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>14</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
@@ -1349,11 +1349,11 @@
       <c r="B28" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="C28" s="4" t="n">
-        <v>31</v>
+      <c r="C28" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1380,8 +1380,8 @@
       <c r="B29" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="C29" s="4" t="n">
-        <v>35</v>
+      <c r="C29" s="5" t="n">
+        <v>31</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>40</v>
@@ -1412,10 +1412,10 @@
         <v>29</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -1442,11 +1442,11 @@
       <c r="B31" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="C31" s="4" t="n">
-        <v>34</v>
+      <c r="C31" s="5" t="n">
+        <v>28</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>31</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>31</v>
@@ -1496,7 +1496,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>QB2</t>
         </is>
@@ -1504,11 +1504,11 @@
       <c r="B33" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="C33" s="10" t="n">
-        <v>58</v>
+      <c r="C33" s="9" t="n">
+        <v>61</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>QB3</t>
         </is>
@@ -1535,11 +1535,11 @@
       <c r="B34" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="C34" s="10" t="n">
-        <v>68</v>
+      <c r="C34" s="9" t="n">
+        <v>69</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1566,11 +1566,11 @@
       <c r="B35" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="C35" s="4" t="n">
-        <v>43</v>
+      <c r="C35" s="5" t="n">
+        <v>36</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
@@ -1597,11 +1597,11 @@
       <c r="B36" s="3" t="n">
         <v>35</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="D36" s="3" t="n">
         <v>25</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>26</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -1629,10 +1629,10 @@
         <v>36</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -1659,11 +1659,11 @@
       <c r="B38" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="C38" s="9" t="n">
-        <v>33</v>
+      <c r="C38" s="5" t="n">
+        <v>38</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -1690,8 +1690,8 @@
       <c r="B39" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="C39" s="9" t="n">
-        <v>28</v>
+      <c r="C39" s="7" t="n">
+        <v>26</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>29</v>
@@ -1722,7 +1722,7 @@
         <v>39</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>15</v>
@@ -1753,10 +1753,10 @@
         <v>40</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
@@ -1784,10 +1784,10 @@
         <v>41</v>
       </c>
       <c r="C42" s="7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1814,11 +1814,11 @@
       <c r="B43" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="C43" s="9" t="n">
-        <v>38</v>
+      <c r="C43" s="5" t="n">
+        <v>41</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         <v>43</v>
       </c>
       <c r="C44" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>QB4</t>
         </is>
@@ -1876,11 +1876,11 @@
       <c r="B45" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="C45" s="10" t="n">
-        <v>67</v>
+      <c r="C45" s="9" t="n">
+        <v>68</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -1907,11 +1907,11 @@
       <c r="B46" s="3" t="n">
         <v>45</v>
       </c>
-      <c r="C46" s="7" t="n">
-        <v>39</v>
+      <c r="C46" s="5" t="n">
+        <v>42</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -1939,10 +1939,10 @@
         <v>46</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -1970,10 +1970,10 @@
         <v>47</v>
       </c>
       <c r="C48" s="7" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         <v>48</v>
       </c>
       <c r="C49" s="7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>49</v>
       </c>
       <c r="C50" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>55</v>
@@ -2063,7 +2063,7 @@
         <v>50</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>47</v>
@@ -2094,7 +2094,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D52" s="3" t="n">
         <v>48</v>
@@ -2125,10 +2125,10 @@
         <v>52</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
@@ -2156,10 +2156,10 @@
         <v>53</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -2186,11 +2186,11 @@
       <c r="B55" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="C55" s="9" t="n">
-        <v>50</v>
+      <c r="C55" s="11" t="n">
+        <v>49</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>QB5</t>
         </is>
@@ -2217,11 +2217,11 @@
       <c r="B56" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="C56" s="10" t="n">
+      <c r="C56" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="D56" s="3" t="n">
         <v>69</v>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>64</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
         <v>56</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -2280,10 +2280,10 @@
         <v>57</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>QB6</t>
         </is>
@@ -2310,11 +2310,11 @@
       <c r="B59" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="C59" s="5" t="n">
-        <v>66</v>
+      <c r="C59" s="4" t="n">
+        <v>67</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -2341,8 +2341,8 @@
       <c r="B60" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="C60" s="5" t="n">
-        <v>45</v>
+      <c r="C60" s="11" t="n">
+        <v>44</v>
       </c>
       <c r="D60" s="3" t="n">
         <v>45</v>
@@ -2373,10 +2373,10 @@
         <v>60</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
@@ -2403,11 +2403,11 @@
       <c r="B62" s="3" t="n">
         <v>61</v>
       </c>
-      <c r="C62" s="9" t="n">
-        <v>56</v>
+      <c r="C62" s="11" t="n">
+        <v>57</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
@@ -2435,7 +2435,7 @@
         <v>62</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>44</v>
@@ -2465,11 +2465,11 @@
       <c r="B64" s="3" t="n">
         <v>63</v>
       </c>
-      <c r="C64" s="10" t="n">
-        <v>89</v>
+      <c r="C64" s="9" t="n">
+        <v>84</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -2496,11 +2496,11 @@
       <c r="B65" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="C65" s="5" t="n">
-        <v>64</v>
+      <c r="C65" s="11" t="n">
+        <v>60</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="11" t="inlineStr">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>QB7</t>
         </is>
@@ -2527,11 +2527,11 @@
       <c r="B66" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="C66" s="4" t="n">
-        <v>77</v>
+      <c r="C66" s="9" t="n">
+        <v>82</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
@@ -2559,10 +2559,10 @@
         <v>66</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="11" t="inlineStr">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>QB8</t>
         </is>
@@ -2589,11 +2589,11 @@
       <c r="B68" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="C68" s="10" t="n">
-        <v>91</v>
+      <c r="C68" s="9" t="n">
+        <v>102</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -2620,11 +2620,11 @@
       <c r="B69" s="3" t="n">
         <v>68</v>
       </c>
-      <c r="C69" s="9" t="n">
-        <v>63</v>
+      <c r="C69" s="5" t="n">
+        <v>71</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -2651,11 +2651,11 @@
       <c r="B70" s="3" t="n">
         <v>69</v>
       </c>
-      <c r="C70" s="9" t="n">
+      <c r="C70" s="11" t="n">
         <v>65</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
@@ -2683,10 +2683,10 @@
         <v>70</v>
       </c>
       <c r="C71" s="7" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -2713,11 +2713,11 @@
       <c r="B72" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="C72" s="5" t="n">
-        <v>73</v>
+      <c r="C72" s="11" t="n">
+        <v>66</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -2744,11 +2744,11 @@
       <c r="B73" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="C73" s="4" t="n">
-        <v>80</v>
+      <c r="C73" s="9" t="n">
+        <v>93</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         <v>73</v>
       </c>
       <c r="C74" s="4" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -2806,11 +2806,11 @@
       <c r="B75" s="3" t="n">
         <v>74</v>
       </c>
-      <c r="C75" s="10" t="n">
-        <v>88</v>
+      <c r="C75" s="9" t="n">
+        <v>87</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -2838,11 +2838,11 @@
         <v>75</v>
       </c>
       <c r="C76" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="D76" s="3" t="n">
         <v>57</v>
       </c>
-      <c r="D76" s="3" t="n">
-        <v>56</v>
-      </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
           <t>Jadarian Price</t>
@@ -2860,7 +2860,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="11" t="inlineStr">
+      <c r="A77" s="10" t="inlineStr">
         <is>
           <t>QB9</t>
         </is>
@@ -2868,11 +2868,11 @@
       <c r="B77" s="3" t="n">
         <v>76</v>
       </c>
-      <c r="C77" s="10" t="n">
-        <v>114</v>
+      <c r="C77" s="9" t="n">
+        <v>115</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
@@ -2900,10 +2900,10 @@
         <v>77</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -2930,11 +2930,11 @@
       <c r="B79" s="3" t="n">
         <v>78</v>
       </c>
-      <c r="C79" s="9" t="n">
-        <v>72</v>
+      <c r="C79" s="11" t="n">
+        <v>70</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="11" t="inlineStr">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>QB10</t>
         </is>
@@ -2962,10 +2962,10 @@
         <v>79</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
@@ -2992,11 +2992,11 @@
       <c r="B81" s="3" t="n">
         <v>80</v>
       </c>
-      <c r="C81" s="10" t="n">
-        <v>96</v>
+      <c r="C81" s="4" t="n">
+        <v>88</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         <v>81</v>
       </c>
       <c r="C82" s="7" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
@@ -3054,11 +3054,11 @@
       <c r="B83" s="3" t="n">
         <v>82</v>
       </c>
-      <c r="C83" s="9" t="n">
-        <v>78</v>
+      <c r="C83" s="5" t="n">
+        <v>81</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -3085,11 +3085,11 @@
       <c r="B84" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="C84" s="10" t="n">
+      <c r="C84" s="9" t="n">
         <v>104</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
@@ -3117,10 +3117,10 @@
         <v>84</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
@@ -3148,10 +3148,10 @@
         <v>85</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -3178,11 +3178,11 @@
       <c r="B87" s="3" t="n">
         <v>86</v>
       </c>
-      <c r="C87" s="10" t="n">
-        <v>115</v>
+      <c r="C87" s="9" t="n">
+        <v>123</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -3209,11 +3209,11 @@
       <c r="B88" s="3" t="n">
         <v>87</v>
       </c>
-      <c r="C88" s="5" t="n">
-        <v>87</v>
+      <c r="C88" s="4" t="n">
+        <v>96</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>62</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
@@ -3272,10 +3272,10 @@
         <v>89</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
@@ -3302,11 +3302,11 @@
       <c r="B91" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="C91" s="10" t="n">
-        <v>105</v>
+      <c r="C91" s="5" t="n">
+        <v>94</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="11" t="inlineStr">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>QB11</t>
         </is>
@@ -3333,11 +3333,11 @@
       <c r="B92" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="C92" s="10" t="n">
-        <v>128</v>
+      <c r="C92" s="9" t="n">
+        <v>119</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>92</v>
       </c>
       <c r="C93" s="7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>46</v>
@@ -3395,11 +3395,11 @@
       <c r="B94" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="C94" s="10" t="n">
-        <v>117</v>
+      <c r="C94" s="9" t="n">
+        <v>135</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="11" t="inlineStr">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>QB12</t>
         </is>
@@ -3426,11 +3426,11 @@
       <c r="B95" s="3" t="n">
         <v>94</v>
       </c>
-      <c r="C95" s="10" t="n">
-        <v>123</v>
+      <c r="C95" s="9" t="n">
+        <v>118</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
@@ -3458,10 +3458,10 @@
         <v>95</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
@@ -3489,10 +3489,10 @@
         <v>96</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D97" s="3" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>97</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         <v>98</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="11" t="inlineStr">
+      <c r="A100" s="10" t="inlineStr">
         <is>
           <t>QB13</t>
         </is>
@@ -3581,11 +3581,11 @@
       <c r="B100" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="C100" s="10" t="n">
+      <c r="C100" s="9" t="n">
         <v>142</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="11" t="inlineStr">
+      <c r="A101" s="10" t="inlineStr">
         <is>
           <t>QB14</t>
         </is>
@@ -3612,11 +3612,11 @@
       <c r="B101" s="3" t="n">
         <v>101</v>
       </c>
-      <c r="C101" s="5" t="n">
-        <v>113</v>
+      <c r="C101" s="9" t="n">
+        <v>114</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>138</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="11" t="inlineStr">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>QB15</t>
         </is>
@@ -3674,11 +3674,11 @@
       <c r="B103" s="3" t="n">
         <v>103</v>
       </c>
-      <c r="C103" s="10" t="n">
-        <v>122</v>
+      <c r="C103" s="9" t="n">
+        <v>117</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
@@ -3706,10 +3706,10 @@
         <v>104</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
@@ -3737,10 +3737,10 @@
         <v>105</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
@@ -3767,11 +3767,11 @@
       <c r="B106" s="3" t="n">
         <v>106</v>
       </c>
-      <c r="C106" s="5" t="n">
-        <v>81</v>
+      <c r="C106" s="11" t="n">
+        <v>76</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
@@ -3799,10 +3799,10 @@
         <v>107</v>
       </c>
       <c r="C107" s="7" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
@@ -3829,11 +3829,11 @@
       <c r="B108" s="3" t="n">
         <v>108</v>
       </c>
-      <c r="C108" s="9" t="n">
-        <v>102</v>
+      <c r="C108" s="11" t="n">
+        <v>100</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="11" t="inlineStr">
+      <c r="A109" s="10" t="inlineStr">
         <is>
           <t>QB16</t>
         </is>
@@ -3860,11 +3860,11 @@
       <c r="B109" s="3" t="n">
         <v>109</v>
       </c>
-      <c r="C109" s="10" t="n">
-        <v>130</v>
+      <c r="C109" s="9" t="n">
+        <v>131</v>
       </c>
       <c r="D109" s="3" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
@@ -3892,10 +3892,10 @@
         <v>110</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -3923,10 +3923,10 @@
         <v>111</v>
       </c>
       <c r="C111" s="7" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
@@ -3954,10 +3954,10 @@
         <v>112</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
@@ -3984,11 +3984,11 @@
       <c r="B113" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="C113" s="9" t="n">
-        <v>109</v>
+      <c r="C113" s="5" t="n">
+        <v>112</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="11" t="inlineStr">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>QB17</t>
         </is>
@@ -4016,10 +4016,10 @@
         <v>114</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
@@ -4047,10 +4047,10 @@
         <v>115</v>
       </c>
       <c r="C115" s="7" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
@@ -4077,11 +4077,11 @@
       <c r="B116" s="3" t="n">
         <v>116</v>
       </c>
-      <c r="C116" s="5" t="n">
-        <v>116</v>
+      <c r="C116" s="4" t="n">
+        <v>124</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="11" t="inlineStr">
+      <c r="A117" s="10" t="inlineStr">
         <is>
           <t>QB18</t>
         </is>
@@ -4109,10 +4109,10 @@
         <v>117</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D117" s="3" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="11" t="inlineStr">
+      <c r="A118" s="10" t="inlineStr">
         <is>
           <t>QB19</t>
         </is>
@@ -4139,11 +4139,11 @@
       <c r="B118" s="3" t="n">
         <v>118</v>
       </c>
-      <c r="C118" s="10" t="n">
+      <c r="C118" s="9" t="n">
         <v>141</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
@@ -4170,11 +4170,11 @@
       <c r="B119" s="3" t="n">
         <v>119</v>
       </c>
-      <c r="C119" s="5" t="n">
-        <v>118</v>
+      <c r="C119" s="7" t="n">
+        <v>108</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
@@ -4202,10 +4202,10 @@
         <v>121</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="11" t="inlineStr">
+      <c r="A121" s="10" t="inlineStr">
         <is>
           <t>QB20</t>
         </is>
@@ -4232,11 +4232,11 @@
       <c r="B121" s="3" t="n">
         <v>122</v>
       </c>
-      <c r="C121" s="10" t="n">
+      <c r="C121" s="9" t="n">
         <v>207</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
@@ -4264,10 +4264,10 @@
         <v>123</v>
       </c>
       <c r="C122" s="7" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
@@ -4295,10 +4295,10 @@
         <v>124</v>
       </c>
       <c r="C123" s="7" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
@@ -4325,11 +4325,11 @@
       <c r="B124" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="C124" s="7" t="n">
-        <v>111</v>
+      <c r="C124" s="11" t="n">
+        <v>120</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>74</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>106</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
         <v>128</v>
       </c>
       <c r="C127" s="7" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D127" s="3" t="n">
         <v>88</v>
@@ -4449,11 +4449,11 @@
       <c r="B128" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="C128" s="10" t="n">
-        <v>272</v>
+      <c r="C128" s="9" t="n">
+        <v>274</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
@@ -4481,10 +4481,10 @@
         <v>130</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="11" t="inlineStr">
+      <c r="A130" s="10" t="inlineStr">
         <is>
           <t>QB21</t>
         </is>
@@ -4511,11 +4511,11 @@
       <c r="B130" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="C130" s="10" t="n">
+      <c r="C130" s="9" t="n">
         <v>154</v>
       </c>
       <c r="D130" s="3" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
@@ -4543,10 +4543,10 @@
         <v>132</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
@@ -4574,10 +4574,10 @@
         <v>133</v>
       </c>
       <c r="C132" s="7" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="11" t="inlineStr">
+      <c r="A133" s="10" t="inlineStr">
         <is>
           <t>QB22</t>
         </is>
@@ -4604,11 +4604,11 @@
       <c r="B133" s="3" t="n">
         <v>134</v>
       </c>
-      <c r="C133" s="10" t="n">
+      <c r="C133" s="9" t="n">
         <v>209</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
@@ -4635,11 +4635,11 @@
       <c r="B134" s="3" t="n">
         <v>135</v>
       </c>
-      <c r="C134" s="9" t="n">
-        <v>131</v>
+      <c r="C134" s="5" t="n">
+        <v>132</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>161</v>
@@ -4698,7 +4698,7 @@
         <v>137</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="D136" s="3" t="n">
         <v>162</v>
@@ -4720,7 +4720,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="11" t="inlineStr">
+      <c r="A137" s="10" t="inlineStr">
         <is>
           <t>QB23</t>
         </is>
@@ -4728,11 +4728,11 @@
       <c r="B137" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="C137" s="10" t="n">
+      <c r="C137" s="9" t="n">
         <v>208</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
@@ -4760,10 +4760,10 @@
         <v>139</v>
       </c>
       <c r="C138" s="7" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D138" s="3" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
@@ -4791,10 +4791,10 @@
         <v>140</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="D139" s="3" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
@@ -4822,10 +4822,10 @@
         <v>141</v>
       </c>
       <c r="C140" s="7" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D140" s="3" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>202</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
@@ -4883,11 +4883,11 @@
       <c r="B142" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="C142" s="10" t="n">
-        <v>229</v>
+      <c r="C142" s="9" t="n">
+        <v>252</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
@@ -4914,11 +4914,11 @@
       <c r="B143" s="3" t="n">
         <v>144</v>
       </c>
-      <c r="C143" s="5" t="n">
-        <v>203</v>
+      <c r="C143" s="9" t="n">
+        <v>225</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="11" t="inlineStr">
+      <c r="A144" s="10" t="inlineStr">
         <is>
           <t>QB24</t>
         </is>
@@ -4945,11 +4945,11 @@
       <c r="B144" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="C144" s="10" t="n">
-        <v>243</v>
+      <c r="C144" s="9" t="n">
+        <v>242</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
@@ -4977,10 +4977,10 @@
         <v>146</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>147</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D146" s="3" t="n">
         <v>190</v>
@@ -5038,11 +5038,11 @@
       <c r="B147" s="3" t="n">
         <v>148</v>
       </c>
-      <c r="C147" s="10" t="n">
-        <v>181</v>
+      <c r="C147" s="9" t="n">
+        <v>179</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
@@ -5070,10 +5070,10 @@
         <v>149</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
@@ -5101,10 +5101,10 @@
         <v>150</v>
       </c>
       <c r="C149" s="4" t="n">
-        <v>271</v>
+        <v>221</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="11" t="inlineStr">
+      <c r="A150" s="10" t="inlineStr">
         <is>
           <t>QB25</t>
         </is>
@@ -5132,10 +5132,10 @@
         <v>151</v>
       </c>
       <c r="C150" s="4" t="n">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="11" t="inlineStr">
+      <c r="A151" s="10" t="inlineStr">
         <is>
           <t>QB26</t>
         </is>
@@ -5163,10 +5163,10 @@
         <v>152</v>
       </c>
       <c r="C151" s="4" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
@@ -5194,10 +5194,10 @@
         <v>153</v>
       </c>
       <c r="C152" s="4" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>175</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
@@ -5256,10 +5256,10 @@
         <v>155</v>
       </c>
       <c r="C154" s="4" t="n">
-        <v>235</v>
+        <v>268</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>156</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D155" s="3" t="n">
         <v>191</v>
@@ -5318,10 +5318,10 @@
         <v>158</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
@@ -5349,10 +5349,10 @@
         <v>159</v>
       </c>
       <c r="C157" s="7" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         <v>160</v>
       </c>
       <c r="C158" s="4" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>166</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
@@ -5442,10 +5442,10 @@
         <v>162</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
@@ -5472,11 +5472,11 @@
       <c r="B161" s="3" t="n">
         <v>164</v>
       </c>
-      <c r="C161" s="5" t="n">
-        <v>183</v>
+      <c r="C161" s="4" t="n">
+        <v>199</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         <v>165</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>153</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
@@ -5565,11 +5565,11 @@
       <c r="B164" s="3" t="n">
         <v>167</v>
       </c>
-      <c r="C164" s="9" t="n">
-        <v>136</v>
+      <c r="C164" s="11" t="n">
+        <v>137</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -5597,10 +5597,10 @@
         <v>169</v>
       </c>
       <c r="C165" s="4" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
@@ -5628,10 +5628,10 @@
         <v>170</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
@@ -5659,10 +5659,10 @@
         <v>173</v>
       </c>
       <c r="C167" s="4" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>174</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D168" s="3" t="inlineStr"/>
       <c r="E168" s="3" t="inlineStr">
@@ -5722,7 +5722,7 @@
         <v>167</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
@@ -5750,10 +5750,10 @@
         <v>176</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>95</v>
       </c>
       <c r="D171" s="3" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
@@ -5812,10 +5812,10 @@
         <v>178</v>
       </c>
       <c r="C172" s="4" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="11" t="inlineStr">
+      <c r="A173" s="10" t="inlineStr">
         <is>
           <t>QB27</t>
         </is>
@@ -5846,7 +5846,7 @@
         <v>244</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
@@ -5874,10 +5874,10 @@
         <v>185</v>
       </c>
       <c r="C174" s="4" t="n">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
@@ -5905,10 +5905,10 @@
         <v>186</v>
       </c>
       <c r="C175" s="4" t="n">
-        <v>249</v>
+        <v>298</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
@@ -5936,10 +5936,10 @@
         <v>187</v>
       </c>
       <c r="C176" s="4" t="n">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
@@ -5967,10 +5967,10 @@
         <v>188</v>
       </c>
       <c r="C177" s="4" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -5998,10 +5998,10 @@
         <v>191</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>184</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
@@ -6060,10 +6060,10 @@
         <v>194</v>
       </c>
       <c r="C180" s="4" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
@@ -6090,11 +6090,11 @@
       <c r="B181" s="3" t="n">
         <v>195</v>
       </c>
-      <c r="C181" s="9" t="n">
+      <c r="C181" s="11" t="n">
         <v>162</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
@@ -6122,10 +6122,10 @@
         <v>196</v>
       </c>
       <c r="C182" s="5" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
@@ -6153,10 +6153,10 @@
         <v>197</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
@@ -6184,10 +6184,10 @@
         <v>199</v>
       </c>
       <c r="C184" s="5" t="n">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
@@ -6215,10 +6215,10 @@
         <v>201</v>
       </c>
       <c r="C185" s="5" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
@@ -6246,10 +6246,10 @@
         <v>202</v>
       </c>
       <c r="C186" s="4" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
@@ -6276,11 +6276,11 @@
       <c r="B187" s="3" t="n">
         <v>204</v>
       </c>
-      <c r="C187" s="9" t="n">
-        <v>139</v>
+      <c r="C187" s="11" t="n">
+        <v>140</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
@@ -6307,11 +6307,11 @@
       <c r="B188" s="3" t="n">
         <v>205</v>
       </c>
-      <c r="C188" s="5" t="n">
-        <v>178</v>
+      <c r="C188" s="11" t="n">
+        <v>169</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
@@ -6339,11 +6339,9 @@
         <v>206</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>299</v>
-      </c>
-      <c r="D189" s="3" t="n">
-        <v>286</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="D189" s="3" t="inlineStr"/>
       <c r="E189" s="3" t="inlineStr">
         <is>
           <t>Antonio Williams</t>
@@ -6370,10 +6368,10 @@
         <v>207</v>
       </c>
       <c r="C190" s="4" t="n">
+        <v>281</v>
+      </c>
+      <c r="D190" s="3" t="n">
         <v>264</v>
-      </c>
-      <c r="D190" s="3" t="n">
-        <v>262</v>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
@@ -6400,11 +6398,11 @@
       <c r="B191" s="3" t="n">
         <v>211</v>
       </c>
-      <c r="C191" s="9" t="n">
+      <c r="C191" s="11" t="n">
         <v>168</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
@@ -6432,10 +6430,10 @@
         <v>212</v>
       </c>
       <c r="C192" s="4" t="n">
+        <v>251</v>
+      </c>
+      <c r="D192" s="3" t="n">
         <v>249</v>
-      </c>
-      <c r="D192" s="3" t="n">
-        <v>242</v>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
@@ -6463,10 +6461,10 @@
         <v>213</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
@@ -6494,10 +6492,10 @@
         <v>217</v>
       </c>
       <c r="C194" s="4" t="n">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D194" s="3" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
@@ -6516,7 +6514,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="11" t="inlineStr">
+      <c r="A195" s="10" t="inlineStr">
         <is>
           <t>QB28</t>
         </is>
@@ -6525,10 +6523,10 @@
         <v>219</v>
       </c>
       <c r="C195" s="5" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
@@ -6555,11 +6553,11 @@
       <c r="B196" s="3" t="n">
         <v>221</v>
       </c>
-      <c r="C196" s="4" t="n">
-        <v>294</v>
+      <c r="C196" s="5" t="n">
+        <v>248</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
@@ -6586,11 +6584,11 @@
       <c r="B197" s="3" t="n">
         <v>222</v>
       </c>
-      <c r="C197" s="5" t="n">
-        <v>250</v>
+      <c r="C197" s="4" t="n">
+        <v>273</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
@@ -6609,7 +6607,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="11" t="inlineStr">
+      <c r="A198" s="10" t="inlineStr">
         <is>
           <t>QB29</t>
         </is>
@@ -6621,7 +6619,7 @@
         <v>219</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
@@ -6649,7 +6647,7 @@
         <v>224</v>
       </c>
       <c r="C199" s="4" t="n">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="D199" s="3" t="inlineStr"/>
       <c r="E199" s="3" t="inlineStr">
@@ -6678,10 +6676,10 @@
         <v>225</v>
       </c>
       <c r="C200" s="7" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D200" s="3" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
@@ -6709,10 +6707,10 @@
         <v>228</v>
       </c>
       <c r="C201" s="5" t="n">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
@@ -6743,7 +6741,7 @@
         <v>247</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
@@ -6771,11 +6769,9 @@
         <v>232</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>302</v>
-      </c>
-      <c r="D203" s="3" t="n">
-        <v>299</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="D203" s="3" t="inlineStr"/>
       <c r="E203" s="3" t="inlineStr">
         <is>
           <t>Brandon Aiyuk</t>
@@ -6802,7 +6798,7 @@
         <v>233</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D204" s="3" t="inlineStr"/>
       <c r="E204" s="3" t="inlineStr">
@@ -6822,7 +6818,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="11" t="inlineStr">
+      <c r="A205" s="10" t="inlineStr">
         <is>
           <t>QB30</t>
         </is>
@@ -6831,10 +6827,10 @@
         <v>234</v>
       </c>
       <c r="C205" s="5" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
@@ -6862,10 +6858,10 @@
         <v>235</v>
       </c>
       <c r="C206" s="5" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
@@ -6892,11 +6888,11 @@
       <c r="B207" s="3" t="n">
         <v>237</v>
       </c>
-      <c r="C207" s="4" t="n">
-        <v>283</v>
+      <c r="C207" s="5" t="n">
+        <v>271</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
@@ -6924,10 +6920,10 @@
         <v>238</v>
       </c>
       <c r="C208" s="5" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
@@ -6955,10 +6951,10 @@
         <v>239</v>
       </c>
       <c r="C209" s="4" t="n">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
@@ -6986,10 +6982,10 @@
         <v>240</v>
       </c>
       <c r="C210" s="5" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
@@ -7020,7 +7016,7 @@
         <v>295</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
@@ -7048,10 +7044,10 @@
         <v>242</v>
       </c>
       <c r="C212" s="4" t="n">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="D212" s="3" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
@@ -7078,11 +7074,11 @@
       <c r="B213" s="3" t="n">
         <v>243</v>
       </c>
-      <c r="C213" s="9" t="n">
+      <c r="C213" s="11" t="n">
         <v>165</v>
       </c>
       <c r="D213" s="3" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
@@ -7110,10 +7106,10 @@
         <v>244</v>
       </c>
       <c r="C214" s="4" t="n">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D214" s="3" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
@@ -7140,11 +7136,11 @@
       <c r="B215" s="3" t="n">
         <v>245</v>
       </c>
-      <c r="C215" s="9" t="n">
-        <v>164</v>
+      <c r="C215" s="11" t="n">
+        <v>163</v>
       </c>
       <c r="D215" s="3" t="n">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
@@ -7171,11 +7167,11 @@
       <c r="B216" s="3" t="n">
         <v>246</v>
       </c>
-      <c r="C216" s="4" t="n">
-        <v>300</v>
+      <c r="C216" s="5" t="n">
+        <v>282</v>
       </c>
       <c r="D216" s="3" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
@@ -7203,10 +7199,10 @@
         <v>248</v>
       </c>
       <c r="C217" s="5" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D217" s="3" t="n">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
@@ -7234,10 +7230,10 @@
         <v>249</v>
       </c>
       <c r="C218" s="5" t="n">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D218" s="3" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
@@ -7265,7 +7261,7 @@
         <v>250</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="D219" s="3" t="inlineStr"/>
       <c r="E219" s="3" t="inlineStr">
@@ -7293,11 +7289,11 @@
       <c r="B220" s="3" t="n">
         <v>251</v>
       </c>
-      <c r="C220" s="5" t="n">
-        <v>204</v>
+      <c r="C220" s="11" t="n">
+        <v>186</v>
       </c>
       <c r="D220" s="3" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
@@ -7325,11 +7321,9 @@
         <v>252</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>272</v>
-      </c>
-      <c r="D221" s="3" t="n">
-        <v>287</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="D221" s="3" t="inlineStr"/>
       <c r="E221" s="3" t="inlineStr">
         <is>
           <t>Elijah Sarratt</t>
@@ -7359,7 +7353,7 @@
         <v>236</v>
       </c>
       <c r="D222" s="3" t="n">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
@@ -7386,8 +7380,8 @@
       <c r="B223" s="3" t="n">
         <v>255</v>
       </c>
-      <c r="C223" s="4" t="n">
-        <v>296</v>
+      <c r="C223" s="5" t="n">
+        <v>293</v>
       </c>
       <c r="D223" s="3" t="inlineStr"/>
       <c r="E223" s="3" t="inlineStr">
@@ -7415,11 +7409,11 @@
       <c r="B224" s="3" t="n">
         <v>256</v>
       </c>
-      <c r="C224" s="9" t="n">
+      <c r="C224" s="11" t="n">
         <v>185</v>
       </c>
       <c r="D224" s="3" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
@@ -7450,7 +7444,7 @@
         <v>275</v>
       </c>
       <c r="D225" s="3" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
@@ -7507,7 +7501,7 @@
         <v>259</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
@@ -7536,11 +7530,9 @@
         <v>260</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>282</v>
-      </c>
-      <c r="D228" s="3" t="n">
-        <v>292</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="D228" s="3" t="inlineStr"/>
       <c r="E228" s="3" t="inlineStr">
         <is>
           <t>Tory Horton</t>
@@ -7567,10 +7559,10 @@
         <v>261</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="D229" s="3" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
@@ -7598,10 +7590,10 @@
         <v>262</v>
       </c>
       <c r="C230" s="5" t="n">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="D230" s="3" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
@@ -7629,10 +7621,10 @@
         <v>264</v>
       </c>
       <c r="C231" s="5" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D231" s="3" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
@@ -7660,10 +7652,10 @@
         <v>265</v>
       </c>
       <c r="C232" s="5" t="n">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="D232" s="3" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
@@ -7682,7 +7674,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="11" t="inlineStr">
+      <c r="A233" s="10" t="inlineStr">
         <is>
           <t>QB31</t>
         </is>
@@ -7691,10 +7683,10 @@
         <v>266</v>
       </c>
       <c r="C233" s="5" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D233" s="3" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
@@ -7722,10 +7714,10 @@
         <v>267</v>
       </c>
       <c r="C234" s="5" t="n">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="D234" s="3" t="n">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
@@ -7782,10 +7774,10 @@
         <v>269</v>
       </c>
       <c r="C236" s="5" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D236" s="3" t="n">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
@@ -7813,10 +7805,10 @@
         <v>270</v>
       </c>
       <c r="C237" s="5" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D237" s="3" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
@@ -7844,7 +7836,7 @@
         <v>271</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D238" s="3" t="inlineStr"/>
       <c r="E238" s="3" t="inlineStr">
@@ -7873,10 +7865,10 @@
         <v>272</v>
       </c>
       <c r="C239" s="5" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D239" s="3" t="n">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
@@ -7904,7 +7896,7 @@
         <v>273</v>
       </c>
       <c r="C240" s="4" t="n">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="D240" s="3" t="inlineStr"/>
       <c r="E240" s="3" t="inlineStr">
@@ -7933,10 +7925,10 @@
         <v>274</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D241" s="3" t="n">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
@@ -7964,10 +7956,10 @@
         <v>275</v>
       </c>
       <c r="C242" s="5" t="n">
-        <v>273</v>
+        <v>227</v>
       </c>
       <c r="D242" s="3" t="n">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
@@ -7986,7 +7978,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="11" t="inlineStr">
+      <c r="A243" s="10" t="inlineStr">
         <is>
           <t>QB32</t>
         </is>
@@ -7995,10 +7987,10 @@
         <v>276</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D243" s="3" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
@@ -8026,10 +8018,10 @@
         <v>277</v>
       </c>
       <c r="C244" s="5" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D244" s="3" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
@@ -8056,11 +8048,11 @@
       <c r="B245" s="3" t="n">
         <v>278</v>
       </c>
-      <c r="C245" s="9" t="n">
-        <v>188</v>
+      <c r="C245" s="5" t="n">
+        <v>212</v>
       </c>
       <c r="D245" s="3" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
@@ -8088,7 +8080,7 @@
         <v>280</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>330</v>
+        <v>362</v>
       </c>
       <c r="D246" s="3" t="inlineStr"/>
       <c r="E246" s="3" t="inlineStr">
@@ -8116,8 +8108,8 @@
       <c r="B247" s="3" t="n">
         <v>281</v>
       </c>
-      <c r="C247" s="5" t="n">
-        <v>304</v>
+      <c r="C247" s="4" t="n">
+        <v>345</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
@@ -8149,7 +8141,7 @@
         <v>285</v>
       </c>
       <c r="D248" s="3" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
@@ -8177,10 +8169,10 @@
         <v>283</v>
       </c>
       <c r="C249" s="5" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D249" s="3" t="n">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
@@ -8208,9 +8200,11 @@
         <v>284</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>251</v>
-      </c>
-      <c r="D250" s="3" t="inlineStr"/>
+        <v>212</v>
+      </c>
+      <c r="D250" s="3" t="n">
+        <v>299</v>
+      </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
           <t>Malik Davis</t>
@@ -8237,10 +8231,10 @@
         <v>285</v>
       </c>
       <c r="C251" s="5" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D251" s="3" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
@@ -8267,8 +8261,8 @@
       <c r="B252" s="3" t="n">
         <v>288</v>
       </c>
-      <c r="C252" s="4" t="n">
-        <v>345</v>
+      <c r="C252" s="5" t="n">
+        <v>300</v>
       </c>
       <c r="D252" s="3" t="inlineStr"/>
       <c r="E252" s="3" t="inlineStr">
@@ -8288,7 +8282,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="11" t="inlineStr">
+      <c r="A253" s="10" t="inlineStr">
         <is>
           <t>QB33</t>
         </is>
@@ -8297,9 +8291,11 @@
         <v>289</v>
       </c>
       <c r="C253" s="5" t="n">
-        <v>311</v>
-      </c>
-      <c r="D253" s="3" t="inlineStr"/>
+        <v>245</v>
+      </c>
+      <c r="D253" s="3" t="n">
+        <v>256</v>
+      </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
           <t>Shedeur Sanders</t>
@@ -8326,10 +8322,10 @@
         <v>290</v>
       </c>
       <c r="C254" s="7" t="n">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="D254" s="3" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
@@ -8357,7 +8353,7 @@
         <v>292</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>299</v>
+        <v>324</v>
       </c>
       <c r="D255" s="3" t="inlineStr"/>
       <c r="E255" s="3" t="inlineStr">
@@ -8389,7 +8385,7 @@
         <v>226</v>
       </c>
       <c r="D256" s="3" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
@@ -8417,7 +8413,7 @@
         <v>294</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="D257" s="3" t="inlineStr"/>
       <c r="E257" s="3" t="inlineStr">
@@ -8446,7 +8442,7 @@
         <v>296</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>270</v>
+        <v>312</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
@@ -8475,7 +8471,7 @@
         <v>297</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
@@ -8504,10 +8500,10 @@
         <v>298</v>
       </c>
       <c r="C260" s="5" t="n">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="D260" s="3" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E260" s="3" t="inlineStr">
         <is>
@@ -8526,7 +8522,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="11" t="inlineStr">
+      <c r="A261" s="10" t="inlineStr">
         <is>
           <t>QB34</t>
         </is>
@@ -8535,10 +8531,10 @@
         <v>299</v>
       </c>
       <c r="C261" s="5" t="n">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="D261" s="3" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
@@ -8566,10 +8562,10 @@
         <v>300</v>
       </c>
       <c r="C262" s="5" t="n">
-        <v>265</v>
+        <v>330</v>
       </c>
       <c r="D262" s="3" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E262" s="3" t="inlineStr">
         <is>
@@ -8597,9 +8593,11 @@
         <v>301</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>294</v>
-      </c>
-      <c r="D263" s="3" t="inlineStr"/>
+        <v>299</v>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>300</v>
+      </c>
       <c r="E263" s="3" t="inlineStr">
         <is>
           <t>Kendre Miller</t>
@@ -8617,7 +8615,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="11" t="inlineStr">
+      <c r="A264" s="10" t="inlineStr">
         <is>
           <t>QB35</t>
         </is>
@@ -8626,10 +8624,10 @@
         <v>302</v>
       </c>
       <c r="C264" s="5" t="n">
+        <v>278</v>
+      </c>
+      <c r="D264" s="3" t="n">
         <v>262</v>
-      </c>
-      <c r="D264" s="3" t="n">
-        <v>260</v>
       </c>
       <c r="E264" s="3" t="inlineStr">
         <is>
@@ -8657,10 +8655,10 @@
         <v>304</v>
       </c>
       <c r="C265" s="5" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D265" s="3" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="E265" s="3" t="inlineStr">
         <is>
@@ -8688,7 +8686,7 @@
         <v>305</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>288</v>
+        <v>266</v>
       </c>
       <c r="D266" s="3" t="inlineStr"/>
       <c r="E266" s="3" t="inlineStr">
@@ -8717,10 +8715,10 @@
         <v>306</v>
       </c>
       <c r="C267" s="7" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D267" s="3" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="E267" s="3" t="inlineStr">
         <is>
@@ -8748,7 +8746,7 @@
         <v>309</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D268" s="3" t="inlineStr"/>
       <c r="E268" s="3" t="inlineStr">
@@ -8806,7 +8804,7 @@
         <v>311</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
@@ -8835,7 +8833,7 @@
         <v>312</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr">
@@ -8864,7 +8862,7 @@
         <v>314</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
@@ -8893,10 +8891,10 @@
         <v>316</v>
       </c>
       <c r="C273" s="5" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D273" s="3" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E273" s="3" t="inlineStr">
         <is>
@@ -8924,7 +8922,7 @@
         <v>317</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>292</v>
+        <v>338</v>
       </c>
       <c r="D274" s="3" t="inlineStr"/>
       <c r="E274" s="3" t="inlineStr">
@@ -8944,146 +8942,146 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="6" t="inlineStr">
-        <is>
-          <t>RB98</t>
+      <c r="A275" s="8" t="inlineStr">
+        <is>
+          <t>TE39</t>
         </is>
       </c>
       <c r="B275" s="3" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>329</v>
-      </c>
-      <c r="D275" s="3" t="inlineStr"/>
+        <v>283</v>
+      </c>
+      <c r="D275" s="3" t="n">
+        <v>282</v>
+      </c>
       <c r="E275" s="3" t="inlineStr">
         <is>
-          <t>Audric Estime</t>
+          <t>Darnell Washington</t>
         </is>
       </c>
       <c r="F275" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>PIT (9)</t>
         </is>
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="8" t="inlineStr">
-        <is>
-          <t>TE39</t>
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>WR112</t>
         </is>
       </c>
       <c r="B276" s="3" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C276" s="5" t="n">
-        <v>280</v>
-      </c>
-      <c r="D276" s="3" t="n">
-        <v>278</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="D276" s="3" t="inlineStr"/>
       <c r="E276" s="3" t="inlineStr">
         <is>
-          <t>Darnell Washington</t>
+          <t>Cedric Tillman</t>
         </is>
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
-          <t>PIT (9)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="inlineStr">
-        <is>
-          <t>WR112</t>
+      <c r="A277" s="6" t="inlineStr">
+        <is>
+          <t>RB100</t>
         </is>
       </c>
       <c r="B277" s="3" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>367</v>
+        <v>314</v>
       </c>
       <c r="D277" s="3" t="inlineStr"/>
       <c r="E277" s="3" t="inlineStr">
         <is>
-          <t>Cedric Tillman</t>
+          <t>Kareem Hunt</t>
         </is>
       </c>
       <c r="F277" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>FA ()</t>
         </is>
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="11" t="inlineStr">
-        <is>
-          <t>QB36</t>
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>WR114</t>
         </is>
       </c>
       <c r="B278" s="3" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C278" s="5" t="n">
-        <v>366</v>
-      </c>
-      <c r="D278" s="3" t="inlineStr"/>
+        <v>297</v>
+      </c>
+      <c r="D278" s="3" t="n">
+        <v>274</v>
+      </c>
       <c r="E278" s="3" t="inlineStr">
         <is>
-          <t>J.J. McCarthy</t>
+          <t>Luke McCaffrey</t>
         </is>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
-          <t>MIN (6)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>WR114</t>
+          <t>WR115</t>
         </is>
       </c>
       <c r="B279" s="3" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>298</v>
-      </c>
-      <c r="D279" s="3" t="n">
-        <v>271</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="D279" s="3" t="inlineStr"/>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>Luke McCaffrey</t>
+          <t>Tez Johnson</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>TB (10)</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -9095,24 +9093,26 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>WR115</t>
+          <t>WR116</t>
         </is>
       </c>
       <c r="B280" s="3" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>365</v>
-      </c>
-      <c r="D280" s="3" t="inlineStr"/>
+        <v>270</v>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>241</v>
+      </c>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Tez Johnson</t>
+          <t>Jahan Dotson</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>TB (10)</t>
+          <t>ATL (11)</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -9124,26 +9124,24 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>WR116</t>
+          <t>WR117</t>
         </is>
       </c>
       <c r="B281" s="3" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C281" s="5" t="n">
-        <v>266</v>
-      </c>
-      <c r="D281" s="3" t="n">
-        <v>233</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="D281" s="3" t="inlineStr"/>
       <c r="E281" s="3" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>Jalen Royals</t>
         </is>
       </c>
       <c r="F281" s="3" t="inlineStr">
         <is>
-          <t>ATL (11)</t>
+          <t>KC (5)</t>
         </is>
       </c>
       <c r="G281" s="3" t="inlineStr">
@@ -9153,81 +9151,81 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="inlineStr">
-        <is>
-          <t>WR117</t>
+      <c r="A282" s="8" t="inlineStr">
+        <is>
+          <t>TE40</t>
         </is>
       </c>
       <c r="B282" s="3" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C282" s="5" t="n">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="D282" s="3" t="inlineStr"/>
       <c r="E282" s="3" t="inlineStr">
         <is>
-          <t>Jalen Royals</t>
+          <t>Max Klare</t>
         </is>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>KC (5)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="8" t="inlineStr">
-        <is>
-          <t>TE40</t>
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>WR118</t>
         </is>
       </c>
       <c r="B283" s="3" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C283" s="5" t="n">
-        <v>372</v>
-      </c>
-      <c r="D283" s="3" t="inlineStr"/>
+        <v>205</v>
+      </c>
+      <c r="D283" s="3" t="n">
+        <v>216</v>
+      </c>
       <c r="E283" s="3" t="inlineStr">
         <is>
-          <t>Max Klare</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="F283" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>MIA (6)</t>
         </is>
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>WR118</t>
+          <t>WR120</t>
         </is>
       </c>
       <c r="B284" s="3" t="n">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>206</v>
-      </c>
-      <c r="D284" s="3" t="n">
-        <v>214</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="D284" s="3" t="inlineStr"/>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Caleb Douglas</t>
+          <t>Jalen Tolbert</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
@@ -9244,26 +9242,24 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>WR119</t>
+          <t>WR122</t>
         </is>
       </c>
       <c r="B285" s="3" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>297</v>
-      </c>
-      <c r="D285" s="3" t="n">
-        <v>270</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="D285" s="3" t="inlineStr"/>
       <c r="E285" s="3" t="inlineStr">
         <is>
-          <t>Calvin Austin</t>
+          <t>Joshua Palmer</t>
         </is>
       </c>
       <c r="F285" s="3" t="inlineStr">
         <is>
-          <t>NYG (8)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G285" s="3" t="inlineStr">
@@ -9273,86 +9269,86 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="inlineStr">
-        <is>
-          <t>WR120</t>
+      <c r="A286" s="8" t="inlineStr">
+        <is>
+          <t>TE41</t>
         </is>
       </c>
       <c r="B286" s="3" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>355</v>
+        <v>282</v>
       </c>
       <c r="D286" s="3" t="n">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="E286" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Michael Mayer</t>
         </is>
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>MIA (6)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="inlineStr">
-        <is>
-          <t>WR122</t>
+      <c r="A287" s="8" t="inlineStr">
+        <is>
+          <t>TE42</t>
         </is>
       </c>
       <c r="B287" s="3" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="D287" s="3" t="inlineStr"/>
       <c r="E287" s="3" t="inlineStr">
         <is>
-          <t>Joshua Palmer</t>
+          <t>Elijah Arroyo</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="8" t="inlineStr">
         <is>
-          <t>TE41</t>
+          <t>TE43</t>
         </is>
       </c>
       <c r="B288" s="3" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>322</v>
+        <v>373</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Michael Mayer</t>
+          <t>Tyler Higbee</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>LV (13)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -9362,55 +9358,55 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="8" t="inlineStr">
-        <is>
-          <t>TE42</t>
+      <c r="A289" s="10" t="inlineStr">
+        <is>
+          <t>QB37</t>
         </is>
       </c>
       <c r="B289" s="3" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>334</v>
+        <v>376</v>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>Elijah Arroyo</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="8" t="inlineStr">
         <is>
-          <t>TE43</t>
+          <t>TE45</t>
         </is>
       </c>
       <c r="B290" s="3" t="n">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C290" s="5" t="n">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="D290" s="3" t="inlineStr"/>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Tyler Higbee</t>
+          <t>Dawson Knox</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
@@ -9420,26 +9416,26 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="11" t="inlineStr">
-        <is>
-          <t>QB37</t>
+      <c r="A291" s="10" t="inlineStr">
+        <is>
+          <t>QB38</t>
         </is>
       </c>
       <c r="B291" s="3" t="n">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>376</v>
+        <v>340</v>
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Carson Beck</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>ARI (14)</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
@@ -9451,24 +9447,24 @@
     <row r="292">
       <c r="A292" s="8" t="inlineStr">
         <is>
-          <t>TE45</t>
+          <t>TE47</t>
         </is>
       </c>
       <c r="B292" s="3" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>Dawson Knox</t>
+          <t>Cole Kmet</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>CHI (10)</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
@@ -9478,84 +9474,84 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="11" t="inlineStr">
-        <is>
-          <t>QB38</t>
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>WR124</t>
         </is>
       </c>
       <c r="B293" s="3" t="n">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr">
         <is>
-          <t>Carson Beck</t>
+          <t>Brenen Thompson</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>ARI (14)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="8" t="inlineStr">
-        <is>
-          <t>TE47</t>
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>WR125</t>
         </is>
       </c>
       <c r="B294" s="3" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>369</v>
+        <v>299</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>Cole Kmet</t>
+          <t>DeMario Douglas</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>CHI (10)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>WR124</t>
+          <t>WR126</t>
         </is>
       </c>
       <c r="B295" s="3" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>351</v>
+        <v>321</v>
       </c>
       <c r="D295" s="3" t="inlineStr"/>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>Brenen Thompson</t>
+          <t>Bryce Lance</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>NO (8)</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -9567,24 +9563,26 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>WR125</t>
+          <t>WR128</t>
         </is>
       </c>
       <c r="B296" s="3" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>305</v>
-      </c>
-      <c r="D296" s="3" t="inlineStr"/>
+        <v>287</v>
+      </c>
+      <c r="D296" s="3" t="n">
+        <v>273</v>
+      </c>
       <c r="E296" s="3" t="inlineStr">
         <is>
-          <t>DeMario Douglas</t>
+          <t>Xavier Hutchinson</t>
         </is>
       </c>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>HOU (8)</t>
         </is>
       </c>
       <c r="G296" s="3" t="inlineStr">
@@ -9594,55 +9592,57 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="inlineStr">
-        <is>
-          <t>WR126</t>
+      <c r="A297" s="6" t="inlineStr">
+        <is>
+          <t>RB104</t>
         </is>
       </c>
       <c r="B297" s="3" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="C297" s="5" t="n">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="D297" s="3" t="inlineStr"/>
       <c r="E297" s="3" t="inlineStr">
         <is>
-          <t>Bryce Lance</t>
+          <t>Jawhar Jordan</t>
         </is>
       </c>
       <c r="F297" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>HOU (8)</t>
         </is>
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>WR128</t>
+          <t>WR130</t>
         </is>
       </c>
       <c r="B298" s="3" t="n">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>287</v>
-      </c>
-      <c r="D298" s="3" t="inlineStr"/>
+        <v>249</v>
+      </c>
+      <c r="D298" s="3" t="n">
+        <v>229</v>
+      </c>
       <c r="E298" s="3" t="inlineStr">
         <is>
-          <t>Xavier Hutchinson</t>
+          <t>Treylon Burks</t>
         </is>
       </c>
       <c r="F298" s="3" t="inlineStr">
         <is>
-          <t>HOU (8)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G298" s="3" t="inlineStr">
@@ -9652,57 +9652,55 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="6" t="inlineStr">
-        <is>
-          <t>RB104</t>
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>WR132</t>
         </is>
       </c>
       <c r="B299" s="3" t="n">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>348</v>
+        <v>374</v>
       </c>
       <c r="D299" s="3" t="inlineStr"/>
       <c r="E299" s="3" t="inlineStr">
         <is>
-          <t>Jawhar Jordan</t>
+          <t>Nick Westbrook-Ikhine</t>
         </is>
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>HOU (8)</t>
+          <t>IND (13)</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>WR130</t>
+          <t>WR133</t>
         </is>
       </c>
       <c r="B300" s="3" t="n">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C300" s="5" t="n">
-        <v>267</v>
-      </c>
-      <c r="D300" s="3" t="n">
-        <v>223</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="D300" s="3" t="inlineStr"/>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>Treylon Burks</t>
+          <t>Savion Williams</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>WAS (7)</t>
+          <t>GB (11)</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -9712,205 +9710,147 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="inlineStr">
-        <is>
-          <t>WR132</t>
+      <c r="A301" s="6" t="inlineStr">
+        <is>
+          <t>RB107</t>
         </is>
       </c>
       <c r="B301" s="3" t="n">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="C301" s="5" t="n">
-        <v>374</v>
+        <v>347</v>
       </c>
       <c r="D301" s="3" t="inlineStr"/>
       <c r="E301" s="3" t="inlineStr">
         <is>
-          <t>Nick Westbrook-Ikhine</t>
+          <t>Raheim Sanders</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>IND (13)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="inlineStr">
-        <is>
-          <t>WR133</t>
+      <c r="A302" s="8" t="inlineStr">
+        <is>
+          <t>TE50</t>
         </is>
       </c>
       <c r="B302" s="3" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>356</v>
+        <v>302</v>
       </c>
       <c r="D302" s="3" t="inlineStr"/>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>Savion Williams</t>
+          <t>Eli Raridon</t>
         </is>
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
-          <t>GB (11)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="6" t="inlineStr">
-        <is>
-          <t>RB107</t>
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>WR138</t>
         </is>
       </c>
       <c r="B303" s="3" t="n">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="D303" s="3" t="inlineStr"/>
       <c r="E303" s="3" t="inlineStr">
         <is>
-          <t>Raheim Sanders</t>
+          <t>Zavion Thomas</t>
         </is>
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>CHI (10)</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="8" t="inlineStr">
-        <is>
-          <t>TE50</t>
+      <c r="A304" s="6" t="inlineStr">
+        <is>
+          <t>RB109</t>
         </is>
       </c>
       <c r="B304" s="3" t="n">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="C304" s="5" t="n">
-        <v>303</v>
+        <v>352</v>
       </c>
       <c r="D304" s="3" t="inlineStr"/>
       <c r="E304" s="3" t="inlineStr">
         <is>
-          <t>Eli Raridon</t>
+          <t>Phil Mafah</t>
         </is>
       </c>
       <c r="F304" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>DAL (14)</t>
         </is>
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="inlineStr">
-        <is>
-          <t>WR138</t>
+      <c r="A305" s="8" t="inlineStr">
+        <is>
+          <t>TE52</t>
         </is>
       </c>
       <c r="B305" s="3" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C305" s="5" t="n">
-        <v>358</v>
-      </c>
-      <c r="D305" s="3" t="inlineStr"/>
+        <v>267</v>
+      </c>
+      <c r="D305" s="3" t="n">
+        <v>267</v>
+      </c>
       <c r="E305" s="3" t="inlineStr">
         <is>
-          <t>Zavion Thomas</t>
+          <t>Erick All</t>
         </is>
       </c>
       <c r="F305" s="3" t="inlineStr">
         <is>
-          <t>CHI (10)</t>
+          <t>CIN (6)</t>
         </is>
       </c>
       <c r="G305" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" s="6" t="inlineStr">
-        <is>
-          <t>RB109</t>
-        </is>
-      </c>
-      <c r="B306" s="3" t="n">
-        <v>386</v>
-      </c>
-      <c r="C306" s="5" t="n">
-        <v>349</v>
-      </c>
-      <c r="D306" s="3" t="inlineStr"/>
-      <c r="E306" s="3" t="inlineStr">
-        <is>
-          <t>Phil Mafah</t>
-        </is>
-      </c>
-      <c r="F306" s="3" t="inlineStr">
-        <is>
-          <t>DAL (14)</t>
-        </is>
-      </c>
-      <c r="G306" s="3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="8" t="inlineStr">
-        <is>
-          <t>TE52</t>
-        </is>
-      </c>
-      <c r="B307" s="3" t="n">
-        <v>387</v>
-      </c>
-      <c r="C307" s="5" t="n">
-        <v>281</v>
-      </c>
-      <c r="D307" s="3" t="n">
-        <v>279</v>
-      </c>
-      <c r="E307" s="3" t="inlineStr">
-        <is>
-          <t>Erick All</t>
-        </is>
-      </c>
-      <c r="F307" s="3" t="inlineStr">
-        <is>
-          <t>CIN (6)</t>
-        </is>
-      </c>
-      <c r="G307" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G305"/>
+  <dimension ref="A1:G306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6153,7 +6153,7 @@
         <v>197</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D183" s="3" t="n">
         <v>280</v>
@@ -6461,7 +6461,7 @@
         <v>213</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D193" s="3" t="n">
         <v>290</v>
@@ -6769,7 +6769,7 @@
         <v>232</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D203" s="3" t="inlineStr"/>
       <c r="E203" s="3" t="inlineStr">
@@ -6798,7 +6798,7 @@
         <v>233</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D204" s="3" t="inlineStr"/>
       <c r="E204" s="3" t="inlineStr">
@@ -7167,8 +7167,8 @@
       <c r="B216" s="3" t="n">
         <v>246</v>
       </c>
-      <c r="C216" s="5" t="n">
-        <v>282</v>
+      <c r="C216" s="4" t="n">
+        <v>283</v>
       </c>
       <c r="D216" s="3" t="n">
         <v>294</v>
@@ -7472,7 +7472,7 @@
         <v>258</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D226" s="3" t="inlineStr"/>
       <c r="E226" s="3" t="inlineStr">
@@ -7501,7 +7501,7 @@
         <v>259</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
@@ -7530,7 +7530,7 @@
         <v>260</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D228" s="3" t="inlineStr"/>
       <c r="E228" s="3" t="inlineStr">
@@ -7652,7 +7652,7 @@
         <v>265</v>
       </c>
       <c r="C232" s="5" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D232" s="3" t="n">
         <v>291</v>
@@ -7745,7 +7745,7 @@
         <v>268</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D235" s="3" t="inlineStr"/>
       <c r="E235" s="3" t="inlineStr">
@@ -7895,8 +7895,8 @@
       <c r="B240" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="C240" s="4" t="n">
-        <v>339</v>
+      <c r="C240" s="5" t="n">
+        <v>307</v>
       </c>
       <c r="D240" s="3" t="inlineStr"/>
       <c r="E240" s="3" t="inlineStr">
@@ -7925,7 +7925,7 @@
         <v>274</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D241" s="3" t="n">
         <v>293</v>
@@ -8080,7 +8080,7 @@
         <v>280</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D246" s="3" t="inlineStr"/>
       <c r="E246" s="3" t="inlineStr">
@@ -8109,7 +8109,7 @@
         <v>281</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
@@ -8200,7 +8200,7 @@
         <v>284</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D250" s="3" t="n">
         <v>299</v>
@@ -8353,7 +8353,7 @@
         <v>292</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D255" s="3" t="inlineStr"/>
       <c r="E255" s="3" t="inlineStr">
@@ -8413,7 +8413,7 @@
         <v>294</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D257" s="3" t="inlineStr"/>
       <c r="E257" s="3" t="inlineStr">
@@ -8442,7 +8442,7 @@
         <v>296</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
@@ -8471,7 +8471,7 @@
         <v>297</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
@@ -8562,7 +8562,7 @@
         <v>300</v>
       </c>
       <c r="C262" s="5" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D262" s="3" t="n">
         <v>269</v>
@@ -8593,7 +8593,7 @@
         <v>301</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D263" s="3" t="n">
         <v>300</v>
@@ -8746,7 +8746,7 @@
         <v>309</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D268" s="3" t="inlineStr"/>
       <c r="E268" s="3" t="inlineStr">
@@ -8775,7 +8775,7 @@
         <v>310</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D269" s="3" t="inlineStr"/>
       <c r="E269" s="3" t="inlineStr">
@@ -8804,7 +8804,7 @@
         <v>311</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
@@ -8862,7 +8862,7 @@
         <v>314</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
@@ -8922,7 +8922,7 @@
         <v>317</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="D274" s="3" t="inlineStr"/>
       <c r="E274" s="3" t="inlineStr">
@@ -8942,146 +8942,146 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="8" t="inlineStr">
+      <c r="A275" s="6" t="inlineStr">
+        <is>
+          <t>RB98</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="n">
+        <v>321</v>
+      </c>
+      <c r="C275" s="5" t="n">
+        <v>366</v>
+      </c>
+      <c r="D275" s="3" t="inlineStr"/>
+      <c r="E275" s="3" t="inlineStr">
+        <is>
+          <t>Audric Estime</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="G275" s="3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="8" t="inlineStr">
         <is>
           <t>TE39</t>
         </is>
       </c>
-      <c r="B275" s="3" t="n">
+      <c r="B276" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="C275" s="5" t="n">
+      <c r="C276" s="5" t="n">
         <v>283</v>
       </c>
-      <c r="D275" s="3" t="n">
+      <c r="D276" s="3" t="n">
         <v>282</v>
       </c>
-      <c r="E275" s="3" t="inlineStr">
+      <c r="E276" s="3" t="inlineStr">
         <is>
           <t>Darnell Washington</t>
         </is>
       </c>
-      <c r="F275" s="3" t="inlineStr">
+      <c r="F276" s="3" t="inlineStr">
         <is>
           <t>PIT (9)</t>
         </is>
       </c>
-      <c r="G275" s="3" t="inlineStr">
+      <c r="G276" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
         <is>
           <t>WR112</t>
         </is>
       </c>
-      <c r="B276" s="3" t="n">
+      <c r="B277" s="3" t="n">
         <v>324</v>
       </c>
-      <c r="C276" s="5" t="n">
-        <v>366</v>
-      </c>
-      <c r="D276" s="3" t="inlineStr"/>
-      <c r="E276" s="3" t="inlineStr">
-        <is>
-          <t>Cedric Tillman</t>
-        </is>
-      </c>
-      <c r="F276" s="3" t="inlineStr">
-        <is>
-          <t>CLE (11)</t>
-        </is>
-      </c>
-      <c r="G276" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="6" t="inlineStr">
-        <is>
-          <t>RB100</t>
-        </is>
-      </c>
-      <c r="B277" s="3" t="n">
-        <v>326</v>
-      </c>
       <c r="C277" s="5" t="n">
-        <v>314</v>
+        <v>372</v>
       </c>
       <c r="D277" s="3" t="inlineStr"/>
       <c r="E277" s="3" t="inlineStr">
         <is>
+          <t>Cedric Tillman</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="inlineStr">
+        <is>
+          <t>CLE (11)</t>
+        </is>
+      </c>
+      <c r="G277" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="6" t="inlineStr">
+        <is>
+          <t>RB100</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="n">
+        <v>326</v>
+      </c>
+      <c r="C278" s="5" t="n">
+        <v>314</v>
+      </c>
+      <c r="D278" s="3" t="inlineStr"/>
+      <c r="E278" s="3" t="inlineStr">
+        <is>
           <t>Kareem Hunt</t>
         </is>
       </c>
-      <c r="F277" s="3" t="inlineStr">
+      <c r="F278" s="3" t="inlineStr">
         <is>
           <t>FA ()</t>
         </is>
       </c>
-      <c r="G277" s="3" t="inlineStr">
+      <c r="G278" s="3" t="inlineStr">
         <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="2" t="inlineStr">
-        <is>
-          <t>WR114</t>
-        </is>
-      </c>
-      <c r="B278" s="3" t="n">
-        <v>328</v>
-      </c>
-      <c r="C278" s="5" t="n">
-        <v>297</v>
-      </c>
-      <c r="D278" s="3" t="n">
-        <v>274</v>
-      </c>
-      <c r="E278" s="3" t="inlineStr">
-        <is>
-          <t>Luke McCaffrey</t>
-        </is>
-      </c>
-      <c r="F278" s="3" t="inlineStr">
-        <is>
-          <t>WAS (7)</t>
-        </is>
-      </c>
-      <c r="G278" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>WR115</t>
+          <t>WR114</t>
         </is>
       </c>
       <c r="B279" s="3" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C279" s="5" t="n">
-        <v>368</v>
-      </c>
-      <c r="D279" s="3" t="inlineStr"/>
+        <v>297</v>
+      </c>
+      <c r="D279" s="3" t="n">
+        <v>274</v>
+      </c>
       <c r="E279" s="3" t="inlineStr">
         <is>
-          <t>Tez Johnson</t>
+          <t>Luke McCaffrey</t>
         </is>
       </c>
       <c r="F279" s="3" t="inlineStr">
         <is>
-          <t>TB (10)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G279" s="3" t="inlineStr">
@@ -9093,26 +9093,24 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>WR116</t>
+          <t>WR115</t>
         </is>
       </c>
       <c r="B280" s="3" t="n">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>270</v>
-      </c>
-      <c r="D280" s="3" t="n">
-        <v>241</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="D280" s="3" t="inlineStr"/>
       <c r="E280" s="3" t="inlineStr">
         <is>
-          <t>Jahan Dotson</t>
+          <t>Tez Johnson</t>
         </is>
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>ATL (11)</t>
+          <t>TB (10)</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -9124,108 +9122,110 @@
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
+          <t>WR116</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="C281" s="5" t="n">
+        <v>270</v>
+      </c>
+      <c r="D281" s="3" t="n">
+        <v>241</v>
+      </c>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>Jahan Dotson</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>ATL (11)</t>
+        </is>
+      </c>
+      <c r="G281" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
           <t>WR117</t>
         </is>
       </c>
-      <c r="B281" s="3" t="n">
+      <c r="B282" s="3" t="n">
         <v>331</v>
       </c>
-      <c r="C281" s="5" t="n">
+      <c r="C282" s="5" t="n">
         <v>341</v>
-      </c>
-      <c r="D281" s="3" t="inlineStr"/>
-      <c r="E281" s="3" t="inlineStr">
-        <is>
-          <t>Jalen Royals</t>
-        </is>
-      </c>
-      <c r="F281" s="3" t="inlineStr">
-        <is>
-          <t>KC (5)</t>
-        </is>
-      </c>
-      <c r="G281" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="8" t="inlineStr">
-        <is>
-          <t>TE40</t>
-        </is>
-      </c>
-      <c r="B282" s="3" t="n">
-        <v>332</v>
-      </c>
-      <c r="C282" s="5" t="n">
-        <v>378</v>
       </c>
       <c r="D282" s="3" t="inlineStr"/>
       <c r="E282" s="3" t="inlineStr">
         <is>
+          <t>Jalen Royals</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="inlineStr">
+        <is>
+          <t>KC (5)</t>
+        </is>
+      </c>
+      <c r="G282" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="8" t="inlineStr">
+        <is>
+          <t>TE40</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="n">
+        <v>332</v>
+      </c>
+      <c r="C283" s="5" t="n">
+        <v>379</v>
+      </c>
+      <c r="D283" s="3" t="inlineStr"/>
+      <c r="E283" s="3" t="inlineStr">
+        <is>
           <t>Max Klare</t>
         </is>
       </c>
-      <c r="F282" s="3" t="inlineStr">
+      <c r="F283" s="3" t="inlineStr">
         <is>
           <t>LAR (11)</t>
         </is>
       </c>
-      <c r="G282" s="3" t="inlineStr">
+      <c r="G283" s="3" t="inlineStr">
         <is>
           <t>TE</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="2" t="inlineStr">
-        <is>
-          <t>WR118</t>
-        </is>
-      </c>
-      <c r="B283" s="3" t="n">
-        <v>333</v>
-      </c>
-      <c r="C283" s="5" t="n">
-        <v>205</v>
-      </c>
-      <c r="D283" s="3" t="n">
-        <v>216</v>
-      </c>
-      <c r="E283" s="3" t="inlineStr">
-        <is>
-          <t>Caleb Douglas</t>
-        </is>
-      </c>
-      <c r="F283" s="3" t="inlineStr">
-        <is>
-          <t>MIA (6)</t>
-        </is>
-      </c>
-      <c r="G283" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>WR120</t>
+          <t>WR118</t>
         </is>
       </c>
       <c r="B284" s="3" t="n">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C284" s="5" t="n">
-        <v>358</v>
-      </c>
-      <c r="D284" s="3" t="inlineStr"/>
+        <v>205</v>
+      </c>
+      <c r="D284" s="3" t="n">
+        <v>216</v>
+      </c>
       <c r="E284" s="3" t="inlineStr">
         <is>
-          <t>Jalen Tolbert</t>
+          <t>Caleb Douglas</t>
         </is>
       </c>
       <c r="F284" s="3" t="inlineStr">
@@ -9242,84 +9242,84 @@
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>WR122</t>
+          <t>WR120</t>
         </is>
       </c>
       <c r="B285" s="3" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>323</v>
+        <v>358</v>
       </c>
       <c r="D285" s="3" t="inlineStr"/>
       <c r="E285" s="3" t="inlineStr">
         <is>
+          <t>Jalen Tolbert</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="inlineStr">
+        <is>
+          <t>MIA (6)</t>
+        </is>
+      </c>
+      <c r="G285" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>WR122</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="n">
+        <v>337</v>
+      </c>
+      <c r="C286" s="5" t="n">
+        <v>324</v>
+      </c>
+      <c r="D286" s="3" t="inlineStr"/>
+      <c r="E286" s="3" t="inlineStr">
+        <is>
           <t>Joshua Palmer</t>
         </is>
       </c>
-      <c r="F285" s="3" t="inlineStr">
+      <c r="F286" s="3" t="inlineStr">
         <is>
           <t>BUF (7)</t>
         </is>
       </c>
-      <c r="G285" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="8" t="inlineStr">
-        <is>
-          <t>TE41</t>
-        </is>
-      </c>
-      <c r="B286" s="3" t="n">
-        <v>338</v>
-      </c>
-      <c r="C286" s="5" t="n">
-        <v>282</v>
-      </c>
-      <c r="D286" s="3" t="n">
-        <v>281</v>
-      </c>
-      <c r="E286" s="3" t="inlineStr">
-        <is>
-          <t>Michael Mayer</t>
-        </is>
-      </c>
-      <c r="F286" s="3" t="inlineStr">
-        <is>
-          <t>LV (13)</t>
-        </is>
-      </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="8" t="inlineStr">
         <is>
-          <t>TE42</t>
+          <t>TE41</t>
         </is>
       </c>
       <c r="B287" s="3" t="n">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C287" s="5" t="n">
-        <v>318</v>
-      </c>
-      <c r="D287" s="3" t="inlineStr"/>
+        <v>282</v>
+      </c>
+      <c r="D287" s="3" t="n">
+        <v>281</v>
+      </c>
       <c r="E287" s="3" t="inlineStr">
         <is>
-          <t>Elijah Arroyo</t>
+          <t>Michael Mayer</t>
         </is>
       </c>
       <c r="F287" s="3" t="inlineStr">
         <is>
-          <t>SEA (11)</t>
+          <t>LV (13)</t>
         </is>
       </c>
       <c r="G287" s="3" t="inlineStr">
@@ -9331,24 +9331,24 @@
     <row r="288">
       <c r="A288" s="8" t="inlineStr">
         <is>
-          <t>TE43</t>
+          <t>TE42</t>
         </is>
       </c>
       <c r="B288" s="3" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>373</v>
+        <v>319</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
         <is>
-          <t>Tyler Higbee</t>
+          <t>Elijah Arroyo</t>
         </is>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
-          <t>LAR (11)</t>
+          <t>SEA (11)</t>
         </is>
       </c>
       <c r="G288" s="3" t="inlineStr">
@@ -9358,42 +9358,42 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="10" t="inlineStr">
-        <is>
-          <t>QB37</t>
+      <c r="A289" s="8" t="inlineStr">
+        <is>
+          <t>TE43</t>
         </is>
       </c>
       <c r="B289" s="3" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr">
         <is>
-          <t>Mac Jones</t>
+          <t>Tyler Higbee</t>
         </is>
       </c>
       <c r="F289" s="3" t="inlineStr">
         <is>
-          <t>SF (8)</t>
+          <t>LAR (11)</t>
         </is>
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="8" t="inlineStr">
-        <is>
-          <t>TE45</t>
+      <c r="A290" s="10" t="inlineStr">
+        <is>
+          <t>QB37</t>
         </is>
       </c>
       <c r="B290" s="3" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C290" s="5" t="n">
         <v>377</v>
@@ -9401,128 +9401,128 @@
       <c r="D290" s="3" t="inlineStr"/>
       <c r="E290" s="3" t="inlineStr">
         <is>
-          <t>Dawson Knox</t>
+          <t>Mac Jones</t>
         </is>
       </c>
       <c r="F290" s="3" t="inlineStr">
         <is>
-          <t>BUF (7)</t>
+          <t>SF (8)</t>
         </is>
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="10" t="inlineStr">
-        <is>
-          <t>QB38</t>
+      <c r="A291" s="8" t="inlineStr">
+        <is>
+          <t>TE45</t>
         </is>
       </c>
       <c r="B291" s="3" t="n">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C291" s="5" t="n">
-        <v>340</v>
+        <v>378</v>
       </c>
       <c r="D291" s="3" t="inlineStr"/>
       <c r="E291" s="3" t="inlineStr">
         <is>
-          <t>Carson Beck</t>
+          <t>Dawson Knox</t>
         </is>
       </c>
       <c r="F291" s="3" t="inlineStr">
         <is>
-          <t>ARI (14)</t>
+          <t>BUF (7)</t>
         </is>
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>QB</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="8" t="inlineStr">
-        <is>
-          <t>TE47</t>
+      <c r="A292" s="10" t="inlineStr">
+        <is>
+          <t>QB38</t>
         </is>
       </c>
       <c r="B292" s="3" t="n">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
         <is>
-          <t>Cole Kmet</t>
+          <t>Carson Beck</t>
         </is>
       </c>
       <c r="F292" s="3" t="inlineStr">
         <is>
-          <t>CHI (10)</t>
+          <t>ARI (14)</t>
         </is>
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>QB</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="inlineStr">
-        <is>
-          <t>WR124</t>
+      <c r="A293" s="8" t="inlineStr">
+        <is>
+          <t>TE47</t>
         </is>
       </c>
       <c r="B293" s="3" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr">
         <is>
-          <t>Brenen Thompson</t>
+          <t>Cole Kmet</t>
         </is>
       </c>
       <c r="F293" s="3" t="inlineStr">
         <is>
-          <t>LAC (7)</t>
+          <t>CHI (10)</t>
         </is>
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>WR125</t>
+          <t>WR124</t>
         </is>
       </c>
       <c r="B294" s="3" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>299</v>
+        <v>354</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
         <is>
-          <t>DeMario Douglas</t>
+          <t>Brenen Thompson</t>
         </is>
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>LAC (7)</t>
         </is>
       </c>
       <c r="G294" s="3" t="inlineStr">
@@ -9534,24 +9534,24 @@
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>WR126</t>
+          <t>WR125</t>
         </is>
       </c>
       <c r="B295" s="3" t="n">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C295" s="5" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="D295" s="3" t="inlineStr"/>
       <c r="E295" s="3" t="inlineStr">
         <is>
-          <t>Bryce Lance</t>
+          <t>DeMario Douglas</t>
         </is>
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>NO (8)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -9563,115 +9563,115 @@
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
+          <t>WR126</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="n">
+        <v>355</v>
+      </c>
+      <c r="C296" s="5" t="n">
+        <v>322</v>
+      </c>
+      <c r="D296" s="3" t="inlineStr"/>
+      <c r="E296" s="3" t="inlineStr">
+        <is>
+          <t>Bryce Lance</t>
+        </is>
+      </c>
+      <c r="F296" s="3" t="inlineStr">
+        <is>
+          <t>NO (8)</t>
+        </is>
+      </c>
+      <c r="G296" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
           <t>WR128</t>
         </is>
       </c>
-      <c r="B296" s="3" t="n">
+      <c r="B297" s="3" t="n">
         <v>358</v>
       </c>
-      <c r="C296" s="5" t="n">
+      <c r="C297" s="5" t="n">
         <v>287</v>
       </c>
-      <c r="D296" s="3" t="n">
+      <c r="D297" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="E296" s="3" t="inlineStr">
+      <c r="E297" s="3" t="inlineStr">
         <is>
           <t>Xavier Hutchinson</t>
         </is>
       </c>
-      <c r="F296" s="3" t="inlineStr">
+      <c r="F297" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="G296" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
-        </is>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="6" t="inlineStr">
+      <c r="G297" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="6" t="inlineStr">
         <is>
           <t>RB104</t>
         </is>
       </c>
-      <c r="B297" s="3" t="n">
+      <c r="B298" s="3" t="n">
         <v>360</v>
       </c>
-      <c r="C297" s="5" t="n">
-        <v>350</v>
-      </c>
-      <c r="D297" s="3" t="inlineStr"/>
-      <c r="E297" s="3" t="inlineStr">
+      <c r="C298" s="5" t="n">
+        <v>349</v>
+      </c>
+      <c r="D298" s="3" t="inlineStr"/>
+      <c r="E298" s="3" t="inlineStr">
         <is>
           <t>Jawhar Jordan</t>
         </is>
       </c>
-      <c r="F297" s="3" t="inlineStr">
+      <c r="F298" s="3" t="inlineStr">
         <is>
           <t>HOU (8)</t>
         </is>
       </c>
-      <c r="G297" s="3" t="inlineStr">
+      <c r="G298" s="3" t="inlineStr">
         <is>
           <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="2" t="inlineStr">
-        <is>
-          <t>WR130</t>
-        </is>
-      </c>
-      <c r="B298" s="3" t="n">
-        <v>363</v>
-      </c>
-      <c r="C298" s="5" t="n">
-        <v>249</v>
-      </c>
-      <c r="D298" s="3" t="n">
-        <v>229</v>
-      </c>
-      <c r="E298" s="3" t="inlineStr">
-        <is>
-          <t>Treylon Burks</t>
-        </is>
-      </c>
-      <c r="F298" s="3" t="inlineStr">
-        <is>
-          <t>WAS (7)</t>
-        </is>
-      </c>
-      <c r="G298" s="3" t="inlineStr">
-        <is>
-          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>WR132</t>
+          <t>WR130</t>
         </is>
       </c>
       <c r="B299" s="3" t="n">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C299" s="5" t="n">
-        <v>374</v>
-      </c>
-      <c r="D299" s="3" t="inlineStr"/>
+        <v>249</v>
+      </c>
+      <c r="D299" s="3" t="n">
+        <v>229</v>
+      </c>
       <c r="E299" s="3" t="inlineStr">
         <is>
-          <t>Nick Westbrook-Ikhine</t>
+          <t>Treylon Burks</t>
         </is>
       </c>
       <c r="F299" s="3" t="inlineStr">
         <is>
-          <t>IND (13)</t>
+          <t>WAS (7)</t>
         </is>
       </c>
       <c r="G299" s="3" t="inlineStr">
@@ -9683,24 +9683,24 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>WR133</t>
+          <t>WR132</t>
         </is>
       </c>
       <c r="B300" s="3" t="n">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C300" s="5" t="n">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="D300" s="3" t="inlineStr"/>
       <c r="E300" s="3" t="inlineStr">
         <is>
-          <t>Savion Williams</t>
+          <t>Nick Westbrook-Ikhine</t>
         </is>
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>GB (11)</t>
+          <t>IND (13)</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr">
@@ -9710,147 +9710,176 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="6" t="inlineStr">
-        <is>
-          <t>RB107</t>
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>WR133</t>
         </is>
       </c>
       <c r="B301" s="3" t="n">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="C301" s="5" t="n">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="D301" s="3" t="inlineStr"/>
       <c r="E301" s="3" t="inlineStr">
         <is>
-          <t>Raheim Sanders</t>
+          <t>Savion Williams</t>
         </is>
       </c>
       <c r="F301" s="3" t="inlineStr">
         <is>
-          <t>CLE (11)</t>
+          <t>GB (11)</t>
         </is>
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>WR</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="8" t="inlineStr">
-        <is>
-          <t>TE50</t>
+      <c r="A302" s="6" t="inlineStr">
+        <is>
+          <t>RB107</t>
         </is>
       </c>
       <c r="B302" s="3" t="n">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>302</v>
+        <v>346</v>
       </c>
       <c r="D302" s="3" t="inlineStr"/>
       <c r="E302" s="3" t="inlineStr">
         <is>
-          <t>Eli Raridon</t>
+          <t>Raheim Sanders</t>
         </is>
       </c>
       <c r="F302" s="3" t="inlineStr">
         <is>
-          <t>NE (11)</t>
+          <t>CLE (11)</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>RB</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="inlineStr">
-        <is>
-          <t>WR138</t>
+      <c r="A303" s="8" t="inlineStr">
+        <is>
+          <t>TE50</t>
         </is>
       </c>
       <c r="B303" s="3" t="n">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>360</v>
+        <v>302</v>
       </c>
       <c r="D303" s="3" t="inlineStr"/>
       <c r="E303" s="3" t="inlineStr">
         <is>
-          <t>Zavion Thomas</t>
+          <t>Eli Raridon</t>
         </is>
       </c>
       <c r="F303" s="3" t="inlineStr">
         <is>
-          <t>CHI (10)</t>
+          <t>NE (11)</t>
         </is>
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>TE</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="6" t="inlineStr">
-        <is>
-          <t>RB109</t>
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>WR138</t>
         </is>
       </c>
       <c r="B304" s="3" t="n">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C304" s="5" t="n">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D304" s="3" t="inlineStr"/>
       <c r="E304" s="3" t="inlineStr">
         <is>
+          <t>Zavion Thomas</t>
+        </is>
+      </c>
+      <c r="F304" s="3" t="inlineStr">
+        <is>
+          <t>CHI (10)</t>
+        </is>
+      </c>
+      <c r="G304" s="3" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="6" t="inlineStr">
+        <is>
+          <t>RB109</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="n">
+        <v>386</v>
+      </c>
+      <c r="C305" s="5" t="n">
+        <v>351</v>
+      </c>
+      <c r="D305" s="3" t="inlineStr"/>
+      <c r="E305" s="3" t="inlineStr">
+        <is>
           <t>Phil Mafah</t>
         </is>
       </c>
-      <c r="F304" s="3" t="inlineStr">
+      <c r="F305" s="3" t="inlineStr">
         <is>
           <t>DAL (14)</t>
         </is>
       </c>
-      <c r="G304" s="3" t="inlineStr">
+      <c r="G305" s="3" t="inlineStr">
         <is>
           <t>RB</t>
         </is>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" s="8" t="inlineStr">
+    <row r="306">
+      <c r="A306" s="8" t="inlineStr">
         <is>
           <t>TE52</t>
         </is>
       </c>
-      <c r="B305" s="3" t="n">
+      <c r="B306" s="3" t="n">
         <v>387</v>
       </c>
-      <c r="C305" s="5" t="n">
+      <c r="C306" s="5" t="n">
         <v>267</v>
       </c>
-      <c r="D305" s="3" t="n">
+      <c r="D306" s="3" t="n">
         <v>267</v>
       </c>
-      <c r="E305" s="3" t="inlineStr">
+      <c r="E306" s="3" t="inlineStr">
         <is>
           <t>Erick All</t>
         </is>
       </c>
-      <c r="F305" s="3" t="inlineStr">
+      <c r="F306" s="3" t="inlineStr">
         <is>
           <t>CIN (6)</t>
         </is>
       </c>
-      <c r="G305" s="3" t="inlineStr">
+      <c r="G306" s="3" t="inlineStr">
         <is>
           <t>TE</t>
         </is>

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -6153,7 +6153,7 @@
         <v>197</v>
       </c>
       <c r="C183" s="4" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D183" s="3" t="n">
         <v>280</v>
@@ -6339,7 +6339,7 @@
         <v>206</v>
       </c>
       <c r="C189" s="4" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D189" s="3" t="inlineStr"/>
       <c r="E189" s="3" t="inlineStr">
@@ -6461,7 +6461,7 @@
         <v>213</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D193" s="3" t="n">
         <v>290</v>
@@ -6769,7 +6769,7 @@
         <v>232</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D203" s="3" t="inlineStr"/>
       <c r="E203" s="3" t="inlineStr">
@@ -6798,7 +6798,7 @@
         <v>233</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D204" s="3" t="inlineStr"/>
       <c r="E204" s="3" t="inlineStr">
@@ -6951,7 +6951,7 @@
         <v>239</v>
       </c>
       <c r="C209" s="4" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D209" s="3" t="n">
         <v>268</v>
@@ -7168,7 +7168,7 @@
         <v>246</v>
       </c>
       <c r="C216" s="4" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D216" s="3" t="n">
         <v>294</v>
@@ -7261,7 +7261,7 @@
         <v>250</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D219" s="3" t="inlineStr"/>
       <c r="E219" s="3" t="inlineStr">
@@ -7321,7 +7321,7 @@
         <v>252</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D221" s="3" t="inlineStr"/>
       <c r="E221" s="3" t="inlineStr">
@@ -7501,7 +7501,7 @@
         <v>259</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
@@ -7559,7 +7559,7 @@
         <v>261</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D229" s="3" t="n">
         <v>295</v>
@@ -7745,7 +7745,7 @@
         <v>268</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D235" s="3" t="inlineStr"/>
       <c r="E235" s="3" t="inlineStr">
@@ -7836,7 +7836,7 @@
         <v>271</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D238" s="3" t="inlineStr"/>
       <c r="E238" s="3" t="inlineStr">
@@ -7895,8 +7895,8 @@
       <c r="B240" s="3" t="n">
         <v>273</v>
       </c>
-      <c r="C240" s="5" t="n">
-        <v>307</v>
+      <c r="C240" s="4" t="n">
+        <v>315</v>
       </c>
       <c r="D240" s="3" t="inlineStr"/>
       <c r="E240" s="3" t="inlineStr">
@@ -7987,7 +7987,7 @@
         <v>276</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D243" s="3" t="n">
         <v>263</v>
@@ -8080,7 +8080,7 @@
         <v>280</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D246" s="3" t="inlineStr"/>
       <c r="E246" s="3" t="inlineStr">
@@ -8109,7 +8109,7 @@
         <v>281</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
@@ -8353,7 +8353,7 @@
         <v>292</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D255" s="3" t="inlineStr"/>
       <c r="E255" s="3" t="inlineStr">
@@ -8413,7 +8413,7 @@
         <v>294</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D257" s="3" t="inlineStr"/>
       <c r="E257" s="3" t="inlineStr">
@@ -8442,7 +8442,7 @@
         <v>296</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
@@ -8593,7 +8593,7 @@
         <v>301</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D263" s="3" t="n">
         <v>300</v>
@@ -8686,7 +8686,7 @@
         <v>305</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D266" s="3" t="inlineStr"/>
       <c r="E266" s="3" t="inlineStr">
@@ -8746,7 +8746,7 @@
         <v>309</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D268" s="3" t="inlineStr"/>
       <c r="E268" s="3" t="inlineStr">
@@ -8804,7 +8804,7 @@
         <v>311</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
@@ -8862,7 +8862,7 @@
         <v>314</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
@@ -8922,7 +8922,7 @@
         <v>317</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D274" s="3" t="inlineStr"/>
       <c r="E274" s="3" t="inlineStr">
@@ -8951,7 +8951,7 @@
         <v>321</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="D275" s="3" t="inlineStr"/>
       <c r="E275" s="3" t="inlineStr">
@@ -9011,7 +9011,7 @@
         <v>324</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D277" s="3" t="inlineStr"/>
       <c r="E277" s="3" t="inlineStr">
@@ -9040,7 +9040,7 @@
         <v>326</v>
       </c>
       <c r="C278" s="5" t="n">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="D278" s="3" t="inlineStr"/>
       <c r="E278" s="3" t="inlineStr">
@@ -9338,7 +9338,7 @@
         <v>340</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
@@ -9512,7 +9512,7 @@
         <v>350</v>
       </c>
       <c r="C294" s="5" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D294" s="3" t="inlineStr"/>
       <c r="E294" s="3" t="inlineStr">
@@ -9748,7 +9748,7 @@
         <v>374</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D302" s="3" t="inlineStr"/>
       <c r="E302" s="3" t="inlineStr">
@@ -9777,7 +9777,7 @@
         <v>377</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D303" s="3" t="inlineStr"/>
       <c r="E303" s="3" t="inlineStr">
@@ -9835,7 +9835,7 @@
         <v>386</v>
       </c>
       <c r="C305" s="5" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D305" s="3" t="inlineStr"/>
       <c r="E305" s="3" t="inlineStr">

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -6461,7 +6461,7 @@
         <v>213</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D193" s="3" t="n">
         <v>290</v>
@@ -6647,7 +6647,7 @@
         <v>224</v>
       </c>
       <c r="C199" s="4" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D199" s="3" t="inlineStr"/>
       <c r="E199" s="3" t="inlineStr">
@@ -6769,7 +6769,7 @@
         <v>232</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D203" s="3" t="inlineStr"/>
       <c r="E203" s="3" t="inlineStr">
@@ -6798,7 +6798,7 @@
         <v>233</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D204" s="3" t="inlineStr"/>
       <c r="E204" s="3" t="inlineStr">
@@ -6951,7 +6951,7 @@
         <v>239</v>
       </c>
       <c r="C209" s="4" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D209" s="3" t="n">
         <v>268</v>
@@ -7261,7 +7261,7 @@
         <v>250</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D219" s="3" t="inlineStr"/>
       <c r="E219" s="3" t="inlineStr">
@@ -7321,7 +7321,7 @@
         <v>252</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D221" s="3" t="inlineStr"/>
       <c r="E221" s="3" t="inlineStr">
@@ -7501,7 +7501,7 @@
         <v>259</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
@@ -7530,7 +7530,7 @@
         <v>260</v>
       </c>
       <c r="C228" s="5" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D228" s="3" t="inlineStr"/>
       <c r="E228" s="3" t="inlineStr">
@@ -7652,7 +7652,7 @@
         <v>265</v>
       </c>
       <c r="C232" s="5" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D232" s="3" t="n">
         <v>291</v>
@@ -7745,7 +7745,7 @@
         <v>268</v>
       </c>
       <c r="C235" s="4" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D235" s="3" t="inlineStr"/>
       <c r="E235" s="3" t="inlineStr">
@@ -7836,7 +7836,7 @@
         <v>271</v>
       </c>
       <c r="C238" s="5" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D238" s="3" t="inlineStr"/>
       <c r="E238" s="3" t="inlineStr">
@@ -7896,7 +7896,7 @@
         <v>273</v>
       </c>
       <c r="C240" s="4" t="n">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="D240" s="3" t="inlineStr"/>
       <c r="E240" s="3" t="inlineStr">
@@ -7925,7 +7925,7 @@
         <v>274</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D241" s="3" t="n">
         <v>293</v>
@@ -7987,7 +7987,7 @@
         <v>276</v>
       </c>
       <c r="C243" s="5" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D243" s="3" t="n">
         <v>263</v>
@@ -8080,7 +8080,7 @@
         <v>280</v>
       </c>
       <c r="C246" s="4" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D246" s="3" t="inlineStr"/>
       <c r="E246" s="3" t="inlineStr">
@@ -8109,7 +8109,7 @@
         <v>281</v>
       </c>
       <c r="C247" s="4" t="n">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
@@ -8200,7 +8200,7 @@
         <v>284</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D250" s="3" t="n">
         <v>299</v>
@@ -8353,7 +8353,7 @@
         <v>292</v>
       </c>
       <c r="C255" s="5" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D255" s="3" t="inlineStr"/>
       <c r="E255" s="3" t="inlineStr">
@@ -8413,7 +8413,7 @@
         <v>294</v>
       </c>
       <c r="C257" s="4" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D257" s="3" t="inlineStr"/>
       <c r="E257" s="3" t="inlineStr">
@@ -8442,7 +8442,7 @@
         <v>296</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
@@ -8471,7 +8471,7 @@
         <v>297</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
@@ -8562,7 +8562,7 @@
         <v>300</v>
       </c>
       <c r="C262" s="5" t="n">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D262" s="3" t="n">
         <v>269</v>
@@ -8593,7 +8593,7 @@
         <v>301</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D263" s="3" t="n">
         <v>300</v>
@@ -8746,7 +8746,7 @@
         <v>309</v>
       </c>
       <c r="C268" s="5" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D268" s="3" t="inlineStr"/>
       <c r="E268" s="3" t="inlineStr">
@@ -8775,7 +8775,7 @@
         <v>310</v>
       </c>
       <c r="C269" s="5" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D269" s="3" t="inlineStr"/>
       <c r="E269" s="3" t="inlineStr">
@@ -8804,7 +8804,7 @@
         <v>311</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
@@ -8833,7 +8833,7 @@
         <v>312</v>
       </c>
       <c r="C271" s="5" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D271" s="3" t="inlineStr"/>
       <c r="E271" s="3" t="inlineStr">
@@ -8862,7 +8862,7 @@
         <v>314</v>
       </c>
       <c r="C272" s="5" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D272" s="3" t="inlineStr"/>
       <c r="E272" s="3" t="inlineStr">
@@ -8922,7 +8922,7 @@
         <v>317</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="D274" s="3" t="inlineStr"/>
       <c r="E274" s="3" t="inlineStr">
@@ -8951,7 +8951,7 @@
         <v>321</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D275" s="3" t="inlineStr"/>
       <c r="E275" s="3" t="inlineStr">
@@ -9040,7 +9040,7 @@
         <v>326</v>
       </c>
       <c r="C278" s="5" t="n">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D278" s="3" t="inlineStr"/>
       <c r="E278" s="3" t="inlineStr">
@@ -9160,7 +9160,7 @@
         <v>331</v>
       </c>
       <c r="C282" s="5" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D282" s="3" t="inlineStr"/>
       <c r="E282" s="3" t="inlineStr">
@@ -9278,7 +9278,7 @@
         <v>337</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D286" s="3" t="inlineStr"/>
       <c r="E286" s="3" t="inlineStr">
@@ -9338,7 +9338,7 @@
         <v>340</v>
       </c>
       <c r="C288" s="5" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D288" s="3" t="inlineStr"/>
       <c r="E288" s="3" t="inlineStr">
@@ -9454,7 +9454,7 @@
         <v>348</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
@@ -9570,7 +9570,7 @@
         <v>355</v>
       </c>
       <c r="C296" s="5" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D296" s="3" t="inlineStr"/>
       <c r="E296" s="3" t="inlineStr">
@@ -9630,7 +9630,7 @@
         <v>360</v>
       </c>
       <c r="C298" s="5" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D298" s="3" t="inlineStr"/>
       <c r="E298" s="3" t="inlineStr">
@@ -9835,7 +9835,7 @@
         <v>386</v>
       </c>
       <c r="C305" s="5" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D305" s="3" t="inlineStr"/>
       <c r="E305" s="3" t="inlineStr">

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -5690,7 +5690,7 @@
         <v>174</v>
       </c>
       <c r="C168" s="4" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D168" s="3" t="inlineStr"/>
       <c r="E168" s="3" t="inlineStr">
@@ -6461,7 +6461,7 @@
         <v>213</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D193" s="3" t="n">
         <v>290</v>
@@ -6647,7 +6647,7 @@
         <v>224</v>
       </c>
       <c r="C199" s="4" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D199" s="3" t="inlineStr"/>
       <c r="E199" s="3" t="inlineStr">
@@ -6769,7 +6769,7 @@
         <v>232</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D203" s="3" t="inlineStr"/>
       <c r="E203" s="3" t="inlineStr">
@@ -6798,7 +6798,7 @@
         <v>233</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D204" s="3" t="inlineStr"/>
       <c r="E204" s="3" t="inlineStr">
@@ -7261,7 +7261,7 @@
         <v>250</v>
       </c>
       <c r="C219" s="4" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D219" s="3" t="inlineStr"/>
       <c r="E219" s="3" t="inlineStr">
@@ -7321,7 +7321,7 @@
         <v>252</v>
       </c>
       <c r="C221" s="5" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D221" s="3" t="inlineStr"/>
       <c r="E221" s="3" t="inlineStr">
@@ -7380,8 +7380,8 @@
       <c r="B223" s="3" t="n">
         <v>255</v>
       </c>
-      <c r="C223" s="5" t="n">
-        <v>293</v>
+      <c r="C223" s="4" t="n">
+        <v>303</v>
       </c>
       <c r="D223" s="3" t="inlineStr"/>
       <c r="E223" s="3" t="inlineStr">
@@ -7501,7 +7501,7 @@
         <v>259</v>
       </c>
       <c r="C227" s="4" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D227" s="3" t="inlineStr"/>
       <c r="E227" s="3" t="inlineStr">
@@ -7559,7 +7559,7 @@
         <v>261</v>
       </c>
       <c r="C229" s="4" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D229" s="3" t="n">
         <v>295</v>
@@ -7652,7 +7652,7 @@
         <v>265</v>
       </c>
       <c r="C232" s="5" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D232" s="3" t="n">
         <v>291</v>
@@ -7896,7 +7896,7 @@
         <v>273</v>
       </c>
       <c r="C240" s="4" t="n">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="D240" s="3" t="inlineStr"/>
       <c r="E240" s="3" t="inlineStr">
@@ -7925,7 +7925,7 @@
         <v>274</v>
       </c>
       <c r="C241" s="5" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D241" s="3" t="n">
         <v>293</v>
@@ -8108,8 +8108,8 @@
       <c r="B247" s="3" t="n">
         <v>281</v>
       </c>
-      <c r="C247" s="4" t="n">
-        <v>342</v>
+      <c r="C247" s="5" t="n">
+        <v>322</v>
       </c>
       <c r="D247" s="3" t="inlineStr"/>
       <c r="E247" s="3" t="inlineStr">
@@ -8200,7 +8200,7 @@
         <v>284</v>
       </c>
       <c r="C250" s="5" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D250" s="3" t="n">
         <v>299</v>
@@ -8442,7 +8442,7 @@
         <v>296</v>
       </c>
       <c r="C258" s="5" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D258" s="3" t="inlineStr"/>
       <c r="E258" s="3" t="inlineStr">
@@ -8471,7 +8471,7 @@
         <v>297</v>
       </c>
       <c r="C259" s="5" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D259" s="3" t="inlineStr"/>
       <c r="E259" s="3" t="inlineStr">
@@ -8593,7 +8593,7 @@
         <v>301</v>
       </c>
       <c r="C263" s="5" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D263" s="3" t="n">
         <v>300</v>
@@ -8686,7 +8686,7 @@
         <v>305</v>
       </c>
       <c r="C266" s="5" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D266" s="3" t="inlineStr"/>
       <c r="E266" s="3" t="inlineStr">
@@ -8804,7 +8804,7 @@
         <v>311</v>
       </c>
       <c r="C270" s="5" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D270" s="3" t="inlineStr"/>
       <c r="E270" s="3" t="inlineStr">
@@ -8922,7 +8922,7 @@
         <v>317</v>
       </c>
       <c r="C274" s="5" t="n">
-        <v>335</v>
+        <v>360</v>
       </c>
       <c r="D274" s="3" t="inlineStr"/>
       <c r="E274" s="3" t="inlineStr">
@@ -8951,7 +8951,7 @@
         <v>321</v>
       </c>
       <c r="C275" s="5" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D275" s="3" t="inlineStr"/>
       <c r="E275" s="3" t="inlineStr">
@@ -9011,7 +9011,7 @@
         <v>324</v>
       </c>
       <c r="C277" s="5" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D277" s="3" t="inlineStr"/>
       <c r="E277" s="3" t="inlineStr">
@@ -9100,7 +9100,7 @@
         <v>329</v>
       </c>
       <c r="C280" s="5" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D280" s="3" t="inlineStr"/>
       <c r="E280" s="3" t="inlineStr">
@@ -9160,7 +9160,7 @@
         <v>331</v>
       </c>
       <c r="C282" s="5" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D282" s="3" t="inlineStr"/>
       <c r="E282" s="3" t="inlineStr">
@@ -9249,7 +9249,7 @@
         <v>335</v>
       </c>
       <c r="C285" s="5" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D285" s="3" t="inlineStr"/>
       <c r="E285" s="3" t="inlineStr">
@@ -9278,7 +9278,7 @@
         <v>337</v>
       </c>
       <c r="C286" s="5" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D286" s="3" t="inlineStr"/>
       <c r="E286" s="3" t="inlineStr">
@@ -9367,7 +9367,7 @@
         <v>341</v>
       </c>
       <c r="C289" s="5" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D289" s="3" t="inlineStr"/>
       <c r="E289" s="3" t="inlineStr">
@@ -9454,7 +9454,7 @@
         <v>348</v>
       </c>
       <c r="C292" s="5" t="n">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D292" s="3" t="inlineStr"/>
       <c r="E292" s="3" t="inlineStr">
@@ -9483,7 +9483,7 @@
         <v>349</v>
       </c>
       <c r="C293" s="5" t="n">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D293" s="3" t="inlineStr"/>
       <c r="E293" s="3" t="inlineStr">
@@ -9690,7 +9690,7 @@
         <v>365</v>
       </c>
       <c r="C300" s="5" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D300" s="3" t="inlineStr"/>
       <c r="E300" s="3" t="inlineStr">
@@ -9748,7 +9748,7 @@
         <v>374</v>
       </c>
       <c r="C302" s="5" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D302" s="3" t="inlineStr"/>
       <c r="E302" s="3" t="inlineStr">
@@ -9777,7 +9777,7 @@
         <v>377</v>
       </c>
       <c r="C303" s="5" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D303" s="3" t="inlineStr"/>
       <c r="E303" s="3" t="inlineStr">
@@ -9806,7 +9806,7 @@
         <v>383</v>
       </c>
       <c r="C304" s="5" t="n">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="D304" s="3" t="inlineStr"/>
       <c r="E304" s="3" t="inlineStr">

--- a/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
+++ b/frontend/public/data/2026/fpros/fpros_merged_formatted.xlsx
@@ -578,7 +578,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>10</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>20</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>21</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>24</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>22</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>27</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>11</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>15</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>25</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>13</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>43</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>29</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>30</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>31</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
         <v>28</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>32</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>61</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>69</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>33</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>19</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>26</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>34</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>41</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>53</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>68</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>42</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         <v>47</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>40</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>39</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
         <v>55</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>46</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>51</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
@@ -2159,7 +2159,7 @@
         <v>54</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>72</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>67</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>44</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>57</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>48</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>84</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>60</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>82</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>73</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>102</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>71</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>65</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>56</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>66</v>
       </c>
       <c r="D72" s="3" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>93</v>
       </c>
       <c r="D73" s="3" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>78</v>
       </c>
       <c r="D74" s="3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>87</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>58</v>
       </c>
       <c r="D76" s="3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         <v>115</v>
       </c>
       <c r="D77" s="3" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         <v>79</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>70</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>83</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>88</v>
       </c>
       <c r="D81" s="3" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>63</v>
       </c>
       <c r="D82" s="3" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>81</v>
       </c>
       <c r="D83" s="3" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>91</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>127</v>
       </c>
       <c r="D86" s="3" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
@@ -3182,7 +3182,7 @@
         <v>123</v>
       </c>
       <c r="D87" s="3" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>62</v>
       </c>
       <c r="D89" s="3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>101</v>
       </c>
       <c r="D90" s="3" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>94</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         <v>119</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>45</v>
       </c>
       <c r="D93" s="3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>135</v>
       </c>
       <c r="D94" s="3" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>118</v>
       </c>
       <c r="D95" s="3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>80</v>
       </c>
       <c r="D96" s="3" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>109</v>
       </c>
       <c r="D98" s="3" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>121</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>142</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>114</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         <v>138</v>
       </c>
       <c r="D102" s="3" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>117</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>86</v>
       </c>
       <c r="D104" s="3" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>133</v>
       </c>
       <c r="D105" s="3" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>76</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>90</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>100</v>
       </c>
       <c r="D108" s="3" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>113</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>97</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>85</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>112</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>116</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>89</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>124</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>141</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>108</v>
       </c>
       <c r="D119" s="3" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
@@ -4236,7 +4236,7 @@
         <v>207</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>98</v>
       </c>
       <c r="D122" s="3" t="n">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         <v>92</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>120</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>74</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>99</v>
       </c>
       <c r="D127" s="3" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>274</v>
       </c>
       <c r="D128" s="3" t="n">
-        <v>260</v>
+        <v>286</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>134</v>
       </c>
       <c r="D129" s="3" t="n">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>105</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>75</v>
       </c>
       <c r="D132" s="3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         <v>209</v>
       </c>
       <c r="D133" s="3" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>132</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>183</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>139</v>
       </c>
       <c r="D136" s="3" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>208</v>
       </c>
       <c r="D137" s="3" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>202</v>
       </c>
       <c r="D141" s="3" t="n">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>252</v>
       </c>
       <c r="D142" s="3" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>225</v>
       </c>
       <c r="D143" s="3" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>242</v>
       </c>
       <c r="D144" s="3" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>125</v>
       </c>
       <c r="D145" s="3" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         <v>176</v>
       </c>
       <c r="D146" s="3" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>179</v>
       </c>
       <c r="D147" s="3" t="n">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>136</v>
       </c>
       <c r="D148" s="3" t="n">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>221</v>
       </c>
       <c r="D149" s="3" t="n">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>210</v>
       </c>
       <c r="D150" s="3" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>218</v>
       </c>
       <c r="D151" s="3" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>223</v>
       </c>
       <c r="D152" s="3" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>175</v>
       </c>
       <c r="D153" s="3" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>268</v>
       </c>
       <c r="D154" s="3" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>188</v>
       </c>
       <c r="D155" s="3" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>200</v>
       </c>
       <c r="D156" s="3" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>111</v>
       </c>
       <c r="D157" s="3" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         <v>178</v>
       </c>
       <c r="D158" s="3" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>166</v>
       </c>
       <c r="D159" s="3" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>151</v>
       </c>
       <c r="D160" s="3" t="n">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>199</v>
       </c>
       <c r="D161" s="3" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>161</v>
       </c>
       <c r="D162" s="3" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>153</v>
       </c>
       <c r="D163" s="3" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>137</v>
       </c>
       <c r="D164" s="3" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
         <v>201</v>
       </c>
       <c r="D165" s="3" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>182</v>
       </c>
       <c r="D166" s="3" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>214</v>
       </c>
       <c r="D167" s="3" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>167</v>
       </c>
       <c r="D169" s="3" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>181</v>
       </c>
       <c r="D170" s="3" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         <v>277</v>
       </c>
       <c r="D172" s="3" t="n">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>244</v>
       </c>
       <c r="D173" s="3" t="n">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>250</v>
       </c>
       <c r="D174" s="3" t="n">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>298</v>
       </c>
       <c r="D175" s="3" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>246</v>
       </c>
       <c r="D176" s="3" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>286</v>
       </c>
       <c r="D177" s="3" t="n">
-        <v>259</v>
+        <v>243</v>
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>187</v>
       </c>
       <c r="D178" s="3" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>184</v>
       </c>
       <c r="D179" s="3" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>276</v>
       </c>
       <c r="D180" s="3" t="n">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>162</v>
       </c>
       <c r="D181" s="3" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>177</v>
       </c>
       <c r="D182" s="3" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>260</v>
       </c>
       <c r="D183" s="3" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>204</v>
       </c>
       <c r="D184" s="3" t="n">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>180</v>
       </c>
       <c r="D185" s="3" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         <v>272</v>
       </c>
       <c r="D186" s="3" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>140</v>
       </c>
       <c r="D187" s="3" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>169</v>
       </c>
       <c r="D188" s="3" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>281</v>
       </c>
       <c r="D190" s="3" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
@@ -6402,7 +6402,7 @@
         <v>168</v>
       </c>
       <c r="D191" s="3" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
@@ -6433,7 +6433,7 @@
         <v>251</v>
       </c>
       <c r="D192" s="3" t="n">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
@@ -6461,10 +6461,10 @@
         <v>213</v>
       </c>
       <c r="C193" s="5" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D193" s="3" t="n">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
@@ -6494,9 +6494,7 @@
       <c r="C194" s="4" t="n">
         <v>288</v>
       </c>
-      <c r="D194" s="3" t="n">
-        <v>279</v>
-      </c>
+      <c r="D194" s="3" t="inlineStr"/>
       <c r="E194" s="3" t="inlineStr">
         <is>
           <t>Tank Dell</t>
@@ -6526,7 +6524,7 @@
         <v>243</v>
       </c>
       <c r="D195" s="3" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
@@ -6557,7 +6555,7 @@
         <v>248</v>
       </c>
       <c r="D196" s="3" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
@@ -6588,7 +6586,7 @@
         <v>273</v>
       </c>
       <c r="D197" s="3" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
@@ -6619,7 +6617,7 @@
         <v>219</v>
       </c>
       <c r="D198" s="3" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
@@ -6647,7 +6645,7 @@
         <v>224</v>
       </c>
       <c r="C199" s="4" t="n">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="D199" s="3" t="inlineStr"/>
       <c r="E199" s="3" t="inlineStr">
@@ -6710,7 +6708,7 @@
         <v>224</v>
       </c>
       <c r="D201" s="3" t="n">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
@@ -6741,7 +6739,7 @@
         <v>247</v>
       </c>
       <c r="D202" s="3" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
@@ -6769,7 +6767,7 @@
         <v>232</v>
       </c>
       <c r="C203" s="4" t="n">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="D203" s="3" t="inlineStr"/>
       <c r="E203" s="3" t="inlineStr">
@@ -6798,9 +6796,11 @@
         <v>233</v>
       </c>
       <c r="C204" s="5" t="n">
-        <v>224</v>
-      </c>
-      <c r="D204" s="3" t="inlineStr"/>
+        <v>228</v>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>264</v>
+      </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
           <t>Jaylen Wright</t>
@@ -6830,7 +6830,7 @@
         <v>211</v>
       </c>
       <c r="D205" s="3" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>216</v>
       </c>
       <c r="D206" s="3" t="n">
-        <v>240</v>
+        <v>202</v>
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>271</v>
       </c>
       <c r="D207" s="3" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>217</v>
       </c>
       <c r="D208" s="3" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
@@ -6951,10 +6951,10 @@
         <v>239</v>
       </c>
       <c r="C209" s="4" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D209" s="3" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>253</v>
       </c>
       <c r="D210" s="3" t="n">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>295</v>
       </c>
       <c r="D211" s="3" t="n">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>296</v